--- a/data/TNXT.MI.xlsx
+++ b/data/TNXT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="1774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="1775">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">TNXT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6515097618103</t>
+    <t xml:space="preserve">2.65151000022888</t>
   </si>
   <si>
     <t xml:space="preserve">2.59350872039795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53550672531128</t>
+    <t xml:space="preserve">2.5355064868927</t>
   </si>
   <si>
     <t xml:space="preserve">2.52556324005127</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">2.52722072601318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48744773864746</t>
+    <t xml:space="preserve">2.48744797706604</t>
   </si>
   <si>
     <t xml:space="preserve">2.47087597846985</t>
@@ -71,22 +71,22 @@
     <t xml:space="preserve">2.46921873092651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54047799110413</t>
+    <t xml:space="preserve">2.54047822952271</t>
   </si>
   <si>
     <t xml:space="preserve">2.49739122390747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4791624546051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44436073303223</t>
+    <t xml:space="preserve">2.47916197776794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44436097145081</t>
   </si>
   <si>
     <t xml:space="preserve">2.39464473724365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34161448478699</t>
+    <t xml:space="preserve">2.34161496162415</t>
   </si>
   <si>
     <t xml:space="preserve">2.36150097846985</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">2.55207872390747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58522272109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61007976531982</t>
+    <t xml:space="preserve">2.58522248268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6100800037384</t>
   </si>
   <si>
     <t xml:space="preserve">2.56865048408508</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">2.72608327865601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77579951286316</t>
+    <t xml:space="preserve">2.77579975128174</t>
   </si>
   <si>
     <t xml:space="preserve">2.58025121688843</t>
@@ -134,88 +134,88 @@
     <t xml:space="preserve">2.64322352409363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60842251777649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66642451286316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65316700935364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62665152549744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69293975830078</t>
+    <t xml:space="preserve">2.60842275619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.666424036026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65316724777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62665200233459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6929395198822</t>
   </si>
   <si>
     <t xml:space="preserve">2.82551550865173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81722927093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90008902549744</t>
+    <t xml:space="preserve">2.81722950935364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90008950233459</t>
   </si>
   <si>
     <t xml:space="preserve">2.85865950584412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89843225479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8835175037384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87523126602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86694550514221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81888675689697</t>
+    <t xml:space="preserve">2.89843249320984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88351702690125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87523174285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86694526672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81888699531555</t>
   </si>
   <si>
     <t xml:space="preserve">2.82054400444031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85368800163269</t>
+    <t xml:space="preserve">2.85368776321411</t>
   </si>
   <si>
     <t xml:space="preserve">2.79237151145935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8570020198822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90671825408936</t>
+    <t xml:space="preserve">2.85700249671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90671801567078</t>
   </si>
   <si>
     <t xml:space="preserve">2.82882952690125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8503737449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90837526321411</t>
+    <t xml:space="preserve">2.85037350654602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90837502479553</t>
   </si>
   <si>
     <t xml:space="preserve">2.96306276321411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95797753334045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8816967010498</t>
+    <t xml:space="preserve">2.9579770565033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88169693946838</t>
   </si>
   <si>
     <t xml:space="preserve">2.89017271995544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86474585533142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94950199127197</t>
+    <t xml:space="preserve">2.86474561691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94950175285339</t>
   </si>
   <si>
     <t xml:space="preserve">2.92407512664795</t>
@@ -227,67 +227,67 @@
     <t xml:space="preserve">3.11901330947876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9427216053009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94780707359314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88339257240295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87322187423706</t>
+    <t xml:space="preserve">2.94272112846375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94780659675598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8833920955658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87322163581848</t>
   </si>
   <si>
     <t xml:space="preserve">2.85966086387634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03256273269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07037377357483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06866312026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06011033058167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99340033531189</t>
+    <t xml:space="preserve">3.03256297111511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07037329673767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06866335868835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06011056900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99340081214905</t>
   </si>
   <si>
     <t xml:space="preserve">2.98484778404236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93524312973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98313760757446</t>
+    <t xml:space="preserve">2.93524241447449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98313736915588</t>
   </si>
   <si>
     <t xml:space="preserve">2.92497992515564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92326974868774</t>
+    <t xml:space="preserve">2.92326927185059</t>
   </si>
   <si>
     <t xml:space="preserve">2.9677426815033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03616309165955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05839991569519</t>
+    <t xml:space="preserve">3.03616333007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05840039253235</t>
   </si>
   <si>
     <t xml:space="preserve">3.05497908592224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08747887611389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13879442214966</t>
+    <t xml:space="preserve">3.08747863769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13879418373108</t>
   </si>
   <si>
     <t xml:space="preserve">3.12853121757507</t>
@@ -302,331 +302,331 @@
     <t xml:space="preserve">3.12339949607849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12511038780212</t>
+    <t xml:space="preserve">3.12511014938354</t>
   </si>
   <si>
     <t xml:space="preserve">3.14734697341919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16445231437683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16616249084473</t>
+    <t xml:space="preserve">3.16445207595825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16616272926331</t>
   </si>
   <si>
     <t xml:space="preserve">3.24142503738403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30129289627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38681888580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48431801795959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52708125114441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62629079818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63655376434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64510726928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74602699279785</t>
+    <t xml:space="preserve">3.30129313468933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3868191242218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48431777954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52708053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62629103660583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63655400276184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64510607719421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74602723121643</t>
   </si>
   <si>
     <t xml:space="preserve">3.67760610580444</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71181726455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63484382629395</t>
+    <t xml:space="preserve">3.71181702613831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63484311103821</t>
   </si>
   <si>
     <t xml:space="preserve">3.51681780815125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50484418869019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49458122253418</t>
+    <t xml:space="preserve">3.50484490394592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4945809841156</t>
   </si>
   <si>
     <t xml:space="preserve">3.50655484199524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48089718818665</t>
+    <t xml:space="preserve">3.48089694976807</t>
   </si>
   <si>
     <t xml:space="preserve">3.43129229545593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35602974891663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60063290596008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64681720733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69471168518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69984316825867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67589545249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6656322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59721183776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63313364982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57497525215149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6605007648468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68615889549255</t>
+    <t xml:space="preserve">3.35602951049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60063338279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64681649208069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69471216201782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69984340667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67589592933655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66563248634338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59721207618713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63313245773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57497572898865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66050124168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68615865707397</t>
   </si>
   <si>
     <t xml:space="preserve">3.7152373790741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73747396469116</t>
+    <t xml:space="preserve">3.73747444152832</t>
   </si>
   <si>
     <t xml:space="preserve">3.71010613441467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69129061698914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68957996368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73234224319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72036933898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76313209533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77168464660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62115979194641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64168572425842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70326399803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79734253883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75457906723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90852570533752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76655268669128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72892189025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66734313964844</t>
+    <t xml:space="preserve">3.69129014015198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68958020210266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73234272003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72036862373352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76313233375549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77168416976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62115955352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64168500900269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70326447486877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79734230041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75458002090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90852546691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76655292510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72892141342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6673436164856</t>
   </si>
   <si>
     <t xml:space="preserve">3.50997591018677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49800276756287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48944973945618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47234463691711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40392374992371</t>
+    <t xml:space="preserve">3.49800229072571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4894495010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47234487533569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40392398834229</t>
   </si>
   <si>
     <t xml:space="preserve">3.43642401695251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53221273422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5185284614563</t>
+    <t xml:space="preserve">3.53221297264099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51852893829346</t>
   </si>
   <si>
     <t xml:space="preserve">3.46037101745605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50142335891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53563380241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55615973472595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6433961391449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72550082206726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84865808486938</t>
+    <t xml:space="preserve">3.50142312049866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53563356399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55615997314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64339661598206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7255003452301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84865784645081</t>
   </si>
   <si>
     <t xml:space="preserve">3.82984209060669</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8315532207489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87089490890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84523701667786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87431597709656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86405277252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85721111297607</t>
+    <t xml:space="preserve">3.83155226707458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87089419364929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84523630142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87431621551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86405253410339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8572096824646</t>
   </si>
   <si>
     <t xml:space="preserve">3.82471084594727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90681457519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00260400772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17536592483521</t>
+    <t xml:space="preserve">3.90681505203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00260448455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17536640167236</t>
   </si>
   <si>
     <t xml:space="preserve">4.11378765106201</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00773572921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05220937728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08128786087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00602579116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09839296340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01970958709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01115655899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99576187133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03510427474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06247186660767</t>
+    <t xml:space="preserve">4.00773477554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05220890045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08128833770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0060248374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09839200973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01970863342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01115703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99576163291931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0351037979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06247234344482</t>
   </si>
   <si>
     <t xml:space="preserve">4.13773488998413</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12233972549438</t>
+    <t xml:space="preserve">4.12234020233154</t>
   </si>
   <si>
     <t xml:space="preserve">4.14799737930298</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18905067443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25918197631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22839260101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20615530014038</t>
+    <t xml:space="preserve">4.18905019760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2591814994812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22839117050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20615577697754</t>
   </si>
   <si>
     <t xml:space="preserve">4.02142000198364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99405169487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01799917221069</t>
+    <t xml:space="preserve">3.99405121803284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01799869537354</t>
   </si>
   <si>
     <t xml:space="preserve">4.02655172348022</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07615613937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12747192382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11891841888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10523509979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09668254852295</t>
+    <t xml:space="preserve">4.07615661621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12747240066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11891984939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1052360534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09668207168579</t>
   </si>
   <si>
     <t xml:space="preserve">4.10181379318237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07102489471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09497165679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13089227676392</t>
+    <t xml:space="preserve">4.0710244178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09497213363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13089275360107</t>
   </si>
   <si>
     <t xml:space="preserve">4.21641874313354</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">4.52431106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54996967315674</t>
+    <t xml:space="preserve">4.54996871948242</t>
   </si>
   <si>
     <t xml:space="preserve">4.53713989257812</t>
@@ -644,22 +644,22 @@
     <t xml:space="preserve">4.46444272994995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50293064117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56707525253296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62266540527344</t>
+    <t xml:space="preserve">4.50292921066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56707429885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6226658821106</t>
   </si>
   <si>
     <t xml:space="preserve">4.63549470901489</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58417940139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60128450393677</t>
+    <t xml:space="preserve">4.58417987823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60128402709961</t>
   </si>
   <si>
     <t xml:space="preserve">4.57562637329102</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">4.61838960647583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53286361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55852127075195</t>
+    <t xml:space="preserve">4.53286409378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55852174758911</t>
   </si>
   <si>
     <t xml:space="preserve">4.48154783248901</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">4.5157585144043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49010133743286</t>
+    <t xml:space="preserve">4.4901008605957</t>
   </si>
   <si>
     <t xml:space="preserve">4.51148223876953</t>
@@ -695,19 +695,19 @@
     <t xml:space="preserve">4.7595067024231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78944110870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73384952545166</t>
+    <t xml:space="preserve">4.78944063186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7338490486145</t>
   </si>
   <si>
     <t xml:space="preserve">4.77233600616455</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76378297805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65687608718872</t>
+    <t xml:space="preserve">4.76378345489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65687561035156</t>
   </si>
   <si>
     <t xml:space="preserve">4.69536256790161</t>
@@ -716,16 +716,16 @@
     <t xml:space="preserve">4.8279275894165</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90062427520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91772890090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94338750839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98614978790283</t>
+    <t xml:space="preserve">4.90062379837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91772937774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94338703155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98615026473999</t>
   </si>
   <si>
     <t xml:space="preserve">5.04174184799194</t>
@@ -737,40 +737,40 @@
     <t xml:space="preserve">5.0716757774353</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08022832870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99470281600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09305667877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06050682067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91728448867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94766569137573</t>
+    <t xml:space="preserve">5.08022880554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99470329284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09305715560913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06050634384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91728496551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94766521453857</t>
   </si>
   <si>
     <t xml:space="preserve">4.92596530914307</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90426445007324</t>
+    <t xml:space="preserve">4.9042649269104</t>
   </si>
   <si>
     <t xml:space="preserve">4.82180404663086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73500299453735</t>
+    <t xml:space="preserve">4.7350025177002</t>
   </si>
   <si>
     <t xml:space="preserve">4.72198247909546</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59178066253662</t>
+    <t xml:space="preserve">4.59178018569946</t>
   </si>
   <si>
     <t xml:space="preserve">4.64386129379272</t>
@@ -779,25 +779,25 @@
     <t xml:space="preserve">4.73066186904907</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66556119918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65254163742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60914134979248</t>
+    <t xml:space="preserve">4.66556215286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6525411605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60914039611816</t>
   </si>
   <si>
     <t xml:space="preserve">4.65688133239746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54837989807129</t>
+    <t xml:space="preserve">4.54837942123413</t>
   </si>
   <si>
     <t xml:space="preserve">4.53536033630371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47025966644287</t>
+    <t xml:space="preserve">4.47025918960571</t>
   </si>
   <si>
     <t xml:space="preserve">4.59612131118774</t>
@@ -806,16 +806,16 @@
     <t xml:space="preserve">4.47459888458252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48761940002441</t>
+    <t xml:space="preserve">4.48761892318726</t>
   </si>
   <si>
     <t xml:space="preserve">4.46157836914062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4138388633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38779783248901</t>
+    <t xml:space="preserve">4.41383838653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38779735565186</t>
   </si>
   <si>
     <t xml:space="preserve">4.39213800430298</t>
@@ -824,52 +824,52 @@
     <t xml:space="preserve">4.40949821472168</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55706071853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52233982086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57008123397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53970003128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47893905639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43553876876831</t>
+    <t xml:space="preserve">4.55706024169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52234029769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57008028030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53969955444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47893857955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43553829193115</t>
   </si>
   <si>
     <t xml:space="preserve">4.42251825332642</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4311990737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45289945602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51365900039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68726205825806</t>
+    <t xml:space="preserve">4.43119859695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45289850234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51365852355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68726110458374</t>
   </si>
   <si>
     <t xml:space="preserve">4.60046052932739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6395206451416</t>
+    <t xml:space="preserve">4.63952112197876</t>
   </si>
   <si>
     <t xml:space="preserve">4.56139993667603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58744049072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61782169342041</t>
+    <t xml:space="preserve">4.5874400138855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61782121658325</t>
   </si>
   <si>
     <t xml:space="preserve">4.64820146560669</t>
@@ -881,19 +881,19 @@
     <t xml:space="preserve">4.58310079574585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49629878997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50497961044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42685890197754</t>
+    <t xml:space="preserve">4.49629974365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50497913360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42685842514038</t>
   </si>
   <si>
     <t xml:space="preserve">4.49195957183838</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51800060272217</t>
+    <t xml:space="preserve">4.51800012588501</t>
   </si>
   <si>
     <t xml:space="preserve">4.80878353118896</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">4.77840328216553</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84784364700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83482360839844</t>
+    <t xml:space="preserve">4.84784412384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8348240852356</t>
   </si>
   <si>
     <t xml:space="preserve">4.74368286132812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81312322616577</t>
+    <t xml:space="preserve">4.81312417984009</t>
   </si>
   <si>
     <t xml:space="preserve">4.71330213546753</t>
@@ -923,13 +923,13 @@
     <t xml:space="preserve">4.72632265090942</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69594240188599</t>
+    <t xml:space="preserve">4.69594192504883</t>
   </si>
   <si>
     <t xml:space="preserve">4.76972246170044</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84350442886353</t>
+    <t xml:space="preserve">4.84350347518921</t>
   </si>
   <si>
     <t xml:space="preserve">4.87822389602661</t>
@@ -944,19 +944,19 @@
     <t xml:space="preserve">4.97804546356201</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00842666625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07786703109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04314613342285</t>
+    <t xml:space="preserve">5.00842618942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07786655426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04314661026001</t>
   </si>
   <si>
     <t xml:space="preserve">5.14730787277222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86086463928223</t>
+    <t xml:space="preserve">4.86086416244507</t>
   </si>
   <si>
     <t xml:space="preserve">4.869544506073</t>
@@ -965,22 +965,22 @@
     <t xml:space="preserve">4.96502542495728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90860605239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99974679946899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99106550216675</t>
+    <t xml:space="preserve">4.90860557556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99974632263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99106597900391</t>
   </si>
   <si>
     <t xml:space="preserve">5.15598821640015</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12994766235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2948694229126</t>
+    <t xml:space="preserve">5.12994718551636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29486989974976</t>
   </si>
   <si>
     <t xml:space="preserve">5.41639137268066</t>
@@ -995,25 +995,25 @@
     <t xml:space="preserve">5.48149251937866</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42073202133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.394690990448</t>
+    <t xml:space="preserve">5.42073106765747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39469146728516</t>
   </si>
   <si>
     <t xml:space="preserve">5.35563087463379</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33393001556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37299108505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3382716178894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20806837081909</t>
+    <t xml:space="preserve">5.33393049240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37299060821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33827066421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20806884765625</t>
   </si>
   <si>
     <t xml:space="preserve">5.16466808319092</t>
@@ -1022,73 +1022,73 @@
     <t xml:space="preserve">5.26449012756348</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25146961212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26014947891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18636798858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20372819900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19504880905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16900777816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18202877044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19938850402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22542905807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42507171630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61603403091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7288761138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7115159034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78963613510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82435703277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8764386177063</t>
+    <t xml:space="preserve">5.25147008895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2601490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1863694190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20372867584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19504928588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16900825500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18202781677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19938802719116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22542953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42507219314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61603450775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72887563705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71151542663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78963661193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82435750961304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87643814086914</t>
   </si>
   <si>
     <t xml:space="preserve">5.88511800765991</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93719863891602</t>
+    <t xml:space="preserve">5.93719911575317</t>
   </si>
   <si>
     <t xml:space="preserve">5.85907745361328</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80699634552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92851877212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9719181060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95455884933472</t>
+    <t xml:space="preserve">5.80699682235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92851781845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97191953659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95455932617188</t>
   </si>
   <si>
     <t xml:space="preserve">6.03268003463745</t>
@@ -1097,25 +1097,25 @@
     <t xml:space="preserve">6.1715612411499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2844033241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01531934738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02399921417236</t>
+    <t xml:space="preserve">6.28440284729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01531982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02399969100952</t>
   </si>
   <si>
     <t xml:space="preserve">6.21496152877808</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14552116394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40592479705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07607984542847</t>
+    <t xml:space="preserve">6.14552164077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40592527389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07608032226562</t>
   </si>
   <si>
     <t xml:space="preserve">5.98927879333496</t>
@@ -1124,19 +1124,19 @@
     <t xml:space="preserve">6.04135990142822</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22364139556885</t>
+    <t xml:space="preserve">6.22364187240601</t>
   </si>
   <si>
     <t xml:space="preserve">6.13684129714966</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19760131835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1542010307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05003976821899</t>
+    <t xml:space="preserve">6.19760179519653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15420150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05004024505615</t>
   </si>
   <si>
     <t xml:space="preserve">5.89379787445068</t>
@@ -1148,31 +1148,31 @@
     <t xml:space="preserve">5.70283555984497</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50319290161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58131265640259</t>
+    <t xml:space="preserve">5.50319337844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5813136100769</t>
   </si>
   <si>
     <t xml:space="preserve">5.72019577026367</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76359605789185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91983795166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99795866012573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83303642272949</t>
+    <t xml:space="preserve">5.763596534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91983842849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99795913696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83303737640381</t>
   </si>
   <si>
     <t xml:space="preserve">5.79831647872925</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65943431854248</t>
+    <t xml:space="preserve">5.65943479537964</t>
   </si>
   <si>
     <t xml:space="preserve">5.5118727684021</t>
@@ -1181,7 +1181,7 @@
     <t xml:space="preserve">5.5465931892395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58999443054199</t>
+    <t xml:space="preserve">5.58999395370483</t>
   </si>
   <si>
     <t xml:space="preserve">5.52055311203003</t>
@@ -1193,16 +1193,16 @@
     <t xml:space="preserve">5.44243192672729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46847248077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67679500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6420750617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55527353286743</t>
+    <t xml:space="preserve">5.46847200393677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6767954826355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64207458496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55527305603027</t>
   </si>
   <si>
     <t xml:space="preserve">5.53791379928589</t>
@@ -1223,28 +1223,28 @@
     <t xml:space="preserve">5.45111227035522</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09344053268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81567621231079</t>
+    <t xml:space="preserve">6.09344100952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81567716598511</t>
   </si>
   <si>
     <t xml:space="preserve">5.77227640151978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73755550384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40771198272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24278879165649</t>
+    <t xml:space="preserve">5.73755598068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40771102905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24278926849365</t>
   </si>
   <si>
     <t xml:space="preserve">5.06918716430664</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98238563537598</t>
+    <t xml:space="preserve">4.98238515853882</t>
   </si>
   <si>
     <t xml:space="preserve">5.07618856430054</t>
@@ -1256,13 +1256,13 @@
     <t xml:space="preserve">5.08507776260376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24509763717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11174774169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13841724395752</t>
+    <t xml:space="preserve">5.24509811401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11174821853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13841772079468</t>
   </si>
   <si>
     <t xml:space="preserve">5.20953798294067</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">5.04062843322754</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04951810836792</t>
+    <t xml:space="preserve">5.04951763153076</t>
   </si>
   <si>
     <t xml:space="preserve">4.94283771514893</t>
@@ -1289,10 +1289,10 @@
     <t xml:space="preserve">4.90727806091309</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76503753662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92505788803101</t>
+    <t xml:space="preserve">4.76503849029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92505836486816</t>
   </si>
   <si>
     <t xml:space="preserve">4.88949823379517</t>
@@ -1310,25 +1310,25 @@
     <t xml:space="preserve">4.95172786712646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9339485168457</t>
+    <t xml:space="preserve">4.93394804000854</t>
   </si>
   <si>
     <t xml:space="preserve">4.89838790893555</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80948829650879</t>
+    <t xml:space="preserve">4.80948781967163</t>
   </si>
   <si>
     <t xml:space="preserve">4.78281784057617</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75614786148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98728847503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10285758972168</t>
+    <t xml:space="preserve">4.75614833831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98728799819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10285711288452</t>
   </si>
   <si>
     <t xml:space="preserve">4.960618019104</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">5.2184271812439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27176713943481</t>
+    <t xml:space="preserve">5.27176761627197</t>
   </si>
   <si>
     <t xml:space="preserve">5.33399820327759</t>
@@ -1352,22 +1352,22 @@
     <t xml:space="preserve">5.18286752700806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01395845413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99617862701416</t>
+    <t xml:space="preserve">5.01395797729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99617767333984</t>
   </si>
   <si>
     <t xml:space="preserve">5.00506782531738</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37844800949097</t>
+    <t xml:space="preserve">5.37844848632812</t>
   </si>
   <si>
     <t xml:space="preserve">5.47623729705811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56513786315918</t>
+    <t xml:space="preserve">5.56513833999634</t>
   </si>
   <si>
     <t xml:space="preserve">5.6807074546814</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">5.6540379524231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63625717163086</t>
+    <t xml:space="preserve">5.63625812530518</t>
   </si>
   <si>
     <t xml:space="preserve">5.55624771118164</t>
@@ -1385,13 +1385,13 @@
     <t xml:space="preserve">5.68959760665894</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96518802642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89406824111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77849769592285</t>
+    <t xml:space="preserve">5.96518754959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89406776428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77849721908569</t>
   </si>
   <si>
     <t xml:space="preserve">5.84072780609131</t>
@@ -1400,22 +1400,22 @@
     <t xml:space="preserve">5.76071739196777</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92073774337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83183765411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44956827163696</t>
+    <t xml:space="preserve">5.92073726654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83183670043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4495677947998</t>
   </si>
   <si>
     <t xml:space="preserve">5.5829176902771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43178796768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36955785751343</t>
+    <t xml:space="preserve">5.43178844451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36955738067627</t>
   </si>
   <si>
     <t xml:space="preserve">5.6095871925354</t>
@@ -1445,19 +1445,19 @@
     <t xml:space="preserve">5.71626758575439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73404788970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81405782699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67181777954102</t>
+    <t xml:space="preserve">5.73404741287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81405735015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67181825637817</t>
   </si>
   <si>
     <t xml:space="preserve">5.5117974281311</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85850763320923</t>
+    <t xml:space="preserve">5.85850811004639</t>
   </si>
   <si>
     <t xml:space="preserve">5.66292715072632</t>
@@ -1469,22 +1469,22 @@
     <t xml:space="preserve">5.90295791625977</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79627704620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80516815185547</t>
+    <t xml:space="preserve">5.79627799987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80516767501831</t>
   </si>
   <si>
     <t xml:space="preserve">5.6184778213501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46734809875488</t>
+    <t xml:space="preserve">5.46734762191772</t>
   </si>
   <si>
     <t xml:space="preserve">5.60069799423218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45845699310303</t>
+    <t xml:space="preserve">5.45845746994019</t>
   </si>
   <si>
     <t xml:space="preserve">5.50290775299072</t>
@@ -1493,10 +1493,10 @@
     <t xml:space="preserve">5.34288787841797</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62736749649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52957820892334</t>
+    <t xml:space="preserve">5.62736701965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52957725524902</t>
   </si>
   <si>
     <t xml:space="preserve">5.42289733886719</t>
@@ -1511,28 +1511,28 @@
     <t xml:space="preserve">5.69848775863647</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00074672698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92962789535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94740772247314</t>
+    <t xml:space="preserve">6.00074768066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92962741851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94740724563599</t>
   </si>
   <si>
     <t xml:space="preserve">5.93851757049561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99185800552368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24077796936035</t>
+    <t xml:space="preserve">5.99185657501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24077749252319</t>
   </si>
   <si>
     <t xml:space="preserve">6.40968751907349</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48080730438232</t>
+    <t xml:space="preserve">6.48080778121948</t>
   </si>
   <si>
     <t xml:space="preserve">6.62304735183716</t>
@@ -1541,7 +1541,7 @@
     <t xml:space="preserve">6.84529733657837</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99642705917358</t>
+    <t xml:space="preserve">6.99642658233643</t>
   </si>
   <si>
     <t xml:space="preserve">7.0142068862915</t>
@@ -1550,37 +1550,37 @@
     <t xml:space="preserve">6.90752696990967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91641712188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97864675521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00531721115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0230975151062</t>
+    <t xml:space="preserve">6.91641759872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97864627838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00531768798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02309703826904</t>
   </si>
   <si>
     <t xml:space="preserve">7.2453465461731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27201747894287</t>
+    <t xml:space="preserve">7.27201700210571</t>
   </si>
   <si>
     <t xml:space="preserve">7.33424711227417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47648668289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76985597610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7342963218689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72540616989136</t>
+    <t xml:space="preserve">7.47648763656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76985740661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73429584503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72540760040283</t>
   </si>
   <si>
     <t xml:space="preserve">7.79652690887451</t>
@@ -1598,28 +1598,28 @@
     <t xml:space="preserve">8.15212631225586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12545680999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00099563598633</t>
+    <t xml:space="preserve">8.12545776367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00099754333496</t>
   </si>
   <si>
     <t xml:space="preserve">8.17879676818848</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34770679473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42771625518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48105430603027</t>
+    <t xml:space="preserve">8.34770584106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42771530151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48105621337891</t>
   </si>
   <si>
     <t xml:space="preserve">8.46327686309814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52550601959229</t>
+    <t xml:space="preserve">8.5255069732666</t>
   </si>
   <si>
     <t xml:space="preserve">8.50772571563721</t>
@@ -1628,25 +1628,25 @@
     <t xml:space="preserve">8.66774654388428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8010950088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88999652862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19225692749023</t>
+    <t xml:space="preserve">8.80109596252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8899974822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19225597381592</t>
   </si>
   <si>
     <t xml:space="preserve">9.37005615234375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47673511505127</t>
+    <t xml:space="preserve">9.47673606872559</t>
   </si>
   <si>
     <t xml:space="preserve">9.49451637268066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31671619415283</t>
+    <t xml:space="preserve">9.31671524047852</t>
   </si>
   <si>
     <t xml:space="preserve">9.15669536590576</t>
@@ -1655,13 +1655,13 @@
     <t xml:space="preserve">9.35227680206299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40561580657959</t>
+    <t xml:space="preserve">9.40561676025391</t>
   </si>
   <si>
     <t xml:space="preserve">9.69009494781494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86789703369141</t>
+    <t xml:space="preserve">9.86789608001709</t>
   </si>
   <si>
     <t xml:space="preserve">9.83233642578125</t>
@@ -1673,28 +1673,28 @@
     <t xml:space="preserve">9.44117641448975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21003532409668</t>
+    <t xml:space="preserve">9.21003723144531</t>
   </si>
   <si>
     <t xml:space="preserve">9.58341598510742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51229572296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6723165512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85011577606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0990362167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0279169082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99235725402832</t>
+    <t xml:space="preserve">9.51229667663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67231559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85011672973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0990352630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0279159545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99235534667969</t>
   </si>
   <si>
     <t xml:space="preserve">10.0101356506348</t>
@@ -1706,7 +1706,7 @@
     <t xml:space="preserve">9.88567543029785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2234954833984</t>
+    <t xml:space="preserve">10.2234964370728</t>
   </si>
   <si>
     <t xml:space="preserve">10.4368543624878</t>
@@ -1730,16 +1730,16 @@
     <t xml:space="preserve">11.6814556121826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8948154449463</t>
+    <t xml:space="preserve">11.894814491272</t>
   </si>
   <si>
     <t xml:space="preserve">11.965934753418</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1437358856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6281156539917</t>
+    <t xml:space="preserve">12.1437349319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6281147003174</t>
   </si>
   <si>
     <t xml:space="preserve">11.4001131057739</t>
@@ -1751,16 +1751,16 @@
     <t xml:space="preserve">11.6534490585327</t>
   </si>
   <si>
-    <t xml:space="preserve">11.689640045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.123929977417</t>
+    <t xml:space="preserve">11.6896409988403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1239290237427</t>
   </si>
   <si>
     <t xml:space="preserve">11.7982120513916</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1782159805298</t>
+    <t xml:space="preserve">12.1782169342041</t>
   </si>
   <si>
     <t xml:space="preserve">12.3229789733887</t>
@@ -1772,49 +1772,49 @@
     <t xml:space="preserve">12.8296518325806</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7391748428345</t>
+    <t xml:space="preserve">12.7391729354858</t>
   </si>
   <si>
     <t xml:space="preserve">12.7753648757935</t>
   </si>
   <si>
-    <t xml:space="preserve">12.395359992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2867879867554</t>
+    <t xml:space="preserve">12.3953609466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2867870330811</t>
   </si>
   <si>
     <t xml:space="preserve">12.6306018829346</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4496459960938</t>
+    <t xml:space="preserve">12.4496479034424</t>
   </si>
   <si>
     <t xml:space="preserve">12.2144060134888</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1058349609375</t>
+    <t xml:space="preserve">12.1058340072632</t>
   </si>
   <si>
     <t xml:space="preserve">11.8705940246582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9067850112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4724941253662</t>
+    <t xml:space="preserve">11.9067840576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4724950790405</t>
   </si>
   <si>
     <t xml:space="preserve">11.4182081222534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5810670852661</t>
+    <t xml:space="preserve">11.5810680389404</t>
   </si>
   <si>
     <t xml:space="preserve">11.8524990081787</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0877389907837</t>
+    <t xml:space="preserve">12.0877380371094</t>
   </si>
   <si>
     <t xml:space="preserve">11.8344030380249</t>
@@ -1832,10 +1832,10 @@
     <t xml:space="preserve">11.2734451293945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1829681396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1648721694946</t>
+    <t xml:space="preserve">11.1829671859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1648731231689</t>
   </si>
   <si>
     <t xml:space="preserve">10.8391542434692</t>
@@ -1844,19 +1844,19 @@
     <t xml:space="preserve">10.6401052474976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6762962341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5134363174438</t>
+    <t xml:space="preserve">10.6762971878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5134372711182</t>
   </si>
   <si>
     <t xml:space="preserve">10.9115371704102</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2915410995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1467771530151</t>
+    <t xml:space="preserve">11.2915391921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1467761993408</t>
   </si>
   <si>
     <t xml:space="preserve">10.766773223877</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">10.6220092773438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0020132064819</t>
+    <t xml:space="preserve">11.0020141601562</t>
   </si>
   <si>
     <t xml:space="preserve">10.6039142608643</t>
@@ -1883,16 +1883,16 @@
     <t xml:space="preserve">10.2781972885132</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3143882751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.898193359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9343843460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80771541595459</t>
+    <t xml:space="preserve">10.3143873214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89819431304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93438339233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80771636962891</t>
   </si>
   <si>
     <t xml:space="preserve">9.68104839324951</t>
@@ -1904,10 +1904,10 @@
     <t xml:space="preserve">10.2420063018799</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4772462844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3867692947388</t>
+    <t xml:space="preserve">10.4772472381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3867683410645</t>
   </si>
   <si>
     <t xml:space="preserve">10.4410552978516</t>
@@ -1919,25 +1919,25 @@
     <t xml:space="preserve">10.1153392791748</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3505792617798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4048643112183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7486782073975</t>
+    <t xml:space="preserve">10.3505783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4048652648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7486791610718</t>
   </si>
   <si>
     <t xml:space="preserve">11.0201101303101</t>
   </si>
   <si>
-    <t xml:space="preserve">10.857250213623</t>
+    <t xml:space="preserve">10.8572511672974</t>
   </si>
   <si>
     <t xml:space="preserve">10.8753461837769</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5858201980591</t>
+    <t xml:space="preserve">10.5858182907104</t>
   </si>
   <si>
     <t xml:space="preserve">10.8029642105103</t>
@@ -1946,13 +1946,13 @@
     <t xml:space="preserve">10.7124872207642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7848682403564</t>
+    <t xml:space="preserve">10.7848701477051</t>
   </si>
   <si>
     <t xml:space="preserve">11.2372550964355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3096361160278</t>
+    <t xml:space="preserve">11.3096351623535</t>
   </si>
   <si>
     <t xml:space="preserve">11.4543991088867</t>
@@ -1961,22 +1961,22 @@
     <t xml:space="preserve">11.7258310317993</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9972629547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1601209640503</t>
+    <t xml:space="preserve">11.9972620010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.160120010376</t>
   </si>
   <si>
     <t xml:space="preserve">12.0515480041504</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0334539413452</t>
+    <t xml:space="preserve">12.0334520339966</t>
   </si>
   <si>
     <t xml:space="preserve">11.9429759979248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7620220184326</t>
+    <t xml:space="preserve">11.7620210647583</t>
   </si>
   <si>
     <t xml:space="preserve">10.9477272033691</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">10.9658231735229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1877202987671</t>
+    <t xml:space="preserve">10.1877193450928</t>
   </si>
   <si>
     <t xml:space="preserve">9.98867034912109</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">10.0429573059082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91628837585449</t>
+    <t xml:space="preserve">9.91628932952881</t>
   </si>
   <si>
     <t xml:space="preserve">10.1696243286133</t>
@@ -2009,13 +2009,13 @@
     <t xml:space="preserve">10.1334342956543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3324842453003</t>
+    <t xml:space="preserve">10.332483291626</t>
   </si>
   <si>
     <t xml:space="preserve">10.2239112854004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0972442626953</t>
+    <t xml:space="preserve">10.097243309021</t>
   </si>
   <si>
     <t xml:space="preserve">10.0610523223877</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">10.0791473388672</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1515302658081</t>
+    <t xml:space="preserve">10.1515293121338</t>
   </si>
   <si>
     <t xml:space="preserve">11.056300163269</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">10.5496282577515</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3686752319336</t>
+    <t xml:space="preserve">10.3686742782593</t>
   </si>
   <si>
     <t xml:space="preserve">9.8258113861084</t>
@@ -2045,40 +2045,40 @@
     <t xml:space="preserve">9.77152538299561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.699143409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51818943023682</t>
+    <t xml:space="preserve">9.69914245605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51819038391113</t>
   </si>
   <si>
     <t xml:space="preserve">9.7172384262085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42771339416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5905704498291</t>
+    <t xml:space="preserve">9.42771244049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59057140350342</t>
   </si>
   <si>
     <t xml:space="preserve">11.3639221191406</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9791660308838</t>
+    <t xml:space="preserve">11.9791650772095</t>
   </si>
   <si>
     <t xml:space="preserve">12.4677419662476</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3772659301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3820180892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5629711151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6172580718994</t>
+    <t xml:space="preserve">12.3772668838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3820171356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5629720687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6172590255737</t>
   </si>
   <si>
     <t xml:space="preserve">11.0924911499023</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">10.6943912506104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62676334381104</t>
+    <t xml:space="preserve">9.62676239013672</t>
   </si>
   <si>
     <t xml:space="preserve">8.8034200668335</t>
@@ -2102,13 +2102,13 @@
     <t xml:space="preserve">7.04816484451294</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32864475250244</t>
+    <t xml:space="preserve">7.3286452293396</t>
   </si>
   <si>
     <t xml:space="preserve">7.24721479415894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18388032913208</t>
+    <t xml:space="preserve">7.18388080596924</t>
   </si>
   <si>
     <t xml:space="preserve">6.58673191070557</t>
@@ -2117,31 +2117,31 @@
     <t xml:space="preserve">6.65006589889526</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96673583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97578382492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16578483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05721235275269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28340578079224</t>
+    <t xml:space="preserve">6.96673536300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9757833480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16578531265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.057213306427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28340530395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.60912275314331</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76293325424194</t>
+    <t xml:space="preserve">7.76293420791626</t>
   </si>
   <si>
     <t xml:space="preserve">8.34198760986328</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04341316223145</t>
+    <t xml:space="preserve">8.04341220855713</t>
   </si>
   <si>
     <t xml:space="preserve">8.61341857910156</t>
@@ -2156,16 +2156,16 @@
     <t xml:space="preserve">8.93008804321289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35533142089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04770851135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26485347747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50009441375732</t>
+    <t xml:space="preserve">9.35533046722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04770946502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26485443115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50009346008301</t>
   </si>
   <si>
     <t xml:space="preserve">9.8620023727417</t>
@@ -2177,25 +2177,25 @@
     <t xml:space="preserve">10.9839191436768</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6582002639771</t>
+    <t xml:space="preserve">10.6582012176514</t>
   </si>
   <si>
     <t xml:space="preserve">9.9705753326416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2058153152466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84390735626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4591512680054</t>
+    <t xml:space="preserve">10.2058143615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84390830993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4591503143311</t>
   </si>
   <si>
     <t xml:space="preserve">10.9296321868896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7305812835693</t>
+    <t xml:space="preserve">10.730583190918</t>
   </si>
   <si>
     <t xml:space="preserve">10.8210601806641</t>
@@ -2204,10 +2204,10 @@
     <t xml:space="preserve">12.0696439743042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.558219909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8477468490601</t>
+    <t xml:space="preserve">12.5582208633423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8477458953857</t>
   </si>
   <si>
     <t xml:space="preserve">13.1915588378906</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">12.7934608459473</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4315509796143</t>
+    <t xml:space="preserve">12.4315519332886</t>
   </si>
   <si>
     <t xml:space="preserve">12.5944108963013</t>
@@ -2231,25 +2231,25 @@
     <t xml:space="preserve">12.7210788726807</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8658428192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.155366897583</t>
+    <t xml:space="preserve">12.8658418655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1553678512573</t>
   </si>
   <si>
     <t xml:space="preserve">13.0287008285522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1191778182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9382228851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0829877853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3725128173828</t>
+    <t xml:space="preserve">13.119176864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9382238388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.082986831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3725137710571</t>
   </si>
   <si>
     <t xml:space="preserve">13.3544178009033</t>
@@ -2258,28 +2258,28 @@
     <t xml:space="preserve">15.4534864425659</t>
   </si>
   <si>
-    <t xml:space="preserve">16.249683380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2858734130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3763523101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6477832794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8334903717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0687313079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8696794509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9239692687988</t>
+    <t xml:space="preserve">16.2496852874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2858753204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3763542175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6477851867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8334884643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0687294006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8696813583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9239673614502</t>
   </si>
   <si>
     <t xml:space="preserve">15.9058713912964</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">15.7972984313965</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2677803039551</t>
+    <t xml:space="preserve">16.2677822113037</t>
   </si>
   <si>
     <t xml:space="preserve">16.0325393676758</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">15.942063331604</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6344404220581</t>
+    <t xml:space="preserve">15.6344423294067</t>
   </si>
   <si>
     <t xml:space="preserve">16.1049213409424</t>
@@ -2333,13 +2333,13 @@
     <t xml:space="preserve">14.8925294876099</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6525344848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3630113601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4896764755249</t>
+    <t xml:space="preserve">15.6525363922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3630094528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4896774291992</t>
   </si>
   <si>
     <t xml:space="preserve">15.145866394043</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">15.0372934341431</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7430124282837</t>
+    <t xml:space="preserve">15.7430143356323</t>
   </si>
   <si>
     <t xml:space="preserve">14.8201456069946</t>
@@ -2360,13 +2360,13 @@
     <t xml:space="preserve">17.5887451171875</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7696971893311</t>
+    <t xml:space="preserve">17.7696990966797</t>
   </si>
   <si>
     <t xml:space="preserve">18.0230350494385</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1359024047852</t>
+    <t xml:space="preserve">19.1359062194824</t>
   </si>
   <si>
     <t xml:space="preserve">18.2763729095459</t>
@@ -2378,13 +2378,13 @@
     <t xml:space="preserve">17.4258861541748</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7335090637207</t>
+    <t xml:space="preserve">17.7335071563721</t>
   </si>
   <si>
     <t xml:space="preserve">17.2992191314697</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0458850860596</t>
+    <t xml:space="preserve">17.0458831787109</t>
   </si>
   <si>
     <t xml:space="preserve">17.0277881622314</t>
@@ -2399,31 +2399,31 @@
     <t xml:space="preserve">17.4077930450439</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5025672912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1406555175781</t>
+    <t xml:space="preserve">18.5025653839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1406536102295</t>
   </si>
   <si>
     <t xml:space="preserve">17.96875</t>
   </si>
   <si>
-    <t xml:space="preserve">17.49827003479</t>
+    <t xml:space="preserve">17.4982662200928</t>
   </si>
   <si>
     <t xml:space="preserve">17.9868450164795</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5930423736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1544532775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.244930267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1182651519775</t>
+    <t xml:space="preserve">18.5930404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1544551849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2449321746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1182632446289</t>
   </si>
   <si>
     <t xml:space="preserve">16.8106422424316</t>
@@ -2432,13 +2432,13 @@
     <t xml:space="preserve">16.8287372589111</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9735050201416</t>
+    <t xml:space="preserve">16.9735012054443</t>
   </si>
   <si>
     <t xml:space="preserve">16.9192161560059</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0639801025391</t>
+    <t xml:space="preserve">17.0639781951904</t>
   </si>
   <si>
     <t xml:space="preserve">16.8468360900879</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">16.9011211395264</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3173141479492</t>
+    <t xml:space="preserve">17.3173160552979</t>
   </si>
   <si>
     <t xml:space="preserve">17.2087421417236</t>
@@ -2456,16 +2456,16 @@
     <t xml:space="preserve">17.2268371582031</t>
   </si>
   <si>
-    <t xml:space="preserve">18.366849899292</t>
+    <t xml:space="preserve">18.3668479919434</t>
   </si>
   <si>
     <t xml:space="preserve">18.4573268890381</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6382808685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7287578582764</t>
+    <t xml:space="preserve">18.6382789611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7287559509277</t>
   </si>
   <si>
     <t xml:space="preserve">18.9549503326416</t>
@@ -2474,10 +2474,10 @@
     <t xml:space="preserve">18.8644733428955</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6335258483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6787662506104</t>
+    <t xml:space="preserve">19.6335277557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.678768157959</t>
   </si>
   <si>
     <t xml:space="preserve">19.5430507659912</t>
@@ -2486,25 +2486,25 @@
     <t xml:space="preserve">19.0454254150391</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0001888275146</t>
+    <t xml:space="preserve">19.000186920166</t>
   </si>
   <si>
     <t xml:space="preserve">19.3168563842773</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3216114044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2311325073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0906639099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6835193634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0954170227051</t>
+    <t xml:space="preserve">18.3216094970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2311344146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0906658172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6835174560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0954189300537</t>
   </si>
   <si>
     <t xml:space="preserve">18.004940032959</t>
@@ -2513,31 +2513,31 @@
     <t xml:space="preserve">17.570650100708</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8239879608154</t>
+    <t xml:space="preserve">17.8239860534668</t>
   </si>
   <si>
     <t xml:space="preserve">17.6430320739746</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8058891296387</t>
+    <t xml:space="preserve">17.8058910369873</t>
   </si>
   <si>
     <t xml:space="preserve">19.2716178894043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1811408996582</t>
+    <t xml:space="preserve">19.1811428070068</t>
   </si>
   <si>
     <t xml:space="preserve">20.2668685913086</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4930591583252</t>
+    <t xml:space="preserve">20.4930610656738</t>
   </si>
   <si>
     <t xml:space="preserve">20.9906845092773</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5835380554199</t>
+    <t xml:space="preserve">20.5835399627686</t>
   </si>
   <si>
     <t xml:space="preserve">20.3573455810547</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">19.9049587249756</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7692451477051</t>
+    <t xml:space="preserve">19.7692432403564</t>
   </si>
   <si>
     <t xml:space="preserve">20.7192535400391</t>
@@ -2555,13 +2555,13 @@
     <t xml:space="preserve">19.9954376220703</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2263793945312</t>
+    <t xml:space="preserve">19.2263832092285</t>
   </si>
   <si>
     <t xml:space="preserve">19.4525737762451</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4073352813721</t>
+    <t xml:space="preserve">19.4073371887207</t>
   </si>
   <si>
     <t xml:space="preserve">17.6249351501465</t>
@@ -2570,13 +2570,13 @@
     <t xml:space="preserve">17.7877941131592</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4978103637695</t>
+    <t xml:space="preserve">19.4978122711182</t>
   </si>
   <si>
     <t xml:space="preserve">20.0859146118164</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1311511993408</t>
+    <t xml:space="preserve">20.1311531066895</t>
   </si>
   <si>
     <t xml:space="preserve">19.8597221374512</t>
@@ -2585,16 +2585,16 @@
     <t xml:space="preserve">20.6740169525146</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0359210968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8097286224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.628776550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3121089935303</t>
+    <t xml:space="preserve">21.0359230041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8097305297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6287746429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.312105178833</t>
   </si>
   <si>
     <t xml:space="preserve">20.4478225708008</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">21.2802104949951</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3344974517822</t>
+    <t xml:space="preserve">21.3344993591309</t>
   </si>
   <si>
     <t xml:space="preserve">21.587833404541</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">22.1668872833252</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6192722320557</t>
+    <t xml:space="preserve">22.619270324707</t>
   </si>
   <si>
     <t xml:space="preserve">22.8726081848145</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">21.8592643737793</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0040264129639</t>
+    <t xml:space="preserve">22.0040283203125</t>
   </si>
   <si>
     <t xml:space="preserve">22.2573642730713</t>
@@ -2645,31 +2645,31 @@
     <t xml:space="preserve">22.1126003265381</t>
   </si>
   <si>
-    <t xml:space="preserve">22.058313369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6011772155762</t>
+    <t xml:space="preserve">22.0583114624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6011753082275</t>
   </si>
   <si>
     <t xml:space="preserve">22.6373672485352</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4202213287354</t>
+    <t xml:space="preserve">22.420223236084</t>
   </si>
   <si>
     <t xml:space="preserve">22.4021282196045</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3525924682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2621173858643</t>
+    <t xml:space="preserve">21.3525943756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2621154785156</t>
   </si>
   <si>
     <t xml:space="preserve">22.0945053100586</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5830821990967</t>
+    <t xml:space="preserve">22.5830783843994</t>
   </si>
   <si>
     <t xml:space="preserve">23.0354652404785</t>
@@ -2684,10 +2684,10 @@
     <t xml:space="preserve">23.2707061767578</t>
   </si>
   <si>
-    <t xml:space="preserve">25.044059753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7726249694824</t>
+    <t xml:space="preserve">25.0440578460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7726268768311</t>
   </si>
   <si>
     <t xml:space="preserve">24.9716758728027</t>
@@ -2696,22 +2696,22 @@
     <t xml:space="preserve">25.0621547698975</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9126396179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2383556365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6765727996826</t>
+    <t xml:space="preserve">25.9126377105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.238353729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6765747070312</t>
   </si>
   <si>
     <t xml:space="preserve">26.7130928039551</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5852794647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6583156585693</t>
+    <t xml:space="preserve">26.585277557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.658317565918</t>
   </si>
   <si>
     <t xml:space="preserve">26.8226451873779</t>
@@ -2726,7 +2726,7 @@
     <t xml:space="preserve">27.6260471343994</t>
   </si>
   <si>
-    <t xml:space="preserve">28.064266204834</t>
+    <t xml:space="preserve">28.0642642974854</t>
   </si>
   <si>
     <t xml:space="preserve">28.283374786377</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">28.958963394165</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1275463104248</t>
+    <t xml:space="preserve">30.1275482177734</t>
   </si>
   <si>
     <t xml:space="preserve">29.6528091430664</t>
@@ -2750,55 +2750,55 @@
     <t xml:space="preserve">30.1092872619629</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9632148742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4014320373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2188415527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2961292266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8213901519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1683216094971</t>
+    <t xml:space="preserve">29.9632129669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4014301300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2188396453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2961311340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8213920593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1683177947998</t>
   </si>
   <si>
     <t xml:space="preserve">30.2371006011963</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4154415130615</t>
+    <t xml:space="preserve">29.4154434204102</t>
   </si>
   <si>
     <t xml:space="preserve">29.8536605834961</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1780700683594</t>
+    <t xml:space="preserve">29.178071975708</t>
   </si>
   <si>
     <t xml:space="preserve">30.1458072662354</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7075901031494</t>
+    <t xml:space="preserve">29.7075881958008</t>
   </si>
   <si>
     <t xml:space="preserve">30.0545120239258</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8664131164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.546257019043</t>
+    <t xml:space="preserve">32.8664169311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5462532043457</t>
   </si>
   <si>
     <t xml:space="preserve">34.0532569885254</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0855255126953</t>
+    <t xml:space="preserve">33.0855293273926</t>
   </si>
   <si>
     <t xml:space="preserve">33.7245903015137</t>
@@ -2816,10 +2816,10 @@
     <t xml:space="preserve">33.7976303100586</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1403045654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2863731384277</t>
+    <t xml:space="preserve">33.1403007507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2863693237305</t>
   </si>
   <si>
     <t xml:space="preserve">32.2273445129395</t>
@@ -2831,34 +2831,34 @@
     <t xml:space="preserve">32.7568626403809</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6473007202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0307464599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7751197814941</t>
+    <t xml:space="preserve">32.6473083496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0307502746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7751235961914</t>
   </si>
   <si>
     <t xml:space="preserve">32.4099349975586</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6655654907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6923294067383</t>
+    <t xml:space="preserve">32.6655616760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.692325592041</t>
   </si>
   <si>
     <t xml:space="preserve">35.605281829834</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2401008605957</t>
+    <t xml:space="preserve">35.2400970458984</t>
   </si>
   <si>
     <t xml:space="preserve">35.8791694641113</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4774703979492</t>
+    <t xml:space="preserve">35.4774742126465</t>
   </si>
   <si>
     <t xml:space="preserve">35.0940284729004</t>
@@ -2867,13 +2867,13 @@
     <t xml:space="preserve">35.5870208740234</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7878761291504</t>
+    <t xml:space="preserve">35.7878723144531</t>
   </si>
   <si>
     <t xml:space="preserve">36.0435028076172</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8469009399414</t>
+    <t xml:space="preserve">36.8469047546387</t>
   </si>
   <si>
     <t xml:space="preserve">38.9101829528809</t>
@@ -2882,25 +2882,25 @@
     <t xml:space="preserve">38.4354438781738</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4944725036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3849220275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2205848693848</t>
+    <t xml:space="preserve">39.4944763183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3849182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.220588684082</t>
   </si>
   <si>
     <t xml:space="preserve">39.1292915344238</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1980743408203</t>
+    <t xml:space="preserve">38.1980781555176</t>
   </si>
   <si>
     <t xml:space="preserve">37.6137886047363</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2486000061035</t>
+    <t xml:space="preserve">37.2486038208008</t>
   </si>
   <si>
     <t xml:space="preserve">37.0660095214844</t>
@@ -2909,13 +2909,13 @@
     <t xml:space="preserve">37.2668609619141</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7008285522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.212085723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.559009552002</t>
+    <t xml:space="preserve">36.7008323669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2120819091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5590057373047</t>
   </si>
   <si>
     <t xml:space="preserve">38.0154838562012</t>
@@ -2924,22 +2924,22 @@
     <t xml:space="preserve">37.6503067016602</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6235389709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2315979003906</t>
+    <t xml:space="preserve">35.6235427856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2316017150879</t>
   </si>
   <si>
     <t xml:space="preserve">32.9942283630371</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3594131469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0490074157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.783618927002</t>
+    <t xml:space="preserve">33.3594093322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0490112304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7836227416992</t>
   </si>
   <si>
     <t xml:space="preserve">34.3819236755371</t>
@@ -2951,16 +2951,16 @@
     <t xml:space="preserve">32.9577102661133</t>
   </si>
   <si>
-    <t xml:space="preserve">33.63330078125</t>
+    <t xml:space="preserve">33.6332969665527</t>
   </si>
   <si>
     <t xml:space="preserve">35.513988494873</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4817199707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3173904418945</t>
+    <t xml:space="preserve">36.4817237854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3173866271973</t>
   </si>
   <si>
     <t xml:space="preserve">36.6095352172852</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">37.7781181335449</t>
   </si>
   <si>
-    <t xml:space="preserve">38.271110534668</t>
+    <t xml:space="preserve">38.2711143493652</t>
   </si>
   <si>
     <t xml:space="preserve">39.2023277282715</t>
@@ -2984,28 +2984,28 @@
     <t xml:space="preserve">34.9662132263184</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1488037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4409484863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8876686096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5267486572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8006286621094</t>
+    <t xml:space="preserve">35.1488075256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4409523010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8876724243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5267448425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8006324768066</t>
   </si>
   <si>
     <t xml:space="preserve">37.6685638427734</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4226951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.258358001709</t>
+    <t xml:space="preserve">35.4226913452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2583618164062</t>
   </si>
   <si>
     <t xml:space="preserve">34.9114379882812</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">34.3636627197266</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8341522216797</t>
+    <t xml:space="preserve">33.8341484069824</t>
   </si>
   <si>
     <t xml:space="preserve">33.5967826843262</t>
@@ -3029,22 +3029,22 @@
     <t xml:space="preserve">33.9071846008301</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3131408691406</t>
+    <t xml:space="preserve">35.3131370544434</t>
   </si>
   <si>
     <t xml:space="preserve">34.7105865478516</t>
   </si>
   <si>
-    <t xml:space="preserve">34.345401763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0715217590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1950798034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6150398254395</t>
+    <t xml:space="preserve">34.3454055786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0715179443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1950836181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6150360107422</t>
   </si>
   <si>
     <t xml:space="preserve">33.9254455566406</t>
@@ -3059,10 +3059,10 @@
     <t xml:space="preserve">34.5827713012695</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7288475036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0027313232422</t>
+    <t xml:space="preserve">34.7288436889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0027351379395</t>
   </si>
   <si>
     <t xml:space="preserve">34.8383979797363</t>
@@ -3071,37 +3071,37 @@
     <t xml:space="preserve">34.8749198913574</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5377502441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1725654602051</t>
+    <t xml:space="preserve">32.5377464294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1725692749023</t>
   </si>
   <si>
     <t xml:space="preserve">32.1360511779785</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4519596099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8901805877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1640644073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4294490814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1007862091064</t>
+    <t xml:space="preserve">29.4519577026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8901786804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1640663146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4294509887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1007843017578</t>
   </si>
   <si>
     <t xml:space="preserve">27.6808261871338</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9954814910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2693672180176</t>
+    <t xml:space="preserve">28.9954833984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2693710327148</t>
   </si>
   <si>
     <t xml:space="preserve">28.6850776672363</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">26.9687213897705</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8956813812256</t>
+    <t xml:space="preserve">26.8956832885742</t>
   </si>
   <si>
     <t xml:space="preserve">27.845157623291</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">27.9729690551758</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6668167114258</t>
+    <t xml:space="preserve">28.6668186187744</t>
   </si>
   <si>
     <t xml:space="preserve">29.1232948303223</t>
@@ -3137,16 +3137,16 @@
     <t xml:space="preserve">26.3479099273682</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5445079803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7496089935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7861270904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5670185089111</t>
+    <t xml:space="preserve">25.5445098876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7496109008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7861289978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5670204162598</t>
   </si>
   <si>
     <t xml:space="preserve">27.9547119140625</t>
@@ -3155,13 +3155,13 @@
     <t xml:space="preserve">27.4251976013184</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4799766540527</t>
+    <t xml:space="preserve">27.4799747467041</t>
   </si>
   <si>
     <t xml:space="preserve">27.1147937774658</t>
   </si>
   <si>
-    <t xml:space="preserve">26.731351852417</t>
+    <t xml:space="preserve">26.7313537597656</t>
   </si>
   <si>
     <t xml:space="preserve">27.4069385528564</t>
@@ -3182,22 +3182,22 @@
     <t xml:space="preserve">23.5542621612549</t>
   </si>
   <si>
-    <t xml:space="preserve">24.70458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.097785949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0022411346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7466087341309</t>
+    <t xml:space="preserve">24.7045860290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0977840423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0022392272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7466106414795</t>
   </si>
   <si>
     <t xml:space="preserve">20.7423572540283</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6047916412354</t>
+    <t xml:space="preserve">22.6047897338867</t>
   </si>
   <si>
     <t xml:space="preserve">21.8744239807129</t>
@@ -3206,28 +3206,28 @@
     <t xml:space="preserve">22.5134944915771</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1525650024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2073402404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5402565002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6680717468262</t>
+    <t xml:space="preserve">23.1525630950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2073421478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5402545928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6680698394775</t>
   </si>
   <si>
     <t xml:space="preserve">24.8689212799072</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4489631652832</t>
+    <t xml:space="preserve">24.4489612579346</t>
   </si>
   <si>
     <t xml:space="preserve">25.2341022491455</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5585155487061</t>
+    <t xml:space="preserve">24.5585136413574</t>
   </si>
   <si>
     <t xml:space="preserve">24.0289993286133</t>
@@ -3239,16 +3239,16 @@
     <t xml:space="preserve">24.0472602844238</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3984336853027</t>
+    <t xml:space="preserve">25.3984355926514</t>
   </si>
   <si>
     <t xml:space="preserve">25.4166946411133</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2115917205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.083776473999</t>
+    <t xml:space="preserve">24.2115936279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0837783813477</t>
   </si>
   <si>
     <t xml:space="preserve">23.8098926544189</t>
@@ -3260,10 +3260,10 @@
     <t xml:space="preserve">22.4221973419189</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7326030731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.677827835083</t>
+    <t xml:space="preserve">22.7326049804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6778259277344</t>
   </si>
   <si>
     <t xml:space="preserve">22.2761249542236</t>
@@ -3275,19 +3275,19 @@
     <t xml:space="preserve">22.2213497161865</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8379058837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0935363769531</t>
+    <t xml:space="preserve">21.8379077911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0935344696045</t>
   </si>
   <si>
     <t xml:space="preserve">22.8239002227783</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5457611083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.07102394104</t>
+    <t xml:space="preserve">21.5457630157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0710258483887</t>
   </si>
   <si>
     <t xml:space="preserve">21.9657211303711</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">20.8519134521484</t>
   </si>
   <si>
-    <t xml:space="preserve">20.724100112915</t>
+    <t xml:space="preserve">20.7241020202637</t>
   </si>
   <si>
     <t xml:space="preserve">21.0162467956543</t>
@@ -3338,28 +3338,28 @@
     <t xml:space="preserve">21.3449096679688</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3954372406006</t>
+    <t xml:space="preserve">20.3954391479492</t>
   </si>
   <si>
     <t xml:space="preserve">20.523250579834</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6693229675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.130054473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1933326721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6455593109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5177440643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7368545532227</t>
+    <t xml:space="preserve">20.6693210601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1300525665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1933345794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6455612182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5177459716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7368564605713</t>
   </si>
   <si>
     <t xml:space="preserve">23.0533809661865</t>
@@ -5334,6 +5334,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7600002288818</t>
   </si>
 </sst>
 </file>
@@ -70308,7 +70311,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6504976852</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>155380</v>
@@ -70329,6 +70332,32 @@
         <v>1773</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6495486111</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>233718</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>14.8199996948242</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>14.6599998474121</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>14.7600002288818</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>1774</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TNXT.MI.xlsx
+++ b/data/TNXT.MI.xlsx
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63493776321411</t>
+    <t xml:space="preserve">2.63493752479553</t>
   </si>
   <si>
     <t xml:space="preserve">TNXT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65151000022888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59350872039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5355064868927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52556324005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48579072952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52722072601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48744797706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47087597846985</t>
+    <t xml:space="preserve">2.65150952339172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59350848197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53550672531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52556347846985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48579049110413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5272204875946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48744773864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47087550163269</t>
   </si>
   <si>
     <t xml:space="preserve">2.46921873092651</t>
@@ -77,22 +77,22 @@
     <t xml:space="preserve">2.49739122390747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47916197776794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44436097145081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39464473724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34161496162415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36150097846985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55207872390747</t>
+    <t xml:space="preserve">2.47916221618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44436073303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39464497566223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34161472320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36150121688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55207848548889</t>
   </si>
   <si>
     <t xml:space="preserve">2.58522248268127</t>
@@ -101,16 +101,16 @@
     <t xml:space="preserve">2.6100800037384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56865048408508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63659477233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68962526321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73436951637268</t>
+    <t xml:space="preserve">2.56865072250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63659453392029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68962502479553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7343692779541</t>
   </si>
   <si>
     <t xml:space="preserve">2.72608327865601</t>
@@ -119,10 +119,10 @@
     <t xml:space="preserve">2.77579975128174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58025121688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5620219707489</t>
+    <t xml:space="preserve">2.58025145530701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56202173233032</t>
   </si>
   <si>
     <t xml:space="preserve">2.66808152198792</t>
@@ -134,16 +134,16 @@
     <t xml:space="preserve">2.64322352409363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60842275619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.666424036026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65316724777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62665200233459</t>
+    <t xml:space="preserve">2.60842251777649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66642451286316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65316677093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62665152549744</t>
   </si>
   <si>
     <t xml:space="preserve">2.6929395198822</t>
@@ -155,55 +155,55 @@
     <t xml:space="preserve">2.81722950935364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90008950233459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85865950584412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89843249320984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88351702690125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87523174285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86694526672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81888699531555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82054400444031</t>
+    <t xml:space="preserve">2.90008926391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8586597442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89843225479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88351726531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87523150444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86694550514221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81888651847839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82054376602173</t>
   </si>
   <si>
     <t xml:space="preserve">2.85368776321411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79237151145935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85700249671936</t>
+    <t xml:space="preserve">2.79237127304077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85700225830078</t>
   </si>
   <si>
     <t xml:space="preserve">2.90671801567078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82882952690125</t>
+    <t xml:space="preserve">2.82882976531982</t>
   </si>
   <si>
     <t xml:space="preserve">2.85037350654602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90837502479553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96306276321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9579770565033</t>
+    <t xml:space="preserve">2.90837526321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96306300163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95797729492188</t>
   </si>
   <si>
     <t xml:space="preserve">2.88169693946838</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">2.89017271995544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86474561691284</t>
+    <t xml:space="preserve">2.86474609375</t>
   </si>
   <si>
     <t xml:space="preserve">2.94950175285339</t>
@@ -221,55 +221,55 @@
     <t xml:space="preserve">2.92407512664795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96645283699036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11901330947876</t>
+    <t xml:space="preserve">2.96645307540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11901307106018</t>
   </si>
   <si>
     <t xml:space="preserve">2.94272112846375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94780659675598</t>
+    <t xml:space="preserve">2.94780683517456</t>
   </si>
   <si>
     <t xml:space="preserve">2.8833920955658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87322163581848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85966086387634</t>
+    <t xml:space="preserve">2.8732213973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85966038703918</t>
   </si>
   <si>
     <t xml:space="preserve">3.03256297111511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07037329673767</t>
+    <t xml:space="preserve">3.07037377357483</t>
   </si>
   <si>
     <t xml:space="preserve">3.06866335868835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06011056900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99340081214905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98484778404236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93524241447449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98313736915588</t>
+    <t xml:space="preserve">3.06011080741882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99340057373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98484802246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93524289131165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9831371307373</t>
   </si>
   <si>
     <t xml:space="preserve">2.92497992515564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92326927185059</t>
+    <t xml:space="preserve">2.92326951026917</t>
   </si>
   <si>
     <t xml:space="preserve">2.9677426815033</t>
@@ -278,13 +278,13 @@
     <t xml:space="preserve">3.03616333007812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05840039253235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05497908592224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08747863769531</t>
+    <t xml:space="preserve">3.05839991569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05497932434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08747887611389</t>
   </si>
   <si>
     <t xml:space="preserve">3.13879418373108</t>
@@ -299,10 +299,10 @@
     <t xml:space="preserve">3.15589952468872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12339949607849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12511014938354</t>
+    <t xml:space="preserve">3.12339973449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12511038780212</t>
   </si>
   <si>
     <t xml:space="preserve">3.14734697341919</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">3.16445207595825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16616272926331</t>
+    <t xml:space="preserve">3.16616225242615</t>
   </si>
   <si>
     <t xml:space="preserve">3.24142503738403</t>
@@ -320,49 +320,49 @@
     <t xml:space="preserve">3.30129313468933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3868191242218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48431777954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52708053588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62629103660583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63655400276184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64510607719421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74602723121643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67760610580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71181702613831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63484311103821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51681780815125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50484490394592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4945809841156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50655484199524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48089694976807</t>
+    <t xml:space="preserve">3.38681888580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48431825637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52708101272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62629079818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63655352592468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64510655403137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74602746963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67760634422302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71181654930115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63484334945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51681804656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50484418869019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49458122253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50655508041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48089742660522</t>
   </si>
   <si>
     <t xml:space="preserve">3.43129229545593</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">3.60063338279724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64681649208069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69471216201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69984340667725</t>
+    <t xml:space="preserve">3.64681673049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69471168518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69984316825867</t>
   </si>
   <si>
     <t xml:space="preserve">3.67589592933655</t>
@@ -389,169 +389,169 @@
     <t xml:space="preserve">3.66563248634338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59721207618713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63313245773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57497572898865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66050124168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68615865707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7152373790741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73747444152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71010613441467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69129014015198</t>
+    <t xml:space="preserve">3.59721231460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63313293457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57497549057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66050100326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6861584186554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71523761749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73747396469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71010565757751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69129085540771</t>
   </si>
   <si>
     <t xml:space="preserve">3.68958020210266</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73234272003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72036862373352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76313233375549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77168416976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62115955352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64168500900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70326447486877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79734230041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75458002090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90852546691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76655292510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72892141342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6673436164856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50997591018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49800229072571</t>
+    <t xml:space="preserve">3.73234248161316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7203688621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76313209533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77168488502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62115931510925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64168548583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70326399803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79734206199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75457906723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9085259437561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76655268669128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72892212867737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66734337806702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50997614860535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49800276756287</t>
   </si>
   <si>
     <t xml:space="preserve">3.4894495010376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47234487533569</t>
+    <t xml:space="preserve">3.47234463691711</t>
   </si>
   <si>
     <t xml:space="preserve">3.40392398834229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43642401695251</t>
+    <t xml:space="preserve">3.43642425537109</t>
   </si>
   <si>
     <t xml:space="preserve">3.53221297264099</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51852893829346</t>
+    <t xml:space="preserve">3.51852869987488</t>
   </si>
   <si>
     <t xml:space="preserve">3.46037101745605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50142312049866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53563356399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55615997314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64339661598206</t>
+    <t xml:space="preserve">3.50142335891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53563380241394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55615949630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6433961391449</t>
   </si>
   <si>
     <t xml:space="preserve">3.7255003452301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84865784645081</t>
+    <t xml:space="preserve">3.84865736961365</t>
   </si>
   <si>
     <t xml:space="preserve">3.82984209060669</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83155226707458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87089419364929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84523630142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87431621551514</t>
+    <t xml:space="preserve">3.83155298233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87089467048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8452365398407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8743155002594</t>
   </si>
   <si>
     <t xml:space="preserve">3.86405253410339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8572096824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82471084594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90681505203247</t>
+    <t xml:space="preserve">3.85721063613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82471036911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90681529045105</t>
   </si>
   <si>
     <t xml:space="preserve">4.00260448455811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17536640167236</t>
+    <t xml:space="preserve">4.17536592483521</t>
   </si>
   <si>
     <t xml:space="preserve">4.11378765106201</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00773477554321</t>
+    <t xml:space="preserve">4.00773620605469</t>
   </si>
   <si>
     <t xml:space="preserve">4.05220890045166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08128833770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0060248374939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09839200973511</t>
+    <t xml:space="preserve">4.0812873840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00602436065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09839296340942</t>
   </si>
   <si>
     <t xml:space="preserve">4.01970863342285</t>
@@ -560,13 +560,13 @@
     <t xml:space="preserve">4.01115703582764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99576163291931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0351037979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06247234344482</t>
+    <t xml:space="preserve">3.99576187133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03510427474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06247186660767</t>
   </si>
   <si>
     <t xml:space="preserve">4.13773488998413</t>
@@ -578,28 +578,28 @@
     <t xml:space="preserve">4.14799737930298</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18905019760132</t>
+    <t xml:space="preserve">4.18904972076416</t>
   </si>
   <si>
     <t xml:space="preserve">4.2591814994812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22839117050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20615577697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02142000198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99405121803284</t>
+    <t xml:space="preserve">4.22839212417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2061562538147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0214204788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99405169487</t>
   </si>
   <si>
     <t xml:space="preserve">4.01799869537354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02655172348022</t>
+    <t xml:space="preserve">4.02655124664307</t>
   </si>
   <si>
     <t xml:space="preserve">4.07615661621094</t>
@@ -608,37 +608,37 @@
     <t xml:space="preserve">4.12747240066528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11891984939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1052360534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09668207168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10181379318237</t>
+    <t xml:space="preserve">4.11891937255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10523462295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09668254852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10181427001953</t>
   </si>
   <si>
     <t xml:space="preserve">4.0710244178772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09497213363647</t>
+    <t xml:space="preserve">4.09497165679932</t>
   </si>
   <si>
     <t xml:space="preserve">4.13089275360107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21641874313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52431106567383</t>
+    <t xml:space="preserve">4.21641826629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52431058883667</t>
   </si>
   <si>
     <t xml:space="preserve">4.54996871948242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53713989257812</t>
+    <t xml:space="preserve">4.53713941574097</t>
   </si>
   <si>
     <t xml:space="preserve">4.46444272994995</t>
@@ -650,16 +650,16 @@
     <t xml:space="preserve">4.56707429885864</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6226658821106</t>
+    <t xml:space="preserve">4.62266635894775</t>
   </si>
   <si>
     <t xml:space="preserve">4.63549470901489</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58417987823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60128402709961</t>
+    <t xml:space="preserve">4.58417892456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60128450393677</t>
   </si>
   <si>
     <t xml:space="preserve">4.57562637329102</t>
@@ -668,25 +668,25 @@
     <t xml:space="preserve">4.61838960647583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53286409378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55852174758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48154783248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5157585144043</t>
+    <t xml:space="preserve">4.53286361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55852079391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48154878616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51575899124146</t>
   </si>
   <si>
     <t xml:space="preserve">4.4901008605957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51148223876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63121843338013</t>
+    <t xml:space="preserve">4.51148176193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63121747970581</t>
   </si>
   <si>
     <t xml:space="preserve">4.78516435623169</t>
@@ -695,58 +695,58 @@
     <t xml:space="preserve">4.7595067024231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78944063186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7338490486145</t>
+    <t xml:space="preserve">4.78944110870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73384952545166</t>
   </si>
   <si>
     <t xml:space="preserve">4.77233600616455</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76378345489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65687561035156</t>
+    <t xml:space="preserve">4.76378297805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65687608718872</t>
   </si>
   <si>
     <t xml:space="preserve">4.69536256790161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8279275894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90062379837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91772937774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94338703155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98615026473999</t>
+    <t xml:space="preserve">4.82792711257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90062427520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91772985458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94338655471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98614978790283</t>
   </si>
   <si>
     <t xml:space="preserve">5.04174184799194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02035999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0716757774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08022880554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99470329284668</t>
+    <t xml:space="preserve">5.02036094665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07167482376099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08022832870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99470281600952</t>
   </si>
   <si>
     <t xml:space="preserve">5.09305715560913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06050634384155</t>
+    <t xml:space="preserve">5.06050682067871</t>
   </si>
   <si>
     <t xml:space="preserve">4.91728496551514</t>
@@ -755,19 +755,19 @@
     <t xml:space="preserve">4.94766521453857</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92596530914307</t>
+    <t xml:space="preserve">4.92596483230591</t>
   </si>
   <si>
     <t xml:space="preserve">4.9042649269104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82180404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7350025177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72198247909546</t>
+    <t xml:space="preserve">4.82180452346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73500204086304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72198295593262</t>
   </si>
   <si>
     <t xml:space="preserve">4.59178018569946</t>
@@ -776,52 +776,52 @@
     <t xml:space="preserve">4.64386129379272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73066186904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66556215286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6525411605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60914039611816</t>
+    <t xml:space="preserve">4.73066234588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66556167602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65254163742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60914087295532</t>
   </si>
   <si>
     <t xml:space="preserve">4.65688133239746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54837942123413</t>
+    <t xml:space="preserve">4.54838037490845</t>
   </si>
   <si>
     <t xml:space="preserve">4.53536033630371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47025918960571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59612131118774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47459888458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48761892318726</t>
+    <t xml:space="preserve">4.47025966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59612035751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47459936141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48761987686157</t>
   </si>
   <si>
     <t xml:space="preserve">4.46157836914062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41383838653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38779735565186</t>
+    <t xml:space="preserve">4.4138388633728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38779830932617</t>
   </si>
   <si>
     <t xml:space="preserve">4.39213800430298</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40949821472168</t>
+    <t xml:space="preserve">4.40949773788452</t>
   </si>
   <si>
     <t xml:space="preserve">4.55706024169922</t>
@@ -833,31 +833,31 @@
     <t xml:space="preserve">4.57008028030396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53969955444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47893857955933</t>
+    <t xml:space="preserve">4.53970003128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47893905639648</t>
   </si>
   <si>
     <t xml:space="preserve">4.43553829193115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42251825332642</t>
+    <t xml:space="preserve">4.42251873016357</t>
   </si>
   <si>
     <t xml:space="preserve">4.43119859695435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45289850234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51365852355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68726110458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60046052932739</t>
+    <t xml:space="preserve">4.45289945602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51365947723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68726205825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60046100616455</t>
   </si>
   <si>
     <t xml:space="preserve">4.63952112197876</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">4.56139993667603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5874400138855</t>
+    <t xml:space="preserve">4.58744049072266</t>
   </si>
   <si>
     <t xml:space="preserve">4.61782121658325</t>
@@ -875,28 +875,28 @@
     <t xml:space="preserve">4.64820146560669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60480070114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58310079574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49629974365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50497913360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42685842514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49195957183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51800012588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80878353118896</t>
+    <t xml:space="preserve">4.6048002243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58310127258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49629926681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50497961044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42685747146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49195909500122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51800060272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80878400802612</t>
   </si>
   <si>
     <t xml:space="preserve">4.77840328216553</t>
@@ -905,13 +905,13 @@
     <t xml:space="preserve">4.84784412384033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8348240852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74368286132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81312417984009</t>
+    <t xml:space="preserve">4.83482360839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74368333816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81312370300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.71330213546753</t>
@@ -920,34 +920,34 @@
     <t xml:space="preserve">4.70462226867676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72632265090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69594192504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76972246170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84350347518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87822389602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87388467788696</t>
+    <t xml:space="preserve">4.72632217407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69594144821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7697229385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84350442886353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87822437286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8738842010498</t>
   </si>
   <si>
     <t xml:space="preserve">4.97370576858521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97804546356201</t>
+    <t xml:space="preserve">4.97804594039917</t>
   </si>
   <si>
     <t xml:space="preserve">5.00842618942261</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07786655426025</t>
+    <t xml:space="preserve">5.07786703109741</t>
   </si>
   <si>
     <t xml:space="preserve">5.04314661026001</t>
@@ -959,43 +959,43 @@
     <t xml:space="preserve">4.86086416244507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.869544506073</t>
+    <t xml:space="preserve">4.86954498291016</t>
   </si>
   <si>
     <t xml:space="preserve">4.96502542495728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90860557556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99974632263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99106597900391</t>
+    <t xml:space="preserve">4.90860509872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99974584579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99106550216675</t>
   </si>
   <si>
     <t xml:space="preserve">5.15598821640015</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12994718551636</t>
+    <t xml:space="preserve">5.12994766235352</t>
   </si>
   <si>
     <t xml:space="preserve">5.29486989974976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41639137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48583316802979</t>
+    <t xml:space="preserve">5.41639184951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48583269119263</t>
   </si>
   <si>
     <t xml:space="preserve">5.43375205993652</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48149251937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42073106765747</t>
+    <t xml:space="preserve">5.4814920425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42073154449463</t>
   </si>
   <si>
     <t xml:space="preserve">5.39469146728516</t>
@@ -1007,49 +1007,49 @@
     <t xml:space="preserve">5.33393049240112</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37299060821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33827066421509</t>
+    <t xml:space="preserve">5.37299108505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33827114105225</t>
   </si>
   <si>
     <t xml:space="preserve">5.20806884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16466808319092</t>
+    <t xml:space="preserve">5.16466856002808</t>
   </si>
   <si>
     <t xml:space="preserve">5.26449012756348</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25147008895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2601490020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1863694190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20372867584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19504928588867</t>
+    <t xml:space="preserve">5.25146961212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26014947891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18636846542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20372819900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19504833221436</t>
   </si>
   <si>
     <t xml:space="preserve">5.16900825500488</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18202781677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19938802719116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22542953491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42507219314575</t>
+    <t xml:space="preserve">5.18202877044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19938850402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22542858123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42507171630859</t>
   </si>
   <si>
     <t xml:space="preserve">5.61603450775146</t>
@@ -1058,22 +1058,22 @@
     <t xml:space="preserve">5.72887563705444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71151542663574</t>
+    <t xml:space="preserve">5.71151638031006</t>
   </si>
   <si>
     <t xml:space="preserve">5.78963661193848</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82435750961304</t>
+    <t xml:space="preserve">5.82435655593872</t>
   </si>
   <si>
     <t xml:space="preserve">5.87643814086914</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88511800765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93719911575317</t>
+    <t xml:space="preserve">5.88511753082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93719863891602</t>
   </si>
   <si>
     <t xml:space="preserve">5.85907745361328</t>
@@ -1082,37 +1082,37 @@
     <t xml:space="preserve">5.80699682235718</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92851781845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97191953659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95455932617188</t>
+    <t xml:space="preserve">5.92851829528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97191858291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95455837249756</t>
   </si>
   <si>
     <t xml:space="preserve">6.03268003463745</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1715612411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28440284729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01531982421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02399969100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21496152877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14552164077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40592527389526</t>
+    <t xml:space="preserve">6.17156219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2844033241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01531934738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02399921417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21496200561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14552116394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40592479705811</t>
   </si>
   <si>
     <t xml:space="preserve">6.07608032226562</t>
@@ -1124,10 +1124,10 @@
     <t xml:space="preserve">6.04135990142822</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22364187240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13684129714966</t>
+    <t xml:space="preserve">6.22364234924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13684177398682</t>
   </si>
   <si>
     <t xml:space="preserve">6.19760179519653</t>
@@ -1136,37 +1136,37 @@
     <t xml:space="preserve">6.15420150756836</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05004024505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89379787445068</t>
+    <t xml:space="preserve">6.05003929138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89379739761353</t>
   </si>
   <si>
     <t xml:space="preserve">5.90247821807861</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70283555984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50319337844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5813136100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72019577026367</t>
+    <t xml:space="preserve">5.70283508300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50319290161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58131408691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72019529342651</t>
   </si>
   <si>
     <t xml:space="preserve">5.763596534729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91983842849731</t>
+    <t xml:space="preserve">5.919837474823</t>
   </si>
   <si>
     <t xml:space="preserve">5.99795913696289</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83303737640381</t>
+    <t xml:space="preserve">5.83303689956665</t>
   </si>
   <si>
     <t xml:space="preserve">5.79831647872925</t>
@@ -1178,13 +1178,13 @@
     <t xml:space="preserve">5.5118727684021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5465931892395</t>
+    <t xml:space="preserve">5.54659271240234</t>
   </si>
   <si>
     <t xml:space="preserve">5.58999395370483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52055311203003</t>
+    <t xml:space="preserve">5.52055263519287</t>
   </si>
   <si>
     <t xml:space="preserve">5.38167095184326</t>
@@ -1196,34 +1196,34 @@
     <t xml:space="preserve">5.46847200393677</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6767954826355</t>
+    <t xml:space="preserve">5.67679500579834</t>
   </si>
   <si>
     <t xml:space="preserve">5.64207458496094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55527305603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53791379928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57263422012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5292329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39903116226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39035177230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45111227035522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09344100952148</t>
+    <t xml:space="preserve">5.55527353286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53791332244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57263374328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52923250198364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3990306854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39035129547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45111274719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09344005584717</t>
   </si>
   <si>
     <t xml:space="preserve">5.81567716598511</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">5.77227640151978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73755598068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40771102905273</t>
+    <t xml:space="preserve">5.73755645751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40771150588989</t>
   </si>
   <si>
     <t xml:space="preserve">5.24278926849365</t>
@@ -1244,10 +1244,10 @@
     <t xml:space="preserve">5.06918716430664</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98238515853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07618856430054</t>
+    <t xml:space="preserve">4.98238563537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07618808746338</t>
   </si>
   <si>
     <t xml:space="preserve">5.15619802474976</t>
@@ -1256,49 +1256,49 @@
     <t xml:space="preserve">5.08507776260376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24509811401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11174821853638</t>
+    <t xml:space="preserve">5.24509763717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11174774169922</t>
   </si>
   <si>
     <t xml:space="preserve">5.13841772079468</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20953798294067</t>
+    <t xml:space="preserve">5.20953750610352</t>
   </si>
   <si>
     <t xml:space="preserve">5.06729793548584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0584077835083</t>
+    <t xml:space="preserve">5.05840826034546</t>
   </si>
   <si>
     <t xml:space="preserve">5.04062843322754</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04951763153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94283771514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77392816543579</t>
+    <t xml:space="preserve">5.04951810836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94283819198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77392768859863</t>
   </si>
   <si>
     <t xml:space="preserve">4.90727806091309</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76503849029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92505836486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88949823379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02284812927246</t>
+    <t xml:space="preserve">4.76503801345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92505741119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88949775695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02284860610962</t>
   </si>
   <si>
     <t xml:space="preserve">4.97839784622192</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">4.91616821289062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95172786712646</t>
+    <t xml:space="preserve">4.95172834396362</t>
   </si>
   <si>
     <t xml:space="preserve">4.93394804000854</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">4.78281784057617</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75614833831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98728799819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10285711288452</t>
+    <t xml:space="preserve">4.75614738464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98728895187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10285758972168</t>
   </si>
   <si>
     <t xml:space="preserve">4.960618019104</t>
@@ -1337,19 +1337,19 @@
     <t xml:space="preserve">5.20064783096313</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2184271812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27176761627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33399820327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23620796203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18286752700806</t>
+    <t xml:space="preserve">5.21842765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27176713943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33399772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23620748519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18286800384521</t>
   </si>
   <si>
     <t xml:space="preserve">5.01395797729492</t>
@@ -1358,16 +1358,16 @@
     <t xml:space="preserve">4.99617767333984</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00506782531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37844848632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47623729705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56513833999634</t>
+    <t xml:space="preserve">5.00506830215454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37844753265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47623777389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56513738632202</t>
   </si>
   <si>
     <t xml:space="preserve">5.6807074546814</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">5.6540379524231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63625812530518</t>
+    <t xml:space="preserve">5.63625717163086</t>
   </si>
   <si>
     <t xml:space="preserve">5.55624771118164</t>
@@ -1385,25 +1385,25 @@
     <t xml:space="preserve">5.68959760665894</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96518754959106</t>
+    <t xml:space="preserve">5.96518802642822</t>
   </si>
   <si>
     <t xml:space="preserve">5.89406776428223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77849721908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84072780609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76071739196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92073726654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83183670043945</t>
+    <t xml:space="preserve">5.77849769592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84072732925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76071786880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92073774337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83183765411377</t>
   </si>
   <si>
     <t xml:space="preserve">5.4495677947998</t>
@@ -1412,13 +1412,13 @@
     <t xml:space="preserve">5.5829176902771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43178844451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36955738067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6095871925354</t>
+    <t xml:space="preserve">5.43178796768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36955785751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60958766937256</t>
   </si>
   <si>
     <t xml:space="preserve">5.86739778518677</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">5.59180784225464</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6451473236084</t>
+    <t xml:space="preserve">5.64514780044556</t>
   </si>
   <si>
     <t xml:space="preserve">5.71626758575439</t>
@@ -1448,16 +1448,16 @@
     <t xml:space="preserve">5.73404741287231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81405735015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67181825637817</t>
+    <t xml:space="preserve">5.81405782699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67181777954102</t>
   </si>
   <si>
     <t xml:space="preserve">5.5117974281311</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85850811004639</t>
+    <t xml:space="preserve">5.85850763320923</t>
   </si>
   <si>
     <t xml:space="preserve">5.66292715072632</t>
@@ -1466,10 +1466,10 @@
     <t xml:space="preserve">5.53846788406372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90295791625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79627799987793</t>
+    <t xml:space="preserve">5.90295743942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79627752304077</t>
   </si>
   <si>
     <t xml:space="preserve">5.80516767501831</t>
@@ -1478,22 +1478,22 @@
     <t xml:space="preserve">5.6184778213501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46734762191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60069799423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45845746994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50290775299072</t>
+    <t xml:space="preserve">5.46734809875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60069751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45845794677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50290822982788</t>
   </si>
   <si>
     <t xml:space="preserve">5.34288787841797</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62736701965332</t>
+    <t xml:space="preserve">5.62736749649048</t>
   </si>
   <si>
     <t xml:space="preserve">5.52957725524902</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">5.72515773773193</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70737791061401</t>
+    <t xml:space="preserve">5.70737743377686</t>
   </si>
   <si>
     <t xml:space="preserve">5.69848775863647</t>
@@ -1514,25 +1514,25 @@
     <t xml:space="preserve">6.00074768066406</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92962741851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94740724563599</t>
+    <t xml:space="preserve">5.92962789535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94740772247314</t>
   </si>
   <si>
     <t xml:space="preserve">5.93851757049561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99185657501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24077749252319</t>
+    <t xml:space="preserve">5.99185800552368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24077701568604</t>
   </si>
   <si>
     <t xml:space="preserve">6.40968751907349</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48080778121948</t>
+    <t xml:space="preserve">6.48080730438232</t>
   </si>
   <si>
     <t xml:space="preserve">6.62304735183716</t>
@@ -1541,73 +1541,73 @@
     <t xml:space="preserve">6.84529733657837</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99642658233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0142068862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90752696990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91641759872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97864627838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00531768798828</t>
+    <t xml:space="preserve">6.99642705917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01420736312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90752744674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91641712188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97864723205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00531673431396</t>
   </si>
   <si>
     <t xml:space="preserve">7.02309703826904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2453465461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27201700210571</t>
+    <t xml:space="preserve">7.24534702301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27201747894287</t>
   </si>
   <si>
     <t xml:space="preserve">7.33424711227417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47648763656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76985740661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73429584503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72540760040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79652690887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80541706085205</t>
+    <t xml:space="preserve">7.47648668289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76985645294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7342963218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72540616989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79652643203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80541658401489</t>
   </si>
   <si>
     <t xml:space="preserve">8.22324752807617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21435642242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15212631225586</t>
+    <t xml:space="preserve">8.21435546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15212726593018</t>
   </si>
   <si>
     <t xml:space="preserve">8.12545776367188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00099754333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17879676818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34770584106445</t>
+    <t xml:space="preserve">8.00099658966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17879581451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34770679473877</t>
   </si>
   <si>
     <t xml:space="preserve">8.42771530151367</t>
@@ -1616,46 +1616,46 @@
     <t xml:space="preserve">8.48105621337891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46327686309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5255069732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50772571563721</t>
+    <t xml:space="preserve">8.46327590942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52550601959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50772666931152</t>
   </si>
   <si>
     <t xml:space="preserve">8.66774654388428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80109596252441</t>
+    <t xml:space="preserve">8.8010950088501</t>
   </si>
   <si>
     <t xml:space="preserve">8.8899974822998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19225597381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37005615234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47673606872559</t>
+    <t xml:space="preserve">9.19225692749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37005519866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47673511505127</t>
   </si>
   <si>
     <t xml:space="preserve">9.49451637268066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31671524047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15669536590576</t>
+    <t xml:space="preserve">9.31671714782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15669631958008</t>
   </si>
   <si>
     <t xml:space="preserve">9.35227680206299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40561676025391</t>
+    <t xml:space="preserve">9.40561580657959</t>
   </si>
   <si>
     <t xml:space="preserve">9.69009494781494</t>
@@ -1667,28 +1667,28 @@
     <t xml:space="preserve">9.83233642578125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77899646759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44117641448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21003723144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58341598510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51229667663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67231559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85011672973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0990352630615</t>
+    <t xml:space="preserve">9.77899551391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44117546081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.210036277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58341503143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51229476928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6723165512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8501148223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0990362167358</t>
   </si>
   <si>
     <t xml:space="preserve">10.0279159545898</t>
@@ -1697,25 +1697,25 @@
     <t xml:space="preserve">9.99235534667969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0101356506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76121520996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88567543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2234964370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4368543624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6679964065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.414755821228</t>
+    <t xml:space="preserve">10.0101366043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76121616363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88567638397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2234954833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4368553161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6679954528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4147548675537</t>
   </si>
   <si>
     <t xml:space="preserve">11.3614149093628</t>
@@ -1727,10 +1727,10 @@
     <t xml:space="preserve">11.4325351715088</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6814556121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.894814491272</t>
+    <t xml:space="preserve">11.6814546585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8948154449463</t>
   </si>
   <si>
     <t xml:space="preserve">11.965934753418</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">12.1437349319458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6281147003174</t>
+    <t xml:space="preserve">11.6281156539917</t>
   </si>
   <si>
     <t xml:space="preserve">11.4001131057739</t>
@@ -1751,76 +1751,76 @@
     <t xml:space="preserve">11.6534490585327</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6896409988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1239290237427</t>
+    <t xml:space="preserve">11.689640045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.123929977417</t>
   </si>
   <si>
     <t xml:space="preserve">11.7982120513916</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1782169342041</t>
+    <t xml:space="preserve">12.1782159805298</t>
   </si>
   <si>
     <t xml:space="preserve">12.3229789733887</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9925098419189</t>
+    <t xml:space="preserve">12.9925088882446</t>
   </si>
   <si>
     <t xml:space="preserve">12.8296518325806</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7391729354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7753648757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3953609466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2867870330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6306018829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4496479034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2144060134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1058340072632</t>
+    <t xml:space="preserve">12.7391738891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7753639221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.395359992981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2867879867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6306009292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4496469497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2144069671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1058349609375</t>
   </si>
   <si>
     <t xml:space="preserve">11.8705940246582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9067840576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4724950790405</t>
+    <t xml:space="preserve">11.9067850112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4724941253662</t>
   </si>
   <si>
     <t xml:space="preserve">11.4182081222534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5810680389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8524990081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0877380371094</t>
+    <t xml:space="preserve">11.5810670852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8524980545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0877389907837</t>
   </si>
   <si>
     <t xml:space="preserve">11.8344030380249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.888689994812</t>
+    <t xml:space="preserve">11.8886890411377</t>
   </si>
   <si>
     <t xml:space="preserve">11.4363040924072</t>
@@ -1832,10 +1832,10 @@
     <t xml:space="preserve">11.2734451293945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1829671859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1648731231689</t>
+    <t xml:space="preserve">11.1829681396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1648721694946</t>
   </si>
   <si>
     <t xml:space="preserve">10.8391542434692</t>
@@ -1844,25 +1844,25 @@
     <t xml:space="preserve">10.6401052474976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6762971878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5134372711182</t>
+    <t xml:space="preserve">10.6762962341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5134363174438</t>
   </si>
   <si>
     <t xml:space="preserve">10.9115371704102</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2915391921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1467761993408</t>
+    <t xml:space="preserve">11.2915410995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1467771530151</t>
   </si>
   <si>
     <t xml:space="preserve">10.766773223877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1105861663818</t>
+    <t xml:space="preserve">11.1105871200562</t>
   </si>
   <si>
     <t xml:space="preserve">11.1286821365356</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">10.6220092773438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0020141601562</t>
+    <t xml:space="preserve">11.0020132064819</t>
   </si>
   <si>
     <t xml:space="preserve">10.6039142608643</t>
@@ -1883,19 +1883,19 @@
     <t xml:space="preserve">10.2781972885132</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3143873214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89819431304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93438339233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80771636962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68104839324951</t>
+    <t xml:space="preserve">10.3143882751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89819240570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9343843460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80771541595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6810474395752</t>
   </si>
   <si>
     <t xml:space="preserve">9.95247936248779</t>
@@ -1904,16 +1904,16 @@
     <t xml:space="preserve">10.2420063018799</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4772472381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3867683410645</t>
+    <t xml:space="preserve">10.4772462844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3867692947388</t>
   </si>
   <si>
     <t xml:space="preserve">10.4410552978516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55438041687012</t>
+    <t xml:space="preserve">9.55438137054443</t>
   </si>
   <si>
     <t xml:space="preserve">10.1153392791748</t>
@@ -1922,22 +1922,22 @@
     <t xml:space="preserve">10.3505783081055</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4048652648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7486791610718</t>
+    <t xml:space="preserve">10.4048643112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7486782073975</t>
   </si>
   <si>
     <t xml:space="preserve">11.0201101303101</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8572511672974</t>
+    <t xml:space="preserve">10.857250213623</t>
   </si>
   <si>
     <t xml:space="preserve">10.8753461837769</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5858182907104</t>
+    <t xml:space="preserve">10.5858192443848</t>
   </si>
   <si>
     <t xml:space="preserve">10.8029642105103</t>
@@ -1946,13 +1946,13 @@
     <t xml:space="preserve">10.7124872207642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7848701477051</t>
+    <t xml:space="preserve">10.7848682403564</t>
   </si>
   <si>
     <t xml:space="preserve">11.2372550964355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3096351623535</t>
+    <t xml:space="preserve">11.3096361160278</t>
   </si>
   <si>
     <t xml:space="preserve">11.4543991088867</t>
@@ -1964,19 +1964,19 @@
     <t xml:space="preserve">11.9972620010376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.160120010376</t>
+    <t xml:space="preserve">12.1601209640503</t>
   </si>
   <si>
     <t xml:space="preserve">12.0515480041504</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0334520339966</t>
+    <t xml:space="preserve">12.0334529876709</t>
   </si>
   <si>
     <t xml:space="preserve">11.9429759979248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7620210647583</t>
+    <t xml:space="preserve">11.7620220184326</t>
   </si>
   <si>
     <t xml:space="preserve">10.9477272033691</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">10.9658231735229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1877193450928</t>
+    <t xml:space="preserve">10.1877212524414</t>
   </si>
   <si>
     <t xml:space="preserve">9.98867034912109</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">10.0429573059082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91628932952881</t>
+    <t xml:space="preserve">9.91628837585449</t>
   </si>
   <si>
     <t xml:space="preserve">10.1696243286133</t>
@@ -2006,13 +2006,13 @@
     <t xml:space="preserve">10.4229602813721</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1334342956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.332483291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2239112854004</t>
+    <t xml:space="preserve">10.13343334198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3324842453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2239122390747</t>
   </si>
   <si>
     <t xml:space="preserve">10.097243309021</t>
@@ -2021,10 +2021,10 @@
     <t xml:space="preserve">10.0610523223877</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0791473388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1515293121338</t>
+    <t xml:space="preserve">10.0791482925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1515312194824</t>
   </si>
   <si>
     <t xml:space="preserve">11.056300163269</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">10.5496282577515</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3686742782593</t>
+    <t xml:space="preserve">10.3686752319336</t>
   </si>
   <si>
     <t xml:space="preserve">9.8258113861084</t>
@@ -2045,7 +2045,7 @@
     <t xml:space="preserve">9.77152538299561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69914245605469</t>
+    <t xml:space="preserve">9.699143409729</t>
   </si>
   <si>
     <t xml:space="preserve">9.51819038391113</t>
@@ -2063,22 +2063,22 @@
     <t xml:space="preserve">11.3639221191406</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9791650772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4677419662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3772668838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3820171356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5629720687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6172590255737</t>
+    <t xml:space="preserve">11.9791669845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4677429199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3772659301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3820180892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5629711151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6172580718994</t>
   </si>
   <si>
     <t xml:space="preserve">11.0924911499023</t>
@@ -2093,70 +2093,70 @@
     <t xml:space="preserve">8.8034200668335</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68580055236816</t>
+    <t xml:space="preserve">8.68579959869385</t>
   </si>
   <si>
     <t xml:space="preserve">8.43246459960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04816484451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3286452293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24721479415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18388080596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58673191070557</t>
+    <t xml:space="preserve">7.0481653213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32864427566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24721527099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18388032913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58673238754272</t>
   </si>
   <si>
     <t xml:space="preserve">6.65006589889526</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96673536300659</t>
+    <t xml:space="preserve">6.96673583984375</t>
   </si>
   <si>
     <t xml:space="preserve">6.9757833480835</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16578531265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.057213306427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28340530395508</t>
+    <t xml:space="preserve">7.16578483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05721235275269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28340625762939</t>
   </si>
   <si>
     <t xml:space="preserve">7.60912275314331</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76293420791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34198760986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04341220855713</t>
+    <t xml:space="preserve">7.7629337310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3419885635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04341316223145</t>
   </si>
   <si>
     <t xml:space="preserve">8.61341857910156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41436862945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25151062011719</t>
+    <t xml:space="preserve">8.41436958312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25150966644287</t>
   </si>
   <si>
     <t xml:space="preserve">8.93008804321289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35533046722412</t>
+    <t xml:space="preserve">9.35533142089844</t>
   </si>
   <si>
     <t xml:space="preserve">9.04770946502686</t>
@@ -2165,10 +2165,10 @@
     <t xml:space="preserve">9.26485443115234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50009346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8620023727417</t>
+    <t xml:space="preserve">9.50009441375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86200141906738</t>
   </si>
   <si>
     <t xml:space="preserve">11.2191581726074</t>
@@ -2177,34 +2177,34 @@
     <t xml:space="preserve">10.9839191436768</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6582012176514</t>
+    <t xml:space="preserve">10.6582002639771</t>
   </si>
   <si>
     <t xml:space="preserve">9.9705753326416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2058143615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84390830993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4591503143311</t>
+    <t xml:space="preserve">10.2058153152466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84390735626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4591512680054</t>
   </si>
   <si>
     <t xml:space="preserve">10.9296321868896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.730583190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8210601806641</t>
+    <t xml:space="preserve">10.7305812835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8210592269897</t>
   </si>
   <si>
     <t xml:space="preserve">12.0696439743042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5582208633423</t>
+    <t xml:space="preserve">12.558219909668</t>
   </si>
   <si>
     <t xml:space="preserve">12.8477458953857</t>
@@ -2222,7 +2222,7 @@
     <t xml:space="preserve">12.4315519332886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5944108963013</t>
+    <t xml:space="preserve">12.594409942627</t>
   </si>
   <si>
     <t xml:space="preserve">12.6486968994141</t>
@@ -2231,31 +2231,31 @@
     <t xml:space="preserve">12.7210788726807</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8658418655396</t>
+    <t xml:space="preserve">12.8658428192139</t>
   </si>
   <si>
     <t xml:space="preserve">13.1553678512573</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0287008285522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.119176864624</t>
+    <t xml:space="preserve">13.0286998748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1191787719727</t>
   </si>
   <si>
     <t xml:space="preserve">12.9382238388062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.082986831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3725137710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3544178009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4534864425659</t>
+    <t xml:space="preserve">13.0829877853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3725128173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3544187545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4534873962402</t>
   </si>
   <si>
     <t xml:space="preserve">16.2496852874756</t>
@@ -2264,28 +2264,28 @@
     <t xml:space="preserve">16.2858753204346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3763542175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6477851867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8334884643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0687294006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8696813583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9239673614502</t>
+    <t xml:space="preserve">16.3763523101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6477832794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8334894180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0687313079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8696804046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9239692687988</t>
   </si>
   <si>
     <t xml:space="preserve">15.9058713912964</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8515844345093</t>
+    <t xml:space="preserve">15.8515853881836</t>
   </si>
   <si>
     <t xml:space="preserve">16.0144443511963</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">15.7972984313965</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2677822113037</t>
+    <t xml:space="preserve">16.2677803039551</t>
   </si>
   <si>
     <t xml:space="preserve">16.0325393676758</t>
@@ -2306,22 +2306,22 @@
     <t xml:space="preserve">15.7249164581299</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4125442504883</t>
+    <t xml:space="preserve">16.4125423431396</t>
   </si>
   <si>
     <t xml:space="preserve">15.8153944015503</t>
   </si>
   <si>
-    <t xml:space="preserve">15.942063331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6344423294067</t>
+    <t xml:space="preserve">15.9420623779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6344404220581</t>
   </si>
   <si>
     <t xml:space="preserve">16.1049213409424</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9601573944092</t>
+    <t xml:space="preserve">15.9601564407349</t>
   </si>
   <si>
     <t xml:space="preserve">15.6887264251709</t>
@@ -2330,28 +2330,28 @@
     <t xml:space="preserve">15.6163444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8925294876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6525363922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3630094528198</t>
+    <t xml:space="preserve">14.8925285339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6525344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3630104064941</t>
   </si>
   <si>
     <t xml:space="preserve">15.4896774291992</t>
   </si>
   <si>
-    <t xml:space="preserve">15.145866394043</t>
+    <t xml:space="preserve">15.1458654403687</t>
   </si>
   <si>
     <t xml:space="preserve">15.0372934341431</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7430143356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8201456069946</t>
+    <t xml:space="preserve">15.7430124282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8201465606689</t>
   </si>
   <si>
     <t xml:space="preserve">15.2906274795532</t>
@@ -2366,7 +2366,7 @@
     <t xml:space="preserve">18.0230350494385</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1359062194824</t>
+    <t xml:space="preserve">19.1359024047852</t>
   </si>
   <si>
     <t xml:space="preserve">18.2763729095459</t>
@@ -2378,67 +2378,67 @@
     <t xml:space="preserve">17.4258861541748</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7335071563721</t>
+    <t xml:space="preserve">17.7335090637207</t>
   </si>
   <si>
     <t xml:space="preserve">17.2992191314697</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0458831787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0277881622314</t>
+    <t xml:space="preserve">17.0458850860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0277862548828</t>
   </si>
   <si>
     <t xml:space="preserve">16.7020702362061</t>
   </si>
   <si>
-    <t xml:space="preserve">17.009693145752</t>
+    <t xml:space="preserve">17.0096912384033</t>
   </si>
   <si>
     <t xml:space="preserve">17.4077930450439</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5025653839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1406536102295</t>
+    <t xml:space="preserve">18.5025672912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1406574249268</t>
   </si>
   <si>
     <t xml:space="preserve">17.96875</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4982662200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9868450164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5930404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1544551849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2449321746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1182632446289</t>
+    <t xml:space="preserve">17.49827003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9868431091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5930423736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1544532775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.244930267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1182670593262</t>
   </si>
   <si>
     <t xml:space="preserve">16.8106422424316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8287372589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9735012054443</t>
+    <t xml:space="preserve">16.8287391662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9735050201416</t>
   </si>
   <si>
     <t xml:space="preserve">16.9192161560059</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0639781951904</t>
+    <t xml:space="preserve">17.0639801025391</t>
   </si>
   <si>
     <t xml:space="preserve">16.8468360900879</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">16.9011211395264</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3173160552979</t>
+    <t xml:space="preserve">17.3173141479492</t>
   </si>
   <si>
     <t xml:space="preserve">17.2087421417236</t>
@@ -2456,16 +2456,16 @@
     <t xml:space="preserve">17.2268371582031</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3668479919434</t>
+    <t xml:space="preserve">18.366849899292</t>
   </si>
   <si>
     <t xml:space="preserve">18.4573268890381</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6382789611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7287559509277</t>
+    <t xml:space="preserve">18.6382808685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7287578582764</t>
   </si>
   <si>
     <t xml:space="preserve">18.9549503326416</t>
@@ -2477,16 +2477,16 @@
     <t xml:space="preserve">19.6335277557373</t>
   </si>
   <si>
-    <t xml:space="preserve">19.678768157959</t>
+    <t xml:space="preserve">19.6787662506104</t>
   </si>
   <si>
     <t xml:space="preserve">19.5430507659912</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0454254150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.000186920166</t>
+    <t xml:space="preserve">19.0454235076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0001888275146</t>
   </si>
   <si>
     <t xml:space="preserve">19.3168563842773</t>
@@ -2495,13 +2495,13 @@
     <t xml:space="preserve">18.3216094970703</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2311344146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0906658172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6835174560547</t>
+    <t xml:space="preserve">18.2311325073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0906639099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6835193634033</t>
   </si>
   <si>
     <t xml:space="preserve">18.0954189300537</t>
@@ -2513,13 +2513,13 @@
     <t xml:space="preserve">17.570650100708</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8239860534668</t>
+    <t xml:space="preserve">17.8239879608154</t>
   </si>
   <si>
     <t xml:space="preserve">17.6430320739746</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8058910369873</t>
+    <t xml:space="preserve">17.8058891296387</t>
   </si>
   <si>
     <t xml:space="preserve">19.2716178894043</t>
@@ -2528,7 +2528,7 @@
     <t xml:space="preserve">19.1811428070068</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2668685913086</t>
+    <t xml:space="preserve">20.26686668396</t>
   </si>
   <si>
     <t xml:space="preserve">20.4930610656738</t>
@@ -2537,40 +2537,40 @@
     <t xml:space="preserve">20.9906845092773</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5835399627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3573455810547</t>
+    <t xml:space="preserve">20.5835380554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3573436737061</t>
   </si>
   <si>
     <t xml:space="preserve">19.9049587249756</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7692432403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7192535400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9954376220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2263832092285</t>
+    <t xml:space="preserve">19.7692451477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7192516326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9954357147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2263813018799</t>
   </si>
   <si>
     <t xml:space="preserve">19.4525737762451</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4073371887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6249351501465</t>
+    <t xml:space="preserve">19.4073333740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6249370574951</t>
   </si>
   <si>
     <t xml:space="preserve">17.7877941131592</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4978122711182</t>
+    <t xml:space="preserve">19.4978103637695</t>
   </si>
   <si>
     <t xml:space="preserve">20.0859146118164</t>
@@ -2582,22 +2582,22 @@
     <t xml:space="preserve">19.8597221374512</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6740169525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0359230041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8097305297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6287746429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.312105178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4478225708008</t>
+    <t xml:space="preserve">20.674015045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0359210968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8097286224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.628776550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3121070861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4478244781494</t>
   </si>
   <si>
     <t xml:space="preserve">20.8821105957031</t>
@@ -2606,10 +2606,10 @@
     <t xml:space="preserve">21.2802104949951</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3344993591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.587833404541</t>
+    <t xml:space="preserve">21.3344974517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5878353118896</t>
   </si>
   <si>
     <t xml:space="preserve">21.6602153778076</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">22.1668872833252</t>
   </si>
   <si>
-    <t xml:space="preserve">22.619270324707</t>
+    <t xml:space="preserve">22.6192722320557</t>
   </si>
   <si>
     <t xml:space="preserve">22.8726081848145</t>
@@ -2627,13 +2627,13 @@
     <t xml:space="preserve">23.9040470123291</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7821311950684</t>
+    <t xml:space="preserve">22.7821292877197</t>
   </si>
   <si>
     <t xml:space="preserve">21.8592643737793</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0040283203125</t>
+    <t xml:space="preserve">22.0040264129639</t>
   </si>
   <si>
     <t xml:space="preserve">22.2573642730713</t>
@@ -2645,31 +2645,31 @@
     <t xml:space="preserve">22.1126003265381</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0583114624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6011753082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6373672485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.420223236084</t>
+    <t xml:space="preserve">22.058313369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6011772155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6373653411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4202213287354</t>
   </si>
   <si>
     <t xml:space="preserve">22.4021282196045</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3525943756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2621154785156</t>
+    <t xml:space="preserve">21.3525924682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2621173858643</t>
   </si>
   <si>
     <t xml:space="preserve">22.0945053100586</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5830783843994</t>
+    <t xml:space="preserve">22.5830821990967</t>
   </si>
   <si>
     <t xml:space="preserve">23.0354652404785</t>
@@ -2678,55 +2678,55 @@
     <t xml:space="preserve">23.0173721313477</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3611831665039</t>
+    <t xml:space="preserve">23.3611850738525</t>
   </si>
   <si>
     <t xml:space="preserve">23.2707061767578</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0440578460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7726268768311</t>
+    <t xml:space="preserve">25.044059753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7726249694824</t>
   </si>
   <si>
     <t xml:space="preserve">24.9716758728027</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0621547698975</t>
+    <t xml:space="preserve">25.0621528625488</t>
   </si>
   <si>
     <t xml:space="preserve">25.9126377105713</t>
   </si>
   <si>
-    <t xml:space="preserve">26.238353729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6765747070312</t>
+    <t xml:space="preserve">26.2383575439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6765727996826</t>
   </si>
   <si>
     <t xml:space="preserve">26.7130928039551</t>
   </si>
   <si>
-    <t xml:space="preserve">26.585277557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.658317565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8226451873779</t>
+    <t xml:space="preserve">26.5852794647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6583156585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8226470947266</t>
   </si>
   <si>
     <t xml:space="preserve">26.95046043396</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5712718963623</t>
+    <t xml:space="preserve">27.5712699890137</t>
   </si>
   <si>
     <t xml:space="preserve">27.6260471343994</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0642642974854</t>
+    <t xml:space="preserve">28.064266204834</t>
   </si>
   <si>
     <t xml:space="preserve">28.283374786377</t>
@@ -2735,13 +2735,13 @@
     <t xml:space="preserve">29.8171424865723</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5980319976807</t>
+    <t xml:space="preserve">29.5980339050293</t>
   </si>
   <si>
     <t xml:space="preserve">28.958963394165</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1275482177734</t>
+    <t xml:space="preserve">30.1275444030762</t>
   </si>
   <si>
     <t xml:space="preserve">29.6528091430664</t>
@@ -2750,28 +2750,28 @@
     <t xml:space="preserve">30.1092872619629</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9632129669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4014301300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2188396453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2961311340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8213920593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1683177947998</t>
+    <t xml:space="preserve">29.9632148742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4014320373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2188415527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2961292266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8213901519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1683197021484</t>
   </si>
   <si>
     <t xml:space="preserve">30.2371006011963</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4154434204102</t>
+    <t xml:space="preserve">29.4154415130615</t>
   </si>
   <si>
     <t xml:space="preserve">29.8536605834961</t>
@@ -2780,25 +2780,25 @@
     <t xml:space="preserve">29.178071975708</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1458072662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7075881958008</t>
+    <t xml:space="preserve">30.1458053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7075901031494</t>
   </si>
   <si>
     <t xml:space="preserve">30.0545120239258</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8664169311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5462532043457</t>
+    <t xml:space="preserve">32.8664131164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.546257019043</t>
   </si>
   <si>
     <t xml:space="preserve">34.0532569885254</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0855293273926</t>
+    <t xml:space="preserve">33.0855255126953</t>
   </si>
   <si>
     <t xml:space="preserve">33.7245903015137</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">33.1403007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2863693237305</t>
+    <t xml:space="preserve">33.2863731384277</t>
   </si>
   <si>
     <t xml:space="preserve">32.2273445129395</t>
@@ -2828,46 +2828,46 @@
     <t xml:space="preserve">32.8846740722656</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7568626403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6473083496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0307502746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7751235961914</t>
+    <t xml:space="preserve">32.7568664550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6473045349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0307464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7751197814941</t>
   </si>
   <si>
     <t xml:space="preserve">32.4099349975586</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6655616760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.692325592041</t>
+    <t xml:space="preserve">32.6655654907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6923294067383</t>
   </si>
   <si>
     <t xml:space="preserve">35.605281829834</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2400970458984</t>
+    <t xml:space="preserve">35.2401008605957</t>
   </si>
   <si>
     <t xml:space="preserve">35.8791694641113</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4774742126465</t>
+    <t xml:space="preserve">35.4774703979492</t>
   </si>
   <si>
     <t xml:space="preserve">35.0940284729004</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5870208740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7878723144531</t>
+    <t xml:space="preserve">35.5870246887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7878799438477</t>
   </si>
   <si>
     <t xml:space="preserve">36.0435028076172</t>
@@ -2876,25 +2876,25 @@
     <t xml:space="preserve">36.8469047546387</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9101829528809</t>
+    <t xml:space="preserve">38.9101791381836</t>
   </si>
   <si>
     <t xml:space="preserve">38.4354438781738</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4944763183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3849182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.220588684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1292915344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1980781555176</t>
+    <t xml:space="preserve">39.4944725036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3849220275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2205848693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1292953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1980743408203</t>
   </si>
   <si>
     <t xml:space="preserve">37.6137886047363</t>
@@ -2912,31 +2912,31 @@
     <t xml:space="preserve">36.7008323669434</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2120819091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5590057373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0154838562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6503067016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6235427856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2316017150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9942283630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3594093322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0490112304688</t>
+    <t xml:space="preserve">37.212085723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.559009552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0154876708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6503028869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6235389709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2315979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9942245483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3594169616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0490074157715</t>
   </si>
   <si>
     <t xml:space="preserve">34.7836227416992</t>
@@ -2951,19 +2951,19 @@
     <t xml:space="preserve">32.9577102661133</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6332969665527</t>
+    <t xml:space="preserve">33.63330078125</t>
   </si>
   <si>
     <t xml:space="preserve">35.513988494873</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4817237854004</t>
+    <t xml:space="preserve">36.4817161560059</t>
   </si>
   <si>
     <t xml:space="preserve">36.3173866271973</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6095352172852</t>
+    <t xml:space="preserve">36.6095314025879</t>
   </si>
   <si>
     <t xml:space="preserve">37.7781181335449</t>
@@ -2978,25 +2978,25 @@
     <t xml:space="preserve">36.7190895080566</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8426475524902</t>
+    <t xml:space="preserve">35.8426513671875</t>
   </si>
   <si>
     <t xml:space="preserve">34.9662132263184</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1488075256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4409523010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8876724243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5267448425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8006324768066</t>
+    <t xml:space="preserve">35.1488037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4409484863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8876686096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5267486572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8006248474121</t>
   </si>
   <si>
     <t xml:space="preserve">37.6685638427734</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">35.4226913452148</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2583618164062</t>
+    <t xml:space="preserve">35.258358001709</t>
   </si>
   <si>
     <t xml:space="preserve">34.9114379882812</t>
@@ -3014,10 +3014,10 @@
     <t xml:space="preserve">34.3636627197266</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8341484069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5967826843262</t>
+    <t xml:space="preserve">33.8341522216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5967788696289</t>
   </si>
   <si>
     <t xml:space="preserve">35.3313980102539</t>
@@ -3035,16 +3035,16 @@
     <t xml:space="preserve">34.7105865478516</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3454055786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0715179443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1950836181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6150360107422</t>
+    <t xml:space="preserve">34.345401763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0715217590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1950798034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6150436401367</t>
   </si>
   <si>
     <t xml:space="preserve">33.9254455566406</t>
@@ -3059,10 +3059,10 @@
     <t xml:space="preserve">34.5827713012695</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7288436889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0027351379395</t>
+    <t xml:space="preserve">34.7288475036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0027313232422</t>
   </si>
   <si>
     <t xml:space="preserve">34.8383979797363</t>
@@ -3071,37 +3071,37 @@
     <t xml:space="preserve">34.8749198913574</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5377464294434</t>
+    <t xml:space="preserve">32.5377502441406</t>
   </si>
   <si>
     <t xml:space="preserve">32.1725692749023</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1360511779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4519577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8901786804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1640663146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4294509887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1007843017578</t>
+    <t xml:space="preserve">32.1360473632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4519596099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8901805877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1640644073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4294471740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1007862091064</t>
   </si>
   <si>
     <t xml:space="preserve">27.6808261871338</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9954833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2693710327148</t>
+    <t xml:space="preserve">28.9954814910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2693691253662</t>
   </si>
   <si>
     <t xml:space="preserve">28.6850776672363</t>
@@ -3113,7 +3113,7 @@
     <t xml:space="preserve">26.8956832885742</t>
   </si>
   <si>
-    <t xml:space="preserve">27.845157623291</t>
+    <t xml:space="preserve">27.8451557159424</t>
   </si>
   <si>
     <t xml:space="preserve">27.9729690551758</t>
@@ -3122,7 +3122,7 @@
     <t xml:space="preserve">28.6668186187744</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1232948303223</t>
+    <t xml:space="preserve">29.1232967376709</t>
   </si>
   <si>
     <t xml:space="preserve">28.9224472045898</t>
@@ -3134,13 +3134,13 @@
     <t xml:space="preserve">27.7538623809814</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3479099273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5445098876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7496109008789</t>
+    <t xml:space="preserve">26.3479118347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.544506072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7496089935303</t>
   </si>
   <si>
     <t xml:space="preserve">26.7861289978027</t>
@@ -3149,19 +3149,19 @@
     <t xml:space="preserve">26.5670204162598</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9547119140625</t>
+    <t xml:space="preserve">27.9547138214111</t>
   </si>
   <si>
     <t xml:space="preserve">27.4251976013184</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4799747467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1147937774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7313537597656</t>
+    <t xml:space="preserve">27.4799766540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1147918701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.731351852417</t>
   </si>
   <si>
     <t xml:space="preserve">27.4069385528564</t>
@@ -3176,16 +3176,16 @@
     <t xml:space="preserve">27.4434566497803</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3113899230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5542621612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7045860290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0977840423584</t>
+    <t xml:space="preserve">26.3113918304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5542640686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.70458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.097785949707</t>
   </si>
   <si>
     <t xml:space="preserve">22.0022392272949</t>
@@ -3197,7 +3197,7 @@
     <t xml:space="preserve">20.7423572540283</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6047897338867</t>
+    <t xml:space="preserve">22.6047916412354</t>
   </si>
   <si>
     <t xml:space="preserve">21.8744239807129</t>
@@ -3206,19 +3206,19 @@
     <t xml:space="preserve">22.5134944915771</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1525630950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2073421478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5402545928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6680698394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8689212799072</t>
+    <t xml:space="preserve">23.1525650024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2073402404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5402565002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6680717468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8689193725586</t>
   </si>
   <si>
     <t xml:space="preserve">24.4489612579346</t>
@@ -3227,28 +3227,28 @@
     <t xml:space="preserve">25.2341022491455</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5585136413574</t>
+    <t xml:space="preserve">24.5585155487061</t>
   </si>
   <si>
     <t xml:space="preserve">24.0289993286133</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1385555267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0472602844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3984355926514</t>
+    <t xml:space="preserve">24.138557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0472621917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3984317779541</t>
   </si>
   <si>
     <t xml:space="preserve">25.4166946411133</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2115936279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0837783813477</t>
+    <t xml:space="preserve">24.2115917205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.083776473999</t>
   </si>
   <si>
     <t xml:space="preserve">23.8098926544189</t>
@@ -3260,10 +3260,10 @@
     <t xml:space="preserve">22.4221973419189</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7326049804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6778259277344</t>
+    <t xml:space="preserve">22.7326030731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.677827835083</t>
   </si>
   <si>
     <t xml:space="preserve">22.2761249542236</t>
@@ -3272,22 +3272,22 @@
     <t xml:space="preserve">21.9109439849854</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2213497161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8379077911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0935344696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8239002227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5457630157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0710258483887</t>
+    <t xml:space="preserve">22.2213478088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8379058837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0935363769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.823902130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5457611083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.07102394104</t>
   </si>
   <si>
     <t xml:space="preserve">21.9657211303711</t>
@@ -3308,16 +3308,16 @@
     <t xml:space="preserve">20.0850315093994</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3729267120361</t>
+    <t xml:space="preserve">19.3729248046875</t>
   </si>
   <si>
     <t xml:space="preserve">19.8659229278564</t>
   </si>
   <si>
-    <t xml:space="preserve">19.957218170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9024410247803</t>
+    <t xml:space="preserve">19.9572162628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9024391174316</t>
   </si>
   <si>
     <t xml:space="preserve">20.2493648529053</t>
@@ -3326,7 +3326,7 @@
     <t xml:space="preserve">20.9614677429199</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8519134521484</t>
+    <t xml:space="preserve">20.8519153594971</t>
   </si>
   <si>
     <t xml:space="preserve">20.7241020202637</t>
@@ -3338,13 +3338,13 @@
     <t xml:space="preserve">21.3449096679688</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3954391479492</t>
+    <t xml:space="preserve">20.3954372406006</t>
   </si>
   <si>
     <t xml:space="preserve">20.523250579834</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6693210601807</t>
+    <t xml:space="preserve">20.6693229675293</t>
   </si>
   <si>
     <t xml:space="preserve">22.1300525665283</t>
@@ -3353,13 +3353,13 @@
     <t xml:space="preserve">24.1933345794678</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6455612182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5177459716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7368564605713</t>
+    <t xml:space="preserve">23.6455593109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5177440643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7368545532227</t>
   </si>
   <si>
     <t xml:space="preserve">23.0533809661865</t>
@@ -70337,7 +70337,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6495486111</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>233718</v>
@@ -70358,6 +70358,32 @@
         <v>1774</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6495833333</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>111427</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>14.7600002288818</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>14.6800003051758</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>14.6800003051758</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>14.7399997711182</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1762</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TNXT.MI.xlsx
+++ b/data/TNXT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="1776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="1777">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,76 +47,76 @@
     <t xml:space="preserve">2.65150952339172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59350848197937</t>
+    <t xml:space="preserve">2.59350872039795</t>
   </si>
   <si>
     <t xml:space="preserve">2.53550672531128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52556347846985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48579096794128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52722072601318</t>
+    <t xml:space="preserve">2.52556371688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48579049110413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52722096443176</t>
   </si>
   <si>
     <t xml:space="preserve">2.48744797706604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47087574005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46921849250793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54047822952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49739074707031</t>
+    <t xml:space="preserve">2.47087621688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46921873092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54047846794128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49739122390747</t>
   </si>
   <si>
     <t xml:space="preserve">2.47916197776794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44436097145081</t>
+    <t xml:space="preserve">2.44436073303223</t>
   </si>
   <si>
     <t xml:space="preserve">2.39464473724365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34161448478699</t>
+    <t xml:space="preserve">2.34161472320557</t>
   </si>
   <si>
     <t xml:space="preserve">2.36150097846985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55207872390747</t>
+    <t xml:space="preserve">2.55207848548889</t>
   </si>
   <si>
     <t xml:space="preserve">2.58522272109985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6100800037384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56865048408508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63659501075745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68962550163269</t>
+    <t xml:space="preserve">2.61007976531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56865072250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63659524917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68962526321411</t>
   </si>
   <si>
     <t xml:space="preserve">2.73436975479126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72608351707458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77579951286316</t>
+    <t xml:space="preserve">2.72608327865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77579998970032</t>
   </si>
   <si>
     <t xml:space="preserve">2.58025097846985</t>
@@ -125,61 +125,61 @@
     <t xml:space="preserve">2.56202173233032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66808176040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62830877304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64322352409363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60842251777649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66642427444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65316653251648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62665176391602</t>
+    <t xml:space="preserve">2.66808152198792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62830901145935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64322376251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60842275619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66642451286316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65316700935364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62665200233459</t>
   </si>
   <si>
     <t xml:space="preserve">2.6929395198822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82551503181458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81722903251648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90008950233459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85865926742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89843225479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88351702690125</t>
+    <t xml:space="preserve">2.82551550865173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81722974777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90008902549744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85865950584412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89843201637268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88351726531982</t>
   </si>
   <si>
     <t xml:space="preserve">2.87523150444031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86694502830505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81888675689697</t>
+    <t xml:space="preserve">2.86694550514221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81888651847839</t>
   </si>
   <si>
     <t xml:space="preserve">2.82054400444031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85368752479553</t>
+    <t xml:space="preserve">2.85368776321411</t>
   </si>
   <si>
     <t xml:space="preserve">2.79237174987793</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">2.8570020198822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90671801567078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82882976531982</t>
+    <t xml:space="preserve">2.90671825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82882952690125</t>
   </si>
   <si>
     <t xml:space="preserve">2.85037350654602</t>
@@ -200,34 +200,34 @@
     <t xml:space="preserve">2.90837502479553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96306276321411</t>
+    <t xml:space="preserve">2.96306300163269</t>
   </si>
   <si>
     <t xml:space="preserve">2.95797729492188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88169693946838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89017271995544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86474561691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94950175285339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92407488822937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96645307540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1190128326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94272112846375</t>
+    <t xml:space="preserve">2.88169717788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89017248153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86474609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94950222969055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92407512664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96645331382751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11901330947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9427216053009</t>
   </si>
   <si>
     <t xml:space="preserve">2.94780707359314</t>
@@ -248,19 +248,19 @@
     <t xml:space="preserve">3.07037377357483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06866312026978</t>
+    <t xml:space="preserve">3.06866335868835</t>
   </si>
   <si>
     <t xml:space="preserve">3.06011080741882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99340081214905</t>
+    <t xml:space="preserve">2.99340033531189</t>
   </si>
   <si>
     <t xml:space="preserve">2.98484802246094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93524289131165</t>
+    <t xml:space="preserve">2.9352433681488</t>
   </si>
   <si>
     <t xml:space="preserve">2.98313736915588</t>
@@ -269,22 +269,22 @@
     <t xml:space="preserve">2.92498016357422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92326974868774</t>
+    <t xml:space="preserve">2.92326927185059</t>
   </si>
   <si>
     <t xml:space="preserve">2.9677426815033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0361635684967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05840015411377</t>
+    <t xml:space="preserve">3.03616333007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05839991569519</t>
   </si>
   <si>
     <t xml:space="preserve">3.05497908592224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08747863769531</t>
+    <t xml:space="preserve">3.08747839927673</t>
   </si>
   <si>
     <t xml:space="preserve">3.13879442214966</t>
@@ -296,19 +296,19 @@
     <t xml:space="preserve">3.19010972976685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15589952468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12339973449707</t>
+    <t xml:space="preserve">3.15589928627014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12339949607849</t>
   </si>
   <si>
     <t xml:space="preserve">3.12511014938354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14734673500061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16445159912109</t>
+    <t xml:space="preserve">3.14734697341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16445207595825</t>
   </si>
   <si>
     <t xml:space="preserve">3.16616249084473</t>
@@ -320,88 +320,88 @@
     <t xml:space="preserve">3.30129289627075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3868191242218</t>
+    <t xml:space="preserve">3.38681888580322</t>
   </si>
   <si>
     <t xml:space="preserve">3.48431777954102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52708101272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62629055976868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63655376434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64510607719421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74602723121643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67760634422302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71181678771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63484382629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5168182849884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50484418869019</t>
+    <t xml:space="preserve">3.52708125114441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62629103660583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63655400276184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64510679244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74602699279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67760610580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71181631088257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63484358787537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51681756973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50484442710876</t>
   </si>
   <si>
     <t xml:space="preserve">3.4945809841156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50655484199524</t>
+    <t xml:space="preserve">3.50655508041382</t>
   </si>
   <si>
     <t xml:space="preserve">3.48089742660522</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43129253387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35602998733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60063314437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64681720733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69471168518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69984340667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67589592933655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6656322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59721207618713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63313341140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57497549057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66050124168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68615913391113</t>
+    <t xml:space="preserve">3.43129229545593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35602951049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60063338279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64681673049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69471120834351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69984316825867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67589569091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66563272476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59721231460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63313317298889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57497501373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66050171852112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68615889549255</t>
   </si>
   <si>
     <t xml:space="preserve">3.7152373790741</t>
@@ -410,34 +410,34 @@
     <t xml:space="preserve">3.73747420310974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71010565757751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69129014015198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68958044052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73234224319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72036910057068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76313257217407</t>
+    <t xml:space="preserve">3.71010589599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69129037857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6895797252655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.732342004776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7203688621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76313185691833</t>
   </si>
   <si>
     <t xml:space="preserve">3.77168416976929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62115955352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64168524742126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70326447486877</t>
+    <t xml:space="preserve">3.62115979194641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64168548583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70326399803162</t>
   </si>
   <si>
     <t xml:space="preserve">3.7973427772522</t>
@@ -446,91 +446,91 @@
     <t xml:space="preserve">3.7545793056488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9085259437561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76655292510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72892165184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6673436164856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50997638702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49800229072571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48944973945618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47234463691711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40392398834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43642377853394</t>
+    <t xml:space="preserve">3.90852618217468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76655340194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72892189025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66734385490417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50997591018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49800252914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48944997787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47234487533569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40392422676086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43642401695251</t>
   </si>
   <si>
     <t xml:space="preserve">3.53221273422241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5185284614563</t>
+    <t xml:space="preserve">3.51852822303772</t>
   </si>
   <si>
     <t xml:space="preserve">3.46037125587463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50142288208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53563356399536</t>
+    <t xml:space="preserve">3.50142335891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53563332557678</t>
   </si>
   <si>
     <t xml:space="preserve">3.55615973472595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6433961391449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72550082206726</t>
+    <t xml:space="preserve">3.64339590072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72550058364868</t>
   </si>
   <si>
     <t xml:space="preserve">3.84865784645081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82984185218811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83155179023743</t>
+    <t xml:space="preserve">3.82984232902527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83155298233032</t>
   </si>
   <si>
     <t xml:space="preserve">3.87089443206787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84523582458496</t>
+    <t xml:space="preserve">3.84523630142212</t>
   </si>
   <si>
     <t xml:space="preserve">3.87431597709656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86405253410339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8572108745575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82471108436584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90681457519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00260448455811</t>
+    <t xml:space="preserve">3.86405301094055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85721063613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82471036911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90681552886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00260400772095</t>
   </si>
   <si>
     <t xml:space="preserve">4.17536640167236</t>
@@ -539,13 +539,13 @@
     <t xml:space="preserve">4.11378717422485</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00773572921753</t>
+    <t xml:space="preserve">4.00773620605469</t>
   </si>
   <si>
     <t xml:space="preserve">4.05220890045166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08128786087036</t>
+    <t xml:space="preserve">4.0812873840332</t>
   </si>
   <si>
     <t xml:space="preserve">4.00602531433105</t>
@@ -554,31 +554,31 @@
     <t xml:space="preserve">4.09839296340942</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01970863342285</t>
+    <t xml:space="preserve">4.01970911026001</t>
   </si>
   <si>
     <t xml:space="preserve">4.01115655899048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99576210975647</t>
+    <t xml:space="preserve">3.99576187133789</t>
   </si>
   <si>
     <t xml:space="preserve">4.0351037979126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06247186660767</t>
+    <t xml:space="preserve">4.06247234344482</t>
   </si>
   <si>
     <t xml:space="preserve">4.13773488998413</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1223406791687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14799785614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18905067443848</t>
+    <t xml:space="preserve">4.12234020233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14799737930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18905019760132</t>
   </si>
   <si>
     <t xml:space="preserve">4.25918102264404</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">4.20615577697754</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02141952514648</t>
+    <t xml:space="preserve">4.02142000198364</t>
   </si>
   <si>
     <t xml:space="preserve">3.99405169487</t>
@@ -599,58 +599,58 @@
     <t xml:space="preserve">4.01799869537354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02655124664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07615613937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12747144699097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11891937255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10523509979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09668302536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10181379318237</t>
+    <t xml:space="preserve">4.02655172348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07615661621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12747192382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11891889572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10523557662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09668207168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10181427001953</t>
   </si>
   <si>
     <t xml:space="preserve">4.0710244178772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09497213363647</t>
+    <t xml:space="preserve">4.09497261047363</t>
   </si>
   <si>
     <t xml:space="preserve">4.13089227676392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2164192199707</t>
+    <t xml:space="preserve">4.21641826629639</t>
   </si>
   <si>
     <t xml:space="preserve">4.52431106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54996967315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53713893890381</t>
+    <t xml:space="preserve">4.54996919631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53713989257812</t>
   </si>
   <si>
     <t xml:space="preserve">4.46444272994995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5029296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56707334518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6226658821106</t>
+    <t xml:space="preserve">4.50293016433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56707382202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62266540527344</t>
   </si>
   <si>
     <t xml:space="preserve">4.63549470901489</t>
@@ -665,10 +665,10 @@
     <t xml:space="preserve">4.57562637329102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61838912963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53286409378052</t>
+    <t xml:space="preserve">4.61838960647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53286361694336</t>
   </si>
   <si>
     <t xml:space="preserve">4.55852079391479</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">4.48154783248901</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51575803756714</t>
+    <t xml:space="preserve">4.5157585144043</t>
   </si>
   <si>
     <t xml:space="preserve">4.4901008605957</t>
@@ -686,16 +686,16 @@
     <t xml:space="preserve">4.51148223876953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63121795654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78516435623169</t>
+    <t xml:space="preserve">4.63121843338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78516387939453</t>
   </si>
   <si>
     <t xml:space="preserve">4.7595067024231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78944063186646</t>
+    <t xml:space="preserve">4.7894401550293</t>
   </si>
   <si>
     <t xml:space="preserve">4.73384952545166</t>
@@ -707,22 +707,22 @@
     <t xml:space="preserve">4.76378345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65687608718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69536209106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8279275894165</t>
+    <t xml:space="preserve">4.65687656402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69536256790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82792711257935</t>
   </si>
   <si>
     <t xml:space="preserve">4.90062427520752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91772890090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94338703155518</t>
+    <t xml:space="preserve">4.91772937774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94338798522949</t>
   </si>
   <si>
     <t xml:space="preserve">4.98614978790283</t>
@@ -731,13 +731,13 @@
     <t xml:space="preserve">5.04174184799194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02035999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0716757774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08022880554199</t>
+    <t xml:space="preserve">5.0203595161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07167625427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08022785186768</t>
   </si>
   <si>
     <t xml:space="preserve">4.99470281600952</t>
@@ -749,16 +749,16 @@
     <t xml:space="preserve">5.06050682067871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91728496551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94766569137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92596530914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90426445007324</t>
+    <t xml:space="preserve">4.91728544235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94766521453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92596483230591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9042649269104</t>
   </si>
   <si>
     <t xml:space="preserve">4.8218035697937</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">4.59178066253662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64386129379272</t>
+    <t xml:space="preserve">4.64386081695557</t>
   </si>
   <si>
     <t xml:space="preserve">4.73066186904907</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">4.65254163742065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60914087295532</t>
+    <t xml:space="preserve">4.60914039611816</t>
   </si>
   <si>
     <t xml:space="preserve">4.6568808555603</t>
@@ -797,13 +797,13 @@
     <t xml:space="preserve">4.53535985946655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47025871276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59612083435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47459888458252</t>
+    <t xml:space="preserve">4.47025918960571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59612035751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47459936141968</t>
   </si>
   <si>
     <t xml:space="preserve">4.48761892318726</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.46157884597778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41383743286133</t>
+    <t xml:space="preserve">4.41383838653564</t>
   </si>
   <si>
     <t xml:space="preserve">4.38779735565186</t>
@@ -821,13 +821,13 @@
     <t xml:space="preserve">4.39213800430298</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40949821472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55706071853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52234077453613</t>
+    <t xml:space="preserve">4.40949869155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55706024169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52234029769897</t>
   </si>
   <si>
     <t xml:space="preserve">4.57008075714111</t>
@@ -836,64 +836,64 @@
     <t xml:space="preserve">4.53969955444336</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47893810272217</t>
+    <t xml:space="preserve">4.47893905639648</t>
   </si>
   <si>
     <t xml:space="preserve">4.43553876876831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42251825332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4311990737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45289850234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51365947723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6872615814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60046052932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6395206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56139993667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58744096755981</t>
+    <t xml:space="preserve">4.42251873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43119859695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45289897918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51365900039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68726253509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60046100616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63952159881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56140089035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58744049072266</t>
   </si>
   <si>
     <t xml:space="preserve">4.61782121658325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64820194244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6048002243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58310079574585</t>
+    <t xml:space="preserve">4.64820051193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60480070114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58310031890869</t>
   </si>
   <si>
     <t xml:space="preserve">4.49629974365234</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50498008728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42685842514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49195957183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51799964904785</t>
+    <t xml:space="preserve">4.50497961044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42685890197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49196004867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51799917221069</t>
   </si>
   <si>
     <t xml:space="preserve">4.80878353118896</t>
@@ -908,37 +908,37 @@
     <t xml:space="preserve">4.8348240852356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74368333816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81312274932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71330261230469</t>
+    <t xml:space="preserve">4.74368286132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81312370300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71330213546753</t>
   </si>
   <si>
     <t xml:space="preserve">4.70462226867676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72632265090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69594240188599</t>
+    <t xml:space="preserve">4.72632312774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69594192504883</t>
   </si>
   <si>
     <t xml:space="preserve">4.7697229385376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84350347518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87822389602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8738842010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97370576858521</t>
+    <t xml:space="preserve">4.84350442886353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87822437286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87388467788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97370529174805</t>
   </si>
   <si>
     <t xml:space="preserve">4.97804546356201</t>
@@ -947,16 +947,16 @@
     <t xml:space="preserve">5.00842618942261</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07786750793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04314661026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14730739593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86086463928223</t>
+    <t xml:space="preserve">5.07786703109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04314613342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14730834960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86086368560791</t>
   </si>
   <si>
     <t xml:space="preserve">4.869544506073</t>
@@ -965,100 +965,100 @@
     <t xml:space="preserve">4.96502542495728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90860509872437</t>
+    <t xml:space="preserve">4.90860462188721</t>
   </si>
   <si>
     <t xml:space="preserve">4.99974584579468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99106550216675</t>
+    <t xml:space="preserve">4.99106597900391</t>
   </si>
   <si>
     <t xml:space="preserve">5.15598773956299</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12994718551636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29486989974976</t>
+    <t xml:space="preserve">5.12994813919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2948694229126</t>
   </si>
   <si>
     <t xml:space="preserve">5.41639137268066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48583269119263</t>
+    <t xml:space="preserve">5.48583221435547</t>
   </si>
   <si>
     <t xml:space="preserve">5.43375158309937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4814920425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42073154449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39469146728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35563087463379</t>
+    <t xml:space="preserve">5.48149299621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42073106765747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.394690990448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35563039779663</t>
   </si>
   <si>
     <t xml:space="preserve">5.33393049240112</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37299060821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33827018737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20806884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16466808319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26449060440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25146961212158</t>
+    <t xml:space="preserve">5.37299108505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33827066421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20806932449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16466760635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26449012756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25147008895874</t>
   </si>
   <si>
     <t xml:space="preserve">5.26014995574951</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18636798858643</t>
+    <t xml:space="preserve">5.18636846542358</t>
   </si>
   <si>
     <t xml:space="preserve">5.20372867584229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19504880905151</t>
+    <t xml:space="preserve">5.19504928588867</t>
   </si>
   <si>
     <t xml:space="preserve">5.16900825500488</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18202781677246</t>
+    <t xml:space="preserve">5.18202877044678</t>
   </si>
   <si>
     <t xml:space="preserve">5.19938898086548</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22542953491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42507219314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61603450775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72887516021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71151494979858</t>
+    <t xml:space="preserve">5.22542905807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42507123947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61603403091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72887563705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71151542663574</t>
   </si>
   <si>
     <t xml:space="preserve">5.78963661193848</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">5.95455932617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03268003463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1715612411499</t>
+    <t xml:space="preserve">6.03267955780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17156171798706</t>
   </si>
   <si>
     <t xml:space="preserve">6.28440284729004</t>
@@ -1115,13 +1115,13 @@
     <t xml:space="preserve">6.40592432022095</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07608032226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98927879333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04135990142822</t>
+    <t xml:space="preserve">6.07607984542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98927927017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04136037826538</t>
   </si>
   <si>
     <t xml:space="preserve">6.22364234924316</t>
@@ -1130,22 +1130,22 @@
     <t xml:space="preserve">6.1368408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19760131835938</t>
+    <t xml:space="preserve">6.19760179519653</t>
   </si>
   <si>
     <t xml:space="preserve">6.15420150756836</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05003929138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89379787445068</t>
+    <t xml:space="preserve">6.05003976821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89379739761353</t>
   </si>
   <si>
     <t xml:space="preserve">5.90247821807861</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70283555984497</t>
+    <t xml:space="preserve">5.70283508300781</t>
   </si>
   <si>
     <t xml:space="preserve">5.50319290161133</t>
@@ -1154,10 +1154,10 @@
     <t xml:space="preserve">5.5813136100769</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72019529342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.763596534729</t>
+    <t xml:space="preserve">5.72019577026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76359605789185</t>
   </si>
   <si>
     <t xml:space="preserve">5.91983842849731</t>
@@ -1166,31 +1166,31 @@
     <t xml:space="preserve">5.99795913696289</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83303642272949</t>
+    <t xml:space="preserve">5.83303689956665</t>
   </si>
   <si>
     <t xml:space="preserve">5.79831647872925</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65943479537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51187324523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54659271240234</t>
+    <t xml:space="preserve">5.6594352722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5118727684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54659366607666</t>
   </si>
   <si>
     <t xml:space="preserve">5.58999395370483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52055311203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3816704750061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44243144989014</t>
+    <t xml:space="preserve">5.52055358886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38167095184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44243192672729</t>
   </si>
   <si>
     <t xml:space="preserve">5.46847248077393</t>
@@ -1199,19 +1199,19 @@
     <t xml:space="preserve">5.67679500579834</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6420750617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55527305603027</t>
+    <t xml:space="preserve">5.64207458496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55527353286743</t>
   </si>
   <si>
     <t xml:space="preserve">5.53791332244873</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57263422012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5292329788208</t>
+    <t xml:space="preserve">5.57263374328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52923345565796</t>
   </si>
   <si>
     <t xml:space="preserve">5.39903116226196</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">5.77227640151978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73755550384521</t>
+    <t xml:space="preserve">5.73755598068237</t>
   </si>
   <si>
     <t xml:space="preserve">5.40771150588989</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">5.24278926849365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0691876411438</t>
+    <t xml:space="preserve">5.06918716430664</t>
   </si>
   <si>
     <t xml:space="preserve">4.98238563537598</t>
@@ -1250,19 +1250,19 @@
     <t xml:space="preserve">5.07618808746338</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15619802474976</t>
+    <t xml:space="preserve">5.1561975479126</t>
   </si>
   <si>
     <t xml:space="preserve">5.08507776260376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24509763717651</t>
+    <t xml:space="preserve">5.24509859085083</t>
   </si>
   <si>
     <t xml:space="preserve">5.11174774169922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13841772079468</t>
+    <t xml:space="preserve">5.13841819763184</t>
   </si>
   <si>
     <t xml:space="preserve">5.20953798294067</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">5.04951763153076</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94283771514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77392768859863</t>
+    <t xml:space="preserve">4.94283819198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77392816543579</t>
   </si>
   <si>
     <t xml:space="preserve">4.90727806091309</t>
@@ -1298,28 +1298,28 @@
     <t xml:space="preserve">4.92505788803101</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88949871063232</t>
+    <t xml:space="preserve">4.88949823379517</t>
   </si>
   <si>
     <t xml:space="preserve">5.02284812927246</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97839832305908</t>
+    <t xml:space="preserve">4.97839736938477</t>
   </si>
   <si>
     <t xml:space="preserve">4.91616821289062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95172786712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93394804000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89838790893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80948829650879</t>
+    <t xml:space="preserve">4.95172834396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9339485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89838838577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80948781967163</t>
   </si>
   <si>
     <t xml:space="preserve">4.78281784057617</t>
@@ -1334,19 +1334,19 @@
     <t xml:space="preserve">5.10285758972168</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96061754226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20064830780029</t>
+    <t xml:space="preserve">4.96061849594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20064783096313</t>
   </si>
   <si>
     <t xml:space="preserve">5.21842765808105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27176713943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33399772644043</t>
+    <t xml:space="preserve">5.27176809310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33399820327759</t>
   </si>
   <si>
     <t xml:space="preserve">5.23620796203613</t>
@@ -1361,10 +1361,10 @@
     <t xml:space="preserve">4.99617767333984</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00506830215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37844800949097</t>
+    <t xml:space="preserve">5.00506782531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37844848632812</t>
   </si>
   <si>
     <t xml:space="preserve">5.47623729705811</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">5.56513786315918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6807074546814</t>
+    <t xml:space="preserve">5.68070793151855</t>
   </si>
   <si>
     <t xml:space="preserve">5.6540379524231</t>
@@ -1382,7 +1382,7 @@
     <t xml:space="preserve">5.63625764846802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5562481880188</t>
+    <t xml:space="preserve">5.55624723434448</t>
   </si>
   <si>
     <t xml:space="preserve">5.68959760665894</t>
@@ -1397,22 +1397,22 @@
     <t xml:space="preserve">5.77849769592285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84072780609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76071739196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92073774337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83183717727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44956827163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58291816711426</t>
+    <t xml:space="preserve">5.84072732925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76071786880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92073726654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83183765411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4495677947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5829176902771</t>
   </si>
   <si>
     <t xml:space="preserve">5.43178796768188</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">5.36955785751343</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60958766937256</t>
+    <t xml:space="preserve">5.6095871925354</t>
   </si>
   <si>
     <t xml:space="preserve">5.86739730834961</t>
@@ -1445,52 +1445,52 @@
     <t xml:space="preserve">5.64514780044556</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71626806259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73404788970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81405735015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67181777954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5117974281311</t>
+    <t xml:space="preserve">5.71626710891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73404741287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81405782699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67181825637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51179790496826</t>
   </si>
   <si>
     <t xml:space="preserve">5.85850763320923</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66292715072632</t>
+    <t xml:space="preserve">5.66292762756348</t>
   </si>
   <si>
     <t xml:space="preserve">5.53846788406372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90295791625977</t>
+    <t xml:space="preserve">5.90295743942261</t>
   </si>
   <si>
     <t xml:space="preserve">5.79627752304077</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80516767501831</t>
+    <t xml:space="preserve">5.80516815185547</t>
   </si>
   <si>
     <t xml:space="preserve">5.6184778213501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46734714508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60069799423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45845746994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50290727615356</t>
+    <t xml:space="preserve">5.46734762191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60069751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45845794677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50290775299072</t>
   </si>
   <si>
     <t xml:space="preserve">5.34288787841797</t>
@@ -1499,16 +1499,16 @@
     <t xml:space="preserve">5.62736749649048</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52957773208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42289781570435</t>
+    <t xml:space="preserve">5.52957725524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42289733886719</t>
   </si>
   <si>
     <t xml:space="preserve">5.72515773773193</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70737838745117</t>
+    <t xml:space="preserve">5.70737791061401</t>
   </si>
   <si>
     <t xml:space="preserve">5.69848775863647</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">6.0007472038269</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92962741851807</t>
+    <t xml:space="preserve">5.92962789535522</t>
   </si>
   <si>
     <t xml:space="preserve">5.94740772247314</t>
@@ -1529,28 +1529,28 @@
     <t xml:space="preserve">5.99185705184937</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24077796936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40968751907349</t>
+    <t xml:space="preserve">6.24077749252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40968704223633</t>
   </si>
   <si>
     <t xml:space="preserve">6.48080730438232</t>
   </si>
   <si>
-    <t xml:space="preserve">6.623046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84529685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99642753601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0142068862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90752649307251</t>
+    <t xml:space="preserve">6.62304735183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84529638290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99642658233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01420736312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90752744674683</t>
   </si>
   <si>
     <t xml:space="preserve">6.91641759872437</t>
@@ -1562,25 +1562,25 @@
     <t xml:space="preserve">7.00531721115112</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0230975151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2453465461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27201700210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33424711227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47648620605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76985597610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7342963218689</t>
+    <t xml:space="preserve">7.02309703826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24534749984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27201747894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33424663543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47648668289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76985692977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73429584503174</t>
   </si>
   <si>
     <t xml:space="preserve">7.72540712356567</t>
@@ -1589,19 +1589,19 @@
     <t xml:space="preserve">7.79652690887451</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80541706085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22324657440186</t>
+    <t xml:space="preserve">7.80541610717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22324752807617</t>
   </si>
   <si>
     <t xml:space="preserve">8.21435546875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15212631225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12545680999756</t>
+    <t xml:space="preserve">8.15212726593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12545776367188</t>
   </si>
   <si>
     <t xml:space="preserve">8.00099658966064</t>
@@ -1610,49 +1610,49 @@
     <t xml:space="preserve">8.17879676818848</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34770584106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42771625518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48105525970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46327590942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52550601959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50772762298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66774654388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80109596252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8899974822998</t>
+    <t xml:space="preserve">8.34770774841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42771530151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48105621337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46327686309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5255069732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50772571563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66774559020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8010950088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88999652862549</t>
   </si>
   <si>
     <t xml:space="preserve">9.19225597381592</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37005615234375</t>
+    <t xml:space="preserve">9.37005519866943</t>
   </si>
   <si>
     <t xml:space="preserve">9.47673511505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49451541900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31671619415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15669536590576</t>
+    <t xml:space="preserve">9.49451637268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31671524047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15669631958008</t>
   </si>
   <si>
     <t xml:space="preserve">9.35227680206299</t>
@@ -1664,28 +1664,28 @@
     <t xml:space="preserve">9.69009494781494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86789608001709</t>
+    <t xml:space="preserve">9.86789703369141</t>
   </si>
   <si>
     <t xml:space="preserve">9.83233642578125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77899742126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44117641448975</t>
+    <t xml:space="preserve">9.77899646759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44117546081543</t>
   </si>
   <si>
     <t xml:space="preserve">9.210036277771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58341693878174</t>
+    <t xml:space="preserve">9.58341503143311</t>
   </si>
   <si>
     <t xml:space="preserve">9.51229572296143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67231559753418</t>
+    <t xml:space="preserve">9.6723165512085</t>
   </si>
   <si>
     <t xml:space="preserve">9.85011577606201</t>
@@ -1700,13 +1700,13 @@
     <t xml:space="preserve">9.99235534667969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0101366043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76121520996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88567543029785</t>
+    <t xml:space="preserve">10.0101356506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76121616363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88567638397217</t>
   </si>
   <si>
     <t xml:space="preserve">10.2234954833984</t>
@@ -1715,22 +1715,22 @@
     <t xml:space="preserve">10.4368553161621</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6679954528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4147567749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3614149093628</t>
+    <t xml:space="preserve">10.6679964065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.414755821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3614158630371</t>
   </si>
   <si>
     <t xml:space="preserve">11.3080759048462</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4325361251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6814556121826</t>
+    <t xml:space="preserve">11.4325342178345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6814546585083</t>
   </si>
   <si>
     <t xml:space="preserve">11.8948154449463</t>
@@ -1742,16 +1742,16 @@
     <t xml:space="preserve">12.1437358856201</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6281147003174</t>
+    <t xml:space="preserve">11.6281156539917</t>
   </si>
   <si>
     <t xml:space="preserve">11.4001131057739</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6715440750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6534490585327</t>
+    <t xml:space="preserve">11.6715431213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.653450012207</t>
   </si>
   <si>
     <t xml:space="preserve">11.689640045166</t>
@@ -1760,10 +1760,10 @@
     <t xml:space="preserve">12.1239290237427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7982120513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1782169342041</t>
+    <t xml:space="preserve">11.7982130050659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1782150268555</t>
   </si>
   <si>
     <t xml:space="preserve">12.3229789733887</t>
@@ -1772,34 +1772,34 @@
     <t xml:space="preserve">12.9925088882446</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8296518325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7391738891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7753658294678</t>
+    <t xml:space="preserve">12.8296508789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7391748428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7753639221191</t>
   </si>
   <si>
     <t xml:space="preserve">12.3953609466553</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2867889404297</t>
+    <t xml:space="preserve">12.2867879867554</t>
   </si>
   <si>
     <t xml:space="preserve">12.6306018829346</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4496469497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2144060134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1058349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8705940246582</t>
+    <t xml:space="preserve">12.4496479034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2144069671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1058340072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8705930709839</t>
   </si>
   <si>
     <t xml:space="preserve">11.9067850112915</t>
@@ -1808,10 +1808,10 @@
     <t xml:space="preserve">11.4724941253662</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4182081222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5810680389404</t>
+    <t xml:space="preserve">11.4182071685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5810670852661</t>
   </si>
   <si>
     <t xml:space="preserve">11.852499961853</t>
@@ -1823,16 +1823,16 @@
     <t xml:space="preserve">11.8344030380249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.888689994812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4363050460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3277311325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734451293945</t>
+    <t xml:space="preserve">11.8886890411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4363040924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3277320861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734460830688</t>
   </si>
   <si>
     <t xml:space="preserve">11.1829681396484</t>
@@ -1841,22 +1841,22 @@
     <t xml:space="preserve">11.1648721694946</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8391551971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6401062011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6762962341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5134382247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9115371704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.291540145874</t>
+    <t xml:space="preserve">10.8391542434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6401042938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6762971878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5134363174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9115381240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2915391921997</t>
   </si>
   <si>
     <t xml:space="preserve">11.1467771530151</t>
@@ -1865,25 +1865,25 @@
     <t xml:space="preserve">10.766773223877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1105861663818</t>
+    <t xml:space="preserve">11.1105852127075</t>
   </si>
   <si>
     <t xml:space="preserve">11.1286821365356</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6220092773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0020141601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6039142608643</t>
+    <t xml:space="preserve">10.6220102310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0020132064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6039152145386</t>
   </si>
   <si>
     <t xml:space="preserve">10.4953422546387</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2781963348389</t>
+    <t xml:space="preserve">10.2781972885132</t>
   </si>
   <si>
     <t xml:space="preserve">10.3143873214722</t>
@@ -1895,10 +1895,10 @@
     <t xml:space="preserve">9.93438339233398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80771636962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68104934692383</t>
+    <t xml:space="preserve">9.80771732330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6810474395752</t>
   </si>
   <si>
     <t xml:space="preserve">9.95247936248779</t>
@@ -1913,49 +1913,49 @@
     <t xml:space="preserve">10.3867692947388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4410552978516</t>
+    <t xml:space="preserve">10.4410562515259</t>
   </si>
   <si>
     <t xml:space="preserve">9.55438041687012</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1153402328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3505792617798</t>
+    <t xml:space="preserve">10.1153383255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3505783081055</t>
   </si>
   <si>
     <t xml:space="preserve">10.4048652648926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7486772537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0201091766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.857250213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8753461837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5858201980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8029632568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7124881744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7848691940308</t>
+    <t xml:space="preserve">10.7486791610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0201101303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8572511672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8753471374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5858182907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8029642105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7124872207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7848682403564</t>
   </si>
   <si>
     <t xml:space="preserve">11.2372541427612</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3096361160278</t>
+    <t xml:space="preserve">11.3096351623535</t>
   </si>
   <si>
     <t xml:space="preserve">11.4543991088867</t>
@@ -1964,22 +1964,22 @@
     <t xml:space="preserve">11.7258310317993</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9972620010376</t>
+    <t xml:space="preserve">11.9972610473633</t>
   </si>
   <si>
     <t xml:space="preserve">12.1601209640503</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0515480041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0334539413452</t>
+    <t xml:space="preserve">12.0515470504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0334529876709</t>
   </si>
   <si>
     <t xml:space="preserve">11.9429750442505</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7620210647583</t>
+    <t xml:space="preserve">11.7620220184326</t>
   </si>
   <si>
     <t xml:space="preserve">10.9477281570435</t>
@@ -1991,10 +1991,10 @@
     <t xml:space="preserve">10.1877202987671</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98867034912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0429573059082</t>
+    <t xml:space="preserve">9.98867130279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0429582595825</t>
   </si>
   <si>
     <t xml:space="preserve">9.91628932952881</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">10.1696243286133</t>
   </si>
   <si>
-    <t xml:space="preserve">10.531533241272</t>
+    <t xml:space="preserve">10.5315322875977</t>
   </si>
   <si>
     <t xml:space="preserve">10.4229602813721</t>
@@ -2018,13 +2018,13 @@
     <t xml:space="preserve">10.2239112854004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0972442626953</t>
+    <t xml:space="preserve">10.097243309021</t>
   </si>
   <si>
     <t xml:space="preserve">10.0610513687134</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0791473388672</t>
+    <t xml:space="preserve">10.0791482925415</t>
   </si>
   <si>
     <t xml:space="preserve">10.1515293121338</t>
@@ -2054,16 +2054,16 @@
     <t xml:space="preserve">9.51819038391113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7172384262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42771339416504</t>
+    <t xml:space="preserve">9.71723937988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42771244049072</t>
   </si>
   <si>
     <t xml:space="preserve">9.59057140350342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3639230728149</t>
+    <t xml:space="preserve">11.3639221191406</t>
   </si>
   <si>
     <t xml:space="preserve">11.9791660308838</t>
@@ -2072,10 +2072,10 @@
     <t xml:space="preserve">12.4677419662476</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3772659301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3820180892944</t>
+    <t xml:space="preserve">12.3772668838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3820171356201</t>
   </si>
   <si>
     <t xml:space="preserve">11.5629720687866</t>
@@ -2084,13 +2084,13 @@
     <t xml:space="preserve">11.6172580718994</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0924911499023</t>
+    <t xml:space="preserve">11.092490196228</t>
   </si>
   <si>
     <t xml:space="preserve">10.6943922042847</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62676334381104</t>
+    <t xml:space="preserve">9.6267614364624</t>
   </si>
   <si>
     <t xml:space="preserve">8.8034200668335</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">8.43246459960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0481653213501</t>
+    <t xml:space="preserve">7.04816579818726</t>
   </si>
   <si>
     <t xml:space="preserve">7.32864475250244</t>
@@ -2117,43 +2117,43 @@
     <t xml:space="preserve">6.58673191070557</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65006637573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96673583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97578382492065</t>
+    <t xml:space="preserve">6.65006589889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96673488616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9757833480835</t>
   </si>
   <si>
     <t xml:space="preserve">7.16578531265259</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05721282958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28340530395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60912227630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76293325424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34198760986328</t>
+    <t xml:space="preserve">7.057213306427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28340578079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60912322998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76293420791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3419885635376</t>
   </si>
   <si>
     <t xml:space="preserve">8.04341316223145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61341857910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41436862945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25151062011719</t>
+    <t xml:space="preserve">8.61341953277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41436958312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2515115737915</t>
   </si>
   <si>
     <t xml:space="preserve">8.93008899688721</t>
@@ -2165,16 +2165,16 @@
     <t xml:space="preserve">9.04770851135254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26485252380371</t>
+    <t xml:space="preserve">9.26485347747803</t>
   </si>
   <si>
     <t xml:space="preserve">9.50009441375732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8620023727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2191581726074</t>
+    <t xml:space="preserve">9.86200332641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2191591262817</t>
   </si>
   <si>
     <t xml:space="preserve">10.9839191436768</t>
@@ -2189,40 +2189,40 @@
     <t xml:space="preserve">10.2058143615723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84390640258789</t>
+    <t xml:space="preserve">9.84390735626221</t>
   </si>
   <si>
     <t xml:space="preserve">10.4591512680054</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9296312332153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7305812835693</t>
+    <t xml:space="preserve">10.9296321868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7305822372437</t>
   </si>
   <si>
     <t xml:space="preserve">10.8210601806641</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0696430206299</t>
+    <t xml:space="preserve">12.0696439743042</t>
   </si>
   <si>
     <t xml:space="preserve">12.558219909668</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8477468490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1915597915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7572708129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7934598922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4315509796143</t>
+    <t xml:space="preserve">12.8477458953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1915588378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7572689056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7934608459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4315528869629</t>
   </si>
   <si>
     <t xml:space="preserve">12.5944108963013</t>
@@ -2240,16 +2240,16 @@
     <t xml:space="preserve">13.1553678512573</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0287008285522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.119176864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9382228851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.082986831665</t>
+    <t xml:space="preserve">13.0286998748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1191778182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9382238388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0829858779907</t>
   </si>
   <si>
     <t xml:space="preserve">13.3725137710571</t>
@@ -2258,25 +2258,25 @@
     <t xml:space="preserve">13.3544178009033</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4534883499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.249683380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2858734130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3763542175293</t>
+    <t xml:space="preserve">15.4534864425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2496852874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2858753204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3763561248779</t>
   </si>
   <si>
     <t xml:space="preserve">16.6477832794189</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8334903717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.068733215332</t>
+    <t xml:space="preserve">15.8334884643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0687313079834</t>
   </si>
   <si>
     <t xml:space="preserve">15.8696794509888</t>
@@ -2285,79 +2285,79 @@
     <t xml:space="preserve">15.9239673614502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9058713912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8515853881836</t>
+    <t xml:space="preserve">15.9058704376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8515863418579</t>
   </si>
   <si>
     <t xml:space="preserve">16.0144443511963</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7972984313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2677803039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0325393676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7792043685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7249164581299</t>
+    <t xml:space="preserve">15.7972993850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2677822113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0325374603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.779203414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7249174118042</t>
   </si>
   <si>
     <t xml:space="preserve">16.4125442504883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8153963088989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9420652389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6344404220581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.104923248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9601593017578</t>
+    <t xml:space="preserve">15.815393447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9420614242554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6344394683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1049213409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9601583480835</t>
   </si>
   <si>
     <t xml:space="preserve">15.6887264251709</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6163444519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8925285339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6525363922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3630104064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4896783828735</t>
+    <t xml:space="preserve">15.6163463592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8925275802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6525354385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3630084991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4896774291992</t>
   </si>
   <si>
     <t xml:space="preserve">15.1458654403687</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0372924804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7430124282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8201465606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2906274795532</t>
+    <t xml:space="preserve">15.0372934341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.743013381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8201456069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2906265258789</t>
   </si>
   <si>
     <t xml:space="preserve">17.5887451171875</t>
@@ -2366,43 +2366,43 @@
     <t xml:space="preserve">17.7696990966797</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0230350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1359043121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2763710021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.041130065918</t>
+    <t xml:space="preserve">18.0230369567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1359062194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2763748168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0411319732666</t>
   </si>
   <si>
     <t xml:space="preserve">17.4258880615234</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7335071563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2992191314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0458850860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0277881622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7020683288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0096912384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4077930450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5025672912598</t>
+    <t xml:space="preserve">17.7335109710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2992172241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0458831787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0277862548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7020721435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.009693145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4077911376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5025634765625</t>
   </si>
   <si>
     <t xml:space="preserve">18.1406536102295</t>
@@ -2420,55 +2420,55 @@
     <t xml:space="preserve">18.5930404663086</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1544551849365</t>
+    <t xml:space="preserve">17.1544570922852</t>
   </si>
   <si>
     <t xml:space="preserve">17.2449321746826</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1182632446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8106422424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8287372589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.973503112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9192161560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0639801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8468360900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9011211395264</t>
+    <t xml:space="preserve">17.1182670593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8106441497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8287391662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9735012054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9192180633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0639781951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8468341827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9011192321777</t>
   </si>
   <si>
     <t xml:space="preserve">17.3173141479492</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2087421417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2268371582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3668479919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4573268890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6382808685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7287559509277</t>
+    <t xml:space="preserve">17.2087440490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2268390655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.366849899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4573249816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6382789611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.728759765625</t>
   </si>
   <si>
     <t xml:space="preserve">18.9549503326416</t>
@@ -2477,10 +2477,10 @@
     <t xml:space="preserve">18.8644733428955</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6335277557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6787662506104</t>
+    <t xml:space="preserve">19.6335315704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.678768157959</t>
   </si>
   <si>
     <t xml:space="preserve">19.5430507659912</t>
@@ -2504,7 +2504,7 @@
     <t xml:space="preserve">19.0906658172607</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6835155487061</t>
+    <t xml:space="preserve">18.6835193634033</t>
   </si>
   <si>
     <t xml:space="preserve">18.0954170227051</t>
@@ -2516,13 +2516,13 @@
     <t xml:space="preserve">17.5706520080566</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8239879608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6430320739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8058910369873</t>
+    <t xml:space="preserve">17.8239860534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.643030166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8058891296387</t>
   </si>
   <si>
     <t xml:space="preserve">19.2716197967529</t>
@@ -2534,16 +2534,16 @@
     <t xml:space="preserve">20.26686668396</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4930591583252</t>
+    <t xml:space="preserve">20.4930610656738</t>
   </si>
   <si>
     <t xml:space="preserve">20.9906845092773</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5835380554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3573474884033</t>
+    <t xml:space="preserve">20.5835399627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3573455810547</t>
   </si>
   <si>
     <t xml:space="preserve">19.9049587249756</t>
@@ -2552,43 +2552,43 @@
     <t xml:space="preserve">19.7692432403564</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7192535400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9954376220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2263793945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4525756835938</t>
+    <t xml:space="preserve">20.7192516326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9954357147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2263832092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4525718688965</t>
   </si>
   <si>
     <t xml:space="preserve">19.4073371887207</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6249332427979</t>
+    <t xml:space="preserve">17.6249370574951</t>
   </si>
   <si>
     <t xml:space="preserve">17.7877941131592</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4978122711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0859146118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1311492919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8597221374512</t>
+    <t xml:space="preserve">19.4978103637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.085916519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1311511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8597202301025</t>
   </si>
   <si>
     <t xml:space="preserve">20.674015045166</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0359230041504</t>
+    <t xml:space="preserve">21.035924911499</t>
   </si>
   <si>
     <t xml:space="preserve">20.8097305297852</t>
@@ -2597,34 +2597,34 @@
     <t xml:space="preserve">20.6287746429443</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3121089935303</t>
+    <t xml:space="preserve">20.312105178833</t>
   </si>
   <si>
     <t xml:space="preserve">20.4478225708008</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8821105957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2802124023438</t>
+    <t xml:space="preserve">20.8821125030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2802085876465</t>
   </si>
   <si>
     <t xml:space="preserve">21.3344974517822</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5878314971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6602153778076</t>
+    <t xml:space="preserve">21.587833404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6602172851562</t>
   </si>
   <si>
     <t xml:space="preserve">22.1668872833252</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6192722320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8726100921631</t>
+    <t xml:space="preserve">22.619270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8726081848145</t>
   </si>
   <si>
     <t xml:space="preserve">23.9040470123291</t>
@@ -2633,10 +2633,10 @@
     <t xml:space="preserve">22.7821311950684</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8592624664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0040283203125</t>
+    <t xml:space="preserve">21.8592643737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0040264129639</t>
   </si>
   <si>
     <t xml:space="preserve">22.2573642730713</t>
@@ -2651,37 +2651,37 @@
     <t xml:space="preserve">22.058313369751</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6011772155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6373691558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.420223236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4021263122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3525924682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2621173858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0945072174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.583080291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0354671478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0173721313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3611812591553</t>
+    <t xml:space="preserve">22.6011753082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6373653411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4202213287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4021282196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3525943756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.262113571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0945053100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5830783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0354652404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0173740386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3611850738525</t>
   </si>
   <si>
     <t xml:space="preserve">23.2707061767578</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">25.0440578460693</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7726249694824</t>
+    <t xml:space="preserve">24.7726268768311</t>
   </si>
   <si>
     <t xml:space="preserve">24.9716777801514</t>
@@ -2702,61 +2702,61 @@
     <t xml:space="preserve">25.9126377105713</t>
   </si>
   <si>
-    <t xml:space="preserve">26.238353729248</t>
+    <t xml:space="preserve">26.2383556365967</t>
   </si>
   <si>
     <t xml:space="preserve">26.6765727996826</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7130928039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5852794647217</t>
+    <t xml:space="preserve">26.7130908966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.585277557373</t>
   </si>
   <si>
     <t xml:space="preserve">26.6583156585693</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8226451873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9504623413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5712718963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.626049041748</t>
+    <t xml:space="preserve">26.8226470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.95046043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5712699890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6260471343994</t>
   </si>
   <si>
     <t xml:space="preserve">28.064266204834</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2833766937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8171443939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5980319976807</t>
+    <t xml:space="preserve">28.283374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8171424865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.598030090332</t>
   </si>
   <si>
     <t xml:space="preserve">28.958963394165</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1275501251221</t>
+    <t xml:space="preserve">30.1275482177734</t>
   </si>
   <si>
     <t xml:space="preserve">29.652811050415</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1092910766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9632148742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4014358520508</t>
+    <t xml:space="preserve">30.1092872619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9632129669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4014320373535</t>
   </si>
   <si>
     <t xml:space="preserve">30.2188396453857</t>
@@ -2765,49 +2765,49 @@
     <t xml:space="preserve">31.2961292266846</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8213901519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1683216094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2371006011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4154415130615</t>
+    <t xml:space="preserve">30.8213920593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1683177947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2371025085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4154434204102</t>
   </si>
   <si>
     <t xml:space="preserve">29.8536605834961</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1780700683594</t>
+    <t xml:space="preserve">29.178071975708</t>
   </si>
   <si>
     <t xml:space="preserve">30.1458072662354</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7075881958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0545101165771</t>
+    <t xml:space="preserve">29.7075862884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0545082092285</t>
   </si>
   <si>
     <t xml:space="preserve">32.8664131164551</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5462532043457</t>
+    <t xml:space="preserve">34.546257019043</t>
   </si>
   <si>
     <t xml:space="preserve">34.0532569885254</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0855293273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7245903015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6880760192871</t>
+    <t xml:space="preserve">33.0855255126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7245941162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6880722045898</t>
   </si>
   <si>
     <t xml:space="preserve">33.5785179138184</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">33.2863731384277</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2273445129395</t>
+    <t xml:space="preserve">32.2273483276367</t>
   </si>
   <si>
     <t xml:space="preserve">32.8846740722656</t>
@@ -2834,25 +2834,25 @@
     <t xml:space="preserve">32.7568626403809</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6473007202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0307502746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7751235961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4099349975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6655654907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6923294067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.605281829834</t>
+    <t xml:space="preserve">32.6473045349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0307464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7751197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4099388122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6655616760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.692325592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6052780151367</t>
   </si>
   <si>
     <t xml:space="preserve">35.2401008605957</t>
@@ -2864,28 +2864,28 @@
     <t xml:space="preserve">35.4774703979492</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0940284729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5870208740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7878723144531</t>
+    <t xml:space="preserve">35.0940246582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5870246887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7878761291504</t>
   </si>
   <si>
     <t xml:space="preserve">36.0435028076172</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8469047546387</t>
+    <t xml:space="preserve">36.8469009399414</t>
   </si>
   <si>
     <t xml:space="preserve">38.9101829528809</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4354476928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4944763183594</t>
+    <t xml:space="preserve">38.4354438781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4944725036621</t>
   </si>
   <si>
     <t xml:space="preserve">39.3849182128906</t>
@@ -2894,31 +2894,31 @@
     <t xml:space="preserve">39.220588684082</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1292915344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1980743408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6137886047363</t>
+    <t xml:space="preserve">39.1292953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1980781555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6137847900391</t>
   </si>
   <si>
     <t xml:space="preserve">37.2486038208008</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0660095214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2668647766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7008285522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2120819091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.559009552002</t>
+    <t xml:space="preserve">37.0660133361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2668609619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7008323669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.212085723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5590057373047</t>
   </si>
   <si>
     <t xml:space="preserve">38.0154838562012</t>
@@ -2927,28 +2927,28 @@
     <t xml:space="preserve">37.6503067016602</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6235389709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2315979003906</t>
+    <t xml:space="preserve">35.6235427856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2316017150879</t>
   </si>
   <si>
     <t xml:space="preserve">32.9942283630371</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3594131469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0490074157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.783618927002</t>
+    <t xml:space="preserve">33.3594093322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0490112304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7836227416992</t>
   </si>
   <si>
     <t xml:space="preserve">34.3819236755371</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8931770324707</t>
+    <t xml:space="preserve">34.893180847168</t>
   </si>
   <si>
     <t xml:space="preserve">32.9577102661133</t>
@@ -2960,13 +2960,13 @@
     <t xml:space="preserve">35.513988494873</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4817199707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3173904418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6095352172852</t>
+    <t xml:space="preserve">36.4817237854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3173866271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6095314025879</t>
   </si>
   <si>
     <t xml:space="preserve">37.7781181335449</t>
@@ -2975,70 +2975,70 @@
     <t xml:space="preserve">38.271110534668</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2023277282715</t>
+    <t xml:space="preserve">39.2023315429688</t>
   </si>
   <si>
     <t xml:space="preserve">36.7190895080566</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8426475524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9662132263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1488037109375</t>
+    <t xml:space="preserve">35.8426513671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9662170410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1488075256348</t>
   </si>
   <si>
     <t xml:space="preserve">35.4409523010254</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8876724243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5267448425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8006286621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6685638427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4226951599121</t>
+    <t xml:space="preserve">37.8876762390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.526741027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8006324768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6685600280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4226875305176</t>
   </si>
   <si>
     <t xml:space="preserve">35.258358001709</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9114379882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3636665344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8341522216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5967826843262</t>
+    <t xml:space="preserve">34.911434173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3636589050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8341484069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5967788696289</t>
   </si>
   <si>
     <t xml:space="preserve">35.3313980102539</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2175903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9071807861328</t>
+    <t xml:space="preserve">34.2175941467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9071846008301</t>
   </si>
   <si>
     <t xml:space="preserve">35.3131370544434</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7105827331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3454055786133</t>
+    <t xml:space="preserve">34.7105865478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.345401763916</t>
   </si>
   <si>
     <t xml:space="preserve">34.0715179443359</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">33.1950798034668</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6150398254395</t>
+    <t xml:space="preserve">33.6150360107422</t>
   </si>
   <si>
     <t xml:space="preserve">33.9254455566406</t>
@@ -3056,13 +3056,13 @@
     <t xml:space="preserve">33.9437026977539</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6192893981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5827751159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7288436889648</t>
+    <t xml:space="preserve">34.6192932128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5827713012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7288475036621</t>
   </si>
   <si>
     <t xml:space="preserve">35.0027313232422</t>
@@ -3077,52 +3077,52 @@
     <t xml:space="preserve">32.5377502441406</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1725692749023</t>
+    <t xml:space="preserve">32.1725654602051</t>
   </si>
   <si>
     <t xml:space="preserve">32.1360511779785</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4519596099854</t>
+    <t xml:space="preserve">29.4519577026367</t>
   </si>
   <si>
     <t xml:space="preserve">29.8901805877686</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1640644073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4294490814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1007843017578</t>
+    <t xml:space="preserve">30.1640663146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4294471740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1007862091064</t>
   </si>
   <si>
     <t xml:space="preserve">27.6808242797852</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9954833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2693691253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6850757598877</t>
+    <t xml:space="preserve">28.9954814910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2693710327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6850776672363</t>
   </si>
   <si>
     <t xml:space="preserve">26.9687213897705</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8956813812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.845157623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9729690551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6668167114258</t>
+    <t xml:space="preserve">26.8956832885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8451557159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9729709625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6668186187744</t>
   </si>
   <si>
     <t xml:space="preserve">29.1232948303223</t>
@@ -3134,10 +3134,10 @@
     <t xml:space="preserve">27.6077880859375</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7538623809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3479080200195</t>
+    <t xml:space="preserve">27.7538604736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3479099273682</t>
   </si>
   <si>
     <t xml:space="preserve">25.5445079803467</t>
@@ -3146,10 +3146,10 @@
     <t xml:space="preserve">26.7496089935303</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7861270904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5670185089111</t>
+    <t xml:space="preserve">26.7861289978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5670204162598</t>
   </si>
   <si>
     <t xml:space="preserve">27.9547119140625</t>
@@ -3158,13 +3158,13 @@
     <t xml:space="preserve">27.4251976013184</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4799747467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1147956848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.731351852417</t>
+    <t xml:space="preserve">27.4799766540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1147937774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7313537597656</t>
   </si>
   <si>
     <t xml:space="preserve">27.4069385528564</t>
@@ -3179,34 +3179,34 @@
     <t xml:space="preserve">27.4434566497803</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3113899230957</t>
+    <t xml:space="preserve">26.3113918304443</t>
   </si>
   <si>
     <t xml:space="preserve">23.5542621612549</t>
   </si>
   <si>
-    <t xml:space="preserve">24.70458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.097785949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0022411346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7466106414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7423572540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6047897338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8744258880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5134944915771</t>
+    <t xml:space="preserve">24.7045879364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0977840423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0022392272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7466125488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.742359161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6047916412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8744239807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5134925842285</t>
   </si>
   <si>
     <t xml:space="preserve">23.1525630950928</t>
@@ -3218,13 +3218,13 @@
     <t xml:space="preserve">24.5402565002441</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6680717468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8689212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4489650726318</t>
+    <t xml:space="preserve">24.6680698394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8689193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4489612579346</t>
   </si>
   <si>
     <t xml:space="preserve">25.2341022491455</t>
@@ -3233,7 +3233,7 @@
     <t xml:space="preserve">24.5585155487061</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0289993286133</t>
+    <t xml:space="preserve">24.0290012359619</t>
   </si>
   <si>
     <t xml:space="preserve">24.1385555267334</t>
@@ -3242,7 +3242,7 @@
     <t xml:space="preserve">24.0472602844238</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3984336853027</t>
+    <t xml:space="preserve">25.3984375</t>
   </si>
   <si>
     <t xml:space="preserve">25.4166946411133</t>
@@ -3251,22 +3251,22 @@
     <t xml:space="preserve">24.2115917205811</t>
   </si>
   <si>
-    <t xml:space="preserve">24.083776473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8098907470703</t>
+    <t xml:space="preserve">24.0837783813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8098926544189</t>
   </si>
   <si>
     <t xml:space="preserve">23.3351554870605</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4221992492676</t>
+    <t xml:space="preserve">22.4221973419189</t>
   </si>
   <si>
     <t xml:space="preserve">22.7326030731201</t>
   </si>
   <si>
-    <t xml:space="preserve">22.677827835083</t>
+    <t xml:space="preserve">22.6778259277344</t>
   </si>
   <si>
     <t xml:space="preserve">22.2761249542236</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">21.9109439849854</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2213497161865</t>
+    <t xml:space="preserve">22.2213478088379</t>
   </si>
   <si>
     <t xml:space="preserve">21.8379077911377</t>
@@ -3284,34 +3284,34 @@
     <t xml:space="preserve">22.0935363769531</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8239002227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5457611083984</t>
+    <t xml:space="preserve">22.8238983154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5457630157471</t>
   </si>
   <si>
     <t xml:space="preserve">21.07102394104</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9657211303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1988353729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2718715667725</t>
+    <t xml:space="preserve">21.9657192230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1988372802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2718734741211</t>
   </si>
   <si>
     <t xml:space="preserve">20.8884315490723</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6875820159912</t>
+    <t xml:space="preserve">20.6875839233398</t>
   </si>
   <si>
     <t xml:space="preserve">20.0850315093994</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3729267120361</t>
+    <t xml:space="preserve">19.3729248046875</t>
   </si>
   <si>
     <t xml:space="preserve">19.8659229278564</t>
@@ -3320,16 +3320,16 @@
     <t xml:space="preserve">19.9572200775146</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9024391174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2493648529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9614696502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8519134521484</t>
+    <t xml:space="preserve">19.9024410247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2493629455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9614677429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8519153594971</t>
   </si>
   <si>
     <t xml:space="preserve">20.724100112915</t>
@@ -3338,7 +3338,7 @@
     <t xml:space="preserve">21.0162467956543</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3449096679688</t>
+    <t xml:space="preserve">21.3449077606201</t>
   </si>
   <si>
     <t xml:space="preserve">20.3954372406006</t>
@@ -3350,43 +3350,43 @@
     <t xml:space="preserve">20.6693229675293</t>
   </si>
   <si>
-    <t xml:space="preserve">22.130054473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1933307647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6455593109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5177459716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7368545532227</t>
+    <t xml:space="preserve">22.1300525665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1933345794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6455612182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5177478790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7368564605713</t>
   </si>
   <si>
     <t xml:space="preserve">23.0533809661865</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9240760803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7393531799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8711585998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.744348526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6914310455322</t>
+    <t xml:space="preserve">22.9240741729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7393550872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8711566925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7443466186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6914291381836</t>
   </si>
   <si>
     <t xml:space="preserve">19.2850399017334</t>
   </si>
   <si>
-    <t xml:space="preserve">20.319486618042</t>
+    <t xml:space="preserve">20.3194885253906</t>
   </si>
   <si>
     <t xml:space="preserve">20.4303207397461</t>
@@ -3395,19 +3395,19 @@
     <t xml:space="preserve">21.2246265411377</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3539333343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.316987991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7603244781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6494884490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4278240203857</t>
+    <t xml:space="preserve">21.3539352416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3169898986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7603225708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6494922637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4278221130371</t>
   </si>
   <si>
     <t xml:space="preserve">21.55712890625</t>
@@ -3425,13 +3425,13 @@
     <t xml:space="preserve">20.3379592895508</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9130954742432</t>
+    <t xml:space="preserve">19.9130973815918</t>
   </si>
   <si>
     <t xml:space="preserve">20.9475440979004</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0374050140381</t>
+    <t xml:space="preserve">22.0374069213867</t>
   </si>
   <si>
     <t xml:space="preserve">22.4992141723633</t>
@@ -3446,10 +3446,10 @@
     <t xml:space="preserve">20.8182392120361</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1532363891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2271251678467</t>
+    <t xml:space="preserve">20.1532344818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2271270751953</t>
   </si>
   <si>
     <t xml:space="preserve">20.4487915039062</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">21.0029602050781</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0768508911133</t>
+    <t xml:space="preserve">21.0768489837646</t>
   </si>
   <si>
     <t xml:space="preserve">21.8157405853271</t>
@@ -3470,22 +3470,22 @@
     <t xml:space="preserve">22.3883800506592</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2960205078125</t>
+    <t xml:space="preserve">22.2960186004639</t>
   </si>
   <si>
     <t xml:space="preserve">22.5361576080322</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7578258514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2985172271729</t>
+    <t xml:space="preserve">22.7578239440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2985153198242</t>
   </si>
   <si>
     <t xml:space="preserve">21.5017127990723</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7787933349609</t>
+    <t xml:space="preserve">21.7787952423096</t>
   </si>
   <si>
     <t xml:space="preserve">21.7233791351318</t>
@@ -3494,22 +3494,22 @@
     <t xml:space="preserve">21.6864337921143</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8896312713623</t>
+    <t xml:space="preserve">21.889627456665</t>
   </si>
   <si>
     <t xml:space="preserve">21.704906463623</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6519889831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0424022674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0054569244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1162929534912</t>
+    <t xml:space="preserve">20.6519870758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0424041748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0054588317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1162910461426</t>
   </si>
   <si>
     <t xml:space="preserve">20.0978202819824</t>
@@ -3521,40 +3521,40 @@
     <t xml:space="preserve">19.7468452453613</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5436515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8417072296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.472261428833</t>
+    <t xml:space="preserve">19.5436534881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8417053222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4722595214844</t>
   </si>
   <si>
     <t xml:space="preserve">19.1926784515381</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5830936431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2413558959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0566349029541</t>
+    <t xml:space="preserve">18.5830955505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2413578033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0566329956055</t>
   </si>
   <si>
     <t xml:space="preserve">17.7426052093506</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4562854766846</t>
+    <t xml:space="preserve">17.4562835693359</t>
   </si>
   <si>
     <t xml:space="preserve">17.622537612915</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6989250183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5326728820801</t>
+    <t xml:space="preserve">16.6989231109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5326747894287</t>
   </si>
   <si>
     <t xml:space="preserve">16.8374652862549</t>
@@ -3563,10 +3563,10 @@
     <t xml:space="preserve">16.9852428436279</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2807998657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0037174224854</t>
+    <t xml:space="preserve">17.280797958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0037155151367</t>
   </si>
   <si>
     <t xml:space="preserve">17.6779537200928</t>
@@ -3578,13 +3578,13 @@
     <t xml:space="preserve">17.8164958953857</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5855922698975</t>
+    <t xml:space="preserve">17.5855941772461</t>
   </si>
   <si>
     <t xml:space="preserve">17.5024681091309</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0683670043945</t>
+    <t xml:space="preserve">17.0683689117432</t>
   </si>
   <si>
     <t xml:space="preserve">17.234619140625</t>
@@ -3593,13 +3593,13 @@
     <t xml:space="preserve">17.2530918121338</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9390621185303</t>
+    <t xml:space="preserve">16.9390640258789</t>
   </si>
   <si>
     <t xml:space="preserve">16.8005218505859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8836460113525</t>
+    <t xml:space="preserve">16.8836479187012</t>
   </si>
   <si>
     <t xml:space="preserve">17.4285774230957</t>
@@ -3614,19 +3614,19 @@
     <t xml:space="preserve">17.7333698272705</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3429565429688</t>
+    <t xml:space="preserve">18.3429546356201</t>
   </si>
   <si>
     <t xml:space="preserve">19.4697608947754</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5805969238281</t>
+    <t xml:space="preserve">19.5805988311768</t>
   </si>
   <si>
     <t xml:space="preserve">19.3589286804199</t>
   </si>
   <si>
-    <t xml:space="preserve">19.044900894165</t>
+    <t xml:space="preserve">19.0449028015137</t>
   </si>
   <si>
     <t xml:space="preserve">18.7493438720703</t>
@@ -3638,34 +3638,34 @@
     <t xml:space="preserve">18.2967739105225</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4907341003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0079574584961</t>
+    <t xml:space="preserve">18.4907321929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0079555511475</t>
   </si>
   <si>
     <t xml:space="preserve">20.0239315032959</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8392086029053</t>
+    <t xml:space="preserve">19.8392066955566</t>
   </si>
   <si>
     <t xml:space="preserve">20.8736553192139</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9080982208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3329620361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9105987548828</t>
+    <t xml:space="preserve">21.9081001281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3329639434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9106006622314</t>
   </si>
   <si>
     <t xml:space="preserve">20.5226802825928</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3354625701904</t>
+    <t xml:space="preserve">21.3354606628418</t>
   </si>
   <si>
     <t xml:space="preserve">21.2430992126465</t>
@@ -3677,7 +3677,7 @@
     <t xml:space="preserve">21.7418518066406</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2800445556641</t>
+    <t xml:space="preserve">21.2800464630127</t>
   </si>
   <si>
     <t xml:space="preserve">21.409351348877</t>
@@ -3689,7 +3689,7 @@
     <t xml:space="preserve">21.1507377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0583763122559</t>
+    <t xml:space="preserve">21.0583782196045</t>
   </si>
   <si>
     <t xml:space="preserve">20.3933753967285</t>
@@ -3698,13 +3698,13 @@
     <t xml:space="preserve">20.2455978393555</t>
   </si>
   <si>
-    <t xml:space="preserve">19.931568145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9685153961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2825412750244</t>
+    <t xml:space="preserve">19.9315700531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9685134887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.282543182373</t>
   </si>
   <si>
     <t xml:space="preserve">20.9290714263916</t>
@@ -3716,43 +3716,43 @@
     <t xml:space="preserve">22.831714630127</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2750492095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6075496673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3304653167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0349082946777</t>
+    <t xml:space="preserve">23.2750511169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6075477600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3304672241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0349102020264</t>
   </si>
   <si>
     <t xml:space="preserve">23.4412975311279</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9031047821045</t>
+    <t xml:space="preserve">23.9031028747559</t>
   </si>
   <si>
     <t xml:space="preserve">23.792272567749</t>
   </si>
   <si>
-    <t xml:space="preserve">23.127269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7553272247314</t>
+    <t xml:space="preserve">23.1272716522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7553253173828</t>
   </si>
   <si>
     <t xml:space="preserve">23.8846340179443</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4782447814941</t>
+    <t xml:space="preserve">23.4782428741455</t>
   </si>
   <si>
     <t xml:space="preserve">23.1087989807129</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9979629516602</t>
+    <t xml:space="preserve">22.9979648590088</t>
   </si>
   <si>
     <t xml:space="preserve">23.0164375305176</t>
@@ -3770,7 +3770,7 @@
     <t xml:space="preserve">24.1247730255127</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5151882171631</t>
+    <t xml:space="preserve">23.5151863098145</t>
   </si>
   <si>
     <t xml:space="preserve">22.8686580657959</t>
@@ -3782,16 +3782,16 @@
     <t xml:space="preserve">22.9056015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8132438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6285209655762</t>
+    <t xml:space="preserve">22.8132419586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6285190582275</t>
   </si>
   <si>
     <t xml:space="preserve">22.4622688293457</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2221298217773</t>
+    <t xml:space="preserve">22.2221279144287</t>
   </si>
   <si>
     <t xml:space="preserve">22.2036571502686</t>
@@ -3800,28 +3800,28 @@
     <t xml:space="preserve">22.0004634857178</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0558776855469</t>
+    <t xml:space="preserve">22.0558795928955</t>
   </si>
   <si>
     <t xml:space="preserve">22.2590751647949</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8342132568359</t>
+    <t xml:space="preserve">21.8342113494873</t>
   </si>
   <si>
     <t xml:space="preserve">22.0928249359131</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2406005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2615718841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3404560089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.656982421875</t>
+    <t xml:space="preserve">22.2406024932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2615737915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3404579162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6569843292236</t>
   </si>
   <si>
     <t xml:space="preserve">19.1187896728516</t>
@@ -3833,22 +3833,22 @@
     <t xml:space="preserve">18.6754550933838</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0264301300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2690658569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5092067718506</t>
+    <t xml:space="preserve">19.0264282226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2690677642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.509204864502</t>
   </si>
   <si>
     <t xml:space="preserve">18.8232326507568</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5461502075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7123985290527</t>
+    <t xml:space="preserve">18.5461521148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7124004364014</t>
   </si>
   <si>
     <t xml:space="preserve">18.7308731079102</t>
@@ -3863,40 +3863,40 @@
     <t xml:space="preserve">18.3614273071289</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7980251312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5486488342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1422576904297</t>
+    <t xml:space="preserve">17.798023223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5486469268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1422557830811</t>
   </si>
   <si>
     <t xml:space="preserve">16.9483013153076</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9205894470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8651752471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5696201324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8559379577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1145515441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7451057434082</t>
+    <t xml:space="preserve">16.9205913543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8651733398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5696182250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8559398651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1145496368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7451038360596</t>
   </si>
   <si>
     <t xml:space="preserve">16.9021186828613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8744125366211</t>
+    <t xml:space="preserve">16.8744106292725</t>
   </si>
   <si>
     <t xml:space="preserve">16.7912845611572</t>
@@ -3914,7 +3914,7 @@
     <t xml:space="preserve">16.671215057373</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7635746002197</t>
+    <t xml:space="preserve">16.7635765075684</t>
   </si>
   <si>
     <t xml:space="preserve">16.7728118896484</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">16.5234375</t>
   </si>
   <si>
-    <t xml:space="preserve">15.710657119751</t>
+    <t xml:space="preserve">15.7106561660767</t>
   </si>
   <si>
     <t xml:space="preserve">16.0708656311035</t>
@@ -3932,10 +3932,10 @@
     <t xml:space="preserve">16.0893383026123</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0062141418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0523948669434</t>
+    <t xml:space="preserve">16.0062122344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0523929595947</t>
   </si>
   <si>
     <t xml:space="preserve">16.6896858215332</t>
@@ -5340,6 +5340,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.8100004196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8900003433228</t>
   </si>
 </sst>
 </file>
@@ -70418,7 +70421,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6494675926</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>143379</v>
@@ -70439,6 +70442,32 @@
         <v>1766</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6495717593</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>137938</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>14.9099998474121</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>14.7600002288818</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>14.8299999237061</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>14.8900003433228</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>1776</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TNXT.MI.xlsx
+++ b/data/TNXT.MI.xlsx
@@ -44,61 +44,61 @@
     <t xml:space="preserve">TNXT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65150928497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59350872039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53550720214844</t>
+    <t xml:space="preserve">2.65150952339172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59350848197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5355064868927</t>
   </si>
   <si>
     <t xml:space="preserve">2.52556347846985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48579096794128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52722072601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48744821548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47087574005127</t>
+    <t xml:space="preserve">2.48579072952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52722096443176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48744773864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47087550163269</t>
   </si>
   <si>
     <t xml:space="preserve">2.46921849250793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54047822952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49739122390747</t>
+    <t xml:space="preserve">2.54047799110413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49739098548889</t>
   </si>
   <si>
     <t xml:space="preserve">2.47916197776794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44436025619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39464449882507</t>
+    <t xml:space="preserve">2.44436097145081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39464473724365</t>
   </si>
   <si>
     <t xml:space="preserve">2.34161448478699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36150074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55207872390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58522248268127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6100800037384</t>
+    <t xml:space="preserve">2.36150097846985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55207896232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58522272109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61007976531982</t>
   </si>
   <si>
     <t xml:space="preserve">2.56865048408508</t>
@@ -110,16 +110,16 @@
     <t xml:space="preserve">2.68962526321411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73436975479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72608375549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77579951286316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58025121688843</t>
+    <t xml:space="preserve">2.73436951637268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72608351707458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7758002281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58025145530701</t>
   </si>
   <si>
     <t xml:space="preserve">2.56202220916748</t>
@@ -128,16 +128,16 @@
     <t xml:space="preserve">2.66808152198792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62830877304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64322376251221</t>
+    <t xml:space="preserve">2.62830901145935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64322352409363</t>
   </si>
   <si>
     <t xml:space="preserve">2.60842251777649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66642427444458</t>
+    <t xml:space="preserve">2.666424036026</t>
   </si>
   <si>
     <t xml:space="preserve">2.65316677093506</t>
@@ -146,16 +146,16 @@
     <t xml:space="preserve">2.62665176391602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69293999671936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82551527023315</t>
+    <t xml:space="preserve">2.6929395198822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82551550865173</t>
   </si>
   <si>
     <t xml:space="preserve">2.81722927093506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90008926391602</t>
+    <t xml:space="preserve">2.90008902549744</t>
   </si>
   <si>
     <t xml:space="preserve">2.85865926742554</t>
@@ -167,109 +167,109 @@
     <t xml:space="preserve">2.8835175037384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87523126602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86694550514221</t>
+    <t xml:space="preserve">2.87523150444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86694526672363</t>
   </si>
   <si>
     <t xml:space="preserve">2.81888651847839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82054352760315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85368776321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79237174987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85700249671936</t>
+    <t xml:space="preserve">2.82054376602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85368800163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79237127304077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85700225830078</t>
   </si>
   <si>
     <t xml:space="preserve">2.90671801567078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8288300037384</t>
+    <t xml:space="preserve">2.82883024215698</t>
   </si>
   <si>
     <t xml:space="preserve">2.85037350654602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90837502479553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96306300163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95797729492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88169693946838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89017248153687</t>
+    <t xml:space="preserve">2.90837550163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96306276321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95797777175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88169717788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89017295837402</t>
   </si>
   <si>
     <t xml:space="preserve">2.86474585533142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94950199127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92407464981079</t>
+    <t xml:space="preserve">2.94950222969055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92407488822937</t>
   </si>
   <si>
     <t xml:space="preserve">2.96645307540894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1190128326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94272112846375</t>
+    <t xml:space="preserve">3.11901330947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94272136688232</t>
   </si>
   <si>
     <t xml:space="preserve">2.94780707359314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8833920955658</t>
+    <t xml:space="preserve">2.88339233398438</t>
   </si>
   <si>
     <t xml:space="preserve">2.87322163581848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85966038703918</t>
+    <t xml:space="preserve">2.85966086387634</t>
   </si>
   <si>
     <t xml:space="preserve">3.03256273269653</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07037305831909</t>
+    <t xml:space="preserve">3.07037377357483</t>
   </si>
   <si>
     <t xml:space="preserve">3.06866312026978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06011056900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99340057373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98484826087952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93524265289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9831371307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92498016357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92326998710632</t>
+    <t xml:space="preserve">3.06011033058167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99340033531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98484802246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93524312973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98313689231873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92497992515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92326951026917</t>
   </si>
   <si>
     <t xml:space="preserve">2.96774291992188</t>
@@ -278,19 +278,19 @@
     <t xml:space="preserve">3.03616333007812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05840039253235</t>
+    <t xml:space="preserve">3.05840015411377</t>
   </si>
   <si>
     <t xml:space="preserve">3.05497908592224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08747887611389</t>
+    <t xml:space="preserve">3.08747911453247</t>
   </si>
   <si>
     <t xml:space="preserve">3.13879418373108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12853121757507</t>
+    <t xml:space="preserve">3.12853097915649</t>
   </si>
   <si>
     <t xml:space="preserve">3.19010972976685</t>
@@ -299,25 +299,25 @@
     <t xml:space="preserve">3.15589952468872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12339949607849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12511014938354</t>
+    <t xml:space="preserve">3.12339997291565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12511038780212</t>
   </si>
   <si>
     <t xml:space="preserve">3.14734697341919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16445159912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16616201400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24142527580261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30129265785217</t>
+    <t xml:space="preserve">3.16445183753967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16616249084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24142479896545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30129337310791</t>
   </si>
   <si>
     <t xml:space="preserve">3.38681888580322</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">3.48431801795959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52708148956299</t>
+    <t xml:space="preserve">3.52708125114441</t>
   </si>
   <si>
     <t xml:space="preserve">3.62629055976868</t>
@@ -335,19 +335,19 @@
     <t xml:space="preserve">3.63655376434326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64510679244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74602699279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67760634422302</t>
+    <t xml:space="preserve">3.64510703086853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74602651596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67760682106018</t>
   </si>
   <si>
     <t xml:space="preserve">3.71181678771973</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63484358787537</t>
+    <t xml:space="preserve">3.63484334945679</t>
   </si>
   <si>
     <t xml:space="preserve">3.51681780815125</t>
@@ -359,37 +359,37 @@
     <t xml:space="preserve">3.49458146095276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50655484199524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48089742660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43129253387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35602974891663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60063290596008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64681673049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69471168518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69984340667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67589569091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6656322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59721159934998</t>
+    <t xml:space="preserve">3.50655436515808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48089718818665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43129229545593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35602927207947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60063338279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64681720733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69471144676208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69984292984009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67589592933655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66563272476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59721183776855</t>
   </si>
   <si>
     <t xml:space="preserve">3.63313293457031</t>
@@ -398,25 +398,25 @@
     <t xml:space="preserve">3.57497525215149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66050124168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68615937232971</t>
+    <t xml:space="preserve">3.66050148010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68615889549255</t>
   </si>
   <si>
     <t xml:space="preserve">3.7152373790741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73747420310974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71010613441467</t>
+    <t xml:space="preserve">3.73747396469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71010589599609</t>
   </si>
   <si>
     <t xml:space="preserve">3.69129037857056</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68957996368408</t>
+    <t xml:space="preserve">3.68958020210266</t>
   </si>
   <si>
     <t xml:space="preserve">3.73234272003174</t>
@@ -425,55 +425,55 @@
     <t xml:space="preserve">3.7203688621521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76313209533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77168488502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62115955352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64168524742126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7032642364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79734206199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75457906723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90852570533752</t>
+    <t xml:space="preserve">3.76313233375549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77168536186218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62115931510925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64168572425842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70326375961304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79734230041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75457954406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90852618217468</t>
   </si>
   <si>
     <t xml:space="preserve">3.76655244827271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72892189025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6673436164856</t>
+    <t xml:space="preserve">3.72892212867737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66734290122986</t>
   </si>
   <si>
     <t xml:space="preserve">3.50997591018677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49800229072571</t>
+    <t xml:space="preserve">3.49800252914429</t>
   </si>
   <si>
     <t xml:space="preserve">3.4894495010376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47234487533569</t>
+    <t xml:space="preserve">3.47234463691711</t>
   </si>
   <si>
     <t xml:space="preserve">3.40392398834229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43642377853394</t>
+    <t xml:space="preserve">3.43642401695251</t>
   </si>
   <si>
     <t xml:space="preserve">3.53221249580383</t>
@@ -485,28 +485,28 @@
     <t xml:space="preserve">3.46037101745605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50142335891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53563356399536</t>
+    <t xml:space="preserve">3.50142312049866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5356330871582</t>
   </si>
   <si>
     <t xml:space="preserve">3.55615973472595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6433961391449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72550058364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84865760803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82984232902527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83155298233032</t>
+    <t xml:space="preserve">3.64339637756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72550082206726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84865808486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82984256744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83155274391174</t>
   </si>
   <si>
     <t xml:space="preserve">3.87089467048645</t>
@@ -521,55 +521,55 @@
     <t xml:space="preserve">3.86405277252197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85721015930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82471084594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90681505203247</t>
+    <t xml:space="preserve">3.85721063613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82471060752869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90681552886963</t>
   </si>
   <si>
     <t xml:space="preserve">4.00260400772095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17536592483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11378717422485</t>
+    <t xml:space="preserve">4.17536544799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11378765106201</t>
   </si>
   <si>
     <t xml:space="preserve">4.00773572921753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05220890045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0812873840332</t>
+    <t xml:space="preserve">4.0522084236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08128786087036</t>
   </si>
   <si>
     <t xml:space="preserve">4.00602531433105</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09839344024658</t>
+    <t xml:space="preserve">4.09839296340942</t>
   </si>
   <si>
     <t xml:space="preserve">4.01970911026001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01115703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99576234817505</t>
+    <t xml:space="preserve">4.01115608215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99576187133789</t>
   </si>
   <si>
     <t xml:space="preserve">4.0351037979126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06247234344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13773488998413</t>
+    <t xml:space="preserve">4.06247282028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13773584365845</t>
   </si>
   <si>
     <t xml:space="preserve">4.1223406791687</t>
@@ -578,19 +578,19 @@
     <t xml:space="preserve">4.14799785614014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18905019760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25918054580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22839164733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20615530014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02141952514648</t>
+    <t xml:space="preserve">4.18904972076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25918102264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22839212417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20615577697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02142000198364</t>
   </si>
   <si>
     <t xml:space="preserve">3.99405169487</t>
@@ -602,52 +602,52 @@
     <t xml:space="preserve">4.02655124664307</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07615566253662</t>
+    <t xml:space="preserve">4.07615613937378</t>
   </si>
   <si>
     <t xml:space="preserve">4.12747192382812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11891937255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10523557662964</t>
+    <t xml:space="preserve">4.11891841888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1052360534668</t>
   </si>
   <si>
     <t xml:space="preserve">4.09668207168579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10181427001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0710244178772</t>
+    <t xml:space="preserve">4.10181379318237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07102537155151</t>
   </si>
   <si>
     <t xml:space="preserve">4.09497213363647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13089227676392</t>
+    <t xml:space="preserve">4.13089275360107</t>
   </si>
   <si>
     <t xml:space="preserve">4.21641874313354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52431106567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54996871948242</t>
+    <t xml:space="preserve">4.52431058883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54996967315674</t>
   </si>
   <si>
     <t xml:space="preserve">4.53713989257812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46444320678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5029296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56707429885864</t>
+    <t xml:space="preserve">4.46444272994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50292921066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56707382202148</t>
   </si>
   <si>
     <t xml:space="preserve">4.6226658821106</t>
@@ -656,28 +656,28 @@
     <t xml:space="preserve">4.63549470901489</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58417844772339</t>
+    <t xml:space="preserve">4.58417940139771</t>
   </si>
   <si>
     <t xml:space="preserve">4.60128402709961</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57562637329102</t>
+    <t xml:space="preserve">4.57562685012817</t>
   </si>
   <si>
     <t xml:space="preserve">4.61838912963867</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53286409378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55852174758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48154735565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51575899124146</t>
+    <t xml:space="preserve">4.53286361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55852127075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4815468788147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51575946807861</t>
   </si>
   <si>
     <t xml:space="preserve">4.4901008605957</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">4.51148223876953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63121795654297</t>
+    <t xml:space="preserve">4.63121843338013</t>
   </si>
   <si>
     <t xml:space="preserve">4.78516483306885</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">4.7338490486145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77233505249023</t>
+    <t xml:space="preserve">4.77233600616455</t>
   </si>
   <si>
     <t xml:space="preserve">4.76378345489502</t>
@@ -719,25 +719,25 @@
     <t xml:space="preserve">4.90062379837036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91772937774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94338655471802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98615074157715</t>
+    <t xml:space="preserve">4.91772890090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94338703155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98614978790283</t>
   </si>
   <si>
     <t xml:space="preserve">5.04174137115479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02035999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0716757774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08022737503052</t>
+    <t xml:space="preserve">5.02036046981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07167625427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08022785186768</t>
   </si>
   <si>
     <t xml:space="preserve">4.99470281600952</t>
@@ -746,34 +746,34 @@
     <t xml:space="preserve">5.09305763244629</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06050682067871</t>
+    <t xml:space="preserve">5.06050634384155</t>
   </si>
   <si>
     <t xml:space="preserve">4.91728496551514</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94766569137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92596483230591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9042649269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82180404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73500204086304</t>
+    <t xml:space="preserve">4.94766521453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92596530914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90426445007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82180309295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7350025177002</t>
   </si>
   <si>
     <t xml:space="preserve">4.72198247909546</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59178113937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64386129379272</t>
+    <t xml:space="preserve">4.59178066253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64386177062988</t>
   </si>
   <si>
     <t xml:space="preserve">4.73066234588623</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">4.66556167602539</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6525411605835</t>
+    <t xml:space="preserve">4.65254163742065</t>
   </si>
   <si>
     <t xml:space="preserve">4.60914039611816</t>
@@ -791,61 +791,61 @@
     <t xml:space="preserve">4.65688180923462</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54837942123413</t>
+    <t xml:space="preserve">4.54837989807129</t>
   </si>
   <si>
     <t xml:space="preserve">4.53535985946655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47025918960571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59612083435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47459983825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48761987686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46157884597778</t>
+    <t xml:space="preserve">4.47025871276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59612131118774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47459936141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48761940002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46157836914062</t>
   </si>
   <si>
     <t xml:space="preserve">4.41383838653564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38779735565186</t>
+    <t xml:space="preserve">4.38779783248901</t>
   </si>
   <si>
     <t xml:space="preserve">4.39213752746582</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40949869155884</t>
+    <t xml:space="preserve">4.40949821472168</t>
   </si>
   <si>
     <t xml:space="preserve">4.55706024169922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52233934402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57008028030396</t>
+    <t xml:space="preserve">4.52233982086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57008075714111</t>
   </si>
   <si>
     <t xml:space="preserve">4.53970050811768</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47893905639648</t>
+    <t xml:space="preserve">4.47893953323364</t>
   </si>
   <si>
     <t xml:space="preserve">4.43553876876831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42251777648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43119859695435</t>
+    <t xml:space="preserve">4.42251873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4311990737915</t>
   </si>
   <si>
     <t xml:space="preserve">4.45289897918701</t>
@@ -857,13 +857,13 @@
     <t xml:space="preserve">4.68726205825806</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60046148300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63952159881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56140089035034</t>
+    <t xml:space="preserve">4.60046100616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63952112197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56140041351318</t>
   </si>
   <si>
     <t xml:space="preserve">4.58744049072266</t>
@@ -872,28 +872,28 @@
     <t xml:space="preserve">4.61782121658325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64820146560669</t>
+    <t xml:space="preserve">4.64820098876953</t>
   </si>
   <si>
     <t xml:space="preserve">4.6048002243042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58310079574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49629878997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50497913360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42685842514038</t>
+    <t xml:space="preserve">4.58310127258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49629926681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50497961044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42685890197754</t>
   </si>
   <si>
     <t xml:space="preserve">4.49195909500122</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51799964904785</t>
+    <t xml:space="preserve">4.51800012588501</t>
   </si>
   <si>
     <t xml:space="preserve">4.80878353118896</t>
@@ -902,28 +902,28 @@
     <t xml:space="preserve">4.77840280532837</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84784460067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83482360839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74368286132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81312370300293</t>
+    <t xml:space="preserve">4.84784412384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8348240852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74368238449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81312417984009</t>
   </si>
   <si>
     <t xml:space="preserve">4.71330261230469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7046217918396</t>
+    <t xml:space="preserve">4.70462226867676</t>
   </si>
   <si>
     <t xml:space="preserve">4.72632217407227</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69594192504883</t>
+    <t xml:space="preserve">4.69594240188599</t>
   </si>
   <si>
     <t xml:space="preserve">4.7697229385376</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">4.84350347518921</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87822389602661</t>
+    <t xml:space="preserve">4.87822484970093</t>
   </si>
   <si>
     <t xml:space="preserve">4.87388467788696</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">4.86086416244507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86954498291016</t>
+    <t xml:space="preserve">4.869544506073</t>
   </si>
   <si>
     <t xml:space="preserve">4.96502542495728</t>
@@ -968,22 +968,22 @@
     <t xml:space="preserve">4.90860509872437</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99974632263184</t>
+    <t xml:space="preserve">4.99974584579468</t>
   </si>
   <si>
     <t xml:space="preserve">4.99106645584106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15598773956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12994766235352</t>
+    <t xml:space="preserve">5.1559886932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12994813919067</t>
   </si>
   <si>
     <t xml:space="preserve">5.29486989974976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41639137268066</t>
+    <t xml:space="preserve">5.41639184951782</t>
   </si>
   <si>
     <t xml:space="preserve">5.48583269119263</t>
@@ -992,37 +992,37 @@
     <t xml:space="preserve">5.43375205993652</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48149251937866</t>
+    <t xml:space="preserve">5.48149299621582</t>
   </si>
   <si>
     <t xml:space="preserve">5.42073154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39469146728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35563087463379</t>
+    <t xml:space="preserve">5.394690990448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35563039779663</t>
   </si>
   <si>
     <t xml:space="preserve">5.33393049240112</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37299108505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33827066421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20806837081909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16466808319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26448965072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25146913528442</t>
+    <t xml:space="preserve">5.37299060821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33826971054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20806884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16466856002808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26449012756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25147008895874</t>
   </si>
   <si>
     <t xml:space="preserve">5.26014947891235</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">5.18636846542358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20372915267944</t>
+    <t xml:space="preserve">5.20372867584229</t>
   </si>
   <si>
     <t xml:space="preserve">5.19504880905151</t>
@@ -1043,22 +1043,22 @@
     <t xml:space="preserve">5.18202781677246</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19938898086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22542858123779</t>
+    <t xml:space="preserve">5.19938850402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22542953491211</t>
   </si>
   <si>
     <t xml:space="preserve">5.42507171630859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61603403091431</t>
+    <t xml:space="preserve">5.61603355407715</t>
   </si>
   <si>
     <t xml:space="preserve">5.72887563705444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7115159034729</t>
+    <t xml:space="preserve">5.71151494979858</t>
   </si>
   <si>
     <t xml:space="preserve">5.78963661193848</t>
@@ -1067,49 +1067,49 @@
     <t xml:space="preserve">5.82435703277588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87643814086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88511800765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93719911575317</t>
+    <t xml:space="preserve">5.87643766403198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88511848449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93719863891602</t>
   </si>
   <si>
     <t xml:space="preserve">5.85907745361328</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80699682235718</t>
+    <t xml:space="preserve">5.80699586868286</t>
   </si>
   <si>
     <t xml:space="preserve">5.92851829528809</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97191858291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95455884933472</t>
+    <t xml:space="preserve">5.97191905975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95455932617188</t>
   </si>
   <si>
     <t xml:space="preserve">6.03268003463745</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17156171798706</t>
+    <t xml:space="preserve">6.17156219482422</t>
   </si>
   <si>
     <t xml:space="preserve">6.28440284729004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01531934738159</t>
+    <t xml:space="preserve">6.01531887054443</t>
   </si>
   <si>
     <t xml:space="preserve">6.02399969100952</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21496248245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14552116394043</t>
+    <t xml:space="preserve">6.21496200561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14552068710327</t>
   </si>
   <si>
     <t xml:space="preserve">6.40592527389526</t>
@@ -1118,28 +1118,28 @@
     <t xml:space="preserve">6.07607984542847</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98927974700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04135942459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22364282608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1368408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19760179519653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1542010307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05003976821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89379787445068</t>
+    <t xml:space="preserve">5.98927927017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04135990142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22364234924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13684129714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19760131835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15420150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05003929138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.893798828125</t>
   </si>
   <si>
     <t xml:space="preserve">5.90247774124146</t>
@@ -1151,19 +1151,19 @@
     <t xml:space="preserve">5.50319290161133</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58131313323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72019577026367</t>
+    <t xml:space="preserve">5.58131408691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72019624710083</t>
   </si>
   <si>
     <t xml:space="preserve">5.76359605789185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91983795166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99795866012573</t>
+    <t xml:space="preserve">5.91983842849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99795961380005</t>
   </si>
   <si>
     <t xml:space="preserve">5.83303737640381</t>
@@ -1184,28 +1184,28 @@
     <t xml:space="preserve">5.58999395370483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52055358886719</t>
+    <t xml:space="preserve">5.52055311203003</t>
   </si>
   <si>
     <t xml:space="preserve">5.38167095184326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44243144989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46847248077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67679500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64207458496094</t>
+    <t xml:space="preserve">5.44243240356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46847200393677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67679452896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64207410812378</t>
   </si>
   <si>
     <t xml:space="preserve">5.55527400970459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53791284561157</t>
+    <t xml:space="preserve">5.53791332244873</t>
   </si>
   <si>
     <t xml:space="preserve">5.57263326644897</t>
@@ -1214,19 +1214,19 @@
     <t xml:space="preserve">5.5292329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39903116226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39035129547119</t>
+    <t xml:space="preserve">5.3990306854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39035177230835</t>
   </si>
   <si>
     <t xml:space="preserve">5.45111227035522</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09344053268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81567621231079</t>
+    <t xml:space="preserve">6.09344100952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81567668914795</t>
   </si>
   <si>
     <t xml:space="preserve">5.77227592468262</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">5.73755598068237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40771150588989</t>
+    <t xml:space="preserve">5.40771102905273</t>
   </si>
   <si>
     <t xml:space="preserve">5.24278879165649</t>
@@ -1244,13 +1244,13 @@
     <t xml:space="preserve">5.06918716430664</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98238563537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07618761062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1561975479126</t>
+    <t xml:space="preserve">4.98238611221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07618808746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15619802474976</t>
   </si>
   <si>
     <t xml:space="preserve">5.08507776260376</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">5.11174821853638</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13841772079468</t>
+    <t xml:space="preserve">5.13841867446899</t>
   </si>
   <si>
     <t xml:space="preserve">5.20953798294067</t>
@@ -1271,37 +1271,37 @@
     <t xml:space="preserve">5.14730787277222</t>
   </si>
   <si>
-    <t xml:space="preserve">5.067298412323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05840826034546</t>
+    <t xml:space="preserve">5.06729793548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05840730667114</t>
   </si>
   <si>
     <t xml:space="preserve">5.04062795639038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04951763153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94283771514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77392816543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90727853775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76503753662109</t>
+    <t xml:space="preserve">5.04951810836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94283819198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77392768859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90727806091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76503801345825</t>
   </si>
   <si>
     <t xml:space="preserve">4.92505788803101</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88949775695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02284812927246</t>
+    <t xml:space="preserve">4.88949823379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0228476524353</t>
   </si>
   <si>
     <t xml:space="preserve">4.97839784622192</t>
@@ -1310,28 +1310,28 @@
     <t xml:space="preserve">4.91616821289062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95172786712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9339485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89838790893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80948781967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78281831741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75614786148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98728847503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10285758972168</t>
+    <t xml:space="preserve">4.95172834396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93394804000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89838838577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80948829650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78281784057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75614833831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98728799819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10285806655884</t>
   </si>
   <si>
     <t xml:space="preserve">4.96061754226685</t>
@@ -1340,34 +1340,34 @@
     <t xml:space="preserve">5.20064783096313</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21842813491821</t>
+    <t xml:space="preserve">5.21842765808105</t>
   </si>
   <si>
     <t xml:space="preserve">5.27176809310913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33399724960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23620748519897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18286800384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01395797729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99617719650269</t>
+    <t xml:space="preserve">5.33399772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23620796203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18286752700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01395750045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.996178150177</t>
   </si>
   <si>
     <t xml:space="preserve">5.00506782531738</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37844753265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47623729705811</t>
+    <t xml:space="preserve">5.37844848632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47623777389526</t>
   </si>
   <si>
     <t xml:space="preserve">5.56513786315918</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">5.6807074546814</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65403842926025</t>
+    <t xml:space="preserve">5.6540379524231</t>
   </si>
   <si>
     <t xml:space="preserve">5.63625764846802</t>
@@ -1394,79 +1394,79 @@
     <t xml:space="preserve">5.89406776428223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77849769592285</t>
+    <t xml:space="preserve">5.77849721908569</t>
   </si>
   <si>
     <t xml:space="preserve">5.84072780609131</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76071691513062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92073726654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83183717727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44956827163696</t>
+    <t xml:space="preserve">5.76071786880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92073678970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83183765411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4495677947998</t>
   </si>
   <si>
     <t xml:space="preserve">5.58291816711426</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43178749084473</t>
+    <t xml:space="preserve">5.43178796768188</t>
   </si>
   <si>
     <t xml:space="preserve">5.36955738067627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60958814620972</t>
+    <t xml:space="preserve">5.60958671569824</t>
   </si>
   <si>
     <t xml:space="preserve">5.86739730834961</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78738832473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52068758010864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49401760101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5740270614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59180784225464</t>
+    <t xml:space="preserve">5.78738784790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5206880569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49401807785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57402801513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5918083190918</t>
   </si>
   <si>
     <t xml:space="preserve">5.6451473236084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71626710891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73404741287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81405782699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67181730270386</t>
+    <t xml:space="preserve">5.71626806259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73404836654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81405735015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67181777954102</t>
   </si>
   <si>
     <t xml:space="preserve">5.5117974281311</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85850763320923</t>
+    <t xml:space="preserve">5.85850811004639</t>
   </si>
   <si>
     <t xml:space="preserve">5.66292762756348</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53846788406372</t>
+    <t xml:space="preserve">5.53846740722656</t>
   </si>
   <si>
     <t xml:space="preserve">5.90295743942261</t>
@@ -1481,25 +1481,25 @@
     <t xml:space="preserve">5.6184778213501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46734809875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60069799423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4584584236145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50290775299072</t>
+    <t xml:space="preserve">5.46734714508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60069751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45845699310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50290727615356</t>
   </si>
   <si>
     <t xml:space="preserve">5.34288787841797</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62736797332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52957773208618</t>
+    <t xml:space="preserve">5.62736749649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52957725524902</t>
   </si>
   <si>
     <t xml:space="preserve">5.42289781570435</t>
@@ -1511,7 +1511,7 @@
     <t xml:space="preserve">5.70737743377686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69848728179932</t>
+    <t xml:space="preserve">5.69848775863647</t>
   </si>
   <si>
     <t xml:space="preserve">6.00074768066406</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">5.92962789535522</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94740772247314</t>
+    <t xml:space="preserve">5.94740676879883</t>
   </si>
   <si>
     <t xml:space="preserve">5.93851757049561</t>
@@ -1529,22 +1529,22 @@
     <t xml:space="preserve">5.99185752868652</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24077749252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40968799591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48080682754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.623046875</t>
+    <t xml:space="preserve">6.24077796936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40968751907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48080825805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62304782867432</t>
   </si>
   <si>
     <t xml:space="preserve">6.84529685974121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99642753601074</t>
+    <t xml:space="preserve">6.99642705917358</t>
   </si>
   <si>
     <t xml:space="preserve">7.0142068862915</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">7.2453465461731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27201700210571</t>
+    <t xml:space="preserve">7.27201747894287</t>
   </si>
   <si>
     <t xml:space="preserve">7.33424711227417</t>
@@ -1577,22 +1577,22 @@
     <t xml:space="preserve">7.476487159729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76985692977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73429584503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72540712356567</t>
+    <t xml:space="preserve">7.76985645294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7342963218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72540616989136</t>
   </si>
   <si>
     <t xml:space="preserve">7.79652643203735</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80541658401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22324562072754</t>
+    <t xml:space="preserve">7.80541753768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22324657440186</t>
   </si>
   <si>
     <t xml:space="preserve">8.21435642242432</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">8.15212726593018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12545585632324</t>
+    <t xml:space="preserve">8.12545776367188</t>
   </si>
   <si>
     <t xml:space="preserve">8.00099658966064</t>
@@ -1613,13 +1613,13 @@
     <t xml:space="preserve">8.34770679473877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42771530151367</t>
+    <t xml:space="preserve">8.42771625518799</t>
   </si>
   <si>
     <t xml:space="preserve">8.48105621337891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46327686309814</t>
+    <t xml:space="preserve">8.46327781677246</t>
   </si>
   <si>
     <t xml:space="preserve">8.52550601959229</t>
@@ -1634,55 +1634,55 @@
     <t xml:space="preserve">8.80109596252441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88999557495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19225692749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37005519866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47673606872559</t>
+    <t xml:space="preserve">8.88999652862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19225597381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37005710601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47673511505127</t>
   </si>
   <si>
     <t xml:space="preserve">9.49451637268066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31671524047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15669631958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3522777557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40561676025391</t>
+    <t xml:space="preserve">9.31671619415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15669536590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35227680206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40561580657959</t>
   </si>
   <si>
     <t xml:space="preserve">9.69009590148926</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86789703369141</t>
+    <t xml:space="preserve">9.86789608001709</t>
   </si>
   <si>
     <t xml:space="preserve">9.83233642578125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77899551391602</t>
+    <t xml:space="preserve">9.77899646759033</t>
   </si>
   <si>
     <t xml:space="preserve">9.44117546081543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21003532409668</t>
+    <t xml:space="preserve">9.210036277771</t>
   </si>
   <si>
     <t xml:space="preserve">9.58341598510742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51229572296143</t>
+    <t xml:space="preserve">9.51229667663574</t>
   </si>
   <si>
     <t xml:space="preserve">9.6723165512085</t>
@@ -1691,31 +1691,31 @@
     <t xml:space="preserve">9.85011577606201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0990352630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0279159545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99235439300537</t>
+    <t xml:space="preserve">10.0990362167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0279150009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.992356300354</t>
   </si>
   <si>
     <t xml:space="preserve">10.0101356506348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76121520996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88567543029785</t>
+    <t xml:space="preserve">9.76121425628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88567638397217</t>
   </si>
   <si>
     <t xml:space="preserve">10.2234964370728</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4368562698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6679944992065</t>
+    <t xml:space="preserve">10.4368553161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6679954528809</t>
   </si>
   <si>
     <t xml:space="preserve">11.4147548675537</t>
@@ -1724,16 +1724,16 @@
     <t xml:space="preserve">11.3614149093628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3080768585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4325342178345</t>
+    <t xml:space="preserve">11.3080759048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4325361251831</t>
   </si>
   <si>
     <t xml:space="preserve">11.6814556121826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8948154449463</t>
+    <t xml:space="preserve">11.8948135375977</t>
   </si>
   <si>
     <t xml:space="preserve">11.9659357070923</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">12.1437349319458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6281156539917</t>
+    <t xml:space="preserve">11.6281147003174</t>
   </si>
   <si>
     <t xml:space="preserve">11.4001140594482</t>
@@ -1772,19 +1772,19 @@
     <t xml:space="preserve">12.9925088882446</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8296518325806</t>
+    <t xml:space="preserve">12.8296508789062</t>
   </si>
   <si>
     <t xml:space="preserve">12.7391738891602</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7753648757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.395359992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2867889404297</t>
+    <t xml:space="preserve">12.7753639221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3953609466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2867879867554</t>
   </si>
   <si>
     <t xml:space="preserve">12.6306018829346</t>
@@ -1793,52 +1793,52 @@
     <t xml:space="preserve">12.4496469497681</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2144079208374</t>
+    <t xml:space="preserve">12.2144069671631</t>
   </si>
   <si>
     <t xml:space="preserve">12.1058349609375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8705930709839</t>
+    <t xml:space="preserve">11.8705949783325</t>
   </si>
   <si>
     <t xml:space="preserve">11.9067850112915</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4724950790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4182090759277</t>
+    <t xml:space="preserve">11.4724941253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4182081222534</t>
   </si>
   <si>
     <t xml:space="preserve">11.5810670852661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8524990081787</t>
+    <t xml:space="preserve">11.8524980545044</t>
   </si>
   <si>
     <t xml:space="preserve">12.0877389907837</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8344039916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8886890411377</t>
+    <t xml:space="preserve">11.8344030380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.888689994812</t>
   </si>
   <si>
     <t xml:space="preserve">11.4363050460815</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3277320861816</t>
+    <t xml:space="preserve">11.3277311325073</t>
   </si>
   <si>
     <t xml:space="preserve">11.2734451293945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1829681396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1648731231689</t>
+    <t xml:space="preserve">11.1829690933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1648721694946</t>
   </si>
   <si>
     <t xml:space="preserve">10.8391551971436</t>
@@ -1850,34 +1850,34 @@
     <t xml:space="preserve">10.6762962341309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5134382247925</t>
+    <t xml:space="preserve">10.5134372711182</t>
   </si>
   <si>
     <t xml:space="preserve">10.9115371704102</t>
   </si>
   <si>
-    <t xml:space="preserve">11.291540145874</t>
+    <t xml:space="preserve">11.2915410995483</t>
   </si>
   <si>
     <t xml:space="preserve">11.1467771530151</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7667722702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1105871200562</t>
+    <t xml:space="preserve">10.766773223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1105861663818</t>
   </si>
   <si>
     <t xml:space="preserve">11.1286821365356</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6220102310181</t>
+    <t xml:space="preserve">10.6220092773438</t>
   </si>
   <si>
     <t xml:space="preserve">11.0020132064819</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6039152145386</t>
+    <t xml:space="preserve">10.6039142608643</t>
   </si>
   <si>
     <t xml:space="preserve">10.4953422546387</t>
@@ -1886,7 +1886,7 @@
     <t xml:space="preserve">10.2781972885132</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3143882751465</t>
+    <t xml:space="preserve">10.3143873214722</t>
   </si>
   <si>
     <t xml:space="preserve">9.89819240570068</t>
@@ -1895,13 +1895,13 @@
     <t xml:space="preserve">9.93438339233398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80771541595459</t>
+    <t xml:space="preserve">9.80771636962891</t>
   </si>
   <si>
     <t xml:space="preserve">9.68104839324951</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95247840881348</t>
+    <t xml:space="preserve">9.95247936248779</t>
   </si>
   <si>
     <t xml:space="preserve">10.2420063018799</t>
@@ -1913,37 +1913,37 @@
     <t xml:space="preserve">10.3867692947388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4410572052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55438041687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1153383255005</t>
+    <t xml:space="preserve">10.4410552978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55438137054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1153392791748</t>
   </si>
   <si>
     <t xml:space="preserve">10.3505783081055</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4048652648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7486772537231</t>
+    <t xml:space="preserve">10.4048643112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7486782073975</t>
   </si>
   <si>
     <t xml:space="preserve">11.0201101303101</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8572492599487</t>
+    <t xml:space="preserve">10.8572511672974</t>
   </si>
   <si>
     <t xml:space="preserve">10.8753461837769</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5858201980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8029632568359</t>
+    <t xml:space="preserve">10.5858192443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8029642105103</t>
   </si>
   <si>
     <t xml:space="preserve">10.7124872207642</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">11.4543991088867</t>
   </si>
   <si>
-    <t xml:space="preserve">11.725830078125</t>
+    <t xml:space="preserve">11.7258310317993</t>
   </si>
   <si>
     <t xml:space="preserve">11.9972620010376</t>
@@ -1970,7 +1970,7 @@
     <t xml:space="preserve">12.160120010376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0515470504761</t>
+    <t xml:space="preserve">12.0515480041504</t>
   </si>
   <si>
     <t xml:space="preserve">12.0334529876709</t>
@@ -1979,16 +1979,16 @@
     <t xml:space="preserve">11.9429759979248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7620210647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9477281570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9658231735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1877202987671</t>
+    <t xml:space="preserve">11.7620220184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9477272033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9658222198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1877212524414</t>
   </si>
   <si>
     <t xml:space="preserve">9.98867130279541</t>
@@ -1997,55 +1997,55 @@
     <t xml:space="preserve">10.0429573059082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91628932952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1696243286133</t>
+    <t xml:space="preserve">9.91628837585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1696252822876</t>
   </si>
   <si>
     <t xml:space="preserve">10.531533241272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4229612350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1334342956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.332483291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2239112854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0972423553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0610513687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0791473388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1515293121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0562992095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8934412002563</t>
+    <t xml:space="preserve">10.4229602813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.13343334198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3324842453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2239122390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.097243309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0610523223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0791482925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1515302658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.056300163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.893440246582</t>
   </si>
   <si>
     <t xml:space="preserve">10.5496282577515</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3686742782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82581043243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77152633666992</t>
+    <t xml:space="preserve">10.3686752319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8258113861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77152538299561</t>
   </si>
   <si>
     <t xml:space="preserve">9.69914436340332</t>
@@ -2054,22 +2054,22 @@
     <t xml:space="preserve">9.51819038391113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71724033355713</t>
+    <t xml:space="preserve">9.7172384262085</t>
   </si>
   <si>
     <t xml:space="preserve">9.42771244049072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59057235717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3639221191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9791660308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4677419662476</t>
+    <t xml:space="preserve">9.59057140350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3639230728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9791669845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4677429199219</t>
   </si>
   <si>
     <t xml:space="preserve">12.3772659301758</t>
@@ -2084,25 +2084,25 @@
     <t xml:space="preserve">11.6172580718994</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0924921035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6943912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62676334381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80341911315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68580055236816</t>
+    <t xml:space="preserve">11.0924911499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6943922042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62676239013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80342102050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68579959869385</t>
   </si>
   <si>
     <t xml:space="preserve">8.43246459960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04816484451294</t>
+    <t xml:space="preserve">7.0481653213501</t>
   </si>
   <si>
     <t xml:space="preserve">7.32864427566528</t>
@@ -2117,7 +2117,7 @@
     <t xml:space="preserve">6.58673238754272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65006589889526</t>
+    <t xml:space="preserve">6.65006542205811</t>
   </si>
   <si>
     <t xml:space="preserve">6.96673583984375</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">7.16578531265259</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05721235275269</t>
+    <t xml:space="preserve">7.05721282958984</t>
   </si>
   <si>
     <t xml:space="preserve">7.28340578079224</t>
@@ -2138,19 +2138,19 @@
     <t xml:space="preserve">7.60912275314331</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76293325424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34198760986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04341411590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61341953277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41436862945557</t>
+    <t xml:space="preserve">7.7629337310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3419885635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04341220855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61341762542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41436958312988</t>
   </si>
   <si>
     <t xml:space="preserve">8.25150966644287</t>
@@ -2159,25 +2159,25 @@
     <t xml:space="preserve">8.93008804321289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35533046722412</t>
+    <t xml:space="preserve">9.35533142089844</t>
   </si>
   <si>
     <t xml:space="preserve">9.04770946502686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26485252380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50009441375732</t>
+    <t xml:space="preserve">9.26485347747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50009536743164</t>
   </si>
   <si>
     <t xml:space="preserve">9.86200141906738</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2191581726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9839191436768</t>
+    <t xml:space="preserve">11.2191591262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9839181900024</t>
   </si>
   <si>
     <t xml:space="preserve">10.6582002639771</t>
@@ -2186,13 +2186,13 @@
     <t xml:space="preserve">9.97057437896729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2058153152466</t>
+    <t xml:space="preserve">10.2058162689209</t>
   </si>
   <si>
     <t xml:space="preserve">9.84390735626221</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4591512680054</t>
+    <t xml:space="preserve">10.4591503143311</t>
   </si>
   <si>
     <t xml:space="preserve">10.9296312332153</t>
@@ -2201,16 +2201,16 @@
     <t xml:space="preserve">10.7305822372437</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8210601806641</t>
+    <t xml:space="preserve">10.8210592269897</t>
   </si>
   <si>
     <t xml:space="preserve">12.0696439743042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5582189559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8477468490601</t>
+    <t xml:space="preserve">12.558219909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8477458953857</t>
   </si>
   <si>
     <t xml:space="preserve">13.1915588378906</t>
@@ -2219,37 +2219,37 @@
     <t xml:space="preserve">12.757269859314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7934598922729</t>
+    <t xml:space="preserve">12.7934608459473</t>
   </si>
   <si>
     <t xml:space="preserve">12.4315519332886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.594409942627</t>
+    <t xml:space="preserve">12.5944108963013</t>
   </si>
   <si>
     <t xml:space="preserve">12.6486968994141</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7210779190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8658409118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1553688049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0287017822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1191778182983</t>
+    <t xml:space="preserve">12.7210788726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8658418655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1553678512573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0286998748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1191787719727</t>
   </si>
   <si>
     <t xml:space="preserve">12.9382238388062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.082986831665</t>
+    <t xml:space="preserve">13.0829877853394</t>
   </si>
   <si>
     <t xml:space="preserve">13.3725128173828</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">13.3544178009033</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4534864425659</t>
+    <t xml:space="preserve">15.4534873962402</t>
   </si>
   <si>
     <t xml:space="preserve">16.2496852874756</t>
@@ -2267,34 +2267,34 @@
     <t xml:space="preserve">16.2858753204346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3763542175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6477832794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8334903717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0687313079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8696813583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9239683151245</t>
+    <t xml:space="preserve">16.3763523101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6477851867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8334894180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0687294006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8696823120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9239673614502</t>
   </si>
   <si>
     <t xml:space="preserve">15.9058713912964</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8515892028809</t>
+    <t xml:space="preserve">15.8515853881836</t>
   </si>
   <si>
     <t xml:space="preserve">16.0144443511963</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7973003387451</t>
+    <t xml:space="preserve">15.7972993850708</t>
   </si>
   <si>
     <t xml:space="preserve">16.2677803039551</t>
@@ -2303,97 +2303,97 @@
     <t xml:space="preserve">16.0325393676758</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7792043685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7249193191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.412540435791</t>
+    <t xml:space="preserve">15.7792053222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7249164581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4125423431396</t>
   </si>
   <si>
     <t xml:space="preserve">15.8153944015503</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9420642852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6344423294067</t>
+    <t xml:space="preserve">15.9420623779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6344413757324</t>
   </si>
   <si>
     <t xml:space="preserve">16.1049213409424</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9601583480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6887264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6163444519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8925275802612</t>
+    <t xml:space="preserve">15.9601564407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6887273788452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6163454055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8925285339355</t>
   </si>
   <si>
     <t xml:space="preserve">15.6525344848633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3630075454712</t>
+    <t xml:space="preserve">15.3630104064941</t>
   </si>
   <si>
     <t xml:space="preserve">15.4896783828735</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1458644866943</t>
+    <t xml:space="preserve">15.1458654403687</t>
   </si>
   <si>
     <t xml:space="preserve">15.0372934341431</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7430114746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8201475143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2906274795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5887489318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7697010040283</t>
+    <t xml:space="preserve">15.7430124282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8201465606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2906284332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5887451171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7696990966797</t>
   </si>
   <si>
     <t xml:space="preserve">18.0230350494385</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1359062194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2763710021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.041130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4258880615234</t>
+    <t xml:space="preserve">19.1359043121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2763729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0411338806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4258861541748</t>
   </si>
   <si>
     <t xml:space="preserve">17.7335090637207</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2992210388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0458850860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0277862548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7020683288574</t>
+    <t xml:space="preserve">17.2992191314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0458831787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0277881622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7020702362061</t>
   </si>
   <si>
     <t xml:space="preserve">17.009693145752</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">18.5025653839111</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1406555175781</t>
+    <t xml:space="preserve">18.1406574249268</t>
   </si>
   <si>
     <t xml:space="preserve">17.9687519073486</t>
@@ -2414,28 +2414,28 @@
     <t xml:space="preserve">17.4982681274414</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9868431091309</t>
+    <t xml:space="preserve">17.9868450164795</t>
   </si>
   <si>
     <t xml:space="preserve">18.5930404663086</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1544551849365</t>
+    <t xml:space="preserve">17.1544532775879</t>
   </si>
   <si>
     <t xml:space="preserve">17.2449321746826</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1182632446289</t>
+    <t xml:space="preserve">17.1182651519775</t>
   </si>
   <si>
     <t xml:space="preserve">16.8106422424316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8287372589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9735012054443</t>
+    <t xml:space="preserve">16.8287391662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9735050201416</t>
   </si>
   <si>
     <t xml:space="preserve">16.9192180633545</t>
@@ -2444,19 +2444,19 @@
     <t xml:space="preserve">17.0639801025391</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8468341827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9011192321777</t>
+    <t xml:space="preserve">16.8468360900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.901123046875</t>
   </si>
   <si>
     <t xml:space="preserve">17.3173141479492</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2087421417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2268390655518</t>
+    <t xml:space="preserve">17.208740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2268352508545</t>
   </si>
   <si>
     <t xml:space="preserve">18.3668479919434</t>
@@ -2465,16 +2465,16 @@
     <t xml:space="preserve">18.4573249816895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6382827758789</t>
+    <t xml:space="preserve">18.6382808685303</t>
   </si>
   <si>
     <t xml:space="preserve">18.7287578582764</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9549503326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8644714355469</t>
+    <t xml:space="preserve">18.9549522399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8644733428955</t>
   </si>
   <si>
     <t xml:space="preserve">19.6335277557373</t>
@@ -2483,16 +2483,16 @@
     <t xml:space="preserve">19.6787662506104</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5430526733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0454292297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0001888275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3168601989746</t>
+    <t xml:space="preserve">19.5430507659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0454254150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0001907348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.316858291626</t>
   </si>
   <si>
     <t xml:space="preserve">18.3216094970703</t>
@@ -2504,16 +2504,16 @@
     <t xml:space="preserve">19.0906658172607</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6835174560547</t>
+    <t xml:space="preserve">18.6835193634033</t>
   </si>
   <si>
     <t xml:space="preserve">18.0954189300537</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0049381256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5706520080566</t>
+    <t xml:space="preserve">18.004940032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.570650100708</t>
   </si>
   <si>
     <t xml:space="preserve">17.8239879608154</t>
@@ -2522,19 +2522,19 @@
     <t xml:space="preserve">17.6430320739746</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8058929443359</t>
+    <t xml:space="preserve">17.8058891296387</t>
   </si>
   <si>
     <t xml:space="preserve">19.2716178894043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1811447143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2668685913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4930591583252</t>
+    <t xml:space="preserve">19.1811428070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.26686668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4930610656738</t>
   </si>
   <si>
     <t xml:space="preserve">20.9906845092773</t>
@@ -2546,73 +2546,73 @@
     <t xml:space="preserve">20.3573455810547</t>
   </si>
   <si>
-    <t xml:space="preserve">19.904956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7692432403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7192535400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9954357147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2263832092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4525756835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4073371887207</t>
+    <t xml:space="preserve">19.9049587249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7692451477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7192516326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9954376220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2263813018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4525737762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4073333740234</t>
   </si>
   <si>
     <t xml:space="preserve">17.6249370574951</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7877960205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4978122711182</t>
+    <t xml:space="preserve">17.7877941131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4978103637695</t>
   </si>
   <si>
     <t xml:space="preserve">20.0859146118164</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1311511993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8597202301025</t>
+    <t xml:space="preserve">20.1311531066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8597221374512</t>
   </si>
   <si>
     <t xml:space="preserve">20.674015045166</t>
   </si>
   <si>
-    <t xml:space="preserve">21.035924911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8097305297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.628776550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.312105178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4478225708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8821144104004</t>
+    <t xml:space="preserve">21.0359210968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8097286224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6287746429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3121089935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4478244781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8821105957031</t>
   </si>
   <si>
     <t xml:space="preserve">21.2802104949951</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3344955444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.587833404541</t>
+    <t xml:space="preserve">21.3344974517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5878353118896</t>
   </si>
   <si>
     <t xml:space="preserve">21.6602153778076</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">22.4745101928711</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1125984191895</t>
+    <t xml:space="preserve">22.1126003265381</t>
   </si>
   <si>
     <t xml:space="preserve">22.058313369751</t>
@@ -2654,13 +2654,13 @@
     <t xml:space="preserve">22.6011772155762</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6373691558838</t>
+    <t xml:space="preserve">22.6373653411865</t>
   </si>
   <si>
     <t xml:space="preserve">22.420223236084</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4021263122559</t>
+    <t xml:space="preserve">22.4021282196045</t>
   </si>
   <si>
     <t xml:space="preserve">21.3525924682617</t>
@@ -2672,19 +2672,19 @@
     <t xml:space="preserve">22.0945053100586</t>
   </si>
   <si>
-    <t xml:space="preserve">22.583080291748</t>
+    <t xml:space="preserve">22.5830821990967</t>
   </si>
   <si>
     <t xml:space="preserve">23.0354652404785</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0173721313477</t>
+    <t xml:space="preserve">23.017370223999</t>
   </si>
   <si>
     <t xml:space="preserve">23.3611831665039</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2707061767578</t>
+    <t xml:space="preserve">23.2707042694092</t>
   </si>
   <si>
     <t xml:space="preserve">25.0440578460693</t>
@@ -2696,16 +2696,16 @@
     <t xml:space="preserve">24.9716758728027</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0621509552002</t>
+    <t xml:space="preserve">25.0621528625488</t>
   </si>
   <si>
     <t xml:space="preserve">25.9126377105713</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2383556365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.676570892334</t>
+    <t xml:space="preserve">26.2383575439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6765727996826</t>
   </si>
   <si>
     <t xml:space="preserve">26.7130928039551</t>
@@ -2717,19 +2717,19 @@
     <t xml:space="preserve">26.6583156585693</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8226470947266</t>
+    <t xml:space="preserve">26.8226451873779</t>
   </si>
   <si>
     <t xml:space="preserve">26.95046043396</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5712699890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.626049041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.064266204834</t>
+    <t xml:space="preserve">27.5712718963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6260471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0642642974854</t>
   </si>
   <si>
     <t xml:space="preserve">28.283374786377</t>
@@ -2738,34 +2738,34 @@
     <t xml:space="preserve">29.8171443939209</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5980319976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9589614868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1275482177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.652811050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1092891693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9632129669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4014358520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2188396453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2961292266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8213920593262</t>
+    <t xml:space="preserve">29.5980339050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.958963394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1275463104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6528091430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1092872619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9632148742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4014320373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2188415527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2961273193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8213901519775</t>
   </si>
   <si>
     <t xml:space="preserve">31.1683158874512</t>
@@ -2774,46 +2774,46 @@
     <t xml:space="preserve">30.2371006011963</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4154415130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8536624908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1780700683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.145809173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7075862884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0545082092285</t>
+    <t xml:space="preserve">29.4154434204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8536605834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.178071975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1458053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7075881958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0545101165771</t>
   </si>
   <si>
     <t xml:space="preserve">32.8664131164551</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5462532043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0532569885254</t>
+    <t xml:space="preserve">34.546257019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0532608032227</t>
   </si>
   <si>
     <t xml:space="preserve">33.0855255126953</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7245941162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6880722045898</t>
+    <t xml:space="preserve">33.7245903015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6880760192871</t>
   </si>
   <si>
     <t xml:space="preserve">33.5785217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4872283935547</t>
+    <t xml:space="preserve">33.4872245788574</t>
   </si>
   <si>
     <t xml:space="preserve">33.7976303100586</t>
@@ -2822,28 +2822,28 @@
     <t xml:space="preserve">33.1403007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">33.286376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2273483276367</t>
+    <t xml:space="preserve">33.2863731384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2273445129395</t>
   </si>
   <si>
     <t xml:space="preserve">32.8846740722656</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7568588256836</t>
+    <t xml:space="preserve">32.7568626403809</t>
   </si>
   <si>
     <t xml:space="preserve">32.6473045349121</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0307464599609</t>
+    <t xml:space="preserve">33.0307502746582</t>
   </si>
   <si>
     <t xml:space="preserve">32.7751197814941</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4099388122559</t>
+    <t xml:space="preserve">32.4099349975586</t>
   </si>
   <si>
     <t xml:space="preserve">32.6655654907227</t>
@@ -2855,13 +2855,13 @@
     <t xml:space="preserve">35.605281829834</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2401008605957</t>
+    <t xml:space="preserve">35.2400970458984</t>
   </si>
   <si>
     <t xml:space="preserve">35.8791694641113</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4774703979492</t>
+    <t xml:space="preserve">35.477466583252</t>
   </si>
   <si>
     <t xml:space="preserve">35.0940284729004</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">35.5870246887207</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7878723144531</t>
+    <t xml:space="preserve">35.7878761291504</t>
   </si>
   <si>
     <t xml:space="preserve">36.0435028076172</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">39.3849220275879</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2205924987793</t>
+    <t xml:space="preserve">39.2205848693848</t>
   </si>
   <si>
     <t xml:space="preserve">39.1292953491211</t>
@@ -2906,16 +2906,16 @@
     <t xml:space="preserve">37.2486038208008</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0660133361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2668609619141</t>
+    <t xml:space="preserve">37.0660095214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2668647766113</t>
   </si>
   <si>
     <t xml:space="preserve">36.7008323669434</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2120819091797</t>
+    <t xml:space="preserve">37.212085723877</t>
   </si>
   <si>
     <t xml:space="preserve">37.559009552002</t>
@@ -2924,31 +2924,31 @@
     <t xml:space="preserve">38.0154838562012</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6503067016602</t>
+    <t xml:space="preserve">37.6503028869629</t>
   </si>
   <si>
     <t xml:space="preserve">35.6235427856445</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2316017150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9942283630371</t>
+    <t xml:space="preserve">33.2315979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9942245483398</t>
   </si>
   <si>
     <t xml:space="preserve">33.3594131469727</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0490112304688</t>
+    <t xml:space="preserve">33.0490074157715</t>
   </si>
   <si>
     <t xml:space="preserve">34.7836227416992</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3819236755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.893180847168</t>
+    <t xml:space="preserve">34.3819198608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8931770324707</t>
   </si>
   <si>
     <t xml:space="preserve">32.9577102661133</t>
@@ -2957,13 +2957,13 @@
     <t xml:space="preserve">33.63330078125</t>
   </si>
   <si>
-    <t xml:space="preserve">35.513988494873</t>
+    <t xml:space="preserve">35.5139923095703</t>
   </si>
   <si>
     <t xml:space="preserve">36.4817199707031</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3173904418945</t>
+    <t xml:space="preserve">36.3173866271973</t>
   </si>
   <si>
     <t xml:space="preserve">36.6095314025879</t>
@@ -2972,16 +2972,16 @@
     <t xml:space="preserve">37.7781181335449</t>
   </si>
   <si>
-    <t xml:space="preserve">38.271110534668</t>
+    <t xml:space="preserve">38.2711143493652</t>
   </si>
   <si>
     <t xml:space="preserve">39.2023315429688</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7190895080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8426475524902</t>
+    <t xml:space="preserve">36.7190933227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8426513671875</t>
   </si>
   <si>
     <t xml:space="preserve">34.9662170410156</t>
@@ -2996,10 +2996,10 @@
     <t xml:space="preserve">37.8876724243164</t>
   </si>
   <si>
-    <t xml:space="preserve">38.526741027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8006324768066</t>
+    <t xml:space="preserve">38.5267448425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8006248474121</t>
   </si>
   <si>
     <t xml:space="preserve">37.6685600280762</t>
@@ -3011,13 +3011,13 @@
     <t xml:space="preserve">35.258358001709</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9114379882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3636589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8341522216797</t>
+    <t xml:space="preserve">34.9114418029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3636627197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8341484069824</t>
   </si>
   <si>
     <t xml:space="preserve">33.5967788696289</t>
@@ -3038,61 +3038,61 @@
     <t xml:space="preserve">34.7105865478516</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3454055786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0715179443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1950759887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6150360107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9254417419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9436988830566</t>
+    <t xml:space="preserve">34.345401763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0715217590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1950836181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6150398254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9254455566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9437065124512</t>
   </si>
   <si>
     <t xml:space="preserve">34.6192893981934</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5827751159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7288436889648</t>
+    <t xml:space="preserve">34.5827713012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7288475036621</t>
   </si>
   <si>
     <t xml:space="preserve">35.0027313232422</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8384017944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8749198913574</t>
+    <t xml:space="preserve">34.8383979797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8749160766602</t>
   </si>
   <si>
     <t xml:space="preserve">32.5377540588379</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1725692749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1360511779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4519577026367</t>
+    <t xml:space="preserve">32.1725730895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1360473632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4519596099854</t>
   </si>
   <si>
     <t xml:space="preserve">29.8901805877686</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1640663146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4294490814209</t>
+    <t xml:space="preserve">30.1640644073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4294471740723</t>
   </si>
   <si>
     <t xml:space="preserve">28.1007862091064</t>
@@ -3104,7 +3104,7 @@
     <t xml:space="preserve">28.9954814910889</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2693710327148</t>
+    <t xml:space="preserve">29.2693691253662</t>
   </si>
   <si>
     <t xml:space="preserve">28.6850776672363</t>
@@ -3116,13 +3116,13 @@
     <t xml:space="preserve">26.8956813812256</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8451557159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9729709625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6668167114258</t>
+    <t xml:space="preserve">27.845157623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9729690551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6668186187744</t>
   </si>
   <si>
     <t xml:space="preserve">29.1232948303223</t>
@@ -3131,22 +3131,22 @@
     <t xml:space="preserve">28.9224452972412</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6077880859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7538604736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3479099273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.544506072998</t>
+    <t xml:space="preserve">27.6077861785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7538623809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3479118347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5445079803467</t>
   </si>
   <si>
     <t xml:space="preserve">26.7496089935303</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7861289978027</t>
+    <t xml:space="preserve">26.7861309051514</t>
   </si>
   <si>
     <t xml:space="preserve">26.5670204162598</t>
@@ -3155,16 +3155,16 @@
     <t xml:space="preserve">27.9547119140625</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4251976013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4799747467041</t>
+    <t xml:space="preserve">27.4251956939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4799766540527</t>
   </si>
   <si>
     <t xml:space="preserve">27.1147937774658</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7313537597656</t>
+    <t xml:space="preserve">26.7313499450684</t>
   </si>
   <si>
     <t xml:space="preserve">27.4069385528564</t>
@@ -3176,13 +3176,13 @@
     <t xml:space="preserve">26.6948337554932</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4434547424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3113918304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5542621612549</t>
+    <t xml:space="preserve">27.4434566497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3113899230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5542640686035</t>
   </si>
   <si>
     <t xml:space="preserve">24.7045879364014</t>
@@ -3194,61 +3194,61 @@
     <t xml:space="preserve">22.0022392272949</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7466125488281</t>
+    <t xml:space="preserve">21.7466106414795</t>
   </si>
   <si>
     <t xml:space="preserve">20.742359161377</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6047897338867</t>
+    <t xml:space="preserve">22.6047916412354</t>
   </si>
   <si>
     <t xml:space="preserve">21.8744258880615</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5134925842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1525630950928</t>
+    <t xml:space="preserve">22.5134944915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1525650024414</t>
   </si>
   <si>
     <t xml:space="preserve">23.2073402404785</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5402545928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6680698394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8689193725586</t>
+    <t xml:space="preserve">24.5402565002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6680717468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8689212799072</t>
   </si>
   <si>
     <t xml:space="preserve">24.4489612579346</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2341041564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5585174560547</t>
+    <t xml:space="preserve">25.2341022491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5585155487061</t>
   </si>
   <si>
     <t xml:space="preserve">24.0290012359619</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1385555267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0472602844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3984355926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4166927337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2115917205811</t>
+    <t xml:space="preserve">24.138557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0472621917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3984336853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4166946411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2115936279297</t>
   </si>
   <si>
     <t xml:space="preserve">24.083776473999</t>
@@ -3257,31 +3257,31 @@
     <t xml:space="preserve">23.8098926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3351535797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4221992492676</t>
+    <t xml:space="preserve">23.3351554870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4221973419189</t>
   </si>
   <si>
     <t xml:space="preserve">22.7326030731201</t>
   </si>
   <si>
-    <t xml:space="preserve">22.677827835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2761268615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9109420776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2213459014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8379077911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0935344696045</t>
+    <t xml:space="preserve">22.6778259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2761249542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9109439849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2213478088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8379058837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0935363769531</t>
   </si>
   <si>
     <t xml:space="preserve">22.8239002227783</t>
@@ -3290,28 +3290,28 @@
     <t xml:space="preserve">21.5457611083984</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0710258483887</t>
+    <t xml:space="preserve">21.07102394104</t>
   </si>
   <si>
     <t xml:space="preserve">21.9657211303711</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1988372802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2718734741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8884296417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6875839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0850296020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3729228973389</t>
+    <t xml:space="preserve">21.1988353729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2718753814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8884315490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6875820159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0850315093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3729248046875</t>
   </si>
   <si>
     <t xml:space="preserve">19.8659229278564</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">20.8519153594971</t>
   </si>
   <si>
-    <t xml:space="preserve">20.724100112915</t>
+    <t xml:space="preserve">20.7241020202637</t>
   </si>
   <si>
     <t xml:space="preserve">21.0162467956543</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">20.3954372406006</t>
   </si>
   <si>
-    <t xml:space="preserve">20.523250579834</t>
+    <t xml:space="preserve">20.5232486724854</t>
   </si>
   <si>
     <t xml:space="preserve">20.6693229675293</t>
@@ -3353,16 +3353,16 @@
     <t xml:space="preserve">22.1300525665283</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1933345794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6455612182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5177478790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7368545532227</t>
+    <t xml:space="preserve">24.1933326721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6455574035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5177459716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.736852645874</t>
   </si>
   <si>
     <t xml:space="preserve">23.0533809661865</t>
@@ -3371,10 +3371,10 @@
     <t xml:space="preserve">22.9240760803223</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7393531799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8711585998535</t>
+    <t xml:space="preserve">22.7393550872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8711566925049</t>
   </si>
   <si>
     <t xml:space="preserve">20.7443466186523</t>
@@ -3398,19 +3398,19 @@
     <t xml:space="preserve">21.3539333343506</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3169898986816</t>
+    <t xml:space="preserve">21.316987991333</t>
   </si>
   <si>
     <t xml:space="preserve">21.7603225708008</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6494903564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4278221130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.55712890625</t>
+    <t xml:space="preserve">21.6494884490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4278240203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5571269989014</t>
   </si>
   <si>
     <t xml:space="preserve">21.7972679138184</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">20.9475440979004</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0374069213867</t>
+    <t xml:space="preserve">22.0374088287354</t>
   </si>
   <si>
     <t xml:space="preserve">22.4992141723633</t>
@@ -3440,22 +3440,22 @@
     <t xml:space="preserve">21.6679611206055</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4647674560547</t>
+    <t xml:space="preserve">21.4647655487061</t>
   </si>
   <si>
     <t xml:space="preserve">20.8182392120361</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1532344818115</t>
+    <t xml:space="preserve">20.1532363891602</t>
   </si>
   <si>
     <t xml:space="preserve">20.2271251678467</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4487915039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3908767700195</t>
+    <t xml:space="preserve">20.4487934112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3908786773682</t>
   </si>
   <si>
     <t xml:space="preserve">21.0029602050781</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">21.2985153198242</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5017108917236</t>
+    <t xml:space="preserve">21.5017127990723</t>
   </si>
   <si>
     <t xml:space="preserve">21.7787952423096</t>
@@ -3509,16 +3509,16 @@
     <t xml:space="preserve">20.0054588317871</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1162929534912</t>
+    <t xml:space="preserve">20.1162910461426</t>
   </si>
   <si>
     <t xml:space="preserve">20.0978202819824</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9500427246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7468452453613</t>
+    <t xml:space="preserve">19.9500408172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.74684715271</t>
   </si>
   <si>
     <t xml:space="preserve">19.5436515808105</t>
@@ -3530,16 +3530,16 @@
     <t xml:space="preserve">18.472261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1926784515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5830955505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2413558959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0566329956055</t>
+    <t xml:space="preserve">19.1926803588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5830974578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2413578033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0566349029541</t>
   </si>
   <si>
     <t xml:space="preserve">17.7426052093506</t>
@@ -3548,7 +3548,7 @@
     <t xml:space="preserve">17.4562854766846</t>
   </si>
   <si>
-    <t xml:space="preserve">17.622537612915</t>
+    <t xml:space="preserve">17.6225357055664</t>
   </si>
   <si>
     <t xml:space="preserve">16.6989231109619</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">16.9852447509766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2807998657227</t>
+    <t xml:space="preserve">17.280797958374</t>
   </si>
   <si>
     <t xml:space="preserve">17.0037155151367</t>
@@ -3575,58 +3575,58 @@
     <t xml:space="preserve">17.6317729949951</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8164978027344</t>
+    <t xml:space="preserve">17.8164958953857</t>
   </si>
   <si>
     <t xml:space="preserve">17.5855941772461</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5024662017822</t>
+    <t xml:space="preserve">17.5024681091309</t>
   </si>
   <si>
     <t xml:space="preserve">17.0683689117432</t>
   </si>
   <si>
-    <t xml:space="preserve">17.234619140625</t>
+    <t xml:space="preserve">17.2346210479736</t>
   </si>
   <si>
     <t xml:space="preserve">17.2530918121338</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9390640258789</t>
+    <t xml:space="preserve">16.9390621185303</t>
   </si>
   <si>
     <t xml:space="preserve">16.8005218505859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8836460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4285774230957</t>
+    <t xml:space="preserve">16.8836479187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4285793304443</t>
   </si>
   <si>
     <t xml:space="preserve">17.7056617736816</t>
   </si>
   <si>
-    <t xml:space="preserve">17.844202041626</t>
+    <t xml:space="preserve">17.8442039489746</t>
   </si>
   <si>
     <t xml:space="preserve">17.7333698272705</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3429565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4697608947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5805988311768</t>
+    <t xml:space="preserve">18.3429546356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4697647094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5805969238281</t>
   </si>
   <si>
     <t xml:space="preserve">19.3589286804199</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0449028015137</t>
+    <t xml:space="preserve">19.044900894165</t>
   </si>
   <si>
     <t xml:space="preserve">18.7493438720703</t>
@@ -3641,13 +3641,13 @@
     <t xml:space="preserve">18.4907341003418</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0079555511475</t>
+    <t xml:space="preserve">19.0079574584961</t>
   </si>
   <si>
     <t xml:space="preserve">20.0239295959473</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8392086029053</t>
+    <t xml:space="preserve">19.8392066955566</t>
   </si>
   <si>
     <t xml:space="preserve">20.8736553192139</t>
@@ -3656,7 +3656,7 @@
     <t xml:space="preserve">21.9081001281738</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3329639434814</t>
+    <t xml:space="preserve">22.3329620361328</t>
   </si>
   <si>
     <t xml:space="preserve">20.9105987548828</t>
@@ -3665,40 +3665,40 @@
     <t xml:space="preserve">20.5226802825928</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3354606628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2430992126465</t>
+    <t xml:space="preserve">21.3354625701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2431011199951</t>
   </si>
   <si>
     <t xml:space="preserve">21.9265727996826</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7418537139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2800464630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.409351348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8526840209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1507377624512</t>
+    <t xml:space="preserve">21.7418518066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2800445556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4093494415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8526859283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1507396697998</t>
   </si>
   <si>
     <t xml:space="preserve">21.0583782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3933773040771</t>
+    <t xml:space="preserve">20.3933753967285</t>
   </si>
   <si>
     <t xml:space="preserve">20.2455978393555</t>
   </si>
   <si>
-    <t xml:space="preserve">19.931568145752</t>
+    <t xml:space="preserve">19.9315700531006</t>
   </si>
   <si>
     <t xml:space="preserve">19.9685134887695</t>
@@ -3734,13 +3734,13 @@
     <t xml:space="preserve">23.9031047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7922744750977</t>
+    <t xml:space="preserve">23.792272567749</t>
   </si>
   <si>
     <t xml:space="preserve">23.127269744873</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7553253173828</t>
+    <t xml:space="preserve">23.7553272247314</t>
   </si>
   <si>
     <t xml:space="preserve">23.8846340179443</t>
@@ -3749,7 +3749,7 @@
     <t xml:space="preserve">23.4782428741455</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1088008880615</t>
+    <t xml:space="preserve">23.1087989807129</t>
   </si>
   <si>
     <t xml:space="preserve">22.9979629516602</t>
@@ -3773,7 +3773,7 @@
     <t xml:space="preserve">23.5151882171631</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8686580657959</t>
+    <t xml:space="preserve">22.8686599731445</t>
   </si>
   <si>
     <t xml:space="preserve">23.4597702026367</t>
@@ -3782,7 +3782,7 @@
     <t xml:space="preserve">22.9056015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8132438659668</t>
+    <t xml:space="preserve">22.8132419586182</t>
   </si>
   <si>
     <t xml:space="preserve">22.6285190582275</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">22.2036571502686</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0004634857178</t>
+    <t xml:space="preserve">22.0004615783691</t>
   </si>
   <si>
     <t xml:space="preserve">22.0558776855469</t>
@@ -3806,31 +3806,31 @@
     <t xml:space="preserve">22.2590751647949</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8342132568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0928249359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2406024932861</t>
+    <t xml:space="preserve">21.8342113494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0928230285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2406005859375</t>
   </si>
   <si>
     <t xml:space="preserve">21.2615718841553</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3404560089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.656982421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1187896728516</t>
+    <t xml:space="preserve">19.3404579162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6569843292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1187915802002</t>
   </si>
   <si>
     <t xml:space="preserve">18.5646228790283</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6754550933838</t>
+    <t xml:space="preserve">18.6754570007324</t>
   </si>
   <si>
     <t xml:space="preserve">19.0264301300049</t>
@@ -3842,19 +3842,19 @@
     <t xml:space="preserve">18.509204864502</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8232326507568</t>
+    <t xml:space="preserve">18.8232345581055</t>
   </si>
   <si>
     <t xml:space="preserve">18.5461502075195</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7124004364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7308750152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6200389862061</t>
+    <t xml:space="preserve">18.7123985290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7308731079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6200370788574</t>
   </si>
   <si>
     <t xml:space="preserve">18.4445514678955</t>
@@ -3863,7 +3863,7 @@
     <t xml:space="preserve">18.3614273071289</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7980251312256</t>
+    <t xml:space="preserve">17.798023223877</t>
   </si>
   <si>
     <t xml:space="preserve">17.5486469268799</t>
@@ -3872,22 +3872,22 @@
     <t xml:space="preserve">17.1422576904297</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9483013153076</t>
+    <t xml:space="preserve">16.948299407959</t>
   </si>
   <si>
     <t xml:space="preserve">16.9205894470215</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8651733398438</t>
+    <t xml:space="preserve">16.8651752471924</t>
   </si>
   <si>
     <t xml:space="preserve">16.5696182250977</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8559398651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1145515441895</t>
+    <t xml:space="preserve">16.8559379577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1145496368408</t>
   </si>
   <si>
     <t xml:space="preserve">16.7451038360596</t>
@@ -3899,13 +3899,13 @@
     <t xml:space="preserve">16.8744106292725</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7912845611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8467025756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8097591400146</t>
+    <t xml:space="preserve">16.7912864685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.846700668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.809757232666</t>
   </si>
   <si>
     <t xml:space="preserve">16.5880889892578</t>
@@ -3917,43 +3917,43 @@
     <t xml:space="preserve">16.7635765075684</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7728118896484</t>
+    <t xml:space="preserve">16.7728137969971</t>
   </si>
   <si>
     <t xml:space="preserve">16.5234375</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7106580734253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0708656311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0893383026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0062141418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0523948669434</t>
+    <t xml:space="preserve">15.710657119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0708675384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0893402099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0062160491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0523929595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6896858215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4710884094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.632661819458</t>
   </si>
   <si>
     <t xml:space="preserve">16.6896877288818</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4710865020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.632661819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6896858215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6611766815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5946426391602</t>
+    <t xml:space="preserve">16.6611747741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5946445465088</t>
   </si>
   <si>
     <t xml:space="preserve">17.2124290466309</t>
@@ -3962,10 +3962,10 @@
     <t xml:space="preserve">17.5830993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">17.944263458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.820707321167</t>
+    <t xml:space="preserve">17.9442653656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8207092285156</t>
   </si>
   <si>
     <t xml:space="preserve">17.8302135467529</t>
@@ -3977,7 +3977,7 @@
     <t xml:space="preserve">16.9938259124756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5661296844482</t>
+    <t xml:space="preserve">16.5661315917969</t>
   </si>
   <si>
     <t xml:space="preserve">16.2809982299805</t>
@@ -3986,13 +3986,13 @@
     <t xml:space="preserve">16.204963684082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.00537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5871801376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7867727279663</t>
+    <t xml:space="preserve">16.0053730010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.58717918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.786771774292</t>
   </si>
   <si>
     <t xml:space="preserve">15.5681705474854</t>
@@ -4010,16 +4010,16 @@
     <t xml:space="preserve">15.3305606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6251974105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4541177749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8723115921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9958667755127</t>
+    <t xml:space="preserve">15.6251983642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4541187286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8723125457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9958686828613</t>
   </si>
   <si>
     <t xml:space="preserve">16.0623989105225</t>
@@ -4028,19 +4028,19 @@
     <t xml:space="preserve">15.7012319564819</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7772674560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8247900009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7487535476685</t>
+    <t xml:space="preserve">15.777268409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8247880935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7487545013428</t>
   </si>
   <si>
     <t xml:space="preserve">15.7392492294312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9388427734375</t>
+    <t xml:space="preserve">15.9388418197632</t>
   </si>
   <si>
     <t xml:space="preserve">16.1859569549561</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">16.1574420928955</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8913192749023</t>
+    <t xml:space="preserve">15.8913202285767</t>
   </si>
   <si>
     <t xml:space="preserve">16.9177932739258</t>
@@ -4061,13 +4061,13 @@
     <t xml:space="preserve">17.0223407745361</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1649055480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.060359954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6231575012207</t>
+    <t xml:space="preserve">17.1649074554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0603580474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6231555938721</t>
   </si>
   <si>
     <t xml:space="preserve">16.7277050018311</t>
@@ -4082,7 +4082,7 @@
     <t xml:space="preserve">16.3000068664551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4996013641357</t>
+    <t xml:space="preserve">16.4995994567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.509105682373</t>
@@ -4109,16 +4109,16 @@
     <t xml:space="preserve">17.4215240478516</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3074722290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2599487304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8628063201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8818140029907</t>
+    <t xml:space="preserve">17.3074703216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2599506378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8628072738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.881814956665</t>
   </si>
   <si>
     <t xml:space="preserve">16.4235649108887</t>
@@ -4130,16 +4130,16 @@
     <t xml:space="preserve">16.1479377746582</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9103288650513</t>
+    <t xml:space="preserve">15.910327911377</t>
   </si>
   <si>
     <t xml:space="preserve">16.2429828643799</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8533020019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8437967300415</t>
+    <t xml:space="preserve">15.8533029556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8437976837158</t>
   </si>
   <si>
     <t xml:space="preserve">14.7793073654175</t>
@@ -4154,10 +4154,10 @@
     <t xml:space="preserve">14.4466543197632</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7222814559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6917285919189</t>
+    <t xml:space="preserve">14.7222805023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6917276382446</t>
   </si>
   <si>
     <t xml:space="preserve">15.4731273651123</t>
@@ -4169,7 +4169,7 @@
     <t xml:space="preserve">15.4921350479126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0929527282715</t>
+    <t xml:space="preserve">15.0929517745972</t>
   </si>
   <si>
     <t xml:space="preserve">15.4446144104004</t>
@@ -4199,7 +4199,7 @@
     <t xml:space="preserve">14.4846715927124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9313774108887</t>
+    <t xml:space="preserve">14.931378364563</t>
   </si>
   <si>
     <t xml:space="preserve">14.9218730926514</t>
@@ -4214,37 +4214,37 @@
     <t xml:space="preserve">14.731785774231</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0074129104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7677631378174</t>
+    <t xml:space="preserve">15.0074119567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7677640914917</t>
   </si>
   <si>
     <t xml:space="preserve">16.1954612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5566253662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.128927230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0528945922852</t>
+    <t xml:space="preserve">16.5566272735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1289291381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0528926849365</t>
   </si>
   <si>
     <t xml:space="preserve">16.3570346832275</t>
   </si>
   <si>
-    <t xml:space="preserve">16.433069229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7467155456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3665390014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3950500488281</t>
+    <t xml:space="preserve">16.4330711364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7467136383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3665370941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3950519561768</t>
   </si>
   <si>
     <t xml:space="preserve">16.4805908203125</t>
@@ -4259,10 +4259,10 @@
     <t xml:space="preserve">16.3285217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6136531829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6991901397705</t>
+    <t xml:space="preserve">16.6136512756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6991920471191</t>
   </si>
   <si>
     <t xml:space="preserve">16.5756359100342</t>
@@ -4271,22 +4271,22 @@
     <t xml:space="preserve">18.5240325927734</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7046165466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6475887298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1988430023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4839744567871</t>
+    <t xml:space="preserve">18.7046146392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.647590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.198844909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4839763641357</t>
   </si>
   <si>
     <t xml:space="preserve">19.5029830932617</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4649639129639</t>
+    <t xml:space="preserve">19.4649658203125</t>
   </si>
   <si>
     <t xml:space="preserve">19.2938861846924</t>
@@ -4295,10 +4295,10 @@
     <t xml:space="preserve">19.1037998199463</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2748794555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0277652740479</t>
+    <t xml:space="preserve">19.2748775482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0277633666992</t>
   </si>
   <si>
     <t xml:space="preserve">18.0868320465088</t>
@@ -4325,16 +4325,16 @@
     <t xml:space="preserve">17.9062480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7541790008545</t>
+    <t xml:space="preserve">17.7541770935059</t>
   </si>
   <si>
     <t xml:space="preserve">18.1818752288818</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9157543182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2103862762451</t>
+    <t xml:space="preserve">17.9157524108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2103881835938</t>
   </si>
   <si>
     <t xml:space="preserve">18.343448638916</t>
@@ -4349,16 +4349,16 @@
     <t xml:space="preserve">18.6570930480957</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5810585021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4289875030518</t>
+    <t xml:space="preserve">18.5810565948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4289894104004</t>
   </si>
   <si>
     <t xml:space="preserve">18.1913795471191</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0488147735596</t>
+    <t xml:space="preserve">18.0488128662109</t>
   </si>
   <si>
     <t xml:space="preserve">18.020299911499</t>
@@ -4376,7 +4376,7 @@
     <t xml:space="preserve">17.9632740020752</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0678215026855</t>
+    <t xml:space="preserve">18.0678234100342</t>
   </si>
   <si>
     <t xml:space="preserve">18.1723709106445</t>
@@ -4406,13 +4406,13 @@
     <t xml:space="preserve">17.8112030029297</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5165672302246</t>
+    <t xml:space="preserve">17.5165691375732</t>
   </si>
   <si>
     <t xml:space="preserve">17.5450801849365</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3169765472412</t>
+    <t xml:space="preserve">17.3169746398926</t>
   </si>
   <si>
     <t xml:space="preserve">17.3264808654785</t>
@@ -4433,10 +4433,10 @@
     <t xml:space="preserve">17.5545845031738</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7636833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8872394561768</t>
+    <t xml:space="preserve">17.7636814117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8872375488281</t>
   </si>
   <si>
     <t xml:space="preserve">18.1533622741699</t>
@@ -4445,19 +4445,19 @@
     <t xml:space="preserve">18.1628665924072</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3549957275391</t>
+    <t xml:space="preserve">17.3549938201904</t>
   </si>
   <si>
     <t xml:space="preserve">17.4690456390381</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4405345916748</t>
+    <t xml:space="preserve">17.4405326843262</t>
   </si>
   <si>
     <t xml:space="preserve">17.1078796386719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0413494110107</t>
+    <t xml:space="preserve">17.0413513183594</t>
   </si>
   <si>
     <t xml:space="preserve">16.9368019104004</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">16.4615821838379</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3095111846924</t>
+    <t xml:space="preserve">16.309513092041</t>
   </si>
   <si>
     <t xml:space="preserve">17.0033321380615</t>
@@ -4493,7 +4493,7 @@
     <t xml:space="preserve">17.6211185455322</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0107975006104</t>
+    <t xml:space="preserve">18.0107955932617</t>
   </si>
   <si>
     <t xml:space="preserve">17.7826900482178</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">17.5355777740479</t>
   </si>
   <si>
-    <t xml:space="preserve">18.001293182373</t>
+    <t xml:space="preserve">18.0012912750244</t>
   </si>
   <si>
     <t xml:space="preserve">18.2674140930176</t>
@@ -70476,7 +70476,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6495138889</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>107697</v>
@@ -70497,6 +70497,32 @@
         <v>1768</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6514699074</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>140302</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>14.9499998092651</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>14.8199996948242</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>14.8800001144409</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>14.8500003814697</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1768</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TNXT.MI.xlsx
+++ b/data/TNXT.MI.xlsx
@@ -38,64 +38,64 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63493776321411</t>
+    <t xml:space="preserve">2.63493752479553</t>
   </si>
   <si>
     <t xml:space="preserve">TNXT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65150952339172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59350848197937</t>
+    <t xml:space="preserve">2.6515097618103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59350872039795</t>
   </si>
   <si>
     <t xml:space="preserve">2.53550672531128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52556347846985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48579096794128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52722024917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4874484539032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47087574005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46921873092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54047799110413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49739098548889</t>
+    <t xml:space="preserve">2.52556324005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48579072952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5272204875946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48744773864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47087597846985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46921896934509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54047846794128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49739074707031</t>
   </si>
   <si>
     <t xml:space="preserve">2.47916197776794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44436097145081</t>
+    <t xml:space="preserve">2.44436073303223</t>
   </si>
   <si>
     <t xml:space="preserve">2.39464473724365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34161448478699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36150074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55207896232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58522272109985</t>
+    <t xml:space="preserve">2.34161472320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36150097846985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55207872390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58522295951843</t>
   </si>
   <si>
     <t xml:space="preserve">2.61007976531982</t>
@@ -110,22 +110,22 @@
     <t xml:space="preserve">2.68962526321411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73436951637268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72608327865601</t>
+    <t xml:space="preserve">2.73436999320984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72608351707458</t>
   </si>
   <si>
     <t xml:space="preserve">2.77579951286316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58025097846985</t>
+    <t xml:space="preserve">2.58025121688843</t>
   </si>
   <si>
     <t xml:space="preserve">2.56202220916748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66808152198792</t>
+    <t xml:space="preserve">2.66808176040649</t>
   </si>
   <si>
     <t xml:space="preserve">2.62830901145935</t>
@@ -134,13 +134,13 @@
     <t xml:space="preserve">2.64322376251221</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60842275619507</t>
+    <t xml:space="preserve">2.60842251777649</t>
   </si>
   <si>
     <t xml:space="preserve">2.66642451286316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65316653251648</t>
+    <t xml:space="preserve">2.65316677093506</t>
   </si>
   <si>
     <t xml:space="preserve">2.62665176391602</t>
@@ -149,34 +149,34 @@
     <t xml:space="preserve">2.69293975830078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82551574707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81722927093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90008926391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85865926742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89843249320984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88351726531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87523126602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86694550514221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81888651847839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82054424285889</t>
+    <t xml:space="preserve">2.82551550865173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81722950935364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90008902549744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8586597442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89843225479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8835175037384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87523102760315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86694526672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81888675689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82054400444031</t>
   </si>
   <si>
     <t xml:space="preserve">2.85368776321411</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">2.8570020198822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90671801567078</t>
+    <t xml:space="preserve">2.90671825408936</t>
   </si>
   <si>
     <t xml:space="preserve">2.8288300037384</t>
@@ -206,37 +206,37 @@
     <t xml:space="preserve">2.95797753334045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88169693946838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89017295837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86474561691284</t>
+    <t xml:space="preserve">2.88169741630554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89017271995544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86474585533142</t>
   </si>
   <si>
     <t xml:space="preserve">2.94950199127197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92407512664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96645307540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11901307106018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94272112846375</t>
+    <t xml:space="preserve">2.92407536506653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96645259857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1190128326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94272136688232</t>
   </si>
   <si>
     <t xml:space="preserve">2.94780707359314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8833920955658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87322163581848</t>
+    <t xml:space="preserve">2.88339233398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8732213973999</t>
   </si>
   <si>
     <t xml:space="preserve">2.85966062545776</t>
@@ -248,28 +248,28 @@
     <t xml:space="preserve">3.07037353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06866335868835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06011056900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99340057373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98484826087952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93524289131165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98313736915588</t>
+    <t xml:space="preserve">3.0686628818512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06011080741882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99340081214905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98484802246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93524312973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9831371307373</t>
   </si>
   <si>
     <t xml:space="preserve">2.92497992515564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92326951026917</t>
+    <t xml:space="preserve">2.92326927185059</t>
   </si>
   <si>
     <t xml:space="preserve">2.96774291992188</t>
@@ -278,67 +278,67 @@
     <t xml:space="preserve">3.03616333007812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05840015411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05497908592224</t>
+    <t xml:space="preserve">3.05839991569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05497884750366</t>
   </si>
   <si>
     <t xml:space="preserve">3.08747887611389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13879442214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12853121757507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19010949134827</t>
+    <t xml:space="preserve">3.13879418373108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12853145599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19010972976685</t>
   </si>
   <si>
     <t xml:space="preserve">3.15589952468872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12339973449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12511014938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14734673500061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16445207595825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16616225242615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24142527580261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30129289627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38681888580322</t>
+    <t xml:space="preserve">3.12339997291565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12511038780212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14734697341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16445183753967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16616249084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24142503738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30129313468933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38681864738464</t>
   </si>
   <si>
     <t xml:space="preserve">3.48431801795959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52708148956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62629103660583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63655400276184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64510703086853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74602675437927</t>
+    <t xml:space="preserve">3.52708101272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62629079818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63655424118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64510655403137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74602770805359</t>
   </si>
   <si>
     <t xml:space="preserve">3.6776065826416</t>
@@ -347,28 +347,28 @@
     <t xml:space="preserve">3.71181654930115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63484406471252</t>
+    <t xml:space="preserve">3.63484358787537</t>
   </si>
   <si>
     <t xml:space="preserve">3.51681780815125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50484442710876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49458146095276</t>
+    <t xml:space="preserve">3.50484466552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4945809841156</t>
   </si>
   <si>
     <t xml:space="preserve">3.50655484199524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48089718818665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43129229545593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35602951049805</t>
+    <t xml:space="preserve">3.4808976650238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43129181861877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35602974891663</t>
   </si>
   <si>
     <t xml:space="preserve">3.60063338279724</t>
@@ -377,49 +377,49 @@
     <t xml:space="preserve">3.64681696891785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69471144676208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69984340667725</t>
+    <t xml:space="preserve">3.69471192359924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69984316825867</t>
   </si>
   <si>
     <t xml:space="preserve">3.67589569091797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66563320159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59721183776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63313293457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57497572898865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66050148010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68615865707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71523761749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73747420310974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71010661125183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69129037857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68958020210266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73234295845032</t>
+    <t xml:space="preserve">3.66563248634338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59721207618713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63313341140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57497525215149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66050171852112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68615889549255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7152373790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73747491836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71010589599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69129061698914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68957996368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73234272003174</t>
   </si>
   <si>
     <t xml:space="preserve">3.7203688621521</t>
@@ -428,25 +428,25 @@
     <t xml:space="preserve">3.76313209533691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77168416976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62115931510925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64168548583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70326399803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79734230041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75457882881165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90852618217468</t>
+    <t xml:space="preserve">3.77168440818787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62115955352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64168572425842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70326352119446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79734253883362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7545793056488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9085259437561</t>
   </si>
   <si>
     <t xml:space="preserve">3.76655268669128</t>
@@ -455,85 +455,85 @@
     <t xml:space="preserve">3.72892165184021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66734313964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50997614860535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49800276756287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48944973945618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47234439849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40392422676086</t>
+    <t xml:space="preserve">3.66734337806702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50997567176819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49800252914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48944997787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47234463691711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40392398834229</t>
   </si>
   <si>
     <t xml:space="preserve">3.43642401695251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53221249580383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5185284614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46037077903748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50142312049866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53563380241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55615949630737</t>
+    <t xml:space="preserve">3.53221273422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51852822303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46037101745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50142335891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53563332557678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55616021156311</t>
   </si>
   <si>
     <t xml:space="preserve">3.64339590072632</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72550058364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84865832328796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82984232902527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83155250549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87089419364929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8452365398407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87431597709656</t>
+    <t xml:space="preserve">3.7255003452301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84865760803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82984256744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83155298233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87089443206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84523701667786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87431526184082</t>
   </si>
   <si>
     <t xml:space="preserve">3.86405277252197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8572108745575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82471060752869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90681505203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00260448455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17536592483521</t>
+    <t xml:space="preserve">3.85721039772034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82471036911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90681529045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00260353088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17536640167236</t>
   </si>
   <si>
     <t xml:space="preserve">4.11378765106201</t>
@@ -545,43 +545,43 @@
     <t xml:space="preserve">4.05220890045166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08128833770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0060248374939</t>
+    <t xml:space="preserve">4.08128786087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00602531433105</t>
   </si>
   <si>
     <t xml:space="preserve">4.09839296340942</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01970863342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01115703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99576187133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0351037979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06247186660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13773488998413</t>
+    <t xml:space="preserve">4.01970911026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01115655899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99576139450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03510427474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06247282028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13773441314697</t>
   </si>
   <si>
     <t xml:space="preserve">4.12233972549438</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14799737930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18904972076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2591814994812</t>
+    <t xml:space="preserve">4.14799833297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18905067443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25918197631836</t>
   </si>
   <si>
     <t xml:space="preserve">4.22839212417603</t>
@@ -593,22 +593,22 @@
     <t xml:space="preserve">4.02142000198364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99405217170715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01799917221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02655124664307</t>
+    <t xml:space="preserve">3.99405121803284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01799821853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02655172348022</t>
   </si>
   <si>
     <t xml:space="preserve">4.07615661621094</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12747240066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11891984939575</t>
+    <t xml:space="preserve">4.12747144699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11891889572144</t>
   </si>
   <si>
     <t xml:space="preserve">4.10523509979248</t>
@@ -617,13 +617,13 @@
     <t xml:space="preserve">4.09668254852295</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10181427001953</t>
+    <t xml:space="preserve">4.10181331634521</t>
   </si>
   <si>
     <t xml:space="preserve">4.07102489471436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09497165679932</t>
+    <t xml:space="preserve">4.09497213363647</t>
   </si>
   <si>
     <t xml:space="preserve">4.13089275360107</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">4.52431106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54996871948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53713941574097</t>
+    <t xml:space="preserve">4.54996967315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53713989257812</t>
   </si>
   <si>
     <t xml:space="preserve">4.46444320678711</t>
@@ -647,37 +647,37 @@
     <t xml:space="preserve">4.5029296875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56707429885864</t>
+    <t xml:space="preserve">4.56707382202148</t>
   </si>
   <si>
     <t xml:space="preserve">4.6226658821106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63549423217773</t>
+    <t xml:space="preserve">4.63549470901489</t>
   </si>
   <si>
     <t xml:space="preserve">4.58417892456055</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60128402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57562589645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61838865280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5328631401062</t>
+    <t xml:space="preserve">4.60128498077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57562637329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61838960647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53286361694336</t>
   </si>
   <si>
     <t xml:space="preserve">4.55852079391479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48154783248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5157585144043</t>
+    <t xml:space="preserve">4.48154830932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51575803756714</t>
   </si>
   <si>
     <t xml:space="preserve">4.4901008605957</t>
@@ -686,16 +686,16 @@
     <t xml:space="preserve">4.51148223876953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63121747970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78516435623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75950717926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78944158554077</t>
+    <t xml:space="preserve">4.63121843338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78516483306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7595067024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78944063186646</t>
   </si>
   <si>
     <t xml:space="preserve">4.7338490486145</t>
@@ -704,25 +704,25 @@
     <t xml:space="preserve">4.77233600616455</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76378393173218</t>
+    <t xml:space="preserve">4.76378345489502</t>
   </si>
   <si>
     <t xml:space="preserve">4.65687608718872</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69536209106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82792711257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90062522888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91772890090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94338655471802</t>
+    <t xml:space="preserve">4.69536256790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8279275894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90062379837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91772985458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94338798522949</t>
   </si>
   <si>
     <t xml:space="preserve">4.98614978790283</t>
@@ -731,40 +731,40 @@
     <t xml:space="preserve">5.04174184799194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02036046981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0716757774353</t>
+    <t xml:space="preserve">5.02035999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07167530059814</t>
   </si>
   <si>
     <t xml:space="preserve">5.08022832870483</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99470281600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09305667877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06050634384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91728496551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94766569137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92596578598022</t>
+    <t xml:space="preserve">4.99470376968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09305715560913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06050682067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91728448867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94766521453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92596483230591</t>
   </si>
   <si>
     <t xml:space="preserve">4.9042649269104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82180404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7350025177002</t>
+    <t xml:space="preserve">4.8218035697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73500299453735</t>
   </si>
   <si>
     <t xml:space="preserve">4.72198247909546</t>
@@ -779,10 +779,10 @@
     <t xml:space="preserve">4.73066234588623</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66556167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65254163742065</t>
+    <t xml:space="preserve">4.66556119918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6525411605835</t>
   </si>
   <si>
     <t xml:space="preserve">4.60914087295532</t>
@@ -791,16 +791,16 @@
     <t xml:space="preserve">4.65688133239746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54837989807129</t>
+    <t xml:space="preserve">4.54838037490845</t>
   </si>
   <si>
     <t xml:space="preserve">4.53536081314087</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47025966644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59612083435059</t>
+    <t xml:space="preserve">4.47025871276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59612035751343</t>
   </si>
   <si>
     <t xml:space="preserve">4.47459936141968</t>
@@ -812,16 +812,16 @@
     <t xml:space="preserve">4.46157836914062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41383838653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3877968788147</t>
+    <t xml:space="preserve">4.41383790969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38779783248901</t>
   </si>
   <si>
     <t xml:space="preserve">4.39213800430298</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40949869155884</t>
+    <t xml:space="preserve">4.40949773788452</t>
   </si>
   <si>
     <t xml:space="preserve">4.55706024169922</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">4.57008028030396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53970003128052</t>
+    <t xml:space="preserve">4.53970050811768</t>
   </si>
   <si>
     <t xml:space="preserve">4.47893905639648</t>
@@ -842,37 +842,37 @@
     <t xml:space="preserve">4.43553876876831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42251825332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4311990737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45289897918701</t>
+    <t xml:space="preserve">4.4225172996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43119859695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45289850234985</t>
   </si>
   <si>
     <t xml:space="preserve">4.51365947723389</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6872615814209</t>
+    <t xml:space="preserve">4.68726205825806</t>
   </si>
   <si>
     <t xml:space="preserve">4.60046052932739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63952112197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56139993667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58744049072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61782073974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64820194244385</t>
+    <t xml:space="preserve">4.6395206451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56140041351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5874400138855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61782169342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64820146560669</t>
   </si>
   <si>
     <t xml:space="preserve">4.60480070114136</t>
@@ -881,28 +881,28 @@
     <t xml:space="preserve">4.58310031890869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49629926681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50498008728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42685890197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49195909500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51800060272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80878400802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77840280532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84784364700317</t>
+    <t xml:space="preserve">4.49629974365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50497961044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42685747146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49195957183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51799964904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80878353118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77840328216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84784460067749</t>
   </si>
   <si>
     <t xml:space="preserve">4.8348240852356</t>
@@ -917,76 +917,76 @@
     <t xml:space="preserve">4.71330213546753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7046217918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72632217407227</t>
+    <t xml:space="preserve">4.70462226867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72632265090942</t>
   </si>
   <si>
     <t xml:space="preserve">4.69594192504883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76972341537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84350395202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87822437286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87388467788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97370624542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97804641723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00842571258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07786655426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04314613342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14730834960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86086463928223</t>
+    <t xml:space="preserve">4.7697229385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84350442886353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87822389602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8738842010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97370529174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97804594039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00842618942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07786750793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04314661026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14730739593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86086416244507</t>
   </si>
   <si>
     <t xml:space="preserve">4.869544506073</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96502590179443</t>
+    <t xml:space="preserve">4.96502494812012</t>
   </si>
   <si>
     <t xml:space="preserve">4.90860509872437</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99974536895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99106597900391</t>
+    <t xml:space="preserve">4.99974632263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99106645584106</t>
   </si>
   <si>
     <t xml:space="preserve">5.15598821640015</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12994766235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29486989974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41639137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48583221435547</t>
+    <t xml:space="preserve">5.12994718551636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29487037658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41639184951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48583269119263</t>
   </si>
   <si>
     <t xml:space="preserve">5.43375205993652</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">5.48149251937866</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42073202133179</t>
+    <t xml:space="preserve">5.42073154449463</t>
   </si>
   <si>
     <t xml:space="preserve">5.39469194412231</t>
@@ -1004,16 +1004,16 @@
     <t xml:space="preserve">5.35563087463379</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33393096923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37299156188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33827018737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20806884765625</t>
+    <t xml:space="preserve">5.33393049240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37299060821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33827114105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20806837081909</t>
   </si>
   <si>
     <t xml:space="preserve">5.16466808319092</t>
@@ -1028,52 +1028,52 @@
     <t xml:space="preserve">5.26014995574951</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18636846542358</t>
+    <t xml:space="preserve">5.18636798858643</t>
   </si>
   <si>
     <t xml:space="preserve">5.20372867584229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19504880905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16900777816772</t>
+    <t xml:space="preserve">5.19504833221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16900825500488</t>
   </si>
   <si>
     <t xml:space="preserve">5.18202829360962</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19938850402832</t>
+    <t xml:space="preserve">5.19938802719116</t>
   </si>
   <si>
     <t xml:space="preserve">5.22542858123779</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42507219314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61603403091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7288761138916</t>
+    <t xml:space="preserve">5.42507171630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61603355407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72887516021729</t>
   </si>
   <si>
     <t xml:space="preserve">5.7115159034729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78963613510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82435750961304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87643718719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88511800765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93719816207886</t>
+    <t xml:space="preserve">5.78963661193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82435703277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87643766403198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88511848449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93719863891602</t>
   </si>
   <si>
     <t xml:space="preserve">5.85907697677612</t>
@@ -1082,10 +1082,10 @@
     <t xml:space="preserve">5.80699682235718</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92851781845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97191905975342</t>
+    <t xml:space="preserve">5.92851829528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9719181060791</t>
   </si>
   <si>
     <t xml:space="preserve">5.95455884933472</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">6.03268003463745</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17156171798706</t>
+    <t xml:space="preserve">6.1715612411499</t>
   </si>
   <si>
     <t xml:space="preserve">6.2844033241272</t>
@@ -1109,61 +1109,61 @@
     <t xml:space="preserve">6.21496200561523</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14552116394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40592527389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07607984542847</t>
+    <t xml:space="preserve">6.14552068710327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40592479705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07608079910278</t>
   </si>
   <si>
     <t xml:space="preserve">5.98927927017212</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04135990142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22364282608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13684129714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19760227203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1542010307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05004024505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89379787445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9024772644043</t>
+    <t xml:space="preserve">6.04136037826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22364187240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1368408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19760131835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15420150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05003976821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89379835128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90247821807861</t>
   </si>
   <si>
     <t xml:space="preserve">5.70283555984497</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50319242477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5813136100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72019624710083</t>
+    <t xml:space="preserve">5.50319290161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58131408691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72019577026367</t>
   </si>
   <si>
     <t xml:space="preserve">5.763596534729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.919837474823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99795961380005</t>
+    <t xml:space="preserve">5.91983795166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99795866012573</t>
   </si>
   <si>
     <t xml:space="preserve">5.83303689956665</t>
@@ -1175,43 +1175,43 @@
     <t xml:space="preserve">5.6594352722168</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51187229156494</t>
+    <t xml:space="preserve">5.5118727684021</t>
   </si>
   <si>
     <t xml:space="preserve">5.5465931892395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58999395370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52055263519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38167142868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44243192672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46847200393677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67679500579834</t>
+    <t xml:space="preserve">5.58999443054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52055311203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38167095184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44243144989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46847248077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67679452896118</t>
   </si>
   <si>
     <t xml:space="preserve">5.64207458496094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55527400970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53791332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57263422012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52923250198364</t>
+    <t xml:space="preserve">5.55527353286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53791379928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57263374328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5292329788208</t>
   </si>
   <si>
     <t xml:space="preserve">5.39903116226196</t>
@@ -1220,58 +1220,58 @@
     <t xml:space="preserve">5.39035177230835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45111179351807</t>
+    <t xml:space="preserve">5.45111131668091</t>
   </si>
   <si>
     <t xml:space="preserve">6.09344053268433</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81567621231079</t>
+    <t xml:space="preserve">5.81567668914795</t>
   </si>
   <si>
     <t xml:space="preserve">5.77227640151978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73755598068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40771198272705</t>
+    <t xml:space="preserve">5.73755550384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40771150588989</t>
   </si>
   <si>
     <t xml:space="preserve">5.24278926849365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06918716430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98238611221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07618808746338</t>
+    <t xml:space="preserve">5.06918811798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98238515853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07618761062622</t>
   </si>
   <si>
     <t xml:space="preserve">5.15619802474976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08507823944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24509763717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11174774169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13841772079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20953798294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1473069190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.067298412323</t>
+    <t xml:space="preserve">5.08507776260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24509811401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11174821853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13841819763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20953845977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14730787277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06729793548584</t>
   </si>
   <si>
     <t xml:space="preserve">5.0584077835083</t>
@@ -1280,40 +1280,40 @@
     <t xml:space="preserve">5.04062795639038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04951810836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94283819198608</t>
+    <t xml:space="preserve">5.04951763153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94283771514893</t>
   </si>
   <si>
     <t xml:space="preserve">4.77392816543579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90727806091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76503801345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92505836486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88949775695801</t>
+    <t xml:space="preserve">4.90727758407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76503753662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92505788803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88949823379517</t>
   </si>
   <si>
     <t xml:space="preserve">5.02284812927246</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97839832305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91616821289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95172834396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9339485168457</t>
+    <t xml:space="preserve">4.97839736938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91616773605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95172786712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93394756317139</t>
   </si>
   <si>
     <t xml:space="preserve">4.89838838577271</t>
@@ -1322,34 +1322,34 @@
     <t xml:space="preserve">4.80948781967163</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78281784057617</t>
+    <t xml:space="preserve">4.78281831741333</t>
   </si>
   <si>
     <t xml:space="preserve">4.75614786148071</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98728799819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10285806655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.960618019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20064735412598</t>
+    <t xml:space="preserve">4.9872875213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10285758972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96061849594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20064783096313</t>
   </si>
   <si>
     <t xml:space="preserve">5.21842765808105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27176809310913</t>
+    <t xml:space="preserve">5.27176713943481</t>
   </si>
   <si>
     <t xml:space="preserve">5.33399772644043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23620748519897</t>
+    <t xml:space="preserve">5.23620796203613</t>
   </si>
   <si>
     <t xml:space="preserve">5.18286752700806</t>
@@ -1364,31 +1364,31 @@
     <t xml:space="preserve">5.00506782531738</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37844800949097</t>
+    <t xml:space="preserve">5.37844848632812</t>
   </si>
   <si>
     <t xml:space="preserve">5.47623777389526</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56513786315918</t>
+    <t xml:space="preserve">5.56513833999634</t>
   </si>
   <si>
     <t xml:space="preserve">5.6807074546814</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65403747558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63625717163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5562481880188</t>
+    <t xml:space="preserve">5.6540379524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63625764846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55624771118164</t>
   </si>
   <si>
     <t xml:space="preserve">5.68959808349609</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96518802642822</t>
+    <t xml:space="preserve">5.96518754959106</t>
   </si>
   <si>
     <t xml:space="preserve">5.89406776428223</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">5.77849769592285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84072780609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76071739196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92073774337769</t>
+    <t xml:space="preserve">5.84072732925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76071786880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92073726654053</t>
   </si>
   <si>
     <t xml:space="preserve">5.83183765411377</t>
@@ -1418,22 +1418,22 @@
     <t xml:space="preserve">5.43178796768188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36955785751343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6095871925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86739778518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78738737106323</t>
+    <t xml:space="preserve">5.36955738067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60958814620972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86739730834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78738784790039</t>
   </si>
   <si>
     <t xml:space="preserve">5.5206880569458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49401760101318</t>
+    <t xml:space="preserve">5.49401712417603</t>
   </si>
   <si>
     <t xml:space="preserve">5.57402753829956</t>
@@ -1442,28 +1442,28 @@
     <t xml:space="preserve">5.59180736541748</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6451473236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71626758575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73404788970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81405782699585</t>
+    <t xml:space="preserve">5.64514684677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71626710891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73404741287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81405735015869</t>
   </si>
   <si>
     <t xml:space="preserve">5.67181777954102</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51179790496826</t>
+    <t xml:space="preserve">5.5117974281311</t>
   </si>
   <si>
     <t xml:space="preserve">5.85850811004639</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66292715072632</t>
+    <t xml:space="preserve">5.66292762756348</t>
   </si>
   <si>
     <t xml:space="preserve">5.53846836090088</t>
@@ -1475,40 +1475,40 @@
     <t xml:space="preserve">5.79627799987793</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80516767501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61847734451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46734762191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60069751739502</t>
+    <t xml:space="preserve">5.80516815185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61847829818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46734857559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60069799423218</t>
   </si>
   <si>
     <t xml:space="preserve">5.45845746994019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50290822982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34288835525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62736701965332</t>
+    <t xml:space="preserve">5.50290775299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34288787841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62736749649048</t>
   </si>
   <si>
     <t xml:space="preserve">5.52957773208618</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42289781570435</t>
+    <t xml:space="preserve">5.42289733886719</t>
   </si>
   <si>
     <t xml:space="preserve">5.72515773773193</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70737838745117</t>
+    <t xml:space="preserve">5.70737791061401</t>
   </si>
   <si>
     <t xml:space="preserve">5.69848728179932</t>
@@ -1526,22 +1526,22 @@
     <t xml:space="preserve">5.93851757049561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99185705184937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24077749252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40968704223633</t>
+    <t xml:space="preserve">5.99185657501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24077701568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40968656539917</t>
   </si>
   <si>
     <t xml:space="preserve">6.48080682754517</t>
   </si>
   <si>
-    <t xml:space="preserve">6.623046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84529733657837</t>
+    <t xml:space="preserve">6.62304735183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84529685974121</t>
   </si>
   <si>
     <t xml:space="preserve">6.99642705917358</t>
@@ -1550,10 +1550,10 @@
     <t xml:space="preserve">7.0142068862915</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90752696990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91641664505005</t>
+    <t xml:space="preserve">6.90752744674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91641759872437</t>
   </si>
   <si>
     <t xml:space="preserve">6.97864723205566</t>
@@ -1562,64 +1562,64 @@
     <t xml:space="preserve">7.00531721115112</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02309703826904</t>
+    <t xml:space="preserve">7.0230975151062</t>
   </si>
   <si>
     <t xml:space="preserve">7.24534702301025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27201795578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33424711227417</t>
+    <t xml:space="preserve">7.27201700210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33424758911133</t>
   </si>
   <si>
     <t xml:space="preserve">7.47648763656616</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76985645294189</t>
+    <t xml:space="preserve">7.76985788345337</t>
   </si>
   <si>
     <t xml:space="preserve">7.7342963218689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7254056930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79652738571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80541610717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22324657440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21435737609863</t>
+    <t xml:space="preserve">7.72540616989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79652786254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80541706085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22324562072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21435642242432</t>
   </si>
   <si>
     <t xml:space="preserve">8.15212631225586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12545776367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00099754333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17879676818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34770584106445</t>
+    <t xml:space="preserve">8.12545680999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00099658966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17879581451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34770679473877</t>
   </si>
   <si>
     <t xml:space="preserve">8.42771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48105525970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46327686309814</t>
+    <t xml:space="preserve">8.48105621337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46327781677246</t>
   </si>
   <si>
     <t xml:space="preserve">8.5255069732666</t>
@@ -1631,31 +1631,31 @@
     <t xml:space="preserve">8.66774654388428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80109596252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8899974822998</t>
+    <t xml:space="preserve">8.80109691619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88999652862549</t>
   </si>
   <si>
     <t xml:space="preserve">9.19225692749023</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37005519866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47673511505127</t>
+    <t xml:space="preserve">9.37005615234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47673606872559</t>
   </si>
   <si>
     <t xml:space="preserve">9.49451637268066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31671619415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15669727325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35227489471436</t>
+    <t xml:space="preserve">9.31671524047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15669631958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35227680206299</t>
   </si>
   <si>
     <t xml:space="preserve">9.40561580657959</t>
@@ -1664,34 +1664,34 @@
     <t xml:space="preserve">9.69009590148926</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86789703369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83233642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77899551391602</t>
+    <t xml:space="preserve">9.86789512634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83233547210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77899646759033</t>
   </si>
   <si>
     <t xml:space="preserve">9.44117641448975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.210036277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58341598510742</t>
+    <t xml:space="preserve">9.21003532409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58341693878174</t>
   </si>
   <si>
     <t xml:space="preserve">9.51229572296143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6723165512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85011672973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0990362167358</t>
+    <t xml:space="preserve">9.67231559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85011577606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0990352630615</t>
   </si>
   <si>
     <t xml:space="preserve">10.0279159545898</t>
@@ -1706,10 +1706,10 @@
     <t xml:space="preserve">9.76121616363525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88567638397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2234954833984</t>
+    <t xml:space="preserve">9.88567543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2234964370728</t>
   </si>
   <si>
     <t xml:space="preserve">10.4368553161621</t>
@@ -1718,19 +1718,19 @@
     <t xml:space="preserve">10.6679954528809</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4147567749023</t>
+    <t xml:space="preserve">11.414755821228</t>
   </si>
   <si>
     <t xml:space="preserve">11.3614149093628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3080749511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4325351715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6814556121826</t>
+    <t xml:space="preserve">11.3080759048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4325342178345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6814546585083</t>
   </si>
   <si>
     <t xml:space="preserve">11.8948154449463</t>
@@ -1739,16 +1739,16 @@
     <t xml:space="preserve">11.9659357070923</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1437339782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6281156539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4001131057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6715450286865</t>
+    <t xml:space="preserve">12.1437349319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6281147003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4001140594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6715440750122</t>
   </si>
   <si>
     <t xml:space="preserve">11.6534490585327</t>
@@ -1760,22 +1760,22 @@
     <t xml:space="preserve">12.123929977417</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7982120513916</t>
+    <t xml:space="preserve">11.7982130050659</t>
   </si>
   <si>
     <t xml:space="preserve">12.1782159805298</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3229789733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9925107955933</t>
+    <t xml:space="preserve">12.3229780197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9925098419189</t>
   </si>
   <si>
     <t xml:space="preserve">12.8296518325806</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7391729354858</t>
+    <t xml:space="preserve">12.7391748428345</t>
   </si>
   <si>
     <t xml:space="preserve">12.7753648757935</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">12.3953609466553</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2867879867554</t>
+    <t xml:space="preserve">12.2867889404297</t>
   </si>
   <si>
     <t xml:space="preserve">12.6306009292603</t>
@@ -1796,19 +1796,19 @@
     <t xml:space="preserve">12.2144060134888</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1058359146118</t>
+    <t xml:space="preserve">12.1058349609375</t>
   </si>
   <si>
     <t xml:space="preserve">11.8705930709839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9067840576172</t>
+    <t xml:space="preserve">11.9067850112915</t>
   </si>
   <si>
     <t xml:space="preserve">11.4724941253662</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4182081222534</t>
+    <t xml:space="preserve">11.4182100296021</t>
   </si>
   <si>
     <t xml:space="preserve">11.5810670852661</t>
@@ -1820,25 +1820,25 @@
     <t xml:space="preserve">12.0877389907837</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8344039916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.888689994812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4363031387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3277311325073</t>
+    <t xml:space="preserve">11.8344030380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8886890411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4363050460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3277320861816</t>
   </si>
   <si>
     <t xml:space="preserve">11.2734460830688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1829681396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1648731231689</t>
+    <t xml:space="preserve">11.1829671859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1648721694946</t>
   </si>
   <si>
     <t xml:space="preserve">10.8391551971436</t>
@@ -1853,10 +1853,10 @@
     <t xml:space="preserve">10.5134372711182</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9115362167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2915391921997</t>
+    <t xml:space="preserve">10.9115371704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.291540145874</t>
   </si>
   <si>
     <t xml:space="preserve">11.1467771530151</t>
@@ -1865,49 +1865,49 @@
     <t xml:space="preserve">10.766773223877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1105871200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1286821365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6220102310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0020141601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6039142608643</t>
+    <t xml:space="preserve">11.1105861663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.12868309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6220092773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0020132064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6039152145386</t>
   </si>
   <si>
     <t xml:space="preserve">10.4953422546387</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2781972885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3143882751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.898193359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93438339233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80771636962891</t>
+    <t xml:space="preserve">10.2781963348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3143873214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89819240570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9343843460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80771732330322</t>
   </si>
   <si>
     <t xml:space="preserve">9.68104839324951</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95247936248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2420063018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4772453308105</t>
+    <t xml:space="preserve">9.95248031616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2420072555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4772472381592</t>
   </si>
   <si>
     <t xml:space="preserve">10.3867692947388</t>
@@ -1919,28 +1919,28 @@
     <t xml:space="preserve">9.55438041687012</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1153392791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3505792617798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4048652648926</t>
+    <t xml:space="preserve">10.1153402328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3505783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4048662185669</t>
   </si>
   <si>
     <t xml:space="preserve">10.7486782073975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0201091766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8572492599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8753461837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5858182907104</t>
+    <t xml:space="preserve">11.0201082229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.857250213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8753452301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5858192443848</t>
   </si>
   <si>
     <t xml:space="preserve">10.8029642105103</t>
@@ -1949,16 +1949,16 @@
     <t xml:space="preserve">10.7124872207642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7848701477051</t>
+    <t xml:space="preserve">10.7848691940308</t>
   </si>
   <si>
     <t xml:space="preserve">11.2372550964355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3096361160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4543981552124</t>
+    <t xml:space="preserve">11.3096351623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4543991088867</t>
   </si>
   <si>
     <t xml:space="preserve">11.725830078125</t>
@@ -1970,22 +1970,22 @@
     <t xml:space="preserve">12.160120010376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0515489578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0334529876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9429759979248</t>
+    <t xml:space="preserve">12.0515470504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0334520339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9429750442505</t>
   </si>
   <si>
     <t xml:space="preserve">11.7620210647583</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9477281570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9658231735229</t>
+    <t xml:space="preserve">10.9477291107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9658241271973</t>
   </si>
   <si>
     <t xml:space="preserve">10.1877202987671</t>
@@ -1994,46 +1994,46 @@
     <t xml:space="preserve">9.98867034912109</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0429573059082</t>
+    <t xml:space="preserve">10.0429563522339</t>
   </si>
   <si>
     <t xml:space="preserve">9.91628932952881</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1696243286133</t>
+    <t xml:space="preserve">10.169623374939</t>
   </si>
   <si>
     <t xml:space="preserve">10.531533241272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4229593276978</t>
+    <t xml:space="preserve">10.4229602813721</t>
   </si>
   <si>
     <t xml:space="preserve">10.13343334198</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3324842453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2239122390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.097243309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0610523223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0791473388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1515293121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0563011169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8934412002563</t>
+    <t xml:space="preserve">10.332483291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2239112854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0972442626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0610513687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0791482925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1515283584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.056300163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.893440246582</t>
   </si>
   <si>
     <t xml:space="preserve">10.5496282577515</t>
@@ -2051,7 +2051,7 @@
     <t xml:space="preserve">9.699143409729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51818943023682</t>
+    <t xml:space="preserve">9.51819038391113</t>
   </si>
   <si>
     <t xml:space="preserve">9.7172384262085</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">9.42771244049072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5905704498291</t>
+    <t xml:space="preserve">9.59057140350342</t>
   </si>
   <si>
     <t xml:space="preserve">11.3639221191406</t>
@@ -2081,16 +2081,16 @@
     <t xml:space="preserve">11.5629720687866</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6172590255737</t>
+    <t xml:space="preserve">11.6172580718994</t>
   </si>
   <si>
     <t xml:space="preserve">11.0924921035767</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6943912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62676239013672</t>
+    <t xml:space="preserve">10.6943922042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62676334381104</t>
   </si>
   <si>
     <t xml:space="preserve">8.80342102050781</t>
@@ -2099,7 +2099,7 @@
     <t xml:space="preserve">8.68580055236816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43246459960938</t>
+    <t xml:space="preserve">8.43246364593506</t>
   </si>
   <si>
     <t xml:space="preserve">7.0481653213501</t>
@@ -2114,13 +2114,13 @@
     <t xml:space="preserve">7.18388080596924</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58673143386841</t>
+    <t xml:space="preserve">6.58673191070557</t>
   </si>
   <si>
     <t xml:space="preserve">6.65006542205811</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96673583984375</t>
+    <t xml:space="preserve">6.96673536300659</t>
   </si>
   <si>
     <t xml:space="preserve">6.9757833480835</t>
@@ -2129,16 +2129,16 @@
     <t xml:space="preserve">7.16578531265259</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05721282958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28340578079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60912275314331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76293325424194</t>
+    <t xml:space="preserve">7.057213306427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28340625762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60912370681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76293420791626</t>
   </si>
   <si>
     <t xml:space="preserve">8.34198760986328</t>
@@ -2147,7 +2147,7 @@
     <t xml:space="preserve">8.04341316223145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61341857910156</t>
+    <t xml:space="preserve">8.61341953277588</t>
   </si>
   <si>
     <t xml:space="preserve">8.41436958312988</t>
@@ -2156,7 +2156,7 @@
     <t xml:space="preserve">8.25151062011719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93008804321289</t>
+    <t xml:space="preserve">8.93008899688721</t>
   </si>
   <si>
     <t xml:space="preserve">9.35533142089844</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">9.86200141906738</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2191600799561</t>
+    <t xml:space="preserve">11.2191581726074</t>
   </si>
   <si>
     <t xml:space="preserve">10.9839191436768</t>
@@ -2183,13 +2183,13 @@
     <t xml:space="preserve">10.6582012176514</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9705753326416</t>
+    <t xml:space="preserve">9.97057628631592</t>
   </si>
   <si>
     <t xml:space="preserve">10.2058153152466</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84390735626221</t>
+    <t xml:space="preserve">9.84390640258789</t>
   </si>
   <si>
     <t xml:space="preserve">10.4591512680054</t>
@@ -2198,13 +2198,13 @@
     <t xml:space="preserve">10.9296321868896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7305822372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8210592269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0696439743042</t>
+    <t xml:space="preserve">10.7305812835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8210601806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0696430206299</t>
   </si>
   <si>
     <t xml:space="preserve">12.558219909668</t>
@@ -2219,49 +2219,49 @@
     <t xml:space="preserve">12.757269859314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7934608459473</t>
+    <t xml:space="preserve">12.7934598922729</t>
   </si>
   <si>
     <t xml:space="preserve">12.4315509796143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.594409942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6486959457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7210788726807</t>
+    <t xml:space="preserve">12.5944108963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6486968994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7210779190063</t>
   </si>
   <si>
     <t xml:space="preserve">12.8658418655396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1553678512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0286998748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1191778182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9382247924805</t>
+    <t xml:space="preserve">13.1553688049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0287008285522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1191787719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9382238388062</t>
   </si>
   <si>
     <t xml:space="preserve">13.082986831665</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3725137710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3544187545776</t>
+    <t xml:space="preserve">13.3725128173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3544178009033</t>
   </si>
   <si>
     <t xml:space="preserve">15.4534845352173</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2496852874756</t>
+    <t xml:space="preserve">16.249683380127</t>
   </si>
   <si>
     <t xml:space="preserve">16.2858753204346</t>
@@ -2273,28 +2273,28 @@
     <t xml:space="preserve">16.6477832794189</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8334903717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0687294006348</t>
+    <t xml:space="preserve">15.8334922790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0687313079834</t>
   </si>
   <si>
     <t xml:space="preserve">15.869683265686</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9239683151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9058694839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8515853881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0144424438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7972984313965</t>
+    <t xml:space="preserve">15.9239664077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9058713912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8515892028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0144443511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7972965240479</t>
   </si>
   <si>
     <t xml:space="preserve">16.2677783966064</t>
@@ -2312,13 +2312,13 @@
     <t xml:space="preserve">16.4125442504883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8153953552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9420614242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6344385147095</t>
+    <t xml:space="preserve">15.8153972625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.942063331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6344423294067</t>
   </si>
   <si>
     <t xml:space="preserve">16.1049213409424</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">15.6887273788452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6163454055786</t>
+    <t xml:space="preserve">15.61634349823</t>
   </si>
   <si>
     <t xml:space="preserve">14.8925275802612</t>
@@ -2339,16 +2339,16 @@
     <t xml:space="preserve">15.6525354385376</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3630104064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4896764755249</t>
+    <t xml:space="preserve">15.3630084991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4896793365479</t>
   </si>
   <si>
     <t xml:space="preserve">15.1458654403687</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0372934341431</t>
+    <t xml:space="preserve">15.0372924804688</t>
   </si>
   <si>
     <t xml:space="preserve">15.7430114746094</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">14.8201465606689</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2906284332275</t>
+    <t xml:space="preserve">15.2906274795532</t>
   </si>
   <si>
     <t xml:space="preserve">17.5887470245361</t>
@@ -2366,16 +2366,16 @@
     <t xml:space="preserve">17.7696990966797</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0230369567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1359024047852</t>
+    <t xml:space="preserve">18.0230350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1359043121338</t>
   </si>
   <si>
     <t xml:space="preserve">18.2763710021973</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0411319732666</t>
+    <t xml:space="preserve">18.041130065918</t>
   </si>
   <si>
     <t xml:space="preserve">17.4258861541748</t>
@@ -2384,10 +2384,10 @@
     <t xml:space="preserve">17.7335090637207</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2992191314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0458869934082</t>
+    <t xml:space="preserve">17.2992210388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0458850860596</t>
   </si>
   <si>
     <t xml:space="preserve">17.0277881622314</t>
@@ -2405,10 +2405,10 @@
     <t xml:space="preserve">18.5025672912598</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1406536102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.96875</t>
+    <t xml:space="preserve">18.1406555175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9687480926514</t>
   </si>
   <si>
     <t xml:space="preserve">17.4982681274414</t>
@@ -2420,13 +2420,13 @@
     <t xml:space="preserve">18.5930404663086</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1544570922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.244930267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1182651519775</t>
+    <t xml:space="preserve">17.1544551849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2449321746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1182613372803</t>
   </si>
   <si>
     <t xml:space="preserve">16.8106422424316</t>
@@ -2441,31 +2441,31 @@
     <t xml:space="preserve">16.9192161560059</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0639801025391</t>
+    <t xml:space="preserve">17.0639781951904</t>
   </si>
   <si>
     <t xml:space="preserve">16.8468341827393</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9011211395264</t>
+    <t xml:space="preserve">16.9011192321777</t>
   </si>
   <si>
     <t xml:space="preserve">17.3173141479492</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2087421417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2268371582031</t>
+    <t xml:space="preserve">17.2087440490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2268390655518</t>
   </si>
   <si>
     <t xml:space="preserve">18.3668479919434</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4573268890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6382808685303</t>
+    <t xml:space="preserve">18.4573249816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6382789611816</t>
   </si>
   <si>
     <t xml:space="preserve">18.7287578582764</t>
@@ -2477,7 +2477,7 @@
     <t xml:space="preserve">18.8644733428955</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6335296630859</t>
+    <t xml:space="preserve">19.6335315704346</t>
   </si>
   <si>
     <t xml:space="preserve">19.6787662506104</t>
@@ -2486,25 +2486,25 @@
     <t xml:space="preserve">19.5430507659912</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0454254150391</t>
+    <t xml:space="preserve">19.0454273223877</t>
   </si>
   <si>
     <t xml:space="preserve">19.0001888275146</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3168563842773</t>
+    <t xml:space="preserve">19.316858291626</t>
   </si>
   <si>
     <t xml:space="preserve">18.3216114044189</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2311344146729</t>
+    <t xml:space="preserve">18.2311325073242</t>
   </si>
   <si>
     <t xml:space="preserve">19.0906677246094</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6835193634033</t>
+    <t xml:space="preserve">18.6835174560547</t>
   </si>
   <si>
     <t xml:space="preserve">18.0954170227051</t>
@@ -2513,22 +2513,22 @@
     <t xml:space="preserve">18.0049381256104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.570650100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8239860534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6430339813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8058910369873</t>
+    <t xml:space="preserve">17.5706520080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8239879608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6430320739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8058929443359</t>
   </si>
   <si>
     <t xml:space="preserve">19.2716197967529</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1811408996582</t>
+    <t xml:space="preserve">19.1811428070068</t>
   </si>
   <si>
     <t xml:space="preserve">20.26686668396</t>
@@ -2543,31 +2543,31 @@
     <t xml:space="preserve">20.5835380554199</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3573436737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9049587249756</t>
+    <t xml:space="preserve">20.3573455810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9049606323242</t>
   </si>
   <si>
     <t xml:space="preserve">19.7692432403564</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7192535400391</t>
+    <t xml:space="preserve">20.7192516326904</t>
   </si>
   <si>
     <t xml:space="preserve">19.9954357147217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2263813018799</t>
+    <t xml:space="preserve">19.2263832092285</t>
   </si>
   <si>
     <t xml:space="preserve">19.4525718688965</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4073352813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6249351501465</t>
+    <t xml:space="preserve">19.4073333740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6249370574951</t>
   </si>
   <si>
     <t xml:space="preserve">17.7877941131592</t>
@@ -2576,10 +2576,10 @@
     <t xml:space="preserve">19.4978122711182</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0859146118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1311511993408</t>
+    <t xml:space="preserve">20.0859127044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1311492919922</t>
   </si>
   <si>
     <t xml:space="preserve">19.8597221374512</t>
@@ -2591,16 +2591,16 @@
     <t xml:space="preserve">21.0359230041504</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8097305297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.628776550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3121070861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4478244781494</t>
+    <t xml:space="preserve">20.8097324371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6287746429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.312105178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4478225708008</t>
   </si>
   <si>
     <t xml:space="preserve">20.8821105957031</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">21.2802104949951</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3344955444336</t>
+    <t xml:space="preserve">21.3344993591309</t>
   </si>
   <si>
     <t xml:space="preserve">21.587833404541</t>
@@ -2621,10 +2621,10 @@
     <t xml:space="preserve">22.1668872833252</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6192722320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8726062774658</t>
+    <t xml:space="preserve">22.619270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8726100921631</t>
   </si>
   <si>
     <t xml:space="preserve">23.9040470123291</t>
@@ -2636,31 +2636,31 @@
     <t xml:space="preserve">21.8592643737793</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0040283203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2573642730713</t>
+    <t xml:space="preserve">22.0040264129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2573661804199</t>
   </si>
   <si>
     <t xml:space="preserve">22.4745101928711</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1126022338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.058313369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6011772155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6373653411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.420223236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4021282196045</t>
+    <t xml:space="preserve">22.1126003265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0583114624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6011734008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6373672485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4202213287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4021263122559</t>
   </si>
   <si>
     <t xml:space="preserve">21.3525943756104</t>
@@ -2672,16 +2672,16 @@
     <t xml:space="preserve">22.09450340271</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5830783843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0354652404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.017370223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3611850738525</t>
+    <t xml:space="preserve">22.583080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0354671478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0173721313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3611831665039</t>
   </si>
   <si>
     <t xml:space="preserve">23.2707061767578</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">24.7726249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9716777801514</t>
+    <t xml:space="preserve">24.9716758728027</t>
   </si>
   <si>
     <t xml:space="preserve">25.0621528625488</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">25.9126377105713</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2383556365967</t>
+    <t xml:space="preserve">26.2383575439453</t>
   </si>
   <si>
     <t xml:space="preserve">26.6765727996826</t>
@@ -70525,7 +70525,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6494212963</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>195713</v>
@@ -70546,6 +70546,32 @@
         <v>1775</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6497916667</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>71062</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>14.8800001144409</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>14.8100004196167</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>14.8299999237061</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>14.8400001525879</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>1764</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TNXT.MI.xlsx
+++ b/data/TNXT.MI.xlsx
@@ -47,34 +47,34 @@
     <t xml:space="preserve">2.65150952339172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59350848197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53550696372986</t>
+    <t xml:space="preserve">2.59350872039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5355064868927</t>
   </si>
   <si>
     <t xml:space="preserve">2.52556347846985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48579072952271</t>
+    <t xml:space="preserve">2.48579096794128</t>
   </si>
   <si>
     <t xml:space="preserve">2.52722072601318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48744773864746</t>
+    <t xml:space="preserve">2.48744821548462</t>
   </si>
   <si>
     <t xml:space="preserve">2.47087574005127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46921849250793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54047799110413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49739098548889</t>
+    <t xml:space="preserve">2.46921873092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54047846794128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49739074707031</t>
   </si>
   <si>
     <t xml:space="preserve">2.47916197776794</t>
@@ -83,49 +83,49 @@
     <t xml:space="preserve">2.44436097145081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39464473724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34161448478699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36150074005127</t>
+    <t xml:space="preserve">2.39464449882507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34161424636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36150097846985</t>
   </si>
   <si>
     <t xml:space="preserve">2.55207872390747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58522272109985</t>
+    <t xml:space="preserve">2.58522295951843</t>
   </si>
   <si>
     <t xml:space="preserve">2.6100800037384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56865048408508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63659501075745</t>
+    <t xml:space="preserve">2.56865072250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63659477233887</t>
   </si>
   <si>
     <t xml:space="preserve">2.68962502479553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73436975479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72608351707458</t>
+    <t xml:space="preserve">2.73436951637268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72608327865601</t>
   </si>
   <si>
     <t xml:space="preserve">2.77579951286316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58025145530701</t>
+    <t xml:space="preserve">2.58025097846985</t>
   </si>
   <si>
     <t xml:space="preserve">2.5620219707489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66808152198792</t>
+    <t xml:space="preserve">2.66808176040649</t>
   </si>
   <si>
     <t xml:space="preserve">2.62830877304077</t>
@@ -137,115 +137,115 @@
     <t xml:space="preserve">2.60842227935791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66642427444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65316677093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62665152549744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6929395198822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82551550865173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81722927093506</t>
+    <t xml:space="preserve">2.66642451286316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65316653251648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62665200233459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69293975830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82551574707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81722950935364</t>
   </si>
   <si>
     <t xml:space="preserve">2.90008950233459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8586597442627</t>
+    <t xml:space="preserve">2.85865950584412</t>
   </si>
   <si>
     <t xml:space="preserve">2.89843225479126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8835175037384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87523150444031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86694526672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81888651847839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82054376602173</t>
+    <t xml:space="preserve">2.88351702690125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87523102760315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86694550514221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81888675689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82054424285889</t>
   </si>
   <si>
     <t xml:space="preserve">2.85368776321411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79237127304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85700225830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90671825408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82882976531982</t>
+    <t xml:space="preserve">2.79237151145935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8570020198822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90671801567078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8288300037384</t>
   </si>
   <si>
     <t xml:space="preserve">2.85037350654602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90837526321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96306276321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9579770565033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88169741630554</t>
+    <t xml:space="preserve">2.90837502479553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96306300163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95797729492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8816967010498</t>
   </si>
   <si>
     <t xml:space="preserve">2.89017271995544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86474561691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94950175285339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92407536506653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96645283699036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11901330947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94272136688232</t>
+    <t xml:space="preserve">2.86474585533142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94950199127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92407512664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96645307540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11901307106018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9427216053009</t>
   </si>
   <si>
     <t xml:space="preserve">2.94780707359314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8833920955658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87322163581848</t>
+    <t xml:space="preserve">2.88339185714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87322187423706</t>
   </si>
   <si>
     <t xml:space="preserve">2.85966086387634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03256249427795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07037329673767</t>
+    <t xml:space="preserve">3.03256320953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07037377357483</t>
   </si>
   <si>
     <t xml:space="preserve">3.06866312026978</t>
@@ -263,10 +263,10 @@
     <t xml:space="preserve">2.93524312973022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98313760757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92498016357422</t>
+    <t xml:space="preserve">2.98313736915588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92497992515564</t>
   </si>
   <si>
     <t xml:space="preserve">2.92326951026917</t>
@@ -275,16 +275,16 @@
     <t xml:space="preserve">2.96774291992188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03616309165955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05840039253235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05497932434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08747863769531</t>
+    <t xml:space="preserve">3.03616333007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05840015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0549795627594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08747887611389</t>
   </si>
   <si>
     <t xml:space="preserve">3.13879418373108</t>
@@ -293,19 +293,19 @@
     <t xml:space="preserve">3.12853145599365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19010996818542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15589928627014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12339973449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12511038780212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14734673500061</t>
+    <t xml:space="preserve">3.19010972976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15589952468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12339997291565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12511014938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14734721183777</t>
   </si>
   <si>
     <t xml:space="preserve">3.16445183753967</t>
@@ -314,25 +314,25 @@
     <t xml:space="preserve">3.16616249084473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24142551422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30129289627075</t>
+    <t xml:space="preserve">3.24142527580261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30129313468933</t>
   </si>
   <si>
     <t xml:space="preserve">3.3868191242218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48431777954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52708101272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62629079818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63655352592468</t>
+    <t xml:space="preserve">3.48431801795959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52708125114441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62629103660583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.636554479599</t>
   </si>
   <si>
     <t xml:space="preserve">3.64510703086853</t>
@@ -347,16 +347,16 @@
     <t xml:space="preserve">3.71181702613831</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63484334945679</t>
+    <t xml:space="preserve">3.63484358787537</t>
   </si>
   <si>
     <t xml:space="preserve">3.51681780815125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50484442710876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49458146095276</t>
+    <t xml:space="preserve">3.50484466552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49458122253418</t>
   </si>
   <si>
     <t xml:space="preserve">3.50655460357666</t>
@@ -368,64 +368,64 @@
     <t xml:space="preserve">3.43129253387451</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35602974891663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60063338279724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64681696891785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69471168518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69984340667725</t>
+    <t xml:space="preserve">3.35602998733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60063314437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64681720733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69471216201782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69984364509583</t>
   </si>
   <si>
     <t xml:space="preserve">3.67589592933655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6656322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59721159934998</t>
+    <t xml:space="preserve">3.66563272476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59721231460571</t>
   </si>
   <si>
     <t xml:space="preserve">3.63313341140747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57497572898865</t>
+    <t xml:space="preserve">3.57497549057007</t>
   </si>
   <si>
     <t xml:space="preserve">3.66050100326538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68615889549255</t>
+    <t xml:space="preserve">3.68615865707397</t>
   </si>
   <si>
     <t xml:space="preserve">3.71523761749268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73747396469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71010661125183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69129037857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68957996368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73234224319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72036910057068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76313185691833</t>
+    <t xml:space="preserve">3.73747372627258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71010613441467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69129061698914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6895797252655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73234272003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72036981582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76313209533691</t>
   </si>
   <si>
     <t xml:space="preserve">3.77168464660645</t>
@@ -434,34 +434,34 @@
     <t xml:space="preserve">3.62115955352783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64168572425842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70326352119446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79734230041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75457906723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90852546691895</t>
+    <t xml:space="preserve">3.64168548583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7032642364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79734253883362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75457954406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9085259437561</t>
   </si>
   <si>
     <t xml:space="preserve">3.76655268669128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72892189025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66734266281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50997614860535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49800229072571</t>
+    <t xml:space="preserve">3.72892165184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66734290122986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50997591018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49800252914429</t>
   </si>
   <si>
     <t xml:space="preserve">3.4894495010376</t>
@@ -470,109 +470,109 @@
     <t xml:space="preserve">3.47234416007996</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40392374992371</t>
+    <t xml:space="preserve">3.40392398834229</t>
   </si>
   <si>
     <t xml:space="preserve">3.43642401695251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53221273422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51852822303772</t>
+    <t xml:space="preserve">3.53221225738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5185284614563</t>
   </si>
   <si>
     <t xml:space="preserve">3.46037101745605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50142335891724</t>
+    <t xml:space="preserve">3.50142359733582</t>
   </si>
   <si>
     <t xml:space="preserve">3.53563356399536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55615997314453</t>
+    <t xml:space="preserve">3.55616021156311</t>
   </si>
   <si>
     <t xml:space="preserve">3.64339661598206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72550106048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84865832328796</t>
+    <t xml:space="preserve">3.72550058364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84865760803223</t>
   </si>
   <si>
     <t xml:space="preserve">3.82984209060669</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83155274391174</t>
+    <t xml:space="preserve">3.83155298233032</t>
   </si>
   <si>
     <t xml:space="preserve">3.87089467048645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84523677825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87431597709656</t>
+    <t xml:space="preserve">3.8452365398407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87431526184082</t>
   </si>
   <si>
     <t xml:space="preserve">3.86405253410339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85721015930176</t>
+    <t xml:space="preserve">3.85721039772034</t>
   </si>
   <si>
     <t xml:space="preserve">3.82471036911011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90681481361389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00260400772095</t>
+    <t xml:space="preserve">3.90681505203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00260353088379</t>
   </si>
   <si>
     <t xml:space="preserve">4.17536640167236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11378765106201</t>
+    <t xml:space="preserve">4.11378717422485</t>
   </si>
   <si>
     <t xml:space="preserve">4.00773525238037</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05220890045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08128786087036</t>
+    <t xml:space="preserve">4.0522084236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0812873840332</t>
   </si>
   <si>
     <t xml:space="preserve">4.00602531433105</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09839296340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01970958709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01115655899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99576234817505</t>
+    <t xml:space="preserve">4.09839248657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01970863342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01115703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99576187133789</t>
   </si>
   <si>
     <t xml:space="preserve">4.0351037979126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06247282028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13773393630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1223406791687</t>
+    <t xml:space="preserve">4.06247234344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13773441314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12233972549438</t>
   </si>
   <si>
     <t xml:space="preserve">4.14799737930298</t>
@@ -581,19 +581,19 @@
     <t xml:space="preserve">4.18905019760132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2591814994812</t>
+    <t xml:space="preserve">4.25918102264404</t>
   </si>
   <si>
     <t xml:space="preserve">4.22839212417603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20615530014038</t>
+    <t xml:space="preserve">4.20615482330322</t>
   </si>
   <si>
     <t xml:space="preserve">4.02142000198364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99405169487</t>
+    <t xml:space="preserve">3.99405121803284</t>
   </si>
   <si>
     <t xml:space="preserve">4.01799917221069</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">4.02655124664307</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07615566253662</t>
+    <t xml:space="preserve">4.07615613937378</t>
   </si>
   <si>
     <t xml:space="preserve">4.12747192382812</t>
@@ -611,55 +611,55 @@
     <t xml:space="preserve">4.11891841888428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10523557662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09668254852295</t>
+    <t xml:space="preserve">4.10523509979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09668302536011</t>
   </si>
   <si>
     <t xml:space="preserve">4.10181427001953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07102537155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09497213363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13089275360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21641826629639</t>
+    <t xml:space="preserve">4.0710244178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09497261047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13089227676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21641874313354</t>
   </si>
   <si>
     <t xml:space="preserve">4.52431106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54996919631958</t>
+    <t xml:space="preserve">4.54996871948242</t>
   </si>
   <si>
     <t xml:space="preserve">4.53713989257812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46444320678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5029296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56707429885864</t>
+    <t xml:space="preserve">4.46444272994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50292921066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5670747756958</t>
   </si>
   <si>
     <t xml:space="preserve">4.6226658821106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63549518585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58417940139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60128402709961</t>
+    <t xml:space="preserve">4.63549423217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58417892456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60128450393677</t>
   </si>
   <si>
     <t xml:space="preserve">4.57562637329102</t>
@@ -668,16 +668,16 @@
     <t xml:space="preserve">4.61838912963867</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53286409378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55852127075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48154830932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5157585144043</t>
+    <t xml:space="preserve">4.53286361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55852174758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48154783248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51575803756714</t>
   </si>
   <si>
     <t xml:space="preserve">4.4901008605957</t>
@@ -686,25 +686,25 @@
     <t xml:space="preserve">4.51148223876953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63121843338013</t>
+    <t xml:space="preserve">4.63121795654297</t>
   </si>
   <si>
     <t xml:space="preserve">4.78516387939453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75950717926025</t>
+    <t xml:space="preserve">4.7595067024231</t>
   </si>
   <si>
     <t xml:space="preserve">4.78944063186646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7338490486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77233648300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76378345489502</t>
+    <t xml:space="preserve">4.73384857177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77233600616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76378297805786</t>
   </si>
   <si>
     <t xml:space="preserve">4.65687656402588</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">4.69536209106445</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8279275894165</t>
+    <t xml:space="preserve">4.82792806625366</t>
   </si>
   <si>
     <t xml:space="preserve">4.90062379837036</t>
@@ -725,79 +725,79 @@
     <t xml:space="preserve">4.94338750839233</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98614978790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04174184799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02036046981812</t>
+    <t xml:space="preserve">4.98614931106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04174137115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02035999298096</t>
   </si>
   <si>
     <t xml:space="preserve">5.07167530059814</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08022832870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99470281600952</t>
+    <t xml:space="preserve">5.08022785186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99470233917236</t>
   </si>
   <si>
     <t xml:space="preserve">5.09305667877197</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06050682067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91728448867798</t>
+    <t xml:space="preserve">5.06050729751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91728496551514</t>
   </si>
   <si>
     <t xml:space="preserve">4.94766521453857</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92596483230591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90426540374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82180404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73500299453735</t>
+    <t xml:space="preserve">4.92596578598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9042649269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8218035697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7350025177002</t>
   </si>
   <si>
     <t xml:space="preserve">4.72198247909546</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59178066253662</t>
+    <t xml:space="preserve">4.59178018569946</t>
   </si>
   <si>
     <t xml:space="preserve">4.64386081695557</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73066186904907</t>
+    <t xml:space="preserve">4.73066234588623</t>
   </si>
   <si>
     <t xml:space="preserve">4.66556215286255</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65254163742065</t>
+    <t xml:space="preserve">4.6525411605835</t>
   </si>
   <si>
     <t xml:space="preserve">4.60914087295532</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65688133239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54838037490845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53536033630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47025918960571</t>
+    <t xml:space="preserve">4.65688180923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54837989807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53535985946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47025871276855</t>
   </si>
   <si>
     <t xml:space="preserve">4.59612131118774</t>
@@ -809,37 +809,37 @@
     <t xml:space="preserve">4.48761940002441</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46157884597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41383838653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38779830932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39213800430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40949773788452</t>
+    <t xml:space="preserve">4.46157836914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41383790969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38779783248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39213848114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40949821472168</t>
   </si>
   <si>
     <t xml:space="preserve">4.55706024169922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52233934402466</t>
+    <t xml:space="preserve">4.52233982086182</t>
   </si>
   <si>
     <t xml:space="preserve">4.57008028030396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53970050811768</t>
+    <t xml:space="preserve">4.53970003128052</t>
   </si>
   <si>
     <t xml:space="preserve">4.47893905639648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43553829193115</t>
+    <t xml:space="preserve">4.43553876876831</t>
   </si>
   <si>
     <t xml:space="preserve">4.42251825332642</t>
@@ -848,19 +848,19 @@
     <t xml:space="preserve">4.43119859695435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45289850234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51365947723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68726205825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60046052932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63952112197876</t>
+    <t xml:space="preserve">4.45289945602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51365995407104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6872615814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60046100616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6395206451416</t>
   </si>
   <si>
     <t xml:space="preserve">4.56140041351318</t>
@@ -869,31 +869,31 @@
     <t xml:space="preserve">4.58744049072266</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61782073974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64820146560669</t>
+    <t xml:space="preserve">4.61782121658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64820098876953</t>
   </si>
   <si>
     <t xml:space="preserve">4.6048002243042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58309984207153</t>
+    <t xml:space="preserve">4.58310079574585</t>
   </si>
   <si>
     <t xml:space="preserve">4.49629926681519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5049786567688</t>
+    <t xml:space="preserve">4.50497913360596</t>
   </si>
   <si>
     <t xml:space="preserve">4.42685794830322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49196004867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51800012588501</t>
+    <t xml:space="preserve">4.49195957183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51799964904785</t>
   </si>
   <si>
     <t xml:space="preserve">4.80878305435181</t>
@@ -905,22 +905,22 @@
     <t xml:space="preserve">4.84784412384033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8348240852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74368286132812</t>
+    <t xml:space="preserve">4.83482456207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74368333816528</t>
   </si>
   <si>
     <t xml:space="preserve">4.81312370300293</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71330213546753</t>
+    <t xml:space="preserve">4.71330308914185</t>
   </si>
   <si>
     <t xml:space="preserve">4.70462226867676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72632312774658</t>
+    <t xml:space="preserve">4.72632217407227</t>
   </si>
   <si>
     <t xml:space="preserve">4.69594192504883</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">4.76972246170044</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84350395202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87822389602661</t>
+    <t xml:space="preserve">4.84350442886353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87822437286377</t>
   </si>
   <si>
     <t xml:space="preserve">4.8738842010498</t>
@@ -947,16 +947,16 @@
     <t xml:space="preserve">5.00842666625977</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07786750793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04314613342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14730739593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86086463928223</t>
+    <t xml:space="preserve">5.07786703109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04314661026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14730787277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86086416244507</t>
   </si>
   <si>
     <t xml:space="preserve">4.869544506073</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">4.90860509872437</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99974584579468</t>
+    <t xml:space="preserve">4.99974632263184</t>
   </si>
   <si>
     <t xml:space="preserve">4.99106597900391</t>
@@ -983,43 +983,43 @@
     <t xml:space="preserve">5.29486989974976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41639137268066</t>
+    <t xml:space="preserve">5.41639089584351</t>
   </si>
   <si>
     <t xml:space="preserve">5.48583316802979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43375158309937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48149251937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42073202133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39469051361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35563039779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33393001556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37299156188965</t>
+    <t xml:space="preserve">5.43375205993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48149299621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42073106765747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39469146728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35563087463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33393049240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37299060821533</t>
   </si>
   <si>
     <t xml:space="preserve">5.33827066421509</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20806837081909</t>
+    <t xml:space="preserve">5.20806884765625</t>
   </si>
   <si>
     <t xml:space="preserve">5.16466808319092</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26448917388916</t>
+    <t xml:space="preserve">5.26448965072632</t>
   </si>
   <si>
     <t xml:space="preserve">5.25146961212158</t>
@@ -1031,10 +1031,10 @@
     <t xml:space="preserve">5.18636846542358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20372867584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19504928588867</t>
+    <t xml:space="preserve">5.20372819900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19504833221436</t>
   </si>
   <si>
     <t xml:space="preserve">5.16900777816772</t>
@@ -1043,37 +1043,37 @@
     <t xml:space="preserve">5.18202877044678</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19938898086548</t>
+    <t xml:space="preserve">5.19938802719116</t>
   </si>
   <si>
     <t xml:space="preserve">5.22542905807495</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42507171630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61603403091431</t>
+    <t xml:space="preserve">5.42507123947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61603450775146</t>
   </si>
   <si>
     <t xml:space="preserve">5.7288761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7115159034729</t>
+    <t xml:space="preserve">5.71151542663574</t>
   </si>
   <si>
     <t xml:space="preserve">5.78963661193848</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82435703277588</t>
+    <t xml:space="preserve">5.82435655593872</t>
   </si>
   <si>
     <t xml:space="preserve">5.87643814086914</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88511848449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93719911575317</t>
+    <t xml:space="preserve">5.88511800765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93719863891602</t>
   </si>
   <si>
     <t xml:space="preserve">5.85907745361328</t>
@@ -1082,25 +1082,25 @@
     <t xml:space="preserve">5.80699682235718</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92851829528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97191858291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95455884933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03267955780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1715612411499</t>
+    <t xml:space="preserve">5.92851877212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97191905975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95455932617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03267908096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17156219482422</t>
   </si>
   <si>
     <t xml:space="preserve">6.28440284729004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01531982421875</t>
+    <t xml:space="preserve">6.01531934738159</t>
   </si>
   <si>
     <t xml:space="preserve">6.02399969100952</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">6.21496152877808</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14552116394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40592479705811</t>
+    <t xml:space="preserve">6.14552068710327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40592527389526</t>
   </si>
   <si>
     <t xml:space="preserve">6.07608032226562</t>
@@ -1121,10 +1121,10 @@
     <t xml:space="preserve">5.98927927017212</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04136037826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22364187240601</t>
+    <t xml:space="preserve">6.04135990142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22364234924316</t>
   </si>
   <si>
     <t xml:space="preserve">6.13684129714966</t>
@@ -1139,13 +1139,13 @@
     <t xml:space="preserve">6.05003976821899</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89379787445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90247869491577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70283555984497</t>
+    <t xml:space="preserve">5.89379692077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90247774124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70283508300781</t>
   </si>
   <si>
     <t xml:space="preserve">5.50319290161133</t>
@@ -1154,13 +1154,13 @@
     <t xml:space="preserve">5.5813136100769</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72019624710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76359605789185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91983890533447</t>
+    <t xml:space="preserve">5.72019577026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76359558105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91983795166016</t>
   </si>
   <si>
     <t xml:space="preserve">5.99795913696289</t>
@@ -1169,19 +1169,19 @@
     <t xml:space="preserve">5.83303689956665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79831647872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65943431854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51187229156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54659366607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58999395370483</t>
+    <t xml:space="preserve">5.79831695556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65943479537964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51187324523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5465931892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58999300003052</t>
   </si>
   <si>
     <t xml:space="preserve">5.52055311203003</t>
@@ -1190,16 +1190,16 @@
     <t xml:space="preserve">5.38167095184326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44243144989014</t>
+    <t xml:space="preserve">5.44243192672729</t>
   </si>
   <si>
     <t xml:space="preserve">5.46847248077393</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67679500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64207458496094</t>
+    <t xml:space="preserve">5.67679452896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64207410812378</t>
   </si>
   <si>
     <t xml:space="preserve">5.55527353286743</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">5.57263422012329</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5292329788208</t>
+    <t xml:space="preserve">5.52923250198364</t>
   </si>
   <si>
     <t xml:space="preserve">5.39903163909912</t>
@@ -1220,25 +1220,25 @@
     <t xml:space="preserve">5.39035129547119</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45111179351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09344100952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81567668914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77227640151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73755550384521</t>
+    <t xml:space="preserve">5.45111227035522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09344053268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81567621231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77227592468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73755598068237</t>
   </si>
   <si>
     <t xml:space="preserve">5.40771198272705</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24278926849365</t>
+    <t xml:space="preserve">5.24278879165649</t>
   </si>
   <si>
     <t xml:space="preserve">5.0691876411438</t>
@@ -1247,22 +1247,22 @@
     <t xml:space="preserve">4.98238515853882</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07618808746338</t>
+    <t xml:space="preserve">5.07618761062622</t>
   </si>
   <si>
     <t xml:space="preserve">5.15619802474976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08507823944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24509763717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11174774169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13841819763184</t>
+    <t xml:space="preserve">5.08507776260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24509811401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11174726486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13841772079468</t>
   </si>
   <si>
     <t xml:space="preserve">5.20953798294067</t>
@@ -1271,43 +1271,43 @@
     <t xml:space="preserve">5.067298412323</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0584077835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04062795639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04951810836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94283819198608</t>
+    <t xml:space="preserve">5.05840826034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04062747955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0495171546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94283771514893</t>
   </si>
   <si>
     <t xml:space="preserve">4.77392816543579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90727758407593</t>
+    <t xml:space="preserve">4.90727806091309</t>
   </si>
   <si>
     <t xml:space="preserve">4.76503801345825</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92505836486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88949775695801</t>
+    <t xml:space="preserve">4.92505788803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88949823379517</t>
   </si>
   <si>
     <t xml:space="preserve">5.02284812927246</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97839784622192</t>
+    <t xml:space="preserve">4.97839736938477</t>
   </si>
   <si>
     <t xml:space="preserve">4.91616773605347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95172786712646</t>
+    <t xml:space="preserve">4.95172834396362</t>
   </si>
   <si>
     <t xml:space="preserve">4.93394804000854</t>
@@ -1322,16 +1322,16 @@
     <t xml:space="preserve">4.78281831741333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75614833831787</t>
+    <t xml:space="preserve">4.75614738464355</t>
   </si>
   <si>
     <t xml:space="preserve">4.98728799819946</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10285758972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.960618019104</t>
+    <t xml:space="preserve">5.10285806655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96061849594116</t>
   </si>
   <si>
     <t xml:space="preserve">5.20064783096313</t>
@@ -1340,37 +1340,37 @@
     <t xml:space="preserve">5.21842765808105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27176713943481</t>
+    <t xml:space="preserve">5.27176761627197</t>
   </si>
   <si>
     <t xml:space="preserve">5.33399724960327</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23620748519897</t>
+    <t xml:space="preserve">5.23620843887329</t>
   </si>
   <si>
     <t xml:space="preserve">5.18286752700806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01395845413208</t>
+    <t xml:space="preserve">5.01395797729492</t>
   </si>
   <si>
     <t xml:space="preserve">4.99617767333984</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00506782531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37844848632812</t>
+    <t xml:space="preserve">5.00506830215454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37844800949097</t>
   </si>
   <si>
     <t xml:space="preserve">5.47623729705811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56513738632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68070697784424</t>
+    <t xml:space="preserve">5.56513786315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68070793151855</t>
   </si>
   <si>
     <t xml:space="preserve">5.6540379524231</t>
@@ -1385,10 +1385,10 @@
     <t xml:space="preserve">5.68959760665894</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96518802642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89406728744507</t>
+    <t xml:space="preserve">5.96518754959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89406776428223</t>
   </si>
   <si>
     <t xml:space="preserve">5.77849769592285</t>
@@ -1397,34 +1397,34 @@
     <t xml:space="preserve">5.84072780609131</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76071786880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92073822021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83183765411377</t>
+    <t xml:space="preserve">5.76071739196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92073774337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83183717727661</t>
   </si>
   <si>
     <t xml:space="preserve">5.44956827163696</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58291721343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43178844451904</t>
+    <t xml:space="preserve">5.5829176902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43178796768188</t>
   </si>
   <si>
     <t xml:space="preserve">5.36955738067627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6095871925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86739778518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78738737106323</t>
+    <t xml:space="preserve">5.60958766937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86739730834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78738832473755</t>
   </si>
   <si>
     <t xml:space="preserve">5.52068758010864</t>
@@ -1433,115 +1433,115 @@
     <t xml:space="preserve">5.49401760101318</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57402801513672</t>
+    <t xml:space="preserve">5.57402753829956</t>
   </si>
   <si>
     <t xml:space="preserve">5.59180784225464</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6451473236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71626758575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73404741287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81405782699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67181777954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5117974281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85850811004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66292715072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53846836090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90295839309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79627799987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80516815185547</t>
+    <t xml:space="preserve">5.64514780044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71626806259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73404788970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81405735015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67181730270386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51179790496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85850763320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66292762756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53846788406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90295743942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79627752304077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80516767501831</t>
   </si>
   <si>
     <t xml:space="preserve">5.6184778213501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46734809875488</t>
+    <t xml:space="preserve">5.46734762191772</t>
   </si>
   <si>
     <t xml:space="preserve">5.60069751739502</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45845746994019</t>
+    <t xml:space="preserve">5.45845794677734</t>
   </si>
   <si>
     <t xml:space="preserve">5.50290822982788</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34288835525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62736701965332</t>
+    <t xml:space="preserve">5.34288787841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62736749649048</t>
   </si>
   <si>
     <t xml:space="preserve">5.52957773208618</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42289733886719</t>
+    <t xml:space="preserve">5.42289781570435</t>
   </si>
   <si>
     <t xml:space="preserve">5.72515773773193</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70737743377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69848728179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00074768066406</t>
+    <t xml:space="preserve">5.70737791061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69848680496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00074815750122</t>
   </si>
   <si>
     <t xml:space="preserve">5.92962789535522</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94740772247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93851709365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99185752868652</t>
+    <t xml:space="preserve">5.9474081993103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93851757049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99185705184937</t>
   </si>
   <si>
     <t xml:space="preserve">6.24077749252319</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40968704223633</t>
+    <t xml:space="preserve">6.40968751907349</t>
   </si>
   <si>
     <t xml:space="preserve">6.48080682754517</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62304735183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84529733657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99642705917358</t>
+    <t xml:space="preserve">6.623046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84529685974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9964280128479</t>
   </si>
   <si>
     <t xml:space="preserve">7.01420640945435</t>
@@ -1550,16 +1550,16 @@
     <t xml:space="preserve">6.90752696990967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91641664505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97864723205566</t>
+    <t xml:space="preserve">6.91641759872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97864675521851</t>
   </si>
   <si>
     <t xml:space="preserve">7.00531673431396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02309703826904</t>
+    <t xml:space="preserve">7.0230975151062</t>
   </si>
   <si>
     <t xml:space="preserve">7.2453465461731</t>
@@ -1568,37 +1568,37 @@
     <t xml:space="preserve">7.27201747894287</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33424758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47648668289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76985645294189</t>
+    <t xml:space="preserve">7.33424711227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47648620605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76985740661621</t>
   </si>
   <si>
     <t xml:space="preserve">7.73429584503174</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72540616989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79652786254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80541706085205</t>
+    <t xml:space="preserve">7.72540760040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79652690887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80541658401489</t>
   </si>
   <si>
     <t xml:space="preserve">8.22324657440186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21435642242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15212631225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12545776367188</t>
+    <t xml:space="preserve">8.21435546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15212726593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12545680999756</t>
   </si>
   <si>
     <t xml:space="preserve">8.00099658966064</t>
@@ -1607,22 +1607,22 @@
     <t xml:space="preserve">8.17879676818848</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34770774841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42771625518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48105621337891</t>
+    <t xml:space="preserve">8.34770584106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42771530151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48105716705322</t>
   </si>
   <si>
     <t xml:space="preserve">8.46327686309814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5255069732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50772571563721</t>
+    <t xml:space="preserve">8.52550601959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50772666931152</t>
   </si>
   <si>
     <t xml:space="preserve">8.66774749755859</t>
@@ -1637,28 +1637,28 @@
     <t xml:space="preserve">9.19225692749023</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37005615234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47673606872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49451541900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31671619415283</t>
+    <t xml:space="preserve">9.37005519866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4767370223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49451732635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31671524047852</t>
   </si>
   <si>
     <t xml:space="preserve">9.15669631958008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35227584838867</t>
+    <t xml:space="preserve">9.3522777557373</t>
   </si>
   <si>
     <t xml:space="preserve">9.40561580657959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69009590148926</t>
+    <t xml:space="preserve">9.69009494781494</t>
   </si>
   <si>
     <t xml:space="preserve">9.86789608001709</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">9.83233547210693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77899551391602</t>
+    <t xml:space="preserve">9.77899646759033</t>
   </si>
   <si>
     <t xml:space="preserve">9.44117546081543</t>
@@ -1679,34 +1679,34 @@
     <t xml:space="preserve">9.58341503143311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51229667663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6723165512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85011672973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0990362167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0279169082642</t>
+    <t xml:space="preserve">9.51229476928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67231559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85011577606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0990343093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0279159545898</t>
   </si>
   <si>
     <t xml:space="preserve">9.99235534667969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0101356506348</t>
+    <t xml:space="preserve">10.0101366043091</t>
   </si>
   <si>
     <t xml:space="preserve">9.76121616363525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88567638397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2234954833984</t>
+    <t xml:space="preserve">9.88567543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2234945297241</t>
   </si>
   <si>
     <t xml:space="preserve">10.4368553161621</t>
@@ -1715,22 +1715,22 @@
     <t xml:space="preserve">10.6679944992065</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4147548675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3614139556885</t>
+    <t xml:space="preserve">11.414755821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3614158630371</t>
   </si>
   <si>
     <t xml:space="preserve">11.3080759048462</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4325351715088</t>
+    <t xml:space="preserve">11.4325361251831</t>
   </si>
   <si>
     <t xml:space="preserve">11.6814556121826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8948154449463</t>
+    <t xml:space="preserve">11.8948163986206</t>
   </si>
   <si>
     <t xml:space="preserve">11.965934753418</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">12.1437349319458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6281156539917</t>
+    <t xml:space="preserve">11.6281147003174</t>
   </si>
   <si>
     <t xml:space="preserve">11.4001131057739</t>
@@ -1754,7 +1754,7 @@
     <t xml:space="preserve">11.689640045166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1239309310913</t>
+    <t xml:space="preserve">12.1239280700684</t>
   </si>
   <si>
     <t xml:space="preserve">11.7982120513916</t>
@@ -1766,13 +1766,13 @@
     <t xml:space="preserve">12.3229789733887</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9925098419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8296518325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7391729354858</t>
+    <t xml:space="preserve">12.9925088882446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8296508789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7391738891602</t>
   </si>
   <si>
     <t xml:space="preserve">12.7753648757935</t>
@@ -1781,28 +1781,28 @@
     <t xml:space="preserve">12.3953609466553</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2867879867554</t>
+    <t xml:space="preserve">12.2867889404297</t>
   </si>
   <si>
     <t xml:space="preserve">12.6306018829346</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4496469497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2144060134888</t>
+    <t xml:space="preserve">12.4496479034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2144079208374</t>
   </si>
   <si>
     <t xml:space="preserve">12.1058349609375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8705940246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9067840576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4724941253662</t>
+    <t xml:space="preserve">11.8705930709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9067850112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4724950790405</t>
   </si>
   <si>
     <t xml:space="preserve">11.4182081222534</t>
@@ -1811,10 +1811,10 @@
     <t xml:space="preserve">11.5810670852661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8524990081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0877380371094</t>
+    <t xml:space="preserve">11.852499961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0877389907837</t>
   </si>
   <si>
     <t xml:space="preserve">11.8344030380249</t>
@@ -1826,10 +1826,10 @@
     <t xml:space="preserve">11.4363040924072</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3277311325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734460830688</t>
+    <t xml:space="preserve">11.3277320861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734451293945</t>
   </si>
   <si>
     <t xml:space="preserve">11.1829681396484</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">11.1648731231689</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8391542434692</t>
+    <t xml:space="preserve">10.8391551971436</t>
   </si>
   <si>
     <t xml:space="preserve">10.6401052474976</t>
@@ -1847,13 +1847,13 @@
     <t xml:space="preserve">10.6762971878052</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5134372711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9115371704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.291540145874</t>
+    <t xml:space="preserve">10.5134382247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9115381240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2915391921997</t>
   </si>
   <si>
     <t xml:space="preserve">11.1467761993408</t>
@@ -1862,7 +1862,7 @@
     <t xml:space="preserve">10.7667722702026</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1105871200562</t>
+    <t xml:space="preserve">11.1105861663818</t>
   </si>
   <si>
     <t xml:space="preserve">11.1286821365356</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">10.6220092773438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0020132064819</t>
+    <t xml:space="preserve">11.0020122528076</t>
   </si>
   <si>
     <t xml:space="preserve">10.6039152145386</t>
@@ -1880,13 +1880,13 @@
     <t xml:space="preserve">10.4953422546387</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2781972885132</t>
+    <t xml:space="preserve">10.2781963348389</t>
   </si>
   <si>
     <t xml:space="preserve">10.3143882751465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.898193359375</t>
+    <t xml:space="preserve">9.89819240570068</t>
   </si>
   <si>
     <t xml:space="preserve">9.9343843460083</t>
@@ -1895,61 +1895,61 @@
     <t xml:space="preserve">9.80771636962891</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68104839324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95247936248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2420063018799</t>
+    <t xml:space="preserve">9.6810474395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95248031616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2420072555542</t>
   </si>
   <si>
     <t xml:space="preserve">10.4772462844849</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3867692947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4410552978516</t>
+    <t xml:space="preserve">10.3867702484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4410562515259</t>
   </si>
   <si>
     <t xml:space="preserve">9.55438041687012</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1153392791748</t>
+    <t xml:space="preserve">10.1153383255005</t>
   </si>
   <si>
     <t xml:space="preserve">10.3505792617798</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4048652648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7486772537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0201091766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.857250213623</t>
+    <t xml:space="preserve">10.4048633575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7486782073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0201101303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8572492599487</t>
   </si>
   <si>
     <t xml:space="preserve">10.8753461837769</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5858182907104</t>
+    <t xml:space="preserve">10.5858192443848</t>
   </si>
   <si>
     <t xml:space="preserve">10.8029642105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7124862670898</t>
+    <t xml:space="preserve">10.7124872207642</t>
   </si>
   <si>
     <t xml:space="preserve">10.7848691940308</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2372550964355</t>
+    <t xml:space="preserve">11.2372541427612</t>
   </si>
   <si>
     <t xml:space="preserve">11.3096361160278</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">12.0334529876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9429759979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7620210647583</t>
+    <t xml:space="preserve">11.9429750442505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7620220184326</t>
   </si>
   <si>
     <t xml:space="preserve">10.9477281570435</t>
@@ -1991,7 +1991,7 @@
     <t xml:space="preserve">9.98867034912109</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0429573059082</t>
+    <t xml:space="preserve">10.0429563522339</t>
   </si>
   <si>
     <t xml:space="preserve">9.91628932952881</t>
@@ -2000,19 +2000,19 @@
     <t xml:space="preserve">10.1696243286133</t>
   </si>
   <si>
-    <t xml:space="preserve">10.531533241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4229602813721</t>
+    <t xml:space="preserve">10.5315341949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4229612350464</t>
   </si>
   <si>
     <t xml:space="preserve">10.13343334198</t>
   </si>
   <si>
-    <t xml:space="preserve">10.332483291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2239122390747</t>
+    <t xml:space="preserve">10.3324823379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2239112854004</t>
   </si>
   <si>
     <t xml:space="preserve">10.097243309021</t>
@@ -2021,73 +2021,73 @@
     <t xml:space="preserve">10.0610523223877</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0791473388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1515302658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0563011169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8934412002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5496282577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3686742782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8258113861084</t>
+    <t xml:space="preserve">10.0791482925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1515293121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.056300163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8934421539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5496273040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3686752319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82581043243408</t>
   </si>
   <si>
     <t xml:space="preserve">9.77152633666992</t>
   </si>
   <si>
-    <t xml:space="preserve">9.699143409729</t>
+    <t xml:space="preserve">9.69914436340332</t>
   </si>
   <si>
     <t xml:space="preserve">9.51819038391113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7172384262085</t>
+    <t xml:space="preserve">9.71723937988281</t>
   </si>
   <si>
     <t xml:space="preserve">9.42771244049072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59057140350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3639230728149</t>
+    <t xml:space="preserve">9.59057235717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3639221191406</t>
   </si>
   <si>
     <t xml:space="preserve">11.9791660308838</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4677410125732</t>
+    <t xml:space="preserve">12.4677419662476</t>
   </si>
   <si>
     <t xml:space="preserve">12.3772659301758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3820171356201</t>
+    <t xml:space="preserve">11.3820180892944</t>
   </si>
   <si>
     <t xml:space="preserve">11.5629720687866</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6172580718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0924911499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6943922042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6267614364624</t>
+    <t xml:space="preserve">11.6172590255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0924921035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.694390296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62676239013672</t>
   </si>
   <si>
     <t xml:space="preserve">8.8034200668335</t>
@@ -2102,19 +2102,19 @@
     <t xml:space="preserve">7.0481653213501</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32864427566528</t>
+    <t xml:space="preserve">7.32864475250244</t>
   </si>
   <si>
     <t xml:space="preserve">7.24721479415894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18388032913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58673191070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65006542205811</t>
+    <t xml:space="preserve">7.1838812828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58673286437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65006589889526</t>
   </si>
   <si>
     <t xml:space="preserve">6.96673583984375</t>
@@ -2126,19 +2126,19 @@
     <t xml:space="preserve">7.16578531265259</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05721282958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28340578079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60912275314331</t>
+    <t xml:space="preserve">7.057213306427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28340530395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60912227630615</t>
   </si>
   <si>
     <t xml:space="preserve">7.76293420791626</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3419885635376</t>
+    <t xml:space="preserve">8.34198760986328</t>
   </si>
   <si>
     <t xml:space="preserve">8.04341316223145</t>
@@ -2147,22 +2147,22 @@
     <t xml:space="preserve">8.61341857910156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41436958312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2515115737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93008804321289</t>
+    <t xml:space="preserve">8.41436862945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25150966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93008899688721</t>
   </si>
   <si>
     <t xml:space="preserve">9.35533142089844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04770851135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26485443115234</t>
+    <t xml:space="preserve">9.04770946502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26485252380371</t>
   </si>
   <si>
     <t xml:space="preserve">9.50009441375732</t>
@@ -2174,13 +2174,13 @@
     <t xml:space="preserve">11.2191581726074</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9839200973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6582002639771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97057628631592</t>
+    <t xml:space="preserve">10.9839191436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6582021713257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97057437896729</t>
   </si>
   <si>
     <t xml:space="preserve">10.2058153152466</t>
@@ -2189,22 +2189,22 @@
     <t xml:space="preserve">9.84390735626221</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4591503143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9296321868896</t>
+    <t xml:space="preserve">10.4591512680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9296312332153</t>
   </si>
   <si>
     <t xml:space="preserve">10.7305822372437</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8210601806641</t>
+    <t xml:space="preserve">10.8210592269897</t>
   </si>
   <si>
     <t xml:space="preserve">12.0696439743042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.558219909668</t>
+    <t xml:space="preserve">12.5582189559937</t>
   </si>
   <si>
     <t xml:space="preserve">12.8477458953857</t>
@@ -2216,16 +2216,16 @@
     <t xml:space="preserve">12.757269859314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7934608459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4315509796143</t>
+    <t xml:space="preserve">12.7934598922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4315519332886</t>
   </si>
   <si>
     <t xml:space="preserve">12.594409942627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6486959457397</t>
+    <t xml:space="preserve">12.6486968994141</t>
   </si>
   <si>
     <t xml:space="preserve">12.7210779190063</t>
@@ -2237,25 +2237,25 @@
     <t xml:space="preserve">13.1553678512573</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0286998748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1191778182983</t>
+    <t xml:space="preserve">13.0287008285522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.119176864624</t>
   </si>
   <si>
     <t xml:space="preserve">12.9382238388062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0829877853394</t>
+    <t xml:space="preserve">13.082986831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.3725137710571</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3544178009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4534845352173</t>
+    <t xml:space="preserve">13.3544187545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4534873962402</t>
   </si>
   <si>
     <t xml:space="preserve">16.2496852874756</t>
@@ -2264,34 +2264,34 @@
     <t xml:space="preserve">16.2858753204346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3763542175293</t>
+    <t xml:space="preserve">16.3763523101807</t>
   </si>
   <si>
     <t xml:space="preserve">16.6477851867676</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8334884643555</t>
+    <t xml:space="preserve">15.8334903717041</t>
   </si>
   <si>
     <t xml:space="preserve">16.0687313079834</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8696823120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9239683151245</t>
+    <t xml:space="preserve">15.8696813583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9239664077759</t>
   </si>
   <si>
     <t xml:space="preserve">15.9058713912964</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8515853881836</t>
+    <t xml:space="preserve">15.8515872955322</t>
   </si>
   <si>
     <t xml:space="preserve">16.0144443511963</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7972984313965</t>
+    <t xml:space="preserve">15.7972965240479</t>
   </si>
   <si>
     <t xml:space="preserve">16.2677803039551</t>
@@ -2300,100 +2300,100 @@
     <t xml:space="preserve">16.0325374603271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.779203414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7249174118042</t>
+    <t xml:space="preserve">15.7792043685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7249193191528</t>
   </si>
   <si>
     <t xml:space="preserve">16.4125423431396</t>
   </si>
   <si>
-    <t xml:space="preserve">15.815393447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.942063331604</t>
+    <t xml:space="preserve">15.8153963088989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9420642852783</t>
   </si>
   <si>
     <t xml:space="preserve">15.6344404220581</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1049194335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9601564407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6887273788452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6163454055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8925275802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.652533531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3630094528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4896774291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.145866394043</t>
+    <t xml:space="preserve">16.104923248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9601583480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6887264251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6163463592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8925285339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6525344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3630084991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4896783828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1458644866943</t>
   </si>
   <si>
     <t xml:space="preserve">15.0372924804688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.743013381958</t>
+    <t xml:space="preserve">15.7430114746094</t>
   </si>
   <si>
     <t xml:space="preserve">14.8201465606689</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2906293869019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5887470245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7697010040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0230369567871</t>
+    <t xml:space="preserve">15.2906274795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5887489318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7696990966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0230350494385</t>
   </si>
   <si>
     <t xml:space="preserve">19.1359043121338</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2763729095459</t>
+    <t xml:space="preserve">18.2763710021973</t>
   </si>
   <si>
     <t xml:space="preserve">18.0411319732666</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4258861541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7335071563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2992191314697</t>
+    <t xml:space="preserve">17.4258880615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7335109710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2992210388184</t>
   </si>
   <si>
     <t xml:space="preserve">17.0458850860596</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0277900695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7020702362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0096950531006</t>
+    <t xml:space="preserve">17.0277881622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7020683288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.009693145752</t>
   </si>
   <si>
     <t xml:space="preserve">17.4077911376953</t>
@@ -2405,40 +2405,40 @@
     <t xml:space="preserve">18.1406555175781</t>
   </si>
   <si>
-    <t xml:space="preserve">17.96875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4982662200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9868431091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5930423736572</t>
+    <t xml:space="preserve">17.9687519073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4982681274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9868450164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5930404663086</t>
   </si>
   <si>
     <t xml:space="preserve">17.1544551849365</t>
   </si>
   <si>
-    <t xml:space="preserve">17.244930267334</t>
+    <t xml:space="preserve">17.2449321746826</t>
   </si>
   <si>
     <t xml:space="preserve">17.1182632446289</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8106441497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8287391662598</t>
+    <t xml:space="preserve">16.8106422424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8287372589111</t>
   </si>
   <si>
     <t xml:space="preserve">16.9735012054443</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9192161560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0639820098877</t>
+    <t xml:space="preserve">16.9192180633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0639801025391</t>
   </si>
   <si>
     <t xml:space="preserve">16.8468341827393</t>
@@ -2459,22 +2459,22 @@
     <t xml:space="preserve">18.3668479919434</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4573249816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6382789611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.728759765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9549522399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8644733428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6335277557373</t>
+    <t xml:space="preserve">18.4573268890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6382808685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7287578582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9549503326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8644714355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6335296630859</t>
   </si>
   <si>
     <t xml:space="preserve">19.6787662506104</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">19.5430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0454235076904</t>
+    <t xml:space="preserve">19.0454292297363</t>
   </si>
   <si>
     <t xml:space="preserve">19.0001888275146</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">18.3216114044189</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2311325073242</t>
+    <t xml:space="preserve">18.2311344146729</t>
   </si>
   <si>
     <t xml:space="preserve">19.0906658172607</t>
@@ -2504,19 +2504,19 @@
     <t xml:space="preserve">18.6835174560547</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0954170227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0049381256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5706520080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8239879608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6430339813232</t>
+    <t xml:space="preserve">18.0954189300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.004940032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.570650100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8239860534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6430320739746</t>
   </si>
   <si>
     <t xml:space="preserve">17.8058910369873</t>
@@ -2525,7 +2525,7 @@
     <t xml:space="preserve">19.2716178894043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1811428070068</t>
+    <t xml:space="preserve">19.1811447143555</t>
   </si>
   <si>
     <t xml:space="preserve">20.26686668396</t>
@@ -2540,76 +2540,76 @@
     <t xml:space="preserve">20.5835361480713</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3573436737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9049587249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7692451477051</t>
+    <t xml:space="preserve">20.3573455810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9049606323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7692432403564</t>
   </si>
   <si>
     <t xml:space="preserve">20.7192535400391</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9954357147217</t>
+    <t xml:space="preserve">19.9954376220703</t>
   </si>
   <si>
     <t xml:space="preserve">19.2263813018799</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4525737762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4073352813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6249351501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7877960205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4978122711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0859146118164</t>
+    <t xml:space="preserve">19.4525756835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4073371887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6249370574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7877941131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4978103637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0859127044678</t>
   </si>
   <si>
     <t xml:space="preserve">20.1311511993408</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8597221374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6740169525146</t>
+    <t xml:space="preserve">19.8597202301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.674015045166</t>
   </si>
   <si>
     <t xml:space="preserve">21.0359230041504</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8097305297852</t>
+    <t xml:space="preserve">20.8097267150879</t>
   </si>
   <si>
     <t xml:space="preserve">20.628776550293</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3121070861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4478244781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8821105957031</t>
+    <t xml:space="preserve">20.312105178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4478225708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8821125030518</t>
   </si>
   <si>
     <t xml:space="preserve">21.2802104949951</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3344974517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5878353118896</t>
+    <t xml:space="preserve">21.3344955444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.587833404541</t>
   </si>
   <si>
     <t xml:space="preserve">21.6602153778076</t>
@@ -2627,31 +2627,31 @@
     <t xml:space="preserve">23.9040470123291</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7821311950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8592643737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0040264129639</t>
+    <t xml:space="preserve">22.7821292877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8592624664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0040245056152</t>
   </si>
   <si>
     <t xml:space="preserve">22.2573642730713</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4745101928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1126022338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0583114624023</t>
+    <t xml:space="preserve">22.4745082855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1126003265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.058313369751</t>
   </si>
   <si>
     <t xml:space="preserve">22.6011772155762</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6373653411865</t>
+    <t xml:space="preserve">22.6373691558838</t>
   </si>
   <si>
     <t xml:space="preserve">22.420223236084</t>
@@ -2666,28 +2666,28 @@
     <t xml:space="preserve">21.2621154785156</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0945053100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.583080291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0354652404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.017370223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3611850738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2707061767578</t>
+    <t xml:space="preserve">22.09450340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5830783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0354671478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0173721313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3611831665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2707080841064</t>
   </si>
   <si>
     <t xml:space="preserve">25.0440578460693</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7726268768311</t>
+    <t xml:space="preserve">24.7726249694824</t>
   </si>
   <si>
     <t xml:space="preserve">24.9716758728027</t>
@@ -2696,43 +2696,43 @@
     <t xml:space="preserve">25.0621528625488</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9126396179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2383556365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6765747070312</t>
+    <t xml:space="preserve">25.9126377105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.238353729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.676570892334</t>
   </si>
   <si>
     <t xml:space="preserve">26.7130928039551</t>
   </si>
   <si>
-    <t xml:space="preserve">26.585277557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.658317565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8226451873779</t>
+    <t xml:space="preserve">26.5852794647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6583156585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8226470947266</t>
   </si>
   <si>
     <t xml:space="preserve">26.95046043396</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5712718963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6260471343994</t>
+    <t xml:space="preserve">27.5712699890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.626049041748</t>
   </si>
   <si>
     <t xml:space="preserve">28.064266204834</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2833728790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8171405792236</t>
+    <t xml:space="preserve">28.283374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8171443939209</t>
   </si>
   <si>
     <t xml:space="preserve">29.5980319976807</t>
@@ -2747,16 +2747,16 @@
     <t xml:space="preserve">29.652811050415</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1092872619629</t>
+    <t xml:space="preserve">30.1092891693115</t>
   </si>
   <si>
     <t xml:space="preserve">29.9632129669189</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4014320373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2188415527344</t>
+    <t xml:space="preserve">30.4014358520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2188396453857</t>
   </si>
   <si>
     <t xml:space="preserve">31.2961292266846</t>
@@ -2765,7 +2765,7 @@
     <t xml:space="preserve">30.8213920593262</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1683177947998</t>
+    <t xml:space="preserve">31.1683158874512</t>
   </si>
   <si>
     <t xml:space="preserve">30.2371006011963</t>
@@ -2774,22 +2774,22 @@
     <t xml:space="preserve">29.4154415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8536605834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.178071975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1458072662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7075881958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0545101165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8664169311523</t>
+    <t xml:space="preserve">29.8536624908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1780700683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.145809173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7075862884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0545082092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8664131164551</t>
   </si>
   <si>
     <t xml:space="preserve">34.5462532043457</t>
@@ -2798,16 +2798,16 @@
     <t xml:space="preserve">34.0532569885254</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0855293273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7245903015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6880798339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5785179138184</t>
+    <t xml:space="preserve">33.0855255126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7245941162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6880722045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5785217285156</t>
   </si>
   <si>
     <t xml:space="preserve">33.4872283935547</t>
@@ -2819,40 +2819,40 @@
     <t xml:space="preserve">33.1403007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2863731384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2273445129395</t>
+    <t xml:space="preserve">33.286376953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2273483276367</t>
   </si>
   <si>
     <t xml:space="preserve">32.8846740722656</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7568626403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6473083496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0307502746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7751235961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4099349975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6655616760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6923294067383</t>
+    <t xml:space="preserve">32.7568588256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6473045349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0307464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7751197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4099388122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6655654907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.692325592041</t>
   </si>
   <si>
     <t xml:space="preserve">35.605281829834</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2400970458984</t>
+    <t xml:space="preserve">35.2401008605957</t>
   </si>
   <si>
     <t xml:space="preserve">35.8791694641113</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">35.5870246887207</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7878761291504</t>
+    <t xml:space="preserve">35.7878723144531</t>
   </si>
   <si>
     <t xml:space="preserve">36.0435028076172</t>
@@ -2879,22 +2879,22 @@
     <t xml:space="preserve">38.9101829528809</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4354438781738</t>
+    <t xml:space="preserve">38.4354476928711</t>
   </si>
   <si>
     <t xml:space="preserve">39.4944725036621</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3849182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.220588684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1292915344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1980781555176</t>
+    <t xml:space="preserve">39.3849220275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2205924987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1292953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1980743408203</t>
   </si>
   <si>
     <t xml:space="preserve">37.6137886047363</t>
@@ -2903,7 +2903,7 @@
     <t xml:space="preserve">37.2486038208008</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0660095214844</t>
+    <t xml:space="preserve">37.0660133361816</t>
   </si>
   <si>
     <t xml:space="preserve">37.2668609619141</t>
@@ -2915,10 +2915,10 @@
     <t xml:space="preserve">37.2120819091797</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5590057373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0154876708984</t>
+    <t xml:space="preserve">37.559009552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0154838562012</t>
   </si>
   <si>
     <t xml:space="preserve">37.6503067016602</t>
@@ -2933,16 +2933,16 @@
     <t xml:space="preserve">32.9942283630371</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3594093322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0490074157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7836265563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3819274902344</t>
+    <t xml:space="preserve">33.3594131469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0490112304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7836227416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3819236755371</t>
   </si>
   <si>
     <t xml:space="preserve">34.893180847168</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">32.9577102661133</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6332969665527</t>
+    <t xml:space="preserve">33.63330078125</t>
   </si>
   <si>
     <t xml:space="preserve">35.513988494873</t>
@@ -2960,16 +2960,16 @@
     <t xml:space="preserve">36.4817199707031</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3173866271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6095352172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7781143188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2711143493652</t>
+    <t xml:space="preserve">36.3173904418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6095314025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7781181335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.271110534668</t>
   </si>
   <si>
     <t xml:space="preserve">39.2023315429688</t>
@@ -2978,22 +2978,22 @@
     <t xml:space="preserve">36.7190895080566</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8426513671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9662132263184</t>
+    <t xml:space="preserve">35.8426475524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9662170410156</t>
   </si>
   <si>
     <t xml:space="preserve">35.1488075256348</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4409523010254</t>
+    <t xml:space="preserve">35.4409484863281</t>
   </si>
   <si>
     <t xml:space="preserve">37.8876724243164</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5267448425293</t>
+    <t xml:space="preserve">38.526741027832</t>
   </si>
   <si>
     <t xml:space="preserve">38.8006324768066</t>
@@ -3002,22 +3002,22 @@
     <t xml:space="preserve">37.6685600280762</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4226875305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2583618164062</t>
+    <t xml:space="preserve">35.4226913452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.258358001709</t>
   </si>
   <si>
     <t xml:space="preserve">34.9114379882812</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3636627197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8341484069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5967826843262</t>
+    <t xml:space="preserve">34.3636589050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8341522216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5967788696289</t>
   </si>
   <si>
     <t xml:space="preserve">35.3313980102539</t>
@@ -3035,43 +3035,43 @@
     <t xml:space="preserve">34.7105865478516</t>
   </si>
   <si>
-    <t xml:space="preserve">34.345401763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0715141296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1950798034668</t>
+    <t xml:space="preserve">34.3454055786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0715179443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1950759887695</t>
   </si>
   <si>
     <t xml:space="preserve">33.6150360107422</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9254455566406</t>
+    <t xml:space="preserve">33.9254417419434</t>
   </si>
   <si>
     <t xml:space="preserve">33.9436988830566</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6192855834961</t>
+    <t xml:space="preserve">34.6192893981934</t>
   </si>
   <si>
     <t xml:space="preserve">34.5827751159668</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7288475036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0027351379395</t>
+    <t xml:space="preserve">34.7288436889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0027313232422</t>
   </si>
   <si>
     <t xml:space="preserve">34.8384017944336</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8749160766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5377464294434</t>
+    <t xml:space="preserve">34.8749198913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5377540588379</t>
   </si>
   <si>
     <t xml:space="preserve">32.1725692749023</t>
@@ -3083,22 +3083,22 @@
     <t xml:space="preserve">29.4519577026367</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8901786804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1640682220459</t>
+    <t xml:space="preserve">29.8901805877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1640663146973</t>
   </si>
   <si>
     <t xml:space="preserve">28.4294490814209</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1007843017578</t>
+    <t xml:space="preserve">28.1007862091064</t>
   </si>
   <si>
     <t xml:space="preserve">27.6808242797852</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9954833984375</t>
+    <t xml:space="preserve">28.9954814910889</t>
   </si>
   <si>
     <t xml:space="preserve">29.2693710327148</t>
@@ -3110,25 +3110,25 @@
     <t xml:space="preserve">26.9687213897705</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8956832885742</t>
+    <t xml:space="preserve">26.8956813812256</t>
   </si>
   <si>
     <t xml:space="preserve">27.8451557159424</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9729690551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6668186187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1232967376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9224472045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6077861785889</t>
+    <t xml:space="preserve">27.9729709625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6668167114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1232948303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9224452972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6077880859375</t>
   </si>
   <si>
     <t xml:space="preserve">27.7538604736328</t>
@@ -3137,16 +3137,16 @@
     <t xml:space="preserve">26.3479099273682</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5445079803467</t>
+    <t xml:space="preserve">25.544506072998</t>
   </si>
   <si>
     <t xml:space="preserve">26.7496089935303</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7861309051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5670185089111</t>
+    <t xml:space="preserve">26.7861289978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5670204162598</t>
   </si>
   <si>
     <t xml:space="preserve">27.9547119140625</t>
@@ -3155,7 +3155,7 @@
     <t xml:space="preserve">27.4251976013184</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4799728393555</t>
+    <t xml:space="preserve">27.4799747467041</t>
   </si>
   <si>
     <t xml:space="preserve">27.1147937774658</t>
@@ -3170,40 +3170,40 @@
     <t xml:space="preserve">27.9912300109863</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6948318481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4434566497803</t>
+    <t xml:space="preserve">26.6948337554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4434547424316</t>
   </si>
   <si>
     <t xml:space="preserve">26.3113918304443</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5542640686035</t>
+    <t xml:space="preserve">23.5542621612549</t>
   </si>
   <si>
     <t xml:space="preserve">24.7045879364014</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0977840423584</t>
+    <t xml:space="preserve">23.097785949707</t>
   </si>
   <si>
     <t xml:space="preserve">22.0022392272949</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7466106414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7423572540283</t>
+    <t xml:space="preserve">21.7466125488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.742359161377</t>
   </si>
   <si>
     <t xml:space="preserve">22.6047897338867</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8744239807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5134944915771</t>
+    <t xml:space="preserve">21.8744258880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5134925842285</t>
   </si>
   <si>
     <t xml:space="preserve">23.1525630950928</t>
@@ -3215,7 +3215,7 @@
     <t xml:space="preserve">24.5402545928955</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6680679321289</t>
+    <t xml:space="preserve">24.6680698394775</t>
   </si>
   <si>
     <t xml:space="preserve">24.8689193725586</t>
@@ -3224,10 +3224,10 @@
     <t xml:space="preserve">24.4489612579346</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2341022491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5585136413574</t>
+    <t xml:space="preserve">25.2341041564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5585174560547</t>
   </si>
   <si>
     <t xml:space="preserve">24.0290012359619</t>
@@ -3239,76 +3239,76 @@
     <t xml:space="preserve">24.0472602844238</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3984336853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4166946411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2115936279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0837783813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8098907470703</t>
+    <t xml:space="preserve">25.3984355926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4166927337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2115917205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.083776473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8098926544189</t>
   </si>
   <si>
     <t xml:space="preserve">23.3351535797119</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4221973419189</t>
+    <t xml:space="preserve">22.4221992492676</t>
   </si>
   <si>
     <t xml:space="preserve">22.7326030731201</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6778259277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2761249542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9109439849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2213478088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8379096984863</t>
+    <t xml:space="preserve">22.677827835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2761268615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9109420776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2213459014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8379077911377</t>
   </si>
   <si>
     <t xml:space="preserve">22.0935344696045</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8238983154297</t>
+    <t xml:space="preserve">22.8239002227783</t>
   </si>
   <si>
     <t xml:space="preserve">21.5457611083984</t>
   </si>
   <si>
-    <t xml:space="preserve">21.07102394104</t>
+    <t xml:space="preserve">21.0710258483887</t>
   </si>
   <si>
     <t xml:space="preserve">21.9657211303711</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1988353729248</t>
+    <t xml:space="preserve">21.1988372802734</t>
   </si>
   <si>
     <t xml:space="preserve">21.2718734741211</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8884315490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6875820159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0850315093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3729267120361</t>
+    <t xml:space="preserve">20.8884296417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6875839233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0850296020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3729228973389</t>
   </si>
   <si>
     <t xml:space="preserve">19.8659229278564</t>
@@ -3317,7 +3317,7 @@
     <t xml:space="preserve">19.957218170166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9024410247803</t>
+    <t xml:space="preserve">19.9024391174316</t>
   </si>
   <si>
     <t xml:space="preserve">20.2493629455566</t>
@@ -3326,10 +3326,10 @@
     <t xml:space="preserve">20.9614677429199</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8519134521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7241020202637</t>
+    <t xml:space="preserve">20.8519153594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.724100112915</t>
   </si>
   <si>
     <t xml:space="preserve">21.0162467956543</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">20.3954372406006</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5232486724854</t>
+    <t xml:space="preserve">20.523250579834</t>
   </si>
   <si>
     <t xml:space="preserve">20.6693229675293</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">22.1300525665283</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1933326721191</t>
+    <t xml:space="preserve">24.1933345794678</t>
   </si>
   <si>
     <t xml:space="preserve">23.6455612182617</t>
@@ -3359,7 +3359,7 @@
     <t xml:space="preserve">23.5177478790283</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7368564605713</t>
+    <t xml:space="preserve">23.7368545532227</t>
   </si>
   <si>
     <t xml:space="preserve">23.0533809661865</t>
@@ -3368,10 +3368,10 @@
     <t xml:space="preserve">22.9240760803223</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7393550872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8711566925049</t>
+    <t xml:space="preserve">22.7393531799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8711585998535</t>
   </si>
   <si>
     <t xml:space="preserve">20.7443466186523</t>
@@ -3395,19 +3395,19 @@
     <t xml:space="preserve">21.3539333343506</t>
   </si>
   <si>
-    <t xml:space="preserve">21.316987991333</t>
+    <t xml:space="preserve">21.3169898986816</t>
   </si>
   <si>
     <t xml:space="preserve">21.7603225708008</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6494884490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4278240203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5571269989014</t>
+    <t xml:space="preserve">21.6494903564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4278221130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.55712890625</t>
   </si>
   <si>
     <t xml:space="preserve">21.7972679138184</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">20.9475440979004</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0374088287354</t>
+    <t xml:space="preserve">22.0374069213867</t>
   </si>
   <si>
     <t xml:space="preserve">22.4992141723633</t>
@@ -3437,22 +3437,22 @@
     <t xml:space="preserve">21.6679611206055</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4647655487061</t>
+    <t xml:space="preserve">21.4647674560547</t>
   </si>
   <si>
     <t xml:space="preserve">20.8182392120361</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1532363891602</t>
+    <t xml:space="preserve">20.1532344818115</t>
   </si>
   <si>
     <t xml:space="preserve">20.2271251678467</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4487934112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3908786773682</t>
+    <t xml:space="preserve">20.4487915039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3908767700195</t>
   </si>
   <si>
     <t xml:space="preserve">21.0029602050781</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">21.2985153198242</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5017127990723</t>
+    <t xml:space="preserve">21.5017108917236</t>
   </si>
   <si>
     <t xml:space="preserve">21.7787952423096</t>
@@ -3506,16 +3506,16 @@
     <t xml:space="preserve">20.0054588317871</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1162910461426</t>
+    <t xml:space="preserve">20.1162929534912</t>
   </si>
   <si>
     <t xml:space="preserve">20.0978202819824</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9500408172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.74684715271</t>
+    <t xml:space="preserve">19.9500427246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7468452453613</t>
   </si>
   <si>
     <t xml:space="preserve">19.5436515808105</t>
@@ -3527,16 +3527,16 @@
     <t xml:space="preserve">18.472261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1926803588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5830974578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2413578033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0566349029541</t>
+    <t xml:space="preserve">19.1926784515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5830955505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2413558959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0566329956055</t>
   </si>
   <si>
     <t xml:space="preserve">17.7426052093506</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">17.4562854766846</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6225357055664</t>
+    <t xml:space="preserve">17.622537612915</t>
   </si>
   <si>
     <t xml:space="preserve">16.6989231109619</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">16.9852447509766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.280797958374</t>
+    <t xml:space="preserve">17.2807998657227</t>
   </si>
   <si>
     <t xml:space="preserve">17.0037155151367</t>
@@ -3572,58 +3572,58 @@
     <t xml:space="preserve">17.6317729949951</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8164958953857</t>
+    <t xml:space="preserve">17.8164978027344</t>
   </si>
   <si>
     <t xml:space="preserve">17.5855941772461</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5024681091309</t>
+    <t xml:space="preserve">17.5024662017822</t>
   </si>
   <si>
     <t xml:space="preserve">17.0683689117432</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2346210479736</t>
+    <t xml:space="preserve">17.234619140625</t>
   </si>
   <si>
     <t xml:space="preserve">17.2530918121338</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9390621185303</t>
+    <t xml:space="preserve">16.9390640258789</t>
   </si>
   <si>
     <t xml:space="preserve">16.8005218505859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8836479187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4285793304443</t>
+    <t xml:space="preserve">16.8836460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4285774230957</t>
   </si>
   <si>
     <t xml:space="preserve">17.7056617736816</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8442039489746</t>
+    <t xml:space="preserve">17.844202041626</t>
   </si>
   <si>
     <t xml:space="preserve">17.7333698272705</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3429546356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4697647094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5805969238281</t>
+    <t xml:space="preserve">18.3429565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4697608947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5805988311768</t>
   </si>
   <si>
     <t xml:space="preserve">19.3589286804199</t>
   </si>
   <si>
-    <t xml:space="preserve">19.044900894165</t>
+    <t xml:space="preserve">19.0449028015137</t>
   </si>
   <si>
     <t xml:space="preserve">18.7493438720703</t>
@@ -3638,13 +3638,13 @@
     <t xml:space="preserve">18.4907341003418</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0079574584961</t>
+    <t xml:space="preserve">19.0079555511475</t>
   </si>
   <si>
     <t xml:space="preserve">20.0239295959473</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8392066955566</t>
+    <t xml:space="preserve">19.8392086029053</t>
   </si>
   <si>
     <t xml:space="preserve">20.8736553192139</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">21.9081001281738</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3329620361328</t>
+    <t xml:space="preserve">22.3329639434814</t>
   </si>
   <si>
     <t xml:space="preserve">20.9105987548828</t>
@@ -3662,40 +3662,40 @@
     <t xml:space="preserve">20.5226802825928</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3354625701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2431011199951</t>
+    <t xml:space="preserve">21.3354606628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2430992126465</t>
   </si>
   <si>
     <t xml:space="preserve">21.9265727996826</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7418518066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2800445556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4093494415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8526859283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1507396697998</t>
+    <t xml:space="preserve">21.7418537139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2800464630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.409351348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8526840209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1507377624512</t>
   </si>
   <si>
     <t xml:space="preserve">21.0583782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3933753967285</t>
+    <t xml:space="preserve">20.3933773040771</t>
   </si>
   <si>
     <t xml:space="preserve">20.2455978393555</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9315700531006</t>
+    <t xml:space="preserve">19.931568145752</t>
   </si>
   <si>
     <t xml:space="preserve">19.9685134887695</t>
@@ -3731,13 +3731,13 @@
     <t xml:space="preserve">23.9031047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">23.792272567749</t>
+    <t xml:space="preserve">23.7922744750977</t>
   </si>
   <si>
     <t xml:space="preserve">23.127269744873</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7553272247314</t>
+    <t xml:space="preserve">23.7553253173828</t>
   </si>
   <si>
     <t xml:space="preserve">23.8846340179443</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">23.4782428741455</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1087989807129</t>
+    <t xml:space="preserve">23.1088008880615</t>
   </si>
   <si>
     <t xml:space="preserve">22.9979629516602</t>
@@ -3770,7 +3770,7 @@
     <t xml:space="preserve">23.5151882171631</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8686599731445</t>
+    <t xml:space="preserve">22.8686580657959</t>
   </si>
   <si>
     <t xml:space="preserve">23.4597702026367</t>
@@ -3779,7 +3779,7 @@
     <t xml:space="preserve">22.9056015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8132419586182</t>
+    <t xml:space="preserve">22.8132438659668</t>
   </si>
   <si>
     <t xml:space="preserve">22.6285190582275</t>
@@ -3794,7 +3794,7 @@
     <t xml:space="preserve">22.2036571502686</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0004615783691</t>
+    <t xml:space="preserve">22.0004634857178</t>
   </si>
   <si>
     <t xml:space="preserve">22.0558776855469</t>
@@ -3803,31 +3803,31 @@
     <t xml:space="preserve">22.2590751647949</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8342113494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0928230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2406005859375</t>
+    <t xml:space="preserve">21.8342132568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0928249359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2406024932861</t>
   </si>
   <si>
     <t xml:space="preserve">21.2615718841553</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3404579162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6569843292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1187915802002</t>
+    <t xml:space="preserve">19.3404560089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.656982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1187896728516</t>
   </si>
   <si>
     <t xml:space="preserve">18.5646228790283</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6754570007324</t>
+    <t xml:space="preserve">18.6754550933838</t>
   </si>
   <si>
     <t xml:space="preserve">19.0264301300049</t>
@@ -3839,19 +3839,19 @@
     <t xml:space="preserve">18.509204864502</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8232345581055</t>
+    <t xml:space="preserve">18.8232326507568</t>
   </si>
   <si>
     <t xml:space="preserve">18.5461502075195</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7123985290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7308731079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6200370788574</t>
+    <t xml:space="preserve">18.7124004364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7308750152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6200389862061</t>
   </si>
   <si>
     <t xml:space="preserve">18.4445514678955</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">18.3614273071289</t>
   </si>
   <si>
-    <t xml:space="preserve">17.798023223877</t>
+    <t xml:space="preserve">17.7980251312256</t>
   </si>
   <si>
     <t xml:space="preserve">17.5486469268799</t>
@@ -3869,22 +3869,22 @@
     <t xml:space="preserve">17.1422576904297</t>
   </si>
   <si>
-    <t xml:space="preserve">16.948299407959</t>
+    <t xml:space="preserve">16.9483013153076</t>
   </si>
   <si>
     <t xml:space="preserve">16.9205894470215</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8651752471924</t>
+    <t xml:space="preserve">16.8651733398438</t>
   </si>
   <si>
     <t xml:space="preserve">16.5696182250977</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8559379577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1145496368408</t>
+    <t xml:space="preserve">16.8559398651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1145515441895</t>
   </si>
   <si>
     <t xml:space="preserve">16.7451038360596</t>
@@ -3896,13 +3896,13 @@
     <t xml:space="preserve">16.8744106292725</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7912864685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.846700668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.809757232666</t>
+    <t xml:space="preserve">16.7912845611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8467025756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8097591400146</t>
   </si>
   <si>
     <t xml:space="preserve">16.5880889892578</t>
@@ -3914,43 +3914,43 @@
     <t xml:space="preserve">16.7635765075684</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7728137969971</t>
+    <t xml:space="preserve">16.7728118896484</t>
   </si>
   <si>
     <t xml:space="preserve">16.5234375</t>
   </si>
   <si>
-    <t xml:space="preserve">15.710657119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0708675384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0893402099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0062160491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0523929595947</t>
+    <t xml:space="preserve">15.7106580734253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0708656311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0893383026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0062141418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0523948669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6896877288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4710865020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.632661819458</t>
   </si>
   <si>
     <t xml:space="preserve">16.6896858215332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4710884094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.632661819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6896877288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6611747741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5946445465088</t>
+    <t xml:space="preserve">16.6611766815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5946426391602</t>
   </si>
   <si>
     <t xml:space="preserve">17.2124290466309</t>
@@ -3959,10 +3959,10 @@
     <t xml:space="preserve">17.5830993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9442653656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8207092285156</t>
+    <t xml:space="preserve">17.944263458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.820707321167</t>
   </si>
   <si>
     <t xml:space="preserve">17.8302135467529</t>
@@ -3974,7 +3974,7 @@
     <t xml:space="preserve">16.9938259124756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5661315917969</t>
+    <t xml:space="preserve">16.5661296844482</t>
   </si>
   <si>
     <t xml:space="preserve">16.2809982299805</t>
@@ -3983,13 +3983,13 @@
     <t xml:space="preserve">16.204963684082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0053730010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.58717918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.786771774292</t>
+    <t xml:space="preserve">16.00537109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5871801376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7867727279663</t>
   </si>
   <si>
     <t xml:space="preserve">15.5681705474854</t>
@@ -4007,16 +4007,16 @@
     <t xml:space="preserve">15.3305606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6251983642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4541187286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8723125457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9958686828613</t>
+    <t xml:space="preserve">15.6251974105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4541177749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8723115921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9958667755127</t>
   </si>
   <si>
     <t xml:space="preserve">16.0623989105225</t>
@@ -4025,19 +4025,19 @@
     <t xml:space="preserve">15.7012319564819</t>
   </si>
   <si>
-    <t xml:space="preserve">15.777268409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8247880935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7487545013428</t>
+    <t xml:space="preserve">15.7772674560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8247900009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7487535476685</t>
   </si>
   <si>
     <t xml:space="preserve">15.7392492294312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9388418197632</t>
+    <t xml:space="preserve">15.9388427734375</t>
   </si>
   <si>
     <t xml:space="preserve">16.1859569549561</t>
@@ -4046,7 +4046,7 @@
     <t xml:space="preserve">16.1574420928955</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8913202285767</t>
+    <t xml:space="preserve">15.8913192749023</t>
   </si>
   <si>
     <t xml:space="preserve">16.9177932739258</t>
@@ -4058,13 +4058,13 @@
     <t xml:space="preserve">17.0223407745361</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1649074554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0603580474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6231555938721</t>
+    <t xml:space="preserve">17.1649055480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.060359954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6231575012207</t>
   </si>
   <si>
     <t xml:space="preserve">16.7277050018311</t>
@@ -4079,7 +4079,7 @@
     <t xml:space="preserve">16.3000068664551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4995994567871</t>
+    <t xml:space="preserve">16.4996013641357</t>
   </si>
   <si>
     <t xml:space="preserve">16.509105682373</t>
@@ -4106,16 +4106,16 @@
     <t xml:space="preserve">17.4215240478516</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3074703216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2599506378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8628072738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.881814956665</t>
+    <t xml:space="preserve">17.3074722290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2599487304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8628063201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8818140029907</t>
   </si>
   <si>
     <t xml:space="preserve">16.4235649108887</t>
@@ -4127,16 +4127,16 @@
     <t xml:space="preserve">16.1479377746582</t>
   </si>
   <si>
-    <t xml:space="preserve">15.910327911377</t>
+    <t xml:space="preserve">15.9103288650513</t>
   </si>
   <si>
     <t xml:space="preserve">16.2429828643799</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8533029556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8437976837158</t>
+    <t xml:space="preserve">15.8533020019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8437967300415</t>
   </si>
   <si>
     <t xml:space="preserve">14.7793073654175</t>
@@ -4151,10 +4151,10 @@
     <t xml:space="preserve">14.4466543197632</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7222805023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6917276382446</t>
+    <t xml:space="preserve">14.7222814559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6917285919189</t>
   </si>
   <si>
     <t xml:space="preserve">15.4731273651123</t>
@@ -4166,7 +4166,7 @@
     <t xml:space="preserve">15.4921350479126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0929517745972</t>
+    <t xml:space="preserve">15.0929527282715</t>
   </si>
   <si>
     <t xml:space="preserve">15.4446144104004</t>
@@ -4196,7 +4196,7 @@
     <t xml:space="preserve">14.4846715927124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.931378364563</t>
+    <t xml:space="preserve">14.9313774108887</t>
   </si>
   <si>
     <t xml:space="preserve">14.9218730926514</t>
@@ -4211,37 +4211,37 @@
     <t xml:space="preserve">14.731785774231</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0074119567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7677640914917</t>
+    <t xml:space="preserve">15.0074129104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7677631378174</t>
   </si>
   <si>
     <t xml:space="preserve">16.1954612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5566272735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1289291381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0528926849365</t>
+    <t xml:space="preserve">16.5566253662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.128927230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0528945922852</t>
   </si>
   <si>
     <t xml:space="preserve">16.3570346832275</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4330711364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7467136383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3665370941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3950519561768</t>
+    <t xml:space="preserve">16.433069229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7467155456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3665390014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3950500488281</t>
   </si>
   <si>
     <t xml:space="preserve">16.4805908203125</t>
@@ -4256,10 +4256,10 @@
     <t xml:space="preserve">16.3285217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6136512756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6991920471191</t>
+    <t xml:space="preserve">16.6136531829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6991901397705</t>
   </si>
   <si>
     <t xml:space="preserve">16.5756359100342</t>
@@ -4268,22 +4268,22 @@
     <t xml:space="preserve">18.5240325927734</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7046146392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.647590637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.198844909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4839763641357</t>
+    <t xml:space="preserve">18.7046165466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6475887298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1988430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4839744567871</t>
   </si>
   <si>
     <t xml:space="preserve">19.5029830932617</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4649658203125</t>
+    <t xml:space="preserve">19.4649639129639</t>
   </si>
   <si>
     <t xml:space="preserve">19.2938861846924</t>
@@ -4292,10 +4292,10 @@
     <t xml:space="preserve">19.1037998199463</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2748775482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0277633666992</t>
+    <t xml:space="preserve">19.2748794555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0277652740479</t>
   </si>
   <si>
     <t xml:space="preserve">18.0868320465088</t>
@@ -4322,16 +4322,16 @@
     <t xml:space="preserve">17.9062480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7541770935059</t>
+    <t xml:space="preserve">17.7541790008545</t>
   </si>
   <si>
     <t xml:space="preserve">18.1818752288818</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9157524108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2103881835938</t>
+    <t xml:space="preserve">17.9157543182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2103862762451</t>
   </si>
   <si>
     <t xml:space="preserve">18.343448638916</t>
@@ -4346,16 +4346,16 @@
     <t xml:space="preserve">18.6570930480957</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5810565948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4289894104004</t>
+    <t xml:space="preserve">18.5810585021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4289875030518</t>
   </si>
   <si>
     <t xml:space="preserve">18.1913795471191</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0488128662109</t>
+    <t xml:space="preserve">18.0488147735596</t>
   </si>
   <si>
     <t xml:space="preserve">18.020299911499</t>
@@ -4373,7 +4373,7 @@
     <t xml:space="preserve">17.9632740020752</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0678234100342</t>
+    <t xml:space="preserve">18.0678215026855</t>
   </si>
   <si>
     <t xml:space="preserve">18.1723709106445</t>
@@ -4403,13 +4403,13 @@
     <t xml:space="preserve">17.8112030029297</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5165691375732</t>
+    <t xml:space="preserve">17.5165672302246</t>
   </si>
   <si>
     <t xml:space="preserve">17.5450801849365</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3169746398926</t>
+    <t xml:space="preserve">17.3169765472412</t>
   </si>
   <si>
     <t xml:space="preserve">17.3264808654785</t>
@@ -4430,10 +4430,10 @@
     <t xml:space="preserve">17.5545845031738</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7636814117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8872375488281</t>
+    <t xml:space="preserve">17.7636833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8872394561768</t>
   </si>
   <si>
     <t xml:space="preserve">18.1533622741699</t>
@@ -4442,19 +4442,19 @@
     <t xml:space="preserve">18.1628665924072</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3549938201904</t>
+    <t xml:space="preserve">17.3549957275391</t>
   </si>
   <si>
     <t xml:space="preserve">17.4690456390381</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4405326843262</t>
+    <t xml:space="preserve">17.4405345916748</t>
   </si>
   <si>
     <t xml:space="preserve">17.1078796386719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0413513183594</t>
+    <t xml:space="preserve">17.0413494110107</t>
   </si>
   <si>
     <t xml:space="preserve">16.9368019104004</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">16.4615821838379</t>
   </si>
   <si>
-    <t xml:space="preserve">16.309513092041</t>
+    <t xml:space="preserve">16.3095111846924</t>
   </si>
   <si>
     <t xml:space="preserve">17.0033321380615</t>
@@ -4490,7 +4490,7 @@
     <t xml:space="preserve">17.6211185455322</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0107955932617</t>
+    <t xml:space="preserve">18.0107975006104</t>
   </si>
   <si>
     <t xml:space="preserve">17.7826900482178</t>
@@ -4505,7 +4505,7 @@
     <t xml:space="preserve">17.5355777740479</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0012912750244</t>
+    <t xml:space="preserve">18.001293182373</t>
   </si>
   <si>
     <t xml:space="preserve">18.2674140930176</t>
@@ -70580,7 +70580,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6496064815</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>146053</v>
@@ -70601,6 +70601,32 @@
         <v>1777</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6910416667</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>129995</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>14.9300003051758</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>14.8599996566772</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>14.8999996185303</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>14.8999996185303</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1766</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TNXT.MI.xlsx
+++ b/data/TNXT.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">2.65150952339172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59350872039795</t>
+    <t xml:space="preserve">2.59350848197937</t>
   </si>
   <si>
     <t xml:space="preserve">2.5355064868927</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">2.52556347846985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48579096794128</t>
+    <t xml:space="preserve">2.48579072952271</t>
   </si>
   <si>
     <t xml:space="preserve">2.52722072601318</t>
@@ -65,82 +65,82 @@
     <t xml:space="preserve">2.48744821548462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47087574005127</t>
+    <t xml:space="preserve">2.47087597846985</t>
   </si>
   <si>
     <t xml:space="preserve">2.46921873092651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54047846794128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49739074707031</t>
+    <t xml:space="preserve">2.54047870635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49739122390747</t>
   </si>
   <si>
     <t xml:space="preserve">2.47916197776794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44436097145081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39464449882507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34161424636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36150097846985</t>
+    <t xml:space="preserve">2.44436049461365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39464497566223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34161496162415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36150121688843</t>
   </si>
   <si>
     <t xml:space="preserve">2.55207872390747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58522295951843</t>
+    <t xml:space="preserve">2.58522272109985</t>
   </si>
   <si>
     <t xml:space="preserve">2.6100800037384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56865072250366</t>
+    <t xml:space="preserve">2.56865048408508</t>
   </si>
   <si>
     <t xml:space="preserve">2.63659477233887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68962502479553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73436951637268</t>
+    <t xml:space="preserve">2.68962526321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73436975479126</t>
   </si>
   <si>
     <t xml:space="preserve">2.72608327865601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77579951286316</t>
+    <t xml:space="preserve">2.77579975128174</t>
   </si>
   <si>
     <t xml:space="preserve">2.58025097846985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5620219707489</t>
+    <t xml:space="preserve">2.56202220916748</t>
   </si>
   <si>
     <t xml:space="preserve">2.66808176040649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62830877304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64322376251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60842227935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66642451286316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65316653251648</t>
+    <t xml:space="preserve">2.62830901145935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64322328567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60842251777649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66642427444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65316700935364</t>
   </si>
   <si>
     <t xml:space="preserve">2.62665200233459</t>
@@ -149,10 +149,10 @@
     <t xml:space="preserve">2.69293975830078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82551574707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81722950935364</t>
+    <t xml:space="preserve">2.82551550865173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81722927093506</t>
   </si>
   <si>
     <t xml:space="preserve">2.90008950233459</t>
@@ -161,22 +161,22 @@
     <t xml:space="preserve">2.85865950584412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89843225479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88351702690125</t>
+    <t xml:space="preserve">2.89843249320984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8835175037384</t>
   </si>
   <si>
     <t xml:space="preserve">2.87523102760315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86694550514221</t>
+    <t xml:space="preserve">2.86694502830505</t>
   </si>
   <si>
     <t xml:space="preserve">2.81888675689697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82054424285889</t>
+    <t xml:space="preserve">2.82054400444031</t>
   </si>
   <si>
     <t xml:space="preserve">2.85368776321411</t>
@@ -185,19 +185,19 @@
     <t xml:space="preserve">2.79237151145935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8570020198822</t>
+    <t xml:space="preserve">2.85700225830078</t>
   </si>
   <si>
     <t xml:space="preserve">2.90671801567078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8288300037384</t>
+    <t xml:space="preserve">2.82882976531982</t>
   </si>
   <si>
     <t xml:space="preserve">2.85037350654602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90837502479553</t>
+    <t xml:space="preserve">2.90837526321411</t>
   </si>
   <si>
     <t xml:space="preserve">2.96306300163269</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">2.95797729492188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8816967010498</t>
+    <t xml:space="preserve">2.88169693946838</t>
   </si>
   <si>
     <t xml:space="preserve">2.89017271995544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86474585533142</t>
+    <t xml:space="preserve">2.86474561691284</t>
   </si>
   <si>
     <t xml:space="preserve">2.94950199127197</t>
@@ -230,22 +230,22 @@
     <t xml:space="preserve">2.9427216053009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94780707359314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88339185714722</t>
+    <t xml:space="preserve">2.94780683517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8833920955658</t>
   </si>
   <si>
     <t xml:space="preserve">2.87322187423706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85966086387634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03256320953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07037377357483</t>
+    <t xml:space="preserve">2.85966062545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03256273269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07037353515625</t>
   </si>
   <si>
     <t xml:space="preserve">3.06866312026978</t>
@@ -260,37 +260,37 @@
     <t xml:space="preserve">2.98484802246094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93524312973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98313736915588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92497992515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92326951026917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96774291992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03616333007812</t>
+    <t xml:space="preserve">2.93524265289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98313689231873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92498016357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92326927185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9677426815033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0361635684967</t>
   </si>
   <si>
     <t xml:space="preserve">3.05840015411377</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0549795627594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08747887611389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13879418373108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12853145599365</t>
+    <t xml:space="preserve">3.05497908592224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08747863769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13879442214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12853121757507</t>
   </si>
   <si>
     <t xml:space="preserve">3.19010972976685</t>
@@ -299,16 +299,16 @@
     <t xml:space="preserve">3.15589952468872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12339997291565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12511014938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14734721183777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16445183753967</t>
+    <t xml:space="preserve">3.12339949607849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12511038780212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14734697341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16445207595825</t>
   </si>
   <si>
     <t xml:space="preserve">3.16616249084473</t>
@@ -323,64 +323,64 @@
     <t xml:space="preserve">3.3868191242218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48431801795959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52708125114441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62629103660583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.636554479599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64510703086853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74602675437927</t>
+    <t xml:space="preserve">3.48431825637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52708077430725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62629079818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63655376434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64510655403137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74602699279785</t>
   </si>
   <si>
     <t xml:space="preserve">3.67760634422302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71181702613831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63484358787537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51681780815125</t>
+    <t xml:space="preserve">3.71181654930115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63484382629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51681756973267</t>
   </si>
   <si>
     <t xml:space="preserve">3.50484466552734</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49458122253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50655460357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48089718818665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43129253387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35602998733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60063314437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64681720733643</t>
+    <t xml:space="preserve">3.49458074569702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50655484199524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48089694976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43129229545593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35602951049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60063290596008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64681673049927</t>
   </si>
   <si>
     <t xml:space="preserve">3.69471216201782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69984364509583</t>
+    <t xml:space="preserve">3.69984316825867</t>
   </si>
   <si>
     <t xml:space="preserve">3.67589592933655</t>
@@ -389,58 +389,58 @@
     <t xml:space="preserve">3.66563272476196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59721231460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63313341140747</t>
+    <t xml:space="preserve">3.59721255302429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63313293457031</t>
   </si>
   <si>
     <t xml:space="preserve">3.57497549057007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66050100326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68615865707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71523761749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73747372627258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71010613441467</t>
+    <t xml:space="preserve">3.66050124168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68615889549255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71523714065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73747420310974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71010637283325</t>
   </si>
   <si>
     <t xml:space="preserve">3.69129061698914</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6895797252655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73234272003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72036981582642</t>
+    <t xml:space="preserve">3.68958020210266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73234248161316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7203688621521</t>
   </si>
   <si>
     <t xml:space="preserve">3.76313209533691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77168464660645</t>
+    <t xml:space="preserve">3.77168416976929</t>
   </si>
   <si>
     <t xml:space="preserve">3.62115955352783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64168548583984</t>
+    <t xml:space="preserve">3.64168524742126</t>
   </si>
   <si>
     <t xml:space="preserve">3.7032642364502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79734253883362</t>
+    <t xml:space="preserve">3.7973427772522</t>
   </si>
   <si>
     <t xml:space="preserve">3.75457954406738</t>
@@ -452,31 +452,31 @@
     <t xml:space="preserve">3.76655268669128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72892165184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66734290122986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50997591018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49800252914429</t>
+    <t xml:space="preserve">3.72892141342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66734385490417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50997614860535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49800229072571</t>
   </si>
   <si>
     <t xml:space="preserve">3.4894495010376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47234416007996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40392398834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43642401695251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53221225738525</t>
+    <t xml:space="preserve">3.47234463691711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40392374992371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43642377853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53221297264099</t>
   </si>
   <si>
     <t xml:space="preserve">3.5185284614563</t>
@@ -485,13 +485,13 @@
     <t xml:space="preserve">3.46037101745605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50142359733582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53563356399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55616021156311</t>
+    <t xml:space="preserve">3.50142312049866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53563332557678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55615997314453</t>
   </si>
   <si>
     <t xml:space="preserve">3.64339661598206</t>
@@ -500,79 +500,79 @@
     <t xml:space="preserve">3.72550058364868</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84865760803223</t>
+    <t xml:space="preserve">3.84865784645081</t>
   </si>
   <si>
     <t xml:space="preserve">3.82984209060669</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83155298233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87089467048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8452365398407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87431526184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86405253410339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85721039772034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82471036911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90681505203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00260353088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17536640167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11378717422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00773525238037</t>
+    <t xml:space="preserve">3.83155226707458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87089419364929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84523630142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87431573867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86405301094055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85721063613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82471084594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90681552886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00260496139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17536592483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11378812789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00773572921753</t>
   </si>
   <si>
     <t xml:space="preserve">4.0522084236145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0812873840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00602531433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09839248657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01970863342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01115703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99576187133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0351037979126</t>
+    <t xml:space="preserve">4.08128786087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00602436065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09839200973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01970911026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01115655899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99576210975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03510427474976</t>
   </si>
   <si>
     <t xml:space="preserve">4.06247234344482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13773441314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12233972549438</t>
+    <t xml:space="preserve">4.13773488998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12234020233154</t>
   </si>
   <si>
     <t xml:space="preserve">4.14799737930298</t>
@@ -581,49 +581,49 @@
     <t xml:space="preserve">4.18905019760132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25918102264404</t>
+    <t xml:space="preserve">4.2591814994812</t>
   </si>
   <si>
     <t xml:space="preserve">4.22839212417603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20615482330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02142000198364</t>
+    <t xml:space="preserve">4.20615530014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0214204788208</t>
   </si>
   <si>
     <t xml:space="preserve">3.99405121803284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01799917221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02655124664307</t>
+    <t xml:space="preserve">4.01799869537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02655172348022</t>
   </si>
   <si>
     <t xml:space="preserve">4.07615613937378</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12747192382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11891841888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10523509979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09668302536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10181427001953</t>
+    <t xml:space="preserve">4.12747144699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11891937255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1052360534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09668207168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10181379318237</t>
   </si>
   <si>
     <t xml:space="preserve">4.0710244178772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09497261047363</t>
+    <t xml:space="preserve">4.09497213363647</t>
   </si>
   <si>
     <t xml:space="preserve">4.13089227676392</t>
@@ -647,130 +647,130 @@
     <t xml:space="preserve">4.50292921066284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5670747756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6226658821106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63549423217773</t>
+    <t xml:space="preserve">4.56707429885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62266540527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63549470901489</t>
   </si>
   <si>
     <t xml:space="preserve">4.58417892456055</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60128450393677</t>
+    <t xml:space="preserve">4.60128402709961</t>
   </si>
   <si>
     <t xml:space="preserve">4.57562637329102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61838912963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53286361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55852174758911</t>
+    <t xml:space="preserve">4.61838960647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53286409378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55852079391479</t>
   </si>
   <si>
     <t xml:space="preserve">4.48154783248901</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51575803756714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4901008605957</t>
+    <t xml:space="preserve">4.5157585144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49010038375854</t>
   </si>
   <si>
     <t xml:space="preserve">4.51148223876953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63121795654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78516387939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7595067024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78944063186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73384857177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77233600616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76378297805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65687656402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69536209106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82792806625366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90062379837036</t>
+    <t xml:space="preserve">4.63121843338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78516435623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75950717926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78944110870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73384952545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77233552932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76378345489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65687561035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69536256790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82792711257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90062427520752</t>
   </si>
   <si>
     <t xml:space="preserve">4.91772937774658</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94338750839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98614931106567</t>
+    <t xml:space="preserve">4.94338703155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98614978790283</t>
   </si>
   <si>
     <t xml:space="preserve">5.04174137115479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02035999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07167530059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08022785186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99470233917236</t>
+    <t xml:space="preserve">5.02036046981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0716757774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08022880554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99470329284668</t>
   </si>
   <si>
     <t xml:space="preserve">5.09305667877197</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06050729751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91728496551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94766521453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92596578598022</t>
+    <t xml:space="preserve">5.06050682067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91728448867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94766616821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92596483230591</t>
   </si>
   <si>
     <t xml:space="preserve">4.9042649269104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8218035697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7350025177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72198247909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59178018569946</t>
+    <t xml:space="preserve">4.82180404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73500299453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72198295593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59178066253662</t>
   </si>
   <si>
     <t xml:space="preserve">4.64386081695557</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">4.6525411605835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60914087295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65688180923462</t>
+    <t xml:space="preserve">4.60914039611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65688133239746</t>
   </si>
   <si>
     <t xml:space="preserve">4.54837989807129</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">4.53535985946655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47025871276855</t>
+    <t xml:space="preserve">4.47025966644287</t>
   </si>
   <si>
     <t xml:space="preserve">4.59612131118774</t>
@@ -809,7 +809,7 @@
     <t xml:space="preserve">4.48761940002441</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46157836914062</t>
+    <t xml:space="preserve">4.46157884597778</t>
   </si>
   <si>
     <t xml:space="preserve">4.41383790969849</t>
@@ -821,25 +821,25 @@
     <t xml:space="preserve">4.39213848114014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40949821472168</t>
+    <t xml:space="preserve">4.40949773788452</t>
   </si>
   <si>
     <t xml:space="preserve">4.55706024169922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52233982086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57008028030396</t>
+    <t xml:space="preserve">4.52234029769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57008075714111</t>
   </si>
   <si>
     <t xml:space="preserve">4.53970003128052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47893905639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43553876876831</t>
+    <t xml:space="preserve">4.47893953323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43553829193115</t>
   </si>
   <si>
     <t xml:space="preserve">4.42251825332642</t>
@@ -848,13 +848,13 @@
     <t xml:space="preserve">4.43119859695435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45289945602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51365995407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6872615814209</t>
+    <t xml:space="preserve">4.45289897918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51365900039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68726205825806</t>
   </si>
   <si>
     <t xml:space="preserve">4.60046100616455</t>
@@ -863,10 +863,10 @@
     <t xml:space="preserve">4.6395206451416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56140041351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58744049072266</t>
+    <t xml:space="preserve">4.56139993667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58744096755981</t>
   </si>
   <si>
     <t xml:space="preserve">4.61782121658325</t>
@@ -878,10 +878,10 @@
     <t xml:space="preserve">4.6048002243042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58310079574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49629926681519</t>
+    <t xml:space="preserve">4.58310127258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49629878997803</t>
   </si>
   <si>
     <t xml:space="preserve">4.50497913360596</t>
@@ -890,61 +890,61 @@
     <t xml:space="preserve">4.42685794830322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49195957183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51799964904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80878305435181</t>
+    <t xml:space="preserve">4.49195909500122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51800012588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80878353118896</t>
   </si>
   <si>
     <t xml:space="preserve">4.77840328216553</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84784412384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83482456207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74368333816528</t>
+    <t xml:space="preserve">4.84784317016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8348240852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74368286132812</t>
   </si>
   <si>
     <t xml:space="preserve">4.81312370300293</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71330308914185</t>
+    <t xml:space="preserve">4.71330213546753</t>
   </si>
   <si>
     <t xml:space="preserve">4.70462226867676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72632217407227</t>
+    <t xml:space="preserve">4.72632265090942</t>
   </si>
   <si>
     <t xml:space="preserve">4.69594192504883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76972246170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84350442886353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87822437286377</t>
+    <t xml:space="preserve">4.7697229385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84350395202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87822389602661</t>
   </si>
   <si>
     <t xml:space="preserve">4.8738842010498</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97370529174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97804594039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00842666625977</t>
+    <t xml:space="preserve">4.97370576858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97804546356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00842618942261</t>
   </si>
   <si>
     <t xml:space="preserve">5.07786703109741</t>
@@ -953,52 +953,52 @@
     <t xml:space="preserve">5.04314661026001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14730787277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86086416244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.869544506073</t>
+    <t xml:space="preserve">5.14730834960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86086463928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86954498291016</t>
   </si>
   <si>
     <t xml:space="preserve">4.96502542495728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90860509872437</t>
+    <t xml:space="preserve">4.90860557556152</t>
   </si>
   <si>
     <t xml:space="preserve">4.99974632263184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99106597900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15598821640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12994766235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29486989974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41639089584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48583316802979</t>
+    <t xml:space="preserve">4.99106502532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1559886932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12994718551636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29487037658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41639137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48583269119263</t>
   </si>
   <si>
     <t xml:space="preserve">5.43375205993652</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48149299621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42073106765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39469146728516</t>
+    <t xml:space="preserve">5.4814920425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42073154449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.394690990448</t>
   </si>
   <si>
     <t xml:space="preserve">5.35563087463379</t>
@@ -1010,10 +1010,10 @@
     <t xml:space="preserve">5.37299060821533</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33827066421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20806884765625</t>
+    <t xml:space="preserve">5.33827114105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20806789398193</t>
   </si>
   <si>
     <t xml:space="preserve">5.16466808319092</t>
@@ -1031,34 +1031,34 @@
     <t xml:space="preserve">5.18636846542358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20372819900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19504833221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16900777816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18202877044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19938802719116</t>
+    <t xml:space="preserve">5.20372867584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19504880905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16900825500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18202829360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19938850402832</t>
   </si>
   <si>
     <t xml:space="preserve">5.22542905807495</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42507123947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61603450775146</t>
+    <t xml:space="preserve">5.42507219314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61603403091431</t>
   </si>
   <si>
     <t xml:space="preserve">5.7288761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71151542663574</t>
+    <t xml:space="preserve">5.7115159034729</t>
   </si>
   <si>
     <t xml:space="preserve">5.78963661193848</t>
@@ -1082,19 +1082,19 @@
     <t xml:space="preserve">5.80699682235718</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92851877212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97191905975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95455932617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03267908096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17156219482422</t>
+    <t xml:space="preserve">5.92851829528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9719181060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95455884933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03268003463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1715612411499</t>
   </si>
   <si>
     <t xml:space="preserve">6.28440284729004</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">6.21496152877808</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14552068710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40592527389526</t>
+    <t xml:space="preserve">6.14552211761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40592479705811</t>
   </si>
   <si>
     <t xml:space="preserve">6.07608032226562</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">6.04135990142822</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22364234924316</t>
+    <t xml:space="preserve">6.22364187240601</t>
   </si>
   <si>
     <t xml:space="preserve">6.13684129714966</t>
@@ -1133,55 +1133,55 @@
     <t xml:space="preserve">6.19760179519653</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1542010307312</t>
+    <t xml:space="preserve">6.15420150756836</t>
   </si>
   <si>
     <t xml:space="preserve">6.05003976821899</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89379692077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90247774124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70283508300781</t>
+    <t xml:space="preserve">5.89379787445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90247821807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70283555984497</t>
   </si>
   <si>
     <t xml:space="preserve">5.50319290161133</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5813136100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72019577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76359558105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91983795166016</t>
+    <t xml:space="preserve">5.58131313323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72019624710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.763596534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91983890533447</t>
   </si>
   <si>
     <t xml:space="preserve">5.99795913696289</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83303689956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79831695556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65943479537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51187324523926</t>
+    <t xml:space="preserve">5.83303594589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79831647872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65943431854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5118727684021</t>
   </si>
   <si>
     <t xml:space="preserve">5.5465931892395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58999300003052</t>
+    <t xml:space="preserve">5.58999347686768</t>
   </si>
   <si>
     <t xml:space="preserve">5.52055311203003</t>
@@ -1193,28 +1193,28 @@
     <t xml:space="preserve">5.44243192672729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46847248077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67679452896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64207410812378</t>
+    <t xml:space="preserve">5.46847200393677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67679500579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6420750617981</t>
   </si>
   <si>
     <t xml:space="preserve">5.55527353286743</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53791332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57263422012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52923250198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39903163909912</t>
+    <t xml:space="preserve">5.53791379928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57263374328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52923345565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39903116226196</t>
   </si>
   <si>
     <t xml:space="preserve">5.39035129547119</t>
@@ -1223,43 +1223,43 @@
     <t xml:space="preserve">5.45111227035522</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09344053268433</t>
+    <t xml:space="preserve">6.09344100952148</t>
   </si>
   <si>
     <t xml:space="preserve">5.81567621231079</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77227592468262</t>
+    <t xml:space="preserve">5.77227640151978</t>
   </si>
   <si>
     <t xml:space="preserve">5.73755598068237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40771198272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24278879165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0691876411438</t>
+    <t xml:space="preserve">5.40771102905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24278926849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06918716430664</t>
   </si>
   <si>
     <t xml:space="preserve">4.98238515853882</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07618761062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15619802474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08507776260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24509811401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11174726486206</t>
+    <t xml:space="preserve">5.07618808746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1561975479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0850772857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24509859085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11174821853638</t>
   </si>
   <si>
     <t xml:space="preserve">5.13841772079468</t>
@@ -1268,13 +1268,13 @@
     <t xml:space="preserve">5.20953798294067</t>
   </si>
   <si>
-    <t xml:space="preserve">5.067298412323</t>
+    <t xml:space="preserve">5.06729745864868</t>
   </si>
   <si>
     <t xml:space="preserve">5.05840826034546</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04062747955322</t>
+    <t xml:space="preserve">5.04062843322754</t>
   </si>
   <si>
     <t xml:space="preserve">5.0495171546936</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">4.76503801345825</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92505788803101</t>
+    <t xml:space="preserve">4.92505836486816</t>
   </si>
   <si>
     <t xml:space="preserve">4.88949823379517</t>
@@ -1304,34 +1304,34 @@
     <t xml:space="preserve">4.97839736938477</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91616773605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95172834396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93394804000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89838790893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80948781967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78281831741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75614738464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98728799819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10285806655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96061849594116</t>
+    <t xml:space="preserve">4.91616868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95172786712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9339485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89838838577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80948829650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78281784057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75614786148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98728847503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10285711288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.960618019104</t>
   </si>
   <si>
     <t xml:space="preserve">5.20064783096313</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">5.21842765808105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27176761627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33399724960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23620843887329</t>
+    <t xml:space="preserve">5.27176713943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33399820327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23620796203613</t>
   </si>
   <si>
     <t xml:space="preserve">5.18286752700806</t>
@@ -1361,37 +1361,37 @@
     <t xml:space="preserve">5.00506830215454</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37844800949097</t>
+    <t xml:space="preserve">5.37844848632812</t>
   </si>
   <si>
     <t xml:space="preserve">5.47623729705811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56513786315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68070793151855</t>
+    <t xml:space="preserve">5.56513833999634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6807074546814</t>
   </si>
   <si>
     <t xml:space="preserve">5.6540379524231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63625764846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5562481880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68959760665894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96518754959106</t>
+    <t xml:space="preserve">5.63625812530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55624771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68959808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96518707275391</t>
   </si>
   <si>
     <t xml:space="preserve">5.89406776428223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77849769592285</t>
+    <t xml:space="preserve">5.77849721908569</t>
   </si>
   <si>
     <t xml:space="preserve">5.84072780609131</t>
@@ -1400,22 +1400,22 @@
     <t xml:space="preserve">5.76071739196777</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92073774337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83183717727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44956827163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5829176902771</t>
+    <t xml:space="preserve">5.92073726654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83183670043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4495677947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58291864395142</t>
   </si>
   <si>
     <t xml:space="preserve">5.43178796768188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36955738067627</t>
+    <t xml:space="preserve">5.36955785751343</t>
   </si>
   <si>
     <t xml:space="preserve">5.60958766937256</t>
@@ -1433,28 +1433,28 @@
     <t xml:space="preserve">5.49401760101318</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57402753829956</t>
+    <t xml:space="preserve">5.57402801513672</t>
   </si>
   <si>
     <t xml:space="preserve">5.59180784225464</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64514780044556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71626806259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73404788970947</t>
+    <t xml:space="preserve">5.6451473236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71626758575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73404741287231</t>
   </si>
   <si>
     <t xml:space="preserve">5.81405735015869</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67181730270386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51179790496826</t>
+    <t xml:space="preserve">5.67181777954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5117974281311</t>
   </si>
   <si>
     <t xml:space="preserve">5.85850763320923</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">5.66292762756348</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53846788406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90295743942261</t>
+    <t xml:space="preserve">5.53846740722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90295791625977</t>
   </si>
   <si>
     <t xml:space="preserve">5.79627752304077</t>
@@ -1475,52 +1475,52 @@
     <t xml:space="preserve">5.80516767501831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6184778213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46734762191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60069751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45845794677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50290822982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34288787841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62736749649048</t>
+    <t xml:space="preserve">5.61847734451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46734809875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60069799423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45845746994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50290775299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34288740158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62736797332764</t>
   </si>
   <si>
     <t xml:space="preserve">5.52957773208618</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42289781570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72515773773193</t>
+    <t xml:space="preserve">5.42289733886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72515726089478</t>
   </si>
   <si>
     <t xml:space="preserve">5.70737791061401</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69848680496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00074815750122</t>
+    <t xml:space="preserve">5.69848823547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0007472038269</t>
   </si>
   <si>
     <t xml:space="preserve">5.92962789535522</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9474081993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93851757049561</t>
+    <t xml:space="preserve">5.94740724563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93851661682129</t>
   </si>
   <si>
     <t xml:space="preserve">5.99185705184937</t>
@@ -1529,76 +1529,76 @@
     <t xml:space="preserve">6.24077749252319</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40968751907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48080682754517</t>
+    <t xml:space="preserve">6.40968799591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48080778121948</t>
   </si>
   <si>
     <t xml:space="preserve">6.623046875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84529685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9964280128479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01420640945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90752696990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91641759872437</t>
+    <t xml:space="preserve">6.84529733657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99642658233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0142068862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90752744674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91641807556152</t>
   </si>
   <si>
     <t xml:space="preserve">6.97864675521851</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00531673431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0230975151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2453465461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27201747894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33424711227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47648620605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76985740661621</t>
+    <t xml:space="preserve">7.00531721115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02309703826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24534702301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27201700210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33424663543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47648668289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76985549926758</t>
   </si>
   <si>
     <t xml:space="preserve">7.73429584503174</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72540760040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79652690887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80541658401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22324657440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21435546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15212726593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12545680999756</t>
+    <t xml:space="preserve">7.72540664672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79652786254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80541706085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22324752807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21435642242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15212535858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12545776367188</t>
   </si>
   <si>
     <t xml:space="preserve">8.00099658966064</t>
@@ -1610,13 +1610,13 @@
     <t xml:space="preserve">8.34770584106445</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42771530151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48105716705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46327686309814</t>
+    <t xml:space="preserve">8.42771625518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48105621337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46327781677246</t>
   </si>
   <si>
     <t xml:space="preserve">8.52550601959229</t>
@@ -1625,10 +1625,10 @@
     <t xml:space="preserve">8.50772666931152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66774749755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80109596252441</t>
+    <t xml:space="preserve">8.66774654388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8010950088501</t>
   </si>
   <si>
     <t xml:space="preserve">8.88999652862549</t>
@@ -1637,55 +1637,55 @@
     <t xml:space="preserve">9.19225692749023</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37005519866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4767370223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49451732635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31671524047852</t>
+    <t xml:space="preserve">9.37005615234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47673606872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49451541900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31671619415283</t>
   </si>
   <si>
     <t xml:space="preserve">9.15669631958008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3522777557373</t>
+    <t xml:space="preserve">9.35227680206299</t>
   </si>
   <si>
     <t xml:space="preserve">9.40561580657959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69009494781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86789608001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83233547210693</t>
+    <t xml:space="preserve">9.69009590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86789703369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83233737945557</t>
   </si>
   <si>
     <t xml:space="preserve">9.77899646759033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44117546081543</t>
+    <t xml:space="preserve">9.44117450714111</t>
   </si>
   <si>
     <t xml:space="preserve">9.210036277771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58341503143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51229476928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67231559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85011577606201</t>
+    <t xml:space="preserve">9.58341693878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51229572296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67231464385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85011672973633</t>
   </si>
   <si>
     <t xml:space="preserve">10.0990343093872</t>
@@ -1706,31 +1706,31 @@
     <t xml:space="preserve">9.88567543029785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2234945297241</t>
+    <t xml:space="preserve">10.2234964370728</t>
   </si>
   <si>
     <t xml:space="preserve">10.4368553161621</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6679944992065</t>
+    <t xml:space="preserve">10.6679964065552</t>
   </si>
   <si>
     <t xml:space="preserve">11.414755821228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3614158630371</t>
+    <t xml:space="preserve">11.3614149093628</t>
   </si>
   <si>
     <t xml:space="preserve">11.3080759048462</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4325361251831</t>
+    <t xml:space="preserve">11.4325351715088</t>
   </si>
   <si>
     <t xml:space="preserve">11.6814556121826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8948163986206</t>
+    <t xml:space="preserve">11.894814491272</t>
   </si>
   <si>
     <t xml:space="preserve">11.965934753418</t>
@@ -1754,22 +1754,22 @@
     <t xml:space="preserve">11.689640045166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1239280700684</t>
+    <t xml:space="preserve">12.123929977417</t>
   </si>
   <si>
     <t xml:space="preserve">11.7982120513916</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1782159805298</t>
+    <t xml:space="preserve">12.1782169342041</t>
   </si>
   <si>
     <t xml:space="preserve">12.3229789733887</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9925088882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8296508789062</t>
+    <t xml:space="preserve">12.9925098419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8296518325806</t>
   </si>
   <si>
     <t xml:space="preserve">12.7391738891602</t>
@@ -1781,16 +1781,16 @@
     <t xml:space="preserve">12.3953609466553</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2867889404297</t>
+    <t xml:space="preserve">12.2867879867554</t>
   </si>
   <si>
     <t xml:space="preserve">12.6306018829346</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4496479034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2144079208374</t>
+    <t xml:space="preserve">12.4496469497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2144060134888</t>
   </si>
   <si>
     <t xml:space="preserve">12.1058349609375</t>
@@ -1802,46 +1802,46 @@
     <t xml:space="preserve">11.9067850112915</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4724950790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4182081222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5810670852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.852499961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0877389907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8344030380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8886890411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4363040924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3277320861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734451293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1829681396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1648731231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8391551971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6401052474976</t>
+    <t xml:space="preserve">11.4724960327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4182090759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5810680389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8524990081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0877380371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8344020843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.888689994812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4363050460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3277311325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734460830688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1829671859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1648721694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8391542434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6401062011719</t>
   </si>
   <si>
     <t xml:space="preserve">10.6762971878052</t>
@@ -1850,19 +1850,19 @@
     <t xml:space="preserve">10.5134382247925</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9115381240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2915391921997</t>
+    <t xml:space="preserve">10.9115371704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.291540145874</t>
   </si>
   <si>
     <t xml:space="preserve">11.1467761993408</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7667722702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1105861663818</t>
+    <t xml:space="preserve">10.766773223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1105852127075</t>
   </si>
   <si>
     <t xml:space="preserve">11.1286821365356</t>
@@ -1871,10 +1871,10 @@
     <t xml:space="preserve">10.6220092773438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0020122528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6039152145386</t>
+    <t xml:space="preserve">11.0020132064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6039142608643</t>
   </si>
   <si>
     <t xml:space="preserve">10.4953422546387</t>
@@ -1886,7 +1886,7 @@
     <t xml:space="preserve">10.3143882751465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89819240570068</t>
+    <t xml:space="preserve">9.898193359375</t>
   </si>
   <si>
     <t xml:space="preserve">9.9343843460083</t>
@@ -1895,22 +1895,22 @@
     <t xml:space="preserve">9.80771636962891</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6810474395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95248031616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2420072555542</t>
+    <t xml:space="preserve">9.68104839324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95247936248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2420063018799</t>
   </si>
   <si>
     <t xml:space="preserve">10.4772462844849</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3867702484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4410562515259</t>
+    <t xml:space="preserve">10.3867683410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4410552978516</t>
   </si>
   <si>
     <t xml:space="preserve">9.55438041687012</t>
@@ -1919,25 +1919,25 @@
     <t xml:space="preserve">10.1153383255005</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3505792617798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4048633575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7486782073975</t>
+    <t xml:space="preserve">10.3505783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4048643112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7486791610718</t>
   </si>
   <si>
     <t xml:space="preserve">11.0201101303101</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8572492599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8753461837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5858192443848</t>
+    <t xml:space="preserve">10.857250213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8753452301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5858201980591</t>
   </si>
   <si>
     <t xml:space="preserve">10.8029642105103</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">10.7848691940308</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2372541427612</t>
+    <t xml:space="preserve">11.2372550964355</t>
   </si>
   <si>
     <t xml:space="preserve">11.3096361160278</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">11.4543991088867</t>
   </si>
   <si>
-    <t xml:space="preserve">11.725830078125</t>
+    <t xml:space="preserve">11.7258310317993</t>
   </si>
   <si>
     <t xml:space="preserve">11.9972620010376</t>
@@ -1973,43 +1973,43 @@
     <t xml:space="preserve">12.0334529876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9429750442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7620220184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9477281570435</t>
+    <t xml:space="preserve">11.9429759979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.762020111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9477272033691</t>
   </si>
   <si>
     <t xml:space="preserve">10.9658231735229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1877202987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98867034912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0429563522339</t>
+    <t xml:space="preserve">10.1877193450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98867130279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0429573059082</t>
   </si>
   <si>
     <t xml:space="preserve">9.91628932952881</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1696243286133</t>
+    <t xml:space="preserve">10.169623374939</t>
   </si>
   <si>
     <t xml:space="preserve">10.5315341949463</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4229612350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.13343334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3324823379517</t>
+    <t xml:space="preserve">10.4229602813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1334342956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.332483291626</t>
   </si>
   <si>
     <t xml:space="preserve">10.2239112854004</t>
@@ -2030,61 +2030,61 @@
     <t xml:space="preserve">11.056300163269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8934421539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5496273040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3686752319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82581043243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77152633666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69914436340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51819038391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71723937988281</t>
+    <t xml:space="preserve">10.8934412002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5496282577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3686742782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8258113861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77152538299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.699143409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51818943023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71723747253418</t>
   </si>
   <si>
     <t xml:space="preserve">9.42771244049072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59057235717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3639221191406</t>
+    <t xml:space="preserve">9.59057140350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3639230728149</t>
   </si>
   <si>
     <t xml:space="preserve">11.9791660308838</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4677419662476</t>
+    <t xml:space="preserve">12.4677410125732</t>
   </si>
   <si>
     <t xml:space="preserve">12.3772659301758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3820180892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5629720687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6172590255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0924921035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.694390296936</t>
+    <t xml:space="preserve">11.3820171356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5629711151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6172580718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.092490196228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6943922042847</t>
   </si>
   <si>
     <t xml:space="preserve">9.62676239013672</t>
@@ -2096,7 +2096,7 @@
     <t xml:space="preserve">8.68580055236816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43246364593506</t>
+    <t xml:space="preserve">8.43246459960938</t>
   </si>
   <si>
     <t xml:space="preserve">7.0481653213501</t>
@@ -2108,19 +2108,19 @@
     <t xml:space="preserve">7.24721479415894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1838812828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58673286437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65006589889526</t>
+    <t xml:space="preserve">7.18388080596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58673238754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65006542205811</t>
   </si>
   <si>
     <t xml:space="preserve">6.96673583984375</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97578382492065</t>
+    <t xml:space="preserve">6.9757833480835</t>
   </si>
   <si>
     <t xml:space="preserve">7.16578531265259</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">7.28340530395508</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60912227630615</t>
+    <t xml:space="preserve">7.60912370681763</t>
   </si>
   <si>
     <t xml:space="preserve">7.76293420791626</t>
@@ -2144,49 +2144,49 @@
     <t xml:space="preserve">8.04341316223145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61341857910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41436862945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25150966644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93008899688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35533142089844</t>
+    <t xml:space="preserve">8.61341953277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41436958312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25151062011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93008804321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35533046722412</t>
   </si>
   <si>
     <t xml:space="preserve">9.04770946502686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26485252380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50009441375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86200141906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2191581726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9839191436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6582021713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97057437896729</t>
+    <t xml:space="preserve">9.26485347747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50009346008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86200332641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2191591262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9839181900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6582002639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9705753326416</t>
   </si>
   <si>
     <t xml:space="preserve">10.2058153152466</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84390735626221</t>
+    <t xml:space="preserve">9.84390830993652</t>
   </si>
   <si>
     <t xml:space="preserve">10.4591512680054</t>
@@ -2198,16 +2198,16 @@
     <t xml:space="preserve">10.7305822372437</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8210592269897</t>
+    <t xml:space="preserve">10.8210601806641</t>
   </si>
   <si>
     <t xml:space="preserve">12.0696439743042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5582189559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8477458953857</t>
+    <t xml:space="preserve">12.558219909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8477468490601</t>
   </si>
   <si>
     <t xml:space="preserve">13.1915588378906</t>
@@ -2216,10 +2216,10 @@
     <t xml:space="preserve">12.757269859314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7934598922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4315519332886</t>
+    <t xml:space="preserve">12.7934617996216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4315509796143</t>
   </si>
   <si>
     <t xml:space="preserve">12.594409942627</t>
@@ -2228,10 +2228,10 @@
     <t xml:space="preserve">12.6486968994141</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7210779190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8658418655396</t>
+    <t xml:space="preserve">12.721079826355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8658428192139</t>
   </si>
   <si>
     <t xml:space="preserve">13.1553678512573</t>
@@ -2252,16 +2252,16 @@
     <t xml:space="preserve">13.3725137710571</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3544187545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4534873962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2496852874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2858753204346</t>
+    <t xml:space="preserve">13.354416847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4534883499146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.249683380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2858734130859</t>
   </si>
   <si>
     <t xml:space="preserve">16.3763523101807</t>
@@ -2276,79 +2276,79 @@
     <t xml:space="preserve">16.0687313079834</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8696813583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9239664077759</t>
+    <t xml:space="preserve">15.869683265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9239673614502</t>
   </si>
   <si>
     <t xml:space="preserve">15.9058713912964</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8515872955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0144443511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7972965240479</t>
+    <t xml:space="preserve">15.8515853881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0144462585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7973003387451</t>
   </si>
   <si>
     <t xml:space="preserve">16.2677803039551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0325374603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7792043685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7249193191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4125423431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8153963088989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9420642852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6344404220581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.104923248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9601583480835</t>
+    <t xml:space="preserve">16.0325393676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7792062759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7249183654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4125442504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8153944015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.942063331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6344423294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1049213409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9601573944092</t>
   </si>
   <si>
     <t xml:space="preserve">15.6887264251709</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6163463592529</t>
+    <t xml:space="preserve">15.6163444519043</t>
   </si>
   <si>
     <t xml:space="preserve">14.8925285339355</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6525344848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3630084991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4896783828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1458644866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0372924804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7430114746094</t>
+    <t xml:space="preserve">15.6525363922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3630094528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4896793365479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.14586353302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0372915267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7430143356323</t>
   </si>
   <si>
     <t xml:space="preserve">14.8201465606689</t>
@@ -2357,46 +2357,46 @@
     <t xml:space="preserve">15.2906274795532</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5887489318848</t>
+    <t xml:space="preserve">17.5887451171875</t>
   </si>
   <si>
     <t xml:space="preserve">17.7696990966797</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0230350494385</t>
+    <t xml:space="preserve">18.0230331420898</t>
   </si>
   <si>
     <t xml:space="preserve">19.1359043121338</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2763710021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0411319732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4258880615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7335109710693</t>
+    <t xml:space="preserve">18.2763729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.041130065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4258861541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7335090637207</t>
   </si>
   <si>
     <t xml:space="preserve">17.2992210388184</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0458850860596</t>
+    <t xml:space="preserve">17.0458831787109</t>
   </si>
   <si>
     <t xml:space="preserve">17.0277881622314</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7020683288574</t>
+    <t xml:space="preserve">16.7020702362061</t>
   </si>
   <si>
     <t xml:space="preserve">17.009693145752</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4077911376953</t>
+    <t xml:space="preserve">17.4077930450439</t>
   </si>
   <si>
     <t xml:space="preserve">18.5025653839111</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">18.1406555175781</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9687519073486</t>
+    <t xml:space="preserve">17.96875</t>
   </si>
   <si>
     <t xml:space="preserve">17.4982681274414</t>
@@ -2423,37 +2423,37 @@
     <t xml:space="preserve">17.2449321746826</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1182632446289</t>
+    <t xml:space="preserve">17.1182651519775</t>
   </si>
   <si>
     <t xml:space="preserve">16.8106422424316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8287372589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9735012054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9192180633545</t>
+    <t xml:space="preserve">16.8287391662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.973503112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9192161560059</t>
   </si>
   <si>
     <t xml:space="preserve">17.0639801025391</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8468341827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9011211395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3173141479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2087421417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2268371582031</t>
+    <t xml:space="preserve">16.8468360900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9011192321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3173160552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2087440490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2268390655518</t>
   </si>
   <si>
     <t xml:space="preserve">18.3668479919434</t>
@@ -2471,28 +2471,28 @@
     <t xml:space="preserve">18.9549503326416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8644714355469</t>
+    <t xml:space="preserve">18.8644733428955</t>
   </si>
   <si>
     <t xml:space="preserve">19.6335296630859</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6787662506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5430526733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0454292297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0001888275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.316858291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3216114044189</t>
+    <t xml:space="preserve">19.678768157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5430507659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0454254150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.000186920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3168563842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3216133117676</t>
   </si>
   <si>
     <t xml:space="preserve">18.2311344146729</t>
@@ -2507,10 +2507,10 @@
     <t xml:space="preserve">18.0954189300537</t>
   </si>
   <si>
-    <t xml:space="preserve">18.004940032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.570650100708</t>
+    <t xml:space="preserve">18.0049381256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5706481933594</t>
   </si>
   <si>
     <t xml:space="preserve">17.8239860534668</t>
@@ -2519,52 +2519,52 @@
     <t xml:space="preserve">17.6430320739746</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8058910369873</t>
+    <t xml:space="preserve">17.8058891296387</t>
   </si>
   <si>
     <t xml:space="preserve">19.2716178894043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1811447143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.26686668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4930610656738</t>
+    <t xml:space="preserve">19.1811428070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2668685913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4930591583252</t>
   </si>
   <si>
     <t xml:space="preserve">20.9906845092773</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5835361480713</t>
+    <t xml:space="preserve">20.5835380554199</t>
   </si>
   <si>
     <t xml:space="preserve">20.3573455810547</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9049606323242</t>
+    <t xml:space="preserve">19.9049587249756</t>
   </si>
   <si>
     <t xml:space="preserve">19.7692432403564</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7192535400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9954376220703</t>
+    <t xml:space="preserve">20.7192516326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9954357147217</t>
   </si>
   <si>
     <t xml:space="preserve">19.2263813018799</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4525756835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4073371887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6249370574951</t>
+    <t xml:space="preserve">19.4525737762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4073352813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6249351501465</t>
   </si>
   <si>
     <t xml:space="preserve">17.7877941131592</t>
@@ -2573,22 +2573,22 @@
     <t xml:space="preserve">19.4978103637695</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0859127044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1311511993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8597202301025</t>
+    <t xml:space="preserve">20.0859146118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1311531066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8597221374512</t>
   </si>
   <si>
     <t xml:space="preserve">20.674015045166</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0359230041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8097267150879</t>
+    <t xml:space="preserve">21.035924911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8097286224365</t>
   </si>
   <si>
     <t xml:space="preserve">20.628776550293</t>
@@ -2600,13 +2600,13 @@
     <t xml:space="preserve">20.4478225708008</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8821125030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2802104949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3344955444336</t>
+    <t xml:space="preserve">20.8821105957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2802124023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3344974517822</t>
   </si>
   <si>
     <t xml:space="preserve">21.587833404541</t>
@@ -2621,25 +2621,25 @@
     <t xml:space="preserve">22.6192722320557</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8726081848145</t>
+    <t xml:space="preserve">22.8726100921631</t>
   </si>
   <si>
     <t xml:space="preserve">23.9040470123291</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7821292877197</t>
+    <t xml:space="preserve">22.7821311950684</t>
   </si>
   <si>
     <t xml:space="preserve">21.8592624664307</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0040245056152</t>
+    <t xml:space="preserve">22.0040264129639</t>
   </si>
   <si>
     <t xml:space="preserve">22.2573642730713</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4745082855225</t>
+    <t xml:space="preserve">22.4745101928711</t>
   </si>
   <si>
     <t xml:space="preserve">22.1126003265381</t>
@@ -2663,16 +2663,16 @@
     <t xml:space="preserve">21.3525943756104</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2621154785156</t>
+    <t xml:space="preserve">21.2621173858643</t>
   </si>
   <si>
     <t xml:space="preserve">22.09450340271</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5830783843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0354671478271</t>
+    <t xml:space="preserve">22.583080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0354652404785</t>
   </si>
   <si>
     <t xml:space="preserve">23.0173721313477</t>
@@ -2681,19 +2681,19 @@
     <t xml:space="preserve">23.3611831665039</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2707080841064</t>
+    <t xml:space="preserve">23.2707061767578</t>
   </si>
   <si>
     <t xml:space="preserve">25.0440578460693</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7726249694824</t>
+    <t xml:space="preserve">24.7726268768311</t>
   </si>
   <si>
     <t xml:space="preserve">24.9716758728027</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0621528625488</t>
+    <t xml:space="preserve">25.0621547698975</t>
   </si>
   <si>
     <t xml:space="preserve">25.9126377105713</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">26.238353729248</t>
   </si>
   <si>
-    <t xml:space="preserve">26.676570892334</t>
+    <t xml:space="preserve">26.6765727996826</t>
   </si>
   <si>
     <t xml:space="preserve">26.7130928039551</t>
@@ -2714,88 +2714,88 @@
     <t xml:space="preserve">26.6583156585693</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8226470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.95046043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5712699890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.626049041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.064266204834</t>
+    <t xml:space="preserve">26.8226451873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9504585266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5712718963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6260471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0642642974854</t>
   </si>
   <si>
     <t xml:space="preserve">28.283374786377</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8171443939209</t>
+    <t xml:space="preserve">29.8171424865723</t>
   </si>
   <si>
     <t xml:space="preserve">29.5980319976807</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9589614868164</t>
+    <t xml:space="preserve">28.958963394165</t>
   </si>
   <si>
     <t xml:space="preserve">30.1275482177734</t>
   </si>
   <si>
-    <t xml:space="preserve">29.652811050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1092891693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9632129669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4014358520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2188396453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2961292266846</t>
+    <t xml:space="preserve">29.6528091430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1092872619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9632148742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4014301300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2188415527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2961311340332</t>
   </si>
   <si>
     <t xml:space="preserve">30.8213920593262</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1683158874512</t>
+    <t xml:space="preserve">31.1683177947998</t>
   </si>
   <si>
     <t xml:space="preserve">30.2371006011963</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4154415130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8536624908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1780700683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.145809173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7075862884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0545082092285</t>
+    <t xml:space="preserve">29.4154434204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8536605834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.178071975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1458072662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7075881958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0545120239258</t>
   </si>
   <si>
     <t xml:space="preserve">32.8664131164551</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5462532043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0532569885254</t>
+    <t xml:space="preserve">34.546257019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0532608032227</t>
   </si>
   <si>
     <t xml:space="preserve">33.0855255126953</t>
@@ -2804,31 +2804,31 @@
     <t xml:space="preserve">33.7245941162109</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6880722045898</t>
+    <t xml:space="preserve">33.6880760192871</t>
   </si>
   <si>
     <t xml:space="preserve">33.5785217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4872283935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7976303100586</t>
+    <t xml:space="preserve">33.4872207641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7976341247559</t>
   </si>
   <si>
     <t xml:space="preserve">33.1403007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">33.286376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2273483276367</t>
+    <t xml:space="preserve">33.2863693237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2273445129395</t>
   </si>
   <si>
     <t xml:space="preserve">32.8846740722656</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7568588256836</t>
+    <t xml:space="preserve">32.7568626403809</t>
   </si>
   <si>
     <t xml:space="preserve">32.6473045349121</t>
@@ -2840,10 +2840,10 @@
     <t xml:space="preserve">32.7751197814941</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4099388122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6655654907227</t>
+    <t xml:space="preserve">32.4099349975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6655616760254</t>
   </si>
   <si>
     <t xml:space="preserve">34.692325592041</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">35.605281829834</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2401008605957</t>
+    <t xml:space="preserve">35.2400970458984</t>
   </si>
   <si>
     <t xml:space="preserve">35.8791694641113</t>
@@ -2864,7 +2864,7 @@
     <t xml:space="preserve">35.0940284729004</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5870246887207</t>
+    <t xml:space="preserve">35.5870208740234</t>
   </si>
   <si>
     <t xml:space="preserve">35.7878723144531</t>
@@ -2879,22 +2879,22 @@
     <t xml:space="preserve">38.9101829528809</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4354476928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4944725036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3849220275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2205924987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1292953491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1980743408203</t>
+    <t xml:space="preserve">38.4354438781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4944763183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3849182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2205848693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1292915344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1980781555176</t>
   </si>
   <si>
     <t xml:space="preserve">37.6137886047363</t>
@@ -2903,7 +2903,7 @@
     <t xml:space="preserve">37.2486038208008</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0660133361816</t>
+    <t xml:space="preserve">37.0660095214844</t>
   </si>
   <si>
     <t xml:space="preserve">37.2668609619141</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">36.7008323669434</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2120819091797</t>
+    <t xml:space="preserve">37.212085723877</t>
   </si>
   <si>
     <t xml:space="preserve">37.559009552002</t>
@@ -2921,31 +2921,31 @@
     <t xml:space="preserve">38.0154838562012</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6503067016602</t>
+    <t xml:space="preserve">37.6503105163574</t>
   </si>
   <si>
     <t xml:space="preserve">35.6235427856445</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2316017150879</t>
+    <t xml:space="preserve">33.2315979003906</t>
   </si>
   <si>
     <t xml:space="preserve">32.9942283630371</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3594131469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0490112304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7836227416992</t>
+    <t xml:space="preserve">33.3594093322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0490074157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.783618927002</t>
   </si>
   <si>
     <t xml:space="preserve">34.3819236755371</t>
   </si>
   <si>
-    <t xml:space="preserve">34.893180847168</t>
+    <t xml:space="preserve">34.8931770324707</t>
   </si>
   <si>
     <t xml:space="preserve">32.9577102661133</t>
@@ -2957,31 +2957,31 @@
     <t xml:space="preserve">35.513988494873</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4817199707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3173904418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6095314025879</t>
+    <t xml:space="preserve">36.4817237854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3173866271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6095352172852</t>
   </si>
   <si>
     <t xml:space="preserve">37.7781181335449</t>
   </si>
   <si>
-    <t xml:space="preserve">38.271110534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2023315429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7190895080566</t>
+    <t xml:space="preserve">38.2711143493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2023277282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7190933227539</t>
   </si>
   <si>
     <t xml:space="preserve">35.8426475524902</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9662170410156</t>
+    <t xml:space="preserve">34.9662132263184</t>
   </si>
   <si>
     <t xml:space="preserve">35.1488075256348</t>
@@ -2990,19 +2990,19 @@
     <t xml:space="preserve">35.4409484863281</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8876724243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.526741027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8006324768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6685600280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4226913452148</t>
+    <t xml:space="preserve">37.8876686096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5267448425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8006286621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6685638427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4226951599121</t>
   </si>
   <si>
     <t xml:space="preserve">35.258358001709</t>
@@ -3011,13 +3011,13 @@
     <t xml:space="preserve">34.9114379882812</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3636589050293</t>
+    <t xml:space="preserve">34.3636627197266</t>
   </si>
   <si>
     <t xml:space="preserve">33.8341522216797</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5967788696289</t>
+    <t xml:space="preserve">33.5967826843262</t>
   </si>
   <si>
     <t xml:space="preserve">35.3313980102539</t>
@@ -3038,40 +3038,40 @@
     <t xml:space="preserve">34.3454055786133</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0715179443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1950759887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6150360107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9254417419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9436988830566</t>
+    <t xml:space="preserve">34.0715217590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1950836181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6150398254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9254455566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9437026977539</t>
   </si>
   <si>
     <t xml:space="preserve">34.6192893981934</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5827751159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7288436889648</t>
+    <t xml:space="preserve">34.5827713012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7288475036621</t>
   </si>
   <si>
     <t xml:space="preserve">35.0027313232422</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8384017944336</t>
+    <t xml:space="preserve">34.8383979797363</t>
   </si>
   <si>
     <t xml:space="preserve">34.8749198913574</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5377540588379</t>
+    <t xml:space="preserve">32.5377502441406</t>
   </si>
   <si>
     <t xml:space="preserve">32.1725692749023</t>
@@ -3083,67 +3083,67 @@
     <t xml:space="preserve">29.4519577026367</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8901805877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1640663146973</t>
+    <t xml:space="preserve">29.8901786804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1640644073486</t>
   </si>
   <si>
     <t xml:space="preserve">28.4294490814209</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1007862091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6808242797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9954814910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2693710327148</t>
+    <t xml:space="preserve">28.1007843017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6808261871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9954833984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2693691253662</t>
   </si>
   <si>
     <t xml:space="preserve">28.6850776672363</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9687213897705</t>
+    <t xml:space="preserve">26.9687194824219</t>
   </si>
   <si>
     <t xml:space="preserve">26.8956813812256</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8451557159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9729709625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6668167114258</t>
+    <t xml:space="preserve">27.845157623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9729690551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6668186187744</t>
   </si>
   <si>
     <t xml:space="preserve">29.1232948303223</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9224452972412</t>
+    <t xml:space="preserve">28.9224472045898</t>
   </si>
   <si>
     <t xml:space="preserve">27.6077880859375</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7538604736328</t>
+    <t xml:space="preserve">27.7538623809814</t>
   </si>
   <si>
     <t xml:space="preserve">26.3479099273682</t>
   </si>
   <si>
-    <t xml:space="preserve">25.544506072998</t>
+    <t xml:space="preserve">25.5445098876953</t>
   </si>
   <si>
     <t xml:space="preserve">26.7496089935303</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7861289978027</t>
+    <t xml:space="preserve">26.7861270904541</t>
   </si>
   <si>
     <t xml:space="preserve">26.5670204162598</t>
@@ -3155,13 +3155,13 @@
     <t xml:space="preserve">27.4251976013184</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4799747467041</t>
+    <t xml:space="preserve">27.4799766540527</t>
   </si>
   <si>
     <t xml:space="preserve">27.1147937774658</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7313537597656</t>
+    <t xml:space="preserve">26.731351852417</t>
   </si>
   <si>
     <t xml:space="preserve">27.4069385528564</t>
@@ -3173,10 +3173,10 @@
     <t xml:space="preserve">26.6948337554932</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4434547424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3113918304443</t>
+    <t xml:space="preserve">27.4434566497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3113899230957</t>
   </si>
   <si>
     <t xml:space="preserve">23.5542621612549</t>
@@ -3191,91 +3191,91 @@
     <t xml:space="preserve">22.0022392272949</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7466125488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.742359161377</t>
+    <t xml:space="preserve">21.7466106414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7423572540283</t>
   </si>
   <si>
     <t xml:space="preserve">22.6047897338867</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8744258880615</t>
+    <t xml:space="preserve">21.8744239807129</t>
   </si>
   <si>
     <t xml:space="preserve">22.5134925842285</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1525630950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2073402404785</t>
+    <t xml:space="preserve">23.1525650024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2073421478271</t>
   </si>
   <si>
     <t xml:space="preserve">24.5402545928955</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6680698394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8689193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4489612579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2341041564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5585174560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0290012359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1385555267334</t>
+    <t xml:space="preserve">24.6680717468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8689212799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4489631652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2341022491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5585155487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0289993286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.138557434082</t>
   </si>
   <si>
     <t xml:space="preserve">24.0472602844238</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3984355926514</t>
+    <t xml:space="preserve">25.3984336853027</t>
   </si>
   <si>
     <t xml:space="preserve">25.4166927337646</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2115917205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.083776473999</t>
+    <t xml:space="preserve">24.2115936279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0837783813477</t>
   </si>
   <si>
     <t xml:space="preserve">23.8098926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3351535797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4221992492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7326030731201</t>
+    <t xml:space="preserve">23.3351554870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4221973419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7326049804688</t>
   </si>
   <si>
     <t xml:space="preserve">22.677827835083</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2761268615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9109420776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2213459014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8379077911377</t>
+    <t xml:space="preserve">22.2761249542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9109439849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2213497161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8379058837891</t>
   </si>
   <si>
     <t xml:space="preserve">22.0935344696045</t>
@@ -3284,31 +3284,31 @@
     <t xml:space="preserve">22.8239002227783</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5457611083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0710258483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9657211303711</t>
+    <t xml:space="preserve">21.5457630157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.07102394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9657192230225</t>
   </si>
   <si>
     <t xml:space="preserve">21.1988372802734</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2718734741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8884296417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6875839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0850296020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3729228973389</t>
+    <t xml:space="preserve">21.2718753814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8884315490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6875820159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0850315093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3729267120361</t>
   </si>
   <si>
     <t xml:space="preserve">19.8659229278564</t>
@@ -3317,16 +3317,16 @@
     <t xml:space="preserve">19.957218170166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9024391174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2493629455566</t>
+    <t xml:space="preserve">19.9024410247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2493648529053</t>
   </si>
   <si>
     <t xml:space="preserve">20.9614677429199</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8519153594971</t>
+    <t xml:space="preserve">20.8519134521484</t>
   </si>
   <si>
     <t xml:space="preserve">20.724100112915</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">21.0162467956543</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3449096679688</t>
+    <t xml:space="preserve">21.3449115753174</t>
   </si>
   <si>
     <t xml:space="preserve">20.3954372406006</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">20.523250579834</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6693229675293</t>
+    <t xml:space="preserve">20.6693210601807</t>
   </si>
   <si>
     <t xml:space="preserve">22.1300525665283</t>
@@ -3353,10 +3353,10 @@
     <t xml:space="preserve">24.1933345794678</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6455612182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5177478790283</t>
+    <t xml:space="preserve">23.6455593109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5177440643311</t>
   </si>
   <si>
     <t xml:space="preserve">23.7368545532227</t>
@@ -3365,22 +3365,22 @@
     <t xml:space="preserve">23.0533809661865</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9240760803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7393531799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8711585998535</t>
+    <t xml:space="preserve">22.9240741729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7393550872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8711566925049</t>
   </si>
   <si>
     <t xml:space="preserve">20.7443466186523</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6914291381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2850399017334</t>
+    <t xml:space="preserve">19.6914310455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2850379943848</t>
   </si>
   <si>
     <t xml:space="preserve">20.319486618042</t>
@@ -3392,19 +3392,19 @@
     <t xml:space="preserve">21.2246265411377</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3539333343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3169898986816</t>
+    <t xml:space="preserve">21.3539352416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.316987991333</t>
   </si>
   <si>
     <t xml:space="preserve">21.7603225708008</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6494903564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4278221130371</t>
+    <t xml:space="preserve">21.6494884490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4278240203857</t>
   </si>
   <si>
     <t xml:space="preserve">21.55712890625</t>
@@ -3413,16 +3413,16 @@
     <t xml:space="preserve">21.7972679138184</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5596256256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7812938690186</t>
+    <t xml:space="preserve">20.559627532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7812919616699</t>
   </si>
   <si>
     <t xml:space="preserve">20.3379592895508</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9130973815918</t>
+    <t xml:space="preserve">19.9130954742432</t>
   </si>
   <si>
     <t xml:space="preserve">20.9475440979004</t>
@@ -3443,7 +3443,7 @@
     <t xml:space="preserve">20.8182392120361</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1532344818115</t>
+    <t xml:space="preserve">20.1532363891602</t>
   </si>
   <si>
     <t xml:space="preserve">20.2271251678467</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">20.4487915039062</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3908767700195</t>
+    <t xml:space="preserve">21.3908786773682</t>
   </si>
   <si>
     <t xml:space="preserve">21.0029602050781</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">22.3883800506592</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2960186004639</t>
+    <t xml:space="preserve">22.2960205078125</t>
   </si>
   <si>
     <t xml:space="preserve">22.5361576080322</t>
@@ -3479,10 +3479,10 @@
     <t xml:space="preserve">21.2985153198242</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5017108917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7787952423096</t>
+    <t xml:space="preserve">21.5017127990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7787933349609</t>
   </si>
   <si>
     <t xml:space="preserve">21.7233791351318</t>
@@ -3506,13 +3506,13 @@
     <t xml:space="preserve">20.0054588317871</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1162929534912</t>
+    <t xml:space="preserve">20.1162910461426</t>
   </si>
   <si>
     <t xml:space="preserve">20.0978202819824</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9500427246094</t>
+    <t xml:space="preserve">19.9500408172607</t>
   </si>
   <si>
     <t xml:space="preserve">19.7468452453613</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">18.5830955505371</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2413558959961</t>
+    <t xml:space="preserve">18.2413578033447</t>
   </si>
   <si>
     <t xml:space="preserve">18.0566329956055</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">17.4562854766846</t>
   </si>
   <si>
-    <t xml:space="preserve">17.622537612915</t>
+    <t xml:space="preserve">17.6225357055664</t>
   </si>
   <si>
     <t xml:space="preserve">16.6989231109619</t>
@@ -3557,13 +3557,13 @@
     <t xml:space="preserve">16.8374652862549</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9852447509766</t>
+    <t xml:space="preserve">16.9852428436279</t>
   </si>
   <si>
     <t xml:space="preserve">17.2807998657227</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0037155151367</t>
+    <t xml:space="preserve">17.0037174224854</t>
   </si>
   <si>
     <t xml:space="preserve">17.6779537200928</t>
@@ -3572,40 +3572,40 @@
     <t xml:space="preserve">17.6317729949951</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8164978027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5855941772461</t>
+    <t xml:space="preserve">17.8164939880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5855922698975</t>
   </si>
   <si>
     <t xml:space="preserve">17.5024662017822</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0683689117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.234619140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2530918121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9390640258789</t>
+    <t xml:space="preserve">17.0683670043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2346210479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2530899047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9390621185303</t>
   </si>
   <si>
     <t xml:space="preserve">16.8005218505859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8836460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4285774230957</t>
+    <t xml:space="preserve">16.8836479187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4285793304443</t>
   </si>
   <si>
     <t xml:space="preserve">17.7056617736816</t>
   </si>
   <si>
-    <t xml:space="preserve">17.844202041626</t>
+    <t xml:space="preserve">17.8442039489746</t>
   </si>
   <si>
     <t xml:space="preserve">17.7333698272705</t>
@@ -3614,16 +3614,16 @@
     <t xml:space="preserve">18.3429565429688</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4697608947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5805988311768</t>
+    <t xml:space="preserve">19.469762802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5805969238281</t>
   </si>
   <si>
     <t xml:space="preserve">19.3589286804199</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0449028015137</t>
+    <t xml:space="preserve">19.044900894165</t>
   </si>
   <si>
     <t xml:space="preserve">18.7493438720703</t>
@@ -3632,19 +3632,19 @@
     <t xml:space="preserve">18.3891353607178</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2967739105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4907341003418</t>
+    <t xml:space="preserve">18.2967720031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4907321929932</t>
   </si>
   <si>
     <t xml:space="preserve">19.0079555511475</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0239295959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8392086029053</t>
+    <t xml:space="preserve">20.0239315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8392066955566</t>
   </si>
   <si>
     <t xml:space="preserve">20.8736553192139</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">21.9081001281738</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3329639434814</t>
+    <t xml:space="preserve">22.3329620361328</t>
   </si>
   <si>
     <t xml:space="preserve">20.9105987548828</t>
@@ -3677,31 +3677,31 @@
     <t xml:space="preserve">21.2800464630127</t>
   </si>
   <si>
-    <t xml:space="preserve">21.409351348877</t>
+    <t xml:space="preserve">21.4093494415283</t>
   </si>
   <si>
     <t xml:space="preserve">21.8526840209961</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1507377624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0583782196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3933773040771</t>
+    <t xml:space="preserve">21.1507396697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0583763122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3933753967285</t>
   </si>
   <si>
     <t xml:space="preserve">20.2455978393555</t>
   </si>
   <si>
-    <t xml:space="preserve">19.931568145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9685134887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2825412750244</t>
+    <t xml:space="preserve">19.9315700531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9685153961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.282543182373</t>
   </si>
   <si>
     <t xml:space="preserve">20.9290714263916</t>
@@ -3728,16 +3728,16 @@
     <t xml:space="preserve">23.4412975311279</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9031047821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7922744750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.127269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7553253173828</t>
+    <t xml:space="preserve">23.9031028747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7922706604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1272716522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7553272247314</t>
   </si>
   <si>
     <t xml:space="preserve">23.8846340179443</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">23.4782428741455</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1088008880615</t>
+    <t xml:space="preserve">23.1087970733643</t>
   </si>
   <si>
     <t xml:space="preserve">22.9979629516602</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">23.0164375305176</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9585227966309</t>
+    <t xml:space="preserve">23.9585247039795</t>
   </si>
   <si>
     <t xml:space="preserve">23.5706043243408</t>
@@ -3767,10 +3767,10 @@
     <t xml:space="preserve">24.1247730255127</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5151882171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8686580657959</t>
+    <t xml:space="preserve">23.5151863098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8686599731445</t>
   </si>
   <si>
     <t xml:space="preserve">23.4597702026367</t>
@@ -3782,7 +3782,7 @@
     <t xml:space="preserve">22.8132438659668</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6285190582275</t>
+    <t xml:space="preserve">22.6285209655762</t>
   </si>
   <si>
     <t xml:space="preserve">22.4622688293457</t>
@@ -3794,7 +3794,7 @@
     <t xml:space="preserve">22.2036571502686</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0004634857178</t>
+    <t xml:space="preserve">22.0004615783691</t>
   </si>
   <si>
     <t xml:space="preserve">22.0558776855469</t>
@@ -3806,19 +3806,19 @@
     <t xml:space="preserve">21.8342132568359</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0928249359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2406024932861</t>
+    <t xml:space="preserve">22.0928230285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2406005859375</t>
   </si>
   <si>
     <t xml:space="preserve">21.2615718841553</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3404560089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.656982421875</t>
+    <t xml:space="preserve">19.3404579162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6569843292236</t>
   </si>
   <si>
     <t xml:space="preserve">19.1187896728516</t>
@@ -3836,19 +3836,19 @@
     <t xml:space="preserve">18.2690658569336</t>
   </si>
   <si>
-    <t xml:space="preserve">18.509204864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8232326507568</t>
+    <t xml:space="preserve">18.5092067718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8232345581055</t>
   </si>
   <si>
     <t xml:space="preserve">18.5461502075195</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7124004364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7308750152588</t>
+    <t xml:space="preserve">18.7123985290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7308712005615</t>
   </si>
   <si>
     <t xml:space="preserve">18.6200389862061</t>
@@ -3863,13 +3863,13 @@
     <t xml:space="preserve">17.7980251312256</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5486469268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1422576904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9483013153076</t>
+    <t xml:space="preserve">17.5486488342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1422557830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.948299407959</t>
   </si>
   <si>
     <t xml:space="preserve">16.9205894470215</t>
@@ -3878,10 +3878,10 @@
     <t xml:space="preserve">16.8651733398438</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5696182250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8559398651123</t>
+    <t xml:space="preserve">16.5696201324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8559379577637</t>
   </si>
   <si>
     <t xml:space="preserve">17.1145515441895</t>
@@ -3893,7 +3893,7 @@
     <t xml:space="preserve">16.9021186828613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8744106292725</t>
+    <t xml:space="preserve">16.8744125366211</t>
   </si>
   <si>
     <t xml:space="preserve">16.7912845611572</t>
@@ -3902,10 +3902,10 @@
     <t xml:space="preserve">16.8467025756836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8097591400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5880889892578</t>
+    <t xml:space="preserve">16.809757232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5880870819092</t>
   </si>
   <si>
     <t xml:space="preserve">16.671215057373</t>
@@ -3914,43 +3914,43 @@
     <t xml:space="preserve">16.7635765075684</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7728118896484</t>
+    <t xml:space="preserve">16.7728137969971</t>
   </si>
   <si>
     <t xml:space="preserve">16.5234375</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7106580734253</t>
+    <t xml:space="preserve">15.710657119751</t>
   </si>
   <si>
     <t xml:space="preserve">16.0708656311035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0893383026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0062141418457</t>
+    <t xml:space="preserve">16.0893402099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0062160491943</t>
   </si>
   <si>
     <t xml:space="preserve">16.0523948669434</t>
   </si>
   <si>
+    <t xml:space="preserve">16.6896858215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4710884094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.632661819458</t>
+  </si>
+  <si>
     <t xml:space="preserve">16.6896877288818</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4710865020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.632661819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6896858215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6611766815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5946426391602</t>
+    <t xml:space="preserve">16.6611747741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5946445465088</t>
   </si>
   <si>
     <t xml:space="preserve">17.2124290466309</t>
@@ -3959,10 +3959,10 @@
     <t xml:space="preserve">17.5830993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">17.944263458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.820707321167</t>
+    <t xml:space="preserve">17.9442653656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8207092285156</t>
   </si>
   <si>
     <t xml:space="preserve">17.8302135467529</t>
@@ -3974,7 +3974,7 @@
     <t xml:space="preserve">16.9938259124756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5661296844482</t>
+    <t xml:space="preserve">16.5661315917969</t>
   </si>
   <si>
     <t xml:space="preserve">16.2809982299805</t>
@@ -3983,13 +3983,13 @@
     <t xml:space="preserve">16.204963684082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.00537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5871801376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7867727279663</t>
+    <t xml:space="preserve">16.0053730010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.58717918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.786771774292</t>
   </si>
   <si>
     <t xml:space="preserve">15.5681705474854</t>
@@ -4007,16 +4007,16 @@
     <t xml:space="preserve">15.3305606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6251974105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4541177749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8723115921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9958667755127</t>
+    <t xml:space="preserve">15.6251983642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4541187286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8723125457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9958686828613</t>
   </si>
   <si>
     <t xml:space="preserve">16.0623989105225</t>
@@ -4025,19 +4025,19 @@
     <t xml:space="preserve">15.7012319564819</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7772674560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8247900009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7487535476685</t>
+    <t xml:space="preserve">15.777268409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8247880935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7487545013428</t>
   </si>
   <si>
     <t xml:space="preserve">15.7392492294312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9388427734375</t>
+    <t xml:space="preserve">15.9388418197632</t>
   </si>
   <si>
     <t xml:space="preserve">16.1859569549561</t>
@@ -4046,7 +4046,7 @@
     <t xml:space="preserve">16.1574420928955</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8913192749023</t>
+    <t xml:space="preserve">15.8913202285767</t>
   </si>
   <si>
     <t xml:space="preserve">16.9177932739258</t>
@@ -4058,13 +4058,13 @@
     <t xml:space="preserve">17.0223407745361</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1649055480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.060359954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6231575012207</t>
+    <t xml:space="preserve">17.1649074554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0603580474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6231555938721</t>
   </si>
   <si>
     <t xml:space="preserve">16.7277050018311</t>
@@ -4079,7 +4079,7 @@
     <t xml:space="preserve">16.3000068664551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4996013641357</t>
+    <t xml:space="preserve">16.4995994567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.509105682373</t>
@@ -4106,16 +4106,16 @@
     <t xml:space="preserve">17.4215240478516</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3074722290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2599487304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8628063201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8818140029907</t>
+    <t xml:space="preserve">17.3074703216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2599506378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8628072738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.881814956665</t>
   </si>
   <si>
     <t xml:space="preserve">16.4235649108887</t>
@@ -4127,16 +4127,16 @@
     <t xml:space="preserve">16.1479377746582</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9103288650513</t>
+    <t xml:space="preserve">15.910327911377</t>
   </si>
   <si>
     <t xml:space="preserve">16.2429828643799</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8533020019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8437967300415</t>
+    <t xml:space="preserve">15.8533029556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8437976837158</t>
   </si>
   <si>
     <t xml:space="preserve">14.7793073654175</t>
@@ -4151,10 +4151,10 @@
     <t xml:space="preserve">14.4466543197632</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7222814559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6917285919189</t>
+    <t xml:space="preserve">14.7222805023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6917276382446</t>
   </si>
   <si>
     <t xml:space="preserve">15.4731273651123</t>
@@ -4166,7 +4166,7 @@
     <t xml:space="preserve">15.4921350479126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0929527282715</t>
+    <t xml:space="preserve">15.0929517745972</t>
   </si>
   <si>
     <t xml:space="preserve">15.4446144104004</t>
@@ -4196,7 +4196,7 @@
     <t xml:space="preserve">14.4846715927124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9313774108887</t>
+    <t xml:space="preserve">14.931378364563</t>
   </si>
   <si>
     <t xml:space="preserve">14.9218730926514</t>
@@ -4211,37 +4211,37 @@
     <t xml:space="preserve">14.731785774231</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0074129104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7677631378174</t>
+    <t xml:space="preserve">15.0074119567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7677640914917</t>
   </si>
   <si>
     <t xml:space="preserve">16.1954612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5566253662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.128927230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0528945922852</t>
+    <t xml:space="preserve">16.5566272735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1289291381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0528926849365</t>
   </si>
   <si>
     <t xml:space="preserve">16.3570346832275</t>
   </si>
   <si>
-    <t xml:space="preserve">16.433069229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7467155456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3665390014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3950500488281</t>
+    <t xml:space="preserve">16.4330711364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7467136383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3665370941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3950519561768</t>
   </si>
   <si>
     <t xml:space="preserve">16.4805908203125</t>
@@ -4256,10 +4256,10 @@
     <t xml:space="preserve">16.3285217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6136531829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6991901397705</t>
+    <t xml:space="preserve">16.6136512756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6991920471191</t>
   </si>
   <si>
     <t xml:space="preserve">16.5756359100342</t>
@@ -4268,22 +4268,22 @@
     <t xml:space="preserve">18.5240325927734</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7046165466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6475887298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1988430023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4839744567871</t>
+    <t xml:space="preserve">18.7046146392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.647590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.198844909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4839763641357</t>
   </si>
   <si>
     <t xml:space="preserve">19.5029830932617</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4649639129639</t>
+    <t xml:space="preserve">19.4649658203125</t>
   </si>
   <si>
     <t xml:space="preserve">19.2938861846924</t>
@@ -4292,10 +4292,10 @@
     <t xml:space="preserve">19.1037998199463</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2748794555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0277652740479</t>
+    <t xml:space="preserve">19.2748775482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0277633666992</t>
   </si>
   <si>
     <t xml:space="preserve">18.0868320465088</t>
@@ -4322,16 +4322,16 @@
     <t xml:space="preserve">17.9062480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7541790008545</t>
+    <t xml:space="preserve">17.7541770935059</t>
   </si>
   <si>
     <t xml:space="preserve">18.1818752288818</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9157543182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2103862762451</t>
+    <t xml:space="preserve">17.9157524108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2103881835938</t>
   </si>
   <si>
     <t xml:space="preserve">18.343448638916</t>
@@ -4346,16 +4346,16 @@
     <t xml:space="preserve">18.6570930480957</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5810585021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4289875030518</t>
+    <t xml:space="preserve">18.5810565948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4289894104004</t>
   </si>
   <si>
     <t xml:space="preserve">18.1913795471191</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0488147735596</t>
+    <t xml:space="preserve">18.0488128662109</t>
   </si>
   <si>
     <t xml:space="preserve">18.020299911499</t>
@@ -4373,7 +4373,7 @@
     <t xml:space="preserve">17.9632740020752</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0678215026855</t>
+    <t xml:space="preserve">18.0678234100342</t>
   </si>
   <si>
     <t xml:space="preserve">18.1723709106445</t>
@@ -4403,13 +4403,13 @@
     <t xml:space="preserve">17.8112030029297</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5165672302246</t>
+    <t xml:space="preserve">17.5165691375732</t>
   </si>
   <si>
     <t xml:space="preserve">17.5450801849365</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3169765472412</t>
+    <t xml:space="preserve">17.3169746398926</t>
   </si>
   <si>
     <t xml:space="preserve">17.3264808654785</t>
@@ -4430,10 +4430,10 @@
     <t xml:space="preserve">17.5545845031738</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7636833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8872394561768</t>
+    <t xml:space="preserve">17.7636814117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8872375488281</t>
   </si>
   <si>
     <t xml:space="preserve">18.1533622741699</t>
@@ -4442,19 +4442,19 @@
     <t xml:space="preserve">18.1628665924072</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3549957275391</t>
+    <t xml:space="preserve">17.3549938201904</t>
   </si>
   <si>
     <t xml:space="preserve">17.4690456390381</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4405345916748</t>
+    <t xml:space="preserve">17.4405326843262</t>
   </si>
   <si>
     <t xml:space="preserve">17.1078796386719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0413494110107</t>
+    <t xml:space="preserve">17.0413513183594</t>
   </si>
   <si>
     <t xml:space="preserve">16.9368019104004</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">16.4615821838379</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3095111846924</t>
+    <t xml:space="preserve">16.309513092041</t>
   </si>
   <si>
     <t xml:space="preserve">17.0033321380615</t>
@@ -4490,7 +4490,7 @@
     <t xml:space="preserve">17.6211185455322</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0107975006104</t>
+    <t xml:space="preserve">18.0107955932617</t>
   </si>
   <si>
     <t xml:space="preserve">17.7826900482178</t>
@@ -4505,7 +4505,7 @@
     <t xml:space="preserve">17.5355777740479</t>
   </si>
   <si>
-    <t xml:space="preserve">18.001293182373</t>
+    <t xml:space="preserve">18.0012912750244</t>
   </si>
   <si>
     <t xml:space="preserve">18.2674140930176</t>
@@ -70606,7 +70606,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6910416667</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>129995</v>
@@ -70627,6 +70627,32 @@
         <v>1766</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.691087963</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>39514</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>14.9300003051758</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>14.8900003433228</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>14.9300003051758</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>14.8900003433228</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>1776</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TNXT.MI.xlsx
+++ b/data/TNXT.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63493776321411</t>
+    <t xml:space="preserve">2.63493800163269</t>
   </si>
   <si>
     <t xml:space="preserve">TNXT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65150952339172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59350848197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5355064868927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52556347846985</t>
+    <t xml:space="preserve">2.6515097618103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59350872039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53550672531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52556371688843</t>
   </si>
   <si>
     <t xml:space="preserve">2.48579072952271</t>
@@ -62,181 +62,181 @@
     <t xml:space="preserve">2.52722072601318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48744821548462</t>
+    <t xml:space="preserve">2.4874484539032</t>
   </si>
   <si>
     <t xml:space="preserve">2.47087597846985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46921873092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54047870635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49739122390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47916197776794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44436049461365</t>
+    <t xml:space="preserve">2.46921849250793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54047822952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49739098548889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4791624546051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44436097145081</t>
   </si>
   <si>
     <t xml:space="preserve">2.39464497566223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34161496162415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36150121688843</t>
+    <t xml:space="preserve">2.34161448478699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36150097846985</t>
   </si>
   <si>
     <t xml:space="preserve">2.55207872390747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58522272109985</t>
+    <t xml:space="preserve">2.58522248268127</t>
   </si>
   <si>
     <t xml:space="preserve">2.6100800037384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56865048408508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63659477233887</t>
+    <t xml:space="preserve">2.56865096092224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63659501075745</t>
   </si>
   <si>
     <t xml:space="preserve">2.68962526321411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73436975479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72608327865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77579975128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58025097846985</t>
+    <t xml:space="preserve">2.73436951637268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72608351707458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77579951286316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58025121688843</t>
   </si>
   <si>
     <t xml:space="preserve">2.56202220916748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66808176040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62830901145935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64322328567505</t>
+    <t xml:space="preserve">2.66808128356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62830853462219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64322352409363</t>
   </si>
   <si>
     <t xml:space="preserve">2.60842251777649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66642427444458</t>
+    <t xml:space="preserve">2.66642451286316</t>
   </si>
   <si>
     <t xml:space="preserve">2.65316700935364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62665200233459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69293975830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82551550865173</t>
+    <t xml:space="preserve">2.62665176391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6929395198822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82551527023315</t>
   </si>
   <si>
     <t xml:space="preserve">2.81722927093506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90008950233459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85865950584412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89843249320984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8835175037384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87523102760315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86694502830505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81888675689697</t>
+    <t xml:space="preserve">2.90008926391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85865926742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89843225479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88351774215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87523150444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86694550514221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81888628005981</t>
   </si>
   <si>
     <t xml:space="preserve">2.82054400444031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85368776321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79237151145935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85700225830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90671801567078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82882976531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85037350654602</t>
+    <t xml:space="preserve">2.85368800163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79237103462219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85700249671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90671825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8288300037384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85037326812744</t>
   </si>
   <si>
     <t xml:space="preserve">2.90837526321411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96306300163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95797729492188</t>
+    <t xml:space="preserve">2.96306252479553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95797753334045</t>
   </si>
   <si>
     <t xml:space="preserve">2.88169693946838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89017271995544</t>
+    <t xml:space="preserve">2.89017248153687</t>
   </si>
   <si>
     <t xml:space="preserve">2.86474561691284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94950199127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92407512664795</t>
+    <t xml:space="preserve">2.94950222969055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92407488822937</t>
   </si>
   <si>
     <t xml:space="preserve">2.96645307540894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11901307106018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9427216053009</t>
+    <t xml:space="preserve">3.11901259422302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94272112846375</t>
   </si>
   <si>
     <t xml:space="preserve">2.94780683517456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8833920955658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87322187423706</t>
+    <t xml:space="preserve">2.88339185714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87322163581848</t>
   </si>
   <si>
     <t xml:space="preserve">2.85966062545776</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">3.03256273269653</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07037353515625</t>
+    <t xml:space="preserve">3.07037329673767</t>
   </si>
   <si>
     <t xml:space="preserve">3.06866312026978</t>
@@ -257,37 +257,37 @@
     <t xml:space="preserve">2.99340057373047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98484802246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93524265289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98313689231873</t>
+    <t xml:space="preserve">2.98484826087952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93524289131165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98313736915588</t>
   </si>
   <si>
     <t xml:space="preserve">2.92498016357422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92326927185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9677426815033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0361635684967</t>
+    <t xml:space="preserve">2.92326951026917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96774291992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03616309165955</t>
   </si>
   <si>
     <t xml:space="preserve">3.05840015411377</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05497908592224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08747863769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13879442214966</t>
+    <t xml:space="preserve">3.05497932434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08747887611389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13879418373108</t>
   </si>
   <si>
     <t xml:space="preserve">3.12853121757507</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">3.15589952468872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12339949607849</t>
+    <t xml:space="preserve">3.12339973449707</t>
   </si>
   <si>
     <t xml:space="preserve">3.12511038780212</t>
@@ -311,58 +311,58 @@
     <t xml:space="preserve">3.16445207595825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16616249084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24142527580261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30129313468933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3868191242218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48431825637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52708077430725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62629079818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63655376434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64510655403137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74602699279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67760634422302</t>
+    <t xml:space="preserve">3.16616225242615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24142503738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30129289627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38681864738464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48431777954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52708148956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6262903213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63655352592468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64510679244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74602651596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6776065826416</t>
   </si>
   <si>
     <t xml:space="preserve">3.71181654930115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63484382629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51681756973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50484466552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49458074569702</t>
+    <t xml:space="preserve">3.63484334945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51681780815125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50484442710876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49458122253418</t>
   </si>
   <si>
     <t xml:space="preserve">3.50655484199524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48089694976807</t>
+    <t xml:space="preserve">3.48089718818665</t>
   </si>
   <si>
     <t xml:space="preserve">3.43129229545593</t>
@@ -371,91 +371,91 @@
     <t xml:space="preserve">3.35602951049805</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60063290596008</t>
+    <t xml:space="preserve">3.60063314437866</t>
   </si>
   <si>
     <t xml:space="preserve">3.64681673049927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69471216201782</t>
+    <t xml:space="preserve">3.69471168518066</t>
   </si>
   <si>
     <t xml:space="preserve">3.69984316825867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67589592933655</t>
+    <t xml:space="preserve">3.67589569091797</t>
   </si>
   <si>
     <t xml:space="preserve">3.66563272476196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59721255302429</t>
+    <t xml:space="preserve">3.59721231460571</t>
   </si>
   <si>
     <t xml:space="preserve">3.63313293457031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57497549057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66050124168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68615889549255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71523714065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73747420310974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71010637283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69129061698914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68958020210266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73234248161316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7203688621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76313209533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77168416976929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62115955352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64168524742126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7032642364502</t>
+    <t xml:space="preserve">3.57497501373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66050148010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6861584186554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7152373790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73747444152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71010661125183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69129085540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68957996368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73234272003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72036933898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76313161849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77168440818787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62115907669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64168548583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70326375961304</t>
   </si>
   <si>
     <t xml:space="preserve">3.7973427772522</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75457954406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9085259437561</t>
+    <t xml:space="preserve">3.75457906723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90852618217468</t>
   </si>
   <si>
     <t xml:space="preserve">3.76655268669128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72892141342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66734385490417</t>
+    <t xml:space="preserve">3.72892189025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66734337806702</t>
   </si>
   <si>
     <t xml:space="preserve">3.50997614860535</t>
@@ -476,49 +476,49 @@
     <t xml:space="preserve">3.43642377853394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53221297264099</t>
+    <t xml:space="preserve">3.53221273422241</t>
   </si>
   <si>
     <t xml:space="preserve">3.5185284614563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46037101745605</t>
+    <t xml:space="preserve">3.46037125587463</t>
   </si>
   <si>
     <t xml:space="preserve">3.50142312049866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53563332557678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55615997314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64339661598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72550058364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84865784645081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82984209060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83155226707458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87089419364929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84523630142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87431573867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86405301094055</t>
+    <t xml:space="preserve">3.53563356399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55615973472595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64339590072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72550106048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84865808486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82984232902527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83155298233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87089490890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84523701667786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87431645393372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86405324935913</t>
   </si>
   <si>
     <t xml:space="preserve">3.85721063613892</t>
@@ -527,31 +527,31 @@
     <t xml:space="preserve">3.82471084594727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90681552886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00260496139526</t>
+    <t xml:space="preserve">3.90681505203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00260448455811</t>
   </si>
   <si>
     <t xml:space="preserve">4.17536592483521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11378812789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00773572921753</t>
+    <t xml:space="preserve">4.11378717422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00773525238037</t>
   </si>
   <si>
     <t xml:space="preserve">4.0522084236145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08128786087036</t>
+    <t xml:space="preserve">4.08128690719604</t>
   </si>
   <si>
     <t xml:space="preserve">4.00602436065674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09839200973511</t>
+    <t xml:space="preserve">4.09839344024658</t>
   </si>
   <si>
     <t xml:space="preserve">4.01970911026001</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">4.01115655899048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99576210975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03510427474976</t>
+    <t xml:space="preserve">3.99576187133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0351037979126</t>
   </si>
   <si>
     <t xml:space="preserve">4.06247234344482</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">4.13773488998413</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12234020233154</t>
+    <t xml:space="preserve">4.1223406791687</t>
   </si>
   <si>
     <t xml:space="preserve">4.14799737930298</t>
@@ -587,16 +587,16 @@
     <t xml:space="preserve">4.22839212417603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20615530014038</t>
+    <t xml:space="preserve">4.20615577697754</t>
   </si>
   <si>
     <t xml:space="preserve">4.0214204788208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99405121803284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01799869537354</t>
+    <t xml:space="preserve">3.99405169487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01799917221069</t>
   </si>
   <si>
     <t xml:space="preserve">4.02655172348022</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">4.07615613937378</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12747144699097</t>
+    <t xml:space="preserve">4.12747192382812</t>
   </si>
   <si>
     <t xml:space="preserve">4.11891937255859</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">4.09668207168579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10181379318237</t>
+    <t xml:space="preserve">4.10181427001953</t>
   </si>
   <si>
     <t xml:space="preserve">4.0710244178772</t>
@@ -626,10 +626,10 @@
     <t xml:space="preserve">4.09497213363647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13089227676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21641874313354</t>
+    <t xml:space="preserve">4.13089275360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2164192199707</t>
   </si>
   <si>
     <t xml:space="preserve">4.52431106567383</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">4.56707429885864</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62266540527344</t>
+    <t xml:space="preserve">4.6226658821106</t>
   </si>
   <si>
     <t xml:space="preserve">4.63549470901489</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58417892456055</t>
+    <t xml:space="preserve">4.58417940139771</t>
   </si>
   <si>
     <t xml:space="preserve">4.60128402709961</t>
@@ -665,22 +665,22 @@
     <t xml:space="preserve">4.57562637329102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61838960647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53286409378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55852079391479</t>
+    <t xml:space="preserve">4.61838912963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53286361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55852127075195</t>
   </si>
   <si>
     <t xml:space="preserve">4.48154783248901</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5157585144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49010038375854</t>
+    <t xml:space="preserve">4.51575899124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49010133743286</t>
   </si>
   <si>
     <t xml:space="preserve">4.51148223876953</t>
@@ -689,73 +689,73 @@
     <t xml:space="preserve">4.63121843338013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78516435623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75950717926025</t>
+    <t xml:space="preserve">4.78516483306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75950765609741</t>
   </si>
   <si>
     <t xml:space="preserve">4.78944110870361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73384952545166</t>
+    <t xml:space="preserve">4.7338490486145</t>
   </si>
   <si>
     <t xml:space="preserve">4.77233552932739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76378345489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65687561035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69536256790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82792711257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90062427520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91772937774658</t>
+    <t xml:space="preserve">4.76378297805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65687608718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69536209106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8279275894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90062379837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91772890090942</t>
   </si>
   <si>
     <t xml:space="preserve">4.94338703155518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98614978790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04174137115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02036046981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0716757774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08022880554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99470329284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09305667877197</t>
+    <t xml:space="preserve">4.98615026473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04174184799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02035999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07167530059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08022737503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99470233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09305715560913</t>
   </si>
   <si>
     <t xml:space="preserve">5.06050682067871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91728448867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94766616821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92596483230591</t>
+    <t xml:space="preserve">4.91728544235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94766521453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92596530914307</t>
   </si>
   <si>
     <t xml:space="preserve">4.9042649269104</t>
@@ -767,79 +767,79 @@
     <t xml:space="preserve">4.73500299453735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72198295593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59178066253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64386081695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73066234588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66556215286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6525411605835</t>
+    <t xml:space="preserve">4.7219820022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59178113937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64386177062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73066186904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66556167602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65254163742065</t>
   </si>
   <si>
     <t xml:space="preserve">4.60914039611816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65688133239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54837989807129</t>
+    <t xml:space="preserve">4.65688180923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54837942123413</t>
   </si>
   <si>
     <t xml:space="preserve">4.53535985946655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47025966644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59612131118774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47459936141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48761940002441</t>
+    <t xml:space="preserve">4.47025871276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59612083435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47459888458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48761987686157</t>
   </si>
   <si>
     <t xml:space="preserve">4.46157884597778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41383790969849</t>
+    <t xml:space="preserve">4.41383838653564</t>
   </si>
   <si>
     <t xml:space="preserve">4.38779783248901</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39213848114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40949773788452</t>
+    <t xml:space="preserve">4.39213752746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40949821472168</t>
   </si>
   <si>
     <t xml:space="preserve">4.55706024169922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52234029769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57008075714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53970003128052</t>
+    <t xml:space="preserve">4.52233982086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57007932662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53970050811768</t>
   </si>
   <si>
     <t xml:space="preserve">4.47893953323364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43553829193115</t>
+    <t xml:space="preserve">4.43553876876831</t>
   </si>
   <si>
     <t xml:space="preserve">4.42251825332642</t>
@@ -848,10 +848,10 @@
     <t xml:space="preserve">4.43119859695435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45289897918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51365900039673</t>
+    <t xml:space="preserve">4.45289850234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51365947723389</t>
   </si>
   <si>
     <t xml:space="preserve">4.68726205825806</t>
@@ -860,22 +860,22 @@
     <t xml:space="preserve">4.60046100616455</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6395206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56139993667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58744096755981</t>
+    <t xml:space="preserve">4.63952159881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56140041351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58744049072266</t>
   </si>
   <si>
     <t xml:space="preserve">4.61782121658325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64820098876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6048002243042</t>
+    <t xml:space="preserve">4.64820146560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60480117797852</t>
   </si>
   <si>
     <t xml:space="preserve">4.58310127258301</t>
@@ -887,61 +887,61 @@
     <t xml:space="preserve">4.50497913360596</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42685794830322</t>
+    <t xml:space="preserve">4.42685890197754</t>
   </si>
   <si>
     <t xml:space="preserve">4.49195909500122</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51800012588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80878353118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77840328216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84784317016602</t>
+    <t xml:space="preserve">4.51799964904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80878305435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77840280532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84784412384033</t>
   </si>
   <si>
     <t xml:space="preserve">4.8348240852356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74368286132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81312370300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71330213546753</t>
+    <t xml:space="preserve">4.74368333816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81312417984009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71330261230469</t>
   </si>
   <si>
     <t xml:space="preserve">4.70462226867676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72632265090942</t>
+    <t xml:space="preserve">4.72632217407227</t>
   </si>
   <si>
     <t xml:space="preserve">4.69594192504883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7697229385376</t>
+    <t xml:space="preserve">4.76972341537476</t>
   </si>
   <si>
     <t xml:space="preserve">4.84350395202637</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87822389602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8738842010498</t>
+    <t xml:space="preserve">4.87822437286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87388467788696</t>
   </si>
   <si>
     <t xml:space="preserve">4.97370576858521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97804546356201</t>
+    <t xml:space="preserve">4.97804594039917</t>
   </si>
   <si>
     <t xml:space="preserve">5.00842618942261</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">5.04314661026001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14730834960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86086463928223</t>
+    <t xml:space="preserve">5.14730787277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86086368560791</t>
   </si>
   <si>
     <t xml:space="preserve">4.86954498291016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96502542495728</t>
+    <t xml:space="preserve">4.96502494812012</t>
   </si>
   <si>
     <t xml:space="preserve">4.90860557556152</t>
@@ -971,19 +971,19 @@
     <t xml:space="preserve">4.99974632263184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99106502532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1559886932373</t>
+    <t xml:space="preserve">4.99106597900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15598821640015</t>
   </si>
   <si>
     <t xml:space="preserve">5.12994718551636</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29487037658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41639137268066</t>
+    <t xml:space="preserve">5.2948694229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41639184951782</t>
   </si>
   <si>
     <t xml:space="preserve">5.48583269119263</t>
@@ -992,13 +992,13 @@
     <t xml:space="preserve">5.43375205993652</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4814920425415</t>
+    <t xml:space="preserve">5.48149299621582</t>
   </si>
   <si>
     <t xml:space="preserve">5.42073154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">5.394690990448</t>
+    <t xml:space="preserve">5.39469146728516</t>
   </si>
   <si>
     <t xml:space="preserve">5.35563087463379</t>
@@ -1007,31 +1007,31 @@
     <t xml:space="preserve">5.33393049240112</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37299060821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33827114105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20806789398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16466808319092</t>
+    <t xml:space="preserve">5.37299108505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33826971054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20806884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16466856002808</t>
   </si>
   <si>
     <t xml:space="preserve">5.26448965072632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25146961212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26014947891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18636846542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20372867584229</t>
+    <t xml:space="preserve">5.25147008895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2601490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18636894226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20372915267944</t>
   </si>
   <si>
     <t xml:space="preserve">5.19504880905151</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">5.16900825500488</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18202829360962</t>
+    <t xml:space="preserve">5.1820273399353</t>
   </si>
   <si>
     <t xml:space="preserve">5.19938850402832</t>
@@ -1061,19 +1061,19 @@
     <t xml:space="preserve">5.7115159034729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78963661193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82435655593872</t>
+    <t xml:space="preserve">5.78963613510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82435703277588</t>
   </si>
   <si>
     <t xml:space="preserve">5.87643814086914</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88511800765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93719863891602</t>
+    <t xml:space="preserve">5.88511848449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93719911575317</t>
   </si>
   <si>
     <t xml:space="preserve">5.85907745361328</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">5.92851829528809</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9719181060791</t>
+    <t xml:space="preserve">5.97191905975342</t>
   </si>
   <si>
     <t xml:space="preserve">5.95455884933472</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">6.03268003463745</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1715612411499</t>
+    <t xml:space="preserve">6.17156219482422</t>
   </si>
   <si>
     <t xml:space="preserve">6.28440284729004</t>
@@ -1103,28 +1103,28 @@
     <t xml:space="preserve">6.01531934738159</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02399969100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21496152877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14552211761475</t>
+    <t xml:space="preserve">6.02399921417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21496200561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14552116394043</t>
   </si>
   <si>
     <t xml:space="preserve">6.40592479705811</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07608032226562</t>
+    <t xml:space="preserve">6.07607984542847</t>
   </si>
   <si>
     <t xml:space="preserve">5.98927927017212</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04135990142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22364187240601</t>
+    <t xml:space="preserve">6.04136037826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22364234924316</t>
   </si>
   <si>
     <t xml:space="preserve">6.13684129714966</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">6.19760179519653</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15420150756836</t>
+    <t xml:space="preserve">6.1542010307312</t>
   </si>
   <si>
     <t xml:space="preserve">6.05003976821899</t>
@@ -1142,70 +1142,70 @@
     <t xml:space="preserve">5.89379787445068</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90247821807861</t>
+    <t xml:space="preserve">5.90247774124146</t>
   </si>
   <si>
     <t xml:space="preserve">5.70283555984497</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50319290161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58131313323975</t>
+    <t xml:space="preserve">5.50319337844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58131408691406</t>
   </si>
   <si>
     <t xml:space="preserve">5.72019624710083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.763596534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91983890533447</t>
+    <t xml:space="preserve">5.76359605789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91983795166016</t>
   </si>
   <si>
     <t xml:space="preserve">5.99795913696289</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83303594589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79831647872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65943431854248</t>
+    <t xml:space="preserve">5.83303785324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79831600189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6594352722168</t>
   </si>
   <si>
     <t xml:space="preserve">5.5118727684021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5465931892395</t>
+    <t xml:space="preserve">5.54659366607666</t>
   </si>
   <si>
     <t xml:space="preserve">5.58999347686768</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52055311203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38167095184326</t>
+    <t xml:space="preserve">5.52055358886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38167190551758</t>
   </si>
   <si>
     <t xml:space="preserve">5.44243192672729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46847200393677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67679500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6420750617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55527353286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53791379928589</t>
+    <t xml:space="preserve">5.46847248077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6767954826355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64207458496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55527400970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53791332244873</t>
   </si>
   <si>
     <t xml:space="preserve">5.57263374328613</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">5.39903116226196</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39035129547119</t>
+    <t xml:space="preserve">5.39035177230835</t>
   </si>
   <si>
     <t xml:space="preserve">5.45111227035522</t>
@@ -1226,16 +1226,16 @@
     <t xml:space="preserve">6.09344100952148</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81567621231079</t>
+    <t xml:space="preserve">5.81567668914795</t>
   </si>
   <si>
     <t xml:space="preserve">5.77227640151978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73755598068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40771102905273</t>
+    <t xml:space="preserve">5.73755645751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40771198272705</t>
   </si>
   <si>
     <t xml:space="preserve">5.24278926849365</t>
@@ -1247,19 +1247,19 @@
     <t xml:space="preserve">4.98238515853882</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07618808746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1561975479126</t>
+    <t xml:space="preserve">5.07618761062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15619802474976</t>
   </si>
   <si>
     <t xml:space="preserve">5.0850772857666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24509859085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11174821853638</t>
+    <t xml:space="preserve">5.24509763717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11174774169922</t>
   </si>
   <si>
     <t xml:space="preserve">5.13841772079468</t>
@@ -1268,22 +1268,22 @@
     <t xml:space="preserve">5.20953798294067</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06729745864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05840826034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04062843322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0495171546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94283771514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77392816543579</t>
+    <t xml:space="preserve">5.06729793548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0584077835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04062795639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04951810836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94283723831177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77392768859863</t>
   </si>
   <si>
     <t xml:space="preserve">4.90727806091309</t>
@@ -1292,10 +1292,10 @@
     <t xml:space="preserve">4.76503801345825</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92505836486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88949823379517</t>
+    <t xml:space="preserve">4.92505741119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88949775695801</t>
   </si>
   <si>
     <t xml:space="preserve">5.02284812927246</t>
@@ -1304,25 +1304,25 @@
     <t xml:space="preserve">4.97839736938477</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91616868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95172786712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9339485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89838838577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80948829650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78281784057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75614786148071</t>
+    <t xml:space="preserve">4.91616821289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95172834396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93394804000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89838790893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80948781967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78281831741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75614833831787</t>
   </si>
   <si>
     <t xml:space="preserve">4.98728847503662</t>
@@ -1340,76 +1340,76 @@
     <t xml:space="preserve">5.21842765808105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27176713943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33399820327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23620796203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18286752700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01395797729492</t>
+    <t xml:space="preserve">5.27176761627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33399772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23620748519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18286800384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01395845413208</t>
   </si>
   <si>
     <t xml:space="preserve">4.99617767333984</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00506830215454</t>
+    <t xml:space="preserve">5.00506782531738</t>
   </si>
   <si>
     <t xml:space="preserve">5.37844848632812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47623729705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56513833999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6807074546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6540379524231</t>
+    <t xml:space="preserve">5.47623777389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56513786315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68070793151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65403842926025</t>
   </si>
   <si>
     <t xml:space="preserve">5.63625812530518</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55624771118164</t>
+    <t xml:space="preserve">5.5562481880188</t>
   </si>
   <si>
     <t xml:space="preserve">5.68959808349609</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96518707275391</t>
+    <t xml:space="preserve">5.96518754959106</t>
   </si>
   <si>
     <t xml:space="preserve">5.89406776428223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77849721908569</t>
+    <t xml:space="preserve">5.77849769592285</t>
   </si>
   <si>
     <t xml:space="preserve">5.84072780609131</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76071739196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92073726654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83183670043945</t>
+    <t xml:space="preserve">5.76071786880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92073774337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83183717727661</t>
   </si>
   <si>
     <t xml:space="preserve">5.4495677947998</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58291864395142</t>
+    <t xml:space="preserve">5.58291816711426</t>
   </si>
   <si>
     <t xml:space="preserve">5.43178796768188</t>
@@ -1418,67 +1418,67 @@
     <t xml:space="preserve">5.36955785751343</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60958766937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86739730834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78738832473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52068758010864</t>
+    <t xml:space="preserve">5.60958814620972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86739778518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78738784790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5206880569458</t>
   </si>
   <si>
     <t xml:space="preserve">5.49401760101318</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57402801513672</t>
+    <t xml:space="preserve">5.57402753829956</t>
   </si>
   <si>
     <t xml:space="preserve">5.59180784225464</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6451473236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71626758575439</t>
+    <t xml:space="preserve">5.64514780044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71626806259155</t>
   </si>
   <si>
     <t xml:space="preserve">5.73404741287231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81405735015869</t>
+    <t xml:space="preserve">5.81405830383301</t>
   </si>
   <si>
     <t xml:space="preserve">5.67181777954102</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5117974281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85850763320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66292762756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53846740722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90295791625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79627752304077</t>
+    <t xml:space="preserve">5.51179838180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85850811004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66292810440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53846836090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90295743942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79627799987793</t>
   </si>
   <si>
     <t xml:space="preserve">5.80516767501831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61847734451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46734809875488</t>
+    <t xml:space="preserve">5.6184778213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46734714508057</t>
   </si>
   <si>
     <t xml:space="preserve">5.60069799423218</t>
@@ -1490,10 +1490,10 @@
     <t xml:space="preserve">5.50290775299072</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34288740158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62736797332764</t>
+    <t xml:space="preserve">5.34288787841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62736749649048</t>
   </si>
   <si>
     <t xml:space="preserve">5.52957773208618</t>
@@ -1508,37 +1508,37 @@
     <t xml:space="preserve">5.70737791061401</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69848823547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0007472038269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92962789535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94740724563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93851661682129</t>
+    <t xml:space="preserve">5.69848775863647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00074768066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92962741851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94740772247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93851709365845</t>
   </si>
   <si>
     <t xml:space="preserve">5.99185705184937</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24077749252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40968799591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48080778121948</t>
+    <t xml:space="preserve">6.24077796936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40968704223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48080730438232</t>
   </si>
   <si>
     <t xml:space="preserve">6.623046875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84529733657837</t>
+    <t xml:space="preserve">6.84529685974121</t>
   </si>
   <si>
     <t xml:space="preserve">6.99642658233643</t>
@@ -1547,10 +1547,10 @@
     <t xml:space="preserve">7.0142068862915</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90752744674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91641807556152</t>
+    <t xml:space="preserve">6.90752696990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91641712188721</t>
   </si>
   <si>
     <t xml:space="preserve">6.97864675521851</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">7.00531721115112</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02309703826904</t>
+    <t xml:space="preserve">7.0230975151062</t>
   </si>
   <si>
     <t xml:space="preserve">7.24534702301025</t>
@@ -1568,55 +1568,55 @@
     <t xml:space="preserve">7.27201700210571</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33424663543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47648668289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76985549926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73429584503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72540664672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79652786254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80541706085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22324752807617</t>
+    <t xml:space="preserve">7.33424758911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.476487159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76985645294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73429679870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72540760040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79652643203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80541658401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22324562072754</t>
   </si>
   <si>
     <t xml:space="preserve">8.21435642242432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15212535858154</t>
+    <t xml:space="preserve">8.15212631225586</t>
   </si>
   <si>
     <t xml:space="preserve">8.12545776367188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00099658966064</t>
+    <t xml:space="preserve">8.00099754333496</t>
   </si>
   <si>
     <t xml:space="preserve">8.17879676818848</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34770584106445</t>
+    <t xml:space="preserve">8.34770679473877</t>
   </si>
   <si>
     <t xml:space="preserve">8.42771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48105621337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46327781677246</t>
+    <t xml:space="preserve">8.48105525970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46327686309814</t>
   </si>
   <si>
     <t xml:space="preserve">8.52550601959229</t>
@@ -1631,106 +1631,106 @@
     <t xml:space="preserve">8.8010950088501</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88999652862549</t>
+    <t xml:space="preserve">8.88999557495117</t>
   </si>
   <si>
     <t xml:space="preserve">9.19225692749023</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37005615234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47673606872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49451541900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31671619415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15669631958008</t>
+    <t xml:space="preserve">9.37005710601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47673511505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49451637268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31671524047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15669536590576</t>
   </si>
   <si>
     <t xml:space="preserve">9.35227680206299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40561580657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69009590148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86789703369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83233737945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77899646759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44117450714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.210036277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58341693878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51229572296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67231464385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85011672973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0990343093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0279159545898</t>
+    <t xml:space="preserve">9.40561676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69009494781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86789608001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83233642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77899551391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44117546081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21003532409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58341598510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51229667663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67231559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8501148223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0990362167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0279169082642</t>
   </si>
   <si>
     <t xml:space="preserve">9.99235534667969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0101366043091</t>
+    <t xml:space="preserve">10.0101356506348</t>
   </si>
   <si>
     <t xml:space="preserve">9.76121616363525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88567543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2234964370728</t>
+    <t xml:space="preserve">9.88567447662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2234954833984</t>
   </si>
   <si>
     <t xml:space="preserve">10.4368553161621</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6679964065552</t>
+    <t xml:space="preserve">10.6679954528809</t>
   </si>
   <si>
     <t xml:space="preserve">11.414755821228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3614149093628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3080759048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4325351715088</t>
+    <t xml:space="preserve">11.3614158630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3080768585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4325361251831</t>
   </si>
   <si>
     <t xml:space="preserve">11.6814556121826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.894814491272</t>
+    <t xml:space="preserve">11.8948154449463</t>
   </si>
   <si>
     <t xml:space="preserve">11.965934753418</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">12.1437349319458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6281147003174</t>
+    <t xml:space="preserve">11.628116607666</t>
   </si>
   <si>
     <t xml:space="preserve">11.4001131057739</t>
@@ -1754,22 +1754,22 @@
     <t xml:space="preserve">11.689640045166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.123929977417</t>
+    <t xml:space="preserve">12.1239280700684</t>
   </si>
   <si>
     <t xml:space="preserve">11.7982120513916</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1782169342041</t>
+    <t xml:space="preserve">12.1782159805298</t>
   </si>
   <si>
     <t xml:space="preserve">12.3229789733887</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9925098419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8296518325806</t>
+    <t xml:space="preserve">12.9925088882446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8296508789062</t>
   </si>
   <si>
     <t xml:space="preserve">12.7391738891602</t>
@@ -1781,16 +1781,16 @@
     <t xml:space="preserve">12.3953609466553</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2867879867554</t>
+    <t xml:space="preserve">12.2867889404297</t>
   </si>
   <si>
     <t xml:space="preserve">12.6306018829346</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4496469497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2144060134888</t>
+    <t xml:space="preserve">12.4496479034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2144079208374</t>
   </si>
   <si>
     <t xml:space="preserve">12.1058349609375</t>
@@ -1802,46 +1802,46 @@
     <t xml:space="preserve">11.9067850112915</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4724960327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4182090759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5810680389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8524990081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0877380371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8344020843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.888689994812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4363050460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3277311325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734460830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1829671859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1648721694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8391542434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6401062011719</t>
+    <t xml:space="preserve">11.4724950790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4182081222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5810670852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.852499961853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0877389907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8344030380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8886890411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4363040924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3277320861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734451293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1829681396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1648731231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8391551971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6401052474976</t>
   </si>
   <si>
     <t xml:space="preserve">10.6762971878052</t>
@@ -1850,19 +1850,19 @@
     <t xml:space="preserve">10.5134382247925</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9115371704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.291540145874</t>
+    <t xml:space="preserve">10.9115381240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2915391921997</t>
   </si>
   <si>
     <t xml:space="preserve">11.1467761993408</t>
   </si>
   <si>
-    <t xml:space="preserve">10.766773223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1105852127075</t>
+    <t xml:space="preserve">10.7667722702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1105861663818</t>
   </si>
   <si>
     <t xml:space="preserve">11.1286821365356</t>
@@ -1871,10 +1871,10 @@
     <t xml:space="preserve">10.6220092773438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0020132064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6039142608643</t>
+    <t xml:space="preserve">11.0020122528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6039152145386</t>
   </si>
   <si>
     <t xml:space="preserve">10.4953422546387</t>
@@ -1886,7 +1886,7 @@
     <t xml:space="preserve">10.3143882751465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.898193359375</t>
+    <t xml:space="preserve">9.89819240570068</t>
   </si>
   <si>
     <t xml:space="preserve">9.9343843460083</t>
@@ -1895,22 +1895,22 @@
     <t xml:space="preserve">9.80771636962891</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68104839324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95247936248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2420063018799</t>
+    <t xml:space="preserve">9.6810474395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95248031616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2420072555542</t>
   </si>
   <si>
     <t xml:space="preserve">10.4772462844849</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3867683410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4410552978516</t>
+    <t xml:space="preserve">10.3867702484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4410562515259</t>
   </si>
   <si>
     <t xml:space="preserve">9.55438041687012</t>
@@ -1919,25 +1919,25 @@
     <t xml:space="preserve">10.1153383255005</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3505783081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4048643112183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7486791610718</t>
+    <t xml:space="preserve">10.3505792617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4048633575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7486782073975</t>
   </si>
   <si>
     <t xml:space="preserve">11.0201101303101</t>
   </si>
   <si>
-    <t xml:space="preserve">10.857250213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8753452301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5858201980591</t>
+    <t xml:space="preserve">10.8572492599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8753461837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5858192443848</t>
   </si>
   <si>
     <t xml:space="preserve">10.8029642105103</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">10.7848691940308</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2372550964355</t>
+    <t xml:space="preserve">11.2372541427612</t>
   </si>
   <si>
     <t xml:space="preserve">11.3096361160278</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">11.4543991088867</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7258310317993</t>
+    <t xml:space="preserve">11.725830078125</t>
   </si>
   <si>
     <t xml:space="preserve">11.9972620010376</t>
@@ -1973,43 +1973,43 @@
     <t xml:space="preserve">12.0334529876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9429759979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.762020111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9477272033691</t>
+    <t xml:space="preserve">11.9429750442505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7620220184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9477281570435</t>
   </si>
   <si>
     <t xml:space="preserve">10.9658231735229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1877193450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98867130279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0429573059082</t>
+    <t xml:space="preserve">10.1877202987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98867034912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0429563522339</t>
   </si>
   <si>
     <t xml:space="preserve">9.91628932952881</t>
   </si>
   <si>
-    <t xml:space="preserve">10.169623374939</t>
+    <t xml:space="preserve">10.1696243286133</t>
   </si>
   <si>
     <t xml:space="preserve">10.5315341949463</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4229602813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1334342956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.332483291626</t>
+    <t xml:space="preserve">10.4229612350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.13343334198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3324823379517</t>
   </si>
   <si>
     <t xml:space="preserve">10.2239112854004</t>
@@ -2030,61 +2030,61 @@
     <t xml:space="preserve">11.056300163269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8934412002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5496282577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3686742782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8258113861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77152538299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.699143409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51818943023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71723747253418</t>
+    <t xml:space="preserve">10.8934421539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5496273040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3686752319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82581043243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77152633666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69914436340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51819038391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71723937988281</t>
   </si>
   <si>
     <t xml:space="preserve">9.42771244049072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59057140350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3639230728149</t>
+    <t xml:space="preserve">9.59057235717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3639221191406</t>
   </si>
   <si>
     <t xml:space="preserve">11.9791660308838</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4677410125732</t>
+    <t xml:space="preserve">12.4677419662476</t>
   </si>
   <si>
     <t xml:space="preserve">12.3772659301758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3820171356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5629711151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6172580718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.092490196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6943922042847</t>
+    <t xml:space="preserve">11.3820180892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5629720687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6172590255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0924921035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.694390296936</t>
   </si>
   <si>
     <t xml:space="preserve">9.62676239013672</t>
@@ -2096,7 +2096,7 @@
     <t xml:space="preserve">8.68580055236816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43246459960938</t>
+    <t xml:space="preserve">8.43246364593506</t>
   </si>
   <si>
     <t xml:space="preserve">7.0481653213501</t>
@@ -2108,19 +2108,19 @@
     <t xml:space="preserve">7.24721479415894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18388080596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58673238754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65006542205811</t>
+    <t xml:space="preserve">7.1838812828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58673286437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65006589889526</t>
   </si>
   <si>
     <t xml:space="preserve">6.96673583984375</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9757833480835</t>
+    <t xml:space="preserve">6.97578382492065</t>
   </si>
   <si>
     <t xml:space="preserve">7.16578531265259</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">7.28340530395508</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60912370681763</t>
+    <t xml:space="preserve">7.60912227630615</t>
   </si>
   <si>
     <t xml:space="preserve">7.76293420791626</t>
@@ -2144,49 +2144,49 @@
     <t xml:space="preserve">8.04341316223145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61341953277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41436958312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25151062011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93008804321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35533046722412</t>
+    <t xml:space="preserve">8.61341857910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41436862945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25150966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93008899688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35533142089844</t>
   </si>
   <si>
     <t xml:space="preserve">9.04770946502686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26485347747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50009346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86200332641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2191591262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9839181900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6582002639771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9705753326416</t>
+    <t xml:space="preserve">9.26485252380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50009441375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86200141906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2191581726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9839191436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6582021713257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97057437896729</t>
   </si>
   <si>
     <t xml:space="preserve">10.2058153152466</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84390830993652</t>
+    <t xml:space="preserve">9.84390735626221</t>
   </si>
   <si>
     <t xml:space="preserve">10.4591512680054</t>
@@ -2198,16 +2198,16 @@
     <t xml:space="preserve">10.7305822372437</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8210601806641</t>
+    <t xml:space="preserve">10.8210592269897</t>
   </si>
   <si>
     <t xml:space="preserve">12.0696439743042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.558219909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8477468490601</t>
+    <t xml:space="preserve">12.5582189559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8477458953857</t>
   </si>
   <si>
     <t xml:space="preserve">13.1915588378906</t>
@@ -2216,10 +2216,10 @@
     <t xml:space="preserve">12.757269859314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7934617996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4315509796143</t>
+    <t xml:space="preserve">12.7934598922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4315519332886</t>
   </si>
   <si>
     <t xml:space="preserve">12.594409942627</t>
@@ -2228,10 +2228,10 @@
     <t xml:space="preserve">12.6486968994141</t>
   </si>
   <si>
-    <t xml:space="preserve">12.721079826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8658428192139</t>
+    <t xml:space="preserve">12.7210779190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8658418655396</t>
   </si>
   <si>
     <t xml:space="preserve">13.1553678512573</t>
@@ -2252,16 +2252,16 @@
     <t xml:space="preserve">13.3725137710571</t>
   </si>
   <si>
-    <t xml:space="preserve">13.354416847229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4534883499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.249683380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2858734130859</t>
+    <t xml:space="preserve">13.3544187545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4534873962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2496852874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2858753204346</t>
   </si>
   <si>
     <t xml:space="preserve">16.3763523101807</t>
@@ -2276,79 +2276,79 @@
     <t xml:space="preserve">16.0687313079834</t>
   </si>
   <si>
-    <t xml:space="preserve">15.869683265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9239673614502</t>
+    <t xml:space="preserve">15.8696813583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9239664077759</t>
   </si>
   <si>
     <t xml:space="preserve">15.9058713912964</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8515853881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0144462585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7973003387451</t>
+    <t xml:space="preserve">15.8515872955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0144443511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7972965240479</t>
   </si>
   <si>
     <t xml:space="preserve">16.2677803039551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0325393676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7792062759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7249183654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4125442504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8153944015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.942063331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6344423294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1049213409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9601573944092</t>
+    <t xml:space="preserve">16.0325374603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7792043685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7249193191528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4125423431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8153963088989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9420642852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6344404220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.104923248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9601583480835</t>
   </si>
   <si>
     <t xml:space="preserve">15.6887264251709</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6163444519043</t>
+    <t xml:space="preserve">15.6163463592529</t>
   </si>
   <si>
     <t xml:space="preserve">14.8925285339355</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6525363922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3630094528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4896793365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.14586353302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0372915267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7430143356323</t>
+    <t xml:space="preserve">15.6525344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3630084991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4896783828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1458644866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0372924804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7430114746094</t>
   </si>
   <si>
     <t xml:space="preserve">14.8201465606689</t>
@@ -2357,46 +2357,46 @@
     <t xml:space="preserve">15.2906274795532</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5887451171875</t>
+    <t xml:space="preserve">17.5887489318848</t>
   </si>
   <si>
     <t xml:space="preserve">17.7696990966797</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0230331420898</t>
+    <t xml:space="preserve">18.0230350494385</t>
   </si>
   <si>
     <t xml:space="preserve">19.1359043121338</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2763729095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.041130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4258861541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7335090637207</t>
+    <t xml:space="preserve">18.2763710021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0411319732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4258880615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7335109710693</t>
   </si>
   <si>
     <t xml:space="preserve">17.2992210388184</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0458831787109</t>
+    <t xml:space="preserve">17.0458850860596</t>
   </si>
   <si>
     <t xml:space="preserve">17.0277881622314</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7020702362061</t>
+    <t xml:space="preserve">16.7020683288574</t>
   </si>
   <si>
     <t xml:space="preserve">17.009693145752</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4077930450439</t>
+    <t xml:space="preserve">17.4077911376953</t>
   </si>
   <si>
     <t xml:space="preserve">18.5025653839111</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">18.1406555175781</t>
   </si>
   <si>
-    <t xml:space="preserve">17.96875</t>
+    <t xml:space="preserve">17.9687519073486</t>
   </si>
   <si>
     <t xml:space="preserve">17.4982681274414</t>
@@ -2423,37 +2423,37 @@
     <t xml:space="preserve">17.2449321746826</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1182651519775</t>
+    <t xml:space="preserve">17.1182632446289</t>
   </si>
   <si>
     <t xml:space="preserve">16.8106422424316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8287391662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.973503112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9192161560059</t>
+    <t xml:space="preserve">16.8287372589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9735012054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9192180633545</t>
   </si>
   <si>
     <t xml:space="preserve">17.0639801025391</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8468360900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9011192321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3173160552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2087440490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2268390655518</t>
+    <t xml:space="preserve">16.8468341827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9011211395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3173141479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2087421417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2268371582031</t>
   </si>
   <si>
     <t xml:space="preserve">18.3668479919434</t>
@@ -2471,28 +2471,28 @@
     <t xml:space="preserve">18.9549503326416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8644733428955</t>
+    <t xml:space="preserve">18.8644714355469</t>
   </si>
   <si>
     <t xml:space="preserve">19.6335296630859</t>
   </si>
   <si>
-    <t xml:space="preserve">19.678768157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5430507659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0454254150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.000186920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3168563842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3216133117676</t>
+    <t xml:space="preserve">19.6787662506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5430526733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0454292297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0001888275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.316858291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3216114044189</t>
   </si>
   <si>
     <t xml:space="preserve">18.2311344146729</t>
@@ -2507,10 +2507,10 @@
     <t xml:space="preserve">18.0954189300537</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0049381256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5706481933594</t>
+    <t xml:space="preserve">18.004940032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.570650100708</t>
   </si>
   <si>
     <t xml:space="preserve">17.8239860534668</t>
@@ -2519,52 +2519,52 @@
     <t xml:space="preserve">17.6430320739746</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8058891296387</t>
+    <t xml:space="preserve">17.8058910369873</t>
   </si>
   <si>
     <t xml:space="preserve">19.2716178894043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1811428070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2668685913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4930591583252</t>
+    <t xml:space="preserve">19.1811447143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.26686668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4930610656738</t>
   </si>
   <si>
     <t xml:space="preserve">20.9906845092773</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5835380554199</t>
+    <t xml:space="preserve">20.5835361480713</t>
   </si>
   <si>
     <t xml:space="preserve">20.3573455810547</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9049587249756</t>
+    <t xml:space="preserve">19.9049606323242</t>
   </si>
   <si>
     <t xml:space="preserve">19.7692432403564</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7192516326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9954357147217</t>
+    <t xml:space="preserve">20.7192535400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9954376220703</t>
   </si>
   <si>
     <t xml:space="preserve">19.2263813018799</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4525737762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4073352813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6249351501465</t>
+    <t xml:space="preserve">19.4525756835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4073371887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6249370574951</t>
   </si>
   <si>
     <t xml:space="preserve">17.7877941131592</t>
@@ -2573,22 +2573,22 @@
     <t xml:space="preserve">19.4978103637695</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0859146118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1311531066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8597221374512</t>
+    <t xml:space="preserve">20.0859127044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1311511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8597202301025</t>
   </si>
   <si>
     <t xml:space="preserve">20.674015045166</t>
   </si>
   <si>
-    <t xml:space="preserve">21.035924911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8097286224365</t>
+    <t xml:space="preserve">21.0359230041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8097267150879</t>
   </si>
   <si>
     <t xml:space="preserve">20.628776550293</t>
@@ -2600,13 +2600,13 @@
     <t xml:space="preserve">20.4478225708008</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8821105957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2802124023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3344974517822</t>
+    <t xml:space="preserve">20.8821125030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2802104949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3344955444336</t>
   </si>
   <si>
     <t xml:space="preserve">21.587833404541</t>
@@ -2621,25 +2621,25 @@
     <t xml:space="preserve">22.6192722320557</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8726100921631</t>
+    <t xml:space="preserve">22.8726081848145</t>
   </si>
   <si>
     <t xml:space="preserve">23.9040470123291</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7821311950684</t>
+    <t xml:space="preserve">22.7821292877197</t>
   </si>
   <si>
     <t xml:space="preserve">21.8592624664307</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0040264129639</t>
+    <t xml:space="preserve">22.0040245056152</t>
   </si>
   <si>
     <t xml:space="preserve">22.2573642730713</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4745101928711</t>
+    <t xml:space="preserve">22.4745082855225</t>
   </si>
   <si>
     <t xml:space="preserve">22.1126003265381</t>
@@ -2663,16 +2663,16 @@
     <t xml:space="preserve">21.3525943756104</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2621173858643</t>
+    <t xml:space="preserve">21.2621154785156</t>
   </si>
   <si>
     <t xml:space="preserve">22.09450340271</t>
   </si>
   <si>
-    <t xml:space="preserve">22.583080291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0354652404785</t>
+    <t xml:space="preserve">22.5830783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0354671478271</t>
   </si>
   <si>
     <t xml:space="preserve">23.0173721313477</t>
@@ -2681,19 +2681,19 @@
     <t xml:space="preserve">23.3611831665039</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2707061767578</t>
+    <t xml:space="preserve">23.2707080841064</t>
   </si>
   <si>
     <t xml:space="preserve">25.0440578460693</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7726268768311</t>
+    <t xml:space="preserve">24.7726249694824</t>
   </si>
   <si>
     <t xml:space="preserve">24.9716758728027</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0621547698975</t>
+    <t xml:space="preserve">25.0621528625488</t>
   </si>
   <si>
     <t xml:space="preserve">25.9126377105713</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">26.238353729248</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6765727996826</t>
+    <t xml:space="preserve">26.676570892334</t>
   </si>
   <si>
     <t xml:space="preserve">26.7130928039551</t>
@@ -2714,88 +2714,88 @@
     <t xml:space="preserve">26.6583156585693</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8226451873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9504585266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5712718963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6260471343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0642642974854</t>
+    <t xml:space="preserve">26.8226470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.95046043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5712699890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.626049041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.064266204834</t>
   </si>
   <si>
     <t xml:space="preserve">28.283374786377</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8171424865723</t>
+    <t xml:space="preserve">29.8171443939209</t>
   </si>
   <si>
     <t xml:space="preserve">29.5980319976807</t>
   </si>
   <si>
-    <t xml:space="preserve">28.958963394165</t>
+    <t xml:space="preserve">28.9589614868164</t>
   </si>
   <si>
     <t xml:space="preserve">30.1275482177734</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6528091430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1092872619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9632148742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4014301300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2188415527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2961311340332</t>
+    <t xml:space="preserve">29.652811050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1092891693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9632129669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4014358520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2188396453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2961292266846</t>
   </si>
   <si>
     <t xml:space="preserve">30.8213920593262</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1683177947998</t>
+    <t xml:space="preserve">31.1683158874512</t>
   </si>
   <si>
     <t xml:space="preserve">30.2371006011963</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4154434204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8536605834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.178071975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1458072662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7075881958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0545120239258</t>
+    <t xml:space="preserve">29.4154415130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8536624908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1780700683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.145809173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7075862884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0545082092285</t>
   </si>
   <si>
     <t xml:space="preserve">32.8664131164551</t>
   </si>
   <si>
-    <t xml:space="preserve">34.546257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0532608032227</t>
+    <t xml:space="preserve">34.5462532043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0532569885254</t>
   </si>
   <si>
     <t xml:space="preserve">33.0855255126953</t>
@@ -2804,31 +2804,31 @@
     <t xml:space="preserve">33.7245941162109</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6880760192871</t>
+    <t xml:space="preserve">33.6880722045898</t>
   </si>
   <si>
     <t xml:space="preserve">33.5785217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4872207641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7976341247559</t>
+    <t xml:space="preserve">33.4872283935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7976303100586</t>
   </si>
   <si>
     <t xml:space="preserve">33.1403007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2863693237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2273445129395</t>
+    <t xml:space="preserve">33.286376953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2273483276367</t>
   </si>
   <si>
     <t xml:space="preserve">32.8846740722656</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7568626403809</t>
+    <t xml:space="preserve">32.7568588256836</t>
   </si>
   <si>
     <t xml:space="preserve">32.6473045349121</t>
@@ -2840,10 +2840,10 @@
     <t xml:space="preserve">32.7751197814941</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4099349975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6655616760254</t>
+    <t xml:space="preserve">32.4099388122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6655654907227</t>
   </si>
   <si>
     <t xml:space="preserve">34.692325592041</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">35.605281829834</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2400970458984</t>
+    <t xml:space="preserve">35.2401008605957</t>
   </si>
   <si>
     <t xml:space="preserve">35.8791694641113</t>
@@ -2864,7 +2864,7 @@
     <t xml:space="preserve">35.0940284729004</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5870208740234</t>
+    <t xml:space="preserve">35.5870246887207</t>
   </si>
   <si>
     <t xml:space="preserve">35.7878723144531</t>
@@ -2879,22 +2879,22 @@
     <t xml:space="preserve">38.9101829528809</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4354438781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4944763183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3849182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2205848693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1292915344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1980781555176</t>
+    <t xml:space="preserve">38.4354476928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4944725036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3849220275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2205924987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1292953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1980743408203</t>
   </si>
   <si>
     <t xml:space="preserve">37.6137886047363</t>
@@ -2903,7 +2903,7 @@
     <t xml:space="preserve">37.2486038208008</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0660095214844</t>
+    <t xml:space="preserve">37.0660133361816</t>
   </si>
   <si>
     <t xml:space="preserve">37.2668609619141</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">36.7008323669434</t>
   </si>
   <si>
-    <t xml:space="preserve">37.212085723877</t>
+    <t xml:space="preserve">37.2120819091797</t>
   </si>
   <si>
     <t xml:space="preserve">37.559009552002</t>
@@ -2921,31 +2921,31 @@
     <t xml:space="preserve">38.0154838562012</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6503105163574</t>
+    <t xml:space="preserve">37.6503067016602</t>
   </si>
   <si>
     <t xml:space="preserve">35.6235427856445</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2315979003906</t>
+    <t xml:space="preserve">33.2316017150879</t>
   </si>
   <si>
     <t xml:space="preserve">32.9942283630371</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3594093322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0490074157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.783618927002</t>
+    <t xml:space="preserve">33.3594131469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0490112304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7836227416992</t>
   </si>
   <si>
     <t xml:space="preserve">34.3819236755371</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8931770324707</t>
+    <t xml:space="preserve">34.893180847168</t>
   </si>
   <si>
     <t xml:space="preserve">32.9577102661133</t>
@@ -2957,31 +2957,31 @@
     <t xml:space="preserve">35.513988494873</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4817237854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3173866271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6095352172852</t>
+    <t xml:space="preserve">36.4817199707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3173904418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6095314025879</t>
   </si>
   <si>
     <t xml:space="preserve">37.7781181335449</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2711143493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2023277282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7190933227539</t>
+    <t xml:space="preserve">38.271110534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2023315429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7190895080566</t>
   </si>
   <si>
     <t xml:space="preserve">35.8426475524902</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9662132263184</t>
+    <t xml:space="preserve">34.9662170410156</t>
   </si>
   <si>
     <t xml:space="preserve">35.1488075256348</t>
@@ -2990,19 +2990,19 @@
     <t xml:space="preserve">35.4409484863281</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8876686096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5267448425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8006286621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6685638427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4226951599121</t>
+    <t xml:space="preserve">37.8876724243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.526741027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8006324768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6685600280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4226913452148</t>
   </si>
   <si>
     <t xml:space="preserve">35.258358001709</t>
@@ -3011,13 +3011,13 @@
     <t xml:space="preserve">34.9114379882812</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3636627197266</t>
+    <t xml:space="preserve">34.3636589050293</t>
   </si>
   <si>
     <t xml:space="preserve">33.8341522216797</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5967826843262</t>
+    <t xml:space="preserve">33.5967788696289</t>
   </si>
   <si>
     <t xml:space="preserve">35.3313980102539</t>
@@ -3038,40 +3038,40 @@
     <t xml:space="preserve">34.3454055786133</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0715217590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1950836181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6150398254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9254455566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9437026977539</t>
+    <t xml:space="preserve">34.0715179443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1950759887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6150360107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9254417419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9436988830566</t>
   </si>
   <si>
     <t xml:space="preserve">34.6192893981934</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5827713012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7288475036621</t>
+    <t xml:space="preserve">34.5827751159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7288436889648</t>
   </si>
   <si>
     <t xml:space="preserve">35.0027313232422</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8383979797363</t>
+    <t xml:space="preserve">34.8384017944336</t>
   </si>
   <si>
     <t xml:space="preserve">34.8749198913574</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5377502441406</t>
+    <t xml:space="preserve">32.5377540588379</t>
   </si>
   <si>
     <t xml:space="preserve">32.1725692749023</t>
@@ -3083,67 +3083,67 @@
     <t xml:space="preserve">29.4519577026367</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8901786804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1640644073486</t>
+    <t xml:space="preserve">29.8901805877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1640663146973</t>
   </si>
   <si>
     <t xml:space="preserve">28.4294490814209</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1007843017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6808261871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9954833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2693691253662</t>
+    <t xml:space="preserve">28.1007862091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6808242797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9954814910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2693710327148</t>
   </si>
   <si>
     <t xml:space="preserve">28.6850776672363</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9687194824219</t>
+    <t xml:space="preserve">26.9687213897705</t>
   </si>
   <si>
     <t xml:space="preserve">26.8956813812256</t>
   </si>
   <si>
-    <t xml:space="preserve">27.845157623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9729690551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6668186187744</t>
+    <t xml:space="preserve">27.8451557159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9729709625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6668167114258</t>
   </si>
   <si>
     <t xml:space="preserve">29.1232948303223</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9224472045898</t>
+    <t xml:space="preserve">28.9224452972412</t>
   </si>
   <si>
     <t xml:space="preserve">27.6077880859375</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7538623809814</t>
+    <t xml:space="preserve">27.7538604736328</t>
   </si>
   <si>
     <t xml:space="preserve">26.3479099273682</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5445098876953</t>
+    <t xml:space="preserve">25.544506072998</t>
   </si>
   <si>
     <t xml:space="preserve">26.7496089935303</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7861270904541</t>
+    <t xml:space="preserve">26.7861289978027</t>
   </si>
   <si>
     <t xml:space="preserve">26.5670204162598</t>
@@ -3155,13 +3155,13 @@
     <t xml:space="preserve">27.4251976013184</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4799766540527</t>
+    <t xml:space="preserve">27.4799747467041</t>
   </si>
   <si>
     <t xml:space="preserve">27.1147937774658</t>
   </si>
   <si>
-    <t xml:space="preserve">26.731351852417</t>
+    <t xml:space="preserve">26.7313537597656</t>
   </si>
   <si>
     <t xml:space="preserve">27.4069385528564</t>
@@ -3173,10 +3173,10 @@
     <t xml:space="preserve">26.6948337554932</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4434566497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3113899230957</t>
+    <t xml:space="preserve">27.4434547424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3113918304443</t>
   </si>
   <si>
     <t xml:space="preserve">23.5542621612549</t>
@@ -3191,91 +3191,91 @@
     <t xml:space="preserve">22.0022392272949</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7466106414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7423572540283</t>
+    <t xml:space="preserve">21.7466125488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.742359161377</t>
   </si>
   <si>
     <t xml:space="preserve">22.6047897338867</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8744239807129</t>
+    <t xml:space="preserve">21.8744258880615</t>
   </si>
   <si>
     <t xml:space="preserve">22.5134925842285</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1525650024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2073421478271</t>
+    <t xml:space="preserve">23.1525630950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2073402404785</t>
   </si>
   <si>
     <t xml:space="preserve">24.5402545928955</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6680717468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8689212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4489631652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2341022491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5585155487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0289993286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.138557434082</t>
+    <t xml:space="preserve">24.6680698394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8689193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4489612579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2341041564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5585174560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0290012359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1385555267334</t>
   </si>
   <si>
     <t xml:space="preserve">24.0472602844238</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3984336853027</t>
+    <t xml:space="preserve">25.3984355926514</t>
   </si>
   <si>
     <t xml:space="preserve">25.4166927337646</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2115936279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0837783813477</t>
+    <t xml:space="preserve">24.2115917205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.083776473999</t>
   </si>
   <si>
     <t xml:space="preserve">23.8098926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3351554870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4221973419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7326049804688</t>
+    <t xml:space="preserve">23.3351535797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4221992492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7326030731201</t>
   </si>
   <si>
     <t xml:space="preserve">22.677827835083</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2761249542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9109439849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2213497161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8379058837891</t>
+    <t xml:space="preserve">22.2761268615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9109420776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2213459014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8379077911377</t>
   </si>
   <si>
     <t xml:space="preserve">22.0935344696045</t>
@@ -3284,31 +3284,31 @@
     <t xml:space="preserve">22.8239002227783</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5457630157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.07102394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9657192230225</t>
+    <t xml:space="preserve">21.5457611083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0710258483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9657211303711</t>
   </si>
   <si>
     <t xml:space="preserve">21.1988372802734</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2718753814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8884315490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6875820159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0850315093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3729267120361</t>
+    <t xml:space="preserve">21.2718734741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8884296417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6875839233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0850296020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3729228973389</t>
   </si>
   <si>
     <t xml:space="preserve">19.8659229278564</t>
@@ -3317,16 +3317,16 @@
     <t xml:space="preserve">19.957218170166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9024410247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2493648529053</t>
+    <t xml:space="preserve">19.9024391174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2493629455566</t>
   </si>
   <si>
     <t xml:space="preserve">20.9614677429199</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8519134521484</t>
+    <t xml:space="preserve">20.8519153594971</t>
   </si>
   <si>
     <t xml:space="preserve">20.724100112915</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">21.0162467956543</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3449115753174</t>
+    <t xml:space="preserve">21.3449096679688</t>
   </si>
   <si>
     <t xml:space="preserve">20.3954372406006</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">20.523250579834</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6693210601807</t>
+    <t xml:space="preserve">20.6693229675293</t>
   </si>
   <si>
     <t xml:space="preserve">22.1300525665283</t>
@@ -3353,10 +3353,10 @@
     <t xml:space="preserve">24.1933345794678</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6455593109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5177440643311</t>
+    <t xml:space="preserve">23.6455612182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5177478790283</t>
   </si>
   <si>
     <t xml:space="preserve">23.7368545532227</t>
@@ -3365,22 +3365,22 @@
     <t xml:space="preserve">23.0533809661865</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9240741729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7393550872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8711566925049</t>
+    <t xml:space="preserve">22.9240760803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7393531799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8711585998535</t>
   </si>
   <si>
     <t xml:space="preserve">20.7443466186523</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6914310455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2850379943848</t>
+    <t xml:space="preserve">19.6914291381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2850399017334</t>
   </si>
   <si>
     <t xml:space="preserve">20.319486618042</t>
@@ -3392,19 +3392,19 @@
     <t xml:space="preserve">21.2246265411377</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3539352416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.316987991333</t>
+    <t xml:space="preserve">21.3539333343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3169898986816</t>
   </si>
   <si>
     <t xml:space="preserve">21.7603225708008</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6494884490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4278240203857</t>
+    <t xml:space="preserve">21.6494903564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4278221130371</t>
   </si>
   <si>
     <t xml:space="preserve">21.55712890625</t>
@@ -3413,16 +3413,16 @@
     <t xml:space="preserve">21.7972679138184</t>
   </si>
   <si>
-    <t xml:space="preserve">20.559627532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7812919616699</t>
+    <t xml:space="preserve">20.5596256256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7812938690186</t>
   </si>
   <si>
     <t xml:space="preserve">20.3379592895508</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9130954742432</t>
+    <t xml:space="preserve">19.9130973815918</t>
   </si>
   <si>
     <t xml:space="preserve">20.9475440979004</t>
@@ -3443,7 +3443,7 @@
     <t xml:space="preserve">20.8182392120361</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1532363891602</t>
+    <t xml:space="preserve">20.1532344818115</t>
   </si>
   <si>
     <t xml:space="preserve">20.2271251678467</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">20.4487915039062</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3908786773682</t>
+    <t xml:space="preserve">21.3908767700195</t>
   </si>
   <si>
     <t xml:space="preserve">21.0029602050781</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">22.3883800506592</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2960205078125</t>
+    <t xml:space="preserve">22.2960186004639</t>
   </si>
   <si>
     <t xml:space="preserve">22.5361576080322</t>
@@ -3479,10 +3479,10 @@
     <t xml:space="preserve">21.2985153198242</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5017127990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7787933349609</t>
+    <t xml:space="preserve">21.5017108917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7787952423096</t>
   </si>
   <si>
     <t xml:space="preserve">21.7233791351318</t>
@@ -3506,13 +3506,13 @@
     <t xml:space="preserve">20.0054588317871</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1162910461426</t>
+    <t xml:space="preserve">20.1162929534912</t>
   </si>
   <si>
     <t xml:space="preserve">20.0978202819824</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9500408172607</t>
+    <t xml:space="preserve">19.9500427246094</t>
   </si>
   <si>
     <t xml:space="preserve">19.7468452453613</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">18.5830955505371</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2413578033447</t>
+    <t xml:space="preserve">18.2413558959961</t>
   </si>
   <si>
     <t xml:space="preserve">18.0566329956055</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">17.4562854766846</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6225357055664</t>
+    <t xml:space="preserve">17.622537612915</t>
   </si>
   <si>
     <t xml:space="preserve">16.6989231109619</t>
@@ -3557,13 +3557,13 @@
     <t xml:space="preserve">16.8374652862549</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9852428436279</t>
+    <t xml:space="preserve">16.9852447509766</t>
   </si>
   <si>
     <t xml:space="preserve">17.2807998657227</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0037174224854</t>
+    <t xml:space="preserve">17.0037155151367</t>
   </si>
   <si>
     <t xml:space="preserve">17.6779537200928</t>
@@ -3572,40 +3572,40 @@
     <t xml:space="preserve">17.6317729949951</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8164939880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5855922698975</t>
+    <t xml:space="preserve">17.8164978027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5855941772461</t>
   </si>
   <si>
     <t xml:space="preserve">17.5024662017822</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0683670043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2346210479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2530899047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9390621185303</t>
+    <t xml:space="preserve">17.0683689117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.234619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2530918121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9390640258789</t>
   </si>
   <si>
     <t xml:space="preserve">16.8005218505859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8836479187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4285793304443</t>
+    <t xml:space="preserve">16.8836460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4285774230957</t>
   </si>
   <si>
     <t xml:space="preserve">17.7056617736816</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8442039489746</t>
+    <t xml:space="preserve">17.844202041626</t>
   </si>
   <si>
     <t xml:space="preserve">17.7333698272705</t>
@@ -3614,16 +3614,16 @@
     <t xml:space="preserve">18.3429565429688</t>
   </si>
   <si>
-    <t xml:space="preserve">19.469762802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5805969238281</t>
+    <t xml:space="preserve">19.4697608947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5805988311768</t>
   </si>
   <si>
     <t xml:space="preserve">19.3589286804199</t>
   </si>
   <si>
-    <t xml:space="preserve">19.044900894165</t>
+    <t xml:space="preserve">19.0449028015137</t>
   </si>
   <si>
     <t xml:space="preserve">18.7493438720703</t>
@@ -3632,19 +3632,19 @@
     <t xml:space="preserve">18.3891353607178</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2967720031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4907321929932</t>
+    <t xml:space="preserve">18.2967739105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4907341003418</t>
   </si>
   <si>
     <t xml:space="preserve">19.0079555511475</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0239315032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8392066955566</t>
+    <t xml:space="preserve">20.0239295959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8392086029053</t>
   </si>
   <si>
     <t xml:space="preserve">20.8736553192139</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">21.9081001281738</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3329620361328</t>
+    <t xml:space="preserve">22.3329639434814</t>
   </si>
   <si>
     <t xml:space="preserve">20.9105987548828</t>
@@ -3677,31 +3677,31 @@
     <t xml:space="preserve">21.2800464630127</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4093494415283</t>
+    <t xml:space="preserve">21.409351348877</t>
   </si>
   <si>
     <t xml:space="preserve">21.8526840209961</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1507396697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0583763122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3933753967285</t>
+    <t xml:space="preserve">21.1507377624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0583782196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3933773040771</t>
   </si>
   <si>
     <t xml:space="preserve">20.2455978393555</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9315700531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9685153961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.282543182373</t>
+    <t xml:space="preserve">19.931568145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9685134887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2825412750244</t>
   </si>
   <si>
     <t xml:space="preserve">20.9290714263916</t>
@@ -3728,16 +3728,16 @@
     <t xml:space="preserve">23.4412975311279</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9031028747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7922706604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1272716522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7553272247314</t>
+    <t xml:space="preserve">23.9031047821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7922744750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.127269744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7553253173828</t>
   </si>
   <si>
     <t xml:space="preserve">23.8846340179443</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">23.4782428741455</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1087970733643</t>
+    <t xml:space="preserve">23.1088008880615</t>
   </si>
   <si>
     <t xml:space="preserve">22.9979629516602</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">23.0164375305176</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9585247039795</t>
+    <t xml:space="preserve">23.9585227966309</t>
   </si>
   <si>
     <t xml:space="preserve">23.5706043243408</t>
@@ -3767,10 +3767,10 @@
     <t xml:space="preserve">24.1247730255127</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5151863098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8686599731445</t>
+    <t xml:space="preserve">23.5151882171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8686580657959</t>
   </si>
   <si>
     <t xml:space="preserve">23.4597702026367</t>
@@ -3782,7 +3782,7 @@
     <t xml:space="preserve">22.8132438659668</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6285209655762</t>
+    <t xml:space="preserve">22.6285190582275</t>
   </si>
   <si>
     <t xml:space="preserve">22.4622688293457</t>
@@ -3794,7 +3794,7 @@
     <t xml:space="preserve">22.2036571502686</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0004615783691</t>
+    <t xml:space="preserve">22.0004634857178</t>
   </si>
   <si>
     <t xml:space="preserve">22.0558776855469</t>
@@ -3806,19 +3806,19 @@
     <t xml:space="preserve">21.8342132568359</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0928230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2406005859375</t>
+    <t xml:space="preserve">22.0928249359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2406024932861</t>
   </si>
   <si>
     <t xml:space="preserve">21.2615718841553</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3404579162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6569843292236</t>
+    <t xml:space="preserve">19.3404560089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.656982421875</t>
   </si>
   <si>
     <t xml:space="preserve">19.1187896728516</t>
@@ -3836,19 +3836,19 @@
     <t xml:space="preserve">18.2690658569336</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5092067718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8232345581055</t>
+    <t xml:space="preserve">18.509204864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8232326507568</t>
   </si>
   <si>
     <t xml:space="preserve">18.5461502075195</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7123985290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7308712005615</t>
+    <t xml:space="preserve">18.7124004364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7308750152588</t>
   </si>
   <si>
     <t xml:space="preserve">18.6200389862061</t>
@@ -3863,13 +3863,13 @@
     <t xml:space="preserve">17.7980251312256</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5486488342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1422557830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.948299407959</t>
+    <t xml:space="preserve">17.5486469268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1422576904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9483013153076</t>
   </si>
   <si>
     <t xml:space="preserve">16.9205894470215</t>
@@ -3878,10 +3878,10 @@
     <t xml:space="preserve">16.8651733398438</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5696201324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8559379577637</t>
+    <t xml:space="preserve">16.5696182250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8559398651123</t>
   </si>
   <si>
     <t xml:space="preserve">17.1145515441895</t>
@@ -3893,7 +3893,7 @@
     <t xml:space="preserve">16.9021186828613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8744125366211</t>
+    <t xml:space="preserve">16.8744106292725</t>
   </si>
   <si>
     <t xml:space="preserve">16.7912845611572</t>
@@ -3902,10 +3902,10 @@
     <t xml:space="preserve">16.8467025756836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.809757232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5880870819092</t>
+    <t xml:space="preserve">16.8097591400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5880889892578</t>
   </si>
   <si>
     <t xml:space="preserve">16.671215057373</t>
@@ -3914,43 +3914,43 @@
     <t xml:space="preserve">16.7635765075684</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7728137969971</t>
+    <t xml:space="preserve">16.7728118896484</t>
   </si>
   <si>
     <t xml:space="preserve">16.5234375</t>
   </si>
   <si>
-    <t xml:space="preserve">15.710657119751</t>
+    <t xml:space="preserve">15.7106580734253</t>
   </si>
   <si>
     <t xml:space="preserve">16.0708656311035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0893402099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0062160491943</t>
+    <t xml:space="preserve">16.0893383026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0062141418457</t>
   </si>
   <si>
     <t xml:space="preserve">16.0523948669434</t>
   </si>
   <si>
+    <t xml:space="preserve">16.6896877288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4710865020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.632661819458</t>
+  </si>
+  <si>
     <t xml:space="preserve">16.6896858215332</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4710884094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.632661819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6896877288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6611747741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5946445465088</t>
+    <t xml:space="preserve">16.6611766815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5946426391602</t>
   </si>
   <si>
     <t xml:space="preserve">17.2124290466309</t>
@@ -3959,10 +3959,10 @@
     <t xml:space="preserve">17.5830993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9442653656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8207092285156</t>
+    <t xml:space="preserve">17.944263458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.820707321167</t>
   </si>
   <si>
     <t xml:space="preserve">17.8302135467529</t>
@@ -3974,7 +3974,7 @@
     <t xml:space="preserve">16.9938259124756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5661315917969</t>
+    <t xml:space="preserve">16.5661296844482</t>
   </si>
   <si>
     <t xml:space="preserve">16.2809982299805</t>
@@ -3983,13 +3983,13 @@
     <t xml:space="preserve">16.204963684082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0053730010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.58717918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.786771774292</t>
+    <t xml:space="preserve">16.00537109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5871801376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7867727279663</t>
   </si>
   <si>
     <t xml:space="preserve">15.5681705474854</t>
@@ -4007,16 +4007,16 @@
     <t xml:space="preserve">15.3305606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6251983642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4541187286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8723125457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9958686828613</t>
+    <t xml:space="preserve">15.6251974105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4541177749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8723115921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9958667755127</t>
   </si>
   <si>
     <t xml:space="preserve">16.0623989105225</t>
@@ -4025,19 +4025,19 @@
     <t xml:space="preserve">15.7012319564819</t>
   </si>
   <si>
-    <t xml:space="preserve">15.777268409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8247880935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7487545013428</t>
+    <t xml:space="preserve">15.7772674560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8247900009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7487535476685</t>
   </si>
   <si>
     <t xml:space="preserve">15.7392492294312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9388418197632</t>
+    <t xml:space="preserve">15.9388427734375</t>
   </si>
   <si>
     <t xml:space="preserve">16.1859569549561</t>
@@ -4046,7 +4046,7 @@
     <t xml:space="preserve">16.1574420928955</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8913202285767</t>
+    <t xml:space="preserve">15.8913192749023</t>
   </si>
   <si>
     <t xml:space="preserve">16.9177932739258</t>
@@ -4058,13 +4058,13 @@
     <t xml:space="preserve">17.0223407745361</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1649074554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0603580474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6231555938721</t>
+    <t xml:space="preserve">17.1649055480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.060359954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6231575012207</t>
   </si>
   <si>
     <t xml:space="preserve">16.7277050018311</t>
@@ -4079,7 +4079,7 @@
     <t xml:space="preserve">16.3000068664551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4995994567871</t>
+    <t xml:space="preserve">16.4996013641357</t>
   </si>
   <si>
     <t xml:space="preserve">16.509105682373</t>
@@ -4106,16 +4106,16 @@
     <t xml:space="preserve">17.4215240478516</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3074703216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2599506378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8628072738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.881814956665</t>
+    <t xml:space="preserve">17.3074722290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2599487304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8628063201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8818140029907</t>
   </si>
   <si>
     <t xml:space="preserve">16.4235649108887</t>
@@ -4127,16 +4127,16 @@
     <t xml:space="preserve">16.1479377746582</t>
   </si>
   <si>
-    <t xml:space="preserve">15.910327911377</t>
+    <t xml:space="preserve">15.9103288650513</t>
   </si>
   <si>
     <t xml:space="preserve">16.2429828643799</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8533029556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8437976837158</t>
+    <t xml:space="preserve">15.8533020019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8437967300415</t>
   </si>
   <si>
     <t xml:space="preserve">14.7793073654175</t>
@@ -4151,10 +4151,10 @@
     <t xml:space="preserve">14.4466543197632</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7222805023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6917276382446</t>
+    <t xml:space="preserve">14.7222814559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6917285919189</t>
   </si>
   <si>
     <t xml:space="preserve">15.4731273651123</t>
@@ -4166,7 +4166,7 @@
     <t xml:space="preserve">15.4921350479126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0929517745972</t>
+    <t xml:space="preserve">15.0929527282715</t>
   </si>
   <si>
     <t xml:space="preserve">15.4446144104004</t>
@@ -4196,7 +4196,7 @@
     <t xml:space="preserve">14.4846715927124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.931378364563</t>
+    <t xml:space="preserve">14.9313774108887</t>
   </si>
   <si>
     <t xml:space="preserve">14.9218730926514</t>
@@ -4211,37 +4211,37 @@
     <t xml:space="preserve">14.731785774231</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0074119567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7677640914917</t>
+    <t xml:space="preserve">15.0074129104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7677631378174</t>
   </si>
   <si>
     <t xml:space="preserve">16.1954612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5566272735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1289291381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0528926849365</t>
+    <t xml:space="preserve">16.5566253662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.128927230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0528945922852</t>
   </si>
   <si>
     <t xml:space="preserve">16.3570346832275</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4330711364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7467136383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3665370941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3950519561768</t>
+    <t xml:space="preserve">16.433069229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7467155456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3665390014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3950500488281</t>
   </si>
   <si>
     <t xml:space="preserve">16.4805908203125</t>
@@ -4256,10 +4256,10 @@
     <t xml:space="preserve">16.3285217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6136512756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6991920471191</t>
+    <t xml:space="preserve">16.6136531829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6991901397705</t>
   </si>
   <si>
     <t xml:space="preserve">16.5756359100342</t>
@@ -4268,22 +4268,22 @@
     <t xml:space="preserve">18.5240325927734</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7046146392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.647590637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.198844909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4839763641357</t>
+    <t xml:space="preserve">18.7046165466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6475887298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1988430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4839744567871</t>
   </si>
   <si>
     <t xml:space="preserve">19.5029830932617</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4649658203125</t>
+    <t xml:space="preserve">19.4649639129639</t>
   </si>
   <si>
     <t xml:space="preserve">19.2938861846924</t>
@@ -4292,10 +4292,10 @@
     <t xml:space="preserve">19.1037998199463</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2748775482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0277633666992</t>
+    <t xml:space="preserve">19.2748794555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0277652740479</t>
   </si>
   <si>
     <t xml:space="preserve">18.0868320465088</t>
@@ -4322,16 +4322,16 @@
     <t xml:space="preserve">17.9062480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7541770935059</t>
+    <t xml:space="preserve">17.7541790008545</t>
   </si>
   <si>
     <t xml:space="preserve">18.1818752288818</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9157524108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2103881835938</t>
+    <t xml:space="preserve">17.9157543182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2103862762451</t>
   </si>
   <si>
     <t xml:space="preserve">18.343448638916</t>
@@ -4346,16 +4346,16 @@
     <t xml:space="preserve">18.6570930480957</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5810565948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4289894104004</t>
+    <t xml:space="preserve">18.5810585021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4289875030518</t>
   </si>
   <si>
     <t xml:space="preserve">18.1913795471191</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0488128662109</t>
+    <t xml:space="preserve">18.0488147735596</t>
   </si>
   <si>
     <t xml:space="preserve">18.020299911499</t>
@@ -4373,7 +4373,7 @@
     <t xml:space="preserve">17.9632740020752</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0678234100342</t>
+    <t xml:space="preserve">18.0678215026855</t>
   </si>
   <si>
     <t xml:space="preserve">18.1723709106445</t>
@@ -4403,13 +4403,13 @@
     <t xml:space="preserve">17.8112030029297</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5165691375732</t>
+    <t xml:space="preserve">17.5165672302246</t>
   </si>
   <si>
     <t xml:space="preserve">17.5450801849365</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3169746398926</t>
+    <t xml:space="preserve">17.3169765472412</t>
   </si>
   <si>
     <t xml:space="preserve">17.3264808654785</t>
@@ -4430,10 +4430,10 @@
     <t xml:space="preserve">17.5545845031738</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7636814117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8872375488281</t>
+    <t xml:space="preserve">17.7636833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8872394561768</t>
   </si>
   <si>
     <t xml:space="preserve">18.1533622741699</t>
@@ -4442,19 +4442,19 @@
     <t xml:space="preserve">18.1628665924072</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3549938201904</t>
+    <t xml:space="preserve">17.3549957275391</t>
   </si>
   <si>
     <t xml:space="preserve">17.4690456390381</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4405326843262</t>
+    <t xml:space="preserve">17.4405345916748</t>
   </si>
   <si>
     <t xml:space="preserve">17.1078796386719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0413513183594</t>
+    <t xml:space="preserve">17.0413494110107</t>
   </si>
   <si>
     <t xml:space="preserve">16.9368019104004</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">16.4615821838379</t>
   </si>
   <si>
-    <t xml:space="preserve">16.309513092041</t>
+    <t xml:space="preserve">16.3095111846924</t>
   </si>
   <si>
     <t xml:space="preserve">17.0033321380615</t>
@@ -4490,7 +4490,7 @@
     <t xml:space="preserve">17.6211185455322</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0107955932617</t>
+    <t xml:space="preserve">18.0107975006104</t>
   </si>
   <si>
     <t xml:space="preserve">17.7826900482178</t>
@@ -4505,7 +4505,7 @@
     <t xml:space="preserve">17.5355777740479</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0012912750244</t>
+    <t xml:space="preserve">18.001293182373</t>
   </si>
   <si>
     <t xml:space="preserve">18.2674140930176</t>
@@ -70632,7 +70632,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.691087963</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>39514</v>
@@ -70653,6 +70653,32 @@
         <v>1776</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6912731481</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>59079</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>14.9099998474121</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>14.8699998855591</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>14.8900003433228</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>14.8900003433228</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>1776</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TNXT.MI.xlsx
+++ b/data/TNXT.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63493800163269</t>
+    <t xml:space="preserve">2.63493752479553</t>
   </si>
   <si>
     <t xml:space="preserve">TNXT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6515097618103</t>
+    <t xml:space="preserve">2.65150952339172</t>
   </si>
   <si>
     <t xml:space="preserve">2.59350872039795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53550672531128</t>
+    <t xml:space="preserve">2.53550624847412</t>
   </si>
   <si>
     <t xml:space="preserve">2.52556371688843</t>
@@ -62,34 +62,34 @@
     <t xml:space="preserve">2.52722072601318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4874484539032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47087597846985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46921849250793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54047822952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49739098548889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4791624546051</t>
+    <t xml:space="preserve">2.48744797706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47087574005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46921873092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54047846794128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49739122390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47916173934937</t>
   </si>
   <si>
     <t xml:space="preserve">2.44436097145081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39464497566223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34161448478699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36150097846985</t>
+    <t xml:space="preserve">2.39464473724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34161472320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36150074005127</t>
   </si>
   <si>
     <t xml:space="preserve">2.55207872390747</t>
@@ -98,58 +98,58 @@
     <t xml:space="preserve">2.58522248268127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6100800037384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56865096092224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63659501075745</t>
+    <t xml:space="preserve">2.61007976531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56865072250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63659477233887</t>
   </si>
   <si>
     <t xml:space="preserve">2.68962526321411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73436951637268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72608351707458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77579951286316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58025121688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56202220916748</t>
+    <t xml:space="preserve">2.7343692779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72608327865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77579975128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58025097846985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5620219707489</t>
   </si>
   <si>
     <t xml:space="preserve">2.66808128356934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62830853462219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64322352409363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60842251777649</t>
+    <t xml:space="preserve">2.62830924987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64322376251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60842275619507</t>
   </si>
   <si>
     <t xml:space="preserve">2.66642451286316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65316700935364</t>
+    <t xml:space="preserve">2.65316677093506</t>
   </si>
   <si>
     <t xml:space="preserve">2.62665176391602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6929395198822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82551527023315</t>
+    <t xml:space="preserve">2.69293975830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82551574707031</t>
   </si>
   <si>
     <t xml:space="preserve">2.81722927093506</t>
@@ -161,34 +161,34 @@
     <t xml:space="preserve">2.85865926742554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89843225479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88351774215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87523150444031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86694550514221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81888628005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82054400444031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85368800163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79237103462219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85700249671936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90671825408936</t>
+    <t xml:space="preserve">2.89843249320984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88351726531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87523126602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86694526672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81888675689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82054424285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85368776321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79237151145935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8570020198822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9067177772522</t>
   </si>
   <si>
     <t xml:space="preserve">2.8288300037384</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">2.85037326812744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90837526321411</t>
+    <t xml:space="preserve">2.90837502479553</t>
   </si>
   <si>
     <t xml:space="preserve">2.96306252479553</t>
@@ -209,28 +209,28 @@
     <t xml:space="preserve">2.88169693946838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89017248153687</t>
+    <t xml:space="preserve">2.89017295837402</t>
   </si>
   <si>
     <t xml:space="preserve">2.86474561691284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94950222969055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92407488822937</t>
+    <t xml:space="preserve">2.94950199127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92407512664795</t>
   </si>
   <si>
     <t xml:space="preserve">2.96645307540894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11901259422302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94272112846375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94780683517456</t>
+    <t xml:space="preserve">3.11901307106018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94272136688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9478063583374</t>
   </si>
   <si>
     <t xml:space="preserve">2.88339185714722</t>
@@ -239,13 +239,13 @@
     <t xml:space="preserve">2.87322163581848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85966062545776</t>
+    <t xml:space="preserve">2.85966110229492</t>
   </si>
   <si>
     <t xml:space="preserve">3.03256273269653</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07037329673767</t>
+    <t xml:space="preserve">3.07037401199341</t>
   </si>
   <si>
     <t xml:space="preserve">3.06866312026978</t>
@@ -257,31 +257,31 @@
     <t xml:space="preserve">2.99340057373047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98484826087952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93524289131165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98313736915588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92498016357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92326951026917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96774291992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03616309165955</t>
+    <t xml:space="preserve">2.98484802246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93524241447449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98313760757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92497992515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92326927185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96774315834045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03616333007812</t>
   </si>
   <si>
     <t xml:space="preserve">3.05840015411377</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05497932434082</t>
+    <t xml:space="preserve">3.0549795627594</t>
   </si>
   <si>
     <t xml:space="preserve">3.08747887611389</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">3.13879418373108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12853121757507</t>
+    <t xml:space="preserve">3.12853145599365</t>
   </si>
   <si>
     <t xml:space="preserve">3.19010972976685</t>
@@ -299,19 +299,19 @@
     <t xml:space="preserve">3.15589952468872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12339973449707</t>
+    <t xml:space="preserve">3.12339925765991</t>
   </si>
   <si>
     <t xml:space="preserve">3.12511038780212</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14734697341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16445207595825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16616225242615</t>
+    <t xml:space="preserve">3.14734673500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16445183753967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16616249084473</t>
   </si>
   <si>
     <t xml:space="preserve">3.24142503738403</t>
@@ -320,46 +320,46 @@
     <t xml:space="preserve">3.30129289627075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38681864738464</t>
+    <t xml:space="preserve">3.3868191242218</t>
   </si>
   <si>
     <t xml:space="preserve">3.48431777954102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52708148956299</t>
+    <t xml:space="preserve">3.52708101272583</t>
   </si>
   <si>
     <t xml:space="preserve">3.6262903213501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63655352592468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64510679244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74602651596069</t>
+    <t xml:space="preserve">3.63655376434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64510607719421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74602723121643</t>
   </si>
   <si>
     <t xml:space="preserve">3.6776065826416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71181654930115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63484334945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51681780815125</t>
+    <t xml:space="preserve">3.71181726455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63484358787537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51681733131409</t>
   </si>
   <si>
     <t xml:space="preserve">3.50484442710876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49458122253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50655484199524</t>
+    <t xml:space="preserve">3.4945809841156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50655460357666</t>
   </si>
   <si>
     <t xml:space="preserve">3.48089718818665</t>
@@ -368,19 +368,19 @@
     <t xml:space="preserve">3.43129229545593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35602951049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60063314437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64681673049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69471168518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69984316825867</t>
+    <t xml:space="preserve">3.35602998733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60063290596008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64681720733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69471192359924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69984364509583</t>
   </si>
   <si>
     <t xml:space="preserve">3.67589569091797</t>
@@ -389,64 +389,64 @@
     <t xml:space="preserve">3.66563272476196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59721231460571</t>
+    <t xml:space="preserve">3.59721207618713</t>
   </si>
   <si>
     <t xml:space="preserve">3.63313293457031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57497501373291</t>
+    <t xml:space="preserve">3.57497525215149</t>
   </si>
   <si>
     <t xml:space="preserve">3.66050148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6861584186554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7152373790741</t>
+    <t xml:space="preserve">3.68615865707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71523714065552</t>
   </si>
   <si>
     <t xml:space="preserve">3.73747444152832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71010661125183</t>
+    <t xml:space="preserve">3.71010613441467</t>
   </si>
   <si>
     <t xml:space="preserve">3.69129085540771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68957996368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73234272003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72036933898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76313161849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77168440818787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62115907669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64168548583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70326375961304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7973427772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75457906723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90852618217468</t>
+    <t xml:space="preserve">3.68958020210266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73234248161316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72036910057068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76313233375549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77168464660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62115979194641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64168500900269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70326399803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79734253883362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7545793056488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9085259437561</t>
   </si>
   <si>
     <t xml:space="preserve">3.76655268669128</t>
@@ -464,16 +464,16 @@
     <t xml:space="preserve">3.49800229072571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4894495010376</t>
+    <t xml:space="preserve">3.48944973945618</t>
   </si>
   <si>
     <t xml:space="preserve">3.47234463691711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40392374992371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43642377853394</t>
+    <t xml:space="preserve">3.40392398834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43642425537109</t>
   </si>
   <si>
     <t xml:space="preserve">3.53221273422241</t>
@@ -482,52 +482,52 @@
     <t xml:space="preserve">3.5185284614563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46037125587463</t>
+    <t xml:space="preserve">3.46037101745605</t>
   </si>
   <si>
     <t xml:space="preserve">3.50142312049866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53563356399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55615973472595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64339590072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72550106048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84865808486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82984232902527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83155298233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87089490890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84523701667786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87431645393372</t>
+    <t xml:space="preserve">3.53563332557678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55616021156311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64339685440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72550058364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84865760803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82984209060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83155202865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87089443206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84523725509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87431597709656</t>
   </si>
   <si>
     <t xml:space="preserve">3.86405324935913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85721063613892</t>
+    <t xml:space="preserve">3.8572108745575</t>
   </si>
   <si>
     <t xml:space="preserve">3.82471084594727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90681505203247</t>
+    <t xml:space="preserve">3.90681457519531</t>
   </si>
   <si>
     <t xml:space="preserve">4.00260448455811</t>
@@ -536,25 +536,25 @@
     <t xml:space="preserve">4.17536592483521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11378717422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00773525238037</t>
+    <t xml:space="preserve">4.11378812789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00773572921753</t>
   </si>
   <si>
     <t xml:space="preserve">4.0522084236145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08128690719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00602436065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09839344024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01970911026001</t>
+    <t xml:space="preserve">4.08128786087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0060248374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09839248657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01970958709717</t>
   </si>
   <si>
     <t xml:space="preserve">4.01115655899048</t>
@@ -572,13 +572,13 @@
     <t xml:space="preserve">4.13773488998413</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1223406791687</t>
+    <t xml:space="preserve">4.12234020233154</t>
   </si>
   <si>
     <t xml:space="preserve">4.14799737930298</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18905019760132</t>
+    <t xml:space="preserve">4.18905067443848</t>
   </si>
   <si>
     <t xml:space="preserve">4.2591814994812</t>
@@ -587,31 +587,31 @@
     <t xml:space="preserve">4.22839212417603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20615577697754</t>
+    <t xml:space="preserve">4.20615530014038</t>
   </si>
   <si>
     <t xml:space="preserve">4.0214204788208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99405169487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01799917221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02655172348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07615613937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12747192382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11891937255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1052360534668</t>
+    <t xml:space="preserve">3.99405121803284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01799869537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02655220031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07615661621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12747240066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11891889572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10523557662964</t>
   </si>
   <si>
     <t xml:space="preserve">4.09668207168579</t>
@@ -626,34 +626,34 @@
     <t xml:space="preserve">4.09497213363647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13089275360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2164192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52431106567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54996871948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53713989257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46444272994995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50292921066284</t>
+    <t xml:space="preserve">4.13089227676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21641826629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52431154251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54996919631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53713893890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46444320678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5029296875</t>
   </si>
   <si>
     <t xml:space="preserve">4.56707429885864</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6226658821106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63549470901489</t>
+    <t xml:space="preserve">4.62266540527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63549423217773</t>
   </si>
   <si>
     <t xml:space="preserve">4.58417940139771</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">4.61838912963867</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53286361694336</t>
+    <t xml:space="preserve">4.53286409378052</t>
   </si>
   <si>
     <t xml:space="preserve">4.55852127075195</t>
@@ -677,22 +677,22 @@
     <t xml:space="preserve">4.48154783248901</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51575899124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49010133743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51148223876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63121843338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78516483306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75950765609741</t>
+    <t xml:space="preserve">4.5157585144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49010038375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51148176193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63121891021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78516435623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7595067024231</t>
   </si>
   <si>
     <t xml:space="preserve">4.78944110870361</t>
@@ -707,19 +707,19 @@
     <t xml:space="preserve">4.76378297805786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65687608718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69536209106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8279275894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90062379837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91772890090942</t>
+    <t xml:space="preserve">4.65687561035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69536256790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82792711257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90062475204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91772937774658</t>
   </si>
   <si>
     <t xml:space="preserve">4.94338703155518</t>
@@ -728,58 +728,58 @@
     <t xml:space="preserve">4.98615026473999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04174184799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02035999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07167530059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08022737503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99470233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09305715560913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06050682067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91728544235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94766521453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92596530914307</t>
+    <t xml:space="preserve">5.04174137115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0203595161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0716757774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08022832870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99470281600952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09305667877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06050634384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91728496551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94766569137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92596578598022</t>
   </si>
   <si>
     <t xml:space="preserve">4.9042649269104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82180404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73500299453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7219820022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59178113937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64386177062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73066186904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66556167602539</t>
+    <t xml:space="preserve">4.8218035697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7350025177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72198247909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59178161621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64386081695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73066139221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66556215286255</t>
   </si>
   <si>
     <t xml:space="preserve">4.65254163742065</t>
@@ -788,16 +788,16 @@
     <t xml:space="preserve">4.60914039611816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65688180923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54837942123413</t>
+    <t xml:space="preserve">4.65688133239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54837989807129</t>
   </si>
   <si>
     <t xml:space="preserve">4.53535985946655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47025871276855</t>
+    <t xml:space="preserve">4.47025918960571</t>
   </si>
   <si>
     <t xml:space="preserve">4.59612083435059</t>
@@ -806,10 +806,10 @@
     <t xml:space="preserve">4.47459888458252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48761987686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46157884597778</t>
+    <t xml:space="preserve">4.4876184463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46157932281494</t>
   </si>
   <si>
     <t xml:space="preserve">4.41383838653564</t>
@@ -830,13 +830,13 @@
     <t xml:space="preserve">4.52233982086182</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57007932662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53970050811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47893953323364</t>
+    <t xml:space="preserve">4.57008028030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53970003128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47893905639648</t>
   </si>
   <si>
     <t xml:space="preserve">4.43553876876831</t>
@@ -845,10 +845,10 @@
     <t xml:space="preserve">4.42251825332642</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43119859695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45289850234985</t>
+    <t xml:space="preserve">4.4311990737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45289897918701</t>
   </si>
   <si>
     <t xml:space="preserve">4.51365947723389</t>
@@ -860,28 +860,28 @@
     <t xml:space="preserve">4.60046100616455</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63952159881592</t>
+    <t xml:space="preserve">4.6395206451416</t>
   </si>
   <si>
     <t xml:space="preserve">4.56140041351318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58744049072266</t>
+    <t xml:space="preserve">4.58744096755981</t>
   </si>
   <si>
     <t xml:space="preserve">4.61782121658325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64820146560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60480117797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58310127258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49629878997803</t>
+    <t xml:space="preserve">4.64820098876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6048002243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58310079574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49629926681519</t>
   </si>
   <si>
     <t xml:space="preserve">4.50497913360596</t>
@@ -890,28 +890,28 @@
     <t xml:space="preserve">4.42685890197754</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49195909500122</t>
+    <t xml:space="preserve">4.49196004867554</t>
   </si>
   <si>
     <t xml:space="preserve">4.51799964904785</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80878305435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77840280532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84784412384033</t>
+    <t xml:space="preserve">4.80878353118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77840328216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84784460067749</t>
   </si>
   <si>
     <t xml:space="preserve">4.8348240852356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74368333816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81312417984009</t>
+    <t xml:space="preserve">4.74368238449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81312370300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.71330261230469</t>
@@ -923,19 +923,19 @@
     <t xml:space="preserve">4.72632217407227</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69594192504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76972341537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84350395202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87822437286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87388467788696</t>
+    <t xml:space="preserve">4.69594240188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76972246170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84350442886353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87822389602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8738842010498</t>
   </si>
   <si>
     <t xml:space="preserve">4.97370576858521</t>
@@ -944,46 +944,46 @@
     <t xml:space="preserve">4.97804594039917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00842618942261</t>
+    <t xml:space="preserve">5.00842666625977</t>
   </si>
   <si>
     <t xml:space="preserve">5.07786703109741</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04314661026001</t>
+    <t xml:space="preserve">5.04314613342285</t>
   </si>
   <si>
     <t xml:space="preserve">5.14730787277222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86086368560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86954498291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96502494812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90860557556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99974632263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99106597900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15598821640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12994718551636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2948694229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41639184951782</t>
+    <t xml:space="preserve">4.86086416244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.869544506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96502542495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90860509872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99974584579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99106550216675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15598773956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12994766235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29487037658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41639137268066</t>
   </si>
   <si>
     <t xml:space="preserve">5.48583269119263</t>
@@ -992,85 +992,85 @@
     <t xml:space="preserve">5.43375205993652</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48149299621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42073154449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39469146728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35563087463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33393049240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37299108505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33826971054077</t>
+    <t xml:space="preserve">5.48149251937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42073202133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.394690990448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35563039779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33393001556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37299060821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33827066421509</t>
   </si>
   <si>
     <t xml:space="preserve">5.20806884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16466856002808</t>
+    <t xml:space="preserve">5.16466808319092</t>
   </si>
   <si>
     <t xml:space="preserve">5.26448965072632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25147008895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2601490020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18636894226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20372915267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19504880905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16900825500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1820273399353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19938850402832</t>
+    <t xml:space="preserve">5.25146913528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26014995574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18636798858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20372867584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19504928588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16900777816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18202877044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19938898086548</t>
   </si>
   <si>
     <t xml:space="preserve">5.22542905807495</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42507219314575</t>
+    <t xml:space="preserve">5.42507171630859</t>
   </si>
   <si>
     <t xml:space="preserve">5.61603403091431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7288761138916</t>
+    <t xml:space="preserve">5.72887563705444</t>
   </si>
   <si>
     <t xml:space="preserve">5.7115159034729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78963613510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82435703277588</t>
+    <t xml:space="preserve">5.78963661193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82435655593872</t>
   </si>
   <si>
     <t xml:space="preserve">5.87643814086914</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88511848449707</t>
+    <t xml:space="preserve">5.88511800765991</t>
   </si>
   <si>
     <t xml:space="preserve">5.93719911575317</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">5.85907745361328</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80699682235718</t>
+    <t xml:space="preserve">5.80699729919434</t>
   </si>
   <si>
     <t xml:space="preserve">5.92851829528809</t>
@@ -1094,31 +1094,31 @@
     <t xml:space="preserve">6.03268003463745</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17156219482422</t>
+    <t xml:space="preserve">6.17156171798706</t>
   </si>
   <si>
     <t xml:space="preserve">6.28440284729004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01531934738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02399921417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21496200561523</t>
+    <t xml:space="preserve">6.01531887054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02399969100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21496248245239</t>
   </si>
   <si>
     <t xml:space="preserve">6.14552116394043</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40592479705811</t>
+    <t xml:space="preserve">6.40592432022095</t>
   </si>
   <si>
     <t xml:space="preserve">6.07607984542847</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98927927017212</t>
+    <t xml:space="preserve">5.98927879333496</t>
   </si>
   <si>
     <t xml:space="preserve">6.04136037826538</t>
@@ -1127,52 +1127,52 @@
     <t xml:space="preserve">6.22364234924316</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13684129714966</t>
+    <t xml:space="preserve">6.1368408203125</t>
   </si>
   <si>
     <t xml:space="preserve">6.19760179519653</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1542010307312</t>
+    <t xml:space="preserve">6.15420150756836</t>
   </si>
   <si>
     <t xml:space="preserve">6.05003976821899</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89379787445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90247774124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70283555984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50319337844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58131408691406</t>
+    <t xml:space="preserve">5.89379692077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90247821807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70283508300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50319242477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58131313323975</t>
   </si>
   <si>
     <t xml:space="preserve">5.72019624710083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76359605789185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91983795166016</t>
+    <t xml:space="preserve">5.76359510421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91983842849731</t>
   </si>
   <si>
     <t xml:space="preserve">5.99795913696289</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83303785324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79831600189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6594352722168</t>
+    <t xml:space="preserve">5.83303689956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79831647872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65943431854248</t>
   </si>
   <si>
     <t xml:space="preserve">5.5118727684021</t>
@@ -1181,49 +1181,49 @@
     <t xml:space="preserve">5.54659366607666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58999347686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52055358886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38167190551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44243192672729</t>
+    <t xml:space="preserve">5.58999395370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52055263519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38167095184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44243240356445</t>
   </si>
   <si>
     <t xml:space="preserve">5.46847248077393</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6767954826355</t>
+    <t xml:space="preserve">5.67679500579834</t>
   </si>
   <si>
     <t xml:space="preserve">5.64207458496094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55527400970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53791332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57263374328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52923345565796</t>
+    <t xml:space="preserve">5.55527353286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53791284561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57263422012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5292329788208</t>
   </si>
   <si>
     <t xml:space="preserve">5.39903116226196</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39035177230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45111227035522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09344100952148</t>
+    <t xml:space="preserve">5.39035129547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45111274719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09344053268433</t>
   </si>
   <si>
     <t xml:space="preserve">5.81567668914795</t>
@@ -1232,28 +1232,28 @@
     <t xml:space="preserve">5.77227640151978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73755645751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40771198272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24278926849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06918716430664</t>
+    <t xml:space="preserve">5.73755598068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40771102905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24278879165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0691876411438</t>
   </si>
   <si>
     <t xml:space="preserve">4.98238515853882</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07618761062622</t>
+    <t xml:space="preserve">5.07618808746338</t>
   </si>
   <si>
     <t xml:space="preserve">5.15619802474976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0850772857666</t>
+    <t xml:space="preserve">5.08507776260376</t>
   </si>
   <si>
     <t xml:space="preserve">5.24509763717651</t>
@@ -1262,16 +1262,16 @@
     <t xml:space="preserve">5.11174774169922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13841772079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20953798294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06729793548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0584077835083</t>
+    <t xml:space="preserve">5.13841724395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20953750610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.067298412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05840826034546</t>
   </si>
   <si>
     <t xml:space="preserve">5.04062795639038</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">5.04951810836792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94283723831177</t>
+    <t xml:space="preserve">4.94283771514893</t>
   </si>
   <si>
     <t xml:space="preserve">4.77392768859863</t>
@@ -1289,10 +1289,10 @@
     <t xml:space="preserve">4.90727806091309</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76503801345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92505741119385</t>
+    <t xml:space="preserve">4.76503753662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92505788803101</t>
   </si>
   <si>
     <t xml:space="preserve">4.88949775695801</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">4.93394804000854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89838790893555</t>
+    <t xml:space="preserve">4.89838838577271</t>
   </si>
   <si>
     <t xml:space="preserve">4.80948781967163</t>
@@ -1328,16 +1328,16 @@
     <t xml:space="preserve">4.98728847503662</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10285711288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.960618019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20064783096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21842765808105</t>
+    <t xml:space="preserve">5.10285806655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96061849594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20064735412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21842813491821</t>
   </si>
   <si>
     <t xml:space="preserve">5.27176761627197</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">4.99617767333984</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00506782531738</t>
+    <t xml:space="preserve">5.00506830215454</t>
   </si>
   <si>
     <t xml:space="preserve">5.37844848632812</t>
@@ -1370,13 +1370,13 @@
     <t xml:space="preserve">5.56513786315918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68070793151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65403842926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63625812530518</t>
+    <t xml:space="preserve">5.6807074546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6540379524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63625764846802</t>
   </si>
   <si>
     <t xml:space="preserve">5.5562481880188</t>
@@ -1388,10 +1388,10 @@
     <t xml:space="preserve">5.96518754959106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89406776428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77849769592285</t>
+    <t xml:space="preserve">5.89406728744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77849721908569</t>
   </si>
   <si>
     <t xml:space="preserve">5.84072780609131</t>
@@ -1400,16 +1400,16 @@
     <t xml:space="preserve">5.76071786880493</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92073774337769</t>
+    <t xml:space="preserve">5.92073822021484</t>
   </si>
   <si>
     <t xml:space="preserve">5.83183717727661</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4495677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58291816711426</t>
+    <t xml:space="preserve">5.44956874847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5829176902771</t>
   </si>
   <si>
     <t xml:space="preserve">5.43178796768188</t>
@@ -1418,28 +1418,28 @@
     <t xml:space="preserve">5.36955785751343</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60958814620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86739778518677</t>
+    <t xml:space="preserve">5.60958766937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86739730834961</t>
   </si>
   <si>
     <t xml:space="preserve">5.78738784790039</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5206880569458</t>
+    <t xml:space="preserve">5.52068758010864</t>
   </si>
   <si>
     <t xml:space="preserve">5.49401760101318</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57402753829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59180784225464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64514780044556</t>
+    <t xml:space="preserve">5.5740270614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59180736541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6451473236084</t>
   </si>
   <si>
     <t xml:space="preserve">5.71626806259155</t>
@@ -1448,10 +1448,10 @@
     <t xml:space="preserve">5.73404741287231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81405830383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67181777954102</t>
+    <t xml:space="preserve">5.81405782699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67181730270386</t>
   </si>
   <si>
     <t xml:space="preserve">5.51179838180542</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">5.85850811004639</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66292810440063</t>
+    <t xml:space="preserve">5.66292762756348</t>
   </si>
   <si>
     <t xml:space="preserve">5.53846836090088</t>
@@ -1475,10 +1475,10 @@
     <t xml:space="preserve">5.80516767501831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6184778213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46734714508057</t>
+    <t xml:space="preserve">5.61847734451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46734762191772</t>
   </si>
   <si>
     <t xml:space="preserve">5.60069799423218</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">5.45845746994019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50290775299072</t>
+    <t xml:space="preserve">5.50290822982788</t>
   </si>
   <si>
     <t xml:space="preserve">5.34288787841797</t>
@@ -1499,25 +1499,25 @@
     <t xml:space="preserve">5.52957773208618</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42289733886719</t>
+    <t xml:space="preserve">5.42289781570435</t>
   </si>
   <si>
     <t xml:space="preserve">5.72515726089478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70737791061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69848775863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00074768066406</t>
+    <t xml:space="preserve">5.70737743377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69848728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0007472038269</t>
   </si>
   <si>
     <t xml:space="preserve">5.92962741851807</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94740772247314</t>
+    <t xml:space="preserve">5.9474081993103</t>
   </si>
   <si>
     <t xml:space="preserve">5.93851709365845</t>
@@ -1526,22 +1526,22 @@
     <t xml:space="preserve">5.99185705184937</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24077796936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40968704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48080730438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.623046875</t>
+    <t xml:space="preserve">6.24077844619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40968751907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48080682754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62304639816284</t>
   </si>
   <si>
     <t xml:space="preserve">6.84529685974121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99642658233643</t>
+    <t xml:space="preserve">6.99642705917358</t>
   </si>
   <si>
     <t xml:space="preserve">7.0142068862915</t>
@@ -1556,7 +1556,7 @@
     <t xml:space="preserve">6.97864675521851</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00531721115112</t>
+    <t xml:space="preserve">7.00531673431396</t>
   </si>
   <si>
     <t xml:space="preserve">7.0230975151062</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">7.24534702301025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27201700210571</t>
+    <t xml:space="preserve">7.27201747894287</t>
   </si>
   <si>
     <t xml:space="preserve">7.33424758911133</t>
@@ -1580,25 +1580,25 @@
     <t xml:space="preserve">7.73429679870605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72540760040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79652643203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80541658401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22324562072754</t>
+    <t xml:space="preserve">7.72540664672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79652738571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80541753768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22324657440186</t>
   </si>
   <si>
     <t xml:space="preserve">8.21435642242432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15212631225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12545776367188</t>
+    <t xml:space="preserve">8.15212726593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12545680999756</t>
   </si>
   <si>
     <t xml:space="preserve">8.00099754333496</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">8.17879676818848</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34770679473877</t>
+    <t xml:space="preserve">8.34770774841309</t>
   </si>
   <si>
     <t xml:space="preserve">8.42771625518799</t>
@@ -1628,16 +1628,16 @@
     <t xml:space="preserve">8.66774654388428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8010950088501</t>
+    <t xml:space="preserve">8.80109596252441</t>
   </si>
   <si>
     <t xml:space="preserve">8.88999557495117</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19225692749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37005710601807</t>
+    <t xml:space="preserve">9.19225788116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37005615234375</t>
   </si>
   <si>
     <t xml:space="preserve">9.47673511505127</t>
@@ -1646,19 +1646,19 @@
     <t xml:space="preserve">9.49451637268066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31671524047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15669536590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35227680206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40561676025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69009494781494</t>
+    <t xml:space="preserve">9.31671619415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15669631958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35227584838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40561580657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69009590148926</t>
   </si>
   <si>
     <t xml:space="preserve">9.86789608001709</t>
@@ -1670,13 +1670,13 @@
     <t xml:space="preserve">9.77899551391602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44117546081543</t>
+    <t xml:space="preserve">9.44117641448975</t>
   </si>
   <si>
     <t xml:space="preserve">9.21003532409668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58341598510742</t>
+    <t xml:space="preserve">9.58341503143311</t>
   </si>
   <si>
     <t xml:space="preserve">9.51229667663574</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">9.67231559753418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8501148223877</t>
+    <t xml:space="preserve">9.85011577606201</t>
   </si>
   <si>
     <t xml:space="preserve">10.0990362167358</t>
@@ -1697,31 +1697,31 @@
     <t xml:space="preserve">9.99235534667969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0101356506348</t>
+    <t xml:space="preserve">10.0101366043091</t>
   </si>
   <si>
     <t xml:space="preserve">9.76121616363525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88567447662354</t>
+    <t xml:space="preserve">9.88567543029785</t>
   </si>
   <si>
     <t xml:space="preserve">10.2234954833984</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4368553161621</t>
+    <t xml:space="preserve">10.4368562698364</t>
   </si>
   <si>
     <t xml:space="preserve">10.6679954528809</t>
   </si>
   <si>
-    <t xml:space="preserve">11.414755821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3614158630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3080768585205</t>
+    <t xml:space="preserve">11.4147548675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3614149093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3080759048462</t>
   </si>
   <si>
     <t xml:space="preserve">11.4325361251831</t>
@@ -1730,7 +1730,7 @@
     <t xml:space="preserve">11.6814556121826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8948154449463</t>
+    <t xml:space="preserve">11.8948163986206</t>
   </si>
   <si>
     <t xml:space="preserve">11.965934753418</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">12.1437349319458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.628116607666</t>
+    <t xml:space="preserve">11.6281156539917</t>
   </si>
   <si>
     <t xml:space="preserve">11.4001131057739</t>
@@ -1754,10 +1754,10 @@
     <t xml:space="preserve">11.689640045166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1239280700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7982120513916</t>
+    <t xml:space="preserve">12.1239290237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7982130050659</t>
   </si>
   <si>
     <t xml:space="preserve">12.1782159805298</t>
@@ -1766,13 +1766,13 @@
     <t xml:space="preserve">12.3229789733887</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9925088882446</t>
+    <t xml:space="preserve">12.9925098419189</t>
   </si>
   <si>
     <t xml:space="preserve">12.8296508789062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7391738891602</t>
+    <t xml:space="preserve">12.7391748428345</t>
   </si>
   <si>
     <t xml:space="preserve">12.7753648757935</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">12.3953609466553</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2867889404297</t>
+    <t xml:space="preserve">12.2867879867554</t>
   </si>
   <si>
     <t xml:space="preserve">12.6306018829346</t>
@@ -1790,13 +1790,13 @@
     <t xml:space="preserve">12.4496479034424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2144079208374</t>
+    <t xml:space="preserve">12.2144069671631</t>
   </si>
   <si>
     <t xml:space="preserve">12.1058349609375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8705930709839</t>
+    <t xml:space="preserve">11.8705940246582</t>
   </si>
   <si>
     <t xml:space="preserve">11.9067850112915</t>
@@ -1805,16 +1805,16 @@
     <t xml:space="preserve">11.4724950790405</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4182081222534</t>
+    <t xml:space="preserve">11.4182071685791</t>
   </si>
   <si>
     <t xml:space="preserve">11.5810670852661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.852499961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0877389907837</t>
+    <t xml:space="preserve">11.8524990081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.087739944458</t>
   </si>
   <si>
     <t xml:space="preserve">11.8344030380249</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">11.1648731231689</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8391551971436</t>
+    <t xml:space="preserve">10.8391542434692</t>
   </si>
   <si>
     <t xml:space="preserve">10.6401052474976</t>
@@ -1847,16 +1847,16 @@
     <t xml:space="preserve">10.6762971878052</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5134382247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9115381240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2915391921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1467761993408</t>
+    <t xml:space="preserve">10.5134372711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9115371704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.291540145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1467771530151</t>
   </si>
   <si>
     <t xml:space="preserve">10.7667722702026</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">10.6220092773438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0020122528076</t>
+    <t xml:space="preserve">11.0020132064819</t>
   </si>
   <si>
     <t xml:space="preserve">10.6039152145386</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">10.4953422546387</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2781963348389</t>
+    <t xml:space="preserve">10.2781972885132</t>
   </si>
   <si>
     <t xml:space="preserve">10.3143882751465</t>
@@ -1910,7 +1910,7 @@
     <t xml:space="preserve">10.3867702484131</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4410562515259</t>
+    <t xml:space="preserve">10.4410552978516</t>
   </si>
   <si>
     <t xml:space="preserve">9.55438041687012</t>
@@ -1931,13 +1931,13 @@
     <t xml:space="preserve">11.0201101303101</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8572492599487</t>
+    <t xml:space="preserve">10.857250213623</t>
   </si>
   <si>
     <t xml:space="preserve">10.8753461837769</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5858192443848</t>
+    <t xml:space="preserve">10.5858182907104</t>
   </si>
   <si>
     <t xml:space="preserve">10.8029642105103</t>
@@ -1955,16 +1955,16 @@
     <t xml:space="preserve">11.3096361160278</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4543991088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.725830078125</t>
+    <t xml:space="preserve">11.4543981552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7258310317993</t>
   </si>
   <si>
     <t xml:space="preserve">11.9972620010376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.160120010376</t>
+    <t xml:space="preserve">12.1601209640503</t>
   </si>
   <si>
     <t xml:space="preserve">12.0515480041504</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">12.0334529876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9429750442505</t>
+    <t xml:space="preserve">11.9429759979248</t>
   </si>
   <si>
     <t xml:space="preserve">11.7620220184326</t>
@@ -2006,10 +2006,10 @@
     <t xml:space="preserve">10.4229612350464</t>
   </si>
   <si>
-    <t xml:space="preserve">10.13343334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3324823379517</t>
+    <t xml:space="preserve">10.1334342956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.332483291626</t>
   </si>
   <si>
     <t xml:space="preserve">10.2239112854004</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">10.097243309021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0610523223877</t>
+    <t xml:space="preserve">10.061053276062</t>
   </si>
   <si>
     <t xml:space="preserve">10.0791482925415</t>
@@ -2051,13 +2051,13 @@
     <t xml:space="preserve">9.51819038391113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71723937988281</t>
+    <t xml:space="preserve">9.7172384262085</t>
   </si>
   <si>
     <t xml:space="preserve">9.42771244049072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59057235717773</t>
+    <t xml:space="preserve">9.59057140350342</t>
   </si>
   <si>
     <t xml:space="preserve">11.3639221191406</t>
@@ -2072,10 +2072,10 @@
     <t xml:space="preserve">12.3772659301758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3820180892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5629720687866</t>
+    <t xml:space="preserve">11.3820171356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5629711151123</t>
   </si>
   <si>
     <t xml:space="preserve">11.6172590255737</t>
@@ -2096,13 +2096,13 @@
     <t xml:space="preserve">8.68580055236816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43246364593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0481653213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32864475250244</t>
+    <t xml:space="preserve">8.43246459960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04816484451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3286452293396</t>
   </si>
   <si>
     <t xml:space="preserve">7.24721479415894</t>
@@ -2111,13 +2111,13 @@
     <t xml:space="preserve">7.1838812828064</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58673286437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65006589889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96673583984375</t>
+    <t xml:space="preserve">6.58673238754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65006542205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96673631668091</t>
   </si>
   <si>
     <t xml:space="preserve">6.97578382492065</t>
@@ -2132,10 +2132,10 @@
     <t xml:space="preserve">7.28340530395508</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60912227630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76293420791626</t>
+    <t xml:space="preserve">7.60912322998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76293325424194</t>
   </si>
   <si>
     <t xml:space="preserve">8.34198760986328</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">9.04770946502686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26485252380371</t>
+    <t xml:space="preserve">9.26485347747803</t>
   </si>
   <si>
     <t xml:space="preserve">9.50009441375732</t>
@@ -2171,19 +2171,19 @@
     <t xml:space="preserve">9.86200141906738</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2191581726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9839191436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6582021713257</t>
+    <t xml:space="preserve">11.2191591262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9839181900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6582012176514</t>
   </si>
   <si>
     <t xml:space="preserve">9.97057437896729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2058153152466</t>
+    <t xml:space="preserve">10.2058162689209</t>
   </si>
   <si>
     <t xml:space="preserve">9.84390735626221</t>
@@ -2192,7 +2192,7 @@
     <t xml:space="preserve">10.4591512680054</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9296312332153</t>
+    <t xml:space="preserve">10.9296321868896</t>
   </si>
   <si>
     <t xml:space="preserve">10.7305822372437</t>
@@ -2219,10 +2219,10 @@
     <t xml:space="preserve">12.7934598922729</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4315519332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.594409942627</t>
+    <t xml:space="preserve">12.4315509796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5944108963013</t>
   </si>
   <si>
     <t xml:space="preserve">12.6486968994141</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">13.0287008285522</t>
   </si>
   <si>
-    <t xml:space="preserve">13.119176864624</t>
+    <t xml:space="preserve">13.1191778182983</t>
   </si>
   <si>
     <t xml:space="preserve">12.9382238388062</t>
@@ -2249,16 +2249,16 @@
     <t xml:space="preserve">13.082986831665</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3725137710571</t>
+    <t xml:space="preserve">13.3725128173828</t>
   </si>
   <si>
     <t xml:space="preserve">13.3544187545776</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4534873962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2496852874756</t>
+    <t xml:space="preserve">15.4534854888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.249683380127</t>
   </si>
   <si>
     <t xml:space="preserve">16.2858753204346</t>
@@ -2303,13 +2303,13 @@
     <t xml:space="preserve">15.7792043685913</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7249193191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4125423431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8153963088989</t>
+    <t xml:space="preserve">15.7249174118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4125442504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8153944015503</t>
   </si>
   <si>
     <t xml:space="preserve">15.9420642852783</t>
@@ -2318,10 +2318,10 @@
     <t xml:space="preserve">15.6344404220581</t>
   </si>
   <si>
-    <t xml:space="preserve">16.104923248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9601583480835</t>
+    <t xml:space="preserve">16.1049213409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9601564407349</t>
   </si>
   <si>
     <t xml:space="preserve">15.6887264251709</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">15.6525344848633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3630084991455</t>
+    <t xml:space="preserve">15.3630094528198</t>
   </si>
   <si>
     <t xml:space="preserve">15.4896783828735</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">15.1458644866943</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0372924804688</t>
+    <t xml:space="preserve">15.0372943878174</t>
   </si>
   <si>
     <t xml:space="preserve">15.7430114746094</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">15.2906274795532</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5887489318848</t>
+    <t xml:space="preserve">17.5887470245361</t>
   </si>
   <si>
     <t xml:space="preserve">17.7696990966797</t>
@@ -2366,7 +2366,7 @@
     <t xml:space="preserve">18.0230350494385</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1359043121338</t>
+    <t xml:space="preserve">19.1359024047852</t>
   </si>
   <si>
     <t xml:space="preserve">18.2763710021973</t>
@@ -2390,13 +2390,13 @@
     <t xml:space="preserve">17.0277881622314</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7020683288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.009693145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4077911376953</t>
+    <t xml:space="preserve">16.7020702362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0096950531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4077892303467</t>
   </si>
   <si>
     <t xml:space="preserve">18.5025653839111</t>
@@ -2411,13 +2411,13 @@
     <t xml:space="preserve">17.4982681274414</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9868450164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5930404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1544551849365</t>
+    <t xml:space="preserve">17.9868431091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5930423736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1544570922852</t>
   </si>
   <si>
     <t xml:space="preserve">17.2449321746826</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">17.1182632446289</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8106422424316</t>
+    <t xml:space="preserve">16.8106441497803</t>
   </si>
   <si>
     <t xml:space="preserve">16.8287372589111</t>
@@ -2441,13 +2441,13 @@
     <t xml:space="preserve">17.0639801025391</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8468341827393</t>
+    <t xml:space="preserve">16.8468360900879</t>
   </si>
   <si>
     <t xml:space="preserve">16.9011211395264</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3173141479492</t>
+    <t xml:space="preserve">17.3173122406006</t>
   </si>
   <si>
     <t xml:space="preserve">17.2087421417236</t>
@@ -2465,10 +2465,10 @@
     <t xml:space="preserve">18.6382808685303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7287578582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9549503326416</t>
+    <t xml:space="preserve">18.728759765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9549522399902</t>
   </si>
   <si>
     <t xml:space="preserve">18.8644714355469</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">19.5430526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0454292297363</t>
+    <t xml:space="preserve">19.0454273223877</t>
   </si>
   <si>
     <t xml:space="preserve">19.0001888275146</t>
@@ -2501,13 +2501,13 @@
     <t xml:space="preserve">19.0906658172607</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6835174560547</t>
+    <t xml:space="preserve">18.6835193634033</t>
   </si>
   <si>
     <t xml:space="preserve">18.0954189300537</t>
   </si>
   <si>
-    <t xml:space="preserve">18.004940032959</t>
+    <t xml:space="preserve">18.0049419403076</t>
   </si>
   <si>
     <t xml:space="preserve">17.570650100708</t>
@@ -2525,10 +2525,10 @@
     <t xml:space="preserve">19.2716178894043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1811447143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.26686668396</t>
+    <t xml:space="preserve">19.1811428070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2668685913086</t>
   </si>
   <si>
     <t xml:space="preserve">20.4930610656738</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">19.9954376220703</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2263813018799</t>
+    <t xml:space="preserve">19.2263793945312</t>
   </si>
   <si>
     <t xml:space="preserve">19.4525756835938</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">20.0859127044678</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1311511993408</t>
+    <t xml:space="preserve">20.1311531066895</t>
   </si>
   <si>
     <t xml:space="preserve">19.8597202301025</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">20.674015045166</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0359230041504</t>
+    <t xml:space="preserve">21.0359210968018</t>
   </si>
   <si>
     <t xml:space="preserve">20.8097267150879</t>
@@ -2600,13 +2600,13 @@
     <t xml:space="preserve">20.4478225708008</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8821125030518</t>
+    <t xml:space="preserve">20.8821105957031</t>
   </si>
   <si>
     <t xml:space="preserve">21.2802104949951</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3344955444336</t>
+    <t xml:space="preserve">21.3344974517822</t>
   </si>
   <si>
     <t xml:space="preserve">21.587833404541</t>
@@ -2630,10 +2630,10 @@
     <t xml:space="preserve">22.7821292877197</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8592624664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0040245056152</t>
+    <t xml:space="preserve">21.8592643737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0040264129639</t>
   </si>
   <si>
     <t xml:space="preserve">22.2573642730713</t>
@@ -2645,13 +2645,13 @@
     <t xml:space="preserve">22.1126003265381</t>
   </si>
   <si>
-    <t xml:space="preserve">22.058313369751</t>
+    <t xml:space="preserve">22.0583152770996</t>
   </si>
   <si>
     <t xml:space="preserve">22.6011772155762</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6373691558838</t>
+    <t xml:space="preserve">22.6373672485352</t>
   </si>
   <si>
     <t xml:space="preserve">22.420223236084</t>
@@ -2669,10 +2669,10 @@
     <t xml:space="preserve">22.09450340271</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5830783843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0354671478271</t>
+    <t xml:space="preserve">22.583080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0354652404785</t>
   </si>
   <si>
     <t xml:space="preserve">23.0173721313477</t>
@@ -2681,10 +2681,10 @@
     <t xml:space="preserve">23.3611831665039</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2707080841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0440578460693</t>
+    <t xml:space="preserve">23.2707061767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.044059753418</t>
   </si>
   <si>
     <t xml:space="preserve">24.7726249694824</t>
@@ -2696,10 +2696,10 @@
     <t xml:space="preserve">25.0621528625488</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9126377105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.238353729248</t>
+    <t xml:space="preserve">25.9126396179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2383556365967</t>
   </si>
   <si>
     <t xml:space="preserve">26.676570892334</t>
@@ -70658,7 +70658,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.6912731481</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>59079</v>
@@ -70679,6 +70679,32 @@
         <v>1776</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.6910185185</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>158645</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>14.8999996185303</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>14.8100004196167</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>14.8999996185303</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>14.8100004196167</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>1775</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TNXT.MI.xlsx
+++ b/data/TNXT.MI.xlsx
@@ -44,19 +44,19 @@
     <t xml:space="preserve">TNXT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6515097618103</t>
+    <t xml:space="preserve">2.65151000022888</t>
   </si>
   <si>
     <t xml:space="preserve">2.59350872039795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53550696372986</t>
+    <t xml:space="preserve">2.53550672531128</t>
   </si>
   <si>
     <t xml:space="preserve">2.52556347846985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48579072952271</t>
+    <t xml:space="preserve">2.48579096794128</t>
   </si>
   <si>
     <t xml:space="preserve">2.52722072601318</t>
@@ -65,40 +65,40 @@
     <t xml:space="preserve">2.48744797706604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47087574005127</t>
+    <t xml:space="preserve">2.47087597846985</t>
   </si>
   <si>
     <t xml:space="preserve">2.46921849250793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54047822952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49739098548889</t>
+    <t xml:space="preserve">2.54047846794128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49739122390747</t>
   </si>
   <si>
     <t xml:space="preserve">2.47916197776794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44436049461365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39464449882507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34161448478699</t>
+    <t xml:space="preserve">2.44436097145081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39464497566223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34161472320557</t>
   </si>
   <si>
     <t xml:space="preserve">2.36150097846985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55207872390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58522248268127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61007952690125</t>
+    <t xml:space="preserve">2.55207896232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58522295951843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6100800037384</t>
   </si>
   <si>
     <t xml:space="preserve">2.56865072250366</t>
@@ -107,19 +107,19 @@
     <t xml:space="preserve">2.63659501075745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68962550163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73436975479126</t>
+    <t xml:space="preserve">2.68962526321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7343692779541</t>
   </si>
   <si>
     <t xml:space="preserve">2.72608351707458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77579927444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58025121688843</t>
+    <t xml:space="preserve">2.77579975128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58025097846985</t>
   </si>
   <si>
     <t xml:space="preserve">2.56202173233032</t>
@@ -137,31 +137,31 @@
     <t xml:space="preserve">2.60842251777649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66642451286316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65316677093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62665176391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69293975830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82551527023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81722974777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90008950233459</t>
+    <t xml:space="preserve">2.66642427444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65316700935364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62665152549744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6929395198822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82551550865173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81722950935364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90008926391602</t>
   </si>
   <si>
     <t xml:space="preserve">2.85865926742554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89843249320984</t>
+    <t xml:space="preserve">2.89843201637268</t>
   </si>
   <si>
     <t xml:space="preserve">2.88351726531982</t>
@@ -170,19 +170,19 @@
     <t xml:space="preserve">2.87523150444031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86694550514221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81888628005981</t>
+    <t xml:space="preserve">2.86694574356079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81888675689697</t>
   </si>
   <si>
     <t xml:space="preserve">2.82054400444031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85368776321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79237151145935</t>
+    <t xml:space="preserve">2.85368800163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79237174987793</t>
   </si>
   <si>
     <t xml:space="preserve">2.85700178146362</t>
@@ -194,46 +194,46 @@
     <t xml:space="preserve">2.82882976531982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85037326812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90837526321411</t>
+    <t xml:space="preserve">2.85037350654602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90837550163269</t>
   </si>
   <si>
     <t xml:space="preserve">2.96306300163269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95797729492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88169741630554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89017248153687</t>
+    <t xml:space="preserve">2.9579770565033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8816967010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89017295837402</t>
   </si>
   <si>
     <t xml:space="preserve">2.86474585533142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94950175285339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92407488822937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96645331382751</t>
+    <t xml:space="preserve">2.94950199127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92407512664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96645307540894</t>
   </si>
   <si>
     <t xml:space="preserve">3.11901307106018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9427216053009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94780683517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88339185714722</t>
+    <t xml:space="preserve">2.94272136688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94780707359314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88339233398438</t>
   </si>
   <si>
     <t xml:space="preserve">2.87322163581848</t>
@@ -242,16 +242,16 @@
     <t xml:space="preserve">2.85966062545776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03256297111511</t>
+    <t xml:space="preserve">3.03256273269653</t>
   </si>
   <si>
     <t xml:space="preserve">3.07037353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06866312026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06011080741882</t>
+    <t xml:space="preserve">3.06866335868835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0601110458374</t>
   </si>
   <si>
     <t xml:space="preserve">2.99340057373047</t>
@@ -260,16 +260,16 @@
     <t xml:space="preserve">2.98484778404236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93524289131165</t>
+    <t xml:space="preserve">2.93524265289307</t>
   </si>
   <si>
     <t xml:space="preserve">2.98313736915588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9249804019928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92326903343201</t>
+    <t xml:space="preserve">2.92498016357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92326927185059</t>
   </si>
   <si>
     <t xml:space="preserve">2.96774291992188</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">3.05840015411377</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05497908592224</t>
+    <t xml:space="preserve">3.05497884750366</t>
   </si>
   <si>
     <t xml:space="preserve">3.08747863769531</t>
@@ -290,28 +290,28 @@
     <t xml:space="preserve">3.13879442214966</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12853097915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19010949134827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15589952468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12339997291565</t>
+    <t xml:space="preserve">3.12853074073792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19010996818542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15589928627014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12339949607849</t>
   </si>
   <si>
     <t xml:space="preserve">3.12511014938354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14734721183777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16445207595825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16616225242615</t>
+    <t xml:space="preserve">3.14734673500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16445183753967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16616249084473</t>
   </si>
   <si>
     <t xml:space="preserve">3.24142503738403</t>
@@ -320,13 +320,13 @@
     <t xml:space="preserve">3.30129289627075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3868191242218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48431825637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52708148956299</t>
+    <t xml:space="preserve">3.38681888580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48431777954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52708101272583</t>
   </si>
   <si>
     <t xml:space="preserve">3.62629079818726</t>
@@ -338,31 +338,31 @@
     <t xml:space="preserve">3.64510703086853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74602651596069</t>
+    <t xml:space="preserve">3.74602746963501</t>
   </si>
   <si>
     <t xml:space="preserve">3.6776065826416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71181678771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63484334945679</t>
+    <t xml:space="preserve">3.71181750297546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63484358787537</t>
   </si>
   <si>
     <t xml:space="preserve">3.51681780815125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50484418869019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4945809841156</t>
+    <t xml:space="preserve">3.50484466552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49458122253418</t>
   </si>
   <si>
     <t xml:space="preserve">3.50655508041382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48089742660522</t>
+    <t xml:space="preserve">3.48089694976807</t>
   </si>
   <si>
     <t xml:space="preserve">3.43129205703735</t>
@@ -374,46 +374,46 @@
     <t xml:space="preserve">3.60063290596008</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64681720733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69471168518066</t>
+    <t xml:space="preserve">3.64681696891785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69471192359924</t>
   </si>
   <si>
     <t xml:space="preserve">3.69984292984009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67589569091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6656322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59721231460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63313317298889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57497525215149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66050148010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68615865707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7152373790741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73747444152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71010637283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69129061698914</t>
+    <t xml:space="preserve">3.67589592933655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66563320159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59721207618713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63313293457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57497549057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66050124168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68615937232971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71523761749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7374746799469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71010565757751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69129037857056</t>
   </si>
   <si>
     <t xml:space="preserve">3.68957996368408</t>
@@ -425,109 +425,109 @@
     <t xml:space="preserve">3.72036933898926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76313161849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77168488502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62115955352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64168524742126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70326399803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79734253883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7545793056488</t>
+    <t xml:space="preserve">3.76313233375549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77168440818787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62115979194641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64168548583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70326447486877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79734230041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75457978248596</t>
   </si>
   <si>
     <t xml:space="preserve">3.9085259437561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76655292510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72892117500305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66734337806702</t>
+    <t xml:space="preserve">3.76655268669128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72892165184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6673436164856</t>
   </si>
   <si>
     <t xml:space="preserve">3.50997591018677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49800276756287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48944973945618</t>
+    <t xml:space="preserve">3.49800229072571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4894495010376</t>
   </si>
   <si>
     <t xml:space="preserve">3.47234463691711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40392422676086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43642401695251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53221273422241</t>
+    <t xml:space="preserve">3.40392398834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43642425537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53221297264099</t>
   </si>
   <si>
     <t xml:space="preserve">3.5185284614563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46037101745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50142312049866</t>
+    <t xml:space="preserve">3.46037077903748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50142335891724</t>
   </si>
   <si>
     <t xml:space="preserve">3.53563332557678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55615973472595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6433961391449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72550058364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84865808486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82984209060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8315532207489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87089395523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8452365398407</t>
+    <t xml:space="preserve">3.55615997314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64339637756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72550082206726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84865784645081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82984256744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83155250549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87089467048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84523630142212</t>
   </si>
   <si>
     <t xml:space="preserve">3.87431526184082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86405253410339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8572108745575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82471084594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90681505203247</t>
+    <t xml:space="preserve">3.86405277252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85720992088318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82471108436584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90681552886963</t>
   </si>
   <si>
     <t xml:space="preserve">4.00260400772095</t>
@@ -536,10 +536,10 @@
     <t xml:space="preserve">4.17536640167236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11378717422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00773572921753</t>
+    <t xml:space="preserve">4.11378812789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00773620605469</t>
   </si>
   <si>
     <t xml:space="preserve">4.05220890045166</t>
@@ -548,43 +548,43 @@
     <t xml:space="preserve">4.08128786087036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00602531433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09839248657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01970863342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01115655899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99576139450073</t>
+    <t xml:space="preserve">4.0060248374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09839296340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01970911026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01115703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99576187133789</t>
   </si>
   <si>
     <t xml:space="preserve">4.0351037979126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06247186660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13773441314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12234020233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14799785614014</t>
+    <t xml:space="preserve">4.06247282028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13773488998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12234115600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14799833297729</t>
   </si>
   <si>
     <t xml:space="preserve">4.18904972076416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2591814994812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22839117050171</t>
+    <t xml:space="preserve">4.25918102264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22839260101318</t>
   </si>
   <si>
     <t xml:space="preserve">4.20615530014038</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">4.02142000198364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99405121803284</t>
+    <t xml:space="preserve">3.99405169487</t>
   </si>
   <si>
     <t xml:space="preserve">4.01799869537354</t>
@@ -605,13 +605,13 @@
     <t xml:space="preserve">4.07615613937378</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12747192382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11891889572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10523509979248</t>
+    <t xml:space="preserve">4.12747240066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11891937255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10523557662964</t>
   </si>
   <si>
     <t xml:space="preserve">4.09668207168579</t>
@@ -620,43 +620,43 @@
     <t xml:space="preserve">4.10181379318237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07102537155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09497213363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13089275360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21641874313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52431154251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54996919631958</t>
+    <t xml:space="preserve">4.0710244178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09497261047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13089227676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21641826629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52431106567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54996871948242</t>
   </si>
   <si>
     <t xml:space="preserve">4.53713941574097</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46444272994995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50292921066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56707429885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6226658821106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63549518585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58417892456055</t>
+    <t xml:space="preserve">4.46444320678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56707382202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62266492843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63549470901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58417940139771</t>
   </si>
   <si>
     <t xml:space="preserve">4.60128402709961</t>
@@ -674,10 +674,10 @@
     <t xml:space="preserve">4.55852079391479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48154735565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5157585144043</t>
+    <t xml:space="preserve">4.48154830932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51575899124146</t>
   </si>
   <si>
     <t xml:space="preserve">4.4901008605957</t>
@@ -692,79 +692,79 @@
     <t xml:space="preserve">4.78516483306885</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75950622558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78944110870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73384952545166</t>
+    <t xml:space="preserve">4.75950717926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7894401550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7338490486145</t>
   </si>
   <si>
     <t xml:space="preserve">4.77233552932739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76378345489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65687656402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69536304473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8279275894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90062379837036</t>
+    <t xml:space="preserve">4.76378393173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65687608718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69536161422729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82792711257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90062427520752</t>
   </si>
   <si>
     <t xml:space="preserve">4.91772937774658</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94338750839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98614978790283</t>
+    <t xml:space="preserve">4.94338798522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98615026473999</t>
   </si>
   <si>
     <t xml:space="preserve">5.0417423248291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02036046981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0716757774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08022880554199</t>
+    <t xml:space="preserve">5.02035999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07167530059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08022832870483</t>
   </si>
   <si>
     <t xml:space="preserve">4.99470281600952</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09305763244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06050634384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91728496551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94766521453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92596435546875</t>
+    <t xml:space="preserve">5.09305715560913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06050682067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91728544235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94766473770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92596578598022</t>
   </si>
   <si>
     <t xml:space="preserve">4.9042649269104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8218035697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7350025177002</t>
+    <t xml:space="preserve">4.82180309295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73500204086304</t>
   </si>
   <si>
     <t xml:space="preserve">4.72198247909546</t>
@@ -791,58 +791,58 @@
     <t xml:space="preserve">4.65688133239746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54837989807129</t>
+    <t xml:space="preserve">4.54838037490845</t>
   </si>
   <si>
     <t xml:space="preserve">4.53535985946655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47025871276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59612035751343</t>
+    <t xml:space="preserve">4.47025966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59612131118774</t>
   </si>
   <si>
     <t xml:space="preserve">4.47459936141968</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48761987686157</t>
+    <t xml:space="preserve">4.48761892318726</t>
   </si>
   <si>
     <t xml:space="preserve">4.46157884597778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4138388633728</t>
+    <t xml:space="preserve">4.41383838653564</t>
   </si>
   <si>
     <t xml:space="preserve">4.38779783248901</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39213848114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40949821472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55705976486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52233982086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57008075714111</t>
+    <t xml:space="preserve">4.39213800430298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40949773788452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55706071853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52234029769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57008028030396</t>
   </si>
   <si>
     <t xml:space="preserve">4.53970003128052</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47893905639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43553829193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42251825332642</t>
+    <t xml:space="preserve">4.47893857955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43553924560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42251873016357</t>
   </si>
   <si>
     <t xml:space="preserve">4.43119859695435</t>
@@ -854,16 +854,16 @@
     <t xml:space="preserve">4.51365900039673</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68726205825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60046052932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6395206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56139993667603</t>
+    <t xml:space="preserve">4.68726253509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60046100616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63952112197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56140041351318</t>
   </si>
   <si>
     <t xml:space="preserve">4.58744049072266</t>
@@ -872,13 +872,13 @@
     <t xml:space="preserve">4.61782121658325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64820098876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6048002243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58310031890869</t>
+    <t xml:space="preserve">4.64820146560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60480070114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58310079574585</t>
   </si>
   <si>
     <t xml:space="preserve">4.49629926681519</t>
@@ -893,16 +893,16 @@
     <t xml:space="preserve">4.49195957183838</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51799917221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80878400802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77840280532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84784460067749</t>
+    <t xml:space="preserve">4.51800012588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80878305435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77840423583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84784412384033</t>
   </si>
   <si>
     <t xml:space="preserve">4.8348240852356</t>
@@ -911,43 +911,43 @@
     <t xml:space="preserve">4.74368286132812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81312417984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71330165863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70462274551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72632312774658</t>
+    <t xml:space="preserve">4.81312370300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71330261230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70462226867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72632265090942</t>
   </si>
   <si>
     <t xml:space="preserve">4.69594192504883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76972341537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84350395202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87822389602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8738842010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97370576858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97804641723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00842571258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07786655426025</t>
+    <t xml:space="preserve">4.7697229385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84350442886353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87822437286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87388372421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97370529174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97804594039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00842618942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07786750793457</t>
   </si>
   <si>
     <t xml:space="preserve">5.04314661026001</t>
@@ -959,16 +959,16 @@
     <t xml:space="preserve">4.86086416244507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.869544506073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96502494812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90860509872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99974584579468</t>
+    <t xml:space="preserve">4.86954498291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96502542495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90860462188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99974679946899</t>
   </si>
   <si>
     <t xml:space="preserve">4.99106597900391</t>
@@ -977,22 +977,22 @@
     <t xml:space="preserve">5.1559886932373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12994766235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29487037658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41639089584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48583269119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43375205993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48149251937866</t>
+    <t xml:space="preserve">5.12994718551636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2948694229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41639137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48583221435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43375158309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48149347305298</t>
   </si>
   <si>
     <t xml:space="preserve">5.42073154449463</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">5.39469146728516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35563087463379</t>
+    <t xml:space="preserve">5.35563039779663</t>
   </si>
   <si>
     <t xml:space="preserve">5.33393049240112</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37299060821533</t>
+    <t xml:space="preserve">5.37299108505249</t>
   </si>
   <si>
     <t xml:space="preserve">5.33827114105225</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20806884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16466808319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26449012756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25146961212158</t>
+    <t xml:space="preserve">5.20806932449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16466760635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26448965072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25147008895874</t>
   </si>
   <si>
     <t xml:space="preserve">5.26014995574951</t>
@@ -1031,43 +1031,43 @@
     <t xml:space="preserve">5.18636846542358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20372867584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19504880905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16900825500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18202877044678</t>
+    <t xml:space="preserve">5.20372819900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19504833221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16900873184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18202829360962</t>
   </si>
   <si>
     <t xml:space="preserve">5.19938850402832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22542905807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42507123947144</t>
+    <t xml:space="preserve">5.22542953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42507171630859</t>
   </si>
   <si>
     <t xml:space="preserve">5.61603403091431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72887563705444</t>
+    <t xml:space="preserve">5.7288761138916</t>
   </si>
   <si>
     <t xml:space="preserve">5.71151542663574</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78963661193848</t>
+    <t xml:space="preserve">5.78963613510132</t>
   </si>
   <si>
     <t xml:space="preserve">5.82435703277588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87643766403198</t>
+    <t xml:space="preserve">5.87643814086914</t>
   </si>
   <si>
     <t xml:space="preserve">5.88511800765991</t>
@@ -1082,7 +1082,7 @@
     <t xml:space="preserve">5.80699682235718</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92851877212524</t>
+    <t xml:space="preserve">5.92851829528809</t>
   </si>
   <si>
     <t xml:space="preserve">5.97191858291626</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">5.95455884933472</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03268003463745</t>
+    <t xml:space="preserve">6.03267908096313</t>
   </si>
   <si>
     <t xml:space="preserve">6.17156171798706</t>
@@ -1100,70 +1100,70 @@
     <t xml:space="preserve">6.28440284729004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01531887054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02400064468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21496152877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14552116394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40592432022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07608079910278</t>
+    <t xml:space="preserve">6.01531934738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02399921417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21496200561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14552164077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40592479705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07608032226562</t>
   </si>
   <si>
     <t xml:space="preserve">5.98927927017212</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04135990142822</t>
+    <t xml:space="preserve">6.04136037826538</t>
   </si>
   <si>
     <t xml:space="preserve">6.22364234924316</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13684129714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19760179519653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15420198440552</t>
+    <t xml:space="preserve">6.1368408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19760274887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1542010307312</t>
   </si>
   <si>
     <t xml:space="preserve">6.05003976821899</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89379787445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90247821807861</t>
+    <t xml:space="preserve">5.89379739761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90247869491577</t>
   </si>
   <si>
     <t xml:space="preserve">5.70283555984497</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50319290161133</t>
+    <t xml:space="preserve">5.50319242477417</t>
   </si>
   <si>
     <t xml:space="preserve">5.58131408691406</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72019577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76359605789185</t>
+    <t xml:space="preserve">5.72019624710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.763596534729</t>
   </si>
   <si>
     <t xml:space="preserve">5.91983795166016</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99795913696289</t>
+    <t xml:space="preserve">5.99795866012573</t>
   </si>
   <si>
     <t xml:space="preserve">5.83303689956665</t>
@@ -1172,58 +1172,58 @@
     <t xml:space="preserve">5.79831647872925</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6594352722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51187229156494</t>
+    <t xml:space="preserve">5.65943479537964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5118727684021</t>
   </si>
   <si>
     <t xml:space="preserve">5.54659366607666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58999443054199</t>
+    <t xml:space="preserve">5.58999395370483</t>
   </si>
   <si>
     <t xml:space="preserve">5.52055311203003</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38167142868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44243192672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46847200393677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6767954826355</t>
+    <t xml:space="preserve">5.3816704750061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44243240356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46847295761108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67679500579834</t>
   </si>
   <si>
     <t xml:space="preserve">5.64207458496094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55527305603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53791379928589</t>
+    <t xml:space="preserve">5.55527400970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53791284561157</t>
   </si>
   <si>
     <t xml:space="preserve">5.57263374328613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52923345565796</t>
+    <t xml:space="preserve">5.5292329788208</t>
   </si>
   <si>
     <t xml:space="preserve">5.39903116226196</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39035129547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45111179351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09344053268433</t>
+    <t xml:space="preserve">5.39035177230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45111131668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09344100952148</t>
   </si>
   <si>
     <t xml:space="preserve">5.81567621231079</t>
@@ -1232,55 +1232,55 @@
     <t xml:space="preserve">5.77227592468262</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73755550384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40771102905273</t>
+    <t xml:space="preserve">5.73755598068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40771198272705</t>
   </si>
   <si>
     <t xml:space="preserve">5.24278926849365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06918716430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98238611221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07618808746338</t>
+    <t xml:space="preserve">5.0691876411438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98238515853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07618761062622</t>
   </si>
   <si>
     <t xml:space="preserve">5.15619802474976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08507776260376</t>
+    <t xml:space="preserve">5.0850772857666</t>
   </si>
   <si>
     <t xml:space="preserve">5.24509811401367</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11174821853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13841724395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20953798294067</t>
+    <t xml:space="preserve">5.11174774169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13841819763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20953845977783</t>
   </si>
   <si>
     <t xml:space="preserve">5.06729745864868</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05840826034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04062795639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04951810836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94283819198608</t>
+    <t xml:space="preserve">5.0584077835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04062843322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04951763153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94283771514893</t>
   </si>
   <si>
     <t xml:space="preserve">4.77392816543579</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">4.76503801345825</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92505836486816</t>
+    <t xml:space="preserve">4.92505741119385</t>
   </si>
   <si>
     <t xml:space="preserve">4.88949775695801</t>
@@ -1313,28 +1313,28 @@
     <t xml:space="preserve">4.93394804000854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89838838577271</t>
+    <t xml:space="preserve">4.89838790893555</t>
   </si>
   <si>
     <t xml:space="preserve">4.80948781967163</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78281784057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75614738464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98728799819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10285806655884</t>
+    <t xml:space="preserve">4.78281831741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75614786148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98728847503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10285711288452</t>
   </si>
   <si>
     <t xml:space="preserve">4.960618019104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20064735412598</t>
+    <t xml:space="preserve">5.20064830780029</t>
   </si>
   <si>
     <t xml:space="preserve">5.21842765808105</t>
@@ -1343,46 +1343,46 @@
     <t xml:space="preserve">5.27176761627197</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33399820327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23620843887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18286800384521</t>
+    <t xml:space="preserve">5.33399772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23620748519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18286752700806</t>
   </si>
   <si>
     <t xml:space="preserve">5.01395797729492</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99617719650269</t>
+    <t xml:space="preserve">4.99617767333984</t>
   </si>
   <si>
     <t xml:space="preserve">5.00506782531738</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37844800949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47623777389526</t>
+    <t xml:space="preserve">5.37844848632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47623729705811</t>
   </si>
   <si>
     <t xml:space="preserve">5.56513786315918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68070793151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65403842926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63625717163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55624675750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68959760665894</t>
+    <t xml:space="preserve">5.6807074546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65403747558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63625764846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55624771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68959808349609</t>
   </si>
   <si>
     <t xml:space="preserve">5.96518754959106</t>
@@ -1397,19 +1397,19 @@
     <t xml:space="preserve">5.84072732925415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76071786880493</t>
+    <t xml:space="preserve">5.76071739196777</t>
   </si>
   <si>
     <t xml:space="preserve">5.92073726654053</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83183717727661</t>
+    <t xml:space="preserve">5.83183765411377</t>
   </si>
   <si>
     <t xml:space="preserve">5.4495677947998</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5829176902771</t>
+    <t xml:space="preserve">5.58291721343994</t>
   </si>
   <si>
     <t xml:space="preserve">5.43178796768188</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">5.60958766937256</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86739730834961</t>
+    <t xml:space="preserve">5.86739778518677</t>
   </si>
   <si>
     <t xml:space="preserve">5.78738784790039</t>
@@ -1442,37 +1442,37 @@
     <t xml:space="preserve">5.64514780044556</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71626758575439</t>
+    <t xml:space="preserve">5.71626710891724</t>
   </si>
   <si>
     <t xml:space="preserve">5.73404741287231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81405782699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67181825637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51179790496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85850763320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66292762756348</t>
+    <t xml:space="preserve">5.81405735015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67181777954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5117974281311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85850811004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66292715072632</t>
   </si>
   <si>
     <t xml:space="preserve">5.53846836090088</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90295743942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79627799987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80516815185547</t>
+    <t xml:space="preserve">5.90295791625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79627752304077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80516767501831</t>
   </si>
   <si>
     <t xml:space="preserve">5.6184778213501</t>
@@ -1481,43 +1481,43 @@
     <t xml:space="preserve">5.46734809875488</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60069704055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45845699310303</t>
+    <t xml:space="preserve">5.60069799423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45845794677734</t>
   </si>
   <si>
     <t xml:space="preserve">5.50290775299072</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34288835525513</t>
+    <t xml:space="preserve">5.34288787841797</t>
   </si>
   <si>
     <t xml:space="preserve">5.62736749649048</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52957725524902</t>
+    <t xml:space="preserve">5.52957773208618</t>
   </si>
   <si>
     <t xml:space="preserve">5.42289733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72515773773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70737743377686</t>
+    <t xml:space="preserve">5.72515821456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70737791061401</t>
   </si>
   <si>
     <t xml:space="preserve">5.69848775863647</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00074768066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92962741851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94740724563599</t>
+    <t xml:space="preserve">6.0007472038269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92962789535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94740772247314</t>
   </si>
   <si>
     <t xml:space="preserve">5.93851757049561</t>
@@ -1526,19 +1526,19 @@
     <t xml:space="preserve">5.99185705184937</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24077796936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40968656539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48080682754517</t>
+    <t xml:space="preserve">6.24077749252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40968751907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48080730438232</t>
   </si>
   <si>
     <t xml:space="preserve">6.62304735183716</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84529638290405</t>
+    <t xml:space="preserve">6.84529685974121</t>
   </si>
   <si>
     <t xml:space="preserve">6.99642658233643</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">7.01420736312866</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90752744674683</t>
+    <t xml:space="preserve">6.90752696990967</t>
   </si>
   <si>
     <t xml:space="preserve">6.91641759872437</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97864770889282</t>
+    <t xml:space="preserve">6.97864723205566</t>
   </si>
   <si>
     <t xml:space="preserve">7.00531721115112</t>
@@ -1565,43 +1565,43 @@
     <t xml:space="preserve">7.24534702301025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27201700210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33424711227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47648763656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76985645294189</t>
+    <t xml:space="preserve">7.27201795578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33424663543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47648668289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76985788345337</t>
   </si>
   <si>
     <t xml:space="preserve">7.73429584503174</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72540664672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79652690887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80541610717773</t>
+    <t xml:space="preserve">7.72540712356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79652786254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80541706085205</t>
   </si>
   <si>
     <t xml:space="preserve">8.22324657440186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21435642242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15212821960449</t>
+    <t xml:space="preserve">8.21435546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15212726593018</t>
   </si>
   <si>
     <t xml:space="preserve">8.12545776367188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00099754333496</t>
+    <t xml:space="preserve">8.00099658966064</t>
   </si>
   <si>
     <t xml:space="preserve">8.17879676818848</t>
@@ -1613,7 +1613,7 @@
     <t xml:space="preserve">8.42771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48105716705322</t>
+    <t xml:space="preserve">8.48105621337891</t>
   </si>
   <si>
     <t xml:space="preserve">8.46327686309814</t>
@@ -1622,19 +1622,19 @@
     <t xml:space="preserve">8.5255069732666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50772666931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66774559020996</t>
+    <t xml:space="preserve">8.50772571563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66774654388428</t>
   </si>
   <si>
     <t xml:space="preserve">8.80109596252441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8899974822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19225692749023</t>
+    <t xml:space="preserve">8.88999557495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19225597381592</t>
   </si>
   <si>
     <t xml:space="preserve">9.37005519866943</t>
@@ -1649,16 +1649,16 @@
     <t xml:space="preserve">9.31671619415283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15669536590576</t>
+    <t xml:space="preserve">9.15669631958008</t>
   </si>
   <si>
     <t xml:space="preserve">9.35227680206299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40561580657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69009590148926</t>
+    <t xml:space="preserve">9.40561676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69009494781494</t>
   </si>
   <si>
     <t xml:space="preserve">9.86789608001709</t>
@@ -1670,91 +1670,91 @@
     <t xml:space="preserve">9.77899551391602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44117546081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21003532409668</t>
+    <t xml:space="preserve">9.44117641448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.210036277771</t>
   </si>
   <si>
     <t xml:space="preserve">9.58341598510742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51229476928711</t>
+    <t xml:space="preserve">9.51229572296143</t>
   </si>
   <si>
     <t xml:space="preserve">9.6723165512085</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85011672973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0990362167358</t>
+    <t xml:space="preserve">9.8501148223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0990352630615</t>
   </si>
   <si>
     <t xml:space="preserve">10.0279159545898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99235439300537</t>
+    <t xml:space="preserve">9.99235534667969</t>
   </si>
   <si>
     <t xml:space="preserve">10.0101356506348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76121616363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88567638397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2234964370728</t>
+    <t xml:space="preserve">9.76121520996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88567543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2234954833984</t>
   </si>
   <si>
     <t xml:space="preserve">10.4368553161621</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6679964065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4147548675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3614158630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3080768585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4325351715088</t>
+    <t xml:space="preserve">10.6679954528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.414755821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3614149093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3080749511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4325342178345</t>
   </si>
   <si>
     <t xml:space="preserve">11.6814546585083</t>
   </si>
   <si>
-    <t xml:space="preserve">11.894814491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.965934753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1437358856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6281156539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4001121520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6715440750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6534490585327</t>
+    <t xml:space="preserve">11.8948154449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9659357070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1437349319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6281147003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4001140594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6715431213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.653450012207</t>
   </si>
   <si>
     <t xml:space="preserve">11.689640045166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.123929977417</t>
+    <t xml:space="preserve">12.1239290237427</t>
   </si>
   <si>
     <t xml:space="preserve">11.7982130050659</t>
@@ -1775,19 +1775,19 @@
     <t xml:space="preserve">12.7391748428345</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7753639221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3953619003296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2867879867554</t>
+    <t xml:space="preserve">12.7753648757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3953609466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2867889404297</t>
   </si>
   <si>
     <t xml:space="preserve">12.6306018829346</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4496479034424</t>
+    <t xml:space="preserve">12.4496469497681</t>
   </si>
   <si>
     <t xml:space="preserve">12.2144069671631</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">11.8705930709839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9067850112915</t>
+    <t xml:space="preserve">11.9067859649658</t>
   </si>
   <si>
     <t xml:space="preserve">11.4724941253662</t>
@@ -1811,22 +1811,22 @@
     <t xml:space="preserve">11.5810670852661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.852499961853</t>
+    <t xml:space="preserve">11.8524990081787</t>
   </si>
   <si>
     <t xml:space="preserve">12.0877389907837</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8344030380249</t>
+    <t xml:space="preserve">11.8344020843506</t>
   </si>
   <si>
     <t xml:space="preserve">11.8886890411377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4363040924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3277320861816</t>
+    <t xml:space="preserve">11.4363050460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.327733039856</t>
   </si>
   <si>
     <t xml:space="preserve">11.2734460830688</t>
@@ -1841,19 +1841,19 @@
     <t xml:space="preserve">10.8391542434692</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6401052474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6762971878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5134372711182</t>
+    <t xml:space="preserve">10.6401042938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6762962341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5134363174438</t>
   </si>
   <si>
     <t xml:space="preserve">10.9115381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2915391921997</t>
+    <t xml:space="preserve">11.291540145874</t>
   </si>
   <si>
     <t xml:space="preserve">11.1467771530151</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">11.1286821365356</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6220092773438</t>
+    <t xml:space="preserve">10.6220102310181</t>
   </si>
   <si>
     <t xml:space="preserve">11.0020132064819</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6039152145386</t>
+    <t xml:space="preserve">10.6039161682129</t>
   </si>
   <si>
     <t xml:space="preserve">10.4953422546387</t>
@@ -1886,13 +1886,13 @@
     <t xml:space="preserve">10.3143873214722</t>
   </si>
   <si>
-    <t xml:space="preserve">9.898193359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9343843460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80771827697754</t>
+    <t xml:space="preserve">9.89819240570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93438339233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80771636962891</t>
   </si>
   <si>
     <t xml:space="preserve">9.6810474395752</t>
@@ -1901,22 +1901,22 @@
     <t xml:space="preserve">9.95247936248779</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2420063018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4772462844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3867702484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4410552978516</t>
+    <t xml:space="preserve">10.2420072555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4772472381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3867683410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4410572052002</t>
   </si>
   <si>
     <t xml:space="preserve">9.55438041687012</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1153383255005</t>
+    <t xml:space="preserve">10.1153392791748</t>
   </si>
   <si>
     <t xml:space="preserve">10.3505783081055</t>
@@ -1928,16 +1928,16 @@
     <t xml:space="preserve">10.7486791610718</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0201091766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8572511672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8753471374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5858182907104</t>
+    <t xml:space="preserve">11.0201101303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.857250213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8753461837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5858192443848</t>
   </si>
   <si>
     <t xml:space="preserve">10.8029642105103</t>
@@ -1946,25 +1946,25 @@
     <t xml:space="preserve">10.7124872207642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7848691940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2372550964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3096342086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4543991088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7258310317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9972620010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.160120010376</t>
+    <t xml:space="preserve">10.7848682403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2372541427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3096361160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.454400062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.725830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9972610473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1601209640503</t>
   </si>
   <si>
     <t xml:space="preserve">12.0515470504761</t>
@@ -1982,13 +1982,13 @@
     <t xml:space="preserve">10.9477281570435</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9658241271973</t>
+    <t xml:space="preserve">10.9658231735229</t>
   </si>
   <si>
     <t xml:space="preserve">10.1877202987671</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98867034912109</t>
+    <t xml:space="preserve">9.98867130279541</t>
   </si>
   <si>
     <t xml:space="preserve">10.0429573059082</t>
@@ -1997,13 +1997,13 @@
     <t xml:space="preserve">9.91628932952881</t>
   </si>
   <si>
-    <t xml:space="preserve">10.169623374939</t>
+    <t xml:space="preserve">10.1696243286133</t>
   </si>
   <si>
     <t xml:space="preserve">10.5315322875977</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4229602813721</t>
+    <t xml:space="preserve">10.4229612350464</t>
   </si>
   <si>
     <t xml:space="preserve">10.13343334198</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">10.097243309021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0610523223877</t>
+    <t xml:space="preserve">10.0610504150391</t>
   </si>
   <si>
     <t xml:space="preserve">10.0791482925415</t>
@@ -2030,13 +2030,13 @@
     <t xml:space="preserve">11.056300163269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8934412002563</t>
+    <t xml:space="preserve">10.893440246582</t>
   </si>
   <si>
     <t xml:space="preserve">10.5496282577515</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3686742782593</t>
+    <t xml:space="preserve">10.368673324585</t>
   </si>
   <si>
     <t xml:space="preserve">9.8258113861084</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">9.699143409729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51819038391113</t>
+    <t xml:space="preserve">9.51818943023682</t>
   </si>
   <si>
     <t xml:space="preserve">9.71723937988281</t>
@@ -2057,7 +2057,7 @@
     <t xml:space="preserve">9.42771244049072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5905704498291</t>
+    <t xml:space="preserve">9.59057235717773</t>
   </si>
   <si>
     <t xml:space="preserve">11.3639221191406</t>
@@ -2069,13 +2069,13 @@
     <t xml:space="preserve">12.4677419662476</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3772668838501</t>
+    <t xml:space="preserve">12.3772659301758</t>
   </si>
   <si>
     <t xml:space="preserve">11.3820171356201</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5629720687866</t>
+    <t xml:space="preserve">11.5629711151123</t>
   </si>
   <si>
     <t xml:space="preserve">11.6172580718994</t>
@@ -2084,43 +2084,43 @@
     <t xml:space="preserve">11.0924911499023</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6943922042847</t>
+    <t xml:space="preserve">10.6943912506104</t>
   </si>
   <si>
     <t xml:space="preserve">9.62676239013672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80341911315918</t>
+    <t xml:space="preserve">8.8034200668335</t>
   </si>
   <si>
     <t xml:space="preserve">8.68580055236816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43246364593506</t>
+    <t xml:space="preserve">8.43246459960938</t>
   </si>
   <si>
     <t xml:space="preserve">7.04816579818726</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32864475250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24721527099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1838812828064</t>
+    <t xml:space="preserve">7.32864427566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24721431732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18388080596924</t>
   </si>
   <si>
     <t xml:space="preserve">6.58673191070557</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65006589889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96673488616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97578287124634</t>
+    <t xml:space="preserve">6.65006542205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96673536300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97578382492065</t>
   </si>
   <si>
     <t xml:space="preserve">7.16578531265259</t>
@@ -2129,16 +2129,16 @@
     <t xml:space="preserve">7.057213306427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28340578079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60912370681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76293468475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3419885635376</t>
+    <t xml:space="preserve">7.28340625762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60912322998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76293420791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34198760986328</t>
   </si>
   <si>
     <t xml:space="preserve">8.04341316223145</t>
@@ -2147,49 +2147,49 @@
     <t xml:space="preserve">8.61341953277588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41436958312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25151062011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93008804321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35533142089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04770946502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26485347747803</t>
+    <t xml:space="preserve">8.4143705368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2515115737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93008995056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35533046722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04770755767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26485443115234</t>
   </si>
   <si>
     <t xml:space="preserve">9.50009441375732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8620023727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2191591262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9839191436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6582021713257</t>
+    <t xml:space="preserve">9.86200332641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2191581726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9839181900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6582002639771</t>
   </si>
   <si>
     <t xml:space="preserve">9.97057628631592</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2058153152466</t>
+    <t xml:space="preserve">10.2058143615723</t>
   </si>
   <si>
     <t xml:space="preserve">9.84390735626221</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4591503143311</t>
+    <t xml:space="preserve">10.4591522216797</t>
   </si>
   <si>
     <t xml:space="preserve">10.9296321868896</t>
@@ -2201,16 +2201,16 @@
     <t xml:space="preserve">10.8210601806641</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0696430206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.558219909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8477468490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1915578842163</t>
+    <t xml:space="preserve">12.0696439743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5582189559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8477458953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1915588378906</t>
   </si>
   <si>
     <t xml:space="preserve">12.757269859314</t>
@@ -2228,7 +2228,7 @@
     <t xml:space="preserve">12.6486968994141</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7210788726807</t>
+    <t xml:space="preserve">12.7210779190063</t>
   </si>
   <si>
     <t xml:space="preserve">12.8658418655396</t>
@@ -2237,16 +2237,16 @@
     <t xml:space="preserve">13.1553688049316</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0287008285522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1191778182983</t>
+    <t xml:space="preserve">13.0286998748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1191787719727</t>
   </si>
   <si>
     <t xml:space="preserve">12.9382238388062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0829858779907</t>
+    <t xml:space="preserve">13.082986831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.3725137710571</t>
@@ -2258,19 +2258,19 @@
     <t xml:space="preserve">15.4534864425659</t>
   </si>
   <si>
-    <t xml:space="preserve">16.249683380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2858772277832</t>
+    <t xml:space="preserve">16.2496852874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2858753204346</t>
   </si>
   <si>
     <t xml:space="preserve">16.3763542175293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6477851867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8334894180298</t>
+    <t xml:space="preserve">16.6477813720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8334903717041</t>
   </si>
   <si>
     <t xml:space="preserve">16.0687313079834</t>
@@ -2282,22 +2282,22 @@
     <t xml:space="preserve">15.9239673614502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9058704376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8515863418579</t>
+    <t xml:space="preserve">15.9058723449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8515882492065</t>
   </si>
   <si>
     <t xml:space="preserve">16.0144443511963</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7972984313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2677822113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0325393676758</t>
+    <t xml:space="preserve">15.7972974777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2677803039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0325374603271</t>
   </si>
   <si>
     <t xml:space="preserve">15.779203414917</t>
@@ -2309,10 +2309,10 @@
     <t xml:space="preserve">16.4125442504883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8153944015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9420614242554</t>
+    <t xml:space="preserve">15.8153953552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.942063331604</t>
   </si>
   <si>
     <t xml:space="preserve">15.6344413757324</t>
@@ -2321,13 +2321,13 @@
     <t xml:space="preserve">16.1049213409424</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9601564407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6887273788452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6163454055786</t>
+    <t xml:space="preserve">15.9601583480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6887264251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6163463592529</t>
   </si>
   <si>
     <t xml:space="preserve">14.8925275802612</t>
@@ -2339,19 +2339,19 @@
     <t xml:space="preserve">15.3630084991455</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4896793365479</t>
+    <t xml:space="preserve">15.4896774291992</t>
   </si>
   <si>
     <t xml:space="preserve">15.1458654403687</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0372943878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7430114746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8201465606689</t>
+    <t xml:space="preserve">15.0372924804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.743013381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8201456069946</t>
   </si>
   <si>
     <t xml:space="preserve">15.2906265258789</t>
@@ -2363,16 +2363,16 @@
     <t xml:space="preserve">17.7696990966797</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0230350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1359043121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2763729095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0411319732666</t>
+    <t xml:space="preserve">18.0230369567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1359062194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2763748168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.041130065918</t>
   </si>
   <si>
     <t xml:space="preserve">17.4258880615234</t>
@@ -2381,31 +2381,31 @@
     <t xml:space="preserve">17.7335109710693</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2992172241211</t>
+    <t xml:space="preserve">17.2992191314697</t>
   </si>
   <si>
     <t xml:space="preserve">17.0458831787109</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0277881622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7020702362061</t>
+    <t xml:space="preserve">17.0277862548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7020721435547</t>
   </si>
   <si>
     <t xml:space="preserve">17.009693145752</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4077892303467</t>
+    <t xml:space="preserve">17.4077911376953</t>
   </si>
   <si>
     <t xml:space="preserve">18.5025653839111</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1406555175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9687519073486</t>
+    <t xml:space="preserve">18.1406536102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.96875</t>
   </si>
   <si>
     <t xml:space="preserve">17.4982681274414</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">18.5930404663086</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1544551849365</t>
+    <t xml:space="preserve">17.1544570922852</t>
   </si>
   <si>
     <t xml:space="preserve">17.2449321746826</t>
@@ -2429,13 +2429,13 @@
     <t xml:space="preserve">16.8106441497803</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8287391662598</t>
+    <t xml:space="preserve">16.8287410736084</t>
   </si>
   <si>
     <t xml:space="preserve">16.9735012054443</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9192161560059</t>
+    <t xml:space="preserve">16.9192180633545</t>
   </si>
   <si>
     <t xml:space="preserve">17.0639781951904</t>
@@ -2444,22 +2444,22 @@
     <t xml:space="preserve">16.8468341827393</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9011211395264</t>
+    <t xml:space="preserve">16.9011192321777</t>
   </si>
   <si>
     <t xml:space="preserve">17.3173141479492</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2087440490723</t>
+    <t xml:space="preserve">17.2087459564209</t>
   </si>
   <si>
     <t xml:space="preserve">17.2268390655518</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3668479919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4573249816895</t>
+    <t xml:space="preserve">18.366849899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4573230743408</t>
   </si>
   <si>
     <t xml:space="preserve">18.6382789611816</t>
@@ -2471,19 +2471,19 @@
     <t xml:space="preserve">18.9549503326416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8644752502441</t>
+    <t xml:space="preserve">18.8644714355469</t>
   </si>
   <si>
     <t xml:space="preserve">19.6335315704346</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6787662506104</t>
+    <t xml:space="preserve">19.678768157959</t>
   </si>
   <si>
     <t xml:space="preserve">19.5430507659912</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0454273223877</t>
+    <t xml:space="preserve">19.0454254150391</t>
   </si>
   <si>
     <t xml:space="preserve">19.0001888275146</t>
@@ -2492,31 +2492,31 @@
     <t xml:space="preserve">19.316858291626</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3216094970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2311305999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0906677246094</t>
+    <t xml:space="preserve">18.3216114044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2311344146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0906658172607</t>
   </si>
   <si>
     <t xml:space="preserve">18.6835193634033</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0954189300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.004940032959</t>
+    <t xml:space="preserve">18.0954151153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0049381256104</t>
   </si>
   <si>
     <t xml:space="preserve">17.5706520080566</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8239841461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.643030166626</t>
+    <t xml:space="preserve">17.8239879608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6430320739746</t>
   </si>
   <si>
     <t xml:space="preserve">17.8058910369873</t>
@@ -2525,7 +2525,7 @@
     <t xml:space="preserve">19.2716197967529</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1811408996582</t>
+    <t xml:space="preserve">19.1811447143555</t>
   </si>
   <si>
     <t xml:space="preserve">20.26686668396</t>
@@ -2537,10 +2537,10 @@
     <t xml:space="preserve">20.9906845092773</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5835380554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3573474884033</t>
+    <t xml:space="preserve">20.5835399627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3573455810547</t>
   </si>
   <si>
     <t xml:space="preserve">19.9049587249756</t>
@@ -2552,16 +2552,16 @@
     <t xml:space="preserve">20.7192516326904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9954376220703</t>
+    <t xml:space="preserve">19.9954357147217</t>
   </si>
   <si>
     <t xml:space="preserve">19.2263832092285</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4525737762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4073371887207</t>
+    <t xml:space="preserve">19.4525718688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4073352813721</t>
   </si>
   <si>
     <t xml:space="preserve">17.6249370574951</t>
@@ -2576,16 +2576,16 @@
     <t xml:space="preserve">20.0859146118164</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1311492919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8597202301025</t>
+    <t xml:space="preserve">20.1311511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8597221374512</t>
   </si>
   <si>
     <t xml:space="preserve">20.674015045166</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0359230041504</t>
+    <t xml:space="preserve">21.035924911499</t>
   </si>
   <si>
     <t xml:space="preserve">20.8097305297852</t>
@@ -2600,13 +2600,13 @@
     <t xml:space="preserve">20.4478225708008</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8821105957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2802104949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3344993591309</t>
+    <t xml:space="preserve">20.8821144104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2802085876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3344974517822</t>
   </si>
   <si>
     <t xml:space="preserve">21.587833404541</t>
@@ -2618,10 +2618,10 @@
     <t xml:space="preserve">22.1668872833252</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6192684173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8726081848145</t>
+    <t xml:space="preserve">22.6192722320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8726100921631</t>
   </si>
   <si>
     <t xml:space="preserve">23.9040470123291</t>
@@ -2639,7 +2639,7 @@
     <t xml:space="preserve">22.2573642730713</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4745101928711</t>
+    <t xml:space="preserve">22.4745082855225</t>
   </si>
   <si>
     <t xml:space="preserve">22.1126003265381</t>
@@ -2651,31 +2651,31 @@
     <t xml:space="preserve">22.6011753082275</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6373672485352</t>
+    <t xml:space="preserve">22.6373653411865</t>
   </si>
   <si>
     <t xml:space="preserve">22.4202213287354</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4021263122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3525943756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.262113571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0945053100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5830783843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0354671478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0173740386963</t>
+    <t xml:space="preserve">22.4021282196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3525924682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2621154785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.09450340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.583080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0354652404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0173721313477</t>
   </si>
   <si>
     <t xml:space="preserve">23.3611831665039</t>
@@ -2687,34 +2687,34 @@
     <t xml:space="preserve">25.0440578460693</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7726268768311</t>
+    <t xml:space="preserve">24.7726249694824</t>
   </si>
   <si>
     <t xml:space="preserve">24.9716777801514</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0621547698975</t>
+    <t xml:space="preserve">25.0621528625488</t>
   </si>
   <si>
     <t xml:space="preserve">25.9126377105713</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2383556365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6765747070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7130928039551</t>
+    <t xml:space="preserve">26.2383575439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.676570892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7130908966064</t>
   </si>
   <si>
     <t xml:space="preserve">26.585277557373</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6583156585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8226451873779</t>
+    <t xml:space="preserve">26.6583137512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8226470947266</t>
   </si>
   <si>
     <t xml:space="preserve">26.95046043396</t>
@@ -2723,19 +2723,19 @@
     <t xml:space="preserve">27.5712699890137</t>
   </si>
   <si>
-    <t xml:space="preserve">27.626049041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.064266204834</t>
+    <t xml:space="preserve">27.6260471343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0642681121826</t>
   </si>
   <si>
     <t xml:space="preserve">28.283374786377</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8171405792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.598030090332</t>
+    <t xml:space="preserve">29.8171443939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5980319976807</t>
   </si>
   <si>
     <t xml:space="preserve">28.958963394165</t>
@@ -2744,13 +2744,13 @@
     <t xml:space="preserve">30.1275482177734</t>
   </si>
   <si>
-    <t xml:space="preserve">29.652811050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1092891693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9632148742676</t>
+    <t xml:space="preserve">29.6528091430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1092872619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9632129669189</t>
   </si>
   <si>
     <t xml:space="preserve">30.4014320373535</t>
@@ -2759,13 +2759,13 @@
     <t xml:space="preserve">30.2188396453857</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2961292266846</t>
+    <t xml:space="preserve">31.2961330413818</t>
   </si>
   <si>
     <t xml:space="preserve">30.8213920593262</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1683177947998</t>
+    <t xml:space="preserve">31.1683139801025</t>
   </si>
   <si>
     <t xml:space="preserve">30.2371006011963</t>
@@ -2777,7 +2777,7 @@
     <t xml:space="preserve">29.8536605834961</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1780738830566</t>
+    <t xml:space="preserve">29.178071975708</t>
   </si>
   <si>
     <t xml:space="preserve">30.1458072662354</t>
@@ -2789,28 +2789,28 @@
     <t xml:space="preserve">30.0545082092285</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8664169311523</t>
+    <t xml:space="preserve">32.8664131164551</t>
   </si>
   <si>
     <t xml:space="preserve">34.5462532043457</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0532569885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0855293273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7245903015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6880760192871</t>
+    <t xml:space="preserve">34.0532608032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.085521697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7245941162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6880722045898</t>
   </si>
   <si>
     <t xml:space="preserve">33.5785179138184</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4872283935547</t>
+    <t xml:space="preserve">33.4872245788574</t>
   </si>
   <si>
     <t xml:space="preserve">33.7976303100586</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">33.1403007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2863731384277</t>
+    <t xml:space="preserve">33.286376953125</t>
   </si>
   <si>
     <t xml:space="preserve">32.2273445129395</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">32.8846740722656</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7568664550781</t>
+    <t xml:space="preserve">32.7568626403809</t>
   </si>
   <si>
     <t xml:space="preserve">32.6473045349121</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">33.0307464599609</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7751235961914</t>
+    <t xml:space="preserve">32.7751197814941</t>
   </si>
   <si>
     <t xml:space="preserve">32.4099388122559</t>
@@ -2846,10 +2846,10 @@
     <t xml:space="preserve">32.6655616760254</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6923294067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6052780151367</t>
+    <t xml:space="preserve">34.692325592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.605281829834</t>
   </si>
   <si>
     <t xml:space="preserve">35.2400970458984</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">35.4774703979492</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0940284729004</t>
+    <t xml:space="preserve">35.0940246582031</t>
   </si>
   <si>
     <t xml:space="preserve">35.5870246887207</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">35.7878761291504</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0434989929199</t>
+    <t xml:space="preserve">36.0435066223145</t>
   </si>
   <si>
     <t xml:space="preserve">36.8469009399414</t>
@@ -2879,19 +2879,19 @@
     <t xml:space="preserve">38.9101829528809</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4354476928711</t>
+    <t xml:space="preserve">38.4354438781738</t>
   </si>
   <si>
     <t xml:space="preserve">39.4944725036621</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3849182128906</t>
+    <t xml:space="preserve">39.3849220275879</t>
   </si>
   <si>
     <t xml:space="preserve">39.220588684082</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1292915344238</t>
+    <t xml:space="preserve">39.1292953491211</t>
   </si>
   <si>
     <t xml:space="preserve">38.1980781555176</t>
@@ -2900,40 +2900,40 @@
     <t xml:space="preserve">37.6137847900391</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2486038208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0660095214844</t>
+    <t xml:space="preserve">37.2486000061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0660133361816</t>
   </si>
   <si>
     <t xml:space="preserve">37.2668609619141</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7008285522461</t>
+    <t xml:space="preserve">36.7008323669434</t>
   </si>
   <si>
     <t xml:space="preserve">37.2120819091797</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5590057373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0154838562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6503105163574</t>
+    <t xml:space="preserve">37.559009552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0154876708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6503067016602</t>
   </si>
   <si>
     <t xml:space="preserve">35.6235427856445</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2316017150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9942245483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3594093322754</t>
+    <t xml:space="preserve">33.2315979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9942283630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3594131469727</t>
   </si>
   <si>
     <t xml:space="preserve">33.0490074157715</t>
@@ -2942,19 +2942,19 @@
     <t xml:space="preserve">34.7836227416992</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3819236755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.893180847168</t>
+    <t xml:space="preserve">34.3819198608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8931770324707</t>
   </si>
   <si>
     <t xml:space="preserve">32.9577102661133</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6332969665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5139923095703</t>
+    <t xml:space="preserve">33.63330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.513988494873</t>
   </si>
   <si>
     <t xml:space="preserve">36.4817199707031</t>
@@ -2963,19 +2963,19 @@
     <t xml:space="preserve">36.3173866271973</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6095352172852</t>
+    <t xml:space="preserve">36.6095314025879</t>
   </si>
   <si>
     <t xml:space="preserve">37.7781181335449</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2711143493652</t>
+    <t xml:space="preserve">38.271110534668</t>
   </si>
   <si>
     <t xml:space="preserve">39.2023315429688</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7190895080566</t>
+    <t xml:space="preserve">36.7190933227539</t>
   </si>
   <si>
     <t xml:space="preserve">35.8426513671875</t>
@@ -2984,7 +2984,7 @@
     <t xml:space="preserve">34.9662132263184</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1488075256348</t>
+    <t xml:space="preserve">35.1488037109375</t>
   </si>
   <si>
     <t xml:space="preserve">35.4409523010254</t>
@@ -2993,34 +2993,34 @@
     <t xml:space="preserve">37.8876724243164</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5267448425293</t>
+    <t xml:space="preserve">38.526741027832</t>
   </si>
   <si>
     <t xml:space="preserve">38.8006324768066</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6685600280762</t>
+    <t xml:space="preserve">37.6685638427734</t>
   </si>
   <si>
     <t xml:space="preserve">35.4226913452148</t>
   </si>
   <si>
-    <t xml:space="preserve">35.258358001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.911434173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3636627197266</t>
+    <t xml:space="preserve">35.2583618164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9114379882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3636589050293</t>
   </si>
   <si>
     <t xml:space="preserve">33.8341484069824</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5967826843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3313941955566</t>
+    <t xml:space="preserve">33.5967750549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3313980102539</t>
   </si>
   <si>
     <t xml:space="preserve">34.2175941467285</t>
@@ -3044,7 +3044,7 @@
     <t xml:space="preserve">33.1950798034668</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6150360107422</t>
+    <t xml:space="preserve">33.6150398254395</t>
   </si>
   <si>
     <t xml:space="preserve">33.9254455566406</t>
@@ -3053,28 +3053,28 @@
     <t xml:space="preserve">33.9437026977539</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6192893981934</t>
+    <t xml:space="preserve">34.6192932128906</t>
   </si>
   <si>
     <t xml:space="preserve">34.5827713012695</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7288475036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0027351379395</t>
+    <t xml:space="preserve">34.7288513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0027313232422</t>
   </si>
   <si>
     <t xml:space="preserve">34.8384017944336</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8749160766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5377464294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1725654602051</t>
+    <t xml:space="preserve">34.8749198913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5377502441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1725692749023</t>
   </si>
   <si>
     <t xml:space="preserve">32.1360511779785</t>
@@ -3083,43 +3083,43 @@
     <t xml:space="preserve">29.4519577026367</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8901786804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1640682220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4294490814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1007843017578</t>
+    <t xml:space="preserve">29.8901805877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1640663146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4294471740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1007881164551</t>
   </si>
   <si>
     <t xml:space="preserve">27.6808242797852</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9954833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2693691253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6850776672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9687213897705</t>
+    <t xml:space="preserve">28.9954814910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2693710327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6850757598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9687194824219</t>
   </si>
   <si>
     <t xml:space="preserve">26.8956832885742</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8451557159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9729690551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6668186187744</t>
+    <t xml:space="preserve">27.845157623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9729709625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6668167114258</t>
   </si>
   <si>
     <t xml:space="preserve">29.1232948303223</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">27.6077880859375</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7538604736328</t>
+    <t xml:space="preserve">27.7538623809814</t>
   </si>
   <si>
     <t xml:space="preserve">26.3479099273682</t>
@@ -3146,16 +3146,16 @@
     <t xml:space="preserve">26.7861289978027</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5670185089111</t>
+    <t xml:space="preserve">26.5670204162598</t>
   </si>
   <si>
     <t xml:space="preserve">27.9547119140625</t>
   </si>
   <si>
-    <t xml:space="preserve">27.425199508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4799747467041</t>
+    <t xml:space="preserve">27.4251976013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4799766540527</t>
   </si>
   <si>
     <t xml:space="preserve">27.1147937774658</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">27.9912300109863</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6948337554932</t>
+    <t xml:space="preserve">26.6948318481445</t>
   </si>
   <si>
     <t xml:space="preserve">27.4434566497803</t>
@@ -3179,16 +3179,16 @@
     <t xml:space="preserve">26.3113918304443</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5542640686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7045879364014</t>
+    <t xml:space="preserve">23.5542621612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.70458984375</t>
   </si>
   <si>
     <t xml:space="preserve">23.0977840423584</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0022392272949</t>
+    <t xml:space="preserve">22.0022411346436</t>
   </si>
   <si>
     <t xml:space="preserve">21.7466125488281</t>
@@ -3197,22 +3197,22 @@
     <t xml:space="preserve">20.742359161377</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6047897338867</t>
+    <t xml:space="preserve">22.6047916412354</t>
   </si>
   <si>
     <t xml:space="preserve">21.8744239807129</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5134944915771</t>
+    <t xml:space="preserve">22.5134925842285</t>
   </si>
   <si>
     <t xml:space="preserve">23.1525630950928</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2073402404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5402545928955</t>
+    <t xml:space="preserve">23.2073421478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5402565002441</t>
   </si>
   <si>
     <t xml:space="preserve">24.6680698394775</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">24.8689193725586</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4489612579346</t>
+    <t xml:space="preserve">24.4489631652832</t>
   </si>
   <si>
     <t xml:space="preserve">25.2341022491455</t>
@@ -3230,7 +3230,7 @@
     <t xml:space="preserve">24.5585155487061</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0290012359619</t>
+    <t xml:space="preserve">24.0290031433105</t>
   </si>
   <si>
     <t xml:space="preserve">24.1385555267334</t>
@@ -3239,13 +3239,13 @@
     <t xml:space="preserve">24.0472602844238</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3984355926514</t>
+    <t xml:space="preserve">25.3984375</t>
   </si>
   <si>
     <t xml:space="preserve">25.4166946411133</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2115936279297</t>
+    <t xml:space="preserve">24.2115917205811</t>
   </si>
   <si>
     <t xml:space="preserve">24.0837783813477</t>
@@ -3254,22 +3254,22 @@
     <t xml:space="preserve">23.8098926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3351554870605</t>
+    <t xml:space="preserve">23.3351535797119</t>
   </si>
   <si>
     <t xml:space="preserve">22.4221973419189</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7326030731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.677827835083</t>
+    <t xml:space="preserve">22.7326049804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6778259277344</t>
   </si>
   <si>
     <t xml:space="preserve">22.2761249542236</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9109439849854</t>
+    <t xml:space="preserve">21.9109420776367</t>
   </si>
   <si>
     <t xml:space="preserve">22.2213478088379</t>
@@ -3281,13 +3281,13 @@
     <t xml:space="preserve">22.0935363769531</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8238964080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5457630157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0710220336914</t>
+    <t xml:space="preserve">22.8239002227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5457611083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0710258483887</t>
   </si>
   <si>
     <t xml:space="preserve">21.9657192230225</t>
@@ -3302,7 +3302,7 @@
     <t xml:space="preserve">20.8884315490723</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6875820159912</t>
+    <t xml:space="preserve">20.6875839233398</t>
   </si>
   <si>
     <t xml:space="preserve">20.0850315093994</t>
@@ -3317,19 +3317,19 @@
     <t xml:space="preserve">19.957218170166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9024391174316</t>
+    <t xml:space="preserve">19.9024410247803</t>
   </si>
   <si>
     <t xml:space="preserve">20.2493629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9614696502686</t>
+    <t xml:space="preserve">20.9614658355713</t>
   </si>
   <si>
     <t xml:space="preserve">20.8519153594971</t>
   </si>
   <si>
-    <t xml:space="preserve">20.724100112915</t>
+    <t xml:space="preserve">20.7241020202637</t>
   </si>
   <si>
     <t xml:space="preserve">21.0162467956543</t>
@@ -3341,22 +3341,22 @@
     <t xml:space="preserve">20.3954372406006</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5232486724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6693229675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.130054473877</t>
+    <t xml:space="preserve">20.523250579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6693248748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1300525665283</t>
   </si>
   <si>
     <t xml:space="preserve">24.1933345794678</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6455612182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5177459716797</t>
+    <t xml:space="preserve">23.6455593109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5177478790283</t>
   </si>
   <si>
     <t xml:space="preserve">23.7368564605713</t>
@@ -3383,7 +3383,7 @@
     <t xml:space="preserve">19.2850399017334</t>
   </si>
   <si>
-    <t xml:space="preserve">20.319486618042</t>
+    <t xml:space="preserve">20.3194885253906</t>
   </si>
   <si>
     <t xml:space="preserve">20.4303207397461</t>
@@ -3392,7 +3392,7 @@
     <t xml:space="preserve">21.2246265411377</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3539333343506</t>
+    <t xml:space="preserve">21.3539352416992</t>
   </si>
   <si>
     <t xml:space="preserve">21.3169898986816</t>
@@ -3401,19 +3401,19 @@
     <t xml:space="preserve">21.7603225708008</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6494903564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4278240203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5571269989014</t>
+    <t xml:space="preserve">21.6494922637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4278221130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.55712890625</t>
   </si>
   <si>
     <t xml:space="preserve">21.7972679138184</t>
   </si>
   <si>
-    <t xml:space="preserve">20.559627532959</t>
+    <t xml:space="preserve">20.5596256256104</t>
   </si>
   <si>
     <t xml:space="preserve">20.7812938690186</t>
@@ -3428,37 +3428,37 @@
     <t xml:space="preserve">20.9475440979004</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0374088287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4992122650146</t>
+    <t xml:space="preserve">22.0374069213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4992141723633</t>
   </si>
   <si>
     <t xml:space="preserve">21.6679611206055</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4647655487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8182373046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1532363891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2271251678467</t>
+    <t xml:space="preserve">21.4647674560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8182392120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1532344818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2271270751953</t>
   </si>
   <si>
     <t xml:space="preserve">20.4487915039062</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3908786773682</t>
+    <t xml:space="preserve">21.3908767700195</t>
   </si>
   <si>
     <t xml:space="preserve">21.0029602050781</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0768508911133</t>
+    <t xml:space="preserve">21.0768489837646</t>
   </si>
   <si>
     <t xml:space="preserve">21.8157405853271</t>
@@ -3473,10 +3473,10 @@
     <t xml:space="preserve">22.5361576080322</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7578258514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2985172271729</t>
+    <t xml:space="preserve">22.7578239440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2985153198242</t>
   </si>
   <si>
     <t xml:space="preserve">21.5017127990723</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">19.9500427246094</t>
   </si>
   <si>
-    <t xml:space="preserve">19.74684715271</t>
+    <t xml:space="preserve">19.7468452453613</t>
   </si>
   <si>
     <t xml:space="preserve">19.5436534881592</t>
@@ -3536,16 +3536,16 @@
     <t xml:space="preserve">18.2413578033447</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0566349029541</t>
+    <t xml:space="preserve">18.0566329956055</t>
   </si>
   <si>
     <t xml:space="preserve">17.7426052093506</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4562854766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6225357055664</t>
+    <t xml:space="preserve">17.4562835693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.622537612915</t>
   </si>
   <si>
     <t xml:space="preserve">16.6989231109619</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">16.8374652862549</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9852447509766</t>
+    <t xml:space="preserve">16.9852428436279</t>
   </si>
   <si>
     <t xml:space="preserve">17.280797958374</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">17.5855941772461</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5024700164795</t>
+    <t xml:space="preserve">17.5024681091309</t>
   </si>
   <si>
     <t xml:space="preserve">17.0683689117432</t>
@@ -3587,7 +3587,7 @@
     <t xml:space="preserve">17.234619140625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2530937194824</t>
+    <t xml:space="preserve">17.2530918121338</t>
   </si>
   <si>
     <t xml:space="preserve">16.9390640258789</t>
@@ -3599,7 +3599,7 @@
     <t xml:space="preserve">16.8836479187012</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4285793304443</t>
+    <t xml:space="preserve">17.4285774230957</t>
   </si>
   <si>
     <t xml:space="preserve">17.7056617736816</t>
@@ -3614,16 +3614,16 @@
     <t xml:space="preserve">18.3429546356201</t>
   </si>
   <si>
-    <t xml:space="preserve">19.469762802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5805969238281</t>
+    <t xml:space="preserve">19.4697608947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5805988311768</t>
   </si>
   <si>
     <t xml:space="preserve">19.3589286804199</t>
   </si>
   <si>
-    <t xml:space="preserve">19.044900894165</t>
+    <t xml:space="preserve">19.0449028015137</t>
   </si>
   <si>
     <t xml:space="preserve">18.7493438720703</t>
@@ -3635,13 +3635,13 @@
     <t xml:space="preserve">18.2967739105225</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4907341003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0079574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0239295959473</t>
+    <t xml:space="preserve">18.4907321929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0079555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0239315032959</t>
   </si>
   <si>
     <t xml:space="preserve">19.8392066955566</t>
@@ -3656,25 +3656,25 @@
     <t xml:space="preserve">22.3329639434814</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9105987548828</t>
+    <t xml:space="preserve">20.9106006622314</t>
   </si>
   <si>
     <t xml:space="preserve">20.5226802825928</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3354625701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2431011199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9265747070312</t>
+    <t xml:space="preserve">21.3354606628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2430992126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9265727996826</t>
   </si>
   <si>
     <t xml:space="preserve">21.7418518066406</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2800445556641</t>
+    <t xml:space="preserve">21.2800464630127</t>
   </si>
   <si>
     <t xml:space="preserve">21.409351348877</t>
@@ -3686,22 +3686,22 @@
     <t xml:space="preserve">21.1507377624512</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0583763122559</t>
+    <t xml:space="preserve">21.0583782196045</t>
   </si>
   <si>
     <t xml:space="preserve">20.3933753967285</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2455997467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.931568145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9685153961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2825412750244</t>
+    <t xml:space="preserve">20.2455978393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9315700531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9685134887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.282543182373</t>
   </si>
   <si>
     <t xml:space="preserve">20.9290714263916</t>
@@ -3719,22 +3719,22 @@
     <t xml:space="preserve">23.6075477600098</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3304653167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0349082946777</t>
+    <t xml:space="preserve">23.3304672241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0349102020264</t>
   </si>
   <si>
     <t xml:space="preserve">23.4412975311279</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9031047821045</t>
+    <t xml:space="preserve">23.9031028747559</t>
   </si>
   <si>
     <t xml:space="preserve">23.792272567749</t>
   </si>
   <si>
-    <t xml:space="preserve">23.127269744873</t>
+    <t xml:space="preserve">23.1272716522217</t>
   </si>
   <si>
     <t xml:space="preserve">23.7553253173828</t>
@@ -3773,7 +3773,7 @@
     <t xml:space="preserve">22.8686580657959</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4597721099854</t>
+    <t xml:space="preserve">23.4597702026367</t>
   </si>
   <si>
     <t xml:space="preserve">22.9056015014648</t>
@@ -3782,22 +3782,22 @@
     <t xml:space="preserve">22.8132419586182</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6285209655762</t>
+    <t xml:space="preserve">22.6285190582275</t>
   </si>
   <si>
     <t xml:space="preserve">22.4622688293457</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2221298217773</t>
+    <t xml:space="preserve">22.2221279144287</t>
   </si>
   <si>
     <t xml:space="preserve">22.2036571502686</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0004615783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0558776855469</t>
+    <t xml:space="preserve">22.0004634857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0558795928955</t>
   </si>
   <si>
     <t xml:space="preserve">22.2590751647949</t>
@@ -3806,13 +3806,13 @@
     <t xml:space="preserve">21.8342113494873</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0928230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2406005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2615718841553</t>
+    <t xml:space="preserve">22.0928249359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2406024932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2615737915039</t>
   </si>
   <si>
     <t xml:space="preserve">19.3404579162598</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">18.6569843292236</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1187915802002</t>
+    <t xml:space="preserve">19.1187896728516</t>
   </si>
   <si>
     <t xml:space="preserve">18.5646228790283</t>
@@ -3830,10 +3830,10 @@
     <t xml:space="preserve">18.6754550933838</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0264301300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2690658569336</t>
+    <t xml:space="preserve">19.0264282226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2690677642822</t>
   </si>
   <si>
     <t xml:space="preserve">18.509204864502</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">18.8232326507568</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5461502075195</t>
+    <t xml:space="preserve">18.5461521148682</t>
   </si>
   <si>
     <t xml:space="preserve">18.7124004364014</t>
@@ -3857,37 +3857,37 @@
     <t xml:space="preserve">18.4445514678955</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3614253997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7980213165283</t>
+    <t xml:space="preserve">18.3614273071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.798023223877</t>
   </si>
   <si>
     <t xml:space="preserve">17.5486469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1422576904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.948299407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9205894470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8651752471924</t>
+    <t xml:space="preserve">17.1422557830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9483013153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9205913543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8651733398438</t>
   </si>
   <si>
     <t xml:space="preserve">16.5696182250977</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8559379577637</t>
+    <t xml:space="preserve">16.8559398651123</t>
   </si>
   <si>
     <t xml:space="preserve">17.1145496368408</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7451019287109</t>
+    <t xml:space="preserve">16.7451038360596</t>
   </si>
   <si>
     <t xml:space="preserve">16.9021186828613</t>
@@ -3911,7 +3911,7 @@
     <t xml:space="preserve">16.671215057373</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7635746002197</t>
+    <t xml:space="preserve">16.7635765075684</t>
   </si>
   <si>
     <t xml:space="preserve">16.7728118896484</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">16.5234375</t>
   </si>
   <si>
-    <t xml:space="preserve">15.710657119751</t>
+    <t xml:space="preserve">15.7106561660767</t>
   </si>
   <si>
     <t xml:space="preserve">16.0708656311035</t>
@@ -3929,25 +3929,25 @@
     <t xml:space="preserve">16.0893383026123</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0062141418457</t>
+    <t xml:space="preserve">16.0062122344971</t>
   </si>
   <si>
     <t xml:space="preserve">16.0523929595947</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6896877288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4710884094238</t>
+    <t xml:space="preserve">16.6896858215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4710865020752</t>
   </si>
   <si>
     <t xml:space="preserve">16.632661819458</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6611747741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5946445465088</t>
+    <t xml:space="preserve">16.6611766815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5946426391602</t>
   </si>
   <si>
     <t xml:space="preserve">17.2124290466309</t>
@@ -3956,10 +3956,10 @@
     <t xml:space="preserve">17.5830993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9442653656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8207092285156</t>
+    <t xml:space="preserve">17.944263458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.820707321167</t>
   </si>
   <si>
     <t xml:space="preserve">17.8302135467529</t>
@@ -3971,7 +3971,7 @@
     <t xml:space="preserve">16.9938259124756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5661315917969</t>
+    <t xml:space="preserve">16.5661296844482</t>
   </si>
   <si>
     <t xml:space="preserve">16.2809982299805</t>
@@ -3980,13 +3980,13 @@
     <t xml:space="preserve">16.204963684082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0053730010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.58717918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.786771774292</t>
+    <t xml:space="preserve">16.00537109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5871801376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7867727279663</t>
   </si>
   <si>
     <t xml:space="preserve">15.5681705474854</t>
@@ -4004,16 +4004,16 @@
     <t xml:space="preserve">15.3305606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6251983642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4541187286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8723125457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9958686828613</t>
+    <t xml:space="preserve">15.6251974105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4541177749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8723115921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9958667755127</t>
   </si>
   <si>
     <t xml:space="preserve">16.0623989105225</t>
@@ -4022,19 +4022,19 @@
     <t xml:space="preserve">15.7012319564819</t>
   </si>
   <si>
-    <t xml:space="preserve">15.777268409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8247880935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7487545013428</t>
+    <t xml:space="preserve">15.7772674560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8247900009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7487535476685</t>
   </si>
   <si>
     <t xml:space="preserve">15.7392492294312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9388418197632</t>
+    <t xml:space="preserve">15.9388427734375</t>
   </si>
   <si>
     <t xml:space="preserve">16.1859569549561</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">16.1574420928955</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8913202285767</t>
+    <t xml:space="preserve">15.8913192749023</t>
   </si>
   <si>
     <t xml:space="preserve">16.9177932739258</t>
@@ -4055,13 +4055,13 @@
     <t xml:space="preserve">17.0223407745361</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1649074554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0603580474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6231555938721</t>
+    <t xml:space="preserve">17.1649055480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.060359954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6231575012207</t>
   </si>
   <si>
     <t xml:space="preserve">16.7277050018311</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">16.3000068664551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4995994567871</t>
+    <t xml:space="preserve">16.4996013641357</t>
   </si>
   <si>
     <t xml:space="preserve">16.509105682373</t>
@@ -4103,16 +4103,16 @@
     <t xml:space="preserve">17.4215240478516</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3074703216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2599506378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8628072738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.881814956665</t>
+    <t xml:space="preserve">17.3074722290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2599487304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8628063201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8818140029907</t>
   </si>
   <si>
     <t xml:space="preserve">16.4235649108887</t>
@@ -4124,16 +4124,16 @@
     <t xml:space="preserve">16.1479377746582</t>
   </si>
   <si>
-    <t xml:space="preserve">15.910327911377</t>
+    <t xml:space="preserve">15.9103288650513</t>
   </si>
   <si>
     <t xml:space="preserve">16.2429828643799</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8533029556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8437976837158</t>
+    <t xml:space="preserve">15.8533020019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8437967300415</t>
   </si>
   <si>
     <t xml:space="preserve">14.7793073654175</t>
@@ -4148,10 +4148,10 @@
     <t xml:space="preserve">14.4466543197632</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7222805023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6917276382446</t>
+    <t xml:space="preserve">14.7222814559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6917285919189</t>
   </si>
   <si>
     <t xml:space="preserve">15.4731273651123</t>
@@ -4163,7 +4163,7 @@
     <t xml:space="preserve">15.4921350479126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0929517745972</t>
+    <t xml:space="preserve">15.0929527282715</t>
   </si>
   <si>
     <t xml:space="preserve">15.4446144104004</t>
@@ -4193,7 +4193,7 @@
     <t xml:space="preserve">14.4846715927124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.931378364563</t>
+    <t xml:space="preserve">14.9313774108887</t>
   </si>
   <si>
     <t xml:space="preserve">14.9218730926514</t>
@@ -4208,37 +4208,37 @@
     <t xml:space="preserve">14.731785774231</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0074119567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7677640914917</t>
+    <t xml:space="preserve">15.0074129104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7677631378174</t>
   </si>
   <si>
     <t xml:space="preserve">16.1954612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5566272735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1289291381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0528926849365</t>
+    <t xml:space="preserve">16.5566253662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.128927230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0528945922852</t>
   </si>
   <si>
     <t xml:space="preserve">16.3570346832275</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4330711364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7467136383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3665370941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3950519561768</t>
+    <t xml:space="preserve">16.433069229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7467155456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3665390014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3950500488281</t>
   </si>
   <si>
     <t xml:space="preserve">16.4805908203125</t>
@@ -4253,10 +4253,10 @@
     <t xml:space="preserve">16.3285217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6136512756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6991920471191</t>
+    <t xml:space="preserve">16.6136531829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6991901397705</t>
   </si>
   <si>
     <t xml:space="preserve">16.5756359100342</t>
@@ -4265,22 +4265,22 @@
     <t xml:space="preserve">18.5240325927734</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7046146392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.647590637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.198844909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4839763641357</t>
+    <t xml:space="preserve">18.7046165466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6475887298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1988430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4839744567871</t>
   </si>
   <si>
     <t xml:space="preserve">19.5029830932617</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4649658203125</t>
+    <t xml:space="preserve">19.4649639129639</t>
   </si>
   <si>
     <t xml:space="preserve">19.2938861846924</t>
@@ -4289,10 +4289,10 @@
     <t xml:space="preserve">19.1037998199463</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2748775482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0277633666992</t>
+    <t xml:space="preserve">19.2748794555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0277652740479</t>
   </si>
   <si>
     <t xml:space="preserve">18.0868320465088</t>
@@ -4319,16 +4319,16 @@
     <t xml:space="preserve">17.9062480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7541770935059</t>
+    <t xml:space="preserve">17.7541790008545</t>
   </si>
   <si>
     <t xml:space="preserve">18.1818752288818</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9157524108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2103881835938</t>
+    <t xml:space="preserve">17.9157543182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2103862762451</t>
   </si>
   <si>
     <t xml:space="preserve">18.343448638916</t>
@@ -4343,16 +4343,16 @@
     <t xml:space="preserve">18.6570930480957</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5810565948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4289894104004</t>
+    <t xml:space="preserve">18.5810585021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4289875030518</t>
   </si>
   <si>
     <t xml:space="preserve">18.1913795471191</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0488128662109</t>
+    <t xml:space="preserve">18.0488147735596</t>
   </si>
   <si>
     <t xml:space="preserve">18.020299911499</t>
@@ -4370,7 +4370,7 @@
     <t xml:space="preserve">17.9632740020752</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0678234100342</t>
+    <t xml:space="preserve">18.0678215026855</t>
   </si>
   <si>
     <t xml:space="preserve">18.1723709106445</t>
@@ -4400,13 +4400,13 @@
     <t xml:space="preserve">17.8112030029297</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5165691375732</t>
+    <t xml:space="preserve">17.5165672302246</t>
   </si>
   <si>
     <t xml:space="preserve">17.5450801849365</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3169746398926</t>
+    <t xml:space="preserve">17.3169765472412</t>
   </si>
   <si>
     <t xml:space="preserve">17.3264808654785</t>
@@ -4427,10 +4427,10 @@
     <t xml:space="preserve">17.5545845031738</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7636814117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8872375488281</t>
+    <t xml:space="preserve">17.7636833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8872394561768</t>
   </si>
   <si>
     <t xml:space="preserve">18.1533622741699</t>
@@ -4439,19 +4439,19 @@
     <t xml:space="preserve">18.1628665924072</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3549938201904</t>
+    <t xml:space="preserve">17.3549957275391</t>
   </si>
   <si>
     <t xml:space="preserve">17.4690456390381</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4405326843262</t>
+    <t xml:space="preserve">17.4405345916748</t>
   </si>
   <si>
     <t xml:space="preserve">17.1078796386719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0413513183594</t>
+    <t xml:space="preserve">17.0413494110107</t>
   </si>
   <si>
     <t xml:space="preserve">16.9368019104004</t>
@@ -4463,7 +4463,7 @@
     <t xml:space="preserve">16.4615821838379</t>
   </si>
   <si>
-    <t xml:space="preserve">16.309513092041</t>
+    <t xml:space="preserve">16.3095111846924</t>
   </si>
   <si>
     <t xml:space="preserve">17.0033321380615</t>
@@ -4487,7 +4487,7 @@
     <t xml:space="preserve">17.6211185455322</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0107955932617</t>
+    <t xml:space="preserve">18.0107975006104</t>
   </si>
   <si>
     <t xml:space="preserve">17.7826900482178</t>
@@ -4502,7 +4502,7 @@
     <t xml:space="preserve">17.5355777740479</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0012912750244</t>
+    <t xml:space="preserve">18.001293182373</t>
   </si>
   <si>
     <t xml:space="preserve">18.2674140930176</t>
@@ -70788,25 +70788,25 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6910069444</v>
+        <v>45967.6909953704</v>
       </c>
       <c r="B2505" t="n">
-        <v>632204</v>
+        <v>122645</v>
       </c>
       <c r="C2505" t="n">
-        <v>14.789999961853</v>
+        <v>14.7700004577637</v>
       </c>
       <c r="D2505" t="n">
-        <v>14.7299995422363</v>
+        <v>14.7399997711182</v>
       </c>
       <c r="E2505" t="n">
-        <v>14.7799997329712</v>
+        <v>14.75</v>
       </c>
       <c r="F2505" t="n">
-        <v>14.75</v>
+        <v>14.7399997711182</v>
       </c>
       <c r="G2505" t="s">
-        <v>1772</v>
+        <v>1761</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>

--- a/data/TNXT.MI.xlsx
+++ b/data/TNXT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="1779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="1780">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,43 +44,43 @@
     <t xml:space="preserve">TNXT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65151000022888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59350848197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53550696372986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52556324005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48579049110413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52722072601318</t>
+    <t xml:space="preserve">2.65150952339172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59350895881653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5355064868927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52556347846985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48579120635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5272204875946</t>
   </si>
   <si>
     <t xml:space="preserve">2.48744821548462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47087597846985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46921849250793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54047846794128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49739098548889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47916173934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44436073303223</t>
+    <t xml:space="preserve">2.47087574005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46921873092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54047822952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49739122390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47916221618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44436097145081</t>
   </si>
   <si>
     <t xml:space="preserve">2.39464449882507</t>
@@ -89,31 +89,31 @@
     <t xml:space="preserve">2.34161448478699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36150097846985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55207848548889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58522295951843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61007976531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56865048408508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63659501075745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68962478637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73436999320984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72608375549316</t>
+    <t xml:space="preserve">2.36150074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55207896232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58522248268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6100800037384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5686502456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63659453392029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68962526321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73436975479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72608351707458</t>
   </si>
   <si>
     <t xml:space="preserve">2.77579951286316</t>
@@ -122,73 +122,73 @@
     <t xml:space="preserve">2.58025121688843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56202173233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66808176040649</t>
+    <t xml:space="preserve">2.5620219707489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66808152198792</t>
   </si>
   <si>
     <t xml:space="preserve">2.62830901145935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64322352409363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60842227935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66642427444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65316700935364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62665176391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6929395198822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82551550865173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81722974777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90008974075317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8586597442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89843273162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8835175037384</t>
+    <t xml:space="preserve">2.64322376251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60842204093933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66642475128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65316677093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62665152549744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69293975830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82551574707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81722927093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90008926391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85865950584412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89843225479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88351726531982</t>
   </si>
   <si>
     <t xml:space="preserve">2.87523126602173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86694526672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81888651847839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82054376602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85368776321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79237151145935</t>
+    <t xml:space="preserve">2.86694550514221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81888675689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82054400444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85368800163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79237127304077</t>
   </si>
   <si>
     <t xml:space="preserve">2.85700225830078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90671801567078</t>
+    <t xml:space="preserve">2.9067177772522</t>
   </si>
   <si>
     <t xml:space="preserve">2.8288300037384</t>
@@ -200,13 +200,13 @@
     <t xml:space="preserve">2.90837550163269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96306252479553</t>
+    <t xml:space="preserve">2.96306276321411</t>
   </si>
   <si>
     <t xml:space="preserve">2.95797753334045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8816967010498</t>
+    <t xml:space="preserve">2.88169693946838</t>
   </si>
   <si>
     <t xml:space="preserve">2.89017295837402</t>
@@ -221,43 +221,43 @@
     <t xml:space="preserve">2.92407512664795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96645331382751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1190128326416</t>
+    <t xml:space="preserve">2.96645307540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11901307106018</t>
   </si>
   <si>
     <t xml:space="preserve">2.94272136688232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94780683517456</t>
+    <t xml:space="preserve">2.94780659675598</t>
   </si>
   <si>
     <t xml:space="preserve">2.8833920955658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8732213973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85966062545776</t>
+    <t xml:space="preserve">2.87322163581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85966038703918</t>
   </si>
   <si>
     <t xml:space="preserve">3.03256297111511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07037353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06866335868835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06011080741882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99340057373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98484826087952</t>
+    <t xml:space="preserve">3.07037377357483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06866312026978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06011033058167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99340081214905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98484778404236</t>
   </si>
   <si>
     <t xml:space="preserve">2.93524289131165</t>
@@ -269,16 +269,16 @@
     <t xml:space="preserve">2.92497992515564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92326927185059</t>
+    <t xml:space="preserve">2.92326951026917</t>
   </si>
   <si>
     <t xml:space="preserve">2.9677426815033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0361635684967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05840015411377</t>
+    <t xml:space="preserve">3.03616380691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05840039253235</t>
   </si>
   <si>
     <t xml:space="preserve">3.05497908592224</t>
@@ -287,19 +287,19 @@
     <t xml:space="preserve">3.08747887611389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13879442214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12853074073792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19010972976685</t>
+    <t xml:space="preserve">3.13879418373108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12853169441223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19010996818542</t>
   </si>
   <si>
     <t xml:space="preserve">3.15589952468872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12339997291565</t>
+    <t xml:space="preserve">3.12339925765991</t>
   </si>
   <si>
     <t xml:space="preserve">3.12511014938354</t>
@@ -308,58 +308,58 @@
     <t xml:space="preserve">3.14734697341919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16445183753967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16616272926331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24142527580261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30129313468933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38681888580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48431825637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52708148956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62629055976868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63655352592468</t>
+    <t xml:space="preserve">3.16445159912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16616249084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24142479896545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30129337310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38681864738464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48431801795959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52708125114441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62629103660583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63655400276184</t>
   </si>
   <si>
     <t xml:space="preserve">3.64510655403137</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74602723121643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67760705947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71181702613831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63484358787537</t>
+    <t xml:space="preserve">3.74602699279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67760634422302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71181678771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63484382629395</t>
   </si>
   <si>
     <t xml:space="preserve">3.51681804656982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50484442710876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49458122253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50655436515808</t>
+    <t xml:space="preserve">3.50484418869019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49458146095276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50655484199524</t>
   </si>
   <si>
     <t xml:space="preserve">3.48089742660522</t>
@@ -371,109 +371,109 @@
     <t xml:space="preserve">3.35602951049805</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60063314437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.646817445755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69471168518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69984340667725</t>
+    <t xml:space="preserve">3.60063338279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64681720733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69471144676208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69984316825867</t>
   </si>
   <si>
     <t xml:space="preserve">3.67589569091797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66563248634338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59721207618713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63313293457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57497501373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66050148010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68615889549255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71523761749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7374746799469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71010613441467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69129061698914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68957996368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73234295845032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7203688621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76313209533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77168464660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62115931510925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64168572425842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70326399803162</t>
+    <t xml:space="preserve">3.66563296318054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59721183776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63313317298889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57497549057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66050124168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68615818023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7152373790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73747444152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71010661125183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69129037857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6895797252655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73234248161316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72036933898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76313233375549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77168440818787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62115955352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64168548583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70326375961304</t>
   </si>
   <si>
     <t xml:space="preserve">3.79734253883362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75457954406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90852618217468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76655268669128</t>
+    <t xml:space="preserve">3.75457882881165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90852642059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76655292510986</t>
   </si>
   <si>
     <t xml:space="preserve">3.72892189025879</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66734313964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50997567176819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49800276756287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4894495010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47234487533569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40392446517944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43642401695251</t>
+    <t xml:space="preserve">3.66734290122986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50997614860535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49800252914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48944973945618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47234439849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40392422676086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43642377853394</t>
   </si>
   <si>
     <t xml:space="preserve">3.53221273422241</t>
@@ -491,97 +491,97 @@
     <t xml:space="preserve">3.53563356399536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55616021156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64339637756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72550082206726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84865784645081</t>
+    <t xml:space="preserve">3.55615997314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64339590072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72550058364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84865808486938</t>
   </si>
   <si>
     <t xml:space="preserve">3.82984256744385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83155298233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87089443206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84523630142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87431573867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86405277252197</t>
+    <t xml:space="preserve">3.83155274391174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87089467048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84523701667786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87431597709656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86405301094055</t>
   </si>
   <si>
     <t xml:space="preserve">3.85721063613892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82471084594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90681457519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00260400772095</t>
+    <t xml:space="preserve">3.82471036911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90681505203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00260448455811</t>
   </si>
   <si>
     <t xml:space="preserve">4.17536640167236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11378812789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00773572921753</t>
+    <t xml:space="preserve">4.11378765106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00773477554321</t>
   </si>
   <si>
     <t xml:space="preserve">4.05220890045166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0812873840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00602531433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09839296340942</t>
+    <t xml:space="preserve">4.08128786087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0060248374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09839248657227</t>
   </si>
   <si>
     <t xml:space="preserve">4.01970911026001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01115655899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99576187133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03510427474976</t>
+    <t xml:space="preserve">4.01115703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99576234817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03510332107544</t>
   </si>
   <si>
     <t xml:space="preserve">4.06247186660767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13773488998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12234020233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14799785614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.189049243927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25918197631836</t>
+    <t xml:space="preserve">4.13773441314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12233972549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14799737930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18905019760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25918102264404</t>
   </si>
   <si>
     <t xml:space="preserve">4.22839212417603</t>
@@ -590,109 +590,109 @@
     <t xml:space="preserve">4.20615577697754</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02142000198364</t>
+    <t xml:space="preserve">4.02141952514648</t>
   </si>
   <si>
     <t xml:space="preserve">3.99405169487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01799821853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02655172348022</t>
+    <t xml:space="preserve">4.01799869537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02655124664307</t>
   </si>
   <si>
     <t xml:space="preserve">4.07615613937378</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12747192382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11891889572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10523509979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09668207168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10181379318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07102537155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09497165679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13089275360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21641874313354</t>
+    <t xml:space="preserve">4.12747240066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11891937255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10523462295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09668254852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10181427001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0710244178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09497213363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13089227676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21641826629639</t>
   </si>
   <si>
     <t xml:space="preserve">4.52431154251099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54996824264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53713989257812</t>
+    <t xml:space="preserve">4.54996871948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53713941574097</t>
   </si>
   <si>
     <t xml:space="preserve">4.46444320678711</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50292921066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56707429885864</t>
+    <t xml:space="preserve">4.50292873382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56707382202148</t>
   </si>
   <si>
     <t xml:space="preserve">4.6226658821106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63549423217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58417940139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60128450393677</t>
+    <t xml:space="preserve">4.63549470901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58417892456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60128402709961</t>
   </si>
   <si>
     <t xml:space="preserve">4.57562637329102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61838960647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53286457061768</t>
+    <t xml:space="preserve">4.61838912963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53286361694336</t>
   </si>
   <si>
     <t xml:space="preserve">4.55852127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48154783248901</t>
+    <t xml:space="preserve">4.48154830932617</t>
   </si>
   <si>
     <t xml:space="preserve">4.51575899124146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49010133743286</t>
+    <t xml:space="preserve">4.4901008605957</t>
   </si>
   <si>
     <t xml:space="preserve">4.51148223876953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63121843338013</t>
+    <t xml:space="preserve">4.63121795654297</t>
   </si>
   <si>
     <t xml:space="preserve">4.78516435623169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7595067024231</t>
+    <t xml:space="preserve">4.75950717926025</t>
   </si>
   <si>
     <t xml:space="preserve">4.78944110870361</t>
@@ -701,34 +701,34 @@
     <t xml:space="preserve">4.73384857177734</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77233648300171</t>
+    <t xml:space="preserve">4.77233552932739</t>
   </si>
   <si>
     <t xml:space="preserve">4.76378345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65687561035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69536209106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82792663574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90062427520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91772890090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94338750839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98614978790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04174137115479</t>
+    <t xml:space="preserve">4.65687656402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69536256790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8279275894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90062475204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91772937774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94338703155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98614931106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04174089431763</t>
   </si>
   <si>
     <t xml:space="preserve">5.0203595161438</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">5.08022832870483</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99470281600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09305763244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06050634384155</t>
+    <t xml:space="preserve">4.99470233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09305715560913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06050682067871</t>
   </si>
   <si>
     <t xml:space="preserve">4.91728496551514</t>
@@ -770,61 +770,61 @@
     <t xml:space="preserve">4.72198247909546</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59178113937378</t>
+    <t xml:space="preserve">4.59178066253662</t>
   </si>
   <si>
     <t xml:space="preserve">4.64386129379272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73066234588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66556119918823</t>
+    <t xml:space="preserve">4.73066186904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66556167602539</t>
   </si>
   <si>
     <t xml:space="preserve">4.65254163742065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60914087295532</t>
+    <t xml:space="preserve">4.60914039611816</t>
   </si>
   <si>
     <t xml:space="preserve">4.65688133239746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54837942123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53536033630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47025918960571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59612083435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47459983825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48761940002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46157932281494</t>
+    <t xml:space="preserve">4.54837989807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53535985946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47025966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59612035751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47459936141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48761987686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46157884597778</t>
   </si>
   <si>
     <t xml:space="preserve">4.41383790969849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38779783248901</t>
+    <t xml:space="preserve">4.38779735565186</t>
   </si>
   <si>
     <t xml:space="preserve">4.39213800430298</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40949869155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55706071853638</t>
+    <t xml:space="preserve">4.40949821472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55706024169922</t>
   </si>
   <si>
     <t xml:space="preserve">4.52233982086182</t>
@@ -833,10 +833,10 @@
     <t xml:space="preserve">4.57008028030396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53970050811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47893857955933</t>
+    <t xml:space="preserve">4.53970003128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47893905639648</t>
   </si>
   <si>
     <t xml:space="preserve">4.43553876876831</t>
@@ -854,13 +854,13 @@
     <t xml:space="preserve">4.51365995407104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68726253509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60046148300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6395206451416</t>
+    <t xml:space="preserve">4.68726205825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60046052932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63952112197876</t>
   </si>
   <si>
     <t xml:space="preserve">4.56140041351318</t>
@@ -869,88 +869,88 @@
     <t xml:space="preserve">4.5874400138855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61782073974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64820194244385</t>
+    <t xml:space="preserve">4.61782121658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64820146560669</t>
   </si>
   <si>
     <t xml:space="preserve">4.60480070114136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58310127258301</t>
+    <t xml:space="preserve">4.58310031890869</t>
   </si>
   <si>
     <t xml:space="preserve">4.49629926681519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50497961044312</t>
+    <t xml:space="preserve">4.50498008728027</t>
   </si>
   <si>
     <t xml:space="preserve">4.42685842514038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49195909500122</t>
+    <t xml:space="preserve">4.49195957183838</t>
   </si>
   <si>
     <t xml:space="preserve">4.51800012588501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80878305435181</t>
+    <t xml:space="preserve">4.80878400802612</t>
   </si>
   <si>
     <t xml:space="preserve">4.77840328216553</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84784412384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83482360839844</t>
+    <t xml:space="preserve">4.84784364700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83482456207275</t>
   </si>
   <si>
     <t xml:space="preserve">4.74368286132812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81312322616577</t>
+    <t xml:space="preserve">4.81312370300293</t>
   </si>
   <si>
     <t xml:space="preserve">4.71330213546753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70462226867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72632217407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69594240188599</t>
+    <t xml:space="preserve">4.7046217918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72632265090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69594144821167</t>
   </si>
   <si>
     <t xml:space="preserve">4.7697229385376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84350442886353</t>
+    <t xml:space="preserve">4.84350395202637</t>
   </si>
   <si>
     <t xml:space="preserve">4.87822437286377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87388372421265</t>
+    <t xml:space="preserve">4.87388467788696</t>
   </si>
   <si>
     <t xml:space="preserve">4.97370576858521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97804546356201</t>
+    <t xml:space="preserve">4.97804641723633</t>
   </si>
   <si>
     <t xml:space="preserve">5.00842618942261</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07786750793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04314661026001</t>
+    <t xml:space="preserve">5.07786703109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04314565658569</t>
   </si>
   <si>
     <t xml:space="preserve">5.14730834960938</t>
@@ -959,25 +959,25 @@
     <t xml:space="preserve">4.86086416244507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86954498291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96502494812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90860509872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99974632263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99106597900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1559886932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12994766235352</t>
+    <t xml:space="preserve">4.869544506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96502590179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90860462188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99974584579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99106550216675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15598821640015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12994813919067</t>
   </si>
   <si>
     <t xml:space="preserve">5.29486989974976</t>
@@ -986,49 +986,49 @@
     <t xml:space="preserve">5.41639137268066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48583269119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43375253677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48149299621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42073106765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39469146728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35563039779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33393001556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37299060821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33827066421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20806884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16466808319092</t>
+    <t xml:space="preserve">5.48583173751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43375158309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48149251937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42073202133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39469194412231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35563087463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33393096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37299108505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33827018737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20806932449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16466760635376</t>
   </si>
   <si>
     <t xml:space="preserve">5.26448965072632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25147008895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26014947891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18636846542358</t>
+    <t xml:space="preserve">5.25146961212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26014995574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18636798858643</t>
   </si>
   <si>
     <t xml:space="preserve">5.20372867584229</t>
@@ -1043,22 +1043,22 @@
     <t xml:space="preserve">5.18202829360962</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19938850402832</t>
+    <t xml:space="preserve">5.19938898086548</t>
   </si>
   <si>
     <t xml:space="preserve">5.22542905807495</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42507171630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61603355407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7288761138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7115159034729</t>
+    <t xml:space="preserve">5.42507219314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61603403091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72887563705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71151542663574</t>
   </si>
   <si>
     <t xml:space="preserve">5.78963661193848</t>
@@ -1067,10 +1067,10 @@
     <t xml:space="preserve">5.82435703277588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87643814086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88511848449707</t>
+    <t xml:space="preserve">5.87643766403198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88511753082275</t>
   </si>
   <si>
     <t xml:space="preserve">5.93719816207886</t>
@@ -1079,34 +1079,34 @@
     <t xml:space="preserve">5.85907697677612</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80699634552002</t>
+    <t xml:space="preserve">5.80699682235718</t>
   </si>
   <si>
     <t xml:space="preserve">5.92851781845093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97191905975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95455932617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03267955780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1715612411499</t>
+    <t xml:space="preserve">5.97191953659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95455837249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03268003463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17156171798706</t>
   </si>
   <si>
     <t xml:space="preserve">6.28440284729004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01531887054443</t>
+    <t xml:space="preserve">6.01531934738159</t>
   </si>
   <si>
     <t xml:space="preserve">6.02399921417236</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21496152877808</t>
+    <t xml:space="preserve">6.21496200561523</t>
   </si>
   <si>
     <t xml:space="preserve">6.14552116394043</t>
@@ -1115,16 +1115,16 @@
     <t xml:space="preserve">6.40592479705811</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07608032226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98927927017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04135942459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22364234924316</t>
+    <t xml:space="preserve">6.07607984542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98927974700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04136037826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22364282608032</t>
   </si>
   <si>
     <t xml:space="preserve">6.13684129714966</t>
@@ -1133,52 +1133,52 @@
     <t xml:space="preserve">6.19760179519653</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15420150756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05004072189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89379787445068</t>
+    <t xml:space="preserve">6.1542010307312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05004024505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89379739761353</t>
   </si>
   <si>
     <t xml:space="preserve">5.90247774124146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70283508300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50319337844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58131313323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72019577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76359558105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91983890533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99795913696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83303689956665</t>
+    <t xml:space="preserve">5.70283555984497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50319242477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5813136100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72019624710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76359605789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91983795166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99795961380005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83303642272949</t>
   </si>
   <si>
     <t xml:space="preserve">5.79831647872925</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65943431854248</t>
+    <t xml:space="preserve">5.65943479537964</t>
   </si>
   <si>
     <t xml:space="preserve">5.5118727684021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54659271240234</t>
+    <t xml:space="preserve">5.5465931892395</t>
   </si>
   <si>
     <t xml:space="preserve">5.58999395370483</t>
@@ -1187,19 +1187,19 @@
     <t xml:space="preserve">5.52055263519287</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38167095184326</t>
+    <t xml:space="preserve">5.38167142868042</t>
   </si>
   <si>
     <t xml:space="preserve">5.44243144989014</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46847295761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67679500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6420750617981</t>
+    <t xml:space="preserve">5.46847200393677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6767954826355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64207458496094</t>
   </si>
   <si>
     <t xml:space="preserve">5.55527400970459</t>
@@ -1208,31 +1208,31 @@
     <t xml:space="preserve">5.53791332244873</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57263326644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52923250198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3990306854248</t>
+    <t xml:space="preserve">5.57263422012329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5292329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39903116226196</t>
   </si>
   <si>
     <t xml:space="preserve">5.39035177230835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45111179351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09344053268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81567764282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77227687835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73755598068237</t>
+    <t xml:space="preserve">5.45111274719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09344100952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81567668914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77227640151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73755645751953</t>
   </si>
   <si>
     <t xml:space="preserve">5.40771150588989</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">5.24278926849365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06918668746948</t>
+    <t xml:space="preserve">5.06918716430664</t>
   </si>
   <si>
     <t xml:space="preserve">4.98238563537598</t>
@@ -1250,22 +1250,22 @@
     <t xml:space="preserve">5.07618808746338</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15619802474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0850772857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24509811401367</t>
+    <t xml:space="preserve">5.1561975479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08507823944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24509763717651</t>
   </si>
   <si>
     <t xml:space="preserve">5.11174774169922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13841819763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20953845977783</t>
+    <t xml:space="preserve">5.13841772079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20953750610352</t>
   </si>
   <si>
     <t xml:space="preserve">5.14730739593506</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">5.067298412323</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0584077835083</t>
+    <t xml:space="preserve">5.05840826034546</t>
   </si>
   <si>
     <t xml:space="preserve">5.04062795639038</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">5.04951763153076</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94283771514893</t>
+    <t xml:space="preserve">4.94283819198608</t>
   </si>
   <si>
     <t xml:space="preserve">4.77392768859863</t>
@@ -1295,10 +1295,10 @@
     <t xml:space="preserve">4.76503801345825</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92505741119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88949871063232</t>
+    <t xml:space="preserve">4.92505836486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88949775695801</t>
   </si>
   <si>
     <t xml:space="preserve">5.02284812927246</t>
@@ -1310,19 +1310,19 @@
     <t xml:space="preserve">4.91616821289062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95172786712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9339485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89838790893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80948829650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78281831741333</t>
+    <t xml:space="preserve">4.95172834396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93394899368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89838838577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80948781967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78281784057617</t>
   </si>
   <si>
     <t xml:space="preserve">4.75614786148071</t>
@@ -1334,10 +1334,10 @@
     <t xml:space="preserve">5.10285758972168</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96061849594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20064830780029</t>
+    <t xml:space="preserve">4.960618019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20064783096313</t>
   </si>
   <si>
     <t xml:space="preserve">5.21842765808105</t>
@@ -1355,34 +1355,34 @@
     <t xml:space="preserve">5.18286752700806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01395750045776</t>
+    <t xml:space="preserve">5.01395797729492</t>
   </si>
   <si>
     <t xml:space="preserve">4.99617767333984</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00506782531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37844848632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47623729705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56513833999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68070697784424</t>
+    <t xml:space="preserve">5.00506830215454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37844800949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47623777389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56513786315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6807074546814</t>
   </si>
   <si>
     <t xml:space="preserve">5.65403747558594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63625812530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55624771118164</t>
+    <t xml:space="preserve">5.63625717163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5562481880188</t>
   </si>
   <si>
     <t xml:space="preserve">5.68959808349609</t>
@@ -1391,31 +1391,31 @@
     <t xml:space="preserve">5.96518754959106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89406728744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77849817276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84072732925415</t>
+    <t xml:space="preserve">5.89406776428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77849769592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84072780609131</t>
   </si>
   <si>
     <t xml:space="preserve">5.76071739196777</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92073726654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83183765411377</t>
+    <t xml:space="preserve">5.92073774337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83183717727661</t>
   </si>
   <si>
     <t xml:space="preserve">5.44956827163696</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5829176902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43178749084473</t>
+    <t xml:space="preserve">5.58291816711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43178796768188</t>
   </si>
   <si>
     <t xml:space="preserve">5.36955785751343</t>
@@ -1433,19 +1433,19 @@
     <t xml:space="preserve">5.5206880569458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49401807785034</t>
+    <t xml:space="preserve">5.49401760101318</t>
   </si>
   <si>
     <t xml:space="preserve">5.5740270614624</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59180784225464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64514780044556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71626710891724</t>
+    <t xml:space="preserve">5.59180736541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6451473236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71626806259155</t>
   </si>
   <si>
     <t xml:space="preserve">5.73404788970947</t>
@@ -1457,49 +1457,49 @@
     <t xml:space="preserve">5.67181777954102</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5117974281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85850763320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66292715072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53846788406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90295696258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79627704620361</t>
+    <t xml:space="preserve">5.51179790496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85850811004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66292762756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53846836090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90295791625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79627799987793</t>
   </si>
   <si>
     <t xml:space="preserve">5.80516767501831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6184778213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46734809875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60069847106934</t>
+    <t xml:space="preserve">5.61847686767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46734762191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60069751739502</t>
   </si>
   <si>
     <t xml:space="preserve">5.45845794677734</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50290727615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34288740158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62736797332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52957725524902</t>
+    <t xml:space="preserve">5.50290775299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34288835525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62736701965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52957773208618</t>
   </si>
   <si>
     <t xml:space="preserve">5.42289781570435</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">5.72515773773193</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70737743377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69848775863647</t>
+    <t xml:space="preserve">5.70737791061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69848728179932</t>
   </si>
   <si>
     <t xml:space="preserve">6.0007472038269</t>
@@ -1520,43 +1520,43 @@
     <t xml:space="preserve">5.92962789535522</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94740724563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93851757049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99185705184937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24077749252319</t>
+    <t xml:space="preserve">5.94740772247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93851709365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99185752868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24077796936035</t>
   </si>
   <si>
     <t xml:space="preserve">6.40968704223633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48080730438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62304735183716</t>
+    <t xml:space="preserve">6.48080682754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.623046875</t>
   </si>
   <si>
     <t xml:space="preserve">6.84529733657837</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99642705917358</t>
+    <t xml:space="preserve">6.99642753601074</t>
   </si>
   <si>
     <t xml:space="preserve">7.0142068862915</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90752744674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91641759872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97864675521851</t>
+    <t xml:space="preserve">6.90752696990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91641712188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97864723205566</t>
   </si>
   <si>
     <t xml:space="preserve">7.00531721115112</t>
@@ -1568,28 +1568,28 @@
     <t xml:space="preserve">7.24534702301025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27201795578003</t>
+    <t xml:space="preserve">7.27201747894287</t>
   </si>
   <si>
     <t xml:space="preserve">7.33424711227417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47648668289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76985740661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7342963218689</t>
+    <t xml:space="preserve">7.476487159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76985645294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73429584503174</t>
   </si>
   <si>
     <t xml:space="preserve">7.72540616989136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79652786254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80541706085205</t>
+    <t xml:space="preserve">7.79652738571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80541563034058</t>
   </si>
   <si>
     <t xml:space="preserve">8.22324657440186</t>
@@ -1604,7 +1604,7 @@
     <t xml:space="preserve">8.12545776367188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00099658966064</t>
+    <t xml:space="preserve">8.00099754333496</t>
   </si>
   <si>
     <t xml:space="preserve">8.17879676818848</t>
@@ -1616,16 +1616,16 @@
     <t xml:space="preserve">8.42771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48105621337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46327781677246</t>
+    <t xml:space="preserve">8.48105525970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46327686309814</t>
   </si>
   <si>
     <t xml:space="preserve">8.5255069732666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50772666931152</t>
+    <t xml:space="preserve">8.50772571563721</t>
   </si>
   <si>
     <t xml:space="preserve">8.66774654388428</t>
@@ -1637,43 +1637,43 @@
     <t xml:space="preserve">8.88999652862549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19225597381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37005424499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47673606872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49451732635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31671524047852</t>
+    <t xml:space="preserve">9.19225788116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37005519866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47673511505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49451637268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31671619415283</t>
   </si>
   <si>
     <t xml:space="preserve">9.15669631958008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35227680206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40561676025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69009590148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86789703369141</t>
+    <t xml:space="preserve">9.35227584838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40561580657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69009494781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86789798736572</t>
   </si>
   <si>
     <t xml:space="preserve">9.83233642578125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77899742126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44117641448975</t>
+    <t xml:space="preserve">9.77899551391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44117546081543</t>
   </si>
   <si>
     <t xml:space="preserve">9.210036277771</t>
@@ -1685,28 +1685,28 @@
     <t xml:space="preserve">9.51229572296143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6723165512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8501148223877</t>
+    <t xml:space="preserve">9.67231559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85011672973633</t>
   </si>
   <si>
     <t xml:space="preserve">10.0990352630615</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0279150009155</t>
+    <t xml:space="preserve">10.0279159545898</t>
   </si>
   <si>
     <t xml:space="preserve">9.99235534667969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0101356506348</t>
+    <t xml:space="preserve">10.0101366043091</t>
   </si>
   <si>
     <t xml:space="preserve">9.76121616363525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88567543029785</t>
+    <t xml:space="preserve">9.88567638397217</t>
   </si>
   <si>
     <t xml:space="preserve">10.2234954833984</t>
@@ -1718,22 +1718,22 @@
     <t xml:space="preserve">10.6679954528809</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4147548675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3614139556885</t>
+    <t xml:space="preserve">11.414755821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3614149093628</t>
   </si>
   <si>
     <t xml:space="preserve">11.3080749511719</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4325342178345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6814546585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.894814491272</t>
+    <t xml:space="preserve">11.4325361251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6814556121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8948154449463</t>
   </si>
   <si>
     <t xml:space="preserve">11.9659357070923</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">11.6281156539917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4001140594482</t>
+    <t xml:space="preserve">11.4001131057739</t>
   </si>
   <si>
     <t xml:space="preserve">11.6715440750122</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">11.689640045166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1239309310913</t>
+    <t xml:space="preserve">12.123929977417</t>
   </si>
   <si>
     <t xml:space="preserve">11.7982120513916</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">12.1782159805298</t>
   </si>
   <si>
-    <t xml:space="preserve">12.322979927063</t>
+    <t xml:space="preserve">12.3229789733887</t>
   </si>
   <si>
     <t xml:space="preserve">12.9925098419189</t>
@@ -1775,28 +1775,28 @@
     <t xml:space="preserve">12.8296508789062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7391748428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7753648757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.395359992981</t>
+    <t xml:space="preserve">12.7391738891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7753639221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3953609466553</t>
   </si>
   <si>
     <t xml:space="preserve">12.2867879867554</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6306028366089</t>
+    <t xml:space="preserve">12.6306009292603</t>
   </si>
   <si>
     <t xml:space="preserve">12.4496479034424</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2144069671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1058340072632</t>
+    <t xml:space="preserve">12.2144060134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1058349609375</t>
   </si>
   <si>
     <t xml:space="preserve">11.8705930709839</t>
@@ -1820,25 +1820,25 @@
     <t xml:space="preserve">12.0877389907837</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8344030380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8886890411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4363040924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3277320861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734460830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1829681396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1648721694946</t>
+    <t xml:space="preserve">11.8344039916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.888689994812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4363031387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3277311325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734451293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1829690933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1648731231689</t>
   </si>
   <si>
     <t xml:space="preserve">10.8391542434692</t>
@@ -1850,82 +1850,82 @@
     <t xml:space="preserve">10.6762962341309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5134382247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9115381240845</t>
+    <t xml:space="preserve">10.5134372711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9115362167358</t>
   </si>
   <si>
     <t xml:space="preserve">11.291540145874</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1467761993408</t>
+    <t xml:space="preserve">11.1467771530151</t>
   </si>
   <si>
     <t xml:space="preserve">10.766773223877</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1105861663818</t>
+    <t xml:space="preserve">11.1105871200562</t>
   </si>
   <si>
     <t xml:space="preserve">11.1286821365356</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6220102310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0020132064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6039161682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4953422546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2781972885132</t>
+    <t xml:space="preserve">10.6220092773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0020141601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6039142608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4953413009644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2781982421875</t>
   </si>
   <si>
     <t xml:space="preserve">10.3143882751465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89819145202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9343843460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80771732330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6810474395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95248031616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2420072555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4772462844849</t>
+    <t xml:space="preserve">9.89819240570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93438339233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80771636962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68104839324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95247840881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2420063018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4772453308105</t>
   </si>
   <si>
     <t xml:space="preserve">10.3867692947388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4410572052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55438137054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1153373718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3505783081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4048652648926</t>
+    <t xml:space="preserve">10.4410552978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55438041687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1153383255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3505802154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4048643112183</t>
   </si>
   <si>
     <t xml:space="preserve">10.7486791610718</t>
@@ -1934,22 +1934,22 @@
     <t xml:space="preserve">11.0201101303101</t>
   </si>
   <si>
-    <t xml:space="preserve">10.857250213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8753461837769</t>
+    <t xml:space="preserve">10.8572492599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8753471374512</t>
   </si>
   <si>
     <t xml:space="preserve">10.5858192443848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8029651641846</t>
+    <t xml:space="preserve">10.8029642105103</t>
   </si>
   <si>
     <t xml:space="preserve">10.7124872207642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7848682403564</t>
+    <t xml:space="preserve">10.7848691940308</t>
   </si>
   <si>
     <t xml:space="preserve">11.2372550964355</t>
@@ -1958,16 +1958,16 @@
     <t xml:space="preserve">11.3096361160278</t>
   </si>
   <si>
-    <t xml:space="preserve">11.454400062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7258291244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9972610473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1601209640503</t>
+    <t xml:space="preserve">11.4543981552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.725830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9972620010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.160120010376</t>
   </si>
   <si>
     <t xml:space="preserve">12.0515480041504</t>
@@ -1976,10 +1976,10 @@
     <t xml:space="preserve">12.0334529876709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9429750442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7620220184326</t>
+    <t xml:space="preserve">11.9429759979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7620210647583</t>
   </si>
   <si>
     <t xml:space="preserve">10.9477281570435</t>
@@ -1988,16 +1988,16 @@
     <t xml:space="preserve">10.9658231735229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1877193450928</t>
+    <t xml:space="preserve">10.1877202987671</t>
   </si>
   <si>
     <t xml:space="preserve">9.98867034912109</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0429563522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91628932952881</t>
+    <t xml:space="preserve">10.0429573059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91629028320312</t>
   </si>
   <si>
     <t xml:space="preserve">10.1696243286133</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">10.531533241272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4229612350464</t>
+    <t xml:space="preserve">10.4229602813721</t>
   </si>
   <si>
     <t xml:space="preserve">10.1334342956543</t>
@@ -2015,43 +2015,43 @@
     <t xml:space="preserve">10.3324842453003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2239112854004</t>
+    <t xml:space="preserve">10.2239122390747</t>
   </si>
   <si>
     <t xml:space="preserve">10.097243309021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0610513687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0791482925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1515293121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0562992095947</t>
+    <t xml:space="preserve">10.0610523223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0791473388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1515302658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0563011169434</t>
   </si>
   <si>
     <t xml:space="preserve">10.8934412002563</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5496282577515</t>
+    <t xml:space="preserve">10.5496273040771</t>
   </si>
   <si>
     <t xml:space="preserve">10.3686742782593</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82581043243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77152633666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.699143409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51819038391113</t>
+    <t xml:space="preserve">9.8258113861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77152538299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69914436340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5181884765625</t>
   </si>
   <si>
     <t xml:space="preserve">9.7172384262085</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">9.42771244049072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59057235717773</t>
+    <t xml:space="preserve">9.5905704498291</t>
   </si>
   <si>
     <t xml:space="preserve">11.3639221191406</t>
@@ -2075,13 +2075,13 @@
     <t xml:space="preserve">12.3772659301758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3820180892944</t>
+    <t xml:space="preserve">11.3820161819458</t>
   </si>
   <si>
     <t xml:space="preserve">11.5629711151123</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6172580718994</t>
+    <t xml:space="preserve">11.6172590255737</t>
   </si>
   <si>
     <t xml:space="preserve">11.0924921035767</t>
@@ -2093,19 +2093,19 @@
     <t xml:space="preserve">9.62676239013672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8034200668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68580055236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43246459960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0481653213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32864427566528</t>
+    <t xml:space="preserve">8.80342102050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68579959869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43246555328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04816484451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32864475250244</t>
   </si>
   <si>
     <t xml:space="preserve">7.24721479415894</t>
@@ -2114,7 +2114,7 @@
     <t xml:space="preserve">7.18388080596924</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58673238754272</t>
+    <t xml:space="preserve">6.58673191070557</t>
   </si>
   <si>
     <t xml:space="preserve">6.65006542205811</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">6.96673583984375</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97578382492065</t>
+    <t xml:space="preserve">6.9757833480835</t>
   </si>
   <si>
     <t xml:space="preserve">7.16578531265259</t>
@@ -2132,40 +2132,40 @@
     <t xml:space="preserve">7.05721282958984</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28340625762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60912322998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76293468475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3419885635376</t>
+    <t xml:space="preserve">7.28340530395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60912275314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76293277740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34198665618896</t>
   </si>
   <si>
     <t xml:space="preserve">8.04341316223145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61341953277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4143705368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25151062011719</t>
+    <t xml:space="preserve">8.61341857910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41436958312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25150966644287</t>
   </si>
   <si>
     <t xml:space="preserve">8.93008804321289</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35533046722412</t>
+    <t xml:space="preserve">9.35533142089844</t>
   </si>
   <si>
     <t xml:space="preserve">9.04770851135254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26485347747803</t>
+    <t xml:space="preserve">9.26485443115234</t>
   </si>
   <si>
     <t xml:space="preserve">9.50009441375732</t>
@@ -2174,10 +2174,10 @@
     <t xml:space="preserve">9.8620023727417</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2191581726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9839191436768</t>
+    <t xml:space="preserve">11.2191591262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9839181900024</t>
   </si>
   <si>
     <t xml:space="preserve">10.6582012176514</t>
@@ -2186,13 +2186,13 @@
     <t xml:space="preserve">9.9705753326416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2058143615723</t>
+    <t xml:space="preserve">10.2058153152466</t>
   </si>
   <si>
     <t xml:space="preserve">9.84390735626221</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4591522216797</t>
+    <t xml:space="preserve">10.4591512680054</t>
   </si>
   <si>
     <t xml:space="preserve">10.9296321868896</t>
@@ -2201,10 +2201,10 @@
     <t xml:space="preserve">10.7305822372437</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8210601806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0696439743042</t>
+    <t xml:space="preserve">10.8210592269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0696449279785</t>
   </si>
   <si>
     <t xml:space="preserve">12.558219909668</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">12.4315519332886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5944108963013</t>
+    <t xml:space="preserve">12.594409942627</t>
   </si>
   <si>
     <t xml:space="preserve">12.6486959457397</t>
@@ -2234,19 +2234,19 @@
     <t xml:space="preserve">12.7210779190063</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8658409118652</t>
+    <t xml:space="preserve">12.8658418655396</t>
   </si>
   <si>
     <t xml:space="preserve">13.1553678512573</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0286998748779</t>
+    <t xml:space="preserve">13.0287008285522</t>
   </si>
   <si>
     <t xml:space="preserve">13.1191778182983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9382228851318</t>
+    <t xml:space="preserve">12.9382238388062</t>
   </si>
   <si>
     <t xml:space="preserve">13.082986831665</t>
@@ -2255,79 +2255,79 @@
     <t xml:space="preserve">13.3725128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3544178009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4534864425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.249683380127</t>
+    <t xml:space="preserve">13.3544187545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.453483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2496871948242</t>
   </si>
   <si>
     <t xml:space="preserve">16.2858772277832</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3763542175293</t>
+    <t xml:space="preserve">16.3763523101807</t>
   </si>
   <si>
     <t xml:space="preserve">16.6477832794189</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8334913253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0687313079834</t>
+    <t xml:space="preserve">15.8334903717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0687294006348</t>
   </si>
   <si>
     <t xml:space="preserve">15.869683265686</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9239673614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9058723449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8515872955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0144462585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7972974777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2677803039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0325374603271</t>
+    <t xml:space="preserve">15.9239683151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9058694839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8515853881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0144424438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7972984313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2677783966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0325393676758</t>
   </si>
   <si>
     <t xml:space="preserve">15.7792043685913</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7249164581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4125423431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8153953552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.942063331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6344413757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1049213409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9601583480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6887264251709</t>
+    <t xml:space="preserve">15.7249174118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4125442504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8153944015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9420623779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6344404220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.104923248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9601564407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6887283325195</t>
   </si>
   <si>
     <t xml:space="preserve">15.6163463592529</t>
@@ -2339,28 +2339,28 @@
     <t xml:space="preserve">15.6525344848633</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3630084991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4896783828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1458654403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0372924804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7430124282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8201456069946</t>
+    <t xml:space="preserve">15.3630104064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4896774291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1458644866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0372934341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.743013381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8201465606689</t>
   </si>
   <si>
     <t xml:space="preserve">15.2906274795532</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5887489318848</t>
+    <t xml:space="preserve">17.5887470245361</t>
   </si>
   <si>
     <t xml:space="preserve">17.7696990966797</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">18.2763729095459</t>
   </si>
   <si>
-    <t xml:space="preserve">18.041130065918</t>
+    <t xml:space="preserve">18.0411319732666</t>
   </si>
   <si>
     <t xml:space="preserve">17.4258861541748</t>
@@ -2384,43 +2384,43 @@
     <t xml:space="preserve">17.7335109710693</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2992210388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0458831787109</t>
+    <t xml:space="preserve">17.2992191314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0458850860596</t>
   </si>
   <si>
     <t xml:space="preserve">17.0277881622314</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7020683288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0096912384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4077911376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5025653839111</t>
+    <t xml:space="preserve">16.7020702362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.009693145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4077892303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5025672912598</t>
   </si>
   <si>
     <t xml:space="preserve">18.1406555175781</t>
   </si>
   <si>
-    <t xml:space="preserve">17.96875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.49827003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9868450164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5930423736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1544551849365</t>
+    <t xml:space="preserve">17.9687519073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4982681274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9868431091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5930404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1544570922852</t>
   </si>
   <si>
     <t xml:space="preserve">17.2449321746826</t>
@@ -2429,19 +2429,19 @@
     <t xml:space="preserve">17.1182651519775</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8106441497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8287410736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9735012054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9192161560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0639781951904</t>
+    <t xml:space="preserve">16.8106422424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8287391662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.973503112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9192180633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0639801025391</t>
   </si>
   <si>
     <t xml:space="preserve">16.8468341827393</t>
@@ -2450,13 +2450,13 @@
     <t xml:space="preserve">16.9011211395264</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3173160552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2087440490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2268390655518</t>
+    <t xml:space="preserve">17.3173122406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2087421417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2268371582031</t>
   </si>
   <si>
     <t xml:space="preserve">18.3668479919434</t>
@@ -2465,25 +2465,25 @@
     <t xml:space="preserve">18.4573249816895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6382789611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7287559509277</t>
+    <t xml:space="preserve">18.6382827758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7287578582764</t>
   </si>
   <si>
     <t xml:space="preserve">18.9549503326416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8644714355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6335296630859</t>
+    <t xml:space="preserve">18.8644733428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6335277557373</t>
   </si>
   <si>
     <t xml:space="preserve">19.6787662506104</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5430526733398</t>
+    <t xml:space="preserve">19.5430507659912</t>
   </si>
   <si>
     <t xml:space="preserve">19.0454254150391</t>
@@ -2492,16 +2492,16 @@
     <t xml:space="preserve">19.0001888275146</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3168601989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3216094970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2311325073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0906677246094</t>
+    <t xml:space="preserve">19.3168563842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3216114044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2311344146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0906658172607</t>
   </si>
   <si>
     <t xml:space="preserve">18.6835193634033</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">18.0954170227051</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0049381256104</t>
+    <t xml:space="preserve">18.004940032959</t>
   </si>
   <si>
     <t xml:space="preserve">17.570650100708</t>
@@ -2522,22 +2522,22 @@
     <t xml:space="preserve">17.6430320739746</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8058929443359</t>
+    <t xml:space="preserve">17.8058910369873</t>
   </si>
   <si>
     <t xml:space="preserve">19.2716178894043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1811447143555</t>
+    <t xml:space="preserve">19.1811408996582</t>
   </si>
   <si>
     <t xml:space="preserve">20.2668685913086</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4930610656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9906845092773</t>
+    <t xml:space="preserve">20.4930591583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9906826019287</t>
   </si>
   <si>
     <t xml:space="preserve">20.5835380554199</t>
@@ -2546,16 +2546,16 @@
     <t xml:space="preserve">20.3573455810547</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9049606323242</t>
+    <t xml:space="preserve">19.904956817627</t>
   </si>
   <si>
     <t xml:space="preserve">19.7692432403564</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7192516326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9954357147217</t>
+    <t xml:space="preserve">20.7192535400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9954376220703</t>
   </si>
   <si>
     <t xml:space="preserve">19.2263813018799</t>
@@ -2564,10 +2564,10 @@
     <t xml:space="preserve">19.4525737762451</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4073371887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6249370574951</t>
+    <t xml:space="preserve">19.4073352813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6249351501465</t>
   </si>
   <si>
     <t xml:space="preserve">17.7877941131592</t>
@@ -2576,67 +2576,67 @@
     <t xml:space="preserve">19.4978122711182</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0859127044678</t>
+    <t xml:space="preserve">20.0859146118164</t>
   </si>
   <si>
     <t xml:space="preserve">20.1311511993408</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8597221374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6740169525146</t>
+    <t xml:space="preserve">19.8597240447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.674015045166</t>
   </si>
   <si>
     <t xml:space="preserve">21.0359230041504</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8097305297852</t>
+    <t xml:space="preserve">20.8097286224365</t>
   </si>
   <si>
     <t xml:space="preserve">20.628776550293</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3121089935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4478225708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8821144104004</t>
+    <t xml:space="preserve">20.3121070861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4478244781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8821105957031</t>
   </si>
   <si>
     <t xml:space="preserve">21.2802104949951</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3344974517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5878314971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.660213470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1668853759766</t>
+    <t xml:space="preserve">21.3344955444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.587833404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6602153778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1668872833252</t>
   </si>
   <si>
     <t xml:space="preserve">22.6192722320557</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8726081848145</t>
+    <t xml:space="preserve">22.8726062774658</t>
   </si>
   <si>
     <t xml:space="preserve">23.9040470123291</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7821292877197</t>
+    <t xml:space="preserve">22.7821311950684</t>
   </si>
   <si>
     <t xml:space="preserve">21.8592643737793</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0040264129639</t>
+    <t xml:space="preserve">22.0040283203125</t>
   </si>
   <si>
     <t xml:space="preserve">22.2573642730713</t>
@@ -2645,22 +2645,22 @@
     <t xml:space="preserve">22.4745101928711</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1125984191895</t>
+    <t xml:space="preserve">22.1126022338867</t>
   </si>
   <si>
     <t xml:space="preserve">22.058313369751</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6011753082275</t>
+    <t xml:space="preserve">22.6011772155762</t>
   </si>
   <si>
     <t xml:space="preserve">22.6373672485352</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4202213287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4021263122559</t>
+    <t xml:space="preserve">22.4202251434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4021282196045</t>
   </si>
   <si>
     <t xml:space="preserve">21.3525924682617</t>
@@ -2681,10 +2681,10 @@
     <t xml:space="preserve">23.017370223999</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3611812591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2707042694092</t>
+    <t xml:space="preserve">23.3611850738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2707061767578</t>
   </si>
   <si>
     <t xml:space="preserve">25.0440578460693</t>
@@ -2705,19 +2705,19 @@
     <t xml:space="preserve">26.2383556365967</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6765727996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7130947113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5852794647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6583156585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8226451873779</t>
+    <t xml:space="preserve">26.676570892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7130908966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.585277557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6583137512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8226470947266</t>
   </si>
   <si>
     <t xml:space="preserve">26.95046043396</t>
@@ -2729,13 +2729,13 @@
     <t xml:space="preserve">27.6260471343994</t>
   </si>
   <si>
-    <t xml:space="preserve">28.064266204834</t>
+    <t xml:space="preserve">28.0642681121826</t>
   </si>
   <si>
     <t xml:space="preserve">28.283374786377</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8171424865723</t>
+    <t xml:space="preserve">29.8171443939209</t>
   </si>
   <si>
     <t xml:space="preserve">29.5980319976807</t>
@@ -2753,22 +2753,22 @@
     <t xml:space="preserve">30.1092872619629</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9632148742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4014339447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2188415527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2961292266846</t>
+    <t xml:space="preserve">29.9632129669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4014320373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2188396453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2961330413818</t>
   </si>
   <si>
     <t xml:space="preserve">30.8213920593262</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1683158874512</t>
+    <t xml:space="preserve">31.1683139801025</t>
   </si>
   <si>
     <t xml:space="preserve">30.2371006011963</t>
@@ -2789,10 +2789,10 @@
     <t xml:space="preserve">29.7075862884521</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0545101165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8664169311523</t>
+    <t xml:space="preserve">30.0545082092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8664131164551</t>
   </si>
   <si>
     <t xml:space="preserve">34.5462532043457</t>
@@ -2801,19 +2801,19 @@
     <t xml:space="preserve">34.0532608032227</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0855255126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7245903015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6880760192871</t>
+    <t xml:space="preserve">33.085521697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7245941162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6880722045898</t>
   </si>
   <si>
     <t xml:space="preserve">33.5785179138184</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4872283935547</t>
+    <t xml:space="preserve">33.4872245788574</t>
   </si>
   <si>
     <t xml:space="preserve">33.7976303100586</t>
@@ -2822,10 +2822,10 @@
     <t xml:space="preserve">33.1403007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2863731384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2273483276367</t>
+    <t xml:space="preserve">33.286376953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2273445129395</t>
   </si>
   <si>
     <t xml:space="preserve">32.8846740722656</t>
@@ -2837,16 +2837,16 @@
     <t xml:space="preserve">32.6473045349121</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0307502746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7751235961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4099349975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6655654907227</t>
+    <t xml:space="preserve">33.0307464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7751197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4099388122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6655616760254</t>
   </si>
   <si>
     <t xml:space="preserve">34.692325592041</t>
@@ -2858,7 +2858,7 @@
     <t xml:space="preserve">35.2400970458984</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8791656494141</t>
+    <t xml:space="preserve">35.8791694641113</t>
   </si>
   <si>
     <t xml:space="preserve">35.4774703979492</t>
@@ -2873,10 +2873,10 @@
     <t xml:space="preserve">35.7878761291504</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0434989929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.8469047546387</t>
+    <t xml:space="preserve">36.0435066223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8469009399414</t>
   </si>
   <si>
     <t xml:space="preserve">38.9101829528809</t>
@@ -2888,13 +2888,13 @@
     <t xml:space="preserve">39.4944725036621</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3849182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2205848693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1292915344238</t>
+    <t xml:space="preserve">39.3849220275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.220588684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1292953491211</t>
   </si>
   <si>
     <t xml:space="preserve">38.1980781555176</t>
@@ -2903,10 +2903,10 @@
     <t xml:space="preserve">37.6137847900391</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2486038208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0660095214844</t>
+    <t xml:space="preserve">37.2486000061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0660133361816</t>
   </si>
   <si>
     <t xml:space="preserve">37.2668609619141</t>
@@ -2927,13 +2927,13 @@
     <t xml:space="preserve">37.6503067016602</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6235389709473</t>
+    <t xml:space="preserve">35.6235427856445</t>
   </si>
   <si>
     <t xml:space="preserve">33.2315979003906</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9942245483398</t>
+    <t xml:space="preserve">32.9942283630371</t>
   </si>
   <si>
     <t xml:space="preserve">33.3594131469727</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">34.7836227416992</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3819236755371</t>
+    <t xml:space="preserve">34.3819198608398</t>
   </si>
   <si>
     <t xml:space="preserve">34.8931770324707</t>
@@ -2954,7 +2954,7 @@
     <t xml:space="preserve">32.9577102661133</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6332969665527</t>
+    <t xml:space="preserve">33.63330078125</t>
   </si>
   <si>
     <t xml:space="preserve">35.513988494873</t>
@@ -2966,16 +2966,16 @@
     <t xml:space="preserve">36.3173866271973</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6095352172852</t>
+    <t xml:space="preserve">36.6095314025879</t>
   </si>
   <si>
     <t xml:space="preserve">37.7781181335449</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2711143493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2023239135742</t>
+    <t xml:space="preserve">38.271110534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2023315429688</t>
   </si>
   <si>
     <t xml:space="preserve">36.7190933227539</t>
@@ -2990,19 +2990,19 @@
     <t xml:space="preserve">35.1488037109375</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4409484863281</t>
+    <t xml:space="preserve">35.4409523010254</t>
   </si>
   <si>
     <t xml:space="preserve">37.8876724243164</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5267448425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8006286621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6685600280762</t>
+    <t xml:space="preserve">38.526741027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8006324768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6685638427734</t>
   </si>
   <si>
     <t xml:space="preserve">35.4226913452148</t>
@@ -3011,28 +3011,28 @@
     <t xml:space="preserve">35.2583618164062</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9114418029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3636627197266</t>
+    <t xml:space="preserve">34.9114379882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3636589050293</t>
   </si>
   <si>
     <t xml:space="preserve">33.8341484069824</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5967788696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3313941955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2175903320312</t>
+    <t xml:space="preserve">33.5967750549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3313980102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2175941467285</t>
   </si>
   <si>
     <t xml:space="preserve">33.9071846008301</t>
   </si>
   <si>
-    <t xml:space="preserve">35.3131408691406</t>
+    <t xml:space="preserve">35.3131370544434</t>
   </si>
   <si>
     <t xml:space="preserve">34.7105865478516</t>
@@ -3053,16 +3053,16 @@
     <t xml:space="preserve">33.9254455566406</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9437065124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6192893981934</t>
+    <t xml:space="preserve">33.9437026977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6192932128906</t>
   </si>
   <si>
     <t xml:space="preserve">34.5827713012695</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7288475036621</t>
+    <t xml:space="preserve">34.7288513183594</t>
   </si>
   <si>
     <t xml:space="preserve">35.0027313232422</t>
@@ -3071,10 +3071,10 @@
     <t xml:space="preserve">34.8384017944336</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8749160766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5377464294434</t>
+    <t xml:space="preserve">34.8749198913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5377502441406</t>
   </si>
   <si>
     <t xml:space="preserve">32.1725692749023</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">32.1360511779785</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4519596099854</t>
+    <t xml:space="preserve">29.4519577026367</t>
   </si>
   <si>
     <t xml:space="preserve">29.8901805877686</t>
@@ -3092,10 +3092,10 @@
     <t xml:space="preserve">30.1640663146973</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4294490814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1007862091064</t>
+    <t xml:space="preserve">28.4294471740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1007881164551</t>
   </si>
   <si>
     <t xml:space="preserve">27.6808242797852</t>
@@ -3104,7 +3104,7 @@
     <t xml:space="preserve">28.9954814910889</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2693691253662</t>
+    <t xml:space="preserve">29.2693710327148</t>
   </si>
   <si>
     <t xml:space="preserve">28.6850757598877</t>
@@ -3113,7 +3113,7 @@
     <t xml:space="preserve">26.9687194824219</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8956813812256</t>
+    <t xml:space="preserve">26.8956832885742</t>
   </si>
   <si>
     <t xml:space="preserve">27.845157623291</t>
@@ -3158,40 +3158,40 @@
     <t xml:space="preserve">27.4251976013184</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4799747467041</t>
+    <t xml:space="preserve">27.4799766540527</t>
   </si>
   <si>
     <t xml:space="preserve">27.1147937774658</t>
   </si>
   <si>
-    <t xml:space="preserve">26.731351852417</t>
+    <t xml:space="preserve">26.7313537597656</t>
   </si>
   <si>
     <t xml:space="preserve">27.4069385528564</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9912281036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6948299407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4434585571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3113899230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5542640686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7045879364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.097785949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0022392272949</t>
+    <t xml:space="preserve">27.9912300109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6948318481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4434566497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3113918304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5542621612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.70458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0977840423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0022411346436</t>
   </si>
   <si>
     <t xml:space="preserve">21.7466125488281</t>
@@ -3200,19 +3200,19 @@
     <t xml:space="preserve">20.742359161377</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6047897338867</t>
+    <t xml:space="preserve">22.6047916412354</t>
   </si>
   <si>
     <t xml:space="preserve">21.8744239807129</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5134944915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1525650024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2073402404785</t>
+    <t xml:space="preserve">22.5134925842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1525630950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2073421478271</t>
   </si>
   <si>
     <t xml:space="preserve">24.5402565002441</t>
@@ -3221,10 +3221,10 @@
     <t xml:space="preserve">24.6680698394775</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8689212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4489612579346</t>
+    <t xml:space="preserve">24.8689193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4489631652832</t>
   </si>
   <si>
     <t xml:space="preserve">25.2341022491455</t>
@@ -3233,16 +3233,16 @@
     <t xml:space="preserve">24.5585155487061</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0290012359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.138557434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0472621917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3984355926514</t>
+    <t xml:space="preserve">24.0290031433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1385555267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0472602844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3984375</t>
   </si>
   <si>
     <t xml:space="preserve">25.4166946411133</t>
@@ -3254,19 +3254,19 @@
     <t xml:space="preserve">24.0837783813477</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8098907470703</t>
+    <t xml:space="preserve">23.8098926544189</t>
   </si>
   <si>
     <t xml:space="preserve">23.3351535797119</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4221992492676</t>
+    <t xml:space="preserve">22.4221973419189</t>
   </si>
   <si>
     <t xml:space="preserve">22.7326049804688</t>
   </si>
   <si>
-    <t xml:space="preserve">22.677827835083</t>
+    <t xml:space="preserve">22.6778259277344</t>
   </si>
   <si>
     <t xml:space="preserve">22.2761249542236</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">21.9109420776367</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2213459014893</t>
+    <t xml:space="preserve">22.2213478088379</t>
   </si>
   <si>
     <t xml:space="preserve">21.8379077911377</t>
@@ -3296,19 +3296,19 @@
     <t xml:space="preserve">21.9657192230225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1988353729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2718715667725</t>
+    <t xml:space="preserve">21.1988372802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2718734741211</t>
   </si>
   <si>
     <t xml:space="preserve">20.8884315490723</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6875820159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.085033416748</t>
+    <t xml:space="preserve">20.6875839233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0850315093994</t>
   </si>
   <si>
     <t xml:space="preserve">19.3729248046875</t>
@@ -3320,22 +3320,22 @@
     <t xml:space="preserve">19.957218170166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9024391174316</t>
+    <t xml:space="preserve">19.9024410247803</t>
   </si>
   <si>
     <t xml:space="preserve">20.2493629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9614677429199</t>
+    <t xml:space="preserve">20.9614658355713</t>
   </si>
   <si>
     <t xml:space="preserve">20.8519153594971</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7241039276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0162487030029</t>
+    <t xml:space="preserve">20.7241020202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0162467956543</t>
   </si>
   <si>
     <t xml:space="preserve">21.3449096679688</t>
@@ -3359,7 +3359,7 @@
     <t xml:space="preserve">23.6455593109131</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5177459716797</t>
+    <t xml:space="preserve">23.5177478790283</t>
   </si>
   <si>
     <t xml:space="preserve">23.7368564605713</t>
@@ -5349,6 +5349,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.7799997329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.710000038147</t>
   </si>
 </sst>
 </file>
@@ -70791,27 +70794,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6911342593</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
-        <v>187764</v>
+        <v>632204</v>
       </c>
       <c r="C2505" t="n">
         <v>14.789999961853</v>
       </c>
       <c r="D2505" t="n">
+        <v>14.7299995422363</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>14.7799997329712</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1773</v>
+      </c>
+      <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>122645</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>14.7700004577637</v>
+      </c>
+      <c r="D2506" t="n">
         <v>14.7399997711182</v>
       </c>
-      <c r="E2505" t="n">
+      <c r="E2506" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>14.7399997711182</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>1762</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
+        <v>187764</v>
+      </c>
+      <c r="C2507" t="n">
+        <v>14.789999961853</v>
+      </c>
+      <c r="D2507" t="n">
+        <v>14.7399997711182</v>
+      </c>
+      <c r="E2507" t="n">
         <v>14.7600002288818</v>
       </c>
-      <c r="F2505" t="n">
+      <c r="F2507" t="n">
         <v>14.7600002288818</v>
       </c>
-      <c r="G2505" t="s">
+      <c r="G2507" t="s">
         <v>1774</v>
       </c>
-      <c r="H2505" t="s">
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6934143519</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>149191</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>14.6999998092651</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>14.789999961853</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>14.710000038147</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>1779</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TNXT.MI.xlsx
+++ b/data/TNXT.MI.xlsx
@@ -44,16 +44,16 @@
     <t xml:space="preserve">TNXT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65150952339172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59350872039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53550624847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52556347846985</t>
+    <t xml:space="preserve">2.6515097618103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59350848197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53550672531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52556324005127</t>
   </si>
   <si>
     <t xml:space="preserve">2.48579072952271</t>
@@ -71,40 +71,40 @@
     <t xml:space="preserve">2.46921873092651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54047870635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49739146232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47916197776794</t>
+    <t xml:space="preserve">2.54047822952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49739098548889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47916173934937</t>
   </si>
   <si>
     <t xml:space="preserve">2.44436097145081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39464473724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34161448478699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36150097846985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55207872390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58522295951843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6100800037384</t>
+    <t xml:space="preserve">2.39464497566223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34161472320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36150121688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55207848548889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58522272109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61007976531982</t>
   </si>
   <si>
     <t xml:space="preserve">2.56865072250366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63659524917603</t>
+    <t xml:space="preserve">2.63659477233887</t>
   </si>
   <si>
     <t xml:space="preserve">2.68962550163269</t>
@@ -116,82 +116,82 @@
     <t xml:space="preserve">2.72608351707458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77579951286316</t>
+    <t xml:space="preserve">2.77579975128174</t>
   </si>
   <si>
     <t xml:space="preserve">2.58025097846985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56202173233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66808152198792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62830924987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64322400093079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60842275619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.666424036026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65316677093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62665200233459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6929395198822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82551527023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81722974777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90008902549744</t>
+    <t xml:space="preserve">2.5620219707489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66808176040649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62830901145935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64322376251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60842227935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66642427444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65316724777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62665176391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69293975830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82551550865173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81722927093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90008926391602</t>
   </si>
   <si>
     <t xml:space="preserve">2.85865926742554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89843249320984</t>
+    <t xml:space="preserve">2.8984317779541</t>
   </si>
   <si>
     <t xml:space="preserve">2.88351702690125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87523126602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86694550514221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81888699531555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82054376602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85368800163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79237174987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85700225830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90671825408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82882928848267</t>
+    <t xml:space="preserve">2.87523150444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86694502830505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81888675689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82054400444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85368776321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79237151145935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8570020198822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90671801567078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82882976531982</t>
   </si>
   <si>
     <t xml:space="preserve">2.85037350654602</t>
@@ -200,10 +200,10 @@
     <t xml:space="preserve">2.90837526321411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96306276321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95797753334045</t>
+    <t xml:space="preserve">2.96306300163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95797729492188</t>
   </si>
   <si>
     <t xml:space="preserve">2.88169693946838</t>
@@ -215,25 +215,25 @@
     <t xml:space="preserve">2.86474585533142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94950222969055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92407512664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96645283699036</t>
+    <t xml:space="preserve">2.94950151443481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92407488822937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96645307540894</t>
   </si>
   <si>
     <t xml:space="preserve">3.11901307106018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94272112846375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94780707359314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88339185714722</t>
+    <t xml:space="preserve">2.94272136688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94780683517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88339233398438</t>
   </si>
   <si>
     <t xml:space="preserve">2.8732213973999</t>
@@ -245,31 +245,31 @@
     <t xml:space="preserve">3.03256273269653</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07037353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06866312026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06011080741882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99340057373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98484778404236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93524265289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9831371307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9249804019928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92326927185059</t>
+    <t xml:space="preserve">3.07037329673767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06866335868835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06011056900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99340033531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98484802246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93524289131165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98313760757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92497992515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92326951026917</t>
   </si>
   <si>
     <t xml:space="preserve">2.96774291992188</t>
@@ -278,76 +278,76 @@
     <t xml:space="preserve">3.03616333007812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05840015411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05497884750366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08747839927673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13879442214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12853121757507</t>
+    <t xml:space="preserve">3.05839991569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05497908592224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08747863769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13879418373108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12853097915649</t>
   </si>
   <si>
     <t xml:space="preserve">3.19010972976685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1558997631073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12339973449707</t>
+    <t xml:space="preserve">3.15589952468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12339925765991</t>
   </si>
   <si>
     <t xml:space="preserve">3.12511014938354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14734697341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16445207595825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16616249084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24142479896545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30129289627075</t>
+    <t xml:space="preserve">3.14734673500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16445183753967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16616225242615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24142503738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30129265785217</t>
   </si>
   <si>
     <t xml:space="preserve">3.38681888580322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48431801795959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52708101272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62629079818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63655352592468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64510655403137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74602699279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6776065826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71181678771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63484334945679</t>
+    <t xml:space="preserve">3.48431777954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52708077430725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62629103660583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63655376434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64510631561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74602723121643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67760634422302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71181726455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63484358787537</t>
   </si>
   <si>
     <t xml:space="preserve">3.51681780815125</t>
@@ -359,16 +359,16 @@
     <t xml:space="preserve">3.49458122253418</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50655508041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48089718818665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43129181861877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35602951049805</t>
+    <t xml:space="preserve">3.50655484199524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48089694976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43129229545593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35602974891663</t>
   </si>
   <si>
     <t xml:space="preserve">3.60063314437866</t>
@@ -380,79 +380,79 @@
     <t xml:space="preserve">3.69471144676208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69984292984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67589569091797</t>
+    <t xml:space="preserve">3.69984340667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67589592933655</t>
   </si>
   <si>
     <t xml:space="preserve">3.66563296318054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59721231460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63313341140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57497501373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66050124168396</t>
+    <t xml:space="preserve">3.59721207618713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63313269615173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57497549057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66050148010254</t>
   </si>
   <si>
     <t xml:space="preserve">3.68615913391113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71523761749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73747420310974</t>
+    <t xml:space="preserve">3.7152373790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73747444152832</t>
   </si>
   <si>
     <t xml:space="preserve">3.71010589599609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69129085540771</t>
+    <t xml:space="preserve">3.69129061698914</t>
   </si>
   <si>
     <t xml:space="preserve">3.68958020210266</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73234272003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72036910057068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76313233375549</t>
+    <t xml:space="preserve">3.73234248161316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72036838531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76313257217407</t>
   </si>
   <si>
     <t xml:space="preserve">3.77168464660645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62116003036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64168500900269</t>
+    <t xml:space="preserve">3.62116026878357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64168524742126</t>
   </si>
   <si>
     <t xml:space="preserve">3.7032642364502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79734253883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75458002090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90852618217468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76655244827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72892117500305</t>
+    <t xml:space="preserve">3.79734230041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75457978248596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9085259437561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76655220985413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72892141342163</t>
   </si>
   <si>
     <t xml:space="preserve">3.6673436164856</t>
@@ -461,16 +461,16 @@
     <t xml:space="preserve">3.50997591018677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49800252914429</t>
+    <t xml:space="preserve">3.49800229072571</t>
   </si>
   <si>
     <t xml:space="preserve">3.48944973945618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47234463691711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40392446517944</t>
+    <t xml:space="preserve">3.47234487533569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40392398834229</t>
   </si>
   <si>
     <t xml:space="preserve">3.43642401695251</t>
@@ -479,52 +479,52 @@
     <t xml:space="preserve">3.53221273422241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5185284614563</t>
+    <t xml:space="preserve">3.51852822303772</t>
   </si>
   <si>
     <t xml:space="preserve">3.46037101745605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50142312049866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53563332557678</t>
+    <t xml:space="preserve">3.50142335891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53563356399536</t>
   </si>
   <si>
     <t xml:space="preserve">3.55616021156311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64339661598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72550058364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84865832328796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82984232902527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83155250549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87089490890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84523606300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87431573867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86405277252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85721063613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82471060752869</t>
+    <t xml:space="preserve">3.6433961391449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72550082206726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84865736961365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82984209060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83155298233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87089419364929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8452365398407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8743155002594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86405229568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85721015930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82471036911011</t>
   </si>
   <si>
     <t xml:space="preserve">3.90681529045105</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">4.17536640167236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11378717422485</t>
+    <t xml:space="preserve">4.11378765106201</t>
   </si>
   <si>
     <t xml:space="preserve">4.00773572921753</t>
@@ -545,64 +545,64 @@
     <t xml:space="preserve">4.05220890045166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0812873840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00602531433105</t>
+    <t xml:space="preserve">4.08128786087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0060248374939</t>
   </si>
   <si>
     <t xml:space="preserve">4.09839248657227</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01970863342285</t>
+    <t xml:space="preserve">4.01970911026001</t>
   </si>
   <si>
     <t xml:space="preserve">4.01115703582764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99576234817505</t>
+    <t xml:space="preserve">3.99576210975647</t>
   </si>
   <si>
     <t xml:space="preserve">4.03510427474976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06247186660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13773488998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1223406791687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14799737930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18904972076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25918054580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22839260101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20615530014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02141952514648</t>
+    <t xml:space="preserve">4.06247282028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13773441314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12234115600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14799785614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18905019760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2591814994812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22839212417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20615577697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02142000198364</t>
   </si>
   <si>
     <t xml:space="preserve">3.99405169487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01799869537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02655124664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07615613937378</t>
+    <t xml:space="preserve">4.01799821853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02655172348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07615661621094</t>
   </si>
   <si>
     <t xml:space="preserve">4.12747240066528</t>
@@ -614,64 +614,64 @@
     <t xml:space="preserve">4.10523509979248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09668207168579</t>
+    <t xml:space="preserve">4.09668254852295</t>
   </si>
   <si>
     <t xml:space="preserve">4.10181379318237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07102537155151</t>
+    <t xml:space="preserve">4.07102489471436</t>
   </si>
   <si>
     <t xml:space="preserve">4.09497165679932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13089275360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21641826629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52431058883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54996919631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53713893890381</t>
+    <t xml:space="preserve">4.13089227676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21641874313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52431154251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54996871948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53713941574097</t>
   </si>
   <si>
     <t xml:space="preserve">4.46444272994995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5029296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56707429885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62266540527344</t>
+    <t xml:space="preserve">4.50292921066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56707382202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62266635894775</t>
   </si>
   <si>
     <t xml:space="preserve">4.63549518585205</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58417940139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60128402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57562685012817</t>
+    <t xml:space="preserve">4.58417987823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60128450393677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57562637329102</t>
   </si>
   <si>
     <t xml:space="preserve">4.61838912963867</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53286361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55852079391479</t>
+    <t xml:space="preserve">4.53286457061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55852127075195</t>
   </si>
   <si>
     <t xml:space="preserve">4.48154830932617</t>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">4.4901008605957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51148271560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63121795654297</t>
+    <t xml:space="preserve">4.51148223876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63121843338013</t>
   </si>
   <si>
     <t xml:space="preserve">4.78516435623169</t>
@@ -695,31 +695,31 @@
     <t xml:space="preserve">4.7595067024231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78944110870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7338490486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77233600616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76378297805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65687608718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69536256790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82792663574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90062427520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91772985458374</t>
+    <t xml:space="preserve">4.78944063186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73384857177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77233552932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76378440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65687561035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69536209106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8279275894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90062475204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91772937774658</t>
   </si>
   <si>
     <t xml:space="preserve">4.94338750839233</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">5.04174184799194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02035999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07167530059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08022832870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99470281600952</t>
+    <t xml:space="preserve">5.02036094665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07167625427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08022880554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99470376968384</t>
   </si>
   <si>
     <t xml:space="preserve">5.09305667877197</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">5.06050682067871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91728544235229</t>
+    <t xml:space="preserve">4.91728496551514</t>
   </si>
   <si>
     <t xml:space="preserve">4.94766521453857</t>
@@ -758,22 +758,22 @@
     <t xml:space="preserve">4.92596530914307</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9042649269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8218035697937</t>
+    <t xml:space="preserve">4.90426397323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82180404663086</t>
   </si>
   <si>
     <t xml:space="preserve">4.73500299453735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72198247909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59178018569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64386081695557</t>
+    <t xml:space="preserve">4.7219820022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59178066253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64386129379272</t>
   </si>
   <si>
     <t xml:space="preserve">4.73066186904907</t>
@@ -785,16 +785,16 @@
     <t xml:space="preserve">4.65254163742065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60914039611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6568808555603</t>
+    <t xml:space="preserve">4.60914134979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65688180923462</t>
   </si>
   <si>
     <t xml:space="preserve">4.54837989807129</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53535985946655</t>
+    <t xml:space="preserve">4.53536033630371</t>
   </si>
   <si>
     <t xml:space="preserve">4.47025918960571</t>
@@ -803,46 +803,46 @@
     <t xml:space="preserve">4.59612035751343</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47459936141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48761892318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46157884597778</t>
+    <t xml:space="preserve">4.47459888458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48761940002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46157836914062</t>
   </si>
   <si>
     <t xml:space="preserve">4.41383790969849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38779783248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39213800430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40949869155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55706024169922</t>
+    <t xml:space="preserve">4.38779830932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39213848114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40949773788452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55706119537354</t>
   </si>
   <si>
     <t xml:space="preserve">4.52233982086182</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57008075714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53969955444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47893905639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43553924560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42251825332642</t>
+    <t xml:space="preserve">4.57008028030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53970050811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47893953323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43553876876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42251777648926</t>
   </si>
   <si>
     <t xml:space="preserve">4.4311990737915</t>
@@ -851,169 +851,169 @@
     <t xml:space="preserve">4.45289850234985</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51365900039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68726205825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60046100616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63952159881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56140089035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5874400138855</t>
+    <t xml:space="preserve">4.51365947723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6872615814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60046052932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63952112197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56140041351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58744049072266</t>
   </si>
   <si>
     <t xml:space="preserve">4.61782121658325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64820098876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6048002243042</t>
+    <t xml:space="preserve">4.64820146560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60480117797852</t>
   </si>
   <si>
     <t xml:space="preserve">4.58310031890869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49629926681519</t>
+    <t xml:space="preserve">4.49629974365234</t>
   </si>
   <si>
     <t xml:space="preserve">4.50497961044312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42685842514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49195957183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51799869537354</t>
+    <t xml:space="preserve">4.42685890197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49195909500122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51800012588501</t>
   </si>
   <si>
     <t xml:space="preserve">4.80878353118896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77840280532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84784412384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8348240852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74368333816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81312417984009</t>
+    <t xml:space="preserve">4.77840375900269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84784364700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83482456207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74368238449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81312322616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.71330261230469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70462226867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72632312774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69594192504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76972246170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84350442886353</t>
+    <t xml:space="preserve">4.7046217918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72632265090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69594240188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7697229385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84350347518921</t>
   </si>
   <si>
     <t xml:space="preserve">4.87822437286377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8738842010498</t>
+    <t xml:space="preserve">4.87388467788696</t>
   </si>
   <si>
     <t xml:space="preserve">4.97370529174805</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97804546356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00842618942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07786703109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04314613342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14730834960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86086368560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.869544506073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96502542495728</t>
+    <t xml:space="preserve">4.97804594039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00842666625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07786655426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04314708709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14730787277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86086416244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86954498291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96502494812012</t>
   </si>
   <si>
     <t xml:space="preserve">4.90860509872437</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99974584579468</t>
+    <t xml:space="preserve">4.99974679946899</t>
   </si>
   <si>
     <t xml:space="preserve">4.99106597900391</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15598773956299</t>
+    <t xml:space="preserve">5.15598821640015</t>
   </si>
   <si>
     <t xml:space="preserve">5.12994813919067</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2948694229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41639089584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48583221435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43375158309937</t>
+    <t xml:space="preserve">5.29486989974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41639137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48583316802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43375205993652</t>
   </si>
   <si>
     <t xml:space="preserve">5.48149251937866</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42073106765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.394690990448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35563039779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33393049240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37299108505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33827066421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20806932449341</t>
+    <t xml:space="preserve">5.42073202133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39469146728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35563087463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33393096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37299060821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33826971054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20806884765625</t>
   </si>
   <si>
     <t xml:space="preserve">5.16466808319092</t>
@@ -1022,19 +1022,19 @@
     <t xml:space="preserve">5.26449012756348</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25147008895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26014995574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18636894226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20372867584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19504928588867</t>
+    <t xml:space="preserve">5.25146913528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26014947891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18636846542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20372915267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19504833221436</t>
   </si>
   <si>
     <t xml:space="preserve">5.16900873184204</t>
@@ -1043,13 +1043,13 @@
     <t xml:space="preserve">5.18202829360962</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19938898086548</t>
+    <t xml:space="preserve">5.19938802719116</t>
   </si>
   <si>
     <t xml:space="preserve">5.22542905807495</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42507123947144</t>
+    <t xml:space="preserve">5.42507171630859</t>
   </si>
   <si>
     <t xml:space="preserve">5.61603403091431</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">5.71151542663574</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78963661193848</t>
+    <t xml:space="preserve">5.78963613510132</t>
   </si>
   <si>
     <t xml:space="preserve">5.82435703277588</t>
@@ -1070,13 +1070,13 @@
     <t xml:space="preserve">5.87643766403198</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88511753082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93719911575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85907697677612</t>
+    <t xml:space="preserve">5.88511800765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93719863891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85907745361328</t>
   </si>
   <si>
     <t xml:space="preserve">5.80699682235718</t>
@@ -1085,76 +1085,76 @@
     <t xml:space="preserve">5.92851877212524</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97191953659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95455932617188</t>
+    <t xml:space="preserve">5.97191905975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95455837249756</t>
   </si>
   <si>
     <t xml:space="preserve">6.03267955780029</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17156219482422</t>
+    <t xml:space="preserve">6.17156171798706</t>
   </si>
   <si>
     <t xml:space="preserve">6.28440284729004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01531934738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02399969100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21496200561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14552116394043</t>
+    <t xml:space="preserve">6.01531982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02399921417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21496248245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14552164077759</t>
   </si>
   <si>
     <t xml:space="preserve">6.40592479705811</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07608032226562</t>
+    <t xml:space="preserve">6.07607984542847</t>
   </si>
   <si>
     <t xml:space="preserve">5.98927927017212</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04136037826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22364234924316</t>
+    <t xml:space="preserve">6.04135942459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22364139556885</t>
   </si>
   <si>
     <t xml:space="preserve">6.1368408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19760179519653</t>
+    <t xml:space="preserve">6.19760227203369</t>
   </si>
   <si>
     <t xml:space="preserve">6.15420150756836</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05003976821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89379739761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90247821807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70283508300781</t>
+    <t xml:space="preserve">6.05004024505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89379787445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90247774124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70283603668213</t>
   </si>
   <si>
     <t xml:space="preserve">5.50319290161133</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5813136100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72019577026367</t>
+    <t xml:space="preserve">5.58131408691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72019624710083</t>
   </si>
   <si>
     <t xml:space="preserve">5.76359605789185</t>
@@ -1163,43 +1163,43 @@
     <t xml:space="preserve">5.91983842849731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99795913696289</t>
+    <t xml:space="preserve">5.99795961380005</t>
   </si>
   <si>
     <t xml:space="preserve">5.83303689956665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79831600189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6594352722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5118727684021</t>
+    <t xml:space="preserve">5.79831695556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65943479537964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51187229156494</t>
   </si>
   <si>
     <t xml:space="preserve">5.54659366607666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58999395370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52055358886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38167095184326</t>
+    <t xml:space="preserve">5.58999347686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52055263519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38167142868042</t>
   </si>
   <si>
     <t xml:space="preserve">5.44243192672729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46847248077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67679500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64207458496094</t>
+    <t xml:space="preserve">5.46847200393677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6767954826355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64207410812378</t>
   </si>
   <si>
     <t xml:space="preserve">5.55527353286743</t>
@@ -1211,19 +1211,19 @@
     <t xml:space="preserve">5.57263374328613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52923345565796</t>
+    <t xml:space="preserve">5.5292329788208</t>
   </si>
   <si>
     <t xml:space="preserve">5.39903116226196</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39035177230835</t>
+    <t xml:space="preserve">5.39035081863403</t>
   </si>
   <si>
     <t xml:space="preserve">5.45111227035522</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09344100952148</t>
+    <t xml:space="preserve">6.09344053268433</t>
   </si>
   <si>
     <t xml:space="preserve">5.81567668914795</t>
@@ -1235,55 +1235,55 @@
     <t xml:space="preserve">5.73755598068237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40771150588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24278926849365</t>
+    <t xml:space="preserve">5.40771102905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24278974533081</t>
   </si>
   <si>
     <t xml:space="preserve">5.06918716430664</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98238611221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07618808746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1561975479126</t>
+    <t xml:space="preserve">4.98238563537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07618761062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15619802474976</t>
   </si>
   <si>
     <t xml:space="preserve">5.08507776260376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24509859085083</t>
+    <t xml:space="preserve">5.24509716033936</t>
   </si>
   <si>
     <t xml:space="preserve">5.11174774169922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13841772079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20953798294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14730787277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06729793548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0584077835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04062795639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04951763153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94283819198608</t>
+    <t xml:space="preserve">5.13841819763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20953845977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14730739593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06729745864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05840730667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04062843322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04951810836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94283771514893</t>
   </si>
   <si>
     <t xml:space="preserve">4.77392816543579</t>
@@ -1295,28 +1295,28 @@
     <t xml:space="preserve">4.76503801345825</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92505788803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88949823379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02284812927246</t>
+    <t xml:space="preserve">4.92505741119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88949775695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0228476524353</t>
   </si>
   <si>
     <t xml:space="preserve">4.97839736938477</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91616868972778</t>
+    <t xml:space="preserve">4.91616821289062</t>
   </si>
   <si>
     <t xml:space="preserve">4.95172834396362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9339485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89838838577271</t>
+    <t xml:space="preserve">4.93394756317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89838790893555</t>
   </si>
   <si>
     <t xml:space="preserve">4.80948781967163</t>
@@ -1331,34 +1331,34 @@
     <t xml:space="preserve">4.98728799819946</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10285806655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96061849594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20064783096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21842765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27176809310913</t>
+    <t xml:space="preserve">5.10285711288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96061754226685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20064735412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2184271812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27176761627197</t>
   </si>
   <si>
     <t xml:space="preserve">5.33399820327759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23620796203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18286752700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01395845413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99617767333984</t>
+    <t xml:space="preserve">5.23620748519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18286800384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01395797729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.996178150177</t>
   </si>
   <si>
     <t xml:space="preserve">5.00506782531738</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">5.47623777389526</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56513786315918</t>
+    <t xml:space="preserve">5.56513833999634</t>
   </si>
   <si>
     <t xml:space="preserve">5.68070793151855</t>
@@ -1379,25 +1379,25 @@
     <t xml:space="preserve">5.6540379524231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63625764846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55624723434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68959760665894</t>
+    <t xml:space="preserve">5.63625812530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55624771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68959808349609</t>
   </si>
   <si>
     <t xml:space="preserve">5.96518754959106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89406776428223</t>
+    <t xml:space="preserve">5.89406728744507</t>
   </si>
   <si>
     <t xml:space="preserve">5.77849769592285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84072732925415</t>
+    <t xml:space="preserve">5.84072780609131</t>
   </si>
   <si>
     <t xml:space="preserve">5.76071786880493</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">5.83183765411377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4495677947998</t>
+    <t xml:space="preserve">5.44956731796265</t>
   </si>
   <si>
     <t xml:space="preserve">5.5829176902771</t>
@@ -1421,37 +1421,37 @@
     <t xml:space="preserve">5.36955785751343</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6095871925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86739730834961</t>
+    <t xml:space="preserve">5.60958766937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86739778518677</t>
   </si>
   <si>
     <t xml:space="preserve">5.78738784790039</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5206880569458</t>
+    <t xml:space="preserve">5.52068853378296</t>
   </si>
   <si>
     <t xml:space="preserve">5.49401760101318</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57402753829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59180736541748</t>
+    <t xml:space="preserve">5.57402801513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59180784225464</t>
   </si>
   <si>
     <t xml:space="preserve">5.64514780044556</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71626710891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73404741287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81405782699585</t>
+    <t xml:space="preserve">5.71626758575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73404788970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81405830383301</t>
   </si>
   <si>
     <t xml:space="preserve">5.67181825637817</t>
@@ -1460,16 +1460,16 @@
     <t xml:space="preserve">5.51179790496826</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85850763320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66292762756348</t>
+    <t xml:space="preserve">5.85850858688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66292810440063</t>
   </si>
   <si>
     <t xml:space="preserve">5.53846788406372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90295743942261</t>
+    <t xml:space="preserve">5.90295791625977</t>
   </si>
   <si>
     <t xml:space="preserve">5.79627752304077</t>
@@ -1478,19 +1478,19 @@
     <t xml:space="preserve">5.80516815185547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6184778213501</t>
+    <t xml:space="preserve">5.61847829818726</t>
   </si>
   <si>
     <t xml:space="preserve">5.46734762191772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60069751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45845794677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50290775299072</t>
+    <t xml:space="preserve">5.60069799423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45845699310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50290727615356</t>
   </si>
   <si>
     <t xml:space="preserve">5.34288787841797</t>
@@ -1499,10 +1499,10 @@
     <t xml:space="preserve">5.62736749649048</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52957725524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42289733886719</t>
+    <t xml:space="preserve">5.52957773208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42289781570435</t>
   </si>
   <si>
     <t xml:space="preserve">5.72515773773193</t>
@@ -1514,64 +1514,64 @@
     <t xml:space="preserve">5.69848775863647</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0007472038269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92962789535522</t>
+    <t xml:space="preserve">6.00074815750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92962741851807</t>
   </si>
   <si>
     <t xml:space="preserve">5.94740772247314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93851709365845</t>
+    <t xml:space="preserve">5.93851757049561</t>
   </si>
   <si>
     <t xml:space="preserve">5.99185705184937</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24077749252319</t>
+    <t xml:space="preserve">6.24077796936035</t>
   </si>
   <si>
     <t xml:space="preserve">6.40968704223633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48080730438232</t>
+    <t xml:space="preserve">6.48080778121948</t>
   </si>
   <si>
     <t xml:space="preserve">6.62304735183716</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84529638290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99642705917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01420736312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90752744674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91641759872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97864723205566</t>
+    <t xml:space="preserve">6.84529733657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99642658233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0142068862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90752696990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91641712188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97864675521851</t>
   </si>
   <si>
     <t xml:space="preserve">7.00531721115112</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02309703826904</t>
+    <t xml:space="preserve">7.0230975151062</t>
   </si>
   <si>
     <t xml:space="preserve">7.24534702301025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27201747894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33424663543701</t>
+    <t xml:space="preserve">7.27201700210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33424711227417</t>
   </si>
   <si>
     <t xml:space="preserve">7.476487159729</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">7.7342963218689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72540712356567</t>
+    <t xml:space="preserve">7.72540664672852</t>
   </si>
   <si>
     <t xml:space="preserve">7.79652643203735</t>
@@ -1592,31 +1592,31 @@
     <t xml:space="preserve">7.80541610717773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22324752807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21435546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15212726593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12545776367188</t>
+    <t xml:space="preserve">8.22324562072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21435642242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15212631225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12545680999756</t>
   </si>
   <si>
     <t xml:space="preserve">8.00099754333496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17879772186279</t>
+    <t xml:space="preserve">8.17879676818848</t>
   </si>
   <si>
     <t xml:space="preserve">8.34770774841309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42771530151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48105621337891</t>
+    <t xml:space="preserve">8.4277172088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48105525970459</t>
   </si>
   <si>
     <t xml:space="preserve">8.46327686309814</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.50772571563721</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66774463653564</t>
+    <t xml:space="preserve">8.66774559020996</t>
   </si>
   <si>
     <t xml:space="preserve">8.8010950088501</t>
@@ -1637,82 +1637,82 @@
     <t xml:space="preserve">8.88999652862549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19225597381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37005519866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47673606872559</t>
+    <t xml:space="preserve">9.1922550201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37005615234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47673511505127</t>
   </si>
   <si>
     <t xml:space="preserve">9.49451637268066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31671524047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15669631958008</t>
+    <t xml:space="preserve">9.31671619415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15669536590576</t>
   </si>
   <si>
     <t xml:space="preserve">9.35227680206299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40561580657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69009494781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86789703369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83233737945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77899646759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44117546081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21003532409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58341503143311</t>
+    <t xml:space="preserve">9.40561676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69009590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86789512634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83233642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77899551391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44117450714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21003723144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58341598510742</t>
   </si>
   <si>
     <t xml:space="preserve">9.51229572296143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6723165512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85011577606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0990352630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0279169082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99235534667969</t>
+    <t xml:space="preserve">9.67231559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8501148223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0990362167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0279159545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.992356300354</t>
   </si>
   <si>
     <t xml:space="preserve">10.0101356506348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76121616363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88567638397217</t>
+    <t xml:space="preserve">9.76121520996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88567543029785</t>
   </si>
   <si>
     <t xml:space="preserve">10.2234954833984</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4368553161621</t>
+    <t xml:space="preserve">10.4368543624878</t>
   </si>
   <si>
     <t xml:space="preserve">10.6679964065552</t>
@@ -1727,25 +1727,25 @@
     <t xml:space="preserve">11.3080759048462</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4325342178345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6814546585083</t>
+    <t xml:space="preserve">11.4325351715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6814556121826</t>
   </si>
   <si>
     <t xml:space="preserve">11.8948154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">11.965934753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1437358856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6281156539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4001121520996</t>
+    <t xml:space="preserve">11.9659357070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1437349319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.628116607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4001131057739</t>
   </si>
   <si>
     <t xml:space="preserve">11.6715440750122</t>
@@ -1757,10 +1757,10 @@
     <t xml:space="preserve">11.689640045166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.123929977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7982130050659</t>
+    <t xml:space="preserve">12.1239290237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7982120513916</t>
   </si>
   <si>
     <t xml:space="preserve">12.1782159805298</t>
@@ -1772,22 +1772,22 @@
     <t xml:space="preserve">12.9925088882446</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8296508789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7391748428345</t>
+    <t xml:space="preserve">12.8296518325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7391729354858</t>
   </si>
   <si>
     <t xml:space="preserve">12.7753639221191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3953619003296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2867879867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6306018829346</t>
+    <t xml:space="preserve">12.3953609466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2867889404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6306009292603</t>
   </si>
   <si>
     <t xml:space="preserve">12.4496479034424</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">12.2144069671631</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1058340072632</t>
+    <t xml:space="preserve">12.1058349609375</t>
   </si>
   <si>
     <t xml:space="preserve">11.8705930709839</t>
@@ -1805,19 +1805,19 @@
     <t xml:space="preserve">11.9067850112915</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4724941253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4182081222534</t>
+    <t xml:space="preserve">11.4724950790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4182090759277</t>
   </si>
   <si>
     <t xml:space="preserve">11.5810670852661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.852499961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0877389907837</t>
+    <t xml:space="preserve">11.8524990081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0877380371094</t>
   </si>
   <si>
     <t xml:space="preserve">11.8344030380249</t>
@@ -1832,22 +1832,22 @@
     <t xml:space="preserve">11.3277320861816</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734460830688</t>
+    <t xml:space="preserve">11.2734451293945</t>
   </si>
   <si>
     <t xml:space="preserve">11.1829681396484</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1648721694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8391542434692</t>
+    <t xml:space="preserve">11.1648731231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8391551971436</t>
   </si>
   <si>
     <t xml:space="preserve">10.6401052474976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6762971878052</t>
+    <t xml:space="preserve">10.6762962341309</t>
   </si>
   <si>
     <t xml:space="preserve">10.5134372711182</t>
@@ -1856,16 +1856,16 @@
     <t xml:space="preserve">10.9115381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2915391921997</t>
+    <t xml:space="preserve">11.291540145874</t>
   </si>
   <si>
     <t xml:space="preserve">11.1467771530151</t>
   </si>
   <si>
-    <t xml:space="preserve">10.766773223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1105852127075</t>
+    <t xml:space="preserve">10.7667722702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1105871200562</t>
   </si>
   <si>
     <t xml:space="preserve">11.1286821365356</t>
@@ -1883,19 +1883,19 @@
     <t xml:space="preserve">10.4953422546387</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2781972885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3143873214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.898193359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9343843460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80771827697754</t>
+    <t xml:space="preserve">10.2781963348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3143882751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89819240570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93438339233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80771636962891</t>
   </si>
   <si>
     <t xml:space="preserve">9.6810474395752</t>
@@ -1910,40 +1910,40 @@
     <t xml:space="preserve">10.4772462844849</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3867702484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4410552978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55438041687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1153383255005</t>
+    <t xml:space="preserve">10.3867692947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4410562515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55438137054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1153392791748</t>
   </si>
   <si>
     <t xml:space="preserve">10.3505783081055</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4048652648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7486791610718</t>
+    <t xml:space="preserve">10.4048643112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7486782073975</t>
   </si>
   <si>
     <t xml:space="preserve">11.0201091766357</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8572511672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8753471374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5858182907104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8029642105103</t>
+    <t xml:space="preserve">10.857250213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8753461837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5858192443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8029632568359</t>
   </si>
   <si>
     <t xml:space="preserve">10.7124872207642</t>
@@ -1952,28 +1952,28 @@
     <t xml:space="preserve">10.7848691940308</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2372550964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3096342086792</t>
+    <t xml:space="preserve">11.2372541427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3096361160278</t>
   </si>
   <si>
     <t xml:space="preserve">11.4543991088867</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7258310317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9972620010376</t>
+    <t xml:space="preserve">11.725830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9972610473633</t>
   </si>
   <si>
     <t xml:space="preserve">12.160120010376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0515470504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0334529876709</t>
+    <t xml:space="preserve">12.0515480041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0334520339966</t>
   </si>
   <si>
     <t xml:space="preserve">11.9429750442505</t>
@@ -1985,10 +1985,10 @@
     <t xml:space="preserve">10.9477281570435</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9658241271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1877202987671</t>
+    <t xml:space="preserve">10.9658231735229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1877212524414</t>
   </si>
   <si>
     <t xml:space="preserve">9.98867034912109</t>
@@ -1997,13 +1997,13 @@
     <t xml:space="preserve">10.0429573059082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91628932952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.169623374939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5315322875977</t>
+    <t xml:space="preserve">9.91628837585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1696243286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.531533241272</t>
   </si>
   <si>
     <t xml:space="preserve">10.4229602813721</t>
@@ -2012,22 +2012,22 @@
     <t xml:space="preserve">10.13343334198</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3324842453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2239112854004</t>
+    <t xml:space="preserve">10.332483291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2239122390747</t>
   </si>
   <si>
     <t xml:space="preserve">10.097243309021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0610523223877</t>
+    <t xml:space="preserve">10.0610513687134</t>
   </si>
   <si>
     <t xml:space="preserve">10.0791482925415</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1515293121338</t>
+    <t xml:space="preserve">10.1515302658081</t>
   </si>
   <si>
     <t xml:space="preserve">11.056300163269</t>
@@ -2036,13 +2036,13 @@
     <t xml:space="preserve">10.8934412002563</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5496282577515</t>
+    <t xml:space="preserve">10.5496273040771</t>
   </si>
   <si>
     <t xml:space="preserve">10.3686742782593</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8258113861084</t>
+    <t xml:space="preserve">9.82581043243408</t>
   </si>
   <si>
     <t xml:space="preserve">9.77152538299561</t>
@@ -2051,7 +2051,7 @@
     <t xml:space="preserve">9.699143409729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51819038391113</t>
+    <t xml:space="preserve">9.51819133758545</t>
   </si>
   <si>
     <t xml:space="preserve">9.71723937988281</t>
@@ -2060,22 +2060,22 @@
     <t xml:space="preserve">9.42771244049072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5905704498291</t>
+    <t xml:space="preserve">9.59057235717773</t>
   </si>
   <si>
     <t xml:space="preserve">11.3639221191406</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9791660308838</t>
+    <t xml:space="preserve">11.9791669845581</t>
   </si>
   <si>
     <t xml:space="preserve">12.4677419662476</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3772668838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3820171356201</t>
+    <t xml:space="preserve">12.3772659301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3820180892944</t>
   </si>
   <si>
     <t xml:space="preserve">11.5629720687866</t>
@@ -2087,13 +2087,13 @@
     <t xml:space="preserve">11.0924911499023</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6943922042847</t>
+    <t xml:space="preserve">10.6943912506104</t>
   </si>
   <si>
     <t xml:space="preserve">9.62676239013672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80341911315918</t>
+    <t xml:space="preserve">8.8034200668335</t>
   </si>
   <si>
     <t xml:space="preserve">8.68580055236816</t>
@@ -2102,40 +2102,40 @@
     <t xml:space="preserve">8.43246364593506</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04816579818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32864475250244</t>
+    <t xml:space="preserve">7.0481653213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32864427566528</t>
   </si>
   <si>
     <t xml:space="preserve">7.24721527099609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1838812828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58673191070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65006589889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96673488616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97578287124634</t>
+    <t xml:space="preserve">7.18388080596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58673286437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65006637573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96673583984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9757833480835</t>
   </si>
   <si>
     <t xml:space="preserve">7.16578531265259</t>
   </si>
   <si>
-    <t xml:space="preserve">7.057213306427</t>
+    <t xml:space="preserve">7.05721282958984</t>
   </si>
   <si>
     <t xml:space="preserve">7.28340578079224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60912370681763</t>
+    <t xml:space="preserve">7.60912227630615</t>
   </si>
   <si>
     <t xml:space="preserve">7.76293468475342</t>
@@ -2147,19 +2147,19 @@
     <t xml:space="preserve">8.04341316223145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61341953277588</t>
+    <t xml:space="preserve">8.61341857910156</t>
   </si>
   <si>
     <t xml:space="preserve">8.41436958312988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25151062011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93008804321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35533142089844</t>
+    <t xml:space="preserve">8.25150966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93008899688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35533046722412</t>
   </si>
   <si>
     <t xml:space="preserve">9.04770946502686</t>
@@ -2171,31 +2171,31 @@
     <t xml:space="preserve">9.50009441375732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8620023727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2191591262817</t>
+    <t xml:space="preserve">9.86200141906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2191581726074</t>
   </si>
   <si>
     <t xml:space="preserve">10.9839191436768</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6582021713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97057628631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2058153152466</t>
+    <t xml:space="preserve">10.6582012176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9705753326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2058143615723</t>
   </si>
   <si>
     <t xml:space="preserve">9.84390735626221</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4591503143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9296321868896</t>
+    <t xml:space="preserve">10.4591512680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9296312332153</t>
   </si>
   <si>
     <t xml:space="preserve">10.7305822372437</t>
@@ -2204,16 +2204,16 @@
     <t xml:space="preserve">10.8210601806641</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0696430206299</t>
+    <t xml:space="preserve">12.0696439743042</t>
   </si>
   <si>
     <t xml:space="preserve">12.558219909668</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8477468490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1915578842163</t>
+    <t xml:space="preserve">12.8477458953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1915588378906</t>
   </si>
   <si>
     <t xml:space="preserve">12.757269859314</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">12.4315519332886</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5944108963013</t>
+    <t xml:space="preserve">12.594409942627</t>
   </si>
   <si>
     <t xml:space="preserve">12.6486968994141</t>
@@ -2234,13 +2234,13 @@
     <t xml:space="preserve">12.7210788726807</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8658418655396</t>
+    <t xml:space="preserve">12.8658428192139</t>
   </si>
   <si>
     <t xml:space="preserve">13.1553688049316</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0287008285522</t>
+    <t xml:space="preserve">13.0286998748779</t>
   </si>
   <si>
     <t xml:space="preserve">13.1191778182983</t>
@@ -2249,28 +2249,28 @@
     <t xml:space="preserve">12.9382238388062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0829858779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3725137710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3544178009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4534864425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.249683380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2858772277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3763542175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6477851867676</t>
+    <t xml:space="preserve">13.0829877853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3725128173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3544187545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4534873962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2496852874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2858753204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3763523101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6477832794189</t>
   </si>
   <si>
     <t xml:space="preserve">15.8334894180298</t>
@@ -2279,16 +2279,16 @@
     <t xml:space="preserve">16.0687313079834</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8696813583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9239673614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9058704376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8515863418579</t>
+    <t xml:space="preserve">15.8696804046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9239692687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9058713912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8515872955322</t>
   </si>
   <si>
     <t xml:space="preserve">16.0144443511963</t>
@@ -2297,70 +2297,70 @@
     <t xml:space="preserve">15.7972984313965</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2677822113037</t>
+    <t xml:space="preserve">16.2677803039551</t>
   </si>
   <si>
     <t xml:space="preserve">16.0325393676758</t>
   </si>
   <si>
-    <t xml:space="preserve">15.779203414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7249174118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4125442504883</t>
+    <t xml:space="preserve">15.7792043685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7249183654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4125423431396</t>
   </si>
   <si>
     <t xml:space="preserve">15.8153944015503</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9420614242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6344413757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1049213409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9601564407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6887273788452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6163454055786</t>
+    <t xml:space="preserve">15.9420623779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6344404220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.104923248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9601583480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6887264251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6163463592529</t>
   </si>
   <si>
     <t xml:space="preserve">14.8925275802612</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6525354385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3630084991455</t>
+    <t xml:space="preserve">15.6525344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3630075454712</t>
   </si>
   <si>
     <t xml:space="preserve">15.4896793365479</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1458654403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0372943878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7430114746094</t>
+    <t xml:space="preserve">15.1458644866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0372915267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7430124282837</t>
   </si>
   <si>
     <t xml:space="preserve">14.8201465606689</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2906265258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5887451171875</t>
+    <t xml:space="preserve">15.2906274795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5887470245361</t>
   </si>
   <si>
     <t xml:space="preserve">17.7696990966797</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">19.1359043121338</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2763729095459</t>
+    <t xml:space="preserve">18.2763710021973</t>
   </si>
   <si>
     <t xml:space="preserve">18.0411319732666</t>
@@ -2381,25 +2381,25 @@
     <t xml:space="preserve">17.4258880615234</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7335109710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2992172241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0458831787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0277881622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7020702362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.009693145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4077892303467</t>
+    <t xml:space="preserve">17.7335090637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2992191314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0458850860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0277862548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7020683288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0096893310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4077930450439</t>
   </si>
   <si>
     <t xml:space="preserve">18.5025653839111</t>
@@ -2408,10 +2408,10 @@
     <t xml:space="preserve">18.1406555175781</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9687519073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4982681274414</t>
+    <t xml:space="preserve">17.96875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.49827003479</t>
   </si>
   <si>
     <t xml:space="preserve">17.9868450164795</t>
@@ -2420,28 +2420,28 @@
     <t xml:space="preserve">18.5930404663086</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1544551849365</t>
+    <t xml:space="preserve">17.1544532775879</t>
   </si>
   <si>
     <t xml:space="preserve">17.2449321746826</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1182651519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8106441497803</t>
+    <t xml:space="preserve">17.1182670593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8106422424316</t>
   </si>
   <si>
     <t xml:space="preserve">16.8287391662598</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9735012054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9192161560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0639781951904</t>
+    <t xml:space="preserve">16.973503112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9192180633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0639801025391</t>
   </si>
   <si>
     <t xml:space="preserve">16.8468341827393</t>
@@ -2453,31 +2453,31 @@
     <t xml:space="preserve">17.3173141479492</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2087440490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2268390655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3668479919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4573249816895</t>
+    <t xml:space="preserve">17.2087421417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2268371582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.366849899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4573268890381</t>
   </si>
   <si>
     <t xml:space="preserve">18.6382789611816</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7287578582764</t>
+    <t xml:space="preserve">18.7287559509277</t>
   </si>
   <si>
     <t xml:space="preserve">18.9549503326416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8644752502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6335315704346</t>
+    <t xml:space="preserve">18.8644733428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6335296630859</t>
   </si>
   <si>
     <t xml:space="preserve">19.6787662506104</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">19.5430507659912</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0454273223877</t>
+    <t xml:space="preserve">19.0454254150391</t>
   </si>
   <si>
     <t xml:space="preserve">19.0001888275146</t>
@@ -2498,13 +2498,13 @@
     <t xml:space="preserve">18.3216094970703</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2311305999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0906677246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6835193634033</t>
+    <t xml:space="preserve">18.2311325073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0906658172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6835155487061</t>
   </si>
   <si>
     <t xml:space="preserve">18.0954189300537</t>
@@ -2513,22 +2513,22 @@
     <t xml:space="preserve">18.004940032959</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5706520080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8239841461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.643030166626</t>
+    <t xml:space="preserve">17.570650100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8239860534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6430320739746</t>
   </si>
   <si>
     <t xml:space="preserve">17.8058910369873</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2716197967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1811408996582</t>
+    <t xml:space="preserve">19.2716178894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1811447143555</t>
   </si>
   <si>
     <t xml:space="preserve">20.26686668396</t>
@@ -2543,19 +2543,19 @@
     <t xml:space="preserve">20.5835380554199</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3573474884033</t>
+    <t xml:space="preserve">20.3573436737061</t>
   </si>
   <si>
     <t xml:space="preserve">19.9049587249756</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7692432403564</t>
+    <t xml:space="preserve">19.7692451477051</t>
   </si>
   <si>
     <t xml:space="preserve">20.7192516326904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9954376220703</t>
+    <t xml:space="preserve">19.9954357147217</t>
   </si>
   <si>
     <t xml:space="preserve">19.2263832092285</t>
@@ -2564,13 +2564,13 @@
     <t xml:space="preserve">19.4525737762451</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4073371887207</t>
+    <t xml:space="preserve">19.4073352813721</t>
   </si>
   <si>
     <t xml:space="preserve">17.6249370574951</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7877941131592</t>
+    <t xml:space="preserve">17.7877960205078</t>
   </si>
   <si>
     <t xml:space="preserve">19.4978103637695</t>
@@ -2579,10 +2579,10 @@
     <t xml:space="preserve">20.0859146118164</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1311492919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8597202301025</t>
+    <t xml:space="preserve">20.1311511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8597221374512</t>
   </si>
   <si>
     <t xml:space="preserve">20.674015045166</t>
@@ -2591,28 +2591,28 @@
     <t xml:space="preserve">21.0359230041504</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8097305297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6287746429443</t>
+    <t xml:space="preserve">20.8097286224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.628776550293</t>
   </si>
   <si>
     <t xml:space="preserve">20.312105178833</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4478225708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8821105957031</t>
+    <t xml:space="preserve">20.4478244781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8821125030518</t>
   </si>
   <si>
     <t xml:space="preserve">21.2802104949951</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3344993591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.587833404541</t>
+    <t xml:space="preserve">21.3344974517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5878353118896</t>
   </si>
   <si>
     <t xml:space="preserve">21.6602153778076</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">22.1668872833252</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6192684173584</t>
+    <t xml:space="preserve">22.6192722320557</t>
   </si>
   <si>
     <t xml:space="preserve">22.8726081848145</t>
@@ -2630,10 +2630,10 @@
     <t xml:space="preserve">23.9040470123291</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7821311950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8592643737793</t>
+    <t xml:space="preserve">22.7821292877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8592624664307</t>
   </si>
   <si>
     <t xml:space="preserve">22.0040264129639</t>
@@ -2642,16 +2642,16 @@
     <t xml:space="preserve">22.2573642730713</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4745101928711</t>
+    <t xml:space="preserve">22.4745082855225</t>
   </si>
   <si>
     <t xml:space="preserve">22.1126003265381</t>
   </si>
   <si>
-    <t xml:space="preserve">22.058313369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6011753082275</t>
+    <t xml:space="preserve">22.0583114624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6011772155762</t>
   </si>
   <si>
     <t xml:space="preserve">22.6373672485352</t>
@@ -2660,67 +2660,67 @@
     <t xml:space="preserve">22.4202213287354</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4021263122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3525943756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.262113571167</t>
+    <t xml:space="preserve">22.4021282196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3525924682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2621173858643</t>
   </si>
   <si>
     <t xml:space="preserve">22.0945053100586</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5830783843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0354671478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0173740386963</t>
+    <t xml:space="preserve">22.583080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0354652404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0173721313477</t>
   </si>
   <si>
     <t xml:space="preserve">23.3611831665039</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2707061767578</t>
+    <t xml:space="preserve">23.2707080841064</t>
   </si>
   <si>
     <t xml:space="preserve">25.0440578460693</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7726268768311</t>
+    <t xml:space="preserve">24.7726249694824</t>
   </si>
   <si>
     <t xml:space="preserve">24.9716777801514</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0621547698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9126377105713</t>
+    <t xml:space="preserve">25.0621528625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9126358032227</t>
   </si>
   <si>
     <t xml:space="preserve">26.2383556365967</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6765747070312</t>
+    <t xml:space="preserve">26.6765727996826</t>
   </si>
   <si>
     <t xml:space="preserve">26.7130928039551</t>
   </si>
   <si>
-    <t xml:space="preserve">26.585277557373</t>
+    <t xml:space="preserve">26.5852794647217</t>
   </si>
   <si>
     <t xml:space="preserve">26.6583156585693</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8226451873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.95046043396</t>
+    <t xml:space="preserve">26.8226470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9504623413086</t>
   </si>
   <si>
     <t xml:space="preserve">27.5712699890137</t>
@@ -2732,13 +2732,13 @@
     <t xml:space="preserve">28.064266204834</t>
   </si>
   <si>
-    <t xml:space="preserve">28.283374786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8171405792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.598030090332</t>
+    <t xml:space="preserve">28.2833766937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8171443939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5980319976807</t>
   </si>
   <si>
     <t xml:space="preserve">28.958963394165</t>
@@ -2750,13 +2750,13 @@
     <t xml:space="preserve">29.652811050415</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1092891693115</t>
+    <t xml:space="preserve">30.1092910766602</t>
   </si>
   <si>
     <t xml:space="preserve">29.9632148742676</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4014320373535</t>
+    <t xml:space="preserve">30.4014358520508</t>
   </si>
   <si>
     <t xml:space="preserve">30.2188396453857</t>
@@ -2765,34 +2765,34 @@
     <t xml:space="preserve">31.2961292266846</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8213920593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1683177947998</t>
+    <t xml:space="preserve">30.8213901519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1683197021484</t>
   </si>
   <si>
     <t xml:space="preserve">30.2371006011963</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4154434204102</t>
+    <t xml:space="preserve">29.4154415130615</t>
   </si>
   <si>
     <t xml:space="preserve">29.8536605834961</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1780738830566</t>
+    <t xml:space="preserve">29.178071975708</t>
   </si>
   <si>
     <t xml:space="preserve">30.1458072662354</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7075862884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0545082092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8664169311523</t>
+    <t xml:space="preserve">29.7075881958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0545101165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8664131164551</t>
   </si>
   <si>
     <t xml:space="preserve">34.5462532043457</t>
@@ -2813,13 +2813,13 @@
     <t xml:space="preserve">33.5785179138184</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4872283935547</t>
+    <t xml:space="preserve">33.4872245788574</t>
   </si>
   <si>
     <t xml:space="preserve">33.7976303100586</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1403007507324</t>
+    <t xml:space="preserve">33.1402969360352</t>
   </si>
   <si>
     <t xml:space="preserve">33.2863731384277</t>
@@ -2837,28 +2837,28 @@
     <t xml:space="preserve">32.6473045349121</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0307464599609</t>
+    <t xml:space="preserve">33.0307502746582</t>
   </si>
   <si>
     <t xml:space="preserve">32.7751235961914</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4099388122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6655616760254</t>
+    <t xml:space="preserve">32.4099349975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6655654907227</t>
   </si>
   <si>
     <t xml:space="preserve">34.6923294067383</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6052780151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2400970458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8791694641113</t>
+    <t xml:space="preserve">35.605281829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2401008605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8791656494141</t>
   </si>
   <si>
     <t xml:space="preserve">35.4774703979492</t>
@@ -2873,10 +2873,10 @@
     <t xml:space="preserve">35.7878761291504</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0434989929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.8469009399414</t>
+    <t xml:space="preserve">36.0435028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8469085693359</t>
   </si>
   <si>
     <t xml:space="preserve">38.9101829528809</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">38.4354476928711</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4944725036621</t>
+    <t xml:space="preserve">39.4944763183594</t>
   </si>
   <si>
     <t xml:space="preserve">39.3849182128906</t>
@@ -2894,49 +2894,49 @@
     <t xml:space="preserve">39.220588684082</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1292915344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1980781555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6137847900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2486038208008</t>
+    <t xml:space="preserve">39.1292953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1980743408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6137886047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.248607635498</t>
   </si>
   <si>
     <t xml:space="preserve">37.0660095214844</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2668609619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7008285522461</t>
+    <t xml:space="preserve">37.2668647766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7008323669434</t>
   </si>
   <si>
     <t xml:space="preserve">37.2120819091797</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5590057373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0154838562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6503105163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6235427856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2316017150879</t>
+    <t xml:space="preserve">37.559009552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0154876708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6503028869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6235389709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2315979003906</t>
   </si>
   <si>
     <t xml:space="preserve">32.9942245483398</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3594093322754</t>
+    <t xml:space="preserve">33.3594169616699</t>
   </si>
   <si>
     <t xml:space="preserve">33.0490074157715</t>
@@ -2948,25 +2948,25 @@
     <t xml:space="preserve">34.3819236755371</t>
   </si>
   <si>
-    <t xml:space="preserve">34.893180847168</t>
+    <t xml:space="preserve">34.8931770324707</t>
   </si>
   <si>
     <t xml:space="preserve">32.9577102661133</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6332969665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5139923095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4817199707031</t>
+    <t xml:space="preserve">33.63330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.513988494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4817161560059</t>
   </si>
   <si>
     <t xml:space="preserve">36.3173866271973</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6095352172852</t>
+    <t xml:space="preserve">36.6095314025879</t>
   </si>
   <si>
     <t xml:space="preserve">37.7781181335449</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">38.2711143493652</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2023315429688</t>
+    <t xml:space="preserve">39.2023277282715</t>
   </si>
   <si>
     <t xml:space="preserve">36.7190895080566</t>
@@ -2987,7 +2987,7 @@
     <t xml:space="preserve">34.9662132263184</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1488075256348</t>
+    <t xml:space="preserve">35.1488037109375</t>
   </si>
   <si>
     <t xml:space="preserve">35.4409523010254</t>
@@ -2999,10 +2999,10 @@
     <t xml:space="preserve">38.5267448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8006324768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6685600280762</t>
+    <t xml:space="preserve">38.8006248474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6685638427734</t>
   </si>
   <si>
     <t xml:space="preserve">35.4226913452148</t>
@@ -3011,34 +3011,34 @@
     <t xml:space="preserve">35.258358001709</t>
   </si>
   <si>
-    <t xml:space="preserve">34.911434173584</t>
+    <t xml:space="preserve">34.9114379882812</t>
   </si>
   <si>
     <t xml:space="preserve">34.3636627197266</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8341484069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5967826843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3313941955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2175941467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9071846008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3131370544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7105865478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.345401763916</t>
+    <t xml:space="preserve">33.8341522216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5967788696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3313980102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2175903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9071807861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3131332397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7105827331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3454055786133</t>
   </si>
   <si>
     <t xml:space="preserve">34.0715179443359</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">33.1950798034668</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6150360107422</t>
+    <t xml:space="preserve">33.6150436401367</t>
   </si>
   <si>
     <t xml:space="preserve">33.9254455566406</t>
@@ -3059,40 +3059,40 @@
     <t xml:space="preserve">34.6192893981934</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5827713012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7288475036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0027351379395</t>
+    <t xml:space="preserve">34.5827751159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7288436889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0027313232422</t>
   </si>
   <si>
     <t xml:space="preserve">34.8384017944336</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8749160766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5377464294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1725654602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1360511779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4519577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8901786804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1640682220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4294490814209</t>
+    <t xml:space="preserve">34.8749198913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5377502441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1725730895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1360473632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4519596099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8901805877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1640644073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4294471740723</t>
   </si>
   <si>
     <t xml:space="preserve">28.1007843017578</t>
@@ -3107,13 +3107,13 @@
     <t xml:space="preserve">29.2693691253662</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6850776672363</t>
+    <t xml:space="preserve">28.6850757598877</t>
   </si>
   <si>
     <t xml:space="preserve">26.9687213897705</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8956832885742</t>
+    <t xml:space="preserve">26.8956813812256</t>
   </si>
   <si>
     <t xml:space="preserve">27.8451557159424</t>
@@ -3125,7 +3125,7 @@
     <t xml:space="preserve">28.6668186187744</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1232948303223</t>
+    <t xml:space="preserve">29.1232967376709</t>
   </si>
   <si>
     <t xml:space="preserve">28.9224452972412</t>
@@ -3134,13 +3134,13 @@
     <t xml:space="preserve">27.6077880859375</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7538604736328</t>
+    <t xml:space="preserve">27.7538623809814</t>
   </si>
   <si>
     <t xml:space="preserve">26.3479099273682</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5445079803467</t>
+    <t xml:space="preserve">25.544506072998</t>
   </si>
   <si>
     <t xml:space="preserve">26.7496089935303</t>
@@ -3149,13 +3149,13 @@
     <t xml:space="preserve">26.7861289978027</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5670185089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9547119140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.425199508667</t>
+    <t xml:space="preserve">26.5670204162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9547138214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4251976013184</t>
   </si>
   <si>
     <t xml:space="preserve">27.4799747467041</t>
@@ -3164,7 +3164,7 @@
     <t xml:space="preserve">27.1147937774658</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7313537597656</t>
+    <t xml:space="preserve">26.731351852417</t>
   </si>
   <si>
     <t xml:space="preserve">27.4069385528564</t>
@@ -3185,10 +3185,10 @@
     <t xml:space="preserve">23.5542640686035</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7045879364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0977840423584</t>
+    <t xml:space="preserve">24.70458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.097785949707</t>
   </si>
   <si>
     <t xml:space="preserve">22.0022392272949</t>
@@ -3197,13 +3197,13 @@
     <t xml:space="preserve">21.7466125488281</t>
   </si>
   <si>
-    <t xml:space="preserve">20.742359161377</t>
+    <t xml:space="preserve">20.7423572540283</t>
   </si>
   <si>
     <t xml:space="preserve">22.6047897338867</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8744239807129</t>
+    <t xml:space="preserve">21.8744258880615</t>
   </si>
   <si>
     <t xml:space="preserve">22.5134944915771</t>
@@ -3212,19 +3212,19 @@
     <t xml:space="preserve">23.1525630950928</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2073402404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5402545928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6680698394775</t>
+    <t xml:space="preserve">23.2073421478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5402565002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6680717468262</t>
   </si>
   <si>
     <t xml:space="preserve">24.8689193725586</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4489612579346</t>
+    <t xml:space="preserve">24.4489631652832</t>
   </si>
   <si>
     <t xml:space="preserve">25.2341022491455</t>
@@ -3233,34 +3233,34 @@
     <t xml:space="preserve">24.5585155487061</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0290012359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1385555267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0472602844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3984355926514</t>
+    <t xml:space="preserve">24.0289993286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.138557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0472621917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3984317779541</t>
   </si>
   <si>
     <t xml:space="preserve">25.4166946411133</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2115936279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0837783813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8098926544189</t>
+    <t xml:space="preserve">24.2115917205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.083776473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8098907470703</t>
   </si>
   <si>
     <t xml:space="preserve">23.3351554870605</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4221973419189</t>
+    <t xml:space="preserve">22.4221992492676</t>
   </si>
   <si>
     <t xml:space="preserve">22.7326030731201</t>
@@ -3284,22 +3284,22 @@
     <t xml:space="preserve">22.0935363769531</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8238964080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5457630157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0710220336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9657192230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1988372802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2718734741211</t>
+    <t xml:space="preserve">22.8239002227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5457611083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.07102394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9657211303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1988353729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2718715667725</t>
   </si>
   <si>
     <t xml:space="preserve">20.8884315490723</t>
@@ -3320,10 +3320,10 @@
     <t xml:space="preserve">19.957218170166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9024391174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2493629455566</t>
+    <t xml:space="preserve">19.902437210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2493648529053</t>
   </si>
   <si>
     <t xml:space="preserve">20.9614696502686</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">20.8519153594971</t>
   </si>
   <si>
-    <t xml:space="preserve">20.724100112915</t>
+    <t xml:space="preserve">20.7241020202637</t>
   </si>
   <si>
     <t xml:space="preserve">21.0162467956543</t>
@@ -3344,43 +3344,43 @@
     <t xml:space="preserve">20.3954372406006</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5232486724854</t>
+    <t xml:space="preserve">20.523250579834</t>
   </si>
   <si>
     <t xml:space="preserve">20.6693229675293</t>
   </si>
   <si>
-    <t xml:space="preserve">22.130054473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1933345794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6455612182617</t>
+    <t xml:space="preserve">22.1300525665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1933326721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6455593109131</t>
   </si>
   <si>
     <t xml:space="preserve">23.5177459716797</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7368564605713</t>
+    <t xml:space="preserve">23.7368545532227</t>
   </si>
   <si>
     <t xml:space="preserve">23.0533809661865</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9240741729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7393550872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8711566925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7443466186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6914291381836</t>
+    <t xml:space="preserve">22.9240760803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7393531799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8711585998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.744348526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6914310455322</t>
   </si>
   <si>
     <t xml:space="preserve">19.2850399017334</t>
@@ -3398,25 +3398,25 @@
     <t xml:space="preserve">21.3539333343506</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3169898986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7603225708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6494903564453</t>
+    <t xml:space="preserve">21.316987991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7603244781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6494884490967</t>
   </si>
   <si>
     <t xml:space="preserve">21.4278240203857</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5571269989014</t>
+    <t xml:space="preserve">21.55712890625</t>
   </si>
   <si>
     <t xml:space="preserve">21.7972679138184</t>
   </si>
   <si>
-    <t xml:space="preserve">20.559627532959</t>
+    <t xml:space="preserve">20.5596256256104</t>
   </si>
   <si>
     <t xml:space="preserve">20.7812938690186</t>
@@ -3425,25 +3425,25 @@
     <t xml:space="preserve">20.3379592895508</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9130973815918</t>
+    <t xml:space="preserve">19.9130954742432</t>
   </si>
   <si>
     <t xml:space="preserve">20.9475440979004</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0374088287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4992122650146</t>
+    <t xml:space="preserve">22.0374050140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4992141723633</t>
   </si>
   <si>
     <t xml:space="preserve">21.6679611206055</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4647655487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8182373046875</t>
+    <t xml:space="preserve">21.4647674560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8182392120361</t>
   </si>
   <si>
     <t xml:space="preserve">20.1532363891602</t>
@@ -3455,7 +3455,7 @@
     <t xml:space="preserve">20.4487915039062</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3908786773682</t>
+    <t xml:space="preserve">21.3908767700195</t>
   </si>
   <si>
     <t xml:space="preserve">21.0029602050781</t>
@@ -3470,7 +3470,7 @@
     <t xml:space="preserve">22.3883800506592</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2960186004639</t>
+    <t xml:space="preserve">22.2960205078125</t>
   </si>
   <si>
     <t xml:space="preserve">22.5361576080322</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">21.5017127990723</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7787952423096</t>
+    <t xml:space="preserve">21.7787933349609</t>
   </si>
   <si>
     <t xml:space="preserve">21.7233791351318</t>
@@ -3494,22 +3494,22 @@
     <t xml:space="preserve">21.6864337921143</t>
   </si>
   <si>
-    <t xml:space="preserve">21.889627456665</t>
+    <t xml:space="preserve">21.8896312713623</t>
   </si>
   <si>
     <t xml:space="preserve">21.704906463623</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6519870758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0424041748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0054588317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1162910461426</t>
+    <t xml:space="preserve">20.6519889831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0424022674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0054569244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1162929534912</t>
   </si>
   <si>
     <t xml:space="preserve">20.0978202819824</t>
@@ -3518,25 +3518,25 @@
     <t xml:space="preserve">19.9500427246094</t>
   </si>
   <si>
-    <t xml:space="preserve">19.74684715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5436534881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8417053222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4722595214844</t>
+    <t xml:space="preserve">19.7468452453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5436515808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8417072296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.472261428833</t>
   </si>
   <si>
     <t xml:space="preserve">19.1926784515381</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5830955505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2413578033447</t>
+    <t xml:space="preserve">18.5830936431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2413558959961</t>
   </si>
   <si>
     <t xml:space="preserve">18.0566349029541</t>
@@ -3548,25 +3548,25 @@
     <t xml:space="preserve">17.4562854766846</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6225357055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6989231109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5326747894287</t>
+    <t xml:space="preserve">17.622537612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6989250183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5326728820801</t>
   </si>
   <si>
     <t xml:space="preserve">16.8374652862549</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9852447509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.280797958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0037155151367</t>
+    <t xml:space="preserve">16.9852428436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2807998657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0037174224854</t>
   </si>
   <si>
     <t xml:space="preserve">17.6779537200928</t>
@@ -3578,31 +3578,31 @@
     <t xml:space="preserve">17.8164958953857</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5855941772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5024700164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0683689117432</t>
+    <t xml:space="preserve">17.5855922698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5024681091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0683670043945</t>
   </si>
   <si>
     <t xml:space="preserve">17.234619140625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2530937194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9390640258789</t>
+    <t xml:space="preserve">17.2530918121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9390621185303</t>
   </si>
   <si>
     <t xml:space="preserve">16.8005218505859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8836479187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4285793304443</t>
+    <t xml:space="preserve">16.8836460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4285774230957</t>
   </si>
   <si>
     <t xml:space="preserve">17.7056617736816</t>
@@ -3614,10 +3614,10 @@
     <t xml:space="preserve">17.7333698272705</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3429546356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.469762802124</t>
+    <t xml:space="preserve">18.3429565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4697608947754</t>
   </si>
   <si>
     <t xml:space="preserve">19.5805969238281</t>
@@ -3644,19 +3644,19 @@
     <t xml:space="preserve">19.0079574584961</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0239295959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8392066955566</t>
+    <t xml:space="preserve">20.0239315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8392086029053</t>
   </si>
   <si>
     <t xml:space="preserve">20.8736553192139</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9081001281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3329639434814</t>
+    <t xml:space="preserve">21.9080982208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3329620361328</t>
   </si>
   <si>
     <t xml:space="preserve">20.9105987548828</t>
@@ -3668,10 +3668,10 @@
     <t xml:space="preserve">21.3354625701904</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2431011199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9265747070312</t>
+    <t xml:space="preserve">21.2430992126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9265727996826</t>
   </si>
   <si>
     <t xml:space="preserve">21.7418518066406</t>
@@ -3695,7 +3695,7 @@
     <t xml:space="preserve">20.3933753967285</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2455997467041</t>
+    <t xml:space="preserve">20.2455978393555</t>
   </si>
   <si>
     <t xml:space="preserve">19.931568145752</t>
@@ -3716,10 +3716,10 @@
     <t xml:space="preserve">22.831714630127</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2750511169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6075477600098</t>
+    <t xml:space="preserve">23.2750492095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6075496673584</t>
   </si>
   <si>
     <t xml:space="preserve">23.3304653167725</t>
@@ -3740,19 +3740,19 @@
     <t xml:space="preserve">23.127269744873</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7553253173828</t>
+    <t xml:space="preserve">23.7553272247314</t>
   </si>
   <si>
     <t xml:space="preserve">23.8846340179443</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4782428741455</t>
+    <t xml:space="preserve">23.4782447814941</t>
   </si>
   <si>
     <t xml:space="preserve">23.1087989807129</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9979648590088</t>
+    <t xml:space="preserve">22.9979629516602</t>
   </si>
   <si>
     <t xml:space="preserve">23.0164375305176</t>
@@ -3770,19 +3770,19 @@
     <t xml:space="preserve">24.1247730255127</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5151863098145</t>
+    <t xml:space="preserve">23.5151882171631</t>
   </si>
   <si>
     <t xml:space="preserve">22.8686580657959</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4597721099854</t>
+    <t xml:space="preserve">23.4597702026367</t>
   </si>
   <si>
     <t xml:space="preserve">22.9056015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8132419586182</t>
+    <t xml:space="preserve">22.8132438659668</t>
   </si>
   <si>
     <t xml:space="preserve">22.6285209655762</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">22.2036571502686</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0004615783691</t>
+    <t xml:space="preserve">22.0004634857178</t>
   </si>
   <si>
     <t xml:space="preserve">22.0558776855469</t>
@@ -3806,10 +3806,10 @@
     <t xml:space="preserve">22.2590751647949</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8342113494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0928230285645</t>
+    <t xml:space="preserve">21.8342132568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0928249359131</t>
   </si>
   <si>
     <t xml:space="preserve">22.2406005859375</t>
@@ -3818,13 +3818,13 @@
     <t xml:space="preserve">21.2615718841553</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3404579162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6569843292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1187915802002</t>
+    <t xml:space="preserve">19.3404560089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.656982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1187896728516</t>
   </si>
   <si>
     <t xml:space="preserve">18.5646228790283</t>
@@ -3839,7 +3839,7 @@
     <t xml:space="preserve">18.2690658569336</t>
   </si>
   <si>
-    <t xml:space="preserve">18.509204864502</t>
+    <t xml:space="preserve">18.5092067718506</t>
   </si>
   <si>
     <t xml:space="preserve">18.8232326507568</t>
@@ -3848,7 +3848,7 @@
     <t xml:space="preserve">18.5461502075195</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7124004364014</t>
+    <t xml:space="preserve">18.7123985290527</t>
   </si>
   <si>
     <t xml:space="preserve">18.7308731079102</t>
@@ -3860,19 +3860,19 @@
     <t xml:space="preserve">18.4445514678955</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3614253997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7980213165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5486469268799</t>
+    <t xml:space="preserve">18.3614273071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7980251312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5486488342285</t>
   </si>
   <si>
     <t xml:space="preserve">17.1422576904297</t>
   </si>
   <si>
-    <t xml:space="preserve">16.948299407959</t>
+    <t xml:space="preserve">16.9483013153076</t>
   </si>
   <si>
     <t xml:space="preserve">16.9205894470215</t>
@@ -3881,22 +3881,22 @@
     <t xml:space="preserve">16.8651752471924</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5696182250977</t>
+    <t xml:space="preserve">16.5696201324463</t>
   </si>
   <si>
     <t xml:space="preserve">16.8559379577637</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1145496368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7451019287109</t>
+    <t xml:space="preserve">17.1145515441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7451057434082</t>
   </si>
   <si>
     <t xml:space="preserve">16.9021186828613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8744106292725</t>
+    <t xml:space="preserve">16.8744125366211</t>
   </si>
   <si>
     <t xml:space="preserve">16.7912845611572</t>
@@ -3935,22 +3935,22 @@
     <t xml:space="preserve">16.0062141418457</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0523929595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6896877288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4710884094238</t>
+    <t xml:space="preserve">16.0523948669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6896858215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4710865020752</t>
   </si>
   <si>
     <t xml:space="preserve">16.632661819458</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6611747741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5946445465088</t>
+    <t xml:space="preserve">16.6611766815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5946426391602</t>
   </si>
   <si>
     <t xml:space="preserve">17.2124290466309</t>
@@ -3959,10 +3959,10 @@
     <t xml:space="preserve">17.5830993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9442653656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8207092285156</t>
+    <t xml:space="preserve">17.944263458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.820707321167</t>
   </si>
   <si>
     <t xml:space="preserve">17.8302135467529</t>
@@ -3974,7 +3974,7 @@
     <t xml:space="preserve">16.9938259124756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5661315917969</t>
+    <t xml:space="preserve">16.5661296844482</t>
   </si>
   <si>
     <t xml:space="preserve">16.2809982299805</t>
@@ -3983,13 +3983,13 @@
     <t xml:space="preserve">16.204963684082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0053730010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.58717918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.786771774292</t>
+    <t xml:space="preserve">16.00537109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5871801376343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7867727279663</t>
   </si>
   <si>
     <t xml:space="preserve">15.5681705474854</t>
@@ -4007,16 +4007,16 @@
     <t xml:space="preserve">15.3305606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6251983642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4541187286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8723125457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9958686828613</t>
+    <t xml:space="preserve">15.6251974105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4541177749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8723115921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9958667755127</t>
   </si>
   <si>
     <t xml:space="preserve">16.0623989105225</t>
@@ -4025,19 +4025,19 @@
     <t xml:space="preserve">15.7012319564819</t>
   </si>
   <si>
-    <t xml:space="preserve">15.777268409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8247880935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7487545013428</t>
+    <t xml:space="preserve">15.7772674560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8247900009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7487535476685</t>
   </si>
   <si>
     <t xml:space="preserve">15.7392492294312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9388418197632</t>
+    <t xml:space="preserve">15.9388427734375</t>
   </si>
   <si>
     <t xml:space="preserve">16.1859569549561</t>
@@ -4046,7 +4046,7 @@
     <t xml:space="preserve">16.1574420928955</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8913202285767</t>
+    <t xml:space="preserve">15.8913192749023</t>
   </si>
   <si>
     <t xml:space="preserve">16.9177932739258</t>
@@ -4058,13 +4058,13 @@
     <t xml:space="preserve">17.0223407745361</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1649074554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0603580474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6231555938721</t>
+    <t xml:space="preserve">17.1649055480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.060359954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6231575012207</t>
   </si>
   <si>
     <t xml:space="preserve">16.7277050018311</t>
@@ -4079,7 +4079,7 @@
     <t xml:space="preserve">16.3000068664551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4995994567871</t>
+    <t xml:space="preserve">16.4996013641357</t>
   </si>
   <si>
     <t xml:space="preserve">16.509105682373</t>
@@ -4106,16 +4106,16 @@
     <t xml:space="preserve">17.4215240478516</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3074703216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2599506378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8628072738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.881814956665</t>
+    <t xml:space="preserve">17.3074722290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2599487304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8628063201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8818140029907</t>
   </si>
   <si>
     <t xml:space="preserve">16.4235649108887</t>
@@ -4127,16 +4127,16 @@
     <t xml:space="preserve">16.1479377746582</t>
   </si>
   <si>
-    <t xml:space="preserve">15.910327911377</t>
+    <t xml:space="preserve">15.9103288650513</t>
   </si>
   <si>
     <t xml:space="preserve">16.2429828643799</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8533029556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8437976837158</t>
+    <t xml:space="preserve">15.8533020019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8437967300415</t>
   </si>
   <si>
     <t xml:space="preserve">14.7793073654175</t>
@@ -4151,10 +4151,10 @@
     <t xml:space="preserve">14.4466543197632</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7222805023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6917276382446</t>
+    <t xml:space="preserve">14.7222814559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6917285919189</t>
   </si>
   <si>
     <t xml:space="preserve">15.4731273651123</t>
@@ -4166,7 +4166,7 @@
     <t xml:space="preserve">15.4921350479126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0929517745972</t>
+    <t xml:space="preserve">15.0929527282715</t>
   </si>
   <si>
     <t xml:space="preserve">15.4446144104004</t>
@@ -4196,7 +4196,7 @@
     <t xml:space="preserve">14.4846715927124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.931378364563</t>
+    <t xml:space="preserve">14.9313774108887</t>
   </si>
   <si>
     <t xml:space="preserve">14.9218730926514</t>
@@ -4211,37 +4211,37 @@
     <t xml:space="preserve">14.731785774231</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0074119567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7677640914917</t>
+    <t xml:space="preserve">15.0074129104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7677631378174</t>
   </si>
   <si>
     <t xml:space="preserve">16.1954612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5566272735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1289291381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0528926849365</t>
+    <t xml:space="preserve">16.5566253662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.128927230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0528945922852</t>
   </si>
   <si>
     <t xml:space="preserve">16.3570346832275</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4330711364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7467136383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3665370941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3950519561768</t>
+    <t xml:space="preserve">16.433069229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7467155456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3665390014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3950500488281</t>
   </si>
   <si>
     <t xml:space="preserve">16.4805908203125</t>
@@ -4256,10 +4256,10 @@
     <t xml:space="preserve">16.3285217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6136512756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6991920471191</t>
+    <t xml:space="preserve">16.6136531829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6991901397705</t>
   </si>
   <si>
     <t xml:space="preserve">16.5756359100342</t>
@@ -4268,22 +4268,22 @@
     <t xml:space="preserve">18.5240325927734</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7046146392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.647590637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.198844909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4839763641357</t>
+    <t xml:space="preserve">18.7046165466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6475887298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1988430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4839744567871</t>
   </si>
   <si>
     <t xml:space="preserve">19.5029830932617</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4649658203125</t>
+    <t xml:space="preserve">19.4649639129639</t>
   </si>
   <si>
     <t xml:space="preserve">19.2938861846924</t>
@@ -4292,10 +4292,10 @@
     <t xml:space="preserve">19.1037998199463</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2748775482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0277633666992</t>
+    <t xml:space="preserve">19.2748794555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0277652740479</t>
   </si>
   <si>
     <t xml:space="preserve">18.0868320465088</t>
@@ -4322,16 +4322,16 @@
     <t xml:space="preserve">17.9062480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7541770935059</t>
+    <t xml:space="preserve">17.7541790008545</t>
   </si>
   <si>
     <t xml:space="preserve">18.1818752288818</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9157524108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2103881835938</t>
+    <t xml:space="preserve">17.9157543182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2103862762451</t>
   </si>
   <si>
     <t xml:space="preserve">18.343448638916</t>
@@ -4346,16 +4346,16 @@
     <t xml:space="preserve">18.6570930480957</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5810565948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4289894104004</t>
+    <t xml:space="preserve">18.5810585021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4289875030518</t>
   </si>
   <si>
     <t xml:space="preserve">18.1913795471191</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0488128662109</t>
+    <t xml:space="preserve">18.0488147735596</t>
   </si>
   <si>
     <t xml:space="preserve">18.020299911499</t>
@@ -4373,7 +4373,7 @@
     <t xml:space="preserve">17.9632740020752</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0678234100342</t>
+    <t xml:space="preserve">18.0678215026855</t>
   </si>
   <si>
     <t xml:space="preserve">18.1723709106445</t>
@@ -4403,13 +4403,13 @@
     <t xml:space="preserve">17.8112030029297</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5165691375732</t>
+    <t xml:space="preserve">17.5165672302246</t>
   </si>
   <si>
     <t xml:space="preserve">17.5450801849365</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3169746398926</t>
+    <t xml:space="preserve">17.3169765472412</t>
   </si>
   <si>
     <t xml:space="preserve">17.3264808654785</t>
@@ -4430,10 +4430,10 @@
     <t xml:space="preserve">17.5545845031738</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7636814117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8872375488281</t>
+    <t xml:space="preserve">17.7636833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8872394561768</t>
   </si>
   <si>
     <t xml:space="preserve">18.1533622741699</t>
@@ -4442,19 +4442,19 @@
     <t xml:space="preserve">18.1628665924072</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3549938201904</t>
+    <t xml:space="preserve">17.3549957275391</t>
   </si>
   <si>
     <t xml:space="preserve">17.4690456390381</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4405326843262</t>
+    <t xml:space="preserve">17.4405345916748</t>
   </si>
   <si>
     <t xml:space="preserve">17.1078796386719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0413513183594</t>
+    <t xml:space="preserve">17.0413494110107</t>
   </si>
   <si>
     <t xml:space="preserve">16.9368019104004</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">16.4615821838379</t>
   </si>
   <si>
-    <t xml:space="preserve">16.309513092041</t>
+    <t xml:space="preserve">16.3095111846924</t>
   </si>
   <si>
     <t xml:space="preserve">17.0033321380615</t>
@@ -4490,7 +4490,7 @@
     <t xml:space="preserve">17.6211185455322</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0107955932617</t>
+    <t xml:space="preserve">18.0107975006104</t>
   </si>
   <si>
     <t xml:space="preserve">17.7826900482178</t>
@@ -4505,7 +4505,7 @@
     <t xml:space="preserve">17.5355777740479</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0012912750244</t>
+    <t xml:space="preserve">18.001293182373</t>
   </si>
   <si>
     <t xml:space="preserve">18.2674140930176</t>
@@ -70924,7 +70924,7 @@
     </row>
     <row r="2510">
       <c r="A2510" s="1" t="n">
-        <v>45973.6909837963</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2510" t="n">
         <v>68491</v>
@@ -70945,6 +70945,32 @@
         <v>1774</v>
       </c>
       <c r="H2510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>45974.6911458333</v>
+      </c>
+      <c r="B2511" t="n">
+        <v>168525</v>
+      </c>
+      <c r="C2511" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>14.7600002288818</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>1773</v>
+      </c>
+      <c r="H2511" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TNXT.MI.xlsx
+++ b/data/TNXT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63493752479553</t>
+    <t xml:space="preserve">2.63493776321411</t>
   </si>
   <si>
     <t xml:space="preserve">TNXT.MI</t>
@@ -50,49 +50,49 @@
     <t xml:space="preserve">2.59350848197937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53550672531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52556324005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48579072952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52722072601318</t>
+    <t xml:space="preserve">2.5355064868927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52556347846985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48579096794128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5272204875946</t>
   </si>
   <si>
     <t xml:space="preserve">2.48744773864746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47087597846985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46921873092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54047822952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49739098548889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47916173934937</t>
+    <t xml:space="preserve">2.47087574005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46921849250793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54047846794128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49739122390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47916197776794</t>
   </si>
   <si>
     <t xml:space="preserve">2.44436097145081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39464497566223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34161472320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36150121688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55207848548889</t>
+    <t xml:space="preserve">2.39464473724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34161448478699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36150074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55207896232605</t>
   </si>
   <si>
     <t xml:space="preserve">2.58522272109985</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">2.63659477233887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68962550163269</t>
+    <t xml:space="preserve">2.68962502479553</t>
   </si>
   <si>
     <t xml:space="preserve">2.73436951637268</t>
@@ -116,64 +116,64 @@
     <t xml:space="preserve">2.72608351707458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77579975128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58025097846985</t>
+    <t xml:space="preserve">2.77579951286316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58025121688843</t>
   </si>
   <si>
     <t xml:space="preserve">2.5620219707489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66808176040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62830901145935</t>
+    <t xml:space="preserve">2.66808152198792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62830877304077</t>
   </si>
   <si>
     <t xml:space="preserve">2.64322376251221</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60842227935791</t>
+    <t xml:space="preserve">2.60842275619507</t>
   </si>
   <si>
     <t xml:space="preserve">2.66642427444458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65316724777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62665176391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69293975830078</t>
+    <t xml:space="preserve">2.65316677093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62665152549744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6929395198822</t>
   </si>
   <si>
     <t xml:space="preserve">2.82551550865173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81722927093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90008926391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85865926742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8984317779541</t>
+    <t xml:space="preserve">2.81722950935364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90008974075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85865950584412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89843225479126</t>
   </si>
   <si>
     <t xml:space="preserve">2.88351702690125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87523150444031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86694502830505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81888675689697</t>
+    <t xml:space="preserve">2.87523126602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86694526672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81888628005981</t>
   </si>
   <si>
     <t xml:space="preserve">2.82054400444031</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">2.85368776321411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79237151145935</t>
+    <t xml:space="preserve">2.79237127304077</t>
   </si>
   <si>
     <t xml:space="preserve">2.8570020198822</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">2.90671801567078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82882976531982</t>
+    <t xml:space="preserve">2.8288300037384</t>
   </si>
   <si>
     <t xml:space="preserve">2.85037350654602</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">2.86474585533142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94950151443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92407488822937</t>
+    <t xml:space="preserve">2.94950175285339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92407536506653</t>
   </si>
   <si>
     <t xml:space="preserve">2.96645307540894</t>
@@ -230,46 +230,46 @@
     <t xml:space="preserve">2.94272136688232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94780683517456</t>
+    <t xml:space="preserve">2.94780707359314</t>
   </si>
   <si>
     <t xml:space="preserve">2.88339233398438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8732213973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85966062545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03256273269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07037329673767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06866335868835</t>
+    <t xml:space="preserve">2.87322115898132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85966086387634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03256297111511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07037377357483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06866312026978</t>
   </si>
   <si>
     <t xml:space="preserve">3.06011056900024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99340033531189</t>
+    <t xml:space="preserve">2.99340057373047</t>
   </si>
   <si>
     <t xml:space="preserve">2.98484802246094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93524289131165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98313760757446</t>
+    <t xml:space="preserve">2.93524312973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98313784599304</t>
   </si>
   <si>
     <t xml:space="preserve">2.92497992515564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92326951026917</t>
+    <t xml:space="preserve">2.92326927185059</t>
   </si>
   <si>
     <t xml:space="preserve">2.96774291992188</t>
@@ -278,73 +278,73 @@
     <t xml:space="preserve">3.03616333007812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05839991569519</t>
+    <t xml:space="preserve">3.05840015411377</t>
   </si>
   <si>
     <t xml:space="preserve">3.05497908592224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08747863769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13879418373108</t>
+    <t xml:space="preserve">3.08747887611389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13879442214966</t>
   </si>
   <si>
     <t xml:space="preserve">3.12853097915649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19010972976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15589952468872</t>
+    <t xml:space="preserve">3.19010996818542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15589928627014</t>
   </si>
   <si>
     <t xml:space="preserve">3.12339925765991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12511014938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14734673500061</t>
+    <t xml:space="preserve">3.12510991096497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14734697341919</t>
   </si>
   <si>
     <t xml:space="preserve">3.16445183753967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16616225242615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24142503738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30129265785217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38681888580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48431777954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52708077430725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62629103660583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63655376434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64510631561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74602723121643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67760634422302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71181726455688</t>
+    <t xml:space="preserve">3.16616249084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24142527580261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30129289627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3868191242218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48431801795959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52708101272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62629055976868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.636554479599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64510703086853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74602699279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67760682106018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71181702613831</t>
   </si>
   <si>
     <t xml:space="preserve">3.63484358787537</t>
@@ -356,25 +356,25 @@
     <t xml:space="preserve">3.50484442710876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49458122253418</t>
+    <t xml:space="preserve">3.4945809841156</t>
   </si>
   <si>
     <t xml:space="preserve">3.50655484199524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48089694976807</t>
+    <t xml:space="preserve">3.48089718818665</t>
   </si>
   <si>
     <t xml:space="preserve">3.43129229545593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35602974891663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60063314437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64681673049927</t>
+    <t xml:space="preserve">3.35602998733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60063338279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64681720733643</t>
   </si>
   <si>
     <t xml:space="preserve">3.69471144676208</t>
@@ -386,25 +386,25 @@
     <t xml:space="preserve">3.67589592933655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66563296318054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59721207618713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63313269615173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57497549057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66050148010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68615913391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7152373790741</t>
+    <t xml:space="preserve">3.6656322479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59721231460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63313341140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57497501373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66050171852112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68615889549255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71523785591125</t>
   </si>
   <si>
     <t xml:space="preserve">3.73747444152832</t>
@@ -413,106 +413,106 @@
     <t xml:space="preserve">3.71010589599609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69129061698914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68958020210266</t>
+    <t xml:space="preserve">3.69129014015198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68957996368408</t>
   </si>
   <si>
     <t xml:space="preserve">3.73234248161316</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72036838531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76313257217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77168464660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62116026878357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64168524742126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7032642364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79734230041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75457978248596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9085259437561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76655220985413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72892141342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6673436164856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50997591018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49800229072571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48944973945618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47234487533569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40392398834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43642401695251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53221273422241</t>
+    <t xml:space="preserve">3.7203688621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76313185691833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77168416976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62115955352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64168548583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70326375961304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79734253883362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75457954406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90852642059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7665536403656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72892165184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66734290122986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50997614860535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49800276756287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4894495010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47234463691711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40392422676086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43642377853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53221249580383</t>
   </si>
   <si>
     <t xml:space="preserve">3.51852822303772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46037101745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50142335891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53563356399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55616021156311</t>
+    <t xml:space="preserve">3.46037125587463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50142312049866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53563332557678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55615973472595</t>
   </si>
   <si>
     <t xml:space="preserve">3.6433961391449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72550082206726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84865736961365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82984209060669</t>
+    <t xml:space="preserve">3.72550106048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84865808486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82984232902527</t>
   </si>
   <si>
     <t xml:space="preserve">3.83155298233032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87089419364929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8452365398407</t>
+    <t xml:space="preserve">3.87089467048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84523701667786</t>
   </si>
   <si>
     <t xml:space="preserve">3.8743155002594</t>
@@ -521,61 +521,61 @@
     <t xml:space="preserve">3.86405229568481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85721015930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82471036911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90681529045105</t>
+    <t xml:space="preserve">3.85721039772034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82471060752869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90681433677673</t>
   </si>
   <si>
     <t xml:space="preserve">4.00260400772095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17536640167236</t>
+    <t xml:space="preserve">4.17536592483521</t>
   </si>
   <si>
     <t xml:space="preserve">4.11378765106201</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00773572921753</t>
+    <t xml:space="preserve">4.00773525238037</t>
   </si>
   <si>
     <t xml:space="preserve">4.05220890045166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08128786087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0060248374939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09839248657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01970911026001</t>
+    <t xml:space="preserve">4.0812873840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00602436065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09839296340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01970863342285</t>
   </si>
   <si>
     <t xml:space="preserve">4.01115703582764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99576210975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03510427474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06247282028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13773441314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12234115600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14799785614014</t>
+    <t xml:space="preserve">3.99576234817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0351037979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06247186660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13773488998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12234020233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14799833297729</t>
   </si>
   <si>
     <t xml:space="preserve">4.18905019760132</t>
@@ -596,16 +596,16 @@
     <t xml:space="preserve">3.99405169487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01799821853638</t>
+    <t xml:space="preserve">4.01799869537354</t>
   </si>
   <si>
     <t xml:space="preserve">4.02655172348022</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07615661621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12747240066528</t>
+    <t xml:space="preserve">4.07615566253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12747192382812</t>
   </si>
   <si>
     <t xml:space="preserve">4.11891889572144</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">4.10523509979248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09668254852295</t>
+    <t xml:space="preserve">4.09668207168579</t>
   </si>
   <si>
     <t xml:space="preserve">4.10181379318237</t>
@@ -626,19 +626,19 @@
     <t xml:space="preserve">4.09497165679932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13089227676392</t>
+    <t xml:space="preserve">4.13089275360107</t>
   </si>
   <si>
     <t xml:space="preserve">4.21641874313354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52431154251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54996871948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53713941574097</t>
+    <t xml:space="preserve">4.52431106567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54996919631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53713989257812</t>
   </si>
   <si>
     <t xml:space="preserve">4.46444272994995</t>
@@ -647,52 +647,52 @@
     <t xml:space="preserve">4.50292921066284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56707382202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62266635894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63549518585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58417987823486</t>
+    <t xml:space="preserve">4.5670747756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6226658821106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63549423217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58417892456055</t>
   </si>
   <si>
     <t xml:space="preserve">4.60128450393677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57562637329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61838912963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53286457061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55852127075195</t>
+    <t xml:space="preserve">4.57562685012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61838960647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53286409378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55852174758911</t>
   </si>
   <si>
     <t xml:space="preserve">4.48154830932617</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51575899124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4901008605957</t>
+    <t xml:space="preserve">4.51575803756714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49009990692139</t>
   </si>
   <si>
     <t xml:space="preserve">4.51148223876953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63121843338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78516435623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7595067024231</t>
+    <t xml:space="preserve">4.63121795654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78516483306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75950717926025</t>
   </si>
   <si>
     <t xml:space="preserve">4.78944063186646</t>
@@ -701,46 +701,46 @@
     <t xml:space="preserve">4.73384857177734</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77233552932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76378440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65687561035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69536209106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8279275894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90062475204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91772937774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94338750839233</t>
+    <t xml:space="preserve">4.77233600616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76378393173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65687608718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69536256790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82792711257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90062379837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91772890090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94338703155518</t>
   </si>
   <si>
     <t xml:space="preserve">4.98615026473999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04174184799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02036094665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07167625427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08022880554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99470376968384</t>
+    <t xml:space="preserve">5.04174137115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02035999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0716757774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08022928237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99470329284668</t>
   </si>
   <si>
     <t xml:space="preserve">5.09305667877197</t>
@@ -752,58 +752,58 @@
     <t xml:space="preserve">4.91728496551514</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94766521453857</t>
+    <t xml:space="preserve">4.94766473770142</t>
   </si>
   <si>
     <t xml:space="preserve">4.92596530914307</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90426397323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82180404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73500299453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7219820022583</t>
+    <t xml:space="preserve">4.90426540374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82180309295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7350025177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72198247909546</t>
   </si>
   <si>
     <t xml:space="preserve">4.59178066253662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64386129379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73066186904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66556167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65254163742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60914134979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65688180923462</t>
+    <t xml:space="preserve">4.64386081695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73066234588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66556119918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6525411605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60914039611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6568808555603</t>
   </si>
   <si>
     <t xml:space="preserve">4.54837989807129</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53536033630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47025918960571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59612035751343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47459888458252</t>
+    <t xml:space="preserve">4.53535985946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47025966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59612083435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47459936141968</t>
   </si>
   <si>
     <t xml:space="preserve">4.48761940002441</t>
@@ -812,85 +812,85 @@
     <t xml:space="preserve">4.46157836914062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41383790969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38779830932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39213848114014</t>
+    <t xml:space="preserve">4.41383743286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38779783248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39213800430298</t>
   </si>
   <si>
     <t xml:space="preserve">4.40949773788452</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55706119537354</t>
+    <t xml:space="preserve">4.55706024169922</t>
   </si>
   <si>
     <t xml:space="preserve">4.52233982086182</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57008028030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53970050811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47893953323364</t>
+    <t xml:space="preserve">4.5700798034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53970098495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47893857955933</t>
   </si>
   <si>
     <t xml:space="preserve">4.43553876876831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42251777648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4311990737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45289850234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51365947723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6872615814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60046052932739</t>
+    <t xml:space="preserve">4.42251825332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43119859695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45289897918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51365995407104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68726253509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60046100616455</t>
   </si>
   <si>
     <t xml:space="preserve">4.63952112197876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56140041351318</t>
+    <t xml:space="preserve">4.56139993667603</t>
   </si>
   <si>
     <t xml:space="preserve">4.58744049072266</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61782121658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64820146560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60480117797852</t>
+    <t xml:space="preserve">4.61782073974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64820194244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6048002243042</t>
   </si>
   <si>
     <t xml:space="preserve">4.58310031890869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49629974365234</t>
+    <t xml:space="preserve">4.49629926681519</t>
   </si>
   <si>
     <t xml:space="preserve">4.50497961044312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42685890197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49195909500122</t>
+    <t xml:space="preserve">4.42685794830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49195957183838</t>
   </si>
   <si>
     <t xml:space="preserve">4.51800012588501</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">4.80878353118896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77840375900269</t>
+    <t xml:space="preserve">4.77840280532837</t>
   </si>
   <si>
     <t xml:space="preserve">4.84784364700317</t>
@@ -908,19 +908,19 @@
     <t xml:space="preserve">4.83482456207275</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74368238449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81312322616577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71330261230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7046217918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72632265090942</t>
+    <t xml:space="preserve">4.74368286132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81312370300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71330213546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70462226867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72632217407227</t>
   </si>
   <si>
     <t xml:space="preserve">4.69594240188599</t>
@@ -929,16 +929,16 @@
     <t xml:space="preserve">4.7697229385376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84350347518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87822437286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87388467788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97370529174805</t>
+    <t xml:space="preserve">4.84350395202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87822484970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8738842010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97370576858521</t>
   </si>
   <si>
     <t xml:space="preserve">4.97804594039917</t>
@@ -947,337 +947,337 @@
     <t xml:space="preserve">5.00842666625977</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07786655426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04314708709717</t>
+    <t xml:space="preserve">5.07786750793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04314661026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14730739593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86086416244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.869544506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96502542495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90860509872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99974632263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99106597900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15598821640015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12994766235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2948694229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41639184951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48583221435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43375158309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4814920425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42073249816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39469242095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35563087463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33393001556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37299156188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33827066421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20806884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16466808319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26448917388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25146961212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26014947891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18636798858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20372867584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19504880905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16900825500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18202829360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19938850402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22542905807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42507171630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61603355407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72887516021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71151638031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78963661193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82435655593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87643814086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88511800765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93719911575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85907697677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80699729919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92851829528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97191858291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95455837249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03268003463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17156171798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28440284729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01531887054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02399921417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21496200561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14552164077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40592432022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07608079910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98927927017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04135990142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22364234924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1368408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19760179519653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1542010307312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05003976821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89379787445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90247869491577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70283508300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50319290161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58131313323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72019577026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76359605789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91983795166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99795913696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83303689956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79831600189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65943479537964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51187324523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5465931892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58999395370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52055263519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3816704750061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44243192672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46847295761108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67679452896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6420750617981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55527400970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53791332244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57263374328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5292329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39903163909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39035129547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45111179351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09344053268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81567621231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77227640151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73755645751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40771198272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24278926849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0691876411438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98238515853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07618761062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15619850158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08507776260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24509811401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11174774169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13841819763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20953798294067</t>
   </si>
   <si>
     <t xml:space="preserve">5.14730787277222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86086416244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86954498291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96502494812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90860509872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99974679946899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99106597900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15598821640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12994813919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29486989974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41639137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48583316802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43375205993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48149251937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42073202133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39469146728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35563087463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33393096923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37299060821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33826971054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20806884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16466808319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26449012756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25146913528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26014947891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18636846542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20372915267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19504833221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16900873184204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18202829360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19938802719116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22542905807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42507171630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61603403091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72887563705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71151542663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78963613510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82435703277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87643766403198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88511800765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93719863891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85907745361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80699682235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92851877212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97191905975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95455837249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03267955780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17156171798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28440284729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01531982421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02399921417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21496248245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14552164077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40592479705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07607984542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98927927017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04135942459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22364139556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1368408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19760227203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15420150756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05004024505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89379787445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90247774124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70283603668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50319290161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58131408691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72019624710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76359605789185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91983842849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99795961380005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83303689956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79831695556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65943479537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51187229156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54659366607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58999347686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52055263519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38167142868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44243192672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46847200393677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6767954826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64207410812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55527353286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53791332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57263374328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5292329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39903116226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39035081863403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45111227035522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09344053268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81567668914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77227640151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73755598068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40771102905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24278974533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06918716430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98238563537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07618761062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15619802474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08507776260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24509716033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11174774169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13841819763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20953845977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14730739593506</t>
-  </si>
-  <si>
     <t xml:space="preserve">5.06729745864868</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05840730667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04062843322754</t>
+    <t xml:space="preserve">5.05840826034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04062795639038</t>
   </si>
   <si>
     <t xml:space="preserve">5.04951810836792</t>
@@ -1292,22 +1292,22 @@
     <t xml:space="preserve">4.90727806091309</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76503801345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92505741119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88949775695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0228476524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97839736938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91616821289062</t>
+    <t xml:space="preserve">4.76503753662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92505788803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88949823379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02284812927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97839784622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91616773605347</t>
   </si>
   <si>
     <t xml:space="preserve">4.95172834396362</t>
@@ -1316,13 +1316,13 @@
     <t xml:space="preserve">4.93394756317139</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89838790893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80948781967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78281784057617</t>
+    <t xml:space="preserve">4.89838838577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80948829650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78281831741333</t>
   </si>
   <si>
     <t xml:space="preserve">4.75614786148071</t>
@@ -1331,31 +1331,31 @@
     <t xml:space="preserve">4.98728799819946</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10285711288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96061754226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20064735412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2184271812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27176761627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33399820327759</t>
+    <t xml:space="preserve">5.10285758972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.960618019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20064783096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21842765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27176713943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33399772644043</t>
   </si>
   <si>
     <t xml:space="preserve">5.23620748519897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18286800384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01395797729492</t>
+    <t xml:space="preserve">5.18286752700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01395750045776</t>
   </si>
   <si>
     <t xml:space="preserve">4.996178150177</t>
@@ -1364,19 +1364,19 @@
     <t xml:space="preserve">5.00506782531738</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37844848632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47623777389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56513833999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68070793151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6540379524231</t>
+    <t xml:space="preserve">5.37844800949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47623729705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56513786315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6807074546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65403747558594</t>
   </si>
   <si>
     <t xml:space="preserve">5.63625812530518</t>
@@ -1388,28 +1388,28 @@
     <t xml:space="preserve">5.68959808349609</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96518754959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89406728744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77849769592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84072780609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76071786880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92073726654053</t>
+    <t xml:space="preserve">5.96518707275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89406776428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77849817276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84072732925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76071739196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92073774337769</t>
   </si>
   <si>
     <t xml:space="preserve">5.83183765411377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44956731796265</t>
+    <t xml:space="preserve">5.44956827163696</t>
   </si>
   <si>
     <t xml:space="preserve">5.5829176902771</t>
@@ -1418,19 +1418,19 @@
     <t xml:space="preserve">5.43178796768188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36955785751343</t>
+    <t xml:space="preserve">5.36955738067627</t>
   </si>
   <si>
     <t xml:space="preserve">5.60958766937256</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86739778518677</t>
+    <t xml:space="preserve">5.86739730834961</t>
   </si>
   <si>
     <t xml:space="preserve">5.78738784790039</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52068853378296</t>
+    <t xml:space="preserve">5.5206880569458</t>
   </si>
   <si>
     <t xml:space="preserve">5.49401760101318</t>
@@ -1439,58 +1439,58 @@
     <t xml:space="preserve">5.57402801513672</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59180784225464</t>
+    <t xml:space="preserve">5.59180736541748</t>
   </si>
   <si>
     <t xml:space="preserve">5.64514780044556</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71626758575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73404788970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81405830383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67181825637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51179790496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85850858688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66292810440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53846788406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90295791625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79627752304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80516815185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61847829818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46734762191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60069799423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45845699310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50290727615356</t>
+    <t xml:space="preserve">5.71626663208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73404741287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81405735015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67181777954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51179695129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85850763320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66292715072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53846836090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90295743942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79627799987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80516767501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61847734451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46734809875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60069847106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45845746994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50290822982788</t>
   </si>
   <si>
     <t xml:space="preserve">5.34288787841797</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">5.52957773208618</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42289781570435</t>
+    <t xml:space="preserve">5.42289733886719</t>
   </si>
   <si>
     <t xml:space="preserve">5.72515773773193</t>
@@ -1514,28 +1514,28 @@
     <t xml:space="preserve">5.69848775863647</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00074815750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92962741851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94740772247314</t>
+    <t xml:space="preserve">6.0007472038269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92962789535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9474081993103</t>
   </si>
   <si>
     <t xml:space="preserve">5.93851757049561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99185705184937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24077796936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40968704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48080778121948</t>
+    <t xml:space="preserve">5.99185657501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24077701568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40968656539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48080682754517</t>
   </si>
   <si>
     <t xml:space="preserve">6.62304735183716</t>
@@ -1544,19 +1544,19 @@
     <t xml:space="preserve">6.84529733657837</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99642658233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0142068862915</t>
+    <t xml:space="preserve">6.99642705917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01420736312866</t>
   </si>
   <si>
     <t xml:space="preserve">6.90752696990967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91641712188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97864675521851</t>
+    <t xml:space="preserve">6.91641759872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97864723205566</t>
   </si>
   <si>
     <t xml:space="preserve">7.00531721115112</t>
@@ -1568,10 +1568,10 @@
     <t xml:space="preserve">7.24534702301025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27201700210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33424711227417</t>
+    <t xml:space="preserve">7.27201747894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33424663543701</t>
   </si>
   <si>
     <t xml:space="preserve">7.476487159729</t>
@@ -1583,16 +1583,16 @@
     <t xml:space="preserve">7.7342963218689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72540664672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79652643203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80541610717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22324562072754</t>
+    <t xml:space="preserve">7.72540616989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79652690887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80541706085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22324657440186</t>
   </si>
   <si>
     <t xml:space="preserve">8.21435642242432</t>
@@ -1601,58 +1601,58 @@
     <t xml:space="preserve">8.15212631225586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12545680999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00099754333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17879676818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34770774841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4277172088623</t>
+    <t xml:space="preserve">8.12545776367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00099658966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17879581451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34770679473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42771625518799</t>
   </si>
   <si>
     <t xml:space="preserve">8.48105525970459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46327686309814</t>
+    <t xml:space="preserve">8.46327781677246</t>
   </si>
   <si>
     <t xml:space="preserve">8.5255069732666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50772571563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66774559020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8010950088501</t>
+    <t xml:space="preserve">8.50772666931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66774654388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80109691619873</t>
   </si>
   <si>
     <t xml:space="preserve">8.88999652862549</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1922550201416</t>
+    <t xml:space="preserve">9.19225597381592</t>
   </si>
   <si>
     <t xml:space="preserve">9.37005615234375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47673511505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49451637268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31671619415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15669536590576</t>
+    <t xml:space="preserve">9.47673606872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49451732635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31671524047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15669727325439</t>
   </si>
   <si>
     <t xml:space="preserve">9.35227680206299</t>
@@ -1667,16 +1667,16 @@
     <t xml:space="preserve">9.86789512634277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83233642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77899551391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44117450714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21003723144531</t>
+    <t xml:space="preserve">9.83233547210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77899646759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44117546081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21003532409668</t>
   </si>
   <si>
     <t xml:space="preserve">9.58341598510742</t>
@@ -1688,13 +1688,13 @@
     <t xml:space="preserve">9.67231559753418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8501148223877</t>
+    <t xml:space="preserve">9.85011577606201</t>
   </si>
   <si>
     <t xml:space="preserve">10.0990362167358</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0279159545898</t>
+    <t xml:space="preserve">10.0279150009155</t>
   </si>
   <si>
     <t xml:space="preserve">9.992356300354</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">10.0101356506348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76121520996094</t>
+    <t xml:space="preserve">9.76121616363525</t>
   </si>
   <si>
     <t xml:space="preserve">9.88567543029785</t>
@@ -1712,28 +1712,28 @@
     <t xml:space="preserve">10.2234954833984</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4368543624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6679964065552</t>
+    <t xml:space="preserve">10.4368553161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6679954528809</t>
   </si>
   <si>
     <t xml:space="preserve">11.414755821228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3614158630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3080759048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4325351715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6814556121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8948154449463</t>
+    <t xml:space="preserve">11.3614149093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3080749511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4325332641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6814546585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8948163986206</t>
   </si>
   <si>
     <t xml:space="preserve">11.9659357070923</t>
@@ -1742,10 +1742,10 @@
     <t xml:space="preserve">12.1437349319458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.628116607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4001131057739</t>
+    <t xml:space="preserve">11.6281147003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4001150131226</t>
   </si>
   <si>
     <t xml:space="preserve">11.6715440750122</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">12.1239290237427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7982120513916</t>
+    <t xml:space="preserve">11.7982130050659</t>
   </si>
   <si>
     <t xml:space="preserve">12.1782159805298</t>
@@ -1769,40 +1769,40 @@
     <t xml:space="preserve">12.3229789733887</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9925088882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8296518325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7391729354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7753639221191</t>
+    <t xml:space="preserve">12.9925098419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8296508789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7391738891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7753648757935</t>
   </si>
   <si>
     <t xml:space="preserve">12.3953609466553</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2867889404297</t>
+    <t xml:space="preserve">12.2867879867554</t>
   </si>
   <si>
     <t xml:space="preserve">12.6306009292603</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4496479034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2144069671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1058349609375</t>
+    <t xml:space="preserve">12.4496469497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2144060134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1058359146118</t>
   </si>
   <si>
     <t xml:space="preserve">11.8705930709839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9067850112915</t>
+    <t xml:space="preserve">11.9067859649658</t>
   </si>
   <si>
     <t xml:space="preserve">11.4724950790405</t>
@@ -1817,7 +1817,7 @@
     <t xml:space="preserve">11.8524990081787</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0877380371094</t>
+    <t xml:space="preserve">12.0877389907837</t>
   </si>
   <si>
     <t xml:space="preserve">11.8344030380249</t>
@@ -1826,46 +1826,46 @@
     <t xml:space="preserve">11.8886890411377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4363040924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3277320861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734451293945</t>
+    <t xml:space="preserve">11.4363031387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3277311325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734460830688</t>
   </si>
   <si>
     <t xml:space="preserve">11.1829681396484</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1648731231689</t>
+    <t xml:space="preserve">11.1648721694946</t>
   </si>
   <si>
     <t xml:space="preserve">10.8391551971436</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6401052474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6762962341309</t>
+    <t xml:space="preserve">10.6401062011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6762971878052</t>
   </si>
   <si>
     <t xml:space="preserve">10.5134372711182</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9115381240845</t>
+    <t xml:space="preserve">10.9115371704102</t>
   </si>
   <si>
     <t xml:space="preserve">11.291540145874</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1467771530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7667722702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1105871200562</t>
+    <t xml:space="preserve">11.1467761993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.766773223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1105861663818</t>
   </si>
   <si>
     <t xml:space="preserve">11.1286821365356</t>
@@ -1874,40 +1874,40 @@
     <t xml:space="preserve">10.6220092773438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0020132064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6039152145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4953422546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2781963348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3143882751465</t>
+    <t xml:space="preserve">11.0020141601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6039142608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.495343208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2781972885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3143863677979</t>
   </si>
   <si>
     <t xml:space="preserve">9.89819240570068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93438339233398</t>
+    <t xml:space="preserve">9.9343843460083</t>
   </si>
   <si>
     <t xml:space="preserve">9.80771636962891</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6810474395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95247936248779</t>
+    <t xml:space="preserve">9.68104839324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95248031616211</t>
   </si>
   <si>
     <t xml:space="preserve">10.2420063018799</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4772462844849</t>
+    <t xml:space="preserve">10.4772472381592</t>
   </si>
   <si>
     <t xml:space="preserve">10.3867692947388</t>
@@ -1916,55 +1916,55 @@
     <t xml:space="preserve">10.4410562515259</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55438137054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1153392791748</t>
+    <t xml:space="preserve">9.55438041687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1153383255005</t>
   </si>
   <si>
     <t xml:space="preserve">10.3505783081055</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4048643112183</t>
+    <t xml:space="preserve">10.4048652648926</t>
   </si>
   <si>
     <t xml:space="preserve">10.7486782073975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0201091766357</t>
+    <t xml:space="preserve">11.0201082229614</t>
   </si>
   <si>
     <t xml:space="preserve">10.857250213623</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8753461837769</t>
+    <t xml:space="preserve">10.8753452301025</t>
   </si>
   <si>
     <t xml:space="preserve">10.5858192443848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8029632568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7124872207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7848691940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2372541427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3096361160278</t>
+    <t xml:space="preserve">10.8029642105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7124862670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7848701477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2372550964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3096351623535</t>
   </si>
   <si>
     <t xml:space="preserve">11.4543991088867</t>
   </si>
   <si>
-    <t xml:space="preserve">11.725830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9972610473633</t>
+    <t xml:space="preserve">11.7258291244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9972620010376</t>
   </si>
   <si>
     <t xml:space="preserve">12.160120010376</t>
@@ -1988,16 +1988,16 @@
     <t xml:space="preserve">10.9658231735229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1877212524414</t>
+    <t xml:space="preserve">10.1877202987671</t>
   </si>
   <si>
     <t xml:space="preserve">9.98867034912109</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0429573059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91628837585449</t>
+    <t xml:space="preserve">10.0429563522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91628932952881</t>
   </si>
   <si>
     <t xml:space="preserve">10.1696243286133</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">10.332483291626</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2239122390747</t>
+    <t xml:space="preserve">10.2239112854004</t>
   </si>
   <si>
     <t xml:space="preserve">10.097243309021</t>
@@ -2024,10 +2024,10 @@
     <t xml:space="preserve">10.0610513687134</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0791482925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1515302658081</t>
+    <t xml:space="preserve">10.0791492462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1515293121338</t>
   </si>
   <si>
     <t xml:space="preserve">11.056300163269</t>
@@ -2036,25 +2036,25 @@
     <t xml:space="preserve">10.8934412002563</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5496273040771</t>
+    <t xml:space="preserve">10.5496282577515</t>
   </si>
   <si>
     <t xml:space="preserve">10.3686742782593</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82581043243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77152538299561</t>
+    <t xml:space="preserve">9.8258113861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77152633666992</t>
   </si>
   <si>
     <t xml:space="preserve">9.699143409729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51819133758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71723937988281</t>
+    <t xml:space="preserve">9.51819038391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7172384262085</t>
   </si>
   <si>
     <t xml:space="preserve">9.42771244049072</t>
@@ -2069,13 +2069,13 @@
     <t xml:space="preserve">11.9791669845581</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4677419662476</t>
+    <t xml:space="preserve">12.4677429199219</t>
   </si>
   <si>
     <t xml:space="preserve">12.3772659301758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3820180892944</t>
+    <t xml:space="preserve">11.3820171356201</t>
   </si>
   <si>
     <t xml:space="preserve">11.5629720687866</t>
@@ -2084,19 +2084,19 @@
     <t xml:space="preserve">11.6172580718994</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0924911499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6943912506104</t>
+    <t xml:space="preserve">11.0924921035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6943922042847</t>
   </si>
   <si>
     <t xml:space="preserve">9.62676239013672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8034200668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68580055236816</t>
+    <t xml:space="preserve">8.80342102050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68580150604248</t>
   </si>
   <si>
     <t xml:space="preserve">8.43246364593506</t>
@@ -2111,13 +2111,13 @@
     <t xml:space="preserve">7.24721527099609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18388080596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58673286437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65006637573242</t>
+    <t xml:space="preserve">7.18388032913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58673191070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65006589889526</t>
   </si>
   <si>
     <t xml:space="preserve">6.96673583984375</t>
@@ -2129,31 +2129,31 @@
     <t xml:space="preserve">7.16578531265259</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05721282958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28340578079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60912227630615</t>
+    <t xml:space="preserve">7.057213306427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28340625762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60912322998047</t>
   </si>
   <si>
     <t xml:space="preserve">7.76293468475342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3419885635376</t>
+    <t xml:space="preserve">8.34198760986328</t>
   </si>
   <si>
     <t xml:space="preserve">8.04341316223145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61341857910156</t>
+    <t xml:space="preserve">8.61341953277588</t>
   </si>
   <si>
     <t xml:space="preserve">8.41436958312988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25150966644287</t>
+    <t xml:space="preserve">8.2515115737915</t>
   </si>
   <si>
     <t xml:space="preserve">8.93008899688721</t>
@@ -2162,46 +2162,46 @@
     <t xml:space="preserve">9.35533046722412</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04770946502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26485347747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50009441375732</t>
+    <t xml:space="preserve">9.04770851135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26485443115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50009346008301</t>
   </si>
   <si>
     <t xml:space="preserve">9.86200141906738</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2191581726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9839191436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6582012176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9705753326416</t>
+    <t xml:space="preserve">11.2191572189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9839200973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6582002639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97057628631592</t>
   </si>
   <si>
     <t xml:space="preserve">10.2058143615723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84390735626221</t>
+    <t xml:space="preserve">9.84390640258789</t>
   </si>
   <si>
     <t xml:space="preserve">10.4591512680054</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9296312332153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7305822372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8210601806641</t>
+    <t xml:space="preserve">10.9296321868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7305812835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8210592269897</t>
   </si>
   <si>
     <t xml:space="preserve">12.0696439743042</t>
@@ -2222,22 +2222,22 @@
     <t xml:space="preserve">12.7934608459473</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4315519332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.594409942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6486968994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7210788726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8658428192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1553688049316</t>
+    <t xml:space="preserve">12.4315509796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5944108963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6486959457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7210779190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8658418655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1553678512573</t>
   </si>
   <si>
     <t xml:space="preserve">13.0286998748779</t>
@@ -2252,16 +2252,16 @@
     <t xml:space="preserve">13.0829877853394</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3725128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3544187545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4534873962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2496852874756</t>
+    <t xml:space="preserve">13.3725137710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3544178009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4534845352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.249683380127</t>
   </si>
   <si>
     <t xml:space="preserve">16.2858753204346</t>
@@ -2273,19 +2273,19 @@
     <t xml:space="preserve">16.6477832794189</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8334894180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0687313079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8696804046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9239692687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9058713912964</t>
+    <t xml:space="preserve">15.8334903717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0687294006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8696823120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9239683151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.905873298645</t>
   </si>
   <si>
     <t xml:space="preserve">15.8515872955322</t>
@@ -2294,49 +2294,49 @@
     <t xml:space="preserve">16.0144443511963</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7972984313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2677803039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0325393676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7792043685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7249183654785</t>
+    <t xml:space="preserve">15.7972965240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2677783966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0325374603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.779203414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7249174118042</t>
   </si>
   <si>
     <t xml:space="preserve">16.4125423431396</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8153944015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9420623779297</t>
+    <t xml:space="preserve">15.8153953552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.942063331604</t>
   </si>
   <si>
     <t xml:space="preserve">15.6344404220581</t>
   </si>
   <si>
-    <t xml:space="preserve">16.104923248291</t>
+    <t xml:space="preserve">16.1049213409424</t>
   </si>
   <si>
     <t xml:space="preserve">15.9601583480835</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6887264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6163463592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8925275802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6525344848633</t>
+    <t xml:space="preserve">15.6887273788452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6163454055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8925285339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.652533531189</t>
   </si>
   <si>
     <t xml:space="preserve">15.3630075454712</t>
@@ -2345,22 +2345,22 @@
     <t xml:space="preserve">15.4896793365479</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1458644866943</t>
+    <t xml:space="preserve">15.1458654403687</t>
   </si>
   <si>
     <t xml:space="preserve">15.0372915267944</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7430124282837</t>
+    <t xml:space="preserve">15.7430114746094</t>
   </si>
   <si>
     <t xml:space="preserve">14.8201465606689</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2906274795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5887470245361</t>
+    <t xml:space="preserve">15.2906284332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5887451171875</t>
   </si>
   <si>
     <t xml:space="preserve">17.7696990966797</t>
@@ -2375,58 +2375,58 @@
     <t xml:space="preserve">18.2763710021973</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0411319732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4258880615234</t>
+    <t xml:space="preserve">18.041130065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4258861541748</t>
   </si>
   <si>
     <t xml:space="preserve">17.7335090637207</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2992191314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0458850860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0277862548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7020683288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0096893310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4077930450439</t>
+    <t xml:space="preserve">17.2992210388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0458831787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0277881622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7020702362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0096912384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4077892303467</t>
   </si>
   <si>
     <t xml:space="preserve">18.5025653839111</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1406555175781</t>
+    <t xml:space="preserve">18.1406536102295</t>
   </si>
   <si>
     <t xml:space="preserve">17.96875</t>
   </si>
   <si>
-    <t xml:space="preserve">17.49827003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9868450164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5930404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1544532775879</t>
+    <t xml:space="preserve">17.4982681274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9868431091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5930423736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1544551849365</t>
   </si>
   <si>
     <t xml:space="preserve">17.2449321746826</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1182670593262</t>
+    <t xml:space="preserve">17.1182632446289</t>
   </si>
   <si>
     <t xml:space="preserve">16.8106422424316</t>
@@ -2438,10 +2438,10 @@
     <t xml:space="preserve">16.973503112793</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9192180633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0639801025391</t>
+    <t xml:space="preserve">16.9192161560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0639781951904</t>
   </si>
   <si>
     <t xml:space="preserve">16.8468341827393</t>
@@ -2450,25 +2450,25 @@
     <t xml:space="preserve">16.9011211395264</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3173141479492</t>
+    <t xml:space="preserve">17.3173160552979</t>
   </si>
   <si>
     <t xml:space="preserve">17.2087421417236</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2268371582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.366849899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4573268890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6382789611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7287559509277</t>
+    <t xml:space="preserve">17.2268390655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3668479919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4573249816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6382808685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7287578582764</t>
   </si>
   <si>
     <t xml:space="preserve">18.9549503326416</t>
@@ -2480,16 +2480,16 @@
     <t xml:space="preserve">19.6335296630859</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6787662506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5430507659912</t>
+    <t xml:space="preserve">19.678768157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5430526733398</t>
   </si>
   <si>
     <t xml:space="preserve">19.0454254150391</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0001888275146</t>
+    <t xml:space="preserve">19.000186920166</t>
   </si>
   <si>
     <t xml:space="preserve">19.316858291626</t>
@@ -2504,28 +2504,28 @@
     <t xml:space="preserve">19.0906658172607</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6835155487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0954189300537</t>
+    <t xml:space="preserve">18.6835193634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0954170227051</t>
   </si>
   <si>
     <t xml:space="preserve">18.004940032959</t>
   </si>
   <si>
-    <t xml:space="preserve">17.570650100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8239860534668</t>
+    <t xml:space="preserve">17.5706520080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8239879608154</t>
   </si>
   <si>
     <t xml:space="preserve">17.6430320739746</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8058910369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2716178894043</t>
+    <t xml:space="preserve">17.8058929443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2716197967529</t>
   </si>
   <si>
     <t xml:space="preserve">19.1811447143555</t>
@@ -2534,22 +2534,22 @@
     <t xml:space="preserve">20.26686668396</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4930610656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9906845092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5835380554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3573436737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9049587249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7692451477051</t>
+    <t xml:space="preserve">20.4930629730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.990686416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5835361480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3573455810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9049606323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7692432403564</t>
   </si>
   <si>
     <t xml:space="preserve">20.7192516326904</t>
@@ -2561,7 +2561,7 @@
     <t xml:space="preserve">19.2263832092285</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4525737762451</t>
+    <t xml:space="preserve">19.4525718688965</t>
   </si>
   <si>
     <t xml:space="preserve">19.4073352813721</t>
@@ -2570,16 +2570,16 @@
     <t xml:space="preserve">17.6249370574951</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7877960205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4978103637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0859146118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1311511993408</t>
+    <t xml:space="preserve">17.7877941131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4978122711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0859127044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1311492919922</t>
   </si>
   <si>
     <t xml:space="preserve">19.8597221374512</t>
@@ -2591,22 +2591,22 @@
     <t xml:space="preserve">21.0359230041504</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8097286224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.628776550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.312105178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4478244781494</t>
+    <t xml:space="preserve">20.8097305297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6287727355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3121070861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4478225708008</t>
   </si>
   <si>
     <t xml:space="preserve">20.8821125030518</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2802104949951</t>
+    <t xml:space="preserve">21.2802124023438</t>
   </si>
   <si>
     <t xml:space="preserve">21.3344974517822</t>
@@ -2618,31 +2618,31 @@
     <t xml:space="preserve">21.6602153778076</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1668872833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6192722320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8726081848145</t>
+    <t xml:space="preserve">22.1668891906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.619270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8726062774658</t>
   </si>
   <si>
     <t xml:space="preserve">23.9040470123291</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7821292877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8592624664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0040264129639</t>
+    <t xml:space="preserve">22.7821311950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8592643737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0040283203125</t>
   </si>
   <si>
     <t xml:space="preserve">22.2573642730713</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4745082855225</t>
+    <t xml:space="preserve">22.4745101928711</t>
   </si>
   <si>
     <t xml:space="preserve">22.1126003265381</t>
@@ -2663,13 +2663,13 @@
     <t xml:space="preserve">22.4021282196045</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3525924682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2621173858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0945053100586</t>
+    <t xml:space="preserve">21.3525943756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2621154785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.09450340271</t>
   </si>
   <si>
     <t xml:space="preserve">22.583080291748</t>
@@ -2678,13 +2678,13 @@
     <t xml:space="preserve">23.0354652404785</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0173721313477</t>
+    <t xml:space="preserve">23.017370223999</t>
   </si>
   <si>
     <t xml:space="preserve">23.3611831665039</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2707080841064</t>
+    <t xml:space="preserve">23.2707042694092</t>
   </si>
   <si>
     <t xml:space="preserve">25.0440578460693</t>
@@ -2693,13 +2693,13 @@
     <t xml:space="preserve">24.7726249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9716777801514</t>
+    <t xml:space="preserve">24.9716758728027</t>
   </si>
   <si>
     <t xml:space="preserve">25.0621528625488</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9126358032227</t>
+    <t xml:space="preserve">25.9126377105713</t>
   </si>
   <si>
     <t xml:space="preserve">26.2383556365967</t>
@@ -2714,94 +2714,94 @@
     <t xml:space="preserve">26.5852794647217</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6583156585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8226470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9504623413086</t>
+    <t xml:space="preserve">26.6583137512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8226451873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.95046043396</t>
   </si>
   <si>
     <t xml:space="preserve">27.5712699890137</t>
   </si>
   <si>
-    <t xml:space="preserve">27.626049041748</t>
+    <t xml:space="preserve">27.6260471343994</t>
   </si>
   <si>
     <t xml:space="preserve">28.064266204834</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2833766937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8171443939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5980319976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.958963394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1275482177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.652811050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1092910766602</t>
+    <t xml:space="preserve">28.283374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8171405792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.598030090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9589614868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1275463104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6528091430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1092891693115</t>
   </si>
   <si>
     <t xml:space="preserve">29.9632148742676</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4014358520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2188396453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2961292266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8213901519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1683197021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2371006011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4154415130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8536605834961</t>
+    <t xml:space="preserve">30.4014320373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2188415527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2961330413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8213920593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1683158874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2370986938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4154434204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8536624908447</t>
   </si>
   <si>
     <t xml:space="preserve">29.178071975708</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1458072662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7075881958008</t>
+    <t xml:space="preserve">30.145809173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7075862884521</t>
   </si>
   <si>
     <t xml:space="preserve">30.0545101165771</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8664131164551</t>
+    <t xml:space="preserve">32.8664169311523</t>
   </si>
   <si>
     <t xml:space="preserve">34.5462532043457</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0532569885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0855293273926</t>
+    <t xml:space="preserve">34.0532608032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0855255126953</t>
   </si>
   <si>
     <t xml:space="preserve">33.7245903015137</t>
@@ -2813,16 +2813,16 @@
     <t xml:space="preserve">33.5785179138184</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4872245788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7976303100586</t>
+    <t xml:space="preserve">33.4872283935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7976341247559</t>
   </si>
   <si>
     <t xml:space="preserve">33.1402969360352</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2863731384277</t>
+    <t xml:space="preserve">33.286376953125</t>
   </si>
   <si>
     <t xml:space="preserve">32.2273445129395</t>
@@ -2831,43 +2831,43 @@
     <t xml:space="preserve">32.8846740722656</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7568664550781</t>
+    <t xml:space="preserve">32.7568626403809</t>
   </si>
   <si>
     <t xml:space="preserve">32.6473045349121</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0307502746582</t>
+    <t xml:space="preserve">33.0307464599609</t>
   </si>
   <si>
     <t xml:space="preserve">32.7751235961914</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4099349975586</t>
+    <t xml:space="preserve">32.4099388122559</t>
   </si>
   <si>
     <t xml:space="preserve">32.6655654907227</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6923294067383</t>
+    <t xml:space="preserve">34.692325592041</t>
   </si>
   <si>
     <t xml:space="preserve">35.605281829834</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2401008605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8791656494141</t>
+    <t xml:space="preserve">35.2400970458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8791694641113</t>
   </si>
   <si>
     <t xml:space="preserve">35.4774703979492</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0940284729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5870246887207</t>
+    <t xml:space="preserve">35.0940246582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5870208740234</t>
   </si>
   <si>
     <t xml:space="preserve">35.7878761291504</t>
@@ -2876,19 +2876,19 @@
     <t xml:space="preserve">36.0435028076172</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8469085693359</t>
+    <t xml:space="preserve">36.8469047546387</t>
   </si>
   <si>
     <t xml:space="preserve">38.9101829528809</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4354476928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4944763183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3849182128906</t>
+    <t xml:space="preserve">38.4354438781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4944725036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3849220275879</t>
   </si>
   <si>
     <t xml:space="preserve">39.220588684082</t>
@@ -2897,22 +2897,22 @@
     <t xml:space="preserve">39.1292953491211</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1980743408203</t>
+    <t xml:space="preserve">38.1980781555176</t>
   </si>
   <si>
     <t xml:space="preserve">37.6137886047363</t>
   </si>
   <si>
-    <t xml:space="preserve">37.248607635498</t>
+    <t xml:space="preserve">37.2486000061035</t>
   </si>
   <si>
     <t xml:space="preserve">37.0660095214844</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2668647766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7008323669434</t>
+    <t xml:space="preserve">37.2668609619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7008285522461</t>
   </si>
   <si>
     <t xml:space="preserve">37.2120819091797</t>
@@ -2921,43 +2921,43 @@
     <t xml:space="preserve">37.559009552002</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0154876708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6503028869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6235389709473</t>
+    <t xml:space="preserve">38.0154914855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6503067016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6235466003418</t>
   </si>
   <si>
     <t xml:space="preserve">33.2315979003906</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9942245483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3594169616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0490074157715</t>
+    <t xml:space="preserve">32.9942283630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3594093322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0490036010742</t>
   </si>
   <si>
     <t xml:space="preserve">34.7836227416992</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3819236755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8931770324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9577102661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.63330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.513988494873</t>
+    <t xml:space="preserve">34.3819198608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.893180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9577140808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6332969665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5139923095703</t>
   </si>
   <si>
     <t xml:space="preserve">36.4817161560059</t>
@@ -2966,7 +2966,7 @@
     <t xml:space="preserve">36.3173866271973</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6095314025879</t>
+    <t xml:space="preserve">36.6095352172852</t>
   </si>
   <si>
     <t xml:space="preserve">37.7781181335449</t>
@@ -2978,13 +2978,13 @@
     <t xml:space="preserve">39.2023277282715</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7190895080566</t>
+    <t xml:space="preserve">36.7190933227539</t>
   </si>
   <si>
     <t xml:space="preserve">35.8426513671875</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9662132263184</t>
+    <t xml:space="preserve">34.9662094116211</t>
   </si>
   <si>
     <t xml:space="preserve">35.1488037109375</t>
@@ -2996,10 +2996,10 @@
     <t xml:space="preserve">37.8876724243164</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5267448425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8006248474121</t>
+    <t xml:space="preserve">38.526741027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8006286621094</t>
   </si>
   <si>
     <t xml:space="preserve">37.6685638427734</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">35.4226913452148</t>
   </si>
   <si>
-    <t xml:space="preserve">35.258358001709</t>
+    <t xml:space="preserve">35.2583618164062</t>
   </si>
   <si>
     <t xml:space="preserve">34.9114379882812</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">34.3636627197266</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8341522216797</t>
+    <t xml:space="preserve">33.8341484069824</t>
   </si>
   <si>
     <t xml:space="preserve">33.5967788696289</t>
@@ -3029,25 +3029,25 @@
     <t xml:space="preserve">34.2175903320312</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9071807861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3131332397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7105827331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3454055786133</t>
+    <t xml:space="preserve">33.9071846008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3131370544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7105865478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.345401763916</t>
   </si>
   <si>
     <t xml:space="preserve">34.0715179443359</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1950798034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6150436401367</t>
+    <t xml:space="preserve">33.1950759887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6150398254395</t>
   </si>
   <si>
     <t xml:space="preserve">33.9254455566406</t>
@@ -3059,10 +3059,10 @@
     <t xml:space="preserve">34.6192893981934</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5827751159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7288436889648</t>
+    <t xml:space="preserve">34.5827713012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7288513183594</t>
   </si>
   <si>
     <t xml:space="preserve">35.0027313232422</t>
@@ -3071,16 +3071,16 @@
     <t xml:space="preserve">34.8384017944336</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8749198913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5377502441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1725730895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1360473632812</t>
+    <t xml:space="preserve">34.8749160766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5377464294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1725692749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1360511779785</t>
   </si>
   <si>
     <t xml:space="preserve">29.4519596099854</t>
@@ -3089,19 +3089,19 @@
     <t xml:space="preserve">29.8901805877686</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1640644073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4294471740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1007843017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6808242797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9954833984375</t>
+    <t xml:space="preserve">30.1640682220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4294490814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1007862091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6808223724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9954814910889</t>
   </si>
   <si>
     <t xml:space="preserve">29.2693691253662</t>
@@ -3110,10 +3110,10 @@
     <t xml:space="preserve">28.6850757598877</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9687213897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8956813812256</t>
+    <t xml:space="preserve">26.9687194824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8956832885742</t>
   </si>
   <si>
     <t xml:space="preserve">27.8451557159424</t>
@@ -3122,13 +3122,13 @@
     <t xml:space="preserve">27.9729690551758</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6668186187744</t>
+    <t xml:space="preserve">28.6668167114258</t>
   </si>
   <si>
     <t xml:space="preserve">29.1232967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9224452972412</t>
+    <t xml:space="preserve">28.9224472045898</t>
   </si>
   <si>
     <t xml:space="preserve">27.6077880859375</t>
@@ -3137,22 +3137,22 @@
     <t xml:space="preserve">27.7538623809814</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3479099273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.544506072998</t>
+    <t xml:space="preserve">26.3479080200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5445079803467</t>
   </si>
   <si>
     <t xml:space="preserve">26.7496089935303</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7861289978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5670204162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9547138214111</t>
+    <t xml:space="preserve">26.7861309051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5670185089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9547119140625</t>
   </si>
   <si>
     <t xml:space="preserve">27.4251976013184</t>
@@ -3167,13 +3167,13 @@
     <t xml:space="preserve">26.731351852417</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4069385528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9912300109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6948337554932</t>
+    <t xml:space="preserve">27.4069404602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9912281036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6948318481445</t>
   </si>
   <si>
     <t xml:space="preserve">27.4434566497803</t>
@@ -3185,25 +3185,25 @@
     <t xml:space="preserve">23.5542640686035</t>
   </si>
   <si>
-    <t xml:space="preserve">24.70458984375</t>
+    <t xml:space="preserve">24.7045879364014</t>
   </si>
   <si>
     <t xml:space="preserve">23.097785949707</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0022392272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7466125488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7423572540283</t>
+    <t xml:space="preserve">22.0022411346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7466106414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.742359161377</t>
   </si>
   <si>
     <t xml:space="preserve">22.6047897338867</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8744258880615</t>
+    <t xml:space="preserve">21.8744239807129</t>
   </si>
   <si>
     <t xml:space="preserve">22.5134944915771</t>
@@ -3212,16 +3212,16 @@
     <t xml:space="preserve">23.1525630950928</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2073421478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5402565002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6680717468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8689193725586</t>
+    <t xml:space="preserve">23.2073402404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5402545928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6680698394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8689212799072</t>
   </si>
   <si>
     <t xml:space="preserve">24.4489631652832</t>
@@ -3233,31 +3233,31 @@
     <t xml:space="preserve">24.5585155487061</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0289993286133</t>
+    <t xml:space="preserve">24.0290031433105</t>
   </si>
   <si>
     <t xml:space="preserve">24.138557434082</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0472621917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3984317779541</t>
+    <t xml:space="preserve">24.0472602844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3984336853027</t>
   </si>
   <si>
     <t xml:space="preserve">25.4166946411133</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2115917205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.083776473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8098907470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3351554870605</t>
+    <t xml:space="preserve">24.2115936279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0837783813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8098926544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3351535797119</t>
   </si>
   <si>
     <t xml:space="preserve">22.4221992492676</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">22.2761249542236</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9109439849854</t>
+    <t xml:space="preserve">21.9109420776367</t>
   </si>
   <si>
     <t xml:space="preserve">22.2213478088379</t>
@@ -3281,10 +3281,10 @@
     <t xml:space="preserve">21.8379077911377</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0935363769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8239002227783</t>
+    <t xml:space="preserve">22.0935344696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8238983154297</t>
   </si>
   <si>
     <t xml:space="preserve">21.5457611083984</t>
@@ -3293,13 +3293,13 @@
     <t xml:space="preserve">21.07102394104</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9657211303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1988353729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2718715667725</t>
+    <t xml:space="preserve">21.9657192230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1988372802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2718734741211</t>
   </si>
   <si>
     <t xml:space="preserve">20.8884315490723</t>
@@ -3317,16 +3317,16 @@
     <t xml:space="preserve">19.8659229278564</t>
   </si>
   <si>
-    <t xml:space="preserve">19.957218170166</t>
+    <t xml:space="preserve">19.9572162628174</t>
   </si>
   <si>
     <t xml:space="preserve">19.902437210083</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2493648529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9614696502686</t>
+    <t xml:space="preserve">20.2493629455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9614677429199</t>
   </si>
   <si>
     <t xml:space="preserve">20.8519153594971</t>
@@ -3338,7 +3338,7 @@
     <t xml:space="preserve">21.0162467956543</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3449096679688</t>
+    <t xml:space="preserve">21.3449115753174</t>
   </si>
   <si>
     <t xml:space="preserve">20.3954372406006</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">20.523250579834</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6693229675293</t>
+    <t xml:space="preserve">20.6693248748779</t>
   </si>
   <si>
     <t xml:space="preserve">22.1300525665283</t>
@@ -3362,25 +3362,25 @@
     <t xml:space="preserve">23.5177459716797</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7368545532227</t>
+    <t xml:space="preserve">23.7368564605713</t>
   </si>
   <si>
     <t xml:space="preserve">23.0533809661865</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9240760803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7393531799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8711585998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.744348526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6914310455322</t>
+    <t xml:space="preserve">22.9240741729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7393550872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8711566925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7443466186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6914291381836</t>
   </si>
   <si>
     <t xml:space="preserve">19.2850399017334</t>
@@ -3398,25 +3398,25 @@
     <t xml:space="preserve">21.3539333343506</t>
   </si>
   <si>
-    <t xml:space="preserve">21.316987991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7603244781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6494884490967</t>
+    <t xml:space="preserve">21.3169898986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7603225708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6494903564453</t>
   </si>
   <si>
     <t xml:space="preserve">21.4278240203857</t>
   </si>
   <si>
-    <t xml:space="preserve">21.55712890625</t>
+    <t xml:space="preserve">21.5571269989014</t>
   </si>
   <si>
     <t xml:space="preserve">21.7972679138184</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5596256256104</t>
+    <t xml:space="preserve">20.559627532959</t>
   </si>
   <si>
     <t xml:space="preserve">20.7812938690186</t>
@@ -3425,25 +3425,25 @@
     <t xml:space="preserve">20.3379592895508</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9130954742432</t>
+    <t xml:space="preserve">19.9130973815918</t>
   </si>
   <si>
     <t xml:space="preserve">20.9475440979004</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0374050140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4992141723633</t>
+    <t xml:space="preserve">22.0374088287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4992122650146</t>
   </si>
   <si>
     <t xml:space="preserve">21.6679611206055</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4647674560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8182392120361</t>
+    <t xml:space="preserve">21.4647655487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8182373046875</t>
   </si>
   <si>
     <t xml:space="preserve">20.1532363891602</t>
@@ -3455,7 +3455,7 @@
     <t xml:space="preserve">20.4487915039062</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3908767700195</t>
+    <t xml:space="preserve">21.3908786773682</t>
   </si>
   <si>
     <t xml:space="preserve">21.0029602050781</t>
@@ -3470,7 +3470,7 @@
     <t xml:space="preserve">22.3883800506592</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2960205078125</t>
+    <t xml:space="preserve">22.2960186004639</t>
   </si>
   <si>
     <t xml:space="preserve">22.5361576080322</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">21.5017127990723</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7787933349609</t>
+    <t xml:space="preserve">21.7787952423096</t>
   </si>
   <si>
     <t xml:space="preserve">21.7233791351318</t>
@@ -3494,22 +3494,22 @@
     <t xml:space="preserve">21.6864337921143</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8896312713623</t>
+    <t xml:space="preserve">21.889627456665</t>
   </si>
   <si>
     <t xml:space="preserve">21.704906463623</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6519889831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0424022674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0054569244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1162929534912</t>
+    <t xml:space="preserve">20.6519870758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0424041748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0054588317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1162910461426</t>
   </si>
   <si>
     <t xml:space="preserve">20.0978202819824</t>
@@ -3518,25 +3518,25 @@
     <t xml:space="preserve">19.9500427246094</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7468452453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5436515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8417072296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.472261428833</t>
+    <t xml:space="preserve">19.74684715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5436534881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8417053222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4722595214844</t>
   </si>
   <si>
     <t xml:space="preserve">19.1926784515381</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5830936431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2413558959961</t>
+    <t xml:space="preserve">18.5830955505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2413578033447</t>
   </si>
   <si>
     <t xml:space="preserve">18.0566349029541</t>
@@ -3548,25 +3548,25 @@
     <t xml:space="preserve">17.4562854766846</t>
   </si>
   <si>
-    <t xml:space="preserve">17.622537612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6989250183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5326728820801</t>
+    <t xml:space="preserve">17.6225357055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6989231109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5326747894287</t>
   </si>
   <si>
     <t xml:space="preserve">16.8374652862549</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9852428436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2807998657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0037174224854</t>
+    <t xml:space="preserve">16.9852447509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.280797958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0037155151367</t>
   </si>
   <si>
     <t xml:space="preserve">17.6779537200928</t>
@@ -3578,31 +3578,31 @@
     <t xml:space="preserve">17.8164958953857</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5855922698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5024681091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0683670043945</t>
+    <t xml:space="preserve">17.5855941772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5024700164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0683689117432</t>
   </si>
   <si>
     <t xml:space="preserve">17.234619140625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2530918121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9390621185303</t>
+    <t xml:space="preserve">17.2530937194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9390640258789</t>
   </si>
   <si>
     <t xml:space="preserve">16.8005218505859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8836460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4285774230957</t>
+    <t xml:space="preserve">16.8836479187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4285793304443</t>
   </si>
   <si>
     <t xml:space="preserve">17.7056617736816</t>
@@ -3614,10 +3614,10 @@
     <t xml:space="preserve">17.7333698272705</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3429565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4697608947754</t>
+    <t xml:space="preserve">18.3429546356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.469762802124</t>
   </si>
   <si>
     <t xml:space="preserve">19.5805969238281</t>
@@ -3644,19 +3644,19 @@
     <t xml:space="preserve">19.0079574584961</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0239315032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8392086029053</t>
+    <t xml:space="preserve">20.0239295959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8392066955566</t>
   </si>
   <si>
     <t xml:space="preserve">20.8736553192139</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9080982208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3329620361328</t>
+    <t xml:space="preserve">21.9081001281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3329639434814</t>
   </si>
   <si>
     <t xml:space="preserve">20.9105987548828</t>
@@ -3668,10 +3668,10 @@
     <t xml:space="preserve">21.3354625701904</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2430992126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9265727996826</t>
+    <t xml:space="preserve">21.2431011199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9265747070312</t>
   </si>
   <si>
     <t xml:space="preserve">21.7418518066406</t>
@@ -3695,7 +3695,7 @@
     <t xml:space="preserve">20.3933753967285</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2455978393555</t>
+    <t xml:space="preserve">20.2455997467041</t>
   </si>
   <si>
     <t xml:space="preserve">19.931568145752</t>
@@ -3716,10 +3716,10 @@
     <t xml:space="preserve">22.831714630127</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2750492095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6075496673584</t>
+    <t xml:space="preserve">23.2750511169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6075477600098</t>
   </si>
   <si>
     <t xml:space="preserve">23.3304653167725</t>
@@ -3740,19 +3740,19 @@
     <t xml:space="preserve">23.127269744873</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7553272247314</t>
+    <t xml:space="preserve">23.7553253173828</t>
   </si>
   <si>
     <t xml:space="preserve">23.8846340179443</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4782447814941</t>
+    <t xml:space="preserve">23.4782428741455</t>
   </si>
   <si>
     <t xml:space="preserve">23.1087989807129</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9979629516602</t>
+    <t xml:space="preserve">22.9979648590088</t>
   </si>
   <si>
     <t xml:space="preserve">23.0164375305176</t>
@@ -3770,19 +3770,19 @@
     <t xml:space="preserve">24.1247730255127</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5151882171631</t>
+    <t xml:space="preserve">23.5151863098145</t>
   </si>
   <si>
     <t xml:space="preserve">22.8686580657959</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4597702026367</t>
+    <t xml:space="preserve">23.4597721099854</t>
   </si>
   <si>
     <t xml:space="preserve">22.9056015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8132438659668</t>
+    <t xml:space="preserve">22.8132419586182</t>
   </si>
   <si>
     <t xml:space="preserve">22.6285209655762</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">22.2036571502686</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0004634857178</t>
+    <t xml:space="preserve">22.0004615783691</t>
   </si>
   <si>
     <t xml:space="preserve">22.0558776855469</t>
@@ -3806,10 +3806,10 @@
     <t xml:space="preserve">22.2590751647949</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8342132568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0928249359131</t>
+    <t xml:space="preserve">21.8342113494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0928230285645</t>
   </si>
   <si>
     <t xml:space="preserve">22.2406005859375</t>
@@ -3818,13 +3818,13 @@
     <t xml:space="preserve">21.2615718841553</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3404560089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.656982421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1187896728516</t>
+    <t xml:space="preserve">19.3404579162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6569843292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1187915802002</t>
   </si>
   <si>
     <t xml:space="preserve">18.5646228790283</t>
@@ -3839,7 +3839,7 @@
     <t xml:space="preserve">18.2690658569336</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5092067718506</t>
+    <t xml:space="preserve">18.509204864502</t>
   </si>
   <si>
     <t xml:space="preserve">18.8232326507568</t>
@@ -3848,7 +3848,7 @@
     <t xml:space="preserve">18.5461502075195</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7123985290527</t>
+    <t xml:space="preserve">18.7124004364014</t>
   </si>
   <si>
     <t xml:space="preserve">18.7308731079102</t>
@@ -3860,19 +3860,19 @@
     <t xml:space="preserve">18.4445514678955</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3614273071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7980251312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5486488342285</t>
+    <t xml:space="preserve">18.3614253997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7980213165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5486469268799</t>
   </si>
   <si>
     <t xml:space="preserve">17.1422576904297</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9483013153076</t>
+    <t xml:space="preserve">16.948299407959</t>
   </si>
   <si>
     <t xml:space="preserve">16.9205894470215</t>
@@ -3881,22 +3881,22 @@
     <t xml:space="preserve">16.8651752471924</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5696201324463</t>
+    <t xml:space="preserve">16.5696182250977</t>
   </si>
   <si>
     <t xml:space="preserve">16.8559379577637</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1145515441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7451057434082</t>
+    <t xml:space="preserve">17.1145496368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7451019287109</t>
   </si>
   <si>
     <t xml:space="preserve">16.9021186828613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8744125366211</t>
+    <t xml:space="preserve">16.8744106292725</t>
   </si>
   <si>
     <t xml:space="preserve">16.7912845611572</t>
@@ -3935,22 +3935,22 @@
     <t xml:space="preserve">16.0062141418457</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0523948669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6896858215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4710865020752</t>
+    <t xml:space="preserve">16.0523929595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6896877288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4710884094238</t>
   </si>
   <si>
     <t xml:space="preserve">16.632661819458</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6611766815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5946426391602</t>
+    <t xml:space="preserve">16.6611747741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5946445465088</t>
   </si>
   <si>
     <t xml:space="preserve">17.2124290466309</t>
@@ -3959,10 +3959,10 @@
     <t xml:space="preserve">17.5830993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">17.944263458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.820707321167</t>
+    <t xml:space="preserve">17.9442653656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8207092285156</t>
   </si>
   <si>
     <t xml:space="preserve">17.8302135467529</t>
@@ -3974,7 +3974,7 @@
     <t xml:space="preserve">16.9938259124756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5661296844482</t>
+    <t xml:space="preserve">16.5661315917969</t>
   </si>
   <si>
     <t xml:space="preserve">16.2809982299805</t>
@@ -3983,13 +3983,13 @@
     <t xml:space="preserve">16.204963684082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.00537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5871801376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7867727279663</t>
+    <t xml:space="preserve">16.0053730010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.58717918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.786771774292</t>
   </si>
   <si>
     <t xml:space="preserve">15.5681705474854</t>
@@ -4007,16 +4007,16 @@
     <t xml:space="preserve">15.3305606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6251974105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4541177749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8723115921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9958667755127</t>
+    <t xml:space="preserve">15.6251983642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4541187286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8723125457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9958686828613</t>
   </si>
   <si>
     <t xml:space="preserve">16.0623989105225</t>
@@ -4025,19 +4025,19 @@
     <t xml:space="preserve">15.7012319564819</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7772674560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8247900009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7487535476685</t>
+    <t xml:space="preserve">15.777268409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8247880935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7487545013428</t>
   </si>
   <si>
     <t xml:space="preserve">15.7392492294312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9388427734375</t>
+    <t xml:space="preserve">15.9388418197632</t>
   </si>
   <si>
     <t xml:space="preserve">16.1859569549561</t>
@@ -4046,7 +4046,7 @@
     <t xml:space="preserve">16.1574420928955</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8913192749023</t>
+    <t xml:space="preserve">15.8913202285767</t>
   </si>
   <si>
     <t xml:space="preserve">16.9177932739258</t>
@@ -4058,13 +4058,13 @@
     <t xml:space="preserve">17.0223407745361</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1649055480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.060359954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6231575012207</t>
+    <t xml:space="preserve">17.1649074554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0603580474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6231555938721</t>
   </si>
   <si>
     <t xml:space="preserve">16.7277050018311</t>
@@ -4079,7 +4079,7 @@
     <t xml:space="preserve">16.3000068664551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4996013641357</t>
+    <t xml:space="preserve">16.4995994567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.509105682373</t>
@@ -4106,16 +4106,16 @@
     <t xml:space="preserve">17.4215240478516</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3074722290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2599487304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8628063201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8818140029907</t>
+    <t xml:space="preserve">17.3074703216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2599506378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8628072738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.881814956665</t>
   </si>
   <si>
     <t xml:space="preserve">16.4235649108887</t>
@@ -4127,16 +4127,16 @@
     <t xml:space="preserve">16.1479377746582</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9103288650513</t>
+    <t xml:space="preserve">15.910327911377</t>
   </si>
   <si>
     <t xml:space="preserve">16.2429828643799</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8533020019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8437967300415</t>
+    <t xml:space="preserve">15.8533029556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8437976837158</t>
   </si>
   <si>
     <t xml:space="preserve">14.7793073654175</t>
@@ -4151,10 +4151,10 @@
     <t xml:space="preserve">14.4466543197632</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7222814559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6917285919189</t>
+    <t xml:space="preserve">14.7222805023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6917276382446</t>
   </si>
   <si>
     <t xml:space="preserve">15.4731273651123</t>
@@ -4166,7 +4166,7 @@
     <t xml:space="preserve">15.4921350479126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0929527282715</t>
+    <t xml:space="preserve">15.0929517745972</t>
   </si>
   <si>
     <t xml:space="preserve">15.4446144104004</t>
@@ -4196,7 +4196,7 @@
     <t xml:space="preserve">14.4846715927124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9313774108887</t>
+    <t xml:space="preserve">14.931378364563</t>
   </si>
   <si>
     <t xml:space="preserve">14.9218730926514</t>
@@ -4211,37 +4211,37 @@
     <t xml:space="preserve">14.731785774231</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0074129104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7677631378174</t>
+    <t xml:space="preserve">15.0074119567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7677640914917</t>
   </si>
   <si>
     <t xml:space="preserve">16.1954612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5566253662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.128927230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0528945922852</t>
+    <t xml:space="preserve">16.5566272735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1289291381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0528926849365</t>
   </si>
   <si>
     <t xml:space="preserve">16.3570346832275</t>
   </si>
   <si>
-    <t xml:space="preserve">16.433069229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7467155456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3665390014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3950500488281</t>
+    <t xml:space="preserve">16.4330711364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7467136383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3665370941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3950519561768</t>
   </si>
   <si>
     <t xml:space="preserve">16.4805908203125</t>
@@ -4256,10 +4256,10 @@
     <t xml:space="preserve">16.3285217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6136531829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6991901397705</t>
+    <t xml:space="preserve">16.6136512756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6991920471191</t>
   </si>
   <si>
     <t xml:space="preserve">16.5756359100342</t>
@@ -4268,22 +4268,22 @@
     <t xml:space="preserve">18.5240325927734</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7046165466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6475887298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1988430023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4839744567871</t>
+    <t xml:space="preserve">18.7046146392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.647590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.198844909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4839763641357</t>
   </si>
   <si>
     <t xml:space="preserve">19.5029830932617</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4649639129639</t>
+    <t xml:space="preserve">19.4649658203125</t>
   </si>
   <si>
     <t xml:space="preserve">19.2938861846924</t>
@@ -4292,10 +4292,10 @@
     <t xml:space="preserve">19.1037998199463</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2748794555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0277652740479</t>
+    <t xml:space="preserve">19.2748775482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0277633666992</t>
   </si>
   <si>
     <t xml:space="preserve">18.0868320465088</t>
@@ -4322,16 +4322,16 @@
     <t xml:space="preserve">17.9062480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7541790008545</t>
+    <t xml:space="preserve">17.7541770935059</t>
   </si>
   <si>
     <t xml:space="preserve">18.1818752288818</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9157543182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2103862762451</t>
+    <t xml:space="preserve">17.9157524108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2103881835938</t>
   </si>
   <si>
     <t xml:space="preserve">18.343448638916</t>
@@ -4346,16 +4346,16 @@
     <t xml:space="preserve">18.6570930480957</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5810585021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4289875030518</t>
+    <t xml:space="preserve">18.5810565948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4289894104004</t>
   </si>
   <si>
     <t xml:space="preserve">18.1913795471191</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0488147735596</t>
+    <t xml:space="preserve">18.0488128662109</t>
   </si>
   <si>
     <t xml:space="preserve">18.020299911499</t>
@@ -4373,7 +4373,7 @@
     <t xml:space="preserve">17.9632740020752</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0678215026855</t>
+    <t xml:space="preserve">18.0678234100342</t>
   </si>
   <si>
     <t xml:space="preserve">18.1723709106445</t>
@@ -4403,13 +4403,13 @@
     <t xml:space="preserve">17.8112030029297</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5165672302246</t>
+    <t xml:space="preserve">17.5165691375732</t>
   </si>
   <si>
     <t xml:space="preserve">17.5450801849365</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3169765472412</t>
+    <t xml:space="preserve">17.3169746398926</t>
   </si>
   <si>
     <t xml:space="preserve">17.3264808654785</t>
@@ -4430,10 +4430,10 @@
     <t xml:space="preserve">17.5545845031738</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7636833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8872394561768</t>
+    <t xml:space="preserve">17.7636814117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8872375488281</t>
   </si>
   <si>
     <t xml:space="preserve">18.1533622741699</t>
@@ -4442,19 +4442,19 @@
     <t xml:space="preserve">18.1628665924072</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3549957275391</t>
+    <t xml:space="preserve">17.3549938201904</t>
   </si>
   <si>
     <t xml:space="preserve">17.4690456390381</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4405345916748</t>
+    <t xml:space="preserve">17.4405326843262</t>
   </si>
   <si>
     <t xml:space="preserve">17.1078796386719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0413494110107</t>
+    <t xml:space="preserve">17.0413513183594</t>
   </si>
   <si>
     <t xml:space="preserve">16.9368019104004</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">16.4615821838379</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3095111846924</t>
+    <t xml:space="preserve">16.309513092041</t>
   </si>
   <si>
     <t xml:space="preserve">17.0033321380615</t>
@@ -4490,7 +4490,7 @@
     <t xml:space="preserve">17.6211185455322</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0107975006104</t>
+    <t xml:space="preserve">18.0107955932617</t>
   </si>
   <si>
     <t xml:space="preserve">17.7826900482178</t>
@@ -4505,7 +4505,7 @@
     <t xml:space="preserve">17.5355777740479</t>
   </si>
   <si>
-    <t xml:space="preserve">18.001293182373</t>
+    <t xml:space="preserve">18.0012912750244</t>
   </si>
   <si>
     <t xml:space="preserve">18.2674140930176</t>
@@ -70950,7 +70950,7 @@
     </row>
     <row r="2511">
       <c r="A2511" s="1" t="n">
-        <v>45974.6911458333</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B2511" t="n">
         <v>168525</v>
@@ -70971,6 +70971,32 @@
         <v>1773</v>
       </c>
       <c r="H2511" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" s="1" t="n">
+        <v>45975.6909953704</v>
+      </c>
+      <c r="B2512" t="n">
+        <v>88490</v>
+      </c>
+      <c r="C2512" t="n">
+        <v>14.7799997329712</v>
+      </c>
+      <c r="D2512" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="E2512" t="n">
+        <v>14.7600002288818</v>
+      </c>
+      <c r="F2512" t="n">
+        <v>14.7700004577637</v>
+      </c>
+      <c r="G2512" t="s">
+        <v>1763</v>
+      </c>
+      <c r="H2512" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TNXT.MI.xlsx
+++ b/data/TNXT.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63493752479553</t>
+    <t xml:space="preserve">2.63493776321411</t>
   </si>
   <si>
     <t xml:space="preserve">TNXT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65150952339172</t>
+    <t xml:space="preserve">2.6515097618103</t>
   </si>
   <si>
     <t xml:space="preserve">2.59350848197937</t>
@@ -56,76 +56,76 @@
     <t xml:space="preserve">2.52556347846985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48579072952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52722096443176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48744821548462</t>
+    <t xml:space="preserve">2.48579049110413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5272204875946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48744797706604</t>
   </si>
   <si>
     <t xml:space="preserve">2.47087597846985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46921873092651</t>
+    <t xml:space="preserve">2.46921849250793</t>
   </si>
   <si>
     <t xml:space="preserve">2.54047822952271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49739098548889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47916150093079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44436097145081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39464497566223</t>
+    <t xml:space="preserve">2.49739074707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4791624546051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44436049461365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39464449882507</t>
   </si>
   <si>
     <t xml:space="preserve">2.34161472320557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36150121688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55207872390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58522272109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6100800037384</t>
+    <t xml:space="preserve">2.36150074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55207896232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58522248268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61007976531982</t>
   </si>
   <si>
     <t xml:space="preserve">2.56865048408508</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63659477233887</t>
+    <t xml:space="preserve">2.63659501075745</t>
   </si>
   <si>
     <t xml:space="preserve">2.68962526321411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73436975479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72608375549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77579975128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58025121688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56202173233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66808128356934</t>
+    <t xml:space="preserve">2.73436951637268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72608351707458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77579951286316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58025074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56202220916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66808152198792</t>
   </si>
   <si>
     <t xml:space="preserve">2.62830877304077</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">2.64322376251221</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60842227935791</t>
+    <t xml:space="preserve">2.60842251777649</t>
   </si>
   <si>
     <t xml:space="preserve">2.66642427444458</t>
@@ -143,43 +143,43 @@
     <t xml:space="preserve">2.65316677093506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62665176391602</t>
+    <t xml:space="preserve">2.62665200233459</t>
   </si>
   <si>
     <t xml:space="preserve">2.69293975830078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82551527023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81722927093506</t>
+    <t xml:space="preserve">2.82551550865173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81722950935364</t>
   </si>
   <si>
     <t xml:space="preserve">2.90008950233459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85865926742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89843201637268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88351726531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87523174285889</t>
+    <t xml:space="preserve">2.85865950584412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89843249320984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88351702690125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87523126602173</t>
   </si>
   <si>
     <t xml:space="preserve">2.86694526672363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81888628005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82054376602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85368728637695</t>
+    <t xml:space="preserve">2.81888651847839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82054424285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85368776321411</t>
   </si>
   <si>
     <t xml:space="preserve">2.79237151145935</t>
@@ -188,37 +188,37 @@
     <t xml:space="preserve">2.8570020198822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90671849250793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82882952690125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85037398338318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90837526321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96306276321411</t>
+    <t xml:space="preserve">2.90671825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82882976531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8503737449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90837502479553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96306300163269</t>
   </si>
   <si>
     <t xml:space="preserve">2.95797729492188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88169741630554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89017224311829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86474561691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94950175285339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92407512664795</t>
+    <t xml:space="preserve">2.88169693946838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89017271995544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86474585533142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94950199127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92407488822937</t>
   </si>
   <si>
     <t xml:space="preserve">2.96645307540894</t>
@@ -227,22 +227,22 @@
     <t xml:space="preserve">3.11901307106018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94272112846375</t>
+    <t xml:space="preserve">2.94272136688232</t>
   </si>
   <si>
     <t xml:space="preserve">2.94780707359314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8833920955658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87322163581848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85966086387634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03256297111511</t>
+    <t xml:space="preserve">2.88339233398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87322187423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85966062545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03256225585938</t>
   </si>
   <si>
     <t xml:space="preserve">3.07037353515625</t>
@@ -251,22 +251,22 @@
     <t xml:space="preserve">3.06866312026978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06011080741882</t>
+    <t xml:space="preserve">3.06011056900024</t>
   </si>
   <si>
     <t xml:space="preserve">2.99340033531189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98484802246094</t>
+    <t xml:space="preserve">2.98484778404236</t>
   </si>
   <si>
     <t xml:space="preserve">2.93524289131165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98313760757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92498016357422</t>
+    <t xml:space="preserve">2.98313736915588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9249804019928</t>
   </si>
   <si>
     <t xml:space="preserve">2.92326951026917</t>
@@ -284,19 +284,19 @@
     <t xml:space="preserve">3.05497932434082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08747863769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13879418373108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12853097915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19010996818542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15589904785156</t>
+    <t xml:space="preserve">3.08747887611389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13879466056824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12853145599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19010972976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15589952468872</t>
   </si>
   <si>
     <t xml:space="preserve">3.12339949607849</t>
@@ -314,88 +314,88 @@
     <t xml:space="preserve">3.16616249084473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24142527580261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30129289627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38681888580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48431801795959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52708101272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62629127502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63655352592468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64510679244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74602675437927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67760682106018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71181654930115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63484334945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51681804656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50484466552734</t>
+    <t xml:space="preserve">3.24142503738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30129337310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3868191242218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48431849479675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52708125114441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62629079818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63655400276184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64510655403137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74602723121643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6776065826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71181726455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63484358787537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51681780815125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50484418869019</t>
   </si>
   <si>
     <t xml:space="preserve">3.49458122253418</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50655436515808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48089718818665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43129181861877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35602951049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60063338279724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64681696891785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69471216201782</t>
+    <t xml:space="preserve">3.50655460357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48089742660522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43129253387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35602974891663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60063290596008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64681720733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69471168518066</t>
   </si>
   <si>
     <t xml:space="preserve">3.69984340667725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67589592933655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6656322479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59721183776855</t>
+    <t xml:space="preserve">3.67589569091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66563248634338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59721207618713</t>
   </si>
   <si>
     <t xml:space="preserve">3.63313317298889</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57497596740723</t>
+    <t xml:space="preserve">3.57497549057007</t>
   </si>
   <si>
     <t xml:space="preserve">3.66050100326538</t>
@@ -407,109 +407,109 @@
     <t xml:space="preserve">3.71523761749268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73747396469116</t>
+    <t xml:space="preserve">3.73747420310974</t>
   </si>
   <si>
     <t xml:space="preserve">3.71010589599609</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69129061698914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68957996368408</t>
+    <t xml:space="preserve">3.69129037857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68958044052124</t>
   </si>
   <si>
     <t xml:space="preserve">3.73234272003174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7203688621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76313209533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77168393135071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62115955352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64168548583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70326399803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79734325408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75457906723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90852546691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76655220985413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72892212867737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66734337806702</t>
+    <t xml:space="preserve">3.72036933898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76313233375549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77168488502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62115979194641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64168572425842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7032642364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7973427772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75457954406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9085259437561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76655268669128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72892165184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66734313964844</t>
   </si>
   <si>
     <t xml:space="preserve">3.50997614860535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49800252914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4894495010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47234416007996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40392374992371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43642401695251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53221273422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51852869987488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46037101745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50142335891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5356330871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55615949630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64339685440063</t>
+    <t xml:space="preserve">3.49800229072571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48944973945618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47234463691711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40392398834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43642377853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53221249580383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51852822303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46037125587463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50142312049866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53563356399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55615997314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64339661598206</t>
   </si>
   <si>
     <t xml:space="preserve">3.72550082206726</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84865784645081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82984256744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83155274391174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87089419364929</t>
+    <t xml:space="preserve">3.84865760803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82984232902527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83155202865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87089443206787</t>
   </si>
   <si>
     <t xml:space="preserve">3.84523677825928</t>
@@ -518,37 +518,37 @@
     <t xml:space="preserve">3.87431573867798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86405253410339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85721039772034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82471036911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90681481361389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00260400772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17536640167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11378765106201</t>
+    <t xml:space="preserve">3.86405277252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85721063613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82471060752869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90681552886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00260448455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17536592483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11378717422485</t>
   </si>
   <si>
     <t xml:space="preserve">4.00773572921753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05220890045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0812873840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00602436065674</t>
+    <t xml:space="preserve">4.0522084236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08128833770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00602531433105</t>
   </si>
   <si>
     <t xml:space="preserve">4.09839248657227</t>
@@ -557,16 +557,16 @@
     <t xml:space="preserve">4.01970911026001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01115608215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99576187133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03510332107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06247282028198</t>
+    <t xml:space="preserve">4.01115655899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99576210975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0351037979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06247234344482</t>
   </si>
   <si>
     <t xml:space="preserve">4.13773488998413</t>
@@ -575,13 +575,13 @@
     <t xml:space="preserve">4.12234020233154</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14799785614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18904972076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25918102264404</t>
+    <t xml:space="preserve">4.14799833297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18905067443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2591814994812</t>
   </si>
   <si>
     <t xml:space="preserve">4.22839164733887</t>
@@ -590,109 +590,109 @@
     <t xml:space="preserve">4.20615577697754</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0214204788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99405121803284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01799917221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02655076980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07615518569946</t>
+    <t xml:space="preserve">4.02142000198364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99405217170715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01799869537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02655172348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07615661621094</t>
   </si>
   <si>
     <t xml:space="preserve">4.12747144699097</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11891937255859</t>
+    <t xml:space="preserve">4.11891889572144</t>
   </si>
   <si>
     <t xml:space="preserve">4.10523509979248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09668254852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10181379318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07102537155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09497213363647</t>
+    <t xml:space="preserve">4.09668302536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10181427001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0710244178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09497165679932</t>
   </si>
   <si>
     <t xml:space="preserve">4.13089227676392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21641874313354</t>
+    <t xml:space="preserve">4.21641826629639</t>
   </si>
   <si>
     <t xml:space="preserve">4.52431106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54996871948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53713989257812</t>
+    <t xml:space="preserve">4.54996919631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53713941574097</t>
   </si>
   <si>
     <t xml:space="preserve">4.46444320678711</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5029296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56707429885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6226658821106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63549518585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58417892456055</t>
+    <t xml:space="preserve">4.50293016433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5670747756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62266540527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63549470901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58417844772339</t>
   </si>
   <si>
     <t xml:space="preserve">4.60128450393677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57562589645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61838960647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53286409378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55852127075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48154830932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51575899124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49010038375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51148271560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63121843338013</t>
+    <t xml:space="preserve">4.57562637329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61839008331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53286361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55852174758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48154783248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5157585144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4901008605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51148319244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63121795654297</t>
   </si>
   <si>
     <t xml:space="preserve">4.78516435623169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7595067024231</t>
+    <t xml:space="preserve">4.75950717926025</t>
   </si>
   <si>
     <t xml:space="preserve">4.78944063186646</t>
@@ -704,88 +704,88 @@
     <t xml:space="preserve">4.77233600616455</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76378345489502</t>
+    <t xml:space="preserve">4.76378297805786</t>
   </si>
   <si>
     <t xml:space="preserve">4.65687608718872</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69536209106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82792711257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90062427520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91772937774658</t>
+    <t xml:space="preserve">4.69536256790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8279275894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90062475204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91772985458374</t>
   </si>
   <si>
     <t xml:space="preserve">4.94338798522949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98614978790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04174137115479</t>
+    <t xml:space="preserve">4.98615026473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04174184799194</t>
   </si>
   <si>
     <t xml:space="preserve">5.02036046981812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07167625427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08022928237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99470233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09305667877197</t>
+    <t xml:space="preserve">5.0716757774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08022832870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99470281600952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09305715560913</t>
   </si>
   <si>
     <t xml:space="preserve">5.06050682067871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91728496551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94766569137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92596530914307</t>
+    <t xml:space="preserve">4.91728448867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94766521453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92596483230591</t>
   </si>
   <si>
     <t xml:space="preserve">4.9042649269104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8218035697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73500299453735</t>
+    <t xml:space="preserve">4.82180404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7350025177002</t>
   </si>
   <si>
     <t xml:space="preserve">4.72198247909546</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59178113937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64386129379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73066186904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66556215286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65254211425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60914039611816</t>
+    <t xml:space="preserve">4.59178066253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64386081695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73066234588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66556167602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65254068374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60914087295532</t>
   </si>
   <si>
     <t xml:space="preserve">4.65688133239746</t>
@@ -803,16 +803,16 @@
     <t xml:space="preserve">4.59612083435059</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47459983825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48761940002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46157932281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41383790969849</t>
+    <t xml:space="preserve">4.47459936141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48761987686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46157884597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41383838653564</t>
   </si>
   <si>
     <t xml:space="preserve">4.38779830932617</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">4.40949773788452</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55706071853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52233934402466</t>
+    <t xml:space="preserve">4.55706024169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52233982086182</t>
   </si>
   <si>
     <t xml:space="preserve">4.57008075714111</t>
@@ -836,19 +836,19 @@
     <t xml:space="preserve">4.53970050811768</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47893905639648</t>
+    <t xml:space="preserve">4.47893953323364</t>
   </si>
   <si>
     <t xml:space="preserve">4.43553829193115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42251873016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43119812011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45289850234985</t>
+    <t xml:space="preserve">4.42251825332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43119859695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45289945602417</t>
   </si>
   <si>
     <t xml:space="preserve">4.51365947723389</t>
@@ -857,34 +857,34 @@
     <t xml:space="preserve">4.68726205825806</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60046100616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6395206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56140041351318</t>
+    <t xml:space="preserve">4.60046052932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63952112197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56139945983887</t>
   </si>
   <si>
     <t xml:space="preserve">4.58744049072266</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61782073974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64820146560669</t>
+    <t xml:space="preserve">4.61782169342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64820194244385</t>
   </si>
   <si>
     <t xml:space="preserve">4.60480070114136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58310031890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49629974365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50497913360596</t>
+    <t xml:space="preserve">4.58310127258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49629926681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50497961044312</t>
   </si>
   <si>
     <t xml:space="preserve">4.42685794830322</t>
@@ -896,46 +896,46 @@
     <t xml:space="preserve">4.51800012588501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80878353118896</t>
+    <t xml:space="preserve">4.80878400802612</t>
   </si>
   <si>
     <t xml:space="preserve">4.77840328216553</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84784364700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83482456207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74368238449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81312322616577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71330213546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70462274551392</t>
+    <t xml:space="preserve">4.84784412384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8348240852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74368286132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81312417984009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71330261230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70462226867676</t>
   </si>
   <si>
     <t xml:space="preserve">4.72632265090942</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69594192504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76972246170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84350442886353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87822437286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8738842010498</t>
+    <t xml:space="preserve">4.69594240188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7697229385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84350395202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87822389602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87388515472412</t>
   </si>
   <si>
     <t xml:space="preserve">4.97370576858521</t>
@@ -944,13 +944,13 @@
     <t xml:space="preserve">4.97804546356201</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00842571258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07786750793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04314708709717</t>
+    <t xml:space="preserve">5.00842666625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07786655426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04314613342285</t>
   </si>
   <si>
     <t xml:space="preserve">5.14730787277222</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">4.96502542495728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90860509872437</t>
+    <t xml:space="preserve">4.90860557556152</t>
   </si>
   <si>
     <t xml:space="preserve">4.99974632263184</t>
@@ -980,28 +980,28 @@
     <t xml:space="preserve">5.12994718551636</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29487037658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41639184951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48583269119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43375158309937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48149251937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42073202133179</t>
+    <t xml:space="preserve">5.29486989974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41639137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48583316802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43375205993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4814920425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42073106765747</t>
   </si>
   <si>
     <t xml:space="preserve">5.39469146728516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35563039779663</t>
+    <t xml:space="preserve">5.35562992095947</t>
   </si>
   <si>
     <t xml:space="preserve">5.33393049240112</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">5.37299108505249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33827018737793</t>
+    <t xml:space="preserve">5.33827066421509</t>
   </si>
   <si>
     <t xml:space="preserve">5.20806884765625</t>
@@ -1019,13 +1019,13 @@
     <t xml:space="preserve">5.16466808319092</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26448917388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25146961212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26014947891235</t>
+    <t xml:space="preserve">5.26448965072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25147008895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26014995574951</t>
   </si>
   <si>
     <t xml:space="preserve">5.18636846542358</t>
@@ -1040,22 +1040,22 @@
     <t xml:space="preserve">5.16900825500488</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18202829360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19938945770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22542858123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42507171630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61603355407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72887563705444</t>
+    <t xml:space="preserve">5.18202877044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19938898086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22542905807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42507219314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61603403091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7288761138916</t>
   </si>
   <si>
     <t xml:space="preserve">5.71151542663574</t>
@@ -1064,49 +1064,49 @@
     <t xml:space="preserve">5.78963661193848</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82435655593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87643766403198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88511800765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93719863891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85907745361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80699682235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92851781845093</t>
+    <t xml:space="preserve">5.82435703277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87643814086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88511753082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93719816207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85907697677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80699634552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92851829528809</t>
   </si>
   <si>
     <t xml:space="preserve">5.97191905975342</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95455837249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03268003463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17156076431274</t>
+    <t xml:space="preserve">5.95455980300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03267955780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17156171798706</t>
   </si>
   <si>
     <t xml:space="preserve">6.28440284729004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01531934738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02400016784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21496248245239</t>
+    <t xml:space="preserve">6.01531982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02399921417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21496200561523</t>
   </si>
   <si>
     <t xml:space="preserve">6.14552164077759</t>
@@ -1118,52 +1118,52 @@
     <t xml:space="preserve">6.07607984542847</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98927879333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04135990142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22364234924316</t>
+    <t xml:space="preserve">5.98927927017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04136037826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22364187240601</t>
   </si>
   <si>
     <t xml:space="preserve">6.13684129714966</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19760131835938</t>
+    <t xml:space="preserve">6.19760227203369</t>
   </si>
   <si>
     <t xml:space="preserve">6.15420150756836</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05003976821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89379835128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90247869491577</t>
+    <t xml:space="preserve">6.05003929138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89379787445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90247821807861</t>
   </si>
   <si>
     <t xml:space="preserve">5.70283555984497</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50319337844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58131408691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72019529342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.763596534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91983890533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99795961380005</t>
+    <t xml:space="preserve">5.50319290161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58131313323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72019624710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76359605789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91983842849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99795866012573</t>
   </si>
   <si>
     <t xml:space="preserve">5.83303594589233</t>
@@ -1172,37 +1172,37 @@
     <t xml:space="preserve">5.79831647872925</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6594352722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5118727684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5465931892395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58999347686768</t>
+    <t xml:space="preserve">5.65943479537964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51187229156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54659271240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58999395370483</t>
   </si>
   <si>
     <t xml:space="preserve">5.52055311203003</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38167095184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44243240356445</t>
+    <t xml:space="preserve">5.3816704750061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44243192672729</t>
   </si>
   <si>
     <t xml:space="preserve">5.46847200393677</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6767954826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64207363128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55527400970459</t>
+    <t xml:space="preserve">5.67679500579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64207458496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55527353286743</t>
   </si>
   <si>
     <t xml:space="preserve">5.53791332244873</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">5.57263374328613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5292329788208</t>
+    <t xml:space="preserve">5.52923345565796</t>
   </si>
   <si>
     <t xml:space="preserve">5.39903163909912</t>
@@ -1220,13 +1220,13 @@
     <t xml:space="preserve">5.39035177230835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45111179351807</t>
+    <t xml:space="preserve">5.45111227035522</t>
   </si>
   <si>
     <t xml:space="preserve">6.09344053268433</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81567621231079</t>
+    <t xml:space="preserve">5.81567668914795</t>
   </si>
   <si>
     <t xml:space="preserve">5.77227640151978</t>
@@ -1235,13 +1235,13 @@
     <t xml:space="preserve">5.73755550384521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40771198272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24278926849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0691876411438</t>
+    <t xml:space="preserve">5.40771150588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24278879165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06918716430664</t>
   </si>
   <si>
     <t xml:space="preserve">4.98238515853882</t>
@@ -1250,13 +1250,13 @@
     <t xml:space="preserve">5.07618761062622</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15619802474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08507776260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24509763717651</t>
+    <t xml:space="preserve">5.1561975479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0850772857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24509811401367</t>
   </si>
   <si>
     <t xml:space="preserve">5.11174821853638</t>
@@ -1265,13 +1265,13 @@
     <t xml:space="preserve">5.13841772079468</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20953798294067</t>
+    <t xml:space="preserve">5.20953845977783</t>
   </si>
   <si>
     <t xml:space="preserve">5.06729793548584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05840826034546</t>
+    <t xml:space="preserve">5.0584077835083</t>
   </si>
   <si>
     <t xml:space="preserve">5.04062795639038</t>
@@ -1280,22 +1280,22 @@
     <t xml:space="preserve">5.04951763153076</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94283819198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77392864227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90727806091309</t>
+    <t xml:space="preserve">4.94283771514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77392816543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9072790145874</t>
   </si>
   <si>
     <t xml:space="preserve">4.76503801345825</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92505788803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88949775695801</t>
+    <t xml:space="preserve">4.92505836486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88949823379517</t>
   </si>
   <si>
     <t xml:space="preserve">5.02284812927246</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">4.89838838577271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80948781967163</t>
+    <t xml:space="preserve">4.80948734283447</t>
   </si>
   <si>
     <t xml:space="preserve">4.78281831741333</t>
@@ -1328,31 +1328,31 @@
     <t xml:space="preserve">4.98728847503662</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10285758972168</t>
+    <t xml:space="preserve">5.10285711288452</t>
   </si>
   <si>
     <t xml:space="preserve">4.960618019104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20064783096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21842765808105</t>
+    <t xml:space="preserve">5.20064735412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2184271812439</t>
   </si>
   <si>
     <t xml:space="preserve">5.27176761627197</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33399772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23620748519897</t>
+    <t xml:space="preserve">5.33399820327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23620843887329</t>
   </si>
   <si>
     <t xml:space="preserve">5.18286752700806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01395750045776</t>
+    <t xml:space="preserve">5.01395797729492</t>
   </si>
   <si>
     <t xml:space="preserve">4.99617767333984</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">5.37844800949097</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47623729705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56513786315918</t>
+    <t xml:space="preserve">5.47623777389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56513833999634</t>
   </si>
   <si>
     <t xml:space="preserve">5.6807074546814</t>
@@ -1376,16 +1376,16 @@
     <t xml:space="preserve">5.6540379524231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63625812530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5562481880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68959760665894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96518754959106</t>
+    <t xml:space="preserve">5.63625764846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55624771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68959808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96518707275391</t>
   </si>
   <si>
     <t xml:space="preserve">5.89406776428223</t>
@@ -1394,34 +1394,34 @@
     <t xml:space="preserve">5.77849769592285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84072828292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76071786880493</t>
+    <t xml:space="preserve">5.84072732925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76071739196777</t>
   </si>
   <si>
     <t xml:space="preserve">5.92073774337769</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83183717727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4495677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5829176902771</t>
+    <t xml:space="preserve">5.83183765411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44956827163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58291816711426</t>
   </si>
   <si>
     <t xml:space="preserve">5.43178796768188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36955738067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60958814620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86739730834961</t>
+    <t xml:space="preserve">5.36955833435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60958671569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86739778518677</t>
   </si>
   <si>
     <t xml:space="preserve">5.78738784790039</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">5.52068758010864</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49401760101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57402801513672</t>
+    <t xml:space="preserve">5.49401712417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57402753829956</t>
   </si>
   <si>
     <t xml:space="preserve">5.59180784225464</t>
@@ -1445,13 +1445,13 @@
     <t xml:space="preserve">5.71626806259155</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73404788970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81405735015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67181825637817</t>
+    <t xml:space="preserve">5.73404741287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81405782699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67181777954102</t>
   </si>
   <si>
     <t xml:space="preserve">5.5117974281311</t>
@@ -1463,31 +1463,31 @@
     <t xml:space="preserve">5.66292762756348</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53846740722656</t>
+    <t xml:space="preserve">5.53846788406372</t>
   </si>
   <si>
     <t xml:space="preserve">5.90295743942261</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79627799987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80516767501831</t>
+    <t xml:space="preserve">5.79627752304077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80516815185547</t>
   </si>
   <si>
     <t xml:space="preserve">5.6184778213501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46734809875488</t>
+    <t xml:space="preserve">5.46734762191772</t>
   </si>
   <si>
     <t xml:space="preserve">5.60069799423218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45845699310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50290822982788</t>
+    <t xml:space="preserve">5.45845746994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50290775299072</t>
   </si>
   <si>
     <t xml:space="preserve">5.34288787841797</t>
@@ -1496,64 +1496,64 @@
     <t xml:space="preserve">5.62736701965332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52957773208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42289733886719</t>
+    <t xml:space="preserve">5.52957725524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42289781570435</t>
   </si>
   <si>
     <t xml:space="preserve">5.72515773773193</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70737743377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69848728179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00074768066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92962789535522</t>
+    <t xml:space="preserve">5.70737791061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69848823547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0007472038269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92962741851807</t>
   </si>
   <si>
     <t xml:space="preserve">5.94740772247314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93851709365845</t>
+    <t xml:space="preserve">5.93851757049561</t>
   </si>
   <si>
     <t xml:space="preserve">5.99185705184937</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24077701568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40968751907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48080682754517</t>
+    <t xml:space="preserve">6.24077796936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40968799591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48080730438232</t>
   </si>
   <si>
     <t xml:space="preserve">6.62304735183716</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84529733657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99642705917358</t>
+    <t xml:space="preserve">6.84529685974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99642658233643</t>
   </si>
   <si>
     <t xml:space="preserve">7.0142068862915</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90752792358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91641712188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97864675521851</t>
+    <t xml:space="preserve">6.90752696990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91641759872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97864723205566</t>
   </si>
   <si>
     <t xml:space="preserve">7.00531721115112</t>
@@ -1562,37 +1562,37 @@
     <t xml:space="preserve">7.02309703826904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24534702301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27201747894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33424663543701</t>
+    <t xml:space="preserve">7.2453465461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27201795578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33424711227417</t>
   </si>
   <si>
     <t xml:space="preserve">7.47648668289185</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76985645294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73429584503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72540616989136</t>
+    <t xml:space="preserve">7.76985549926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73429679870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72540664672852</t>
   </si>
   <si>
     <t xml:space="preserve">7.79652690887451</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80541610717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22324657440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21435642242432</t>
+    <t xml:space="preserve">7.80541515350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22324752807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21435546875</t>
   </si>
   <si>
     <t xml:space="preserve">8.15212631225586</t>
@@ -1601,13 +1601,13 @@
     <t xml:space="preserve">8.12545776367188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00099658966064</t>
+    <t xml:space="preserve">8.00099754333496</t>
   </si>
   <si>
     <t xml:space="preserve">8.17879676818848</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34770679473877</t>
+    <t xml:space="preserve">8.34770584106445</t>
   </si>
   <si>
     <t xml:space="preserve">8.42771625518799</t>
@@ -1616,28 +1616,28 @@
     <t xml:space="preserve">8.48105621337891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46327686309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5255069732666</t>
+    <t xml:space="preserve">8.46327590942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52550601959229</t>
   </si>
   <si>
     <t xml:space="preserve">8.50772666931152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66774749755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8010950088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88999843597412</t>
+    <t xml:space="preserve">8.66774654388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80109691619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88999652862549</t>
   </si>
   <si>
     <t xml:space="preserve">9.19225597381592</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37005519866943</t>
+    <t xml:space="preserve">9.37005615234375</t>
   </si>
   <si>
     <t xml:space="preserve">9.47673606872559</t>
@@ -1652,13 +1652,13 @@
     <t xml:space="preserve">9.15669631958008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35227584838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40561580657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69009590148926</t>
+    <t xml:space="preserve">9.35227680206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40561676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69009685516357</t>
   </si>
   <si>
     <t xml:space="preserve">9.86789608001709</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">9.83233547210693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77899551391602</t>
+    <t xml:space="preserve">9.77899646759033</t>
   </si>
   <si>
     <t xml:space="preserve">9.44117546081543</t>
@@ -1682,16 +1682,16 @@
     <t xml:space="preserve">9.51229572296143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6723165512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85011577606201</t>
+    <t xml:space="preserve">9.67231559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85011672973633</t>
   </si>
   <si>
     <t xml:space="preserve">10.0990352630615</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0279150009155</t>
+    <t xml:space="preserve">10.0279159545898</t>
   </si>
   <si>
     <t xml:space="preserve">9.99235534667969</t>
@@ -1703,19 +1703,19 @@
     <t xml:space="preserve">9.76121616363525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88567638397217</t>
+    <t xml:space="preserve">9.88567543029785</t>
   </si>
   <si>
     <t xml:space="preserve">10.2234964370728</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4368553161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6679954528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4147548675537</t>
+    <t xml:space="preserve">10.4368543624878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6679964065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.414755821228</t>
   </si>
   <si>
     <t xml:space="preserve">11.3614149093628</t>
@@ -1727,22 +1727,22 @@
     <t xml:space="preserve">11.4325361251831</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6814565658569</t>
+    <t xml:space="preserve">11.6814546585083</t>
   </si>
   <si>
     <t xml:space="preserve">11.8948154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">11.965934753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1437339782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6281147003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4001140594482</t>
+    <t xml:space="preserve">11.9659337997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1437349319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6281156539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4001131057739</t>
   </si>
   <si>
     <t xml:space="preserve">11.6715440750122</t>
@@ -1751,19 +1751,19 @@
     <t xml:space="preserve">11.6534490585327</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6896409988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.123929977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7982130050659</t>
+    <t xml:space="preserve">11.689640045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1239290237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7982120513916</t>
   </si>
   <si>
     <t xml:space="preserve">12.1782159805298</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3229789733887</t>
+    <t xml:space="preserve">12.322979927063</t>
   </si>
   <si>
     <t xml:space="preserve">12.9925098419189</t>
@@ -1775,19 +1775,19 @@
     <t xml:space="preserve">12.7391738891602</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7753639221191</t>
+    <t xml:space="preserve">12.7753658294678</t>
   </si>
   <si>
     <t xml:space="preserve">12.3953609466553</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2867889404297</t>
+    <t xml:space="preserve">12.2867879867554</t>
   </si>
   <si>
     <t xml:space="preserve">12.6306018829346</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4496479034424</t>
+    <t xml:space="preserve">12.4496469497681</t>
   </si>
   <si>
     <t xml:space="preserve">12.2144060134888</t>
@@ -1796,16 +1796,16 @@
     <t xml:space="preserve">12.1058349609375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8705930709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9067850112915</t>
+    <t xml:space="preserve">11.8705949783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9067840576172</t>
   </si>
   <si>
     <t xml:space="preserve">11.4724950790405</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4182090759277</t>
+    <t xml:space="preserve">11.4182081222534</t>
   </si>
   <si>
     <t xml:space="preserve">11.5810680389404</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">11.8524990081787</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0877380371094</t>
+    <t xml:space="preserve">12.0877389907837</t>
   </si>
   <si>
     <t xml:space="preserve">11.8344030380249</t>
@@ -1832,22 +1832,22 @@
     <t xml:space="preserve">11.2734460830688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1829681396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1648721694946</t>
+    <t xml:space="preserve">11.1829671859741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1648731231689</t>
   </si>
   <si>
     <t xml:space="preserve">10.8391542434692</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6401062011719</t>
+    <t xml:space="preserve">10.6401052474976</t>
   </si>
   <si>
     <t xml:space="preserve">10.6762971878052</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5134382247925</t>
+    <t xml:space="preserve">10.5134372711182</t>
   </si>
   <si>
     <t xml:space="preserve">10.9115371704102</t>
@@ -1856,19 +1856,19 @@
     <t xml:space="preserve">11.2915391921997</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1467761993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.766773223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1105861663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.12868309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6220102310181</t>
+    <t xml:space="preserve">11.1467771530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7667741775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1105852127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1286821365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6220092773438</t>
   </si>
   <si>
     <t xml:space="preserve">11.0020132064819</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">9.9343843460083</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80771732330322</t>
+    <t xml:space="preserve">9.80771636962891</t>
   </si>
   <si>
     <t xml:space="preserve">9.68104839324951</t>
@@ -1901,19 +1901,19 @@
     <t xml:space="preserve">9.95247936248779</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2420063018799</t>
+    <t xml:space="preserve">10.2420053482056</t>
   </si>
   <si>
     <t xml:space="preserve">10.4772462844849</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3867692947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4410552978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55438041687012</t>
+    <t xml:space="preserve">10.3867683410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4410562515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5543794631958</t>
   </si>
   <si>
     <t xml:space="preserve">10.1153392791748</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">10.3505783081055</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4048652648926</t>
+    <t xml:space="preserve">10.4048643112183</t>
   </si>
   <si>
     <t xml:space="preserve">10.7486782073975</t>
@@ -1934,31 +1934,31 @@
     <t xml:space="preserve">10.857250213623</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8753461837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5858182907104</t>
+    <t xml:space="preserve">10.8753471374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5858192443848</t>
   </si>
   <si>
     <t xml:space="preserve">10.8029642105103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7124862670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7848682403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2372550964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3096361160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4543991088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.725830078125</t>
+    <t xml:space="preserve">10.7124872207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7848691940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2372541427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3096351623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4543981552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7258310317993</t>
   </si>
   <si>
     <t xml:space="preserve">11.9972620010376</t>
@@ -1976,10 +1976,10 @@
     <t xml:space="preserve">11.9429759979248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.762020111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9477281570435</t>
+    <t xml:space="preserve">11.7620210647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9477272033691</t>
   </si>
   <si>
     <t xml:space="preserve">10.9658231735229</t>
@@ -1988,16 +1988,16 @@
     <t xml:space="preserve">10.1877202987671</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98867034912109</t>
+    <t xml:space="preserve">9.98867130279541</t>
   </si>
   <si>
     <t xml:space="preserve">10.0429573059082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91628837585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.169623374939</t>
+    <t xml:space="preserve">9.91628932952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1696243286133</t>
   </si>
   <si>
     <t xml:space="preserve">10.531533241272</t>
@@ -2006,13 +2006,13 @@
     <t xml:space="preserve">10.4229612350464</t>
   </si>
   <si>
-    <t xml:space="preserve">10.13343334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3324823379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2239103317261</t>
+    <t xml:space="preserve">10.1334342956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.332483291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2239112854004</t>
   </si>
   <si>
     <t xml:space="preserve">10.097243309021</t>
@@ -2021,10 +2021,10 @@
     <t xml:space="preserve">10.0610523223877</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0791473388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1515302658081</t>
+    <t xml:space="preserve">10.0791482925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1515293121338</t>
   </si>
   <si>
     <t xml:space="preserve">11.056300163269</t>
@@ -2036,10 +2036,10 @@
     <t xml:space="preserve">10.5496282577515</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3686752319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82581043243408</t>
+    <t xml:space="preserve">10.3686742782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82581233978271</t>
   </si>
   <si>
     <t xml:space="preserve">9.77152538299561</t>
@@ -2051,37 +2051,37 @@
     <t xml:space="preserve">9.51819038391113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7172384262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42771244049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59057235717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3639230728149</t>
+    <t xml:space="preserve">9.71723937988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42771339416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59057140350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3639221191406</t>
   </si>
   <si>
     <t xml:space="preserve">11.9791660308838</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4677410125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3772659301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3820171356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5629720687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6172580718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.092490196228</t>
+    <t xml:space="preserve">12.4677419662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3772668838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3820180892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5629711151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6172590255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0924911499023</t>
   </si>
   <si>
     <t xml:space="preserve">10.6943922042847</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">8.8034200668335</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68580150604248</t>
+    <t xml:space="preserve">8.68580055236816</t>
   </si>
   <si>
     <t xml:space="preserve">8.43246459960938</t>
@@ -2102,19 +2102,19 @@
     <t xml:space="preserve">7.0481653213501</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32864427566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24721527099609</t>
+    <t xml:space="preserve">7.3286452293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24721479415894</t>
   </si>
   <si>
     <t xml:space="preserve">7.18388080596924</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58673238754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65006542205811</t>
+    <t xml:space="preserve">6.58673191070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65006589889526</t>
   </si>
   <si>
     <t xml:space="preserve">6.96673583984375</t>
@@ -2123,16 +2123,16 @@
     <t xml:space="preserve">6.9757833480835</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16578531265259</t>
+    <t xml:space="preserve">7.16578578948975</t>
   </si>
   <si>
     <t xml:space="preserve">7.057213306427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28340578079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60912275314331</t>
+    <t xml:space="preserve">7.28340530395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60912227630615</t>
   </si>
   <si>
     <t xml:space="preserve">7.76293420791626</t>
@@ -2141,13 +2141,13 @@
     <t xml:space="preserve">8.34198760986328</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04341411590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61341953277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41436862945557</t>
+    <t xml:space="preserve">8.04341316223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61341857910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41436958312988</t>
   </si>
   <si>
     <t xml:space="preserve">8.25151062011719</t>
@@ -2165,19 +2165,19 @@
     <t xml:space="preserve">9.26485443115234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50009441375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8620023727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2191581726074</t>
+    <t xml:space="preserve">9.50009346008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86200332641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2191591262817</t>
   </si>
   <si>
     <t xml:space="preserve">10.9839191436768</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6582002639771</t>
+    <t xml:space="preserve">10.6582012176514</t>
   </si>
   <si>
     <t xml:space="preserve">9.97057628631592</t>
@@ -2192,10 +2192,10 @@
     <t xml:space="preserve">10.4591512680054</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9296321868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7305812835693</t>
+    <t xml:space="preserve">10.929633140564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7305822372437</t>
   </si>
   <si>
     <t xml:space="preserve">10.8210601806641</t>
@@ -2204,10 +2204,10 @@
     <t xml:space="preserve">12.0696439743042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5582208633423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8477468490601</t>
+    <t xml:space="preserve">12.558219909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8477458953857</t>
   </si>
   <si>
     <t xml:space="preserve">13.1915588378906</t>
@@ -2219,16 +2219,16 @@
     <t xml:space="preserve">12.7934608459473</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4315509796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.594409942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6486959457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7210779190063</t>
+    <t xml:space="preserve">12.4315519332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5944108963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6486968994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.721079826355</t>
   </si>
   <si>
     <t xml:space="preserve">12.8658418655396</t>
@@ -2237,10 +2237,10 @@
     <t xml:space="preserve">13.1553678512573</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0286989212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1191787719727</t>
+    <t xml:space="preserve">13.0287008285522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1191759109497</t>
   </si>
   <si>
     <t xml:space="preserve">12.9382238388062</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">13.082986831665</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3725137710571</t>
+    <t xml:space="preserve">13.3725128173828</t>
   </si>
   <si>
     <t xml:space="preserve">13.3544178009033</t>
@@ -2261,10 +2261,10 @@
     <t xml:space="preserve">16.249683380127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2858734130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3763542175293</t>
+    <t xml:space="preserve">16.2858753204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3763561248779</t>
   </si>
   <si>
     <t xml:space="preserve">16.6477851867676</t>
@@ -2273,43 +2273,43 @@
     <t xml:space="preserve">15.8334903717041</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0687294006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.869683265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9239683151245</t>
+    <t xml:space="preserve">16.0687313079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8696813583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9239673614502</t>
   </si>
   <si>
     <t xml:space="preserve">15.9058713912964</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8515872955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0144443511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7973003387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2677783966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0325374603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.779203414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7249174118042</t>
+    <t xml:space="preserve">15.8515853881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0144424438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7972984313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2677822113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0325393676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7792024612427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7249164581299</t>
   </si>
   <si>
     <t xml:space="preserve">16.4125442504883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.815393447876</t>
+    <t xml:space="preserve">15.8153944015503</t>
   </si>
   <si>
     <t xml:space="preserve">15.942063331604</t>
@@ -2318,55 +2318,55 @@
     <t xml:space="preserve">15.6344423294067</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1049213409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9601564407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6887273788452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6163454055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8925285339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6525354385376</t>
+    <t xml:space="preserve">16.1049194335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9601573944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6887264251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6163444519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8925294876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6525325775146</t>
   </si>
   <si>
     <t xml:space="preserve">15.3630094528198</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4896774291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1458644866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0372915267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.743013381958</t>
+    <t xml:space="preserve">15.4896783828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1458654403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0372934341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7430143356323</t>
   </si>
   <si>
     <t xml:space="preserve">14.8201465606689</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2906274795532</t>
+    <t xml:space="preserve">15.2906284332275</t>
   </si>
   <si>
     <t xml:space="preserve">17.5887451171875</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7697010040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0230350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1359043121338</t>
+    <t xml:space="preserve">17.7696971893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0230369567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1359062194824</t>
   </si>
   <si>
     <t xml:space="preserve">18.2763729095459</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">18.0411319732666</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4258880615234</t>
+    <t xml:space="preserve">17.4258861541748</t>
   </si>
   <si>
     <t xml:space="preserve">17.7335090637207</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">17.2992191314697</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0458831787109</t>
+    <t xml:space="preserve">17.0458850860596</t>
   </si>
   <si>
     <t xml:space="preserve">17.0277862548828</t>
@@ -2399,13 +2399,13 @@
     <t xml:space="preserve">17.4077911376953</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5025653839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1406536102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.96875</t>
+    <t xml:space="preserve">18.5025634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1406555175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9687519073486</t>
   </si>
   <si>
     <t xml:space="preserve">17.4982681274414</t>
@@ -2414,22 +2414,22 @@
     <t xml:space="preserve">17.9868450164795</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5930404663086</t>
+    <t xml:space="preserve">18.5930423736572</t>
   </si>
   <si>
     <t xml:space="preserve">17.1544551849365</t>
   </si>
   <si>
-    <t xml:space="preserve">17.244930267334</t>
+    <t xml:space="preserve">17.2449321746826</t>
   </si>
   <si>
     <t xml:space="preserve">17.1182651519775</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8106422424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8287372589111</t>
+    <t xml:space="preserve">16.8106441497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8287391662598</t>
   </si>
   <si>
     <t xml:space="preserve">16.973503112793</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">17.0639801025391</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8468322753906</t>
+    <t xml:space="preserve">16.8468360900879</t>
   </si>
   <si>
     <t xml:space="preserve">16.9011192321777</t>
@@ -2450,28 +2450,28 @@
     <t xml:space="preserve">17.3173160552979</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2087440490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2268390655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3668460845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4573249816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6382789611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.728759765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9549522399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8644733428955</t>
+    <t xml:space="preserve">17.2087421417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2268371582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3668479919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4573268890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6382808685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7287578582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9549503326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8644752502441</t>
   </si>
   <si>
     <t xml:space="preserve">19.6335296630859</t>
@@ -2486,19 +2486,19 @@
     <t xml:space="preserve">19.0454254150391</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0001888275146</t>
+    <t xml:space="preserve">19.000186920166</t>
   </si>
   <si>
     <t xml:space="preserve">19.316858291626</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3216133117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2311305999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0906658172607</t>
+    <t xml:space="preserve">18.3216094970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2311325073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0906677246094</t>
   </si>
   <si>
     <t xml:space="preserve">18.6835174560547</t>
@@ -2507,28 +2507,28 @@
     <t xml:space="preserve">18.0954170227051</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0049381256104</t>
+    <t xml:space="preserve">18.004940032959</t>
   </si>
   <si>
     <t xml:space="preserve">17.570650100708</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8239879608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6430339813232</t>
+    <t xml:space="preserve">17.8239860534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6430320739746</t>
   </si>
   <si>
     <t xml:space="preserve">17.8058891296387</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2716178894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1811447143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.26686668396</t>
+    <t xml:space="preserve">19.2716197967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1811428070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2668685913086</t>
   </si>
   <si>
     <t xml:space="preserve">20.4930591583252</t>
@@ -2546,22 +2546,22 @@
     <t xml:space="preserve">19.9049587249756</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7692432403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7192535400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9954357147217</t>
+    <t xml:space="preserve">19.7692451477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7192516326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9954376220703</t>
   </si>
   <si>
     <t xml:space="preserve">19.2263813018799</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4525737762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4073371887207</t>
+    <t xml:space="preserve">19.4525718688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4073352813721</t>
   </si>
   <si>
     <t xml:space="preserve">17.6249370574951</t>
@@ -2570,7 +2570,7 @@
     <t xml:space="preserve">17.7877941131592</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4978103637695</t>
+    <t xml:space="preserve">19.4978122711182</t>
   </si>
   <si>
     <t xml:space="preserve">20.0859146118164</t>
@@ -2579,31 +2579,31 @@
     <t xml:space="preserve">20.1311511993408</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8597221374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.674015045166</t>
+    <t xml:space="preserve">19.8597202301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6740169525146</t>
   </si>
   <si>
     <t xml:space="preserve">21.0359230041504</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8097305297852</t>
+    <t xml:space="preserve">20.8097286224365</t>
   </si>
   <si>
     <t xml:space="preserve">20.628776550293</t>
   </si>
   <si>
-    <t xml:space="preserve">20.312105178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4478206634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8821105957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2802124023438</t>
+    <t xml:space="preserve">20.3121070861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4478225708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8821125030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2802104949951</t>
   </si>
   <si>
     <t xml:space="preserve">21.3344974517822</t>
@@ -2612,13 +2612,13 @@
     <t xml:space="preserve">21.5878353118896</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6602153778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1668872833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6192722320557</t>
+    <t xml:space="preserve">21.660213470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1668853759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.619270324707</t>
   </si>
   <si>
     <t xml:space="preserve">22.8726081848145</t>
@@ -2627,19 +2627,19 @@
     <t xml:space="preserve">23.9040470123291</t>
   </si>
   <si>
-    <t xml:space="preserve">22.782133102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8592643737793</t>
+    <t xml:space="preserve">22.7821311950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8592662811279</t>
   </si>
   <si>
     <t xml:space="preserve">22.0040264129639</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2573661804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4745101928711</t>
+    <t xml:space="preserve">22.2573642730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4745082855225</t>
   </si>
   <si>
     <t xml:space="preserve">22.1126003265381</t>
@@ -2648,76 +2648,76 @@
     <t xml:space="preserve">22.058313369751</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6011772155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6373653411865</t>
+    <t xml:space="preserve">22.6011753082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6373672485352</t>
   </si>
   <si>
     <t xml:space="preserve">22.420223236084</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4021282196045</t>
+    <t xml:space="preserve">22.4021263122559</t>
   </si>
   <si>
     <t xml:space="preserve">21.3525943756104</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2621173858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0945053100586</t>
+    <t xml:space="preserve">21.262113571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0945072174072</t>
   </si>
   <si>
     <t xml:space="preserve">22.5830783843994</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0354690551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.017370223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3611850738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2707061767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0440578460693</t>
+    <t xml:space="preserve">23.0354671478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0173721313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3611831665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2707080841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.044059753418</t>
   </si>
   <si>
     <t xml:space="preserve">24.7726268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9716758728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0621528625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9126396179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2383575439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6765727996826</t>
+    <t xml:space="preserve">24.9716777801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0621547698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9126358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2383518218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6765747070312</t>
   </si>
   <si>
     <t xml:space="preserve">26.7130928039551</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5852794647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6583156585693</t>
+    <t xml:space="preserve">26.585277557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.658317565918</t>
   </si>
   <si>
     <t xml:space="preserve">26.8226451873779</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9504585266113</t>
+    <t xml:space="preserve">26.95046043396</t>
   </si>
   <si>
     <t xml:space="preserve">27.5712718963623</t>
@@ -2726,22 +2726,22 @@
     <t xml:space="preserve">27.6260471343994</t>
   </si>
   <si>
-    <t xml:space="preserve">28.064266204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2833728790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8171405792236</t>
+    <t xml:space="preserve">28.0642642974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.283374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8171424865723</t>
   </si>
   <si>
     <t xml:space="preserve">29.5980319976807</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9589614868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1275463104248</t>
+    <t xml:space="preserve">28.958963394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1275482177734</t>
   </si>
   <si>
     <t xml:space="preserve">29.6528091430664</t>
@@ -2750,16 +2750,16 @@
     <t xml:space="preserve">30.1092872619629</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9632148742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4014320373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2188415527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2961292266846</t>
+    <t xml:space="preserve">29.9632129669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4014301300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2188396453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2961311340332</t>
   </si>
   <si>
     <t xml:space="preserve">30.8213920593262</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">30.2371006011963</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4154415130615</t>
+    <t xml:space="preserve">29.4154434204102</t>
   </si>
   <si>
     <t xml:space="preserve">29.8536605834961</t>
@@ -2786,40 +2786,40 @@
     <t xml:space="preserve">29.7075881958008</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0545101165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8664131164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.546257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0532608032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0855255126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7245941162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6880798339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5785217285156</t>
+    <t xml:space="preserve">30.0545120239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8664169311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5462532043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0532569885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0855293273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7245903015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6880760192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5785179138184</t>
   </si>
   <si>
     <t xml:space="preserve">33.4872245788574</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7976341247559</t>
+    <t xml:space="preserve">33.7976303100586</t>
   </si>
   <si>
     <t xml:space="preserve">33.1403007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2863731384277</t>
+    <t xml:space="preserve">33.2863693237305</t>
   </si>
   <si>
     <t xml:space="preserve">32.2273445129395</t>
@@ -2831,13 +2831,13 @@
     <t xml:space="preserve">32.7568626403809</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6473045349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0307464599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7751197814941</t>
+    <t xml:space="preserve">32.6473083496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0307502746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7751235961914</t>
   </si>
   <si>
     <t xml:space="preserve">32.4099349975586</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">32.6655616760254</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6923294067383</t>
+    <t xml:space="preserve">34.692325592041</t>
   </si>
   <si>
     <t xml:space="preserve">35.605281829834</t>
@@ -2858,16 +2858,16 @@
     <t xml:space="preserve">35.8791694641113</t>
   </si>
   <si>
-    <t xml:space="preserve">35.477466583252</t>
+    <t xml:space="preserve">35.4774742126465</t>
   </si>
   <si>
     <t xml:space="preserve">35.0940284729004</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5870246887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7878761291504</t>
+    <t xml:space="preserve">35.5870208740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7878723144531</t>
   </si>
   <si>
     <t xml:space="preserve">36.0435028076172</t>
@@ -2882,13 +2882,13 @@
     <t xml:space="preserve">38.4354438781738</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4944725036621</t>
+    <t xml:space="preserve">39.4944763183594</t>
   </si>
   <si>
     <t xml:space="preserve">39.3849182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2205848693848</t>
+    <t xml:space="preserve">39.220588684082</t>
   </si>
   <si>
     <t xml:space="preserve">39.1292915344238</t>
@@ -2912,31 +2912,31 @@
     <t xml:space="preserve">36.7008323669434</t>
   </si>
   <si>
-    <t xml:space="preserve">37.212085723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.559009552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0154876708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6503105163574</t>
+    <t xml:space="preserve">37.2120819091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5590057373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0154838562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6503067016602</t>
   </si>
   <si>
     <t xml:space="preserve">35.6235427856445</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2315979003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9942245483398</t>
+    <t xml:space="preserve">33.2316017150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9942283630371</t>
   </si>
   <si>
     <t xml:space="preserve">33.3594093322754</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0490036010742</t>
+    <t xml:space="preserve">33.0490112304688</t>
   </si>
   <si>
     <t xml:space="preserve">34.7836227416992</t>
@@ -2945,19 +2945,19 @@
     <t xml:space="preserve">34.3819236755371</t>
   </si>
   <si>
-    <t xml:space="preserve">34.893180847168</t>
+    <t xml:space="preserve">34.8931770324707</t>
   </si>
   <si>
     <t xml:space="preserve">32.9577102661133</t>
   </si>
   <si>
-    <t xml:space="preserve">33.63330078125</t>
+    <t xml:space="preserve">33.6332969665527</t>
   </si>
   <si>
     <t xml:space="preserve">35.513988494873</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4817199707031</t>
+    <t xml:space="preserve">36.4817237854004</t>
   </si>
   <si>
     <t xml:space="preserve">36.3173866271973</t>
@@ -2972,13 +2972,13 @@
     <t xml:space="preserve">38.2711143493652</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2023315429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7190933227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8426513671875</t>
+    <t xml:space="preserve">39.2023277282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7190895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8426475524902</t>
   </si>
   <si>
     <t xml:space="preserve">34.9662132263184</t>
@@ -2987,25 +2987,25 @@
     <t xml:space="preserve">35.1488075256348</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4409484863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8876686096191</t>
+    <t xml:space="preserve">35.4409523010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8876724243164</t>
   </si>
   <si>
     <t xml:space="preserve">38.5267448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8006286621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6685600280762</t>
+    <t xml:space="preserve">38.8006324768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6685638427734</t>
   </si>
   <si>
     <t xml:space="preserve">35.4226913452148</t>
   </si>
   <si>
-    <t xml:space="preserve">35.258358001709</t>
+    <t xml:space="preserve">35.2583618164062</t>
   </si>
   <si>
     <t xml:space="preserve">34.9114379882812</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">34.3636627197266</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8341522216797</t>
+    <t xml:space="preserve">33.8341484069824</t>
   </si>
   <si>
     <t xml:space="preserve">33.5967826843262</t>
@@ -3035,16 +3035,16 @@
     <t xml:space="preserve">34.7105865478516</t>
   </si>
   <si>
-    <t xml:space="preserve">34.345401763916</t>
+    <t xml:space="preserve">34.3454055786133</t>
   </si>
   <si>
     <t xml:space="preserve">34.0715179443359</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1950798034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6150398254395</t>
+    <t xml:space="preserve">33.1950836181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6150360107422</t>
   </si>
   <si>
     <t xml:space="preserve">33.9254455566406</t>
@@ -3053,25 +3053,25 @@
     <t xml:space="preserve">33.9437026977539</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6192855834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5827751159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7288513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0027313232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8384017944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8749160766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5377502441406</t>
+    <t xml:space="preserve">34.6192893981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5827713012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7288436889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0027351379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8383979797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8749198913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5377464294434</t>
   </si>
   <si>
     <t xml:space="preserve">32.1725692749023</t>
@@ -3089,31 +3089,31 @@
     <t xml:space="preserve">30.1640663146973</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4294471740723</t>
+    <t xml:space="preserve">28.4294509887695</t>
   </si>
   <si>
     <t xml:space="preserve">28.1007843017578</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6808242797852</t>
+    <t xml:space="preserve">27.6808261871338</t>
   </si>
   <si>
     <t xml:space="preserve">28.9954833984375</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2693691253662</t>
+    <t xml:space="preserve">29.2693710327148</t>
   </si>
   <si>
     <t xml:space="preserve">28.6850776672363</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9687194824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8956813812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8451557159424</t>
+    <t xml:space="preserve">26.9687213897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8956832885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.845157623291</t>
   </si>
   <si>
     <t xml:space="preserve">27.9729690551758</t>
@@ -3122,31 +3122,31 @@
     <t xml:space="preserve">28.6668186187744</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1232967376709</t>
+    <t xml:space="preserve">29.1232948303223</t>
   </si>
   <si>
     <t xml:space="preserve">28.9224472045898</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6077861785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7538604736328</t>
+    <t xml:space="preserve">27.6077880859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7538623809814</t>
   </si>
   <si>
     <t xml:space="preserve">26.3479099273682</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5445079803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7496070861816</t>
+    <t xml:space="preserve">25.5445098876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7496109008789</t>
   </si>
   <si>
     <t xml:space="preserve">26.7861289978027</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5670185089111</t>
+    <t xml:space="preserve">26.5670204162598</t>
   </si>
   <si>
     <t xml:space="preserve">27.9547119140625</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">27.1147937774658</t>
   </si>
   <si>
-    <t xml:space="preserve">26.731351852417</t>
+    <t xml:space="preserve">26.7313537597656</t>
   </si>
   <si>
     <t xml:space="preserve">27.4069385528564</t>
@@ -3170,22 +3170,22 @@
     <t xml:space="preserve">27.9912300109863</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6948318481445</t>
+    <t xml:space="preserve">26.6948337554932</t>
   </si>
   <si>
     <t xml:space="preserve">27.4434566497803</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3113918304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5542640686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.70458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.097785949707</t>
+    <t xml:space="preserve">26.3113899230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5542621612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7045860290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0977840423584</t>
   </si>
   <si>
     <t xml:space="preserve">22.0022392272949</t>
@@ -3206,10 +3206,10 @@
     <t xml:space="preserve">22.5134944915771</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1525650024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2073402404785</t>
+    <t xml:space="preserve">23.1525630950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2073421478271</t>
   </si>
   <si>
     <t xml:space="preserve">24.5402545928955</t>
@@ -3218,31 +3218,31 @@
     <t xml:space="preserve">24.6680698394775</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8689193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4489631652832</t>
+    <t xml:space="preserve">24.8689212799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4489612579346</t>
   </si>
   <si>
     <t xml:space="preserve">25.2341022491455</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5585155487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0290012359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.138557434082</t>
+    <t xml:space="preserve">24.5585136413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0289993286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1385555267334</t>
   </si>
   <si>
     <t xml:space="preserve">24.0472602844238</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3984336853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4166927337646</t>
+    <t xml:space="preserve">25.3984355926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4166946411133</t>
   </si>
   <si>
     <t xml:space="preserve">24.2115936279297</t>
@@ -3251,28 +3251,28 @@
     <t xml:space="preserve">24.0837783813477</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8098907470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3351535797119</t>
+    <t xml:space="preserve">23.8098926544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3351554870605</t>
   </si>
   <si>
     <t xml:space="preserve">22.4221973419189</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7326030731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.677827835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.276123046875</t>
+    <t xml:space="preserve">22.7326049804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6778259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2761249542236</t>
   </si>
   <si>
     <t xml:space="preserve">21.9109439849854</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2213478088379</t>
+    <t xml:space="preserve">22.2213497161865</t>
   </si>
   <si>
     <t xml:space="preserve">21.8379077911377</t>
@@ -3284,19 +3284,19 @@
     <t xml:space="preserve">22.8239002227783</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5457611083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0710220336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9657192230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1988372802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2718753814697</t>
+    <t xml:space="preserve">21.5457630157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0710258483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9657211303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1988353729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2718734741211</t>
   </si>
   <si>
     <t xml:space="preserve">20.8884315490723</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">19.9024410247803</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2493629455566</t>
+    <t xml:space="preserve">20.2493648529053</t>
   </si>
   <si>
     <t xml:space="preserve">20.9614677429199</t>
@@ -3329,43 +3329,43 @@
     <t xml:space="preserve">20.8519134521484</t>
   </si>
   <si>
-    <t xml:space="preserve">20.724100112915</t>
+    <t xml:space="preserve">20.7241020202637</t>
   </si>
   <si>
     <t xml:space="preserve">21.0162467956543</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3449115753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.395435333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5232486724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6693229675293</t>
+    <t xml:space="preserve">21.3449096679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3954391479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.523250579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6693210601807</t>
   </si>
   <si>
     <t xml:space="preserve">22.1300525665283</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1933326721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6455593109131</t>
+    <t xml:space="preserve">24.1933345794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6455612182617</t>
   </si>
   <si>
     <t xml:space="preserve">23.5177459716797</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7368545532227</t>
+    <t xml:space="preserve">23.7368564605713</t>
   </si>
   <si>
     <t xml:space="preserve">23.0533809661865</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9240760803223</t>
+    <t xml:space="preserve">22.9240741729736</t>
   </si>
   <si>
     <t xml:space="preserve">22.7393550872803</t>
@@ -3377,10 +3377,10 @@
     <t xml:space="preserve">20.7443466186523</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6914291381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2850399017334</t>
+    <t xml:space="preserve">19.6914310455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2850379943848</t>
   </si>
   <si>
     <t xml:space="preserve">20.319486618042</t>
@@ -3392,7 +3392,7 @@
     <t xml:space="preserve">21.2246265411377</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3539333343506</t>
+    <t xml:space="preserve">21.3539352416992</t>
   </si>
   <si>
     <t xml:space="preserve">21.316987991333</t>
@@ -3407,28 +3407,28 @@
     <t xml:space="preserve">21.4278240203857</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5571269989014</t>
+    <t xml:space="preserve">21.55712890625</t>
   </si>
   <si>
     <t xml:space="preserve">21.7972679138184</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5596256256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7812938690186</t>
+    <t xml:space="preserve">20.559627532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7812919616699</t>
   </si>
   <si>
     <t xml:space="preserve">20.3379592895508</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9130973815918</t>
+    <t xml:space="preserve">19.9130954742432</t>
   </si>
   <si>
     <t xml:space="preserve">20.9475440979004</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0374088287354</t>
+    <t xml:space="preserve">22.0374069213867</t>
   </si>
   <si>
     <t xml:space="preserve">22.4992141723633</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">21.6679611206055</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4647655487061</t>
+    <t xml:space="preserve">21.4647674560547</t>
   </si>
   <si>
     <t xml:space="preserve">20.8182392120361</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">20.2271251678467</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4487934112549</t>
+    <t xml:space="preserve">20.4487915039062</t>
   </si>
   <si>
     <t xml:space="preserve">21.3908786773682</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">22.3883800506592</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2960186004639</t>
+    <t xml:space="preserve">22.2960205078125</t>
   </si>
   <si>
     <t xml:space="preserve">22.5361576080322</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">21.5017127990723</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7787952423096</t>
+    <t xml:space="preserve">21.7787933349609</t>
   </si>
   <si>
     <t xml:space="preserve">21.7233791351318</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">19.9500408172607</t>
   </si>
   <si>
-    <t xml:space="preserve">19.74684715271</t>
+    <t xml:space="preserve">19.7468452453613</t>
   </si>
   <si>
     <t xml:space="preserve">19.5436515808105</t>
@@ -3527,16 +3527,16 @@
     <t xml:space="preserve">18.472261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1926803588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5830974578857</t>
+    <t xml:space="preserve">19.1926784515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5830955505371</t>
   </si>
   <si>
     <t xml:space="preserve">18.2413578033447</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0566349029541</t>
+    <t xml:space="preserve">18.0566329956055</t>
   </si>
   <si>
     <t xml:space="preserve">17.7426052093506</t>
@@ -3557,13 +3557,13 @@
     <t xml:space="preserve">16.8374652862549</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9852447509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.280797958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0037155151367</t>
+    <t xml:space="preserve">16.9852428436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2807998657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0037174224854</t>
   </si>
   <si>
     <t xml:space="preserve">17.6779537200928</t>
@@ -3572,22 +3572,22 @@
     <t xml:space="preserve">17.6317729949951</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8164958953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5855941772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5024681091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0683689117432</t>
+    <t xml:space="preserve">17.8164939880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5855922698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5024662017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0683670043945</t>
   </si>
   <si>
     <t xml:space="preserve">17.2346210479736</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2530918121338</t>
+    <t xml:space="preserve">17.2530899047852</t>
   </si>
   <si>
     <t xml:space="preserve">16.9390621185303</t>
@@ -3611,10 +3611,10 @@
     <t xml:space="preserve">17.7333698272705</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3429546356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4697647094727</t>
+    <t xml:space="preserve">18.3429565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.469762802124</t>
   </si>
   <si>
     <t xml:space="preserve">19.5805969238281</t>
@@ -3632,16 +3632,16 @@
     <t xml:space="preserve">18.3891353607178</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2967739105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4907341003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0079574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0239295959473</t>
+    <t xml:space="preserve">18.2967720031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4907321929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0079555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0239315032959</t>
   </si>
   <si>
     <t xml:space="preserve">19.8392066955566</t>
@@ -3662,31 +3662,31 @@
     <t xml:space="preserve">20.5226802825928</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3354625701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2431011199951</t>
+    <t xml:space="preserve">21.3354606628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2430992126465</t>
   </si>
   <si>
     <t xml:space="preserve">21.9265727996826</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7418518066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2800445556641</t>
+    <t xml:space="preserve">21.7418537139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2800464630127</t>
   </si>
   <si>
     <t xml:space="preserve">21.4093494415283</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8526859283447</t>
+    <t xml:space="preserve">21.8526840209961</t>
   </si>
   <si>
     <t xml:space="preserve">21.1507396697998</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0583782196045</t>
+    <t xml:space="preserve">21.0583763122559</t>
   </si>
   <si>
     <t xml:space="preserve">20.3933753967285</t>
@@ -3698,10 +3698,10 @@
     <t xml:space="preserve">19.9315700531006</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9685134887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2825412750244</t>
+    <t xml:space="preserve">19.9685153961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.282543182373</t>
   </si>
   <si>
     <t xml:space="preserve">20.9290714263916</t>
@@ -3728,13 +3728,13 @@
     <t xml:space="preserve">23.4412975311279</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9031047821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.792272567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.127269744873</t>
+    <t xml:space="preserve">23.9031028747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7922706604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1272716522217</t>
   </si>
   <si>
     <t xml:space="preserve">23.7553272247314</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">23.4782428741455</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1087989807129</t>
+    <t xml:space="preserve">23.1087970733643</t>
   </si>
   <si>
     <t xml:space="preserve">22.9979629516602</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">23.0164375305176</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9585227966309</t>
+    <t xml:space="preserve">23.9585247039795</t>
   </si>
   <si>
     <t xml:space="preserve">23.5706043243408</t>
@@ -3767,7 +3767,7 @@
     <t xml:space="preserve">24.1247730255127</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5151882171631</t>
+    <t xml:space="preserve">23.5151863098145</t>
   </si>
   <si>
     <t xml:space="preserve">22.8686599731445</t>
@@ -3779,10 +3779,10 @@
     <t xml:space="preserve">22.9056015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8132419586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6285190582275</t>
+    <t xml:space="preserve">22.8132438659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6285209655762</t>
   </si>
   <si>
     <t xml:space="preserve">22.4622688293457</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">22.2590751647949</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8342113494873</t>
+    <t xml:space="preserve">21.8342132568359</t>
   </si>
   <si>
     <t xml:space="preserve">22.0928230285645</t>
@@ -3821,13 +3821,13 @@
     <t xml:space="preserve">18.6569843292236</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1187915802002</t>
+    <t xml:space="preserve">19.1187896728516</t>
   </si>
   <si>
     <t xml:space="preserve">18.5646228790283</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6754570007324</t>
+    <t xml:space="preserve">18.6754550933838</t>
   </si>
   <si>
     <t xml:space="preserve">19.0264301300049</t>
@@ -3836,7 +3836,7 @@
     <t xml:space="preserve">18.2690658569336</t>
   </si>
   <si>
-    <t xml:space="preserve">18.509204864502</t>
+    <t xml:space="preserve">18.5092067718506</t>
   </si>
   <si>
     <t xml:space="preserve">18.8232345581055</t>
@@ -3848,10 +3848,10 @@
     <t xml:space="preserve">18.7123985290527</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7308731079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6200370788574</t>
+    <t xml:space="preserve">18.7308712005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6200389862061</t>
   </si>
   <si>
     <t xml:space="preserve">18.4445514678955</t>
@@ -3860,13 +3860,13 @@
     <t xml:space="preserve">18.3614273071289</t>
   </si>
   <si>
-    <t xml:space="preserve">17.798023223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5486469268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1422576904297</t>
+    <t xml:space="preserve">17.7980251312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5486488342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1422557830811</t>
   </si>
   <si>
     <t xml:space="preserve">16.948299407959</t>
@@ -3875,16 +3875,16 @@
     <t xml:space="preserve">16.9205894470215</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8651752471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5696182250977</t>
+    <t xml:space="preserve">16.8651733398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5696201324463</t>
   </si>
   <si>
     <t xml:space="preserve">16.8559379577637</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1145496368408</t>
+    <t xml:space="preserve">17.1145515441895</t>
   </si>
   <si>
     <t xml:space="preserve">16.7451038360596</t>
@@ -3893,19 +3893,19 @@
     <t xml:space="preserve">16.9021186828613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8744106292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7912864685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.846700668335</t>
+    <t xml:space="preserve">16.8744125366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7912845611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8467025756836</t>
   </si>
   <si>
     <t xml:space="preserve">16.809757232666</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5880889892578</t>
+    <t xml:space="preserve">16.5880870819092</t>
   </si>
   <si>
     <t xml:space="preserve">16.671215057373</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">15.710657119751</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0708675384521</t>
+    <t xml:space="preserve">16.0708656311035</t>
   </si>
   <si>
     <t xml:space="preserve">16.0893402099609</t>
@@ -3932,7 +3932,7 @@
     <t xml:space="preserve">16.0062160491943</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0523929595947</t>
+    <t xml:space="preserve">16.0523948669434</t>
   </si>
   <si>
     <t xml:space="preserve">16.6896858215332</t>
@@ -71002,7 +71002,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.6911574074</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>42722</v>
@@ -71023,6 +71023,32 @@
         <v>1773</v>
       </c>
       <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.6912847222</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>183493</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>14.7799997329712</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>14.710000038147</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>14.7600002288818</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>1774</v>
+      </c>
+      <c r="H2514" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TNXT.MI.xlsx
+++ b/data/TNXT.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">TNXT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65151000022888</t>
+    <t xml:space="preserve">2.65150952339172</t>
   </si>
   <si>
     <t xml:space="preserve">2.59350848197937</t>
@@ -56,16 +56,16 @@
     <t xml:space="preserve">2.52556347846985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48579025268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52722072601318</t>
+    <t xml:space="preserve">2.48579049110413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52722096443176</t>
   </si>
   <si>
     <t xml:space="preserve">2.48744821548462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47087597846985</t>
+    <t xml:space="preserve">2.47087574005127</t>
   </si>
   <si>
     <t xml:space="preserve">2.46921873092651</t>
@@ -74,25 +74,25 @@
     <t xml:space="preserve">2.54047799110413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49739122390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47916173934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44436049461365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39464449882507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34161496162415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36150121688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55207872390747</t>
+    <t xml:space="preserve">2.49739146232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47916197776794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44436097145081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39464497566223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34161448478699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36150074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55207848548889</t>
   </si>
   <si>
     <t xml:space="preserve">2.58522272109985</t>
@@ -116,22 +116,22 @@
     <t xml:space="preserve">2.72608351707458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77579951286316</t>
+    <t xml:space="preserve">2.77579975128174</t>
   </si>
   <si>
     <t xml:space="preserve">2.58025097846985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56202173233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66808176040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62830924987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64322400093079</t>
+    <t xml:space="preserve">2.5620219707489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66808199882507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62830853462219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64322352409363</t>
   </si>
   <si>
     <t xml:space="preserve">2.60842251777649</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">2.66642451286316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65316677093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62665128707886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6929395198822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82551574707031</t>
+    <t xml:space="preserve">2.65316653251648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62665176391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69293975830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82551527023315</t>
   </si>
   <si>
     <t xml:space="preserve">2.81722950935364</t>
@@ -161,31 +161,31 @@
     <t xml:space="preserve">2.85865926742554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89843249320984</t>
+    <t xml:space="preserve">2.89843201637268</t>
   </si>
   <si>
     <t xml:space="preserve">2.8835175037384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87523126602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86694574356079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81888604164124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82054400444031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85368752479553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79237127304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8570020198822</t>
+    <t xml:space="preserve">2.87523150444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86694550514221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81888651847839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82054352760315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85368800163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79237174987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85700225830078</t>
   </si>
   <si>
     <t xml:space="preserve">2.90671801567078</t>
@@ -194,13 +194,13 @@
     <t xml:space="preserve">2.82882976531982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85037350654602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90837502479553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96306276321411</t>
+    <t xml:space="preserve">2.85037326812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90837526321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96306300163269</t>
   </si>
   <si>
     <t xml:space="preserve">2.95797729492188</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">2.88169717788696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89017295837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86474585533142</t>
+    <t xml:space="preserve">2.89017248153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86474561691284</t>
   </si>
   <si>
     <t xml:space="preserve">2.94950199127197</t>
@@ -227,25 +227,25 @@
     <t xml:space="preserve">3.11901307106018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94272136688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94780683517456</t>
+    <t xml:space="preserve">2.94272112846375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94780659675598</t>
   </si>
   <si>
     <t xml:space="preserve">2.88339185714722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87322163581848</t>
+    <t xml:space="preserve">2.8732213973999</t>
   </si>
   <si>
     <t xml:space="preserve">2.85966062545776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03256249427795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07037377357483</t>
+    <t xml:space="preserve">3.03256273269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07037353515625</t>
   </si>
   <si>
     <t xml:space="preserve">3.06866312026978</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">2.99340057373047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98484826087952</t>
+    <t xml:space="preserve">2.98484778404236</t>
   </si>
   <si>
     <t xml:space="preserve">2.93524289131165</t>
@@ -269,49 +269,49 @@
     <t xml:space="preserve">2.92497992515564</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92326927185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96774315834045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0361635684967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05840015411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05497860908508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08747887611389</t>
+    <t xml:space="preserve">2.92326951026917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9677426815033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03616285324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05839991569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05497932434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08747863769531</t>
   </si>
   <si>
     <t xml:space="preserve">3.13879442214966</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12853121757507</t>
+    <t xml:space="preserve">3.12853097915649</t>
   </si>
   <si>
     <t xml:space="preserve">3.19010972976685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15589952468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12339973449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12511038780212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14734673500061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16445183753967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16616225242615</t>
+    <t xml:space="preserve">3.1558997631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12339949607849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12511014938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14734721183777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16445207595825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16616249084473</t>
   </si>
   <si>
     <t xml:space="preserve">3.24142527580261</t>
@@ -326,37 +326,37 @@
     <t xml:space="preserve">3.48431777954102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52708101272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62629079818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63655352592468</t>
+    <t xml:space="preserve">3.52708125114441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62629055976868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63655400276184</t>
   </si>
   <si>
     <t xml:space="preserve">3.64510631561279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74602723121643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67760682106018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71181726455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63484334945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5168182849884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50484466552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4945809841156</t>
+    <t xml:space="preserve">3.74602699279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6776065826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71181678771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63484382629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51681780815125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50484442710876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49458122253418</t>
   </si>
   <si>
     <t xml:space="preserve">3.50655508041382</t>
@@ -365,10 +365,10 @@
     <t xml:space="preserve">3.48089718818665</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43129205703735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35602951049805</t>
+    <t xml:space="preserve">3.43129253387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35602974891663</t>
   </si>
   <si>
     <t xml:space="preserve">3.60063362121582</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">3.69471192359924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69984340667725</t>
+    <t xml:space="preserve">3.69984292984009</t>
   </si>
   <si>
     <t xml:space="preserve">3.67589569091797</t>
@@ -395,76 +395,76 @@
     <t xml:space="preserve">3.63313317298889</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57497549057007</t>
+    <t xml:space="preserve">3.57497525215149</t>
   </si>
   <si>
     <t xml:space="preserve">3.66050124168396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68615865707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71523761749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73747444152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71010589599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69129037857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68957996368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73234295845032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72036910057068</t>
+    <t xml:space="preserve">3.68615889549255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71523714065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7374746799469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71010637283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69129061698914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68958020210266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73234248161316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7203688621521</t>
   </si>
   <si>
     <t xml:space="preserve">3.76313185691833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77168416976929</t>
+    <t xml:space="preserve">3.77168488502502</t>
   </si>
   <si>
     <t xml:space="preserve">3.62115955352783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64168524742126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7032642364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79734230041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75457882881165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90852618217468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76655268669128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72892212867737</t>
+    <t xml:space="preserve">3.64168572425842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70326399803162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79734253883362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75457954406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90852570533752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76655340194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72892165184021</t>
   </si>
   <si>
     <t xml:space="preserve">3.66734313964844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50997591018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49800252914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48944997787476</t>
+    <t xml:space="preserve">3.50997614860535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49800205230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4894495010376</t>
   </si>
   <si>
     <t xml:space="preserve">3.47234463691711</t>
@@ -473,49 +473,49 @@
     <t xml:space="preserve">3.40392398834229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43642401695251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53221273422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5185284614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46037125587463</t>
+    <t xml:space="preserve">3.43642354011536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53221249580383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51852798461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46037101745605</t>
   </si>
   <si>
     <t xml:space="preserve">3.50142312049866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53563332557678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55615949630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64339661598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72550058364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84865736961365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82984232902527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83155298233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87089514732361</t>
+    <t xml:space="preserve">3.53563356399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55615997314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64339637756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72550129890442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84865832328796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82984256744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83155250549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87089419364929</t>
   </si>
   <si>
     <t xml:space="preserve">3.8452365398407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87431597709656</t>
+    <t xml:space="preserve">3.87431573867798</t>
   </si>
   <si>
     <t xml:space="preserve">3.86405253410339</t>
@@ -524,19 +524,19 @@
     <t xml:space="preserve">3.85721039772034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82471108436584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90681481361389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00260400772095</t>
+    <t xml:space="preserve">3.82471132278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90681529045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00260496139526</t>
   </si>
   <si>
     <t xml:space="preserve">4.17536640167236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11378717422485</t>
+    <t xml:space="preserve">4.11378765106201</t>
   </si>
   <si>
     <t xml:space="preserve">4.00773525238037</t>
@@ -545,10 +545,10 @@
     <t xml:space="preserve">4.05220890045166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08128786087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00602531433105</t>
+    <t xml:space="preserve">4.08128690719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00602436065674</t>
   </si>
   <si>
     <t xml:space="preserve">4.09839248657227</t>
@@ -557,19 +557,19 @@
     <t xml:space="preserve">4.01970911026001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01115751266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99576187133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0351037979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06247186660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13773536682129</t>
+    <t xml:space="preserve">4.01115703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99576210975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03510284423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06247282028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13773488998413</t>
   </si>
   <si>
     <t xml:space="preserve">4.12234020233154</t>
@@ -584,16 +584,16 @@
     <t xml:space="preserve">4.25918102264404</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22839164733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20615530014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02142000198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99405121803284</t>
+    <t xml:space="preserve">4.22839260101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20615577697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02141904830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99405169487</t>
   </si>
   <si>
     <t xml:space="preserve">4.01799917221069</t>
@@ -605,16 +605,16 @@
     <t xml:space="preserve">4.07615613937378</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12747240066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11891889572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10523509979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09668254852295</t>
+    <t xml:space="preserve">4.12747192382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11891937255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10523557662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09668207168579</t>
   </si>
   <si>
     <t xml:space="preserve">4.10181379318237</t>
@@ -623,43 +623,43 @@
     <t xml:space="preserve">4.07102489471436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09497165679932</t>
+    <t xml:space="preserve">4.09497117996216</t>
   </si>
   <si>
     <t xml:space="preserve">4.13089275360107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21641826629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52431106567383</t>
+    <t xml:space="preserve">4.21641874313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52431058883667</t>
   </si>
   <si>
     <t xml:space="preserve">4.54996919631958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53713989257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46444272994995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50293016433716</t>
+    <t xml:space="preserve">4.53713941574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46444320678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5029296875</t>
   </si>
   <si>
     <t xml:space="preserve">4.56707429885864</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6226658821106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63549518585205</t>
+    <t xml:space="preserve">4.62266540527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63549470901489</t>
   </si>
   <si>
     <t xml:space="preserve">4.58417940139771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60128402709961</t>
+    <t xml:space="preserve">4.60128450393677</t>
   </si>
   <si>
     <t xml:space="preserve">4.57562637329102</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">4.61838912963867</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53286457061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55852174758911</t>
+    <t xml:space="preserve">4.53286361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55852127075195</t>
   </si>
   <si>
     <t xml:space="preserve">4.48154783248901</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">4.4901008605957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51148271560669</t>
+    <t xml:space="preserve">4.51148223876953</t>
   </si>
   <si>
     <t xml:space="preserve">4.63121843338013</t>
@@ -692,34 +692,34 @@
     <t xml:space="preserve">4.78516483306885</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75950622558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78944063186646</t>
+    <t xml:space="preserve">4.75950717926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78944110870361</t>
   </si>
   <si>
     <t xml:space="preserve">4.7338490486145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77233552932739</t>
+    <t xml:space="preserve">4.77233600616455</t>
   </si>
   <si>
     <t xml:space="preserve">4.76378345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6568751335144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69536304473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82792711257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90062475204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91772985458374</t>
+    <t xml:space="preserve">4.65687561035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69536209106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8279275894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90062427520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91772937774658</t>
   </si>
   <si>
     <t xml:space="preserve">4.94338703155518</t>
@@ -728,40 +728,40 @@
     <t xml:space="preserve">4.98614978790283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04174184799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02036046981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07167530059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08022832870483</t>
+    <t xml:space="preserve">5.04174137115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02035999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0716757774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08022785186768</t>
   </si>
   <si>
     <t xml:space="preserve">4.99470281600952</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09305667877197</t>
+    <t xml:space="preserve">5.09305715560913</t>
   </si>
   <si>
     <t xml:space="preserve">5.06050682067871</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91728544235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94766473770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92596578598022</t>
+    <t xml:space="preserve">4.91728496551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94766521453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92596530914307</t>
   </si>
   <si>
     <t xml:space="preserve">4.9042649269104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8218035697937</t>
+    <t xml:space="preserve">4.82180404663086</t>
   </si>
   <si>
     <t xml:space="preserve">4.7350025177002</t>
@@ -779,16 +779,16 @@
     <t xml:space="preserve">4.73066234588623</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66556119918823</t>
+    <t xml:space="preserve">4.66556072235107</t>
   </si>
   <si>
     <t xml:space="preserve">4.65254163742065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60914039611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65688133239746</t>
+    <t xml:space="preserve">4.60914134979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65688180923462</t>
   </si>
   <si>
     <t xml:space="preserve">4.54837989807129</t>
@@ -800,13 +800,13 @@
     <t xml:space="preserve">4.47025918960571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59612131118774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47459936141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48761940002441</t>
+    <t xml:space="preserve">4.59612083435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47459888458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48761987686157</t>
   </si>
   <si>
     <t xml:space="preserve">4.46157884597778</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">4.41383838653564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38779735565186</t>
+    <t xml:space="preserve">4.38779783248901</t>
   </si>
   <si>
     <t xml:space="preserve">4.39213752746582</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">4.52233982086182</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57008075714111</t>
+    <t xml:space="preserve">4.57008028030396</t>
   </si>
   <si>
     <t xml:space="preserve">4.53970003128052</t>
@@ -845,22 +845,22 @@
     <t xml:space="preserve">4.42251873016357</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43119859695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45289850234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51365947723389</t>
+    <t xml:space="preserve">4.43119812011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45289897918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51365900039673</t>
   </si>
   <si>
     <t xml:space="preserve">4.6872615814209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60046148300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63952159881592</t>
+    <t xml:space="preserve">4.60046052932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63952112197876</t>
   </si>
   <si>
     <t xml:space="preserve">4.56139993667603</t>
@@ -872,28 +872,28 @@
     <t xml:space="preserve">4.61782121658325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64820194244385</t>
+    <t xml:space="preserve">4.64820098876953</t>
   </si>
   <si>
     <t xml:space="preserve">4.60480070114136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58310079574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49629926681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50497961044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42685842514038</t>
+    <t xml:space="preserve">4.58310031890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49629974365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50498008728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42685890197754</t>
   </si>
   <si>
     <t xml:space="preserve">4.49195909500122</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51799964904785</t>
+    <t xml:space="preserve">4.51800012588501</t>
   </si>
   <si>
     <t xml:space="preserve">4.80878353118896</t>
@@ -908,370 +908,370 @@
     <t xml:space="preserve">4.8348240852356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74368238449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81312417984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71330165863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70462274551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72632169723511</t>
+    <t xml:space="preserve">4.74368286132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81312370300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71330213546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7046217918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72632217407227</t>
   </si>
   <si>
     <t xml:space="preserve">4.69594192504883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7697229385376</t>
+    <t xml:space="preserve">4.76972246170044</t>
   </si>
   <si>
     <t xml:space="preserve">4.84350395202637</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87822389602661</t>
+    <t xml:space="preserve">4.87822437286377</t>
   </si>
   <si>
     <t xml:space="preserve">4.8738842010498</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97370624542236</t>
+    <t xml:space="preserve">4.97370576858521</t>
   </si>
   <si>
     <t xml:space="preserve">4.97804594039917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00842571258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07786655426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04314708709717</t>
+    <t xml:space="preserve">5.00842666625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07786703109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04314661026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14730787277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86086416244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86954545974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96502494812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90860557556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99974632263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99106597900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15598773956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12994718551636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29486989974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41639137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48583221435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43375205993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48149251937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42073202133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39469146728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35563087463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33393096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37299108505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33827018737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20806932449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16466808319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26449012756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25146961212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26014947891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18636894226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20372915267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19504880905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16900825500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18202877044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19938850402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22542953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42507123947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61603450775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72887563705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71151542663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78963613510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82435655593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87643766403198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88511800765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93719816207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85907745361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80699682235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92851829528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97191905975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95455837249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03268003463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17156171798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28440284729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01531934738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02399921417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21496200561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14552116394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40592527389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07608032226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98927927017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04135942459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22364187240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13684129714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19760179519653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15420150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05004072189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89379787445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90247774124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70283555984497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50319290161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58131408691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72019529342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76359558105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91983795166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99795913696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83303689956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79831647872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65943431854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51187229156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54659366607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58999395370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52055311203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38167142868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44243192672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46847200393677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6767954826355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64207458496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55527353286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53791332244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57263374328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52923250198364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39903116226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39035081863403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45111179351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09344053268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81567716598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77227640151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73755693435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40771102905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24279022216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06918716430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98238563537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07618808746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15619802474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08507823944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24509716033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11174821853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13841772079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20953798294067</t>
   </si>
   <si>
     <t xml:space="preserve">5.14730739593506</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86086416244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86954498291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96502542495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90860557556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99974632263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99106645584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15598821640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12994813919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29486894607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41639089584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48583269119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43375205993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4814920425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42073202133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39469194412231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35563039779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33393049240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37299156188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33827114105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20806932449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16466856002808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26448965072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25146913528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26014947891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18636894226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20372867584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19504880905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16900777816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18202829360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19938898086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22542810440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42507171630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61603403091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7288761138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7115159034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78963613510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82435703277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87643766403198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88511800765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93719863891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85907697677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80699682235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92851829528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97191905975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95455884933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03267955780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17156171798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28440284729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01531934738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02400016784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21496248245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14552116394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40592479705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07608032226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98927927017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04135990142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22364187240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13684129714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19760179519653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1542010307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05003976821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89379787445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90247774124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70283555984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50319290161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5813136100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72019577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76359605789185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91983842849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99795961380005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83303642272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79831600189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6594352722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5118727684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54659366607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58999347686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52055263519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38167095184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44243240356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46847248077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6767954826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64207458496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55527353286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53791332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57263326644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5292329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39903116226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39035177230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45111227035522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09344053268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81567668914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77227640151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73755598068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40771198272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24278926849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06918716430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98238515853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07618761062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15619802474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08507776260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24509811401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11174821853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13841772079468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20953750610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14730787277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06729745864868</t>
+    <t xml:space="preserve">5.06729793548584</t>
   </si>
   <si>
     <t xml:space="preserve">5.0584077835083</t>
@@ -1280,13 +1280,13 @@
     <t xml:space="preserve">5.04062843322754</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04951763153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94283819198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77392768859863</t>
+    <t xml:space="preserve">5.04951810836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94283771514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77392816543579</t>
   </si>
   <si>
     <t xml:space="preserve">4.90727806091309</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">4.97839784622192</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91616821289062</t>
+    <t xml:space="preserve">4.91616868972778</t>
   </si>
   <si>
     <t xml:space="preserve">4.95172834396362</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">4.80948781967163</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78281784057617</t>
+    <t xml:space="preserve">4.78281831741333</t>
   </si>
   <si>
     <t xml:space="preserve">4.75614786148071</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98728847503662</t>
+    <t xml:space="preserve">4.98728799819946</t>
   </si>
   <si>
     <t xml:space="preserve">5.10285711288452</t>
@@ -1340,40 +1340,40 @@
     <t xml:space="preserve">5.20064735412598</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21842813491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27176713943481</t>
+    <t xml:space="preserve">5.21842765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27176761627197</t>
   </si>
   <si>
     <t xml:space="preserve">5.33399820327759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23620748519897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18286800384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01395845413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99617719650269</t>
+    <t xml:space="preserve">5.23620796203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18286752700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01395797729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.996178150177</t>
   </si>
   <si>
     <t xml:space="preserve">5.00506782531738</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37844753265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47623682022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56513786315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68070793151855</t>
+    <t xml:space="preserve">5.37844800949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47623825073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56513833999634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6807074546814</t>
   </si>
   <si>
     <t xml:space="preserve">5.65403747558594</t>
@@ -1382,7 +1382,7 @@
     <t xml:space="preserve">5.63625764846802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55624771118164</t>
+    <t xml:space="preserve">5.5562481880188</t>
   </si>
   <si>
     <t xml:space="preserve">5.68959760665894</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">5.96518754959106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89406776428223</t>
+    <t xml:space="preserve">5.89406728744507</t>
   </si>
   <si>
     <t xml:space="preserve">5.77849769592285</t>
@@ -1403,28 +1403,28 @@
     <t xml:space="preserve">5.76071739196777</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92073774337769</t>
+    <t xml:space="preserve">5.92073726654053</t>
   </si>
   <si>
     <t xml:space="preserve">5.83183717727661</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44956731796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58291816711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43178796768188</t>
+    <t xml:space="preserve">5.4495677947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5829176902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43178844451904</t>
   </si>
   <si>
     <t xml:space="preserve">5.36955785751343</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60958862304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86739778518677</t>
+    <t xml:space="preserve">5.60958766937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86739730834961</t>
   </si>
   <si>
     <t xml:space="preserve">5.78738784790039</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">5.5206880569458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49401760101318</t>
+    <t xml:space="preserve">5.49401807785034</t>
   </si>
   <si>
     <t xml:space="preserve">5.57402801513672</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">5.71626758575439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73404741287231</t>
+    <t xml:space="preserve">5.73404788970947</t>
   </si>
   <si>
     <t xml:space="preserve">5.81405830383301</t>
@@ -1457,52 +1457,52 @@
     <t xml:space="preserve">5.67181777954102</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5117974281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85850763320923</t>
+    <t xml:space="preserve">5.51179790496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85850811004639</t>
   </si>
   <si>
     <t xml:space="preserve">5.66292762756348</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53846836090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90295743942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79627799987793</t>
+    <t xml:space="preserve">5.53846788406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90295791625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79627752304077</t>
   </si>
   <si>
     <t xml:space="preserve">5.80516767501831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6184778213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46734857559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60069799423218</t>
+    <t xml:space="preserve">5.61847734451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46734762191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60069847106934</t>
   </si>
   <si>
     <t xml:space="preserve">5.45845746994019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50290822982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34288740158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62736749649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52957773208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42289686203003</t>
+    <t xml:space="preserve">5.50290775299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34288787841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62736701965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52957725524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42289781570435</t>
   </si>
   <si>
     <t xml:space="preserve">5.72515726089478</t>
@@ -1511,10 +1511,10 @@
     <t xml:space="preserve">5.70737743377686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69848680496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0007472038269</t>
+    <t xml:space="preserve">5.69848728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00074768066406</t>
   </si>
   <si>
     <t xml:space="preserve">5.92962741851807</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">5.94740772247314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93851709365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99185705184937</t>
+    <t xml:space="preserve">5.93851757049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99185752868652</t>
   </si>
   <si>
     <t xml:space="preserve">6.24077749252319</t>
@@ -1535,22 +1535,22 @@
     <t xml:space="preserve">6.40968704223633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48080730438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62304735183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84529733657837</t>
+    <t xml:space="preserve">6.48080778121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.623046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84529781341553</t>
   </si>
   <si>
     <t xml:space="preserve">6.99642705917358</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01420783996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90752744674683</t>
+    <t xml:space="preserve">7.0142068862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90752696990967</t>
   </si>
   <si>
     <t xml:space="preserve">6.91641759872437</t>
@@ -1562,37 +1562,37 @@
     <t xml:space="preserve">7.00531721115112</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0230975151062</t>
+    <t xml:space="preserve">7.02309799194336</t>
   </si>
   <si>
     <t xml:space="preserve">7.2453465461731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27201747894287</t>
+    <t xml:space="preserve">7.27201652526855</t>
   </si>
   <si>
     <t xml:space="preserve">7.33424663543701</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47648668289185</t>
+    <t xml:space="preserve">7.47648763656616</t>
   </si>
   <si>
     <t xml:space="preserve">7.76985692977905</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73429679870605</t>
+    <t xml:space="preserve">7.7342963218689</t>
   </si>
   <si>
     <t xml:space="preserve">7.72540664672852</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79652738571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80541563034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22324752807617</t>
+    <t xml:space="preserve">7.79652643203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80541706085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22324657440186</t>
   </si>
   <si>
     <t xml:space="preserve">8.21435642242432</t>
@@ -1604,19 +1604,19 @@
     <t xml:space="preserve">8.12545776367188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00099563598633</t>
+    <t xml:space="preserve">8.00099754333496</t>
   </si>
   <si>
     <t xml:space="preserve">8.17879676818848</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34770774841309</t>
+    <t xml:space="preserve">8.34770679473877</t>
   </si>
   <si>
     <t xml:space="preserve">8.42771530151367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48105621337891</t>
+    <t xml:space="preserve">8.48105525970459</t>
   </si>
   <si>
     <t xml:space="preserve">8.46327686309814</t>
@@ -1625,10 +1625,10 @@
     <t xml:space="preserve">8.52550601959229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50772762298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66774654388428</t>
+    <t xml:space="preserve">8.50772666931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66774559020996</t>
   </si>
   <si>
     <t xml:space="preserve">8.80109596252441</t>
@@ -1640,16 +1640,16 @@
     <t xml:space="preserve">9.19225597381592</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37005710601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4767370223999</t>
+    <t xml:space="preserve">9.37005615234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47673511505127</t>
   </si>
   <si>
     <t xml:space="preserve">9.49451637268066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31671619415283</t>
+    <t xml:space="preserve">9.31671524047852</t>
   </si>
   <si>
     <t xml:space="preserve">9.15669631958008</t>
@@ -1661,13 +1661,13 @@
     <t xml:space="preserve">9.40561580657959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69009590148926</t>
+    <t xml:space="preserve">9.69009494781494</t>
   </si>
   <si>
     <t xml:space="preserve">9.86789608001709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83233642578125</t>
+    <t xml:space="preserve">9.83233737945557</t>
   </si>
   <si>
     <t xml:space="preserve">9.77899646759033</t>
@@ -1676,10 +1676,10 @@
     <t xml:space="preserve">9.44117546081543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.210036277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58341503143311</t>
+    <t xml:space="preserve">9.21003723144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58341598510742</t>
   </si>
   <si>
     <t xml:space="preserve">9.51229572296143</t>
@@ -1691,28 +1691,28 @@
     <t xml:space="preserve">9.85011577606201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0990352630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0279169082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99235439300537</t>
+    <t xml:space="preserve">10.0990362167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0279159545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.992356300354</t>
   </si>
   <si>
     <t xml:space="preserve">10.0101356506348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76121616363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88567638397217</t>
+    <t xml:space="preserve">9.76121520996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88567543029785</t>
   </si>
   <si>
     <t xml:space="preserve">10.2234964370728</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4368562698364</t>
+    <t xml:space="preserve">10.4368553161621</t>
   </si>
   <si>
     <t xml:space="preserve">10.6679964065552</t>
@@ -1721,7 +1721,7 @@
     <t xml:space="preserve">11.4147548675537</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3614158630371</t>
+    <t xml:space="preserve">11.3614149093628</t>
   </si>
   <si>
     <t xml:space="preserve">11.3080749511719</t>
@@ -1736,16 +1736,16 @@
     <t xml:space="preserve">11.8948154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">11.965934753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1437349319458</t>
+    <t xml:space="preserve">11.9659357070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1437358856201</t>
   </si>
   <si>
     <t xml:space="preserve">11.628116607666</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4001140594482</t>
+    <t xml:space="preserve">11.4001131057739</t>
   </si>
   <si>
     <t xml:space="preserve">11.6715440750122</t>
@@ -1754,10 +1754,10 @@
     <t xml:space="preserve">11.6534481048584</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6896409988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1239290237427</t>
+    <t xml:space="preserve">11.689640045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.123929977417</t>
   </si>
   <si>
     <t xml:space="preserve">11.7982130050659</t>
@@ -1769,13 +1769,13 @@
     <t xml:space="preserve">12.3229789733887</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9925098419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8296508789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7391738891602</t>
+    <t xml:space="preserve">12.9925079345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8296518325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7391729354858</t>
   </si>
   <si>
     <t xml:space="preserve">12.7753639221191</t>
@@ -1784,22 +1784,22 @@
     <t xml:space="preserve">12.3953619003296</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2867879867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6306018829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4496479034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2144060134888</t>
+    <t xml:space="preserve">12.2867889404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6306009292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4496469497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2144069671631</t>
   </si>
   <si>
     <t xml:space="preserve">12.1058349609375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8705930709839</t>
+    <t xml:space="preserve">11.8705940246582</t>
   </si>
   <si>
     <t xml:space="preserve">11.9067850112915</t>
@@ -1808,22 +1808,22 @@
     <t xml:space="preserve">11.4724950790405</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4182100296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5810670852661</t>
+    <t xml:space="preserve">11.4182081222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5810680389404</t>
   </si>
   <si>
     <t xml:space="preserve">11.8524990081787</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0877380371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8344039916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.888689994812</t>
+    <t xml:space="preserve">12.0877389907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8344030380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8886890411377</t>
   </si>
   <si>
     <t xml:space="preserve">11.4363040924072</t>
@@ -1832,7 +1832,7 @@
     <t xml:space="preserve">11.3277320861816</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734460830688</t>
+    <t xml:space="preserve">11.2734451293945</t>
   </si>
   <si>
     <t xml:space="preserve">11.1829681396484</t>
@@ -1841,13 +1841,13 @@
     <t xml:space="preserve">11.1648721694946</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8391551971436</t>
+    <t xml:space="preserve">10.8391542434692</t>
   </si>
   <si>
     <t xml:space="preserve">10.6401062011719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6762971878052</t>
+    <t xml:space="preserve">10.6762962341309</t>
   </si>
   <si>
     <t xml:space="preserve">10.5134382247925</t>
@@ -1856,10 +1856,10 @@
     <t xml:space="preserve">10.9115371704102</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2915391921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1467752456665</t>
+    <t xml:space="preserve">11.291540145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1467771530151</t>
   </si>
   <si>
     <t xml:space="preserve">10.766773223877</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">11.1105861663818</t>
   </si>
   <si>
-    <t xml:space="preserve">11.12868309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6220102310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0020132064819</t>
+    <t xml:space="preserve">11.1286821365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6220092773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0020141601562</t>
   </si>
   <si>
     <t xml:space="preserve">10.6039142608643</t>
@@ -1895,19 +1895,19 @@
     <t xml:space="preserve">9.9343843460083</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80771732330322</t>
+    <t xml:space="preserve">9.80771636962891</t>
   </si>
   <si>
     <t xml:space="preserve">9.68104839324951</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95248031616211</t>
+    <t xml:space="preserve">9.95247936248779</t>
   </si>
   <si>
     <t xml:space="preserve">10.2420063018799</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4772462844849</t>
+    <t xml:space="preserve">10.4772472381592</t>
   </si>
   <si>
     <t xml:space="preserve">10.3867683410645</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">10.4410552978516</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55438041687012</t>
+    <t xml:space="preserve">9.55438137054443</t>
   </si>
   <si>
     <t xml:space="preserve">10.1153392791748</t>
@@ -1931,19 +1931,19 @@
     <t xml:space="preserve">10.7486782073975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0201091766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8572511672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8753452301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5858182907104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8029642105103</t>
+    <t xml:space="preserve">11.0201101303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.857250213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8753461837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5858192443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8029632568359</t>
   </si>
   <si>
     <t xml:space="preserve">10.7124872207642</t>
@@ -1952,43 +1952,43 @@
     <t xml:space="preserve">10.7848691940308</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2372550964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3096361160278</t>
+    <t xml:space="preserve">11.2372541427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3096370697021</t>
   </si>
   <si>
     <t xml:space="preserve">11.4543991088867</t>
   </si>
   <si>
-    <t xml:space="preserve">11.725830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9972620010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1601190567017</t>
+    <t xml:space="preserve">11.7258310317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9972610473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1601209640503</t>
   </si>
   <si>
     <t xml:space="preserve">12.0515480041504</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0334529876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9429759979248</t>
+    <t xml:space="preserve">12.0334520339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9429750442505</t>
   </si>
   <si>
     <t xml:space="preserve">11.7620210647583</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9477272033691</t>
+    <t xml:space="preserve">10.9477281570435</t>
   </si>
   <si>
     <t xml:space="preserve">10.9658231735229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1877202987671</t>
+    <t xml:space="preserve">10.1877212524414</t>
   </si>
   <si>
     <t xml:space="preserve">9.98867034912109</t>
@@ -1997,10 +1997,10 @@
     <t xml:space="preserve">10.0429573059082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91628837585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.169623374939</t>
+    <t xml:space="preserve">9.91628932952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1696243286133</t>
   </si>
   <si>
     <t xml:space="preserve">10.531533241272</t>
@@ -2012,34 +2012,34 @@
     <t xml:space="preserve">10.13343334198</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3324823379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2239112854004</t>
+    <t xml:space="preserve">10.3324842453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2239122390747</t>
   </si>
   <si>
     <t xml:space="preserve">10.097243309021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0610523223877</t>
+    <t xml:space="preserve">10.0610513687134</t>
   </si>
   <si>
     <t xml:space="preserve">10.0791482925415</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1515302658081</t>
+    <t xml:space="preserve">10.1515312194824</t>
   </si>
   <si>
     <t xml:space="preserve">11.056300163269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.893440246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5496282577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3686752319336</t>
+    <t xml:space="preserve">10.8934412002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5496273040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3686742782593</t>
   </si>
   <si>
     <t xml:space="preserve">9.82581043243408</t>
@@ -2048,16 +2048,16 @@
     <t xml:space="preserve">9.77152442932129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.699143409729</t>
+    <t xml:space="preserve">9.69914436340332</t>
   </si>
   <si>
     <t xml:space="preserve">9.51819038391113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7172384262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42771244049072</t>
+    <t xml:space="preserve">9.71723747253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42771339416504</t>
   </si>
   <si>
     <t xml:space="preserve">9.59057235717773</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">11.3639230728149</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9791669845581</t>
+    <t xml:space="preserve">11.9791660308838</t>
   </si>
   <si>
     <t xml:space="preserve">12.4677419662476</t>
@@ -2075,13 +2075,13 @@
     <t xml:space="preserve">12.3772659301758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3820180892944</t>
+    <t xml:space="preserve">11.3820171356201</t>
   </si>
   <si>
     <t xml:space="preserve">11.5629720687866</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6172580718994</t>
+    <t xml:space="preserve">11.6172590255737</t>
   </si>
   <si>
     <t xml:space="preserve">11.092490196228</t>
@@ -2093,16 +2093,16 @@
     <t xml:space="preserve">9.62676239013672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80342102050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68580150604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43246459960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04816484451294</t>
+    <t xml:space="preserve">8.8034200668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68579959869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43246364593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0481653213501</t>
   </si>
   <si>
     <t xml:space="preserve">7.32864427566528</t>
@@ -2111,13 +2111,13 @@
     <t xml:space="preserve">7.24721527099609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18388080596924</t>
+    <t xml:space="preserve">7.18388032913208</t>
   </si>
   <si>
     <t xml:space="preserve">6.58673238754272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65006542205811</t>
+    <t xml:space="preserve">6.65006589889526</t>
   </si>
   <si>
     <t xml:space="preserve">6.96673583984375</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">7.16578578948975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.057213306427</t>
+    <t xml:space="preserve">7.05721282958984</t>
   </si>
   <si>
     <t xml:space="preserve">7.28340578079224</t>
@@ -2147,13 +2147,13 @@
     <t xml:space="preserve">8.04341316223145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61341953277588</t>
+    <t xml:space="preserve">8.61341857910156</t>
   </si>
   <si>
     <t xml:space="preserve">8.41436958312988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25151062011719</t>
+    <t xml:space="preserve">8.25150966644287</t>
   </si>
   <si>
     <t xml:space="preserve">8.93008899688721</t>
@@ -2165,10 +2165,10 @@
     <t xml:space="preserve">9.04770946502686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26485347747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50009441375732</t>
+    <t xml:space="preserve">9.26485443115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50009346008301</t>
   </si>
   <si>
     <t xml:space="preserve">9.8620023727417</t>
@@ -2177,61 +2177,61 @@
     <t xml:space="preserve">11.2191581726074</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9839191436768</t>
+    <t xml:space="preserve">10.9839181900024</t>
   </si>
   <si>
     <t xml:space="preserve">10.6582002639771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9705753326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2058162689209</t>
+    <t xml:space="preserve">9.97057628631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2058153152466</t>
   </si>
   <si>
     <t xml:space="preserve">9.84390640258789</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4591512680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9296321868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7305812835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8210601806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0696430206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5582208633423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8477468490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1915588378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7572689056396</t>
+    <t xml:space="preserve">10.4591522216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9296312332153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7305822372437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8210592269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0696439743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.558219909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8477458953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1915597915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.757269859314</t>
   </si>
   <si>
     <t xml:space="preserve">12.7934608459473</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4315509796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5944108963013</t>
+    <t xml:space="preserve">12.4315519332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.594409942627</t>
   </si>
   <si>
     <t xml:space="preserve">12.6486968994141</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7210779190063</t>
+    <t xml:space="preserve">12.7210788726807</t>
   </si>
   <si>
     <t xml:space="preserve">12.8658418655396</t>
@@ -2246,43 +2246,43 @@
     <t xml:space="preserve">13.1191787719727</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9382238388062</t>
+    <t xml:space="preserve">12.9382247924805</t>
   </si>
   <si>
     <t xml:space="preserve">13.082986831665</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3725137710571</t>
+    <t xml:space="preserve">13.3725128173828</t>
   </si>
   <si>
     <t xml:space="preserve">13.3544178009033</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4534864425659</t>
+    <t xml:space="preserve">15.4534893035889</t>
   </si>
   <si>
     <t xml:space="preserve">16.249683380127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2858734130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3763523101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6477851867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8334903717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0687294006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8696823120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9239664077759</t>
+    <t xml:space="preserve">16.2858753204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3763542175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6477832794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8334894180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.068733215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8696804046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9239673614502</t>
   </si>
   <si>
     <t xml:space="preserve">15.9058713912964</t>
@@ -2291,58 +2291,58 @@
     <t xml:space="preserve">15.8515872955322</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0144443511963</t>
+    <t xml:space="preserve">16.0144462585449</t>
   </si>
   <si>
     <t xml:space="preserve">15.7973003387451</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2677783966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0325374603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7792053222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7249174118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4125442504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8153953552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9420614242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6344423294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1049213409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9601564407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6887273788452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6163454055786</t>
+    <t xml:space="preserve">16.2677803039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0325393676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7792043685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7249164581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4125423431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8153944015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9420623779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6344404220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.104923248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9601583480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6887264251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6163444519043</t>
   </si>
   <si>
     <t xml:space="preserve">14.8925285339355</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6525354385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3630084991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4896774291992</t>
+    <t xml:space="preserve">15.6525363922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3630075454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4896793365479</t>
   </si>
   <si>
     <t xml:space="preserve">15.14586353302</t>
@@ -2351,13 +2351,13 @@
     <t xml:space="preserve">15.0372915267944</t>
   </si>
   <si>
-    <t xml:space="preserve">15.743013381958</t>
+    <t xml:space="preserve">15.7430124282837</t>
   </si>
   <si>
     <t xml:space="preserve">14.8201465606689</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2906284332275</t>
+    <t xml:space="preserve">15.2906274795532</t>
   </si>
   <si>
     <t xml:space="preserve">17.5887451171875</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">19.1359043121338</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2763710021973</t>
+    <t xml:space="preserve">18.2763729095459</t>
   </si>
   <si>
     <t xml:space="preserve">18.0411319732666</t>
@@ -2387,46 +2387,46 @@
     <t xml:space="preserve">17.2992191314697</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0458831787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0277881622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7020702362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0096912384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4077892303467</t>
+    <t xml:space="preserve">17.0458850860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0277862548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7020683288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0096893310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4077930450439</t>
   </si>
   <si>
     <t xml:space="preserve">18.5025653839111</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1406536102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.96875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4982681274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9868450164795</t>
+    <t xml:space="preserve">18.1406555175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9687519073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.49827003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9868431091309</t>
   </si>
   <si>
     <t xml:space="preserve">18.5930404663086</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1544532775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.244930267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1182632446289</t>
+    <t xml:space="preserve">17.1544551849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2449321746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1182670593262</t>
   </si>
   <si>
     <t xml:space="preserve">16.8106422424316</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">16.8287391662598</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9735050201416</t>
+    <t xml:space="preserve">16.973503112793</t>
   </si>
   <si>
     <t xml:space="preserve">16.9192161560059</t>
@@ -2444,22 +2444,22 @@
     <t xml:space="preserve">17.0639781951904</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8468341827393</t>
+    <t xml:space="preserve">16.8468360900879</t>
   </si>
   <si>
     <t xml:space="preserve">16.9011192321777</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3173160552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2087421417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2268390655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3668460845947</t>
+    <t xml:space="preserve">17.3173141479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2087440490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2268371582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3668479919434</t>
   </si>
   <si>
     <t xml:space="preserve">18.4573249816895</t>
@@ -2468,16 +2468,16 @@
     <t xml:space="preserve">18.6382808685303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7287578582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9549522399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8644733428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6335296630859</t>
+    <t xml:space="preserve">18.7287559509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9549503326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8644752502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6335315704346</t>
   </si>
   <si>
     <t xml:space="preserve">19.6787662506104</t>
@@ -2486,25 +2486,25 @@
     <t xml:space="preserve">19.5430488586426</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0454254150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0001888275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3168601989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3216114044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2311325073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0906677246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6835174560547</t>
+    <t xml:space="preserve">19.0454235076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.000186920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.316858291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3216094970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2311305999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0906658172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6835155487061</t>
   </si>
   <si>
     <t xml:space="preserve">18.0954189300537</t>
@@ -2522,7 +2522,7 @@
     <t xml:space="preserve">17.6430320739746</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8058910369873</t>
+    <t xml:space="preserve">17.8058891296387</t>
   </si>
   <si>
     <t xml:space="preserve">19.2716197967529</t>
@@ -2540,13 +2540,13 @@
     <t xml:space="preserve">20.9906845092773</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5835361480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3573455810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9049606323242</t>
+    <t xml:space="preserve">20.5835380554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3573436737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9049587249756</t>
   </si>
   <si>
     <t xml:space="preserve">19.7692432403564</t>
@@ -2555,13 +2555,13 @@
     <t xml:space="preserve">20.7192516326904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.995433807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2263832092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4525718688965</t>
+    <t xml:space="preserve">19.9954357147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2263813018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4525737762451</t>
   </si>
   <si>
     <t xml:space="preserve">19.4073352813721</t>
@@ -2573,7 +2573,7 @@
     <t xml:space="preserve">17.7877941131592</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4978103637695</t>
+    <t xml:space="preserve">19.4978122711182</t>
   </si>
   <si>
     <t xml:space="preserve">20.0859146118164</t>
@@ -2597,10 +2597,10 @@
     <t xml:space="preserve">20.6287746429443</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3121070861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4478225708008</t>
+    <t xml:space="preserve">20.312105178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4478244781494</t>
   </si>
   <si>
     <t xml:space="preserve">20.8821105957031</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">22.1668872833252</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6192722320557</t>
+    <t xml:space="preserve">22.6192741394043</t>
   </si>
   <si>
     <t xml:space="preserve">22.8726081848145</t>
@@ -2633,16 +2633,16 @@
     <t xml:space="preserve">22.7821311950684</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8592643737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0040264129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2573661804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4745101928711</t>
+    <t xml:space="preserve">21.8592624664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0040283203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2573642730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4745082855225</t>
   </si>
   <si>
     <t xml:space="preserve">22.1126003265381</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">22.6011772155762</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6373672485352</t>
+    <t xml:space="preserve">22.6373653411865</t>
   </si>
   <si>
     <t xml:space="preserve">22.420223236084</t>
@@ -2663,25 +2663,25 @@
     <t xml:space="preserve">22.4021282196045</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3525943756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2621154785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.09450340271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5830783843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0354671478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.017370223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3611831665039</t>
+    <t xml:space="preserve">21.3525924682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2621173858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0945053100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.583080291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0354652404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0173721313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3611850738525</t>
   </si>
   <si>
     <t xml:space="preserve">23.2707061767578</t>
@@ -2690,16 +2690,16 @@
     <t xml:space="preserve">25.044059753418</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7726268768311</t>
+    <t xml:space="preserve">24.7726249694824</t>
   </si>
   <si>
     <t xml:space="preserve">24.9716758728027</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0621547698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9126396179199</t>
+    <t xml:space="preserve">25.0621528625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9126377105713</t>
   </si>
   <si>
     <t xml:space="preserve">26.2383575439453</t>
@@ -2717,13 +2717,13 @@
     <t xml:space="preserve">26.6583156585693</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8226451873779</t>
+    <t xml:space="preserve">26.8226470947266</t>
   </si>
   <si>
     <t xml:space="preserve">26.95046043396</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5712718963623</t>
+    <t xml:space="preserve">27.5712699890137</t>
   </si>
   <si>
     <t xml:space="preserve">27.6260471343994</t>
@@ -2738,10 +2738,10 @@
     <t xml:space="preserve">29.8171424865723</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5980319976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9589614868164</t>
+    <t xml:space="preserve">29.5980339050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.958963394165</t>
   </si>
   <si>
     <t xml:space="preserve">30.1275444030762</t>
@@ -2768,13 +2768,13 @@
     <t xml:space="preserve">30.8213901519775</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1683158874512</t>
+    <t xml:space="preserve">31.1683197021484</t>
   </si>
   <si>
     <t xml:space="preserve">30.2371006011963</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4154434204102</t>
+    <t xml:space="preserve">29.4154415130615</t>
   </si>
   <si>
     <t xml:space="preserve">29.8536605834961</t>
@@ -2783,13 +2783,13 @@
     <t xml:space="preserve">29.178071975708</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1458072662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7075881958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0545101165771</t>
+    <t xml:space="preserve">30.1458053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7075901031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0545120239258</t>
   </si>
   <si>
     <t xml:space="preserve">32.8664131164551</t>
@@ -2798,7 +2798,7 @@
     <t xml:space="preserve">34.546257019043</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0532608032227</t>
+    <t xml:space="preserve">34.0532569885254</t>
   </si>
   <si>
     <t xml:space="preserve">33.0855255126953</t>
@@ -2816,13 +2816,13 @@
     <t xml:space="preserve">33.4872245788574</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7976341247559</t>
+    <t xml:space="preserve">33.7976303100586</t>
   </si>
   <si>
     <t xml:space="preserve">33.1403007507324</t>
   </si>
   <si>
-    <t xml:space="preserve">33.286376953125</t>
+    <t xml:space="preserve">33.2863731384277</t>
   </si>
   <si>
     <t xml:space="preserve">32.2273445129395</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">32.8846740722656</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7568626403809</t>
+    <t xml:space="preserve">32.7568664550781</t>
   </si>
   <si>
     <t xml:space="preserve">32.6473045349121</t>
@@ -2843,25 +2843,25 @@
     <t xml:space="preserve">32.7751197814941</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4099388122559</t>
+    <t xml:space="preserve">32.4099349975586</t>
   </si>
   <si>
     <t xml:space="preserve">32.6655654907227</t>
   </si>
   <si>
-    <t xml:space="preserve">34.692325592041</t>
+    <t xml:space="preserve">34.6923294067383</t>
   </si>
   <si>
     <t xml:space="preserve">35.605281829834</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2400970458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8791732788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.477466583252</t>
+    <t xml:space="preserve">35.2401008605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8791694641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4774703979492</t>
   </si>
   <si>
     <t xml:space="preserve">35.0940284729004</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">35.5870246887207</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7878761291504</t>
+    <t xml:space="preserve">35.7878799438477</t>
   </si>
   <si>
     <t xml:space="preserve">36.0435028076172</t>
@@ -2879,10 +2879,10 @@
     <t xml:space="preserve">36.8469047546387</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9101829528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4354476928711</t>
+    <t xml:space="preserve">38.9101791381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4354438781738</t>
   </si>
   <si>
     <t xml:space="preserve">39.4944725036621</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">39.3849220275879</t>
   </si>
   <si>
-    <t xml:space="preserve">39.220588684082</t>
+    <t xml:space="preserve">39.2205848693848</t>
   </si>
   <si>
     <t xml:space="preserve">39.1292953491211</t>
@@ -2903,7 +2903,7 @@
     <t xml:space="preserve">37.6137886047363</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2486000061035</t>
+    <t xml:space="preserve">37.2486038208008</t>
   </si>
   <si>
     <t xml:space="preserve">37.0660095214844</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">37.2668609619141</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7008285522461</t>
+    <t xml:space="preserve">36.7008323669434</t>
   </si>
   <si>
     <t xml:space="preserve">37.212085723877</t>
@@ -2924,10 +2924,10 @@
     <t xml:space="preserve">38.0154876708984</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6503067016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6235466003418</t>
+    <t xml:space="preserve">37.6503028869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6235389709473</t>
   </si>
   <si>
     <t xml:space="preserve">33.2315979003906</t>
@@ -2936,37 +2936,37 @@
     <t xml:space="preserve">32.9942245483398</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3594093322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0490036010742</t>
+    <t xml:space="preserve">33.3594169616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0490074157715</t>
   </si>
   <si>
     <t xml:space="preserve">34.7836227416992</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3819198608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.893180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9577140808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6332969665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5139923095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4817199707031</t>
+    <t xml:space="preserve">34.3819236755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8931770324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9577102661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.63330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.513988494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4817161560059</t>
   </si>
   <si>
     <t xml:space="preserve">36.3173866271973</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6095352172852</t>
+    <t xml:space="preserve">36.6095314025879</t>
   </si>
   <si>
     <t xml:space="preserve">37.7781181335449</t>
@@ -2975,10 +2975,10 @@
     <t xml:space="preserve">38.2711143493652</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2023315429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7190933227539</t>
+    <t xml:space="preserve">39.2023277282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7190895080566</t>
   </si>
   <si>
     <t xml:space="preserve">35.8426513671875</t>
@@ -2987,22 +2987,22 @@
     <t xml:space="preserve">34.9662132263184</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1488075256348</t>
+    <t xml:space="preserve">35.1488037109375</t>
   </si>
   <si>
     <t xml:space="preserve">35.4409484863281</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8876724243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5267448425293</t>
+    <t xml:space="preserve">37.8876686096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5267486572266</t>
   </si>
   <si>
     <t xml:space="preserve">38.8006248474121</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6685600280762</t>
+    <t xml:space="preserve">37.6685638427734</t>
   </si>
   <si>
     <t xml:space="preserve">35.4226913452148</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">34.3636627197266</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8341484069824</t>
+    <t xml:space="preserve">33.8341522216797</t>
   </si>
   <si>
     <t xml:space="preserve">33.5967788696289</t>
@@ -3047,10 +3047,10 @@
     <t xml:space="preserve">33.1950798034668</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6150398254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9254417419434</t>
+    <t xml:space="preserve">33.6150436401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9254455566406</t>
   </si>
   <si>
     <t xml:space="preserve">33.9437026977539</t>
@@ -3062,16 +3062,16 @@
     <t xml:space="preserve">34.5827713012695</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7288513183594</t>
+    <t xml:space="preserve">34.7288475036621</t>
   </si>
   <si>
     <t xml:space="preserve">35.0027313232422</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8384017944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8749160766602</t>
+    <t xml:space="preserve">34.8383979797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8749198913574</t>
   </si>
   <si>
     <t xml:space="preserve">32.5377502441406</t>
@@ -3089,19 +3089,19 @@
     <t xml:space="preserve">29.8901805877686</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1640663146973</t>
+    <t xml:space="preserve">30.1640644073486</t>
   </si>
   <si>
     <t xml:space="preserve">28.4294471740723</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1007843017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6808242797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9954833984375</t>
+    <t xml:space="preserve">28.1007862091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6808261871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9954814910889</t>
   </si>
   <si>
     <t xml:space="preserve">29.2693691253662</t>
@@ -3125,34 +3125,34 @@
     <t xml:space="preserve">28.6668186187744</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1232948303223</t>
+    <t xml:space="preserve">29.1232967376709</t>
   </si>
   <si>
     <t xml:space="preserve">28.9224472045898</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6077861785889</t>
+    <t xml:space="preserve">27.6077880859375</t>
   </si>
   <si>
     <t xml:space="preserve">27.7538623809814</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3479099273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5445079803467</t>
+    <t xml:space="preserve">26.3479118347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.544506072998</t>
   </si>
   <si>
     <t xml:space="preserve">26.7496089935303</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7861309051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5670185089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9547119140625</t>
+    <t xml:space="preserve">26.7861289978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5670204162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9547138214111</t>
   </si>
   <si>
     <t xml:space="preserve">27.4251976013184</t>
@@ -3161,10 +3161,10 @@
     <t xml:space="preserve">27.4799766540527</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1147937774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7313499450684</t>
+    <t xml:space="preserve">27.1147918701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.731351852417</t>
   </si>
   <si>
     <t xml:space="preserve">27.4069385528564</t>
@@ -3185,13 +3185,13 @@
     <t xml:space="preserve">23.5542640686035</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7045879364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0977840423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0022411346436</t>
+    <t xml:space="preserve">24.70458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.097785949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0022392272949</t>
   </si>
   <si>
     <t xml:space="preserve">21.7466106414795</t>
@@ -3215,16 +3215,16 @@
     <t xml:space="preserve">23.2073402404785</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5402545928955</t>
+    <t xml:space="preserve">24.5402565002441</t>
   </si>
   <si>
     <t xml:space="preserve">24.6680717468262</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8689212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4489631652832</t>
+    <t xml:space="preserve">24.8689193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4489612579346</t>
   </si>
   <si>
     <t xml:space="preserve">25.2341022491455</t>
@@ -3233,13 +3233,13 @@
     <t xml:space="preserve">24.5585155487061</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0290031433105</t>
+    <t xml:space="preserve">24.0289993286133</t>
   </si>
   <si>
     <t xml:space="preserve">24.138557434082</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0472602844238</t>
+    <t xml:space="preserve">24.0472621917725</t>
   </si>
   <si>
     <t xml:space="preserve">25.3984317779541</t>
@@ -3248,10 +3248,10 @@
     <t xml:space="preserve">25.4166946411133</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2115936279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0837783813477</t>
+    <t xml:space="preserve">24.2115917205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.083776473999</t>
   </si>
   <si>
     <t xml:space="preserve">23.8098926544189</t>
@@ -3260,13 +3260,13 @@
     <t xml:space="preserve">23.3351554870605</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4221992492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7326011657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6778259277344</t>
+    <t xml:space="preserve">22.4221973419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7326030731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.677827835083</t>
   </si>
   <si>
     <t xml:space="preserve">22.2761249542236</t>
@@ -3278,28 +3278,28 @@
     <t xml:space="preserve">22.2213478088379</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8379077911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0935344696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8238983154297</t>
+    <t xml:space="preserve">21.8379058837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0935363769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.823902130127</t>
   </si>
   <si>
     <t xml:space="preserve">21.5457611083984</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0710220336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9657192230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1988372802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2718753814697</t>
+    <t xml:space="preserve">21.07102394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9657211303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1988353729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2718734741211</t>
   </si>
   <si>
     <t xml:space="preserve">20.8884315490723</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">19.9024391174316</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2493629455566</t>
+    <t xml:space="preserve">20.2493648529053</t>
   </si>
   <si>
     <t xml:space="preserve">20.9614677429199</t>
@@ -3344,22 +3344,22 @@
     <t xml:space="preserve">20.3954372406006</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5232486724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6693248748779</t>
+    <t xml:space="preserve">20.523250579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6693229675293</t>
   </si>
   <si>
     <t xml:space="preserve">22.1300525665283</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1933326721191</t>
+    <t xml:space="preserve">24.1933345794678</t>
   </si>
   <si>
     <t xml:space="preserve">23.6455593109131</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5177459716797</t>
+    <t xml:space="preserve">23.5177440643311</t>
   </si>
   <si>
     <t xml:space="preserve">23.7368545532227</t>
@@ -3368,7 +3368,7 @@
     <t xml:space="preserve">23.0533809661865</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9240760803223</t>
+    <t xml:space="preserve">22.9240741729736</t>
   </si>
   <si>
     <t xml:space="preserve">22.7393550872803</t>
@@ -3380,10 +3380,10 @@
     <t xml:space="preserve">20.7443466186523</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6914291381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2850399017334</t>
+    <t xml:space="preserve">19.6914310455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2850379943848</t>
   </si>
   <si>
     <t xml:space="preserve">20.319486618042</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">21.2246265411377</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3539333343506</t>
+    <t xml:space="preserve">21.3539352416992</t>
   </si>
   <si>
     <t xml:space="preserve">21.316987991333</t>
@@ -3410,28 +3410,28 @@
     <t xml:space="preserve">21.4278240203857</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5571269989014</t>
+    <t xml:space="preserve">21.55712890625</t>
   </si>
   <si>
     <t xml:space="preserve">21.7972679138184</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5596256256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7812938690186</t>
+    <t xml:space="preserve">20.559627532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7812919616699</t>
   </si>
   <si>
     <t xml:space="preserve">20.3379592895508</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9130973815918</t>
+    <t xml:space="preserve">19.9130954742432</t>
   </si>
   <si>
     <t xml:space="preserve">20.9475440979004</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0374088287354</t>
+    <t xml:space="preserve">22.0374069213867</t>
   </si>
   <si>
     <t xml:space="preserve">22.4992141723633</t>
@@ -3440,7 +3440,7 @@
     <t xml:space="preserve">21.6679611206055</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4647655487061</t>
+    <t xml:space="preserve">21.4647674560547</t>
   </si>
   <si>
     <t xml:space="preserve">20.8182392120361</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">20.2271251678467</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4487934112549</t>
+    <t xml:space="preserve">20.4487915039062</t>
   </si>
   <si>
     <t xml:space="preserve">21.3908786773682</t>
@@ -3470,7 +3470,7 @@
     <t xml:space="preserve">22.3883800506592</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2960186004639</t>
+    <t xml:space="preserve">22.2960205078125</t>
   </si>
   <si>
     <t xml:space="preserve">22.5361576080322</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">21.5017127990723</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7787952423096</t>
+    <t xml:space="preserve">21.7787933349609</t>
   </si>
   <si>
     <t xml:space="preserve">21.7233791351318</t>
@@ -3518,7 +3518,7 @@
     <t xml:space="preserve">19.9500408172607</t>
   </si>
   <si>
-    <t xml:space="preserve">19.74684715271</t>
+    <t xml:space="preserve">19.7468452453613</t>
   </si>
   <si>
     <t xml:space="preserve">19.5436515808105</t>
@@ -3530,16 +3530,16 @@
     <t xml:space="preserve">18.472261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1926803588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5830974578857</t>
+    <t xml:space="preserve">19.1926784515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5830955505371</t>
   </si>
   <si>
     <t xml:space="preserve">18.2413578033447</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0566349029541</t>
+    <t xml:space="preserve">18.0566329956055</t>
   </si>
   <si>
     <t xml:space="preserve">17.7426052093506</t>
@@ -3560,13 +3560,13 @@
     <t xml:space="preserve">16.8374652862549</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9852447509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.280797958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0037155151367</t>
+    <t xml:space="preserve">16.9852428436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2807998657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0037174224854</t>
   </si>
   <si>
     <t xml:space="preserve">17.6779537200928</t>
@@ -3575,22 +3575,22 @@
     <t xml:space="preserve">17.6317729949951</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8164958953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5855941772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5024681091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0683689117432</t>
+    <t xml:space="preserve">17.8164939880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5855922698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5024662017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0683670043945</t>
   </si>
   <si>
     <t xml:space="preserve">17.2346210479736</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2530918121338</t>
+    <t xml:space="preserve">17.2530899047852</t>
   </si>
   <si>
     <t xml:space="preserve">16.9390621185303</t>
@@ -3614,10 +3614,10 @@
     <t xml:space="preserve">17.7333698272705</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3429546356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4697647094727</t>
+    <t xml:space="preserve">18.3429565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.469762802124</t>
   </si>
   <si>
     <t xml:space="preserve">19.5805969238281</t>
@@ -3635,16 +3635,16 @@
     <t xml:space="preserve">18.3891353607178</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2967739105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4907341003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0079574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0239295959473</t>
+    <t xml:space="preserve">18.2967720031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4907321929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0079555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0239315032959</t>
   </si>
   <si>
     <t xml:space="preserve">19.8392066955566</t>
@@ -3665,31 +3665,31 @@
     <t xml:space="preserve">20.5226802825928</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3354625701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2431011199951</t>
+    <t xml:space="preserve">21.3354606628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2430992126465</t>
   </si>
   <si>
     <t xml:space="preserve">21.9265727996826</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7418518066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2800445556641</t>
+    <t xml:space="preserve">21.7418537139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2800464630127</t>
   </si>
   <si>
     <t xml:space="preserve">21.4093494415283</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8526859283447</t>
+    <t xml:space="preserve">21.8526840209961</t>
   </si>
   <si>
     <t xml:space="preserve">21.1507396697998</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0583782196045</t>
+    <t xml:space="preserve">21.0583763122559</t>
   </si>
   <si>
     <t xml:space="preserve">20.3933753967285</t>
@@ -3701,10 +3701,10 @@
     <t xml:space="preserve">19.9315700531006</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9685134887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2825412750244</t>
+    <t xml:space="preserve">19.9685153961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.282543182373</t>
   </si>
   <si>
     <t xml:space="preserve">20.9290714263916</t>
@@ -3731,13 +3731,13 @@
     <t xml:space="preserve">23.4412975311279</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9031047821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.792272567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.127269744873</t>
+    <t xml:space="preserve">23.9031028747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7922706604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1272716522217</t>
   </si>
   <si>
     <t xml:space="preserve">23.7553272247314</t>
@@ -3749,7 +3749,7 @@
     <t xml:space="preserve">23.4782428741455</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1087989807129</t>
+    <t xml:space="preserve">23.1087970733643</t>
   </si>
   <si>
     <t xml:space="preserve">22.9979629516602</t>
@@ -3758,7 +3758,7 @@
     <t xml:space="preserve">23.0164375305176</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9585227966309</t>
+    <t xml:space="preserve">23.9585247039795</t>
   </si>
   <si>
     <t xml:space="preserve">23.5706043243408</t>
@@ -3770,7 +3770,7 @@
     <t xml:space="preserve">24.1247730255127</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5151882171631</t>
+    <t xml:space="preserve">23.5151863098145</t>
   </si>
   <si>
     <t xml:space="preserve">22.8686599731445</t>
@@ -3782,10 +3782,10 @@
     <t xml:space="preserve">22.9056015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8132419586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6285190582275</t>
+    <t xml:space="preserve">22.8132438659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6285209655762</t>
   </si>
   <si>
     <t xml:space="preserve">22.4622688293457</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">22.2590751647949</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8342113494873</t>
+    <t xml:space="preserve">21.8342132568359</t>
   </si>
   <si>
     <t xml:space="preserve">22.0928230285645</t>
@@ -3824,13 +3824,13 @@
     <t xml:space="preserve">18.6569843292236</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1187915802002</t>
+    <t xml:space="preserve">19.1187896728516</t>
   </si>
   <si>
     <t xml:space="preserve">18.5646228790283</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6754570007324</t>
+    <t xml:space="preserve">18.6754550933838</t>
   </si>
   <si>
     <t xml:space="preserve">19.0264301300049</t>
@@ -3839,7 +3839,7 @@
     <t xml:space="preserve">18.2690658569336</t>
   </si>
   <si>
-    <t xml:space="preserve">18.509204864502</t>
+    <t xml:space="preserve">18.5092067718506</t>
   </si>
   <si>
     <t xml:space="preserve">18.8232345581055</t>
@@ -3851,10 +3851,10 @@
     <t xml:space="preserve">18.7123985290527</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7308731079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6200370788574</t>
+    <t xml:space="preserve">18.7308712005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6200389862061</t>
   </si>
   <si>
     <t xml:space="preserve">18.4445514678955</t>
@@ -3863,13 +3863,13 @@
     <t xml:space="preserve">18.3614273071289</t>
   </si>
   <si>
-    <t xml:space="preserve">17.798023223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5486469268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1422576904297</t>
+    <t xml:space="preserve">17.7980251312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5486488342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1422557830811</t>
   </si>
   <si>
     <t xml:space="preserve">16.948299407959</t>
@@ -3878,16 +3878,16 @@
     <t xml:space="preserve">16.9205894470215</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8651752471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5696182250977</t>
+    <t xml:space="preserve">16.8651733398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5696201324463</t>
   </si>
   <si>
     <t xml:space="preserve">16.8559379577637</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1145496368408</t>
+    <t xml:space="preserve">17.1145515441895</t>
   </si>
   <si>
     <t xml:space="preserve">16.7451038360596</t>
@@ -3896,19 +3896,19 @@
     <t xml:space="preserve">16.9021186828613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8744106292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7912864685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.846700668335</t>
+    <t xml:space="preserve">16.8744125366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7912845611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8467025756836</t>
   </si>
   <si>
     <t xml:space="preserve">16.809757232666</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5880889892578</t>
+    <t xml:space="preserve">16.5880870819092</t>
   </si>
   <si>
     <t xml:space="preserve">16.671215057373</t>
@@ -3926,7 +3926,7 @@
     <t xml:space="preserve">15.710657119751</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0708675384521</t>
+    <t xml:space="preserve">16.0708656311035</t>
   </si>
   <si>
     <t xml:space="preserve">16.0893402099609</t>
@@ -3935,7 +3935,7 @@
     <t xml:space="preserve">16.0062160491943</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0523929595947</t>
+    <t xml:space="preserve">16.0523948669434</t>
   </si>
   <si>
     <t xml:space="preserve">16.6896858215332</t>
@@ -71109,7 +71109,7 @@
     </row>
     <row r="2517">
       <c r="A2517" s="1" t="n">
-        <v>45982.6909953704</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2517" t="n">
         <v>147919</v>
@@ -71130,6 +71130,32 @@
         <v>1764</v>
       </c>
       <c r="H2517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>45985.6910185185</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>56333</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>14.8100004196167</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>14.7200002670288</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>14.7799997329712</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>14.7399997711182</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>1763</v>
+      </c>
+      <c r="H2518" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TNXT.MI.xlsx
+++ b/data/TNXT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63493776321411</t>
+    <t xml:space="preserve">2.63493800163269</t>
   </si>
   <si>
     <t xml:space="preserve">TNXT.MI</t>
@@ -50,85 +50,85 @@
     <t xml:space="preserve">2.59350848197937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53550672531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52556324005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48579072952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52722072601318</t>
+    <t xml:space="preserve">2.53550696372986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52556347846985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48579096794128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5272204875946</t>
   </si>
   <si>
     <t xml:space="preserve">2.48744797706604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47087597846985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46921873092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54047846794128</t>
+    <t xml:space="preserve">2.47087574005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46921849250793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54047799110413</t>
   </si>
   <si>
     <t xml:space="preserve">2.49739122390747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47916197776794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44436097145081</t>
+    <t xml:space="preserve">2.47916221618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44436049461365</t>
   </si>
   <si>
     <t xml:space="preserve">2.39464473724365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34161472320557</t>
+    <t xml:space="preserve">2.34161448478699</t>
   </si>
   <si>
     <t xml:space="preserve">2.36150097846985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55207872390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58522272109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6100800037384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5686502456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63659524917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68962502479553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73436951637268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72608327865601</t>
+    <t xml:space="preserve">2.55207848548889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58522248268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61007976531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56865096092224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63659477233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68962526321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7343692779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72608351707458</t>
   </si>
   <si>
     <t xml:space="preserve">2.77579975128174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58025121688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56202173233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66808152198792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62830901145935</t>
+    <t xml:space="preserve">2.58025097846985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56202220916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66808128356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62830877304077</t>
   </si>
   <si>
     <t xml:space="preserve">2.64322376251221</t>
@@ -137,10 +137,10 @@
     <t xml:space="preserve">2.60842251777649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66642451286316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65316700935364</t>
+    <t xml:space="preserve">2.66642427444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65316724777222</t>
   </si>
   <si>
     <t xml:space="preserve">2.62665200233459</t>
@@ -155,49 +155,49 @@
     <t xml:space="preserve">2.81722950935364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90008950233459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85865926742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89843225479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88351726531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87523150444031</t>
+    <t xml:space="preserve">2.90008974075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8586597442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89843249320984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88351702690125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87523102760315</t>
   </si>
   <si>
     <t xml:space="preserve">2.86694526672363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81888699531555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82054424285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85368776321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79237151145935</t>
+    <t xml:space="preserve">2.81888651847839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82054400444031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85368800163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79237174987793</t>
   </si>
   <si>
     <t xml:space="preserve">2.8570020198822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9067177772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82882976531982</t>
+    <t xml:space="preserve">2.90671825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82883024215698</t>
   </si>
   <si>
     <t xml:space="preserve">2.85037326812744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90837526321411</t>
+    <t xml:space="preserve">2.90837502479553</t>
   </si>
   <si>
     <t xml:space="preserve">2.96306276321411</t>
@@ -209,67 +209,67 @@
     <t xml:space="preserve">2.88169693946838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89017271995544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86474561691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94950175285339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92407512664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96645307540894</t>
+    <t xml:space="preserve">2.89017248153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86474585533142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94950199127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92407488822937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96645283699036</t>
   </si>
   <si>
     <t xml:space="preserve">3.11901307106018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94272136688232</t>
+    <t xml:space="preserve">2.94272112846375</t>
   </si>
   <si>
     <t xml:space="preserve">2.94780683517456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88339233398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87322187423706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85966110229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03256297111511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07037353515625</t>
+    <t xml:space="preserve">2.8833920955658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8732213973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85966038703918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03256273269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07037305831909</t>
   </si>
   <si>
     <t xml:space="preserve">3.06866335868835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06011080741882</t>
+    <t xml:space="preserve">3.06011056900024</t>
   </si>
   <si>
     <t xml:space="preserve">2.99340057373047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98484778404236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93524265289307</t>
+    <t xml:space="preserve">2.98484802246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93524312973022</t>
   </si>
   <si>
     <t xml:space="preserve">2.98313736915588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92497992515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92326951026917</t>
+    <t xml:space="preserve">2.92498016357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92326927185059</t>
   </si>
   <si>
     <t xml:space="preserve">2.9677426815033</t>
@@ -281,73 +281,73 @@
     <t xml:space="preserve">3.05840015411377</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05497908592224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08747863769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13879442214966</t>
+    <t xml:space="preserve">3.05497884750366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08747887611389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13879418373108</t>
   </si>
   <si>
     <t xml:space="preserve">3.12853097915649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19010996818542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15589952468872</t>
+    <t xml:space="preserve">3.19010949134827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15589928627014</t>
   </si>
   <si>
     <t xml:space="preserve">3.12339973449707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12511014938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14734673500061</t>
+    <t xml:space="preserve">3.12510991096497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14734697341919</t>
   </si>
   <si>
     <t xml:space="preserve">3.16445183753967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16616272926331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24142479896545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30129289627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38681888580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48431777954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52708077430725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62629103660583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63655376434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64510607719421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74602746963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67760634422302</t>
+    <t xml:space="preserve">3.16616249084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24142527580261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30129313468933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38681864738464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48431801795959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52708148956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62629055976868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63655424118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64510703086853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74602723121643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67760682106018</t>
   </si>
   <si>
     <t xml:space="preserve">3.71181678771973</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63484334945679</t>
+    <t xml:space="preserve">3.63484358787537</t>
   </si>
   <si>
     <t xml:space="preserve">3.51681804656982</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">3.50655484199524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48089694976807</t>
+    <t xml:space="preserve">3.48089742660522</t>
   </si>
   <si>
     <t xml:space="preserve">3.43129229545593</t>
@@ -371,31 +371,31 @@
     <t xml:space="preserve">3.35602974891663</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60063338279724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64681673049927</t>
+    <t xml:space="preserve">3.60063362121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64681720733643</t>
   </si>
   <si>
     <t xml:space="preserve">3.69471192359924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69984340667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67589545249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66563296318054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59721207618713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63313269615173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57497549057007</t>
+    <t xml:space="preserve">3.69984316825867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67589592933655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66563272476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59721231460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63313317298889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57497501373291</t>
   </si>
   <si>
     <t xml:space="preserve">3.66050171852112</t>
@@ -404,19 +404,19 @@
     <t xml:space="preserve">3.68615889549255</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71523714065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73747420310974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71010589599609</t>
+    <t xml:space="preserve">3.7152373790741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7374746799469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71010613441467</t>
   </si>
   <si>
     <t xml:space="preserve">3.69129037857056</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6895797252655</t>
+    <t xml:space="preserve">3.68958020210266</t>
   </si>
   <si>
     <t xml:space="preserve">3.73234272003174</t>
@@ -425,49 +425,49 @@
     <t xml:space="preserve">3.72036910057068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76313233375549</t>
+    <t xml:space="preserve">3.76313185691833</t>
   </si>
   <si>
     <t xml:space="preserve">3.77168464660645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62115979194641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64168524742126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70326399803162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79734230041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75457978248596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9085259437561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76655244827271</t>
+    <t xml:space="preserve">3.62115955352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64168572425842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70326375961304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7973427772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75457954406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90852642059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76655340194702</t>
   </si>
   <si>
     <t xml:space="preserve">3.72892141342163</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6673436164856</t>
+    <t xml:space="preserve">3.66734337806702</t>
   </si>
   <si>
     <t xml:space="preserve">3.50997614860535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49800229072571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4894495010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47234487533569</t>
+    <t xml:space="preserve">3.49800252914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48944973945618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47234463691711</t>
   </si>
   <si>
     <t xml:space="preserve">3.40392422676086</t>
@@ -476,13 +476,13 @@
     <t xml:space="preserve">3.43642377853394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53221273422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5185284614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46037101745605</t>
+    <t xml:space="preserve">3.53221249580383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51852822303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46037125587463</t>
   </si>
   <si>
     <t xml:space="preserve">3.50142312049866</t>
@@ -491,46 +491,46 @@
     <t xml:space="preserve">3.53563332557678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55615997314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64339637756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7255003452301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84865832328796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82984232902527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83155226707458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87089490890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84523630142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87431573867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86405253410339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85721039772034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82471060752869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90681505203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00260448455811</t>
+    <t xml:space="preserve">3.55616021156311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6433961391449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72550082206726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84865760803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82984209060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8315532207489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87089395523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84523677825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8743155002594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86405277252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85720992088318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82471084594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90681529045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00260400772095</t>
   </si>
   <si>
     <t xml:space="preserve">4.17536640167236</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">4.11378717422485</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00773525238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0522084236145</t>
+    <t xml:space="preserve">4.00773572921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05220937728882</t>
   </si>
   <si>
     <t xml:space="preserve">4.08128833770752</t>
@@ -551,46 +551,46 @@
     <t xml:space="preserve">4.0060248374939</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09839248657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01970863342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01115703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99576115608215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03510427474976</t>
+    <t xml:space="preserve">4.09839344024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01970911026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01115655899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99576210975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0351037979126</t>
   </si>
   <si>
     <t xml:space="preserve">4.06247234344482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13773488998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1223406791687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14799785614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18905019760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2591814994812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22839212417603</t>
+    <t xml:space="preserve">4.13773441314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12233972549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14799833297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18905067443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25918102264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22839164733887</t>
   </si>
   <si>
     <t xml:space="preserve">4.20615577697754</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0214204788208</t>
+    <t xml:space="preserve">4.02142000198364</t>
   </si>
   <si>
     <t xml:space="preserve">3.99405121803284</t>
@@ -599,19 +599,19 @@
     <t xml:space="preserve">4.01799869537354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02655124664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07615613937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12747240066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11891937255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10523557662964</t>
+    <t xml:space="preserve">4.02655172348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07615566253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12747192382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11891889572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10523414611816</t>
   </si>
   <si>
     <t xml:space="preserve">4.09668254852295</t>
@@ -626,25 +626,25 @@
     <t xml:space="preserve">4.09497213363647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13089227676392</t>
+    <t xml:space="preserve">4.13089275360107</t>
   </si>
   <si>
     <t xml:space="preserve">4.21641874313354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52431154251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54996871948242</t>
+    <t xml:space="preserve">4.52431106567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54996919631958</t>
   </si>
   <si>
     <t xml:space="preserve">4.53713989257812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46444368362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50292921066284</t>
+    <t xml:space="preserve">4.46444272994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5029296875</t>
   </si>
   <si>
     <t xml:space="preserve">4.56707382202148</t>
@@ -653,19 +653,19 @@
     <t xml:space="preserve">4.62266635894775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63549470901489</t>
+    <t xml:space="preserve">4.63549423217773</t>
   </si>
   <si>
     <t xml:space="preserve">4.58417940139771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60128355026245</t>
+    <t xml:space="preserve">4.60128450393677</t>
   </si>
   <si>
     <t xml:space="preserve">4.57562637329102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61839008331299</t>
+    <t xml:space="preserve">4.61838912963867</t>
   </si>
   <si>
     <t xml:space="preserve">4.53286409378052</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">4.48154783248901</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5157585144043</t>
+    <t xml:space="preserve">4.51575899124146</t>
   </si>
   <si>
     <t xml:space="preserve">4.4901008605957</t>
@@ -686,10 +686,10 @@
     <t xml:space="preserve">4.51148223876953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63121795654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78516387939453</t>
+    <t xml:space="preserve">4.63121843338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78516435623169</t>
   </si>
   <si>
     <t xml:space="preserve">4.75950717926025</t>
@@ -707,28 +707,28 @@
     <t xml:space="preserve">4.76378345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6568751335144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69536209106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82792711257935</t>
+    <t xml:space="preserve">4.65687561035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69536256790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8279275894165</t>
   </si>
   <si>
     <t xml:space="preserve">4.90062427520752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91772890090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94338750839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98615074157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0417423248291</t>
+    <t xml:space="preserve">4.91772937774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94338703155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98614931106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04174137115479</t>
   </si>
   <si>
     <t xml:space="preserve">5.02035999298096</t>
@@ -752,19 +752,19 @@
     <t xml:space="preserve">4.91728496551514</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94766569137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92596483230591</t>
+    <t xml:space="preserve">4.94766521453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92596530914307</t>
   </si>
   <si>
     <t xml:space="preserve">4.90426445007324</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8218035697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7350025177002</t>
+    <t xml:space="preserve">4.82180404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73500299453735</t>
   </si>
   <si>
     <t xml:space="preserve">4.72198247909546</t>
@@ -773,16 +773,16 @@
     <t xml:space="preserve">4.59178066253662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64386177062988</t>
+    <t xml:space="preserve">4.64386129379272</t>
   </si>
   <si>
     <t xml:space="preserve">4.73066186904907</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66556167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65254211425781</t>
+    <t xml:space="preserve">4.66556119918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6525411605835</t>
   </si>
   <si>
     <t xml:space="preserve">4.60914087295532</t>
@@ -794,28 +794,28 @@
     <t xml:space="preserve">4.54837989807129</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53535985946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47025918960571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5961217880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47459840774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48761892318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46157884597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41383790969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38779783248901</t>
+    <t xml:space="preserve">4.53536033630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47025966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59612083435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47459936141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48761987686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46157836914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4138388633728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38779735565186</t>
   </si>
   <si>
     <t xml:space="preserve">4.39213800430298</t>
@@ -824,37 +824,37 @@
     <t xml:space="preserve">4.40949821472168</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55706071853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52234029769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57008075714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53970003128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47893857955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43553829193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42251825332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43119859695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45289897918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51365900039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68726205825806</t>
+    <t xml:space="preserve">4.55706024169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52233982086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57008028030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53970050811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47893905639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43553876876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4225172996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4311990737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45289945602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51365995407104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68726253509521</t>
   </si>
   <si>
     <t xml:space="preserve">4.60046100616455</t>
@@ -863,10 +863,10 @@
     <t xml:space="preserve">4.63952112197876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56140041351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58744049072266</t>
+    <t xml:space="preserve">4.56139993667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58744096755981</t>
   </si>
   <si>
     <t xml:space="preserve">4.61782121658325</t>
@@ -878,16 +878,16 @@
     <t xml:space="preserve">4.60480117797852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58310079574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49629974365234</t>
+    <t xml:space="preserve">4.58309984207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49629926681519</t>
   </si>
   <si>
     <t xml:space="preserve">4.50497961044312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42685842514038</t>
+    <t xml:space="preserve">4.42685794830322</t>
   </si>
   <si>
     <t xml:space="preserve">4.49195909500122</t>
@@ -911,46 +911,46 @@
     <t xml:space="preserve">4.74368286132812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81312370300293</t>
+    <t xml:space="preserve">4.81312322616577</t>
   </si>
   <si>
     <t xml:space="preserve">4.71330213546753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70462226867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72632217407227</t>
+    <t xml:space="preserve">4.70462274551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72632265090942</t>
   </si>
   <si>
     <t xml:space="preserve">4.69594192504883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76972246170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84350299835205</t>
+    <t xml:space="preserve">4.76972341537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84350395202637</t>
   </si>
   <si>
     <t xml:space="preserve">4.87822389602661</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8738842010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97370624542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97804594039917</t>
+    <t xml:space="preserve">4.87388372421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97370529174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97804641723633</t>
   </si>
   <si>
     <t xml:space="preserve">5.00842618942261</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07786703109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04314613342285</t>
+    <t xml:space="preserve">5.07786750793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04314661026001</t>
   </si>
   <si>
     <t xml:space="preserve">5.14730787277222</t>
@@ -962,19 +962,19 @@
     <t xml:space="preserve">4.869544506073</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96502542495728</t>
+    <t xml:space="preserve">4.96502494812012</t>
   </si>
   <si>
     <t xml:space="preserve">4.90860509872437</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99974632263184</t>
+    <t xml:space="preserve">4.99974679946899</t>
   </si>
   <si>
     <t xml:space="preserve">4.99106597900391</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15598773956299</t>
+    <t xml:space="preserve">5.15598821640015</t>
   </si>
   <si>
     <t xml:space="preserve">5.12994766235352</t>
@@ -986,10 +986,10 @@
     <t xml:space="preserve">5.41639137268066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48583269119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43375158309937</t>
+    <t xml:space="preserve">5.48583221435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43375205993652</t>
   </si>
   <si>
     <t xml:space="preserve">5.48149251937866</t>
@@ -1001,55 +1001,55 @@
     <t xml:space="preserve">5.39469146728516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35563135147095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33393049240112</t>
+    <t xml:space="preserve">5.35563087463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33393096923828</t>
   </si>
   <si>
     <t xml:space="preserve">5.37299108505249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33827114105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20806932449341</t>
+    <t xml:space="preserve">5.33827066421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20806884765625</t>
   </si>
   <si>
     <t xml:space="preserve">5.16466808319092</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26449012756348</t>
+    <t xml:space="preserve">5.26448965072632</t>
   </si>
   <si>
     <t xml:space="preserve">5.25146961212158</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2601490020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18636894226074</t>
+    <t xml:space="preserve">5.26014947891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18636846542358</t>
   </si>
   <si>
     <t xml:space="preserve">5.20372867584229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19504880905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16900777816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18202781677246</t>
+    <t xml:space="preserve">5.19504833221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16900825500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18202829360962</t>
   </si>
   <si>
     <t xml:space="preserve">5.19938850402832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22542905807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42507219314575</t>
+    <t xml:space="preserve">5.22542858123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42507123947144</t>
   </si>
   <si>
     <t xml:space="preserve">5.61603403091431</t>
@@ -1058,28 +1058,28 @@
     <t xml:space="preserve">5.72887563705444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71151494979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78963708877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82435703277588</t>
+    <t xml:space="preserve">5.7115159034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78963661193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82435750961304</t>
   </si>
   <si>
     <t xml:space="preserve">5.87643766403198</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88511753082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93719863891602</t>
+    <t xml:space="preserve">5.88511848449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93719816207886</t>
   </si>
   <si>
     <t xml:space="preserve">5.85907697677612</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80699634552002</t>
+    <t xml:space="preserve">5.80699682235718</t>
   </si>
   <si>
     <t xml:space="preserve">5.92851781845093</t>
@@ -1091,52 +1091,52 @@
     <t xml:space="preserve">5.95455884933472</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03268003463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17156171798706</t>
+    <t xml:space="preserve">6.03267955780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1715612411499</t>
   </si>
   <si>
     <t xml:space="preserve">6.28440237045288</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01531982421875</t>
+    <t xml:space="preserve">6.01531887054443</t>
   </si>
   <si>
     <t xml:space="preserve">6.02399969100952</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21496200561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14552068710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40592527389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07608032226562</t>
+    <t xml:space="preserve">6.21496295928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14552164077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40592432022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07607984542847</t>
   </si>
   <si>
     <t xml:space="preserve">5.98927879333496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04136037826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22364234924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1368408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19760179519653</t>
+    <t xml:space="preserve">6.04135990142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22364187240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13684129714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19760227203369</t>
   </si>
   <si>
     <t xml:space="preserve">6.15420150756836</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05004024505615</t>
+    <t xml:space="preserve">6.05003929138184</t>
   </si>
   <si>
     <t xml:space="preserve">5.89379787445068</t>
@@ -1145,43 +1145,43 @@
     <t xml:space="preserve">5.90247821807861</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70283555984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50319337844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58131313323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72019577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.763596534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91983795166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99795866012573</t>
+    <t xml:space="preserve">5.70283508300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50319290161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58131408691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72019529342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76359605789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91983842849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99795913696289</t>
   </si>
   <si>
     <t xml:space="preserve">5.83303689956665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79831695556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65943479537964</t>
+    <t xml:space="preserve">5.79831647872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65943431854248</t>
   </si>
   <si>
     <t xml:space="preserve">5.5118727684021</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5465931892395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58999347686768</t>
+    <t xml:space="preserve">5.54659366607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58999395370483</t>
   </si>
   <si>
     <t xml:space="preserve">5.52055311203003</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">5.38167095184326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44243144989014</t>
+    <t xml:space="preserve">5.44243192672729</t>
   </si>
   <si>
     <t xml:space="preserve">5.46847248077393</t>
@@ -1199,13 +1199,13 @@
     <t xml:space="preserve">5.67679500579834</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6420750617981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55527305603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53791379928589</t>
+    <t xml:space="preserve">5.64207458496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55527353286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53791284561157</t>
   </si>
   <si>
     <t xml:space="preserve">5.57263374328613</t>
@@ -1214,16 +1214,16 @@
     <t xml:space="preserve">5.5292329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39903116226196</t>
+    <t xml:space="preserve">5.39903163909912</t>
   </si>
   <si>
     <t xml:space="preserve">5.39035177230835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45111179351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09344100952148</t>
+    <t xml:space="preserve">5.45111227035522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09344053268433</t>
   </si>
   <si>
     <t xml:space="preserve">5.81567668914795</t>
@@ -1235,34 +1235,34 @@
     <t xml:space="preserve">5.73755598068237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40771150588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24278879165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06918716430664</t>
+    <t xml:space="preserve">5.40771102905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24278926849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0691876411438</t>
   </si>
   <si>
     <t xml:space="preserve">4.98238563537598</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07618856430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15619802474976</t>
+    <t xml:space="preserve">5.07618761062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15619850158691</t>
   </si>
   <si>
     <t xml:space="preserve">5.08507776260376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24509811401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11174821853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13841772079468</t>
+    <t xml:space="preserve">5.24509763717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11174869537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13841819763184</t>
   </si>
   <si>
     <t xml:space="preserve">5.20953845977783</t>
@@ -1271,10 +1271,10 @@
     <t xml:space="preserve">5.06729793548584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05840826034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04062843322754</t>
+    <t xml:space="preserve">5.0584077835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04062795639038</t>
   </si>
   <si>
     <t xml:space="preserve">5.04951810836792</t>
@@ -1289,31 +1289,31 @@
     <t xml:space="preserve">4.90727806091309</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76503849029541</t>
+    <t xml:space="preserve">4.76503753662109</t>
   </si>
   <si>
     <t xml:space="preserve">4.92505788803101</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88949823379517</t>
+    <t xml:space="preserve">4.88949775695801</t>
   </si>
   <si>
     <t xml:space="preserve">5.02284812927246</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97839784622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91616773605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95172786712646</t>
+    <t xml:space="preserve">4.97839832305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91616821289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95172834396362</t>
   </si>
   <si>
     <t xml:space="preserve">4.93394804000854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89838790893555</t>
+    <t xml:space="preserve">4.89838886260986</t>
   </si>
   <si>
     <t xml:space="preserve">4.80948781967163</t>
@@ -1322,19 +1322,19 @@
     <t xml:space="preserve">4.78281831741333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75614833831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98728799819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10285758972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96061706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20064783096313</t>
+    <t xml:space="preserve">4.75614786148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9872875213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10285711288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.960618019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20064735412598</t>
   </si>
   <si>
     <t xml:space="preserve">5.21842765808105</t>
@@ -1343,28 +1343,28 @@
     <t xml:space="preserve">5.27176761627197</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33399820327759</t>
+    <t xml:space="preserve">5.33399724960327</t>
   </si>
   <si>
     <t xml:space="preserve">5.23620796203613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18286752700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01395797729492</t>
+    <t xml:space="preserve">5.18286800384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01395750045776</t>
   </si>
   <si>
     <t xml:space="preserve">4.99617767333984</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00506782531738</t>
+    <t xml:space="preserve">5.00506830215454</t>
   </si>
   <si>
     <t xml:space="preserve">5.37844800949097</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47623777389526</t>
+    <t xml:space="preserve">5.47623825073242</t>
   </si>
   <si>
     <t xml:space="preserve">5.56513786315918</t>
@@ -1373,25 +1373,25 @@
     <t xml:space="preserve">5.6807074546814</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6540379524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63625812530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5562481880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68959760665894</t>
+    <t xml:space="preserve">5.65403747558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63625764846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55624771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68959808349609</t>
   </si>
   <si>
     <t xml:space="preserve">5.96518754959106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89406824111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77849769592285</t>
+    <t xml:space="preserve">5.89406776428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77849721908569</t>
   </si>
   <si>
     <t xml:space="preserve">5.84072780609131</t>
@@ -1400,10 +1400,10 @@
     <t xml:space="preserve">5.76071739196777</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92073774337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83183717727661</t>
+    <t xml:space="preserve">5.92073726654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83183765411377</t>
   </si>
   <si>
     <t xml:space="preserve">5.44956827163696</t>
@@ -1412,88 +1412,88 @@
     <t xml:space="preserve">5.5829176902771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43178844451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36955738067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6095871925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86739778518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78738832473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5206880569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49401760101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57402753829956</t>
+    <t xml:space="preserve">5.43178796768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36955785751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60958766937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86739730834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78738784790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52068853378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49401807785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57402801513672</t>
   </si>
   <si>
     <t xml:space="preserve">5.59180736541748</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6451473236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71626758575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73404741287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81405735015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67181825637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5117974281311</t>
+    <t xml:space="preserve">5.64514780044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71626710891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73404788970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81405782699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67181730270386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51179695129395</t>
   </si>
   <si>
     <t xml:space="preserve">5.85850811004639</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66292715072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53846788406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90295791625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79627752304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80516767501831</t>
+    <t xml:space="preserve">5.66292762756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53846740722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90295743942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79627799987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80516815185547</t>
   </si>
   <si>
     <t xml:space="preserve">5.6184778213501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46734809875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60069799423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45845794677734</t>
+    <t xml:space="preserve">5.46734762191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60069847106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45845746994019</t>
   </si>
   <si>
     <t xml:space="preserve">5.50290775299072</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34288740158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62736701965332</t>
+    <t xml:space="preserve">5.34288787841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62736749649048</t>
   </si>
   <si>
     <t xml:space="preserve">5.52957773208618</t>
@@ -1502,16 +1502,16 @@
     <t xml:space="preserve">5.42289781570435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72515726089478</t>
+    <t xml:space="preserve">5.72515773773193</t>
   </si>
   <si>
     <t xml:space="preserve">5.70737791061401</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69848775863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0007472038269</t>
+    <t xml:space="preserve">5.69848728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00074768066406</t>
   </si>
   <si>
     <t xml:space="preserve">5.92962789535522</t>
@@ -1520,49 +1520,49 @@
     <t xml:space="preserve">5.94740724563599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93851804733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99185705184937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24077796936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40968704223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48080682754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.623046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84529685974121</t>
+    <t xml:space="preserve">5.93851757049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99185657501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24077701568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40968751907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48080778121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62304735183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84529733657837</t>
   </si>
   <si>
     <t xml:space="preserve">6.99642705917358</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0142068862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90752744674683</t>
+    <t xml:space="preserve">7.01420736312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90752696990967</t>
   </si>
   <si>
     <t xml:space="preserve">6.91641759872437</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97864723205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00531768798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0230975151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2453465461731</t>
+    <t xml:space="preserve">6.97864675521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00531721115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02309703826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24534702301025</t>
   </si>
   <si>
     <t xml:space="preserve">7.27201747894287</t>
@@ -1571,67 +1571,67 @@
     <t xml:space="preserve">7.33424711227417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47648763656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76985692977905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73429584503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72540664672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79652690887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80541610717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22324752807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21435737609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15212631225586</t>
+    <t xml:space="preserve">7.476487159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76985740661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7342963218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7254056930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79652643203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80541658401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22324562072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21435642242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15212726593018</t>
   </si>
   <si>
     <t xml:space="preserve">8.12545680999756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00099754333496</t>
+    <t xml:space="preserve">8.00099658966064</t>
   </si>
   <si>
     <t xml:space="preserve">8.17879581451416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34770584106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42771530151367</t>
+    <t xml:space="preserve">8.3477087020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42771625518799</t>
   </si>
   <si>
     <t xml:space="preserve">8.48105525970459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46327686309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5255069732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50772571563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66774749755859</t>
+    <t xml:space="preserve">8.46327781677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52550601959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50772666931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66774654388428</t>
   </si>
   <si>
     <t xml:space="preserve">8.80109596252441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88999652862549</t>
+    <t xml:space="preserve">8.88999557495117</t>
   </si>
   <si>
     <t xml:space="preserve">9.19225597381592</t>
@@ -1640,13 +1640,13 @@
     <t xml:space="preserve">9.37005615234375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47673606872559</t>
+    <t xml:space="preserve">9.47673511505127</t>
   </si>
   <si>
     <t xml:space="preserve">9.49451637268066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31671524047852</t>
+    <t xml:space="preserve">9.31671619415283</t>
   </si>
   <si>
     <t xml:space="preserve">9.15669631958008</t>
@@ -1658,28 +1658,28 @@
     <t xml:space="preserve">9.40561676025391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69009494781494</t>
+    <t xml:space="preserve">9.69009590148926</t>
   </si>
   <si>
     <t xml:space="preserve">9.86789608001709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83233547210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77899646759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44117641448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.210036277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58341693878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51229667663574</t>
+    <t xml:space="preserve">9.83233642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77899551391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44117546081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21003532409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58341503143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51229572296143</t>
   </si>
   <si>
     <t xml:space="preserve">9.67231559753418</t>
@@ -1691,13 +1691,13 @@
     <t xml:space="preserve">10.0990362167358</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0279159545898</t>
+    <t xml:space="preserve">10.0279150009155</t>
   </si>
   <si>
     <t xml:space="preserve">9.99235534667969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0101356506348</t>
+    <t xml:space="preserve">10.0101366043091</t>
   </si>
   <si>
     <t xml:space="preserve">9.76121520996094</t>
@@ -1706,13 +1706,13 @@
     <t xml:space="preserve">9.88567543029785</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2234964370728</t>
+    <t xml:space="preserve">10.2234973907471</t>
   </si>
   <si>
     <t xml:space="preserve">10.4368553161621</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6679964065552</t>
+    <t xml:space="preserve">10.6679944992065</t>
   </si>
   <si>
     <t xml:space="preserve">11.414755821228</t>
@@ -1721,10 +1721,10 @@
     <t xml:space="preserve">11.3614149093628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3080759048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4325351715088</t>
+    <t xml:space="preserve">11.3080749511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4325342178345</t>
   </si>
   <si>
     <t xml:space="preserve">11.6814556121826</t>
@@ -1736,55 +1736,55 @@
     <t xml:space="preserve">11.965934753418</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1437339782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6281147003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4001140594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6715450286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.653450012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.689640045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.123929977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7982120513916</t>
+    <t xml:space="preserve">12.1437358856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6281156539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4001150131226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6715440750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6534490585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6896390914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1239290237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7982130050659</t>
   </si>
   <si>
     <t xml:space="preserve">12.1782159805298</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3229789733887</t>
+    <t xml:space="preserve">12.322979927063</t>
   </si>
   <si>
     <t xml:space="preserve">12.9925088882446</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8296508789062</t>
+    <t xml:space="preserve">12.8296518325806</t>
   </si>
   <si>
     <t xml:space="preserve">12.7391738891602</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7753658294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3953619003296</t>
+    <t xml:space="preserve">12.7753648757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.395359992981</t>
   </si>
   <si>
     <t xml:space="preserve">12.2867879867554</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6306028366089</t>
+    <t xml:space="preserve">12.6306009292603</t>
   </si>
   <si>
     <t xml:space="preserve">12.4496469497681</t>
@@ -1793,16 +1793,16 @@
     <t xml:space="preserve">12.2144069671631</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1058340072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8705930709839</t>
+    <t xml:space="preserve">12.1058349609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8705940246582</t>
   </si>
   <si>
     <t xml:space="preserve">11.9067850112915</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4724941253662</t>
+    <t xml:space="preserve">11.4724950790405</t>
   </si>
   <si>
     <t xml:space="preserve">11.4182081222534</t>
@@ -1811,7 +1811,7 @@
     <t xml:space="preserve">11.5810680389404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8524990081787</t>
+    <t xml:space="preserve">11.8524980545044</t>
   </si>
   <si>
     <t xml:space="preserve">12.0877389907837</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">11.8344030380249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.888689994812</t>
+    <t xml:space="preserve">11.8886890411377</t>
   </si>
   <si>
     <t xml:space="preserve">11.4363040924072</t>
@@ -1832,19 +1832,19 @@
     <t xml:space="preserve">11.2734451293945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1829671859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1648731231689</t>
+    <t xml:space="preserve">11.1829690933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1648721694946</t>
   </si>
   <si>
     <t xml:space="preserve">10.8391551971436</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6401042938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6762971878052</t>
+    <t xml:space="preserve">10.6401052474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6762962341309</t>
   </si>
   <si>
     <t xml:space="preserve">10.5134372711182</t>
@@ -1853,31 +1853,31 @@
     <t xml:space="preserve">10.9115371704102</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2915391921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1467761993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7667741775513</t>
+    <t xml:space="preserve">11.2915410995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1467781066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.766773223877</t>
   </si>
   <si>
     <t xml:space="preserve">11.1105861663818</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1286811828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6220092773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0020141601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6039142608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4953422546387</t>
+    <t xml:space="preserve">11.1286821365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6220102310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0020132064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6039152145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.495343208313</t>
   </si>
   <si>
     <t xml:space="preserve">10.2781972885132</t>
@@ -1886,52 +1886,52 @@
     <t xml:space="preserve">10.3143873214722</t>
   </si>
   <si>
-    <t xml:space="preserve">9.898193359375</t>
+    <t xml:space="preserve">9.89819145202637</t>
   </si>
   <si>
     <t xml:space="preserve">9.93438339233398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80771732330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68104839324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95248031616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2420053482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4772462844849</t>
+    <t xml:space="preserve">9.80771636962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6810474395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95247936248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2420063018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4772472381592</t>
   </si>
   <si>
     <t xml:space="preserve">10.3867683410645</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4410552978516</t>
+    <t xml:space="preserve">10.4410562515259</t>
   </si>
   <si>
     <t xml:space="preserve">9.55438041687012</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1153392791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3505792617798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4048643112183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7486791610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0201101303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.857250213623</t>
+    <t xml:space="preserve">10.1153383255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3505783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4048662185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7486782073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0201082229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8572492599487</t>
   </si>
   <si>
     <t xml:space="preserve">10.8753461837769</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">10.5858192443848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8029642105103</t>
+    <t xml:space="preserve">10.8029632568359</t>
   </si>
   <si>
     <t xml:space="preserve">10.7124872207642</t>
@@ -1952,16 +1952,16 @@
     <t xml:space="preserve">11.2372550964355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3096351623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4543981552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7258310317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9972610473633</t>
+    <t xml:space="preserve">11.3096361160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4543991088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.725830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9972620010376</t>
   </si>
   <si>
     <t xml:space="preserve">12.160120010376</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">12.0334520339966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9429759979248</t>
+    <t xml:space="preserve">11.9429750442505</t>
   </si>
   <si>
     <t xml:space="preserve">11.7620210647583</t>
@@ -1982,10 +1982,10 @@
     <t xml:space="preserve">10.9477281570435</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9658231735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1877202987671</t>
+    <t xml:space="preserve">10.9658222198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1877212524414</t>
   </si>
   <si>
     <t xml:space="preserve">9.98867034912109</t>
@@ -1994,16 +1994,16 @@
     <t xml:space="preserve">10.0429573059082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91628837585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.169623374939</t>
+    <t xml:space="preserve">9.91629028320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1696243286133</t>
   </si>
   <si>
     <t xml:space="preserve">10.531533241272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4229612350464</t>
+    <t xml:space="preserve">10.4229602813721</t>
   </si>
   <si>
     <t xml:space="preserve">10.1334342956543</t>
@@ -2018,10 +2018,10 @@
     <t xml:space="preserve">10.097243309021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0610523223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0791482925415</t>
+    <t xml:space="preserve">10.0610513687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0791492462158</t>
   </si>
   <si>
     <t xml:space="preserve">10.1515293121338</t>
@@ -2030,25 +2030,25 @@
     <t xml:space="preserve">11.056300163269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8934412002563</t>
+    <t xml:space="preserve">10.893440246582</t>
   </si>
   <si>
     <t xml:space="preserve">10.5496282577515</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3686742782593</t>
+    <t xml:space="preserve">10.368673324585</t>
   </si>
   <si>
     <t xml:space="preserve">9.8258113861084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77152442932129</t>
+    <t xml:space="preserve">9.77152633666992</t>
   </si>
   <si>
     <t xml:space="preserve">9.699143409729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51818943023682</t>
+    <t xml:space="preserve">9.51819038391113</t>
   </si>
   <si>
     <t xml:space="preserve">9.7172384262085</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">9.59057140350342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3639221191406</t>
+    <t xml:space="preserve">11.3639230728149</t>
   </si>
   <si>
     <t xml:space="preserve">11.9791660308838</t>
@@ -2069,55 +2069,55 @@
     <t xml:space="preserve">12.4677429199219</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3772668838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3820171356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5629720687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6172580718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0924911499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6943922042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62676239013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8034200668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68580055236816</t>
+    <t xml:space="preserve">12.3772649765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3820161819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5629711151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6172590255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0924921035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6943912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62676334381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80342102050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68579959869385</t>
   </si>
   <si>
     <t xml:space="preserve">8.43246459960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0481653213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3286452293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24721479415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18388080596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58673191070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65006637573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96673536300659</t>
+    <t xml:space="preserve">7.04816579818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32864427566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24721527099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18388032913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58673238754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65006589889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96673583984375</t>
   </si>
   <si>
     <t xml:space="preserve">6.9757833480835</t>
@@ -2126,16 +2126,16 @@
     <t xml:space="preserve">7.16578531265259</t>
   </si>
   <si>
-    <t xml:space="preserve">7.057213306427</t>
+    <t xml:space="preserve">7.05721282958984</t>
   </si>
   <si>
     <t xml:space="preserve">7.28340625762939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60912275314331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76293420791626</t>
+    <t xml:space="preserve">7.60912322998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76293468475342</t>
   </si>
   <si>
     <t xml:space="preserve">8.34198760986328</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">8.04341316223145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61341857910156</t>
+    <t xml:space="preserve">8.61341953277588</t>
   </si>
   <si>
     <t xml:space="preserve">8.41436958312988</t>
@@ -2153,22 +2153,22 @@
     <t xml:space="preserve">8.25151062011719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93008804321289</t>
+    <t xml:space="preserve">8.93008899688721</t>
   </si>
   <si>
     <t xml:space="preserve">9.35533046722412</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04770946502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26485347747803</t>
+    <t xml:space="preserve">9.04770851135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26485443115234</t>
   </si>
   <si>
     <t xml:space="preserve">9.50009346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86200332641602</t>
+    <t xml:space="preserve">9.86200141906738</t>
   </si>
   <si>
     <t xml:space="preserve">11.2191581726074</t>
@@ -2177,13 +2177,13 @@
     <t xml:space="preserve">10.9839191436768</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6582002639771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9705753326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2058153152466</t>
+    <t xml:space="preserve">10.6582012176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97057628631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2058143615723</t>
   </si>
   <si>
     <t xml:space="preserve">9.84390735626221</t>
@@ -2198,7 +2198,7 @@
     <t xml:space="preserve">10.7305822372437</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8210601806641</t>
+    <t xml:space="preserve">10.8210592269897</t>
   </si>
   <si>
     <t xml:space="preserve">12.0696439743042</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">12.558219909668</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8477458953857</t>
+    <t xml:space="preserve">12.8477449417114</t>
   </si>
   <si>
     <t xml:space="preserve">13.1915597915649</t>
@@ -2219,67 +2219,67 @@
     <t xml:space="preserve">12.7934608459473</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4315509796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5944108963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6486968994141</t>
+    <t xml:space="preserve">12.4315519332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.594409942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6486959457397</t>
   </si>
   <si>
     <t xml:space="preserve">12.7210788726807</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8658428192139</t>
+    <t xml:space="preserve">12.8658418655396</t>
   </si>
   <si>
     <t xml:space="preserve">13.1553678512573</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0287008285522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.119176864624</t>
+    <t xml:space="preserve">13.0286998748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1191778182983</t>
   </si>
   <si>
     <t xml:space="preserve">12.9382238388062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0829858779907</t>
+    <t xml:space="preserve">13.082986831665</t>
   </si>
   <si>
     <t xml:space="preserve">13.3725128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3544178009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4534864425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.249683380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2858753204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3763542175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6477851867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8334903717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0687313079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8696813583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9239654541016</t>
+    <t xml:space="preserve">13.3544187545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4534854888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2496852874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2858772277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3763523101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6477832794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8334913253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0687294006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8696804046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9239692687988</t>
   </si>
   <si>
     <t xml:space="preserve">15.9058713912964</t>
@@ -2288,10 +2288,10 @@
     <t xml:space="preserve">15.8515872955322</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0144424438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7972984313965</t>
+    <t xml:space="preserve">16.0144443511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7972974777222</t>
   </si>
   <si>
     <t xml:space="preserve">16.2677803039551</t>
@@ -2300,34 +2300,34 @@
     <t xml:space="preserve">16.0325393676758</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7792043685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7249145507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4125442504883</t>
+    <t xml:space="preserve">15.779203414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7249155044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4125423431396</t>
   </si>
   <si>
     <t xml:space="preserve">15.8153963088989</t>
   </si>
   <si>
-    <t xml:space="preserve">15.942063331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6344385147095</t>
+    <t xml:space="preserve">15.9420642852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6344413757324</t>
   </si>
   <si>
     <t xml:space="preserve">16.1049213409424</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9601554870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6887264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6163463592529</t>
+    <t xml:space="preserve">15.9601564407349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6887283325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6163454055786</t>
   </si>
   <si>
     <t xml:space="preserve">14.8925285339355</t>
@@ -2339,49 +2339,49 @@
     <t xml:space="preserve">15.3630084991455</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4896783828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1458644866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0372934341431</t>
+    <t xml:space="preserve">15.4896802902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1458654403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0372915267944</t>
   </si>
   <si>
     <t xml:space="preserve">15.7430124282837</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8201475143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2906284332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5887432098389</t>
+    <t xml:space="preserve">14.8201456069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2906274795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5887451171875</t>
   </si>
   <si>
     <t xml:space="preserve">17.7696990966797</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0230369567871</t>
+    <t xml:space="preserve">18.0230350494385</t>
   </si>
   <si>
     <t xml:space="preserve">19.1359043121338</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2763748168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0411338806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4258861541748</t>
+    <t xml:space="preserve">18.2763729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0411319732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4258880615234</t>
   </si>
   <si>
     <t xml:space="preserve">17.7335090637207</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2992191314697</t>
+    <t xml:space="preserve">17.2992210388184</t>
   </si>
   <si>
     <t xml:space="preserve">17.0458831787109</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">17.0096912384033</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4077911376953</t>
+    <t xml:space="preserve">17.4077930450439</t>
   </si>
   <si>
     <t xml:space="preserve">18.5025653839111</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">17.4982681274414</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9868469238281</t>
+    <t xml:space="preserve">17.9868431091309</t>
   </si>
   <si>
     <t xml:space="preserve">18.5930404663086</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">17.1182651519775</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8106422424316</t>
+    <t xml:space="preserve">16.8106441497803</t>
   </si>
   <si>
     <t xml:space="preserve">16.8287391662598</t>
@@ -2438,25 +2438,25 @@
     <t xml:space="preserve">16.9192161560059</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0639801025391</t>
+    <t xml:space="preserve">17.0639781951904</t>
   </si>
   <si>
     <t xml:space="preserve">16.8468341827393</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9011211395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3173141479492</t>
+    <t xml:space="preserve">16.901123046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3173160552979</t>
   </si>
   <si>
     <t xml:space="preserve">17.2087440490723</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2268371582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.366849899292</t>
+    <t xml:space="preserve">17.2268390655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3668479919434</t>
   </si>
   <si>
     <t xml:space="preserve">18.4573268890381</t>
@@ -2465,7 +2465,7 @@
     <t xml:space="preserve">18.6382808685303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7287559509277</t>
+    <t xml:space="preserve">18.7287578582764</t>
   </si>
   <si>
     <t xml:space="preserve">18.9549503326416</t>
@@ -2480,7 +2480,7 @@
     <t xml:space="preserve">19.678768157959</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5430488586426</t>
+    <t xml:space="preserve">19.5430526733398</t>
   </si>
   <si>
     <t xml:space="preserve">19.0454254150391</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">18.3216094970703</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2311344146729</t>
+    <t xml:space="preserve">18.2311325073242</t>
   </si>
   <si>
     <t xml:space="preserve">19.0906658172607</t>
@@ -2504,7 +2504,7 @@
     <t xml:space="preserve">18.6835174560547</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0954189300537</t>
+    <t xml:space="preserve">18.0954170227051</t>
   </si>
   <si>
     <t xml:space="preserve">18.004940032959</t>
@@ -2513,16 +2513,16 @@
     <t xml:space="preserve">17.570650100708</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8239860534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.643030166626</t>
+    <t xml:space="preserve">17.8239898681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6430320739746</t>
   </si>
   <si>
     <t xml:space="preserve">17.8058910369873</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2716159820557</t>
+    <t xml:space="preserve">19.2716178894043</t>
   </si>
   <si>
     <t xml:space="preserve">19.1811428070068</t>
@@ -2531,28 +2531,28 @@
     <t xml:space="preserve">20.2668685913086</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4930591583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9906845092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5835380554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3573436737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9049606323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7692451477051</t>
+    <t xml:space="preserve">20.4930610656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.990686416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5835361480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3573455810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9049587249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7692432403564</t>
   </si>
   <si>
     <t xml:space="preserve">20.7192516326904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9954395294189</t>
+    <t xml:space="preserve">19.9954357147217</t>
   </si>
   <si>
     <t xml:space="preserve">19.2263813018799</t>
@@ -2564,13 +2564,13 @@
     <t xml:space="preserve">19.4073352813721</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6249351501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7877941131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4978103637695</t>
+    <t xml:space="preserve">17.6249370574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7877922058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4978141784668</t>
   </si>
   <si>
     <t xml:space="preserve">20.0859146118164</t>
@@ -2582,13 +2582,13 @@
     <t xml:space="preserve">19.8597221374512</t>
   </si>
   <si>
-    <t xml:space="preserve">20.674015045166</t>
+    <t xml:space="preserve">20.6740131378174</t>
   </si>
   <si>
     <t xml:space="preserve">21.0359210968018</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8097286224365</t>
+    <t xml:space="preserve">20.8097324371338</t>
   </si>
   <si>
     <t xml:space="preserve">20.6287746429443</t>
@@ -2600,13 +2600,13 @@
     <t xml:space="preserve">20.4478225708008</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8821105957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2802085876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3344993591309</t>
+    <t xml:space="preserve">20.8821125030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2802104949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3344974517822</t>
   </si>
   <si>
     <t xml:space="preserve">21.5878353118896</t>
@@ -2615,10 +2615,10 @@
     <t xml:space="preserve">21.6602172851562</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1668872833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.619270324707</t>
+    <t xml:space="preserve">22.1668891906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6192722320557</t>
   </si>
   <si>
     <t xml:space="preserve">22.8726081848145</t>
@@ -2627,16 +2627,16 @@
     <t xml:space="preserve">23.9040470123291</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7821311950684</t>
+    <t xml:space="preserve">22.7821292877197</t>
   </si>
   <si>
     <t xml:space="preserve">21.8592643737793</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0040283203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2573623657227</t>
+    <t xml:space="preserve">22.0040264129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2573642730713</t>
   </si>
   <si>
     <t xml:space="preserve">22.4745101928711</t>
@@ -2645,22 +2645,22 @@
     <t xml:space="preserve">22.1126003265381</t>
   </si>
   <si>
-    <t xml:space="preserve">22.058313369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6011753082275</t>
+    <t xml:space="preserve">22.0583114624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6011772155762</t>
   </si>
   <si>
     <t xml:space="preserve">22.6373672485352</t>
   </si>
   <si>
-    <t xml:space="preserve">22.420223236084</t>
+    <t xml:space="preserve">22.4202213287354</t>
   </si>
   <si>
     <t xml:space="preserve">22.4021263122559</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3525943756104</t>
+    <t xml:space="preserve">21.3525924682617</t>
   </si>
   <si>
     <t xml:space="preserve">21.2621154785156</t>
@@ -2669,10 +2669,10 @@
     <t xml:space="preserve">22.0945053100586</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5830783843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0354671478271</t>
+    <t xml:space="preserve">22.5830821990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0354652404785</t>
   </si>
   <si>
     <t xml:space="preserve">23.0173721313477</t>
@@ -2681,28 +2681,28 @@
     <t xml:space="preserve">23.3611831665039</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2707061767578</t>
+    <t xml:space="preserve">23.2707042694092</t>
   </si>
   <si>
     <t xml:space="preserve">25.0440578460693</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7726249694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9716777801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0621547698975</t>
+    <t xml:space="preserve">24.7726230621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9716758728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0621528625488</t>
   </si>
   <si>
     <t xml:space="preserve">25.9126358032227</t>
   </si>
   <si>
-    <t xml:space="preserve">26.238353729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6765747070312</t>
+    <t xml:space="preserve">26.2383556365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6765727996826</t>
   </si>
   <si>
     <t xml:space="preserve">26.7130928039551</t>
@@ -2711,7 +2711,7 @@
     <t xml:space="preserve">26.5852794647217</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6583156585693</t>
+    <t xml:space="preserve">26.6583137512207</t>
   </si>
   <si>
     <t xml:space="preserve">26.8226451873779</t>
@@ -2726,13 +2726,13 @@
     <t xml:space="preserve">27.6260471343994</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0642642974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2833766937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8171405792236</t>
+    <t xml:space="preserve">28.064266204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.283374786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8171424865723</t>
   </si>
   <si>
     <t xml:space="preserve">29.5980319976807</t>
@@ -2744,10 +2744,10 @@
     <t xml:space="preserve">30.1275482177734</t>
   </si>
   <si>
-    <t xml:space="preserve">29.652811050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1092872619629</t>
+    <t xml:space="preserve">29.6528091430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1092891693115</t>
   </si>
   <si>
     <t xml:space="preserve">29.9632148742676</t>
@@ -2756,34 +2756,34 @@
     <t xml:space="preserve">30.4014320373535</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2188396453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2961292266846</t>
+    <t xml:space="preserve">30.2188415527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2961311340332</t>
   </si>
   <si>
     <t xml:space="preserve">30.8213920593262</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1683216094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2371025085449</t>
+    <t xml:space="preserve">31.1683158874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2370986938477</t>
   </si>
   <si>
     <t xml:space="preserve">29.4154434204102</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8536605834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1780700683594</t>
+    <t xml:space="preserve">29.8536624908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.178071975708</t>
   </si>
   <si>
     <t xml:space="preserve">30.1458072662354</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7075881958008</t>
+    <t xml:space="preserve">29.7075862884521</t>
   </si>
   <si>
     <t xml:space="preserve">30.0545101165771</t>
@@ -2795,10 +2795,10 @@
     <t xml:space="preserve">34.5462532043457</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0532531738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0855293273926</t>
+    <t xml:space="preserve">34.0532608032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0855255126953</t>
   </si>
   <si>
     <t xml:space="preserve">33.7245903015137</t>
@@ -2807,16 +2807,16 @@
     <t xml:space="preserve">33.6880760192871</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5785179138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4872245788574</t>
+    <t xml:space="preserve">33.5785217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4872283935547</t>
   </si>
   <si>
     <t xml:space="preserve">33.7976303100586</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1403007507324</t>
+    <t xml:space="preserve">33.1402969360352</t>
   </si>
   <si>
     <t xml:space="preserve">33.2863731384277</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">32.2273445129395</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8846778869629</t>
+    <t xml:space="preserve">32.8846740722656</t>
   </si>
   <si>
     <t xml:space="preserve">32.7568626403809</t>
@@ -2834,7 +2834,7 @@
     <t xml:space="preserve">32.6473045349121</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0307464599609</t>
+    <t xml:space="preserve">33.0307502746582</t>
   </si>
   <si>
     <t xml:space="preserve">32.7751235961914</t>
@@ -2849,28 +2849,28 @@
     <t xml:space="preserve">34.692325592041</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6052780151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2401008605957</t>
+    <t xml:space="preserve">35.605281829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2400970458984</t>
   </si>
   <si>
     <t xml:space="preserve">35.8791694641113</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4774742126465</t>
+    <t xml:space="preserve">35.4774703979492</t>
   </si>
   <si>
     <t xml:space="preserve">35.0940246582031</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5870246887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7878723144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0434989929199</t>
+    <t xml:space="preserve">35.5870208740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7878761291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0435028076172</t>
   </si>
   <si>
     <t xml:space="preserve">36.8469047546387</t>
@@ -2879,10 +2879,10 @@
     <t xml:space="preserve">38.9101829528809</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4354476928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4944763183594</t>
+    <t xml:space="preserve">38.4354438781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4944725036621</t>
   </si>
   <si>
     <t xml:space="preserve">39.3849220275879</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">39.2205848693848</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1292915344238</t>
+    <t xml:space="preserve">39.1292953491211</t>
   </si>
   <si>
     <t xml:space="preserve">38.1980781555176</t>
@@ -2903,82 +2903,82 @@
     <t xml:space="preserve">37.2486038208008</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0660133361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2668609619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7008285522461</t>
+    <t xml:space="preserve">37.0660095214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2668647766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7008323669434</t>
   </si>
   <si>
     <t xml:space="preserve">37.2120819091797</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5590057373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0154838562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6503105163574</t>
+    <t xml:space="preserve">37.559009552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0154876708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6503028869629</t>
   </si>
   <si>
     <t xml:space="preserve">35.6235427856445</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2316017150879</t>
+    <t xml:space="preserve">33.2315979003906</t>
   </si>
   <si>
     <t xml:space="preserve">32.9942283630371</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3594093322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0490112304688</t>
+    <t xml:space="preserve">33.3594131469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0490074157715</t>
   </si>
   <si>
     <t xml:space="preserve">34.7836227416992</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3819236755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.893180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.957706451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.63330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.513988494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4817237854004</t>
+    <t xml:space="preserve">34.3819198608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8931770324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9577102661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6332969665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5139923095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4817161560059</t>
   </si>
   <si>
     <t xml:space="preserve">36.3173866271973</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6095352172852</t>
+    <t xml:space="preserve">36.6095314025879</t>
   </si>
   <si>
     <t xml:space="preserve">37.7781181335449</t>
   </si>
   <si>
-    <t xml:space="preserve">38.271110534668</t>
+    <t xml:space="preserve">38.2711143493652</t>
   </si>
   <si>
     <t xml:space="preserve">39.2023277282715</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7190895080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8426475524902</t>
+    <t xml:space="preserve">36.7190933227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8426513671875</t>
   </si>
   <si>
     <t xml:space="preserve">34.9662132263184</t>
@@ -2990,25 +2990,25 @@
     <t xml:space="preserve">35.4409523010254</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8876762390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5267448425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8006324768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6685600280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4226951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.258358001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.911434173584</t>
+    <t xml:space="preserve">37.8876724243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.526741027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8006286621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6685638427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4226913452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2583618164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9114418029785</t>
   </si>
   <si>
     <t xml:space="preserve">34.3636627197266</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">35.3313980102539</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2175941467285</t>
+    <t xml:space="preserve">34.2175903320312</t>
   </si>
   <si>
     <t xml:space="preserve">33.9071846008301</t>
@@ -3044,13 +3044,13 @@
     <t xml:space="preserve">33.1950798034668</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6150360107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9254455566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9437026977539</t>
+    <t xml:space="preserve">33.6150398254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9254493713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9437065124512</t>
   </si>
   <si>
     <t xml:space="preserve">34.6192893981934</t>
@@ -3062,10 +3062,10 @@
     <t xml:space="preserve">34.7288475036621</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0027351379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8384017944336</t>
+    <t xml:space="preserve">35.0027313232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8383979797363</t>
   </si>
   <si>
     <t xml:space="preserve">34.8749160766602</t>
@@ -3074,13 +3074,13 @@
     <t xml:space="preserve">32.5377502441406</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1725654602051</t>
+    <t xml:space="preserve">32.1725730895996</t>
   </si>
   <si>
     <t xml:space="preserve">32.1360511779785</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4519577026367</t>
+    <t xml:space="preserve">29.4519596099854</t>
   </si>
   <si>
     <t xml:space="preserve">29.8901805877686</t>
@@ -3089,28 +3089,28 @@
     <t xml:space="preserve">30.1640663146973</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4294509887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1007843017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6808261871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9954833984375</t>
+    <t xml:space="preserve">28.4294490814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1007881164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6808223724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9954795837402</t>
   </si>
   <si>
     <t xml:space="preserve">29.2693691253662</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6850776672363</t>
+    <t xml:space="preserve">28.6850757598877</t>
   </si>
   <si>
     <t xml:space="preserve">26.9687194824219</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8956832885742</t>
+    <t xml:space="preserve">26.8956813812256</t>
   </si>
   <si>
     <t xml:space="preserve">27.845157623291</t>
@@ -3122,7 +3122,7 @@
     <t xml:space="preserve">28.6668167114258</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1232948303223</t>
+    <t xml:space="preserve">29.1232967376709</t>
   </si>
   <si>
     <t xml:space="preserve">28.9224452972412</t>
@@ -3140,13 +3140,13 @@
     <t xml:space="preserve">25.5445079803467</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7496109008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7861289978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5670185089111</t>
+    <t xml:space="preserve">26.7496089935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7861309051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5670204162598</t>
   </si>
   <si>
     <t xml:space="preserve">27.9547119140625</t>
@@ -3161,16 +3161,16 @@
     <t xml:space="preserve">27.1147937774658</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7313537597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4069385528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9912300109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6948337554932</t>
+    <t xml:space="preserve">26.731351852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4069404602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9912281036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6948318481445</t>
   </si>
   <si>
     <t xml:space="preserve">27.4434566497803</t>
@@ -3182,10 +3182,10 @@
     <t xml:space="preserve">23.5542640686035</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7045860290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0977840423584</t>
+    <t xml:space="preserve">24.7045879364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0977878570557</t>
   </si>
   <si>
     <t xml:space="preserve">22.0022392272949</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">21.7466106414795</t>
   </si>
   <si>
-    <t xml:space="preserve">20.742359161377</t>
+    <t xml:space="preserve">20.7423610687256</t>
   </si>
   <si>
     <t xml:space="preserve">22.6047897338867</t>
@@ -3203,61 +3203,61 @@
     <t xml:space="preserve">21.8744258880615</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5134925842285</t>
+    <t xml:space="preserve">22.5134944915771</t>
   </si>
   <si>
     <t xml:space="preserve">23.1525630950928</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2073421478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5402545928955</t>
+    <t xml:space="preserve">23.2073402404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5402565002441</t>
   </si>
   <si>
     <t xml:space="preserve">24.6680698394775</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8689193725586</t>
+    <t xml:space="preserve">24.8689212799072</t>
   </si>
   <si>
     <t xml:space="preserve">24.4489612579346</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2341041564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5585136413574</t>
+    <t xml:space="preserve">25.2341022491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5585155487061</t>
   </si>
   <si>
     <t xml:space="preserve">24.0290012359619</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1385555267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0472602844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3984355926514</t>
+    <t xml:space="preserve">24.138557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0472621917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3984336853027</t>
   </si>
   <si>
     <t xml:space="preserve">25.4166946411133</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2115917205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0837783813477</t>
+    <t xml:space="preserve">24.2115936279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.083776473999</t>
   </si>
   <si>
     <t xml:space="preserve">23.8098926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3351554870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4221992492676</t>
+    <t xml:space="preserve">23.3351535797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4221973419189</t>
   </si>
   <si>
     <t xml:space="preserve">22.7326049804688</t>
@@ -3272,10 +3272,10 @@
     <t xml:space="preserve">21.9109420776367</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2213497161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8379077911377</t>
+    <t xml:space="preserve">22.2213478088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8379058837891</t>
   </si>
   <si>
     <t xml:space="preserve">22.0935363769531</t>
@@ -3284,13 +3284,13 @@
     <t xml:space="preserve">22.8239002227783</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5457630157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.07102394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9657192230225</t>
+    <t xml:space="preserve">21.5457611083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0710258483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9657211303711</t>
   </si>
   <si>
     <t xml:space="preserve">21.1988353729248</t>
@@ -3308,16 +3308,16 @@
     <t xml:space="preserve">20.0850315093994</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3729267120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8659248352051</t>
+    <t xml:space="preserve">19.3729248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8659229278564</t>
   </si>
   <si>
     <t xml:space="preserve">19.957218170166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9024410247803</t>
+    <t xml:space="preserve">19.902437210083</t>
   </si>
   <si>
     <t xml:space="preserve">20.2493629455566</t>
@@ -3326,16 +3326,16 @@
     <t xml:space="preserve">20.9614677429199</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8519134521484</t>
+    <t xml:space="preserve">20.8519153594971</t>
   </si>
   <si>
     <t xml:space="preserve">20.7241020202637</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0162487030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3449096679688</t>
+    <t xml:space="preserve">21.0162467956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3449115753174</t>
   </si>
   <si>
     <t xml:space="preserve">20.3954372406006</t>
@@ -3347,37 +3347,37 @@
     <t xml:space="preserve">20.6693229675293</t>
   </si>
   <si>
-    <t xml:space="preserve">22.130054473877</t>
+    <t xml:space="preserve">22.1300525665283</t>
   </si>
   <si>
     <t xml:space="preserve">24.1933326721191</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6455593109131</t>
+    <t xml:space="preserve">23.6455574035645</t>
   </si>
   <si>
     <t xml:space="preserve">23.5177459716797</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7368564605713</t>
+    <t xml:space="preserve">23.7368545532227</t>
   </si>
   <si>
     <t xml:space="preserve">23.0533809661865</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9240760803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7393531799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8711585998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.744348526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6914310455322</t>
+    <t xml:space="preserve">22.9240741729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7393550872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8711566925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7443466186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6914291381836</t>
   </si>
   <si>
     <t xml:space="preserve">19.2850399017334</t>
@@ -3395,25 +3395,25 @@
     <t xml:space="preserve">21.3539333343506</t>
   </si>
   <si>
-    <t xml:space="preserve">21.316987991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7603244781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6494884490967</t>
+    <t xml:space="preserve">21.3169898986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7603225708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6494903564453</t>
   </si>
   <si>
     <t xml:space="preserve">21.4278240203857</t>
   </si>
   <si>
-    <t xml:space="preserve">21.55712890625</t>
+    <t xml:space="preserve">21.5571269989014</t>
   </si>
   <si>
     <t xml:space="preserve">21.7972679138184</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5596256256104</t>
+    <t xml:space="preserve">20.559627532959</t>
   </si>
   <si>
     <t xml:space="preserve">20.7812938690186</t>
@@ -3422,25 +3422,25 @@
     <t xml:space="preserve">20.3379592895508</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9130954742432</t>
+    <t xml:space="preserve">19.9130973815918</t>
   </si>
   <si>
     <t xml:space="preserve">20.9475440979004</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0374050140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4992141723633</t>
+    <t xml:space="preserve">22.0374088287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4992122650146</t>
   </si>
   <si>
     <t xml:space="preserve">21.6679611206055</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4647674560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8182392120361</t>
+    <t xml:space="preserve">21.4647655487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8182373046875</t>
   </si>
   <si>
     <t xml:space="preserve">20.1532363891602</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">20.4487915039062</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3908767700195</t>
+    <t xml:space="preserve">21.3908786773682</t>
   </si>
   <si>
     <t xml:space="preserve">21.0029602050781</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">22.3883800506592</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2960205078125</t>
+    <t xml:space="preserve">22.2960186004639</t>
   </si>
   <si>
     <t xml:space="preserve">22.5361576080322</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">21.5017127990723</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7787933349609</t>
+    <t xml:space="preserve">21.7787952423096</t>
   </si>
   <si>
     <t xml:space="preserve">21.7233791351318</t>
@@ -3491,22 +3491,22 @@
     <t xml:space="preserve">21.6864337921143</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8896312713623</t>
+    <t xml:space="preserve">21.889627456665</t>
   </si>
   <si>
     <t xml:space="preserve">21.704906463623</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6519889831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0424022674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0054569244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1162929534912</t>
+    <t xml:space="preserve">20.6519870758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0424041748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0054588317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1162910461426</t>
   </si>
   <si>
     <t xml:space="preserve">20.0978202819824</t>
@@ -3515,25 +3515,25 @@
     <t xml:space="preserve">19.9500427246094</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7468452453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5436515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8417072296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.472261428833</t>
+    <t xml:space="preserve">19.74684715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5436534881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8417053222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4722595214844</t>
   </si>
   <si>
     <t xml:space="preserve">19.1926784515381</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5830936431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2413558959961</t>
+    <t xml:space="preserve">18.5830955505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2413578033447</t>
   </si>
   <si>
     <t xml:space="preserve">18.0566349029541</t>
@@ -3545,25 +3545,25 @@
     <t xml:space="preserve">17.4562854766846</t>
   </si>
   <si>
-    <t xml:space="preserve">17.622537612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6989250183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5326728820801</t>
+    <t xml:space="preserve">17.6225357055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6989231109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5326747894287</t>
   </si>
   <si>
     <t xml:space="preserve">16.8374652862549</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9852428436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2807998657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0037174224854</t>
+    <t xml:space="preserve">16.9852447509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.280797958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0037155151367</t>
   </si>
   <si>
     <t xml:space="preserve">17.6779537200928</t>
@@ -3575,31 +3575,31 @@
     <t xml:space="preserve">17.8164958953857</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5855922698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5024681091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0683670043945</t>
+    <t xml:space="preserve">17.5855941772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5024700164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0683689117432</t>
   </si>
   <si>
     <t xml:space="preserve">17.234619140625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2530918121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9390621185303</t>
+    <t xml:space="preserve">17.2530937194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9390640258789</t>
   </si>
   <si>
     <t xml:space="preserve">16.8005218505859</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8836460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4285774230957</t>
+    <t xml:space="preserve">16.8836479187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4285793304443</t>
   </si>
   <si>
     <t xml:space="preserve">17.7056617736816</t>
@@ -3611,10 +3611,10 @@
     <t xml:space="preserve">17.7333698272705</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3429565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4697608947754</t>
+    <t xml:space="preserve">18.3429546356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.469762802124</t>
   </si>
   <si>
     <t xml:space="preserve">19.5805969238281</t>
@@ -3641,19 +3641,19 @@
     <t xml:space="preserve">19.0079574584961</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0239315032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8392086029053</t>
+    <t xml:space="preserve">20.0239295959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8392066955566</t>
   </si>
   <si>
     <t xml:space="preserve">20.8736553192139</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9080982208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3329620361328</t>
+    <t xml:space="preserve">21.9081001281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3329639434814</t>
   </si>
   <si>
     <t xml:space="preserve">20.9105987548828</t>
@@ -3665,10 +3665,10 @@
     <t xml:space="preserve">21.3354625701904</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2430992126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9265727996826</t>
+    <t xml:space="preserve">21.2431011199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9265747070312</t>
   </si>
   <si>
     <t xml:space="preserve">21.7418518066406</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">20.3933753967285</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2455978393555</t>
+    <t xml:space="preserve">20.2455997467041</t>
   </si>
   <si>
     <t xml:space="preserve">19.931568145752</t>
@@ -3713,10 +3713,10 @@
     <t xml:space="preserve">22.831714630127</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2750492095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6075496673584</t>
+    <t xml:space="preserve">23.2750511169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6075477600098</t>
   </si>
   <si>
     <t xml:space="preserve">23.3304653167725</t>
@@ -3737,19 +3737,19 @@
     <t xml:space="preserve">23.127269744873</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7553272247314</t>
+    <t xml:space="preserve">23.7553253173828</t>
   </si>
   <si>
     <t xml:space="preserve">23.8846340179443</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4782447814941</t>
+    <t xml:space="preserve">23.4782428741455</t>
   </si>
   <si>
     <t xml:space="preserve">23.1087989807129</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9979629516602</t>
+    <t xml:space="preserve">22.9979648590088</t>
   </si>
   <si>
     <t xml:space="preserve">23.0164375305176</t>
@@ -3767,19 +3767,19 @@
     <t xml:space="preserve">24.1247730255127</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5151882171631</t>
+    <t xml:space="preserve">23.5151863098145</t>
   </si>
   <si>
     <t xml:space="preserve">22.8686580657959</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4597702026367</t>
+    <t xml:space="preserve">23.4597721099854</t>
   </si>
   <si>
     <t xml:space="preserve">22.9056015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8132438659668</t>
+    <t xml:space="preserve">22.8132419586182</t>
   </si>
   <si>
     <t xml:space="preserve">22.6285209655762</t>
@@ -3794,7 +3794,7 @@
     <t xml:space="preserve">22.2036571502686</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0004634857178</t>
+    <t xml:space="preserve">22.0004615783691</t>
   </si>
   <si>
     <t xml:space="preserve">22.0558776855469</t>
@@ -3803,10 +3803,10 @@
     <t xml:space="preserve">22.2590751647949</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8342132568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0928249359131</t>
+    <t xml:space="preserve">21.8342113494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0928230285645</t>
   </si>
   <si>
     <t xml:space="preserve">22.2406005859375</t>
@@ -3815,13 +3815,13 @@
     <t xml:space="preserve">21.2615718841553</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3404560089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.656982421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1187896728516</t>
+    <t xml:space="preserve">19.3404579162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6569843292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1187915802002</t>
   </si>
   <si>
     <t xml:space="preserve">18.5646228790283</t>
@@ -3836,7 +3836,7 @@
     <t xml:space="preserve">18.2690658569336</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5092067718506</t>
+    <t xml:space="preserve">18.509204864502</t>
   </si>
   <si>
     <t xml:space="preserve">18.8232326507568</t>
@@ -3845,7 +3845,7 @@
     <t xml:space="preserve">18.5461502075195</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7123985290527</t>
+    <t xml:space="preserve">18.7124004364014</t>
   </si>
   <si>
     <t xml:space="preserve">18.7308731079102</t>
@@ -3857,19 +3857,19 @@
     <t xml:space="preserve">18.4445514678955</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3614273071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7980251312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5486488342285</t>
+    <t xml:space="preserve">18.3614253997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7980213165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5486469268799</t>
   </si>
   <si>
     <t xml:space="preserve">17.1422576904297</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9483013153076</t>
+    <t xml:space="preserve">16.948299407959</t>
   </si>
   <si>
     <t xml:space="preserve">16.9205894470215</t>
@@ -3878,22 +3878,22 @@
     <t xml:space="preserve">16.8651752471924</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5696201324463</t>
+    <t xml:space="preserve">16.5696182250977</t>
   </si>
   <si>
     <t xml:space="preserve">16.8559379577637</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1145515441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7451057434082</t>
+    <t xml:space="preserve">17.1145496368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7451019287109</t>
   </si>
   <si>
     <t xml:space="preserve">16.9021186828613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8744125366211</t>
+    <t xml:space="preserve">16.8744106292725</t>
   </si>
   <si>
     <t xml:space="preserve">16.7912845611572</t>
@@ -3932,22 +3932,22 @@
     <t xml:space="preserve">16.0062141418457</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0523948669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6896858215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4710865020752</t>
+    <t xml:space="preserve">16.0523929595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6896877288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4710884094238</t>
   </si>
   <si>
     <t xml:space="preserve">16.632661819458</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6611766815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5946426391602</t>
+    <t xml:space="preserve">16.6611747741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5946445465088</t>
   </si>
   <si>
     <t xml:space="preserve">17.2124290466309</t>
@@ -3956,10 +3956,10 @@
     <t xml:space="preserve">17.5830993652344</t>
   </si>
   <si>
-    <t xml:space="preserve">17.944263458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.820707321167</t>
+    <t xml:space="preserve">17.9442653656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8207092285156</t>
   </si>
   <si>
     <t xml:space="preserve">17.8302135467529</t>
@@ -3971,7 +3971,7 @@
     <t xml:space="preserve">16.9938259124756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5661296844482</t>
+    <t xml:space="preserve">16.5661315917969</t>
   </si>
   <si>
     <t xml:space="preserve">16.2809982299805</t>
@@ -3980,13 +3980,13 @@
     <t xml:space="preserve">16.204963684082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.00537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5871801376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7867727279663</t>
+    <t xml:space="preserve">16.0053730010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.58717918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.786771774292</t>
   </si>
   <si>
     <t xml:space="preserve">15.5681705474854</t>
@@ -4004,16 +4004,16 @@
     <t xml:space="preserve">15.3305606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6251974105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4541177749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8723115921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9958667755127</t>
+    <t xml:space="preserve">15.6251983642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4541187286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8723125457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9958686828613</t>
   </si>
   <si>
     <t xml:space="preserve">16.0623989105225</t>
@@ -4022,19 +4022,19 @@
     <t xml:space="preserve">15.7012319564819</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7772674560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8247900009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7487535476685</t>
+    <t xml:space="preserve">15.777268409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8247880935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7487545013428</t>
   </si>
   <si>
     <t xml:space="preserve">15.7392492294312</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9388427734375</t>
+    <t xml:space="preserve">15.9388418197632</t>
   </si>
   <si>
     <t xml:space="preserve">16.1859569549561</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">16.1574420928955</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8913192749023</t>
+    <t xml:space="preserve">15.8913202285767</t>
   </si>
   <si>
     <t xml:space="preserve">16.9177932739258</t>
@@ -4055,13 +4055,13 @@
     <t xml:space="preserve">17.0223407745361</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1649055480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.060359954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6231575012207</t>
+    <t xml:space="preserve">17.1649074554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0603580474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6231555938721</t>
   </si>
   <si>
     <t xml:space="preserve">16.7277050018311</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">16.3000068664551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4996013641357</t>
+    <t xml:space="preserve">16.4995994567871</t>
   </si>
   <si>
     <t xml:space="preserve">16.509105682373</t>
@@ -4103,16 +4103,16 @@
     <t xml:space="preserve">17.4215240478516</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3074722290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2599487304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8628063201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8818140029907</t>
+    <t xml:space="preserve">17.3074703216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2599506378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8628072738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.881814956665</t>
   </si>
   <si>
     <t xml:space="preserve">16.4235649108887</t>
@@ -4124,16 +4124,16 @@
     <t xml:space="preserve">16.1479377746582</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9103288650513</t>
+    <t xml:space="preserve">15.910327911377</t>
   </si>
   <si>
     <t xml:space="preserve">16.2429828643799</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8533020019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8437967300415</t>
+    <t xml:space="preserve">15.8533029556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8437976837158</t>
   </si>
   <si>
     <t xml:space="preserve">14.7793073654175</t>
@@ -4148,10 +4148,10 @@
     <t xml:space="preserve">14.4466543197632</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7222814559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6917285919189</t>
+    <t xml:space="preserve">14.7222805023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6917276382446</t>
   </si>
   <si>
     <t xml:space="preserve">15.4731273651123</t>
@@ -4163,7 +4163,7 @@
     <t xml:space="preserve">15.4921350479126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0929527282715</t>
+    <t xml:space="preserve">15.0929517745972</t>
   </si>
   <si>
     <t xml:space="preserve">15.4446144104004</t>
@@ -4193,7 +4193,7 @@
     <t xml:space="preserve">14.4846715927124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9313774108887</t>
+    <t xml:space="preserve">14.931378364563</t>
   </si>
   <si>
     <t xml:space="preserve">14.9218730926514</t>
@@ -4208,37 +4208,37 @@
     <t xml:space="preserve">14.731785774231</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0074129104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7677631378174</t>
+    <t xml:space="preserve">15.0074119567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7677640914917</t>
   </si>
   <si>
     <t xml:space="preserve">16.1954612731934</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5566253662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.128927230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0528945922852</t>
+    <t xml:space="preserve">16.5566272735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1289291381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0528926849365</t>
   </si>
   <si>
     <t xml:space="preserve">16.3570346832275</t>
   </si>
   <si>
-    <t xml:space="preserve">16.433069229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7467155456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3665390014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3950500488281</t>
+    <t xml:space="preserve">16.4330711364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7467136383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3665370941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3950519561768</t>
   </si>
   <si>
     <t xml:space="preserve">16.4805908203125</t>
@@ -4253,10 +4253,10 @@
     <t xml:space="preserve">16.3285217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6136531829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6991901397705</t>
+    <t xml:space="preserve">16.6136512756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6991920471191</t>
   </si>
   <si>
     <t xml:space="preserve">16.5756359100342</t>
@@ -4265,22 +4265,22 @@
     <t xml:space="preserve">18.5240325927734</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7046165466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6475887298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1988430023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4839744567871</t>
+    <t xml:space="preserve">18.7046146392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.647590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.198844909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4839763641357</t>
   </si>
   <si>
     <t xml:space="preserve">19.5029830932617</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4649639129639</t>
+    <t xml:space="preserve">19.4649658203125</t>
   </si>
   <si>
     <t xml:space="preserve">19.2938861846924</t>
@@ -4289,10 +4289,10 @@
     <t xml:space="preserve">19.1037998199463</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2748794555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0277652740479</t>
+    <t xml:space="preserve">19.2748775482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0277633666992</t>
   </si>
   <si>
     <t xml:space="preserve">18.0868320465088</t>
@@ -4319,16 +4319,16 @@
     <t xml:space="preserve">17.9062480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7541790008545</t>
+    <t xml:space="preserve">17.7541770935059</t>
   </si>
   <si>
     <t xml:space="preserve">18.1818752288818</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9157543182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2103862762451</t>
+    <t xml:space="preserve">17.9157524108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2103881835938</t>
   </si>
   <si>
     <t xml:space="preserve">18.343448638916</t>
@@ -4343,16 +4343,16 @@
     <t xml:space="preserve">18.6570930480957</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5810585021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4289875030518</t>
+    <t xml:space="preserve">18.5810565948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4289894104004</t>
   </si>
   <si>
     <t xml:space="preserve">18.1913795471191</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0488147735596</t>
+    <t xml:space="preserve">18.0488128662109</t>
   </si>
   <si>
     <t xml:space="preserve">18.020299911499</t>
@@ -4370,7 +4370,7 @@
     <t xml:space="preserve">17.9632740020752</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0678215026855</t>
+    <t xml:space="preserve">18.0678234100342</t>
   </si>
   <si>
     <t xml:space="preserve">18.1723709106445</t>
@@ -4400,13 +4400,13 @@
     <t xml:space="preserve">17.8112030029297</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5165672302246</t>
+    <t xml:space="preserve">17.5165691375732</t>
   </si>
   <si>
     <t xml:space="preserve">17.5450801849365</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3169765472412</t>
+    <t xml:space="preserve">17.3169746398926</t>
   </si>
   <si>
     <t xml:space="preserve">17.3264808654785</t>
@@ -4427,10 +4427,10 @@
     <t xml:space="preserve">17.5545845031738</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7636833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8872394561768</t>
+    <t xml:space="preserve">17.7636814117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8872375488281</t>
   </si>
   <si>
     <t xml:space="preserve">18.1533622741699</t>
@@ -4439,19 +4439,19 @@
     <t xml:space="preserve">18.1628665924072</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3549957275391</t>
+    <t xml:space="preserve">17.3549938201904</t>
   </si>
   <si>
     <t xml:space="preserve">17.4690456390381</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4405345916748</t>
+    <t xml:space="preserve">17.4405326843262</t>
   </si>
   <si>
     <t xml:space="preserve">17.1078796386719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0413494110107</t>
+    <t xml:space="preserve">17.0413513183594</t>
   </si>
   <si>
     <t xml:space="preserve">16.9368019104004</t>
@@ -4463,7 +4463,7 @@
     <t xml:space="preserve">16.4615821838379</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3095111846924</t>
+    <t xml:space="preserve">16.309513092041</t>
   </si>
   <si>
     <t xml:space="preserve">17.0033321380615</t>
@@ -4487,7 +4487,7 @@
     <t xml:space="preserve">17.6211185455322</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0107975006104</t>
+    <t xml:space="preserve">18.0107955932617</t>
   </si>
   <si>
     <t xml:space="preserve">17.7826900482178</t>
@@ -4502,7 +4502,7 @@
     <t xml:space="preserve">17.5355777740479</t>
   </si>
   <si>
-    <t xml:space="preserve">18.001293182373</t>
+    <t xml:space="preserve">18.0012912750244</t>
   </si>
   <si>
     <t xml:space="preserve">18.2674140930176</t>
@@ -71285,7 +71285,7 @@
     </row>
     <row r="2524">
       <c r="A2524" s="1" t="n">
-        <v>45993.6910763889</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B2524" t="n">
         <v>36095</v>
@@ -71306,6 +71306,32 @@
         <v>1766</v>
       </c>
       <c r="H2524" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" s="1" t="n">
+        <v>45994.6912847222</v>
+      </c>
+      <c r="B2525" t="n">
+        <v>142714</v>
+      </c>
+      <c r="C2525" t="n">
+        <v>14.9200000762939</v>
+      </c>
+      <c r="D2525" t="n">
+        <v>14.8400001525879</v>
+      </c>
+      <c r="E2525" t="n">
+        <v>14.8699998855591</v>
+      </c>
+      <c r="F2525" t="n">
+        <v>14.8999996185303</v>
+      </c>
+      <c r="G2525" t="s">
+        <v>1765</v>
+      </c>
+      <c r="H2525" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TNXT.MI.xlsx
+++ b/data/TNXT.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63493800163269</t>
+    <t xml:space="preserve">2.63493752479553</t>
   </si>
   <si>
     <t xml:space="preserve">TNXT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65150952339172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59350848197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53550696372986</t>
+    <t xml:space="preserve">2.65150928497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59350872039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53550672531128</t>
   </si>
   <si>
     <t xml:space="preserve">2.52556347846985</t>
@@ -65,34 +65,34 @@
     <t xml:space="preserve">2.48744797706604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47087574005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46921849250793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54047799110413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49739122390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47916221618652</t>
+    <t xml:space="preserve">2.47087550163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46921825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54047846794128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49739146232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47916197776794</t>
   </si>
   <si>
     <t xml:space="preserve">2.44436049461365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39464473724365</t>
+    <t xml:space="preserve">2.39464449882507</t>
   </si>
   <si>
     <t xml:space="preserve">2.34161448478699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36150097846985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55207848548889</t>
+    <t xml:space="preserve">2.36150074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55207872390747</t>
   </si>
   <si>
     <t xml:space="preserve">2.58522248268127</t>
@@ -101,37 +101,37 @@
     <t xml:space="preserve">2.61007976531982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56865096092224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63659477233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68962526321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7343692779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72608351707458</t>
+    <t xml:space="preserve">2.56865048408508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63659453392029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68962550163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73436975479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72608375549316</t>
   </si>
   <si>
     <t xml:space="preserve">2.77579975128174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58025097846985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56202220916748</t>
+    <t xml:space="preserve">2.58025145530701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5620219707489</t>
   </si>
   <si>
     <t xml:space="preserve">2.66808128356934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62830877304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64322376251221</t>
+    <t xml:space="preserve">2.62830901145935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64322352409363</t>
   </si>
   <si>
     <t xml:space="preserve">2.60842251777649</t>
@@ -140,10 +140,10 @@
     <t xml:space="preserve">2.66642427444458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65316724777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62665200233459</t>
+    <t xml:space="preserve">2.65316653251648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62665176391602</t>
   </si>
   <si>
     <t xml:space="preserve">2.69293975830078</t>
@@ -152,67 +152,67 @@
     <t xml:space="preserve">2.82551550865173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81722950935364</t>
+    <t xml:space="preserve">2.81722927093506</t>
   </si>
   <si>
     <t xml:space="preserve">2.90008974075317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8586597442627</t>
+    <t xml:space="preserve">2.85865926742554</t>
   </si>
   <si>
     <t xml:space="preserve">2.89843249320984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88351702690125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87523102760315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86694526672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81888651847839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82054400444031</t>
+    <t xml:space="preserve">2.8835175037384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87523126602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86694550514221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81888675689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82054376602173</t>
   </si>
   <si>
     <t xml:space="preserve">2.85368800163269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79237174987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8570020198822</t>
+    <t xml:space="preserve">2.79237151145935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85700225830078</t>
   </si>
   <si>
     <t xml:space="preserve">2.90671825408936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82883024215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85037326812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90837502479553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96306276321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95797729492188</t>
+    <t xml:space="preserve">2.82882952690125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85037350654602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90837526321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96306324005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9579770565033</t>
   </si>
   <si>
     <t xml:space="preserve">2.88169693946838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89017248153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86474585533142</t>
+    <t xml:space="preserve">2.89017271995544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86474561691284</t>
   </si>
   <si>
     <t xml:space="preserve">2.94950199127197</t>
@@ -221,13 +221,13 @@
     <t xml:space="preserve">2.92407488822937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96645283699036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11901307106018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94272112846375</t>
+    <t xml:space="preserve">2.96645307540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1190128326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94272136688232</t>
   </si>
   <si>
     <t xml:space="preserve">2.94780683517456</t>
@@ -236,16 +236,16 @@
     <t xml:space="preserve">2.8833920955658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8732213973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85966038703918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03256273269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07037305831909</t>
+    <t xml:space="preserve">2.87322163581848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85966062545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03256297111511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07037353515625</t>
   </si>
   <si>
     <t xml:space="preserve">3.06866335868835</t>
@@ -257,55 +257,55 @@
     <t xml:space="preserve">2.99340057373047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98484802246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93524312973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98313736915588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92498016357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92326927185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9677426815033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0361635684967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05840015411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05497884750366</t>
+    <t xml:space="preserve">2.98484826087952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93524289131165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9831371307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9249804019928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92326951026917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96774291992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03616333007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05839991569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05497908592224</t>
   </si>
   <si>
     <t xml:space="preserve">3.08747887611389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13879418373108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12853097915649</t>
+    <t xml:space="preserve">3.13879442214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12853121757507</t>
   </si>
   <si>
     <t xml:space="preserve">3.19010949134827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15589928627014</t>
+    <t xml:space="preserve">3.15589952468872</t>
   </si>
   <si>
     <t xml:space="preserve">3.12339973449707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12510991096497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14734697341919</t>
+    <t xml:space="preserve">3.12511014938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14734673500061</t>
   </si>
   <si>
     <t xml:space="preserve">3.16445183753967</t>
@@ -314,28 +314,28 @@
     <t xml:space="preserve">3.16616249084473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24142527580261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30129313468933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38681864738464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48431801795959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52708148956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62629055976868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63655424118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64510703086853</t>
+    <t xml:space="preserve">3.24142503738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30129337310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38681888580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48431754112244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52708125114441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62629008293152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63655400276184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64510631561279</t>
   </si>
   <si>
     <t xml:space="preserve">3.74602723121643</t>
@@ -344,22 +344,22 @@
     <t xml:space="preserve">3.67760682106018</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71181678771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63484358787537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51681804656982</t>
+    <t xml:space="preserve">3.71181702613831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63484334945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5168182849884</t>
   </si>
   <si>
     <t xml:space="preserve">3.50484442710876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49458122253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50655484199524</t>
+    <t xml:space="preserve">3.49458169937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5065553188324</t>
   </si>
   <si>
     <t xml:space="preserve">3.48089742660522</t>
@@ -371,37 +371,37 @@
     <t xml:space="preserve">3.35602974891663</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60063362121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64681720733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69471192359924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69984316825867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67589592933655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66563272476196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59721231460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63313317298889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57497501373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66050171852112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68615889549255</t>
+    <t xml:space="preserve">3.60063338279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64681696891785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69471096992493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69984364509583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67589545249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66563248634338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59721159934998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63313269615173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57497525215149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66050148010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68615865707397</t>
   </si>
   <si>
     <t xml:space="preserve">3.7152373790741</t>
@@ -410,13 +410,13 @@
     <t xml:space="preserve">3.7374746799469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71010613441467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69129037857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68958020210266</t>
+    <t xml:space="preserve">3.71010565757751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69129061698914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68957996368408</t>
   </si>
   <si>
     <t xml:space="preserve">3.73234272003174</t>
@@ -425,43 +425,43 @@
     <t xml:space="preserve">3.72036910057068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76313185691833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77168464660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62115955352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64168572425842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70326375961304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7973427772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75457954406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90852642059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76655340194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72892141342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66734337806702</t>
+    <t xml:space="preserve">3.76313233375549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77168440818787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62115979194641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64168548583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7032642364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79734230041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75457882881165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90852618217468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76655268669128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72892189025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6673436164856</t>
   </si>
   <si>
     <t xml:space="preserve">3.50997614860535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49800252914429</t>
+    <t xml:space="preserve">3.49800229072571</t>
   </si>
   <si>
     <t xml:space="preserve">3.48944973945618</t>
@@ -473,61 +473,61 @@
     <t xml:space="preserve">3.40392422676086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43642377853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53221249580383</t>
+    <t xml:space="preserve">3.43642401695251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53221273422241</t>
   </si>
   <si>
     <t xml:space="preserve">3.51852822303772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46037125587463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50142312049866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53563332557678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55616021156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6433961391449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72550082206726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84865760803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82984209060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8315532207489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87089395523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84523677825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8743155002594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86405277252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85720992088318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82471084594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90681529045105</t>
+    <t xml:space="preserve">3.46037101745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50142335891724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53563380241394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55615973472595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64339590072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72550058364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84865736961365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82984185218811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83155298233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87089419364929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84523630142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87431597709656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86405253410339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85721063613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82471060752869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90681505203247</t>
   </si>
   <si>
     <t xml:space="preserve">4.00260400772095</t>
@@ -539,16 +539,16 @@
     <t xml:space="preserve">4.11378717422485</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00773572921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05220937728882</t>
+    <t xml:space="preserve">4.00773620605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05220890045166</t>
   </si>
   <si>
     <t xml:space="preserve">4.08128833770752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0060248374939</t>
+    <t xml:space="preserve">4.00602531433105</t>
   </si>
   <si>
     <t xml:space="preserve">4.09839344024658</t>
@@ -560,85 +560,85 @@
     <t xml:space="preserve">4.01115655899048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99576210975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0351037979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06247234344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13773441314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12233972549438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14799833297729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18905067443848</t>
+    <t xml:space="preserve">3.99576187133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03510427474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06247186660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13773488998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1223406791687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14799737930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18904972076416</t>
   </si>
   <si>
     <t xml:space="preserve">4.25918102264404</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22839164733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20615577697754</t>
+    <t xml:space="preserve">4.22839212417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20615530014038</t>
   </si>
   <si>
     <t xml:space="preserve">4.02142000198364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99405121803284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01799869537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02655172348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07615566253662</t>
+    <t xml:space="preserve">3.99405169487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01799821853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02655124664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07615613937378</t>
   </si>
   <si>
     <t xml:space="preserve">4.12747192382812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11891889572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10523414611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09668254852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10181379318237</t>
+    <t xml:space="preserve">4.11891937255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10523557662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09668207168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10181427001953</t>
   </si>
   <si>
     <t xml:space="preserve">4.07102489471436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09497213363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13089275360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21641874313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52431106567383</t>
+    <t xml:space="preserve">4.09497165679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13089323043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21641826629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52431058883667</t>
   </si>
   <si>
     <t xml:space="preserve">4.54996919631958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53713989257812</t>
+    <t xml:space="preserve">4.53713941574097</t>
   </si>
   <si>
     <t xml:space="preserve">4.46444272994995</t>
@@ -647,13 +647,13 @@
     <t xml:space="preserve">4.5029296875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56707382202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62266635894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63549423217773</t>
+    <t xml:space="preserve">4.56707429885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6226658821106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63549470901489</t>
   </si>
   <si>
     <t xml:space="preserve">4.58417940139771</t>
@@ -668,13 +668,13 @@
     <t xml:space="preserve">4.61838912963867</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53286409378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55852174758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48154783248901</t>
+    <t xml:space="preserve">4.53286361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55852127075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48154735565186</t>
   </si>
   <si>
     <t xml:space="preserve">4.51575899124146</t>
@@ -686,31 +686,31 @@
     <t xml:space="preserve">4.51148223876953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63121843338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78516435623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75950717926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78944063186646</t>
+    <t xml:space="preserve">4.63121747970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78516483306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75950765609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7894401550293</t>
   </si>
   <si>
     <t xml:space="preserve">4.7338490486145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77233600616455</t>
+    <t xml:space="preserve">4.77233552932739</t>
   </si>
   <si>
     <t xml:space="preserve">4.76378345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65687561035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69536256790161</t>
+    <t xml:space="preserve">4.65687656402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69536209106445</t>
   </si>
   <si>
     <t xml:space="preserve">4.8279275894165</t>
@@ -728,13 +728,13 @@
     <t xml:space="preserve">4.98614931106567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04174137115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02035999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0716757774353</t>
+    <t xml:space="preserve">5.04174184799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02036046981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07167530059814</t>
   </si>
   <si>
     <t xml:space="preserve">5.08022880554199</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">5.09305715560913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06050682067871</t>
+    <t xml:space="preserve">5.06050634384155</t>
   </si>
   <si>
     <t xml:space="preserve">4.91728496551514</t>
@@ -758,16 +758,16 @@
     <t xml:space="preserve">4.92596530914307</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90426445007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82180404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73500299453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72198247909546</t>
+    <t xml:space="preserve">4.9042649269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8218035697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7350025177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7219820022583</t>
   </si>
   <si>
     <t xml:space="preserve">4.59178066253662</t>
@@ -776,40 +776,40 @@
     <t xml:space="preserve">4.64386129379272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73066186904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66556119918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6525411605835</t>
+    <t xml:space="preserve">4.73066234588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66556167602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65254163742065</t>
   </si>
   <si>
     <t xml:space="preserve">4.60914087295532</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65688133239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54837989807129</t>
+    <t xml:space="preserve">4.65688180923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54837942123413</t>
   </si>
   <si>
     <t xml:space="preserve">4.53536033630371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47025966644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59612083435059</t>
+    <t xml:space="preserve">4.47025918960571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59612131118774</t>
   </si>
   <si>
     <t xml:space="preserve">4.47459936141968</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48761987686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46157836914062</t>
+    <t xml:space="preserve">4.48761940002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46157932281494</t>
   </si>
   <si>
     <t xml:space="preserve">4.4138388633728</t>
@@ -818,22 +818,22 @@
     <t xml:space="preserve">4.38779735565186</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39213800430298</t>
+    <t xml:space="preserve">4.39213705062866</t>
   </si>
   <si>
     <t xml:space="preserve">4.40949821472168</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55706024169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52233982086182</t>
+    <t xml:space="preserve">4.55705976486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52233934402466</t>
   </si>
   <si>
     <t xml:space="preserve">4.57008028030396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53970050811768</t>
+    <t xml:space="preserve">4.53969955444336</t>
   </si>
   <si>
     <t xml:space="preserve">4.47893905639648</t>
@@ -842,31 +842,31 @@
     <t xml:space="preserve">4.43553876876831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4225172996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4311990737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45289945602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51365995407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68726253509521</t>
+    <t xml:space="preserve">4.42251777648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43119859695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45289897918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51365947723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6872615814209</t>
   </si>
   <si>
     <t xml:space="preserve">4.60046100616455</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63952112197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56139993667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58744096755981</t>
+    <t xml:space="preserve">4.6395206451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56140089035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58744049072266</t>
   </si>
   <si>
     <t xml:space="preserve">4.61782121658325</t>
@@ -875,19 +875,19 @@
     <t xml:space="preserve">4.64820146560669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60480117797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58309984207153</t>
+    <t xml:space="preserve">4.6048002243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58310079574585</t>
   </si>
   <si>
     <t xml:space="preserve">4.49629926681519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50497961044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42685794830322</t>
+    <t xml:space="preserve">4.50498008728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42685890197754</t>
   </si>
   <si>
     <t xml:space="preserve">4.49195909500122</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">4.51799964904785</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80878353118896</t>
+    <t xml:space="preserve">4.80878400802612</t>
   </si>
   <si>
     <t xml:space="preserve">4.77840328216553</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">4.84784412384033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8348240852356</t>
+    <t xml:space="preserve">4.83482360839844</t>
   </si>
   <si>
     <t xml:space="preserve">4.74368286132812</t>
@@ -917,31 +917,31 @@
     <t xml:space="preserve">4.71330213546753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70462274551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72632265090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69594192504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76972341537476</t>
+    <t xml:space="preserve">4.70462226867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72632312774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69594240188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76972246170044</t>
   </si>
   <si>
     <t xml:space="preserve">4.84350395202637</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87822389602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87388372421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97370529174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97804641723633</t>
+    <t xml:space="preserve">4.87822484970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87388467788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97370576858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97804594039917</t>
   </si>
   <si>
     <t xml:space="preserve">5.00842618942261</t>
@@ -950,43 +950,43 @@
     <t xml:space="preserve">5.07786750793457</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04314661026001</t>
+    <t xml:space="preserve">5.04314708709717</t>
   </si>
   <si>
     <t xml:space="preserve">5.14730787277222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86086416244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.869544506073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96502494812012</t>
+    <t xml:space="preserve">4.86086368560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86954402923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96502542495728</t>
   </si>
   <si>
     <t xml:space="preserve">4.90860509872437</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99974679946899</t>
+    <t xml:space="preserve">4.99974632263184</t>
   </si>
   <si>
     <t xml:space="preserve">4.99106597900391</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15598821640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12994766235352</t>
+    <t xml:space="preserve">5.1559886932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12994718551636</t>
   </si>
   <si>
     <t xml:space="preserve">5.29486989974976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41639137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48583221435547</t>
+    <t xml:space="preserve">5.41639184951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48583316802979</t>
   </si>
   <si>
     <t xml:space="preserve">5.43375205993652</t>
@@ -1010,16 +1010,16 @@
     <t xml:space="preserve">5.37299108505249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33827066421509</t>
+    <t xml:space="preserve">5.33827018737793</t>
   </si>
   <si>
     <t xml:space="preserve">5.20806884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16466808319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26448965072632</t>
+    <t xml:space="preserve">5.16466856002808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26449012756348</t>
   </si>
   <si>
     <t xml:space="preserve">5.25146961212158</t>
@@ -1034,58 +1034,58 @@
     <t xml:space="preserve">5.20372867584229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19504833221436</t>
+    <t xml:space="preserve">5.19504880905151</t>
   </si>
   <si>
     <t xml:space="preserve">5.16900825500488</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18202829360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19938850402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22542858123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42507123947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61603403091431</t>
+    <t xml:space="preserve">5.1820273399353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19938898086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22542905807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42507171630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61603450775146</t>
   </si>
   <si>
     <t xml:space="preserve">5.72887563705444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7115159034729</t>
+    <t xml:space="preserve">5.71151542663574</t>
   </si>
   <si>
     <t xml:space="preserve">5.78963661193848</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82435750961304</t>
+    <t xml:space="preserve">5.82435655593872</t>
   </si>
   <si>
     <t xml:space="preserve">5.87643766403198</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88511848449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93719816207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85907697677612</t>
+    <t xml:space="preserve">5.88511753082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93719911575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85907745361328</t>
   </si>
   <si>
     <t xml:space="preserve">5.80699682235718</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92851781845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97191905975342</t>
+    <t xml:space="preserve">5.92851829528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97191858291626</t>
   </si>
   <si>
     <t xml:space="preserve">5.95455884933472</t>
@@ -1094,49 +1094,49 @@
     <t xml:space="preserve">6.03267955780029</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1715612411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28440237045288</t>
+    <t xml:space="preserve">6.17156171798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2844033241272</t>
   </si>
   <si>
     <t xml:space="preserve">6.01531887054443</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02399969100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21496295928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14552164077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40592432022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07607984542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98927879333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04135990142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22364187240601</t>
+    <t xml:space="preserve">6.02399921417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21496200561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14552068710327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40592527389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07608032226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98927927017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04135942459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22364282608032</t>
   </si>
   <si>
     <t xml:space="preserve">6.13684129714966</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19760227203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15420150756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05003929138184</t>
+    <t xml:space="preserve">6.19760131835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1542010307312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05004024505615</t>
   </si>
   <si>
     <t xml:space="preserve">5.89379787445068</t>
@@ -1145,13 +1145,13 @@
     <t xml:space="preserve">5.90247821807861</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70283508300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50319290161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58131408691406</t>
+    <t xml:space="preserve">5.70283555984497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50319242477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5813136100769</t>
   </si>
   <si>
     <t xml:space="preserve">5.72019529342651</t>
@@ -1160,10 +1160,10 @@
     <t xml:space="preserve">5.76359605789185</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91983842849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99795913696289</t>
+    <t xml:space="preserve">5.91983795166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99795961380005</t>
   </si>
   <si>
     <t xml:space="preserve">5.83303689956665</t>
@@ -1175,16 +1175,16 @@
     <t xml:space="preserve">5.65943431854248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5118727684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54659366607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58999395370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52055311203003</t>
+    <t xml:space="preserve">5.51187229156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5465931892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58999443054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52055358886719</t>
   </si>
   <si>
     <t xml:space="preserve">5.38167095184326</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">5.44243192672729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46847248077393</t>
+    <t xml:space="preserve">5.46847295761108</t>
   </si>
   <si>
     <t xml:space="preserve">5.67679500579834</t>
@@ -1202,16 +1202,16 @@
     <t xml:space="preserve">5.64207458496094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55527353286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53791284561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57263374328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5292329788208</t>
+    <t xml:space="preserve">5.55527400970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53791332244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57263326644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52923250198364</t>
   </si>
   <si>
     <t xml:space="preserve">5.39903163909912</t>
@@ -1220,16 +1220,16 @@
     <t xml:space="preserve">5.39035177230835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45111227035522</t>
+    <t xml:space="preserve">5.45111179351807</t>
   </si>
   <si>
     <t xml:space="preserve">6.09344053268433</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81567668914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77227640151978</t>
+    <t xml:space="preserve">5.81567716598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77227592468262</t>
   </si>
   <si>
     <t xml:space="preserve">5.73755598068237</t>
@@ -1238,40 +1238,40 @@
     <t xml:space="preserve">5.40771102905273</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24278926849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0691876411438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98238563537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07618761062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15619850158691</t>
+    <t xml:space="preserve">5.24278879165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06918716430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98238515853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07618808746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1561975479126</t>
   </si>
   <si>
     <t xml:space="preserve">5.08507776260376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24509763717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11174869537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13841819763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20953845977783</t>
+    <t xml:space="preserve">5.24509811401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11174774169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13841772079468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20953798294067</t>
   </si>
   <si>
     <t xml:space="preserve">5.06729793548584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0584077835083</t>
+    <t xml:space="preserve">5.05840826034546</t>
   </si>
   <si>
     <t xml:space="preserve">5.04062795639038</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">5.04951810836792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94283771514893</t>
+    <t xml:space="preserve">4.94283819198608</t>
   </si>
   <si>
     <t xml:space="preserve">4.77392816543579</t>
@@ -1289,37 +1289,37 @@
     <t xml:space="preserve">4.90727806091309</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76503753662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92505788803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88949775695801</t>
+    <t xml:space="preserve">4.76503801345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92505836486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88949871063232</t>
   </si>
   <si>
     <t xml:space="preserve">5.02284812927246</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97839832305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91616821289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95172834396362</t>
+    <t xml:space="preserve">4.97839736938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91616773605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95172786712646</t>
   </si>
   <si>
     <t xml:space="preserve">4.93394804000854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89838886260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80948781967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78281831741333</t>
+    <t xml:space="preserve">4.89838838577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80948829650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78281784057617</t>
   </si>
   <si>
     <t xml:space="preserve">4.75614786148071</t>
@@ -1334,28 +1334,28 @@
     <t xml:space="preserve">4.960618019104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20064735412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21842765808105</t>
+    <t xml:space="preserve">5.20064830780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21842813491821</t>
   </si>
   <si>
     <t xml:space="preserve">5.27176761627197</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33399724960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23620796203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18286800384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01395750045776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99617767333984</t>
+    <t xml:space="preserve">5.33399772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23620748519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18286752700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01395797729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.996178150177</t>
   </si>
   <si>
     <t xml:space="preserve">5.00506830215454</t>
@@ -1364,7 +1364,7 @@
     <t xml:space="preserve">5.37844800949097</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47623825073242</t>
+    <t xml:space="preserve">5.47623729705811</t>
   </si>
   <si>
     <t xml:space="preserve">5.56513786315918</t>
@@ -1373,10 +1373,10 @@
     <t xml:space="preserve">5.6807074546814</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65403747558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63625764846802</t>
+    <t xml:space="preserve">5.65403842926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63625717163086</t>
   </si>
   <si>
     <t xml:space="preserve">5.55624771118164</t>
@@ -1385,13 +1385,13 @@
     <t xml:space="preserve">5.68959808349609</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96518754959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89406776428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77849721908569</t>
+    <t xml:space="preserve">5.96518707275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89406728744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77849769592285</t>
   </si>
   <si>
     <t xml:space="preserve">5.84072780609131</t>
@@ -1400,10 +1400,10 @@
     <t xml:space="preserve">5.76071739196777</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92073726654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83183765411377</t>
+    <t xml:space="preserve">5.92073774337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83183717727661</t>
   </si>
   <si>
     <t xml:space="preserve">5.44956827163696</t>
@@ -1412,10 +1412,10 @@
     <t xml:space="preserve">5.5829176902771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43178796768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36955785751343</t>
+    <t xml:space="preserve">5.43178749084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36955738067627</t>
   </si>
   <si>
     <t xml:space="preserve">5.60958766937256</t>
@@ -1427,40 +1427,40 @@
     <t xml:space="preserve">5.78738784790039</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52068853378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49401807785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57402801513672</t>
+    <t xml:space="preserve">5.5206880569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49401760101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57402753829956</t>
   </si>
   <si>
     <t xml:space="preserve">5.59180736541748</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64514780044556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71626710891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73404788970947</t>
+    <t xml:space="preserve">5.6451473236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71626758575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73404741287231</t>
   </si>
   <si>
     <t xml:space="preserve">5.81405782699585</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67181730270386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51179695129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85850811004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66292762756348</t>
+    <t xml:space="preserve">5.67181777954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5117974281311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85850715637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66292715072632</t>
   </si>
   <si>
     <t xml:space="preserve">5.53846740722656</t>
@@ -1469,13 +1469,13 @@
     <t xml:space="preserve">5.90295743942261</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79627799987793</t>
+    <t xml:space="preserve">5.79627704620361</t>
   </si>
   <si>
     <t xml:space="preserve">5.80516815185547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6184778213501</t>
+    <t xml:space="preserve">5.61847829818726</t>
   </si>
   <si>
     <t xml:space="preserve">5.46734762191772</t>
@@ -1496,16 +1496,16 @@
     <t xml:space="preserve">5.62736749649048</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52957773208618</t>
+    <t xml:space="preserve">5.52957820892334</t>
   </si>
   <si>
     <t xml:space="preserve">5.42289781570435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72515773773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70737791061401</t>
+    <t xml:space="preserve">5.72515821456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70737743377686</t>
   </si>
   <si>
     <t xml:space="preserve">5.69848728179932</t>
@@ -1517,34 +1517,34 @@
     <t xml:space="preserve">5.92962789535522</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94740724563599</t>
+    <t xml:space="preserve">5.94740772247314</t>
   </si>
   <si>
     <t xml:space="preserve">5.93851757049561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99185657501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24077701568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40968751907349</t>
+    <t xml:space="preserve">5.99185705184937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24077749252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40968799591064</t>
   </si>
   <si>
     <t xml:space="preserve">6.48080778121948</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62304735183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84529733657837</t>
+    <t xml:space="preserve">6.623046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84529685974121</t>
   </si>
   <si>
     <t xml:space="preserve">6.99642705917358</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01420736312866</t>
+    <t xml:space="preserve">7.0142068862915</t>
   </si>
   <si>
     <t xml:space="preserve">6.90752696990967</t>
@@ -1559,19 +1559,19 @@
     <t xml:space="preserve">7.00531721115112</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02309703826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24534702301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27201747894287</t>
+    <t xml:space="preserve">7.0230975151062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2453465461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27201700210571</t>
   </si>
   <si>
     <t xml:space="preserve">7.33424711227417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.476487159729</t>
+    <t xml:space="preserve">7.47648572921753</t>
   </si>
   <si>
     <t xml:space="preserve">7.76985740661621</t>
@@ -1580,43 +1580,43 @@
     <t xml:space="preserve">7.7342963218689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7254056930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79652643203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80541658401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22324562072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21435642242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15212726593018</t>
+    <t xml:space="preserve">7.72540616989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7965259552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80541515350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22324752807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21435546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15212631225586</t>
   </si>
   <si>
     <t xml:space="preserve">8.12545680999756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00099658966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17879581451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3477087020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42771625518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48105525970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46327781677246</t>
+    <t xml:space="preserve">8.00099563598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17879772186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34770584106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4277172088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48105621337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46327686309814</t>
   </si>
   <si>
     <t xml:space="preserve">8.52550601959229</t>
@@ -1625,13 +1625,13 @@
     <t xml:space="preserve">8.50772666931152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66774654388428</t>
+    <t xml:space="preserve">8.66774559020996</t>
   </si>
   <si>
     <t xml:space="preserve">8.80109596252441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88999557495117</t>
+    <t xml:space="preserve">8.88999652862549</t>
   </si>
   <si>
     <t xml:space="preserve">9.19225597381592</t>
@@ -1640,13 +1640,13 @@
     <t xml:space="preserve">9.37005615234375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47673511505127</t>
+    <t xml:space="preserve">9.4767370223999</t>
   </si>
   <si>
     <t xml:space="preserve">9.49451637268066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31671619415283</t>
+    <t xml:space="preserve">9.31671524047852</t>
   </si>
   <si>
     <t xml:space="preserve">9.15669631958008</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">9.35227680206299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40561676025391</t>
+    <t xml:space="preserve">9.40561580657959</t>
   </si>
   <si>
     <t xml:space="preserve">9.69009590148926</t>
@@ -1664,19 +1664,19 @@
     <t xml:space="preserve">9.86789608001709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83233642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77899551391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44117546081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21003532409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58341503143311</t>
+    <t xml:space="preserve">9.83233547210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77899742126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44117641448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.210036277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58341598510742</t>
   </si>
   <si>
     <t xml:space="preserve">9.51229572296143</t>
@@ -1685,16 +1685,16 @@
     <t xml:space="preserve">9.67231559753418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85011577606201</t>
+    <t xml:space="preserve">9.85011672973633</t>
   </si>
   <si>
     <t xml:space="preserve">10.0990362167358</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0279150009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99235534667969</t>
+    <t xml:space="preserve">10.0279159545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.992356300354</t>
   </si>
   <si>
     <t xml:space="preserve">10.0101366043091</t>
@@ -1703,88 +1703,88 @@
     <t xml:space="preserve">9.76121520996094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88567543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2234973907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4368553161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6679944992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.414755821228</t>
+    <t xml:space="preserve">9.88567638397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2234954833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4368562698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6679954528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4147548675537</t>
   </si>
   <si>
     <t xml:space="preserve">11.3614149093628</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3080749511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4325342178345</t>
+    <t xml:space="preserve">11.3080768585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4325351715088</t>
   </si>
   <si>
     <t xml:space="preserve">11.6814556121826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.894814491272</t>
+    <t xml:space="preserve">11.8948154449463</t>
   </si>
   <si>
     <t xml:space="preserve">11.965934753418</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1437358856201</t>
+    <t xml:space="preserve">12.1437349319458</t>
   </si>
   <si>
     <t xml:space="preserve">11.6281156539917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4001150131226</t>
+    <t xml:space="preserve">11.4001140594482</t>
   </si>
   <si>
     <t xml:space="preserve">11.6715440750122</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6534490585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6896390914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1239290237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7982130050659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1782159805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.322979927063</t>
+    <t xml:space="preserve">11.653450012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.689640045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.123929977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7982110977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1782169342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3229789733887</t>
   </si>
   <si>
     <t xml:space="preserve">12.9925088882446</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8296518325806</t>
+    <t xml:space="preserve">12.8296508789062</t>
   </si>
   <si>
     <t xml:space="preserve">12.7391738891602</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7753648757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.395359992981</t>
+    <t xml:space="preserve">12.7753658294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3953619003296</t>
   </si>
   <si>
     <t xml:space="preserve">12.2867879867554</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6306009292603</t>
+    <t xml:space="preserve">12.6306028366089</t>
   </si>
   <si>
     <t xml:space="preserve">12.4496469497681</t>
@@ -1796,34 +1796,34 @@
     <t xml:space="preserve">12.1058349609375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8705940246582</t>
+    <t xml:space="preserve">11.8705930709839</t>
   </si>
   <si>
     <t xml:space="preserve">11.9067850112915</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4724950790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4182081222534</t>
+    <t xml:space="preserve">11.4724941253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4182090759277</t>
   </si>
   <si>
     <t xml:space="preserve">11.5810680389404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8524980545044</t>
+    <t xml:space="preserve">11.852499961853</t>
   </si>
   <si>
     <t xml:space="preserve">12.0877389907837</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8344030380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8886890411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4363040924072</t>
+    <t xml:space="preserve">11.8344039916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.888689994812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4363050460815</t>
   </si>
   <si>
     <t xml:space="preserve">11.3277311325073</t>
@@ -1832,10 +1832,10 @@
     <t xml:space="preserve">11.2734451293945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1829690933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1648721694946</t>
+    <t xml:space="preserve">11.1829681396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1648731231689</t>
   </si>
   <si>
     <t xml:space="preserve">10.8391551971436</t>
@@ -1847,46 +1847,46 @@
     <t xml:space="preserve">10.6762962341309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5134372711182</t>
+    <t xml:space="preserve">10.5134382247925</t>
   </si>
   <si>
     <t xml:space="preserve">10.9115371704102</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2915410995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1467781066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.766773223877</t>
+    <t xml:space="preserve">11.291540145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1467761993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7667741775513</t>
   </si>
   <si>
     <t xml:space="preserve">11.1105861663818</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1286821365356</t>
+    <t xml:space="preserve">11.1286811828613</t>
   </si>
   <si>
     <t xml:space="preserve">10.6220102310181</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0020132064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6039152145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.495343208313</t>
+    <t xml:space="preserve">11.0020141601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6039142608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4953422546387</t>
   </si>
   <si>
     <t xml:space="preserve">10.2781972885132</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3143873214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89819145202637</t>
+    <t xml:space="preserve">10.3143882751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.898193359375</t>
   </si>
   <si>
     <t xml:space="preserve">9.93438339233398</t>
@@ -1895,16 +1895,16 @@
     <t xml:space="preserve">9.80771636962891</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6810474395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95247936248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2420063018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4772472381592</t>
+    <t xml:space="preserve">9.68104839324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95248031616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2420053482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4772462844849</t>
   </si>
   <si>
     <t xml:space="preserve">10.3867683410645</t>
@@ -1916,28 +1916,28 @@
     <t xml:space="preserve">9.55438041687012</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1153383255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3505783081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4048662185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7486782073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0201082229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8572492599487</t>
+    <t xml:space="preserve">10.1153392791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3505792617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4048643112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7486791610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0201101303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.857250213623</t>
   </si>
   <si>
     <t xml:space="preserve">10.8753461837769</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5858192443848</t>
+    <t xml:space="preserve">10.5858201980591</t>
   </si>
   <si>
     <t xml:space="preserve">10.8029632568359</t>
@@ -1958,10 +1958,10 @@
     <t xml:space="preserve">11.4543991088867</t>
   </si>
   <si>
-    <t xml:space="preserve">11.725830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9972620010376</t>
+    <t xml:space="preserve">11.7258310317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9972610473633</t>
   </si>
   <si>
     <t xml:space="preserve">12.160120010376</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">10.9477281570435</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9658222198486</t>
+    <t xml:space="preserve">10.9658231735229</t>
   </si>
   <si>
     <t xml:space="preserve">10.1877212524414</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">10.0429573059082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91629028320312</t>
+    <t xml:space="preserve">9.91628837585449</t>
   </si>
   <si>
     <t xml:space="preserve">10.1696243286133</t>
@@ -2003,10 +2003,10 @@
     <t xml:space="preserve">10.531533241272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4229602813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1334342956543</t>
+    <t xml:space="preserve">10.4229612350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.13343334198</t>
   </si>
   <si>
     <t xml:space="preserve">10.332483291626</t>
@@ -2018,31 +2018,31 @@
     <t xml:space="preserve">10.097243309021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0610513687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0791492462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1515293121338</t>
+    <t xml:space="preserve">10.0610523223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0791482925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1515283584595</t>
   </si>
   <si>
     <t xml:space="preserve">11.056300163269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.893440246582</t>
+    <t xml:space="preserve">10.8934412002563</t>
   </si>
   <si>
     <t xml:space="preserve">10.5496282577515</t>
   </si>
   <si>
-    <t xml:space="preserve">10.368673324585</t>
+    <t xml:space="preserve">10.3686742782593</t>
   </si>
   <si>
     <t xml:space="preserve">9.8258113861084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77152633666992</t>
+    <t xml:space="preserve">9.77152538299561</t>
   </si>
   <si>
     <t xml:space="preserve">9.699143409729</t>
@@ -2060,28 +2060,28 @@
     <t xml:space="preserve">9.59057140350342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3639230728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9791660308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4677429199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3772649765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3820161819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5629711151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6172590255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0924921035767</t>
+    <t xml:space="preserve">11.3639221191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9791669845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4677419662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3772668838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3820171356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5629720687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6172580718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0924911499023</t>
   </si>
   <si>
     <t xml:space="preserve">10.6943912506104</t>
@@ -2090,37 +2090,37 @@
     <t xml:space="preserve">9.62676334381104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80342102050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68579959869385</t>
+    <t xml:space="preserve">8.8034200668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68580055236816</t>
   </si>
   <si>
     <t xml:space="preserve">8.43246459960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04816579818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32864427566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24721527099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18388032913208</t>
+    <t xml:space="preserve">7.0481653213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32864475250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24721479415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18388080596924</t>
   </si>
   <si>
     <t xml:space="preserve">6.58673238754272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65006589889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96673583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9757833480835</t>
+    <t xml:space="preserve">6.65006637573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96673536300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97578382492065</t>
   </si>
   <si>
     <t xml:space="preserve">7.16578531265259</t>
@@ -2132,19 +2132,19 @@
     <t xml:space="preserve">7.28340625762939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60912322998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76293468475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34198760986328</t>
+    <t xml:space="preserve">7.60912179946899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76293420791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34198665618896</t>
   </si>
   <si>
     <t xml:space="preserve">8.04341316223145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61341953277588</t>
+    <t xml:space="preserve">8.61341857910156</t>
   </si>
   <si>
     <t xml:space="preserve">8.41436958312988</t>
@@ -2162,13 +2162,13 @@
     <t xml:space="preserve">9.04770851135254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26485443115234</t>
+    <t xml:space="preserve">9.26485252380371</t>
   </si>
   <si>
     <t xml:space="preserve">9.50009346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86200141906738</t>
+    <t xml:space="preserve">9.8620023727417</t>
   </si>
   <si>
     <t xml:space="preserve">11.2191581726074</t>
@@ -2177,13 +2177,13 @@
     <t xml:space="preserve">10.9839191436768</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6582012176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97057628631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2058143615723</t>
+    <t xml:space="preserve">10.6582002639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9705753326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2058153152466</t>
   </si>
   <si>
     <t xml:space="preserve">9.84390735626221</t>
@@ -2192,7 +2192,7 @@
     <t xml:space="preserve">10.4591512680054</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9296321868896</t>
+    <t xml:space="preserve">10.9296312332153</t>
   </si>
   <si>
     <t xml:space="preserve">10.7305822372437</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">12.558219909668</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8477449417114</t>
+    <t xml:space="preserve">12.8477468490601</t>
   </si>
   <si>
     <t xml:space="preserve">13.1915597915649</t>
@@ -2219,28 +2219,28 @@
     <t xml:space="preserve">12.7934608459473</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4315519332886</t>
+    <t xml:space="preserve">12.4315509796143</t>
   </si>
   <si>
     <t xml:space="preserve">12.594409942627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6486959457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7210788726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8658418655396</t>
+    <t xml:space="preserve">12.6486968994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7210779190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8658428192139</t>
   </si>
   <si>
     <t xml:space="preserve">13.1553678512573</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0286998748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1191778182983</t>
+    <t xml:space="preserve">13.0287008285522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.119176864624</t>
   </si>
   <si>
     <t xml:space="preserve">12.9382238388062</t>
@@ -2252,46 +2252,46 @@
     <t xml:space="preserve">13.3725128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3544187545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4534854888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2496852874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2858772277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3763523101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6477832794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8334913253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0687294006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8696804046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9239692687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9058713912964</t>
+    <t xml:space="preserve">13.3544178009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4534883499146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.249683380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2858734130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3763542175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6477851867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8334903717041</t>
+